--- a/data/descargas/cargos_recurrentes.xlsx
+++ b/data/descargas/cargos_recurrentes.xlsx
@@ -601,7 +601,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reporte generado: 01-01-2026 07:13 a. m. </t>
+          <t xml:space="preserve">Reporte generado: 01-01-2026 07:37 a. m. </t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>

--- a/data/descargas/cargos_recurrentes.xlsx
+++ b/data/descargas/cargos_recurrentes.xlsx
@@ -601,7 +601,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reporte generado: 01-01-2026 07:37 a. m. </t>
+          <t>Reporte generado: 01-01-2026 03:24 p. m.</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>

--- a/data/descargas/cargos_recurrentes.xlsx
+++ b/data/descargas/cargos_recurrentes.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q3"/>
+  <dimension ref="A1:Q14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -599,27 +599,762 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Reporte generado: 01-01-2026 03:24 p. m.</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="n">
+        <v>84502</v>
+      </c>
+      <c r="C3" t="n">
+        <v>290990</v>
+      </c>
+      <c r="D3" t="n">
+        <v>88488</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>CLAUDIA ANTONIETA SALGADO MENDOZA</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>MISION ENSENADA</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>22-12-2025 7:48:13</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>02-02-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>499</v>
+      </c>
+      <c r="M3" t="n">
+        <v>11</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>17-12-2026 7:48:13</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P3" t="n">
+        <v>65133</v>
+      </c>
       <c r="Q3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="n">
+        <v>83298</v>
+      </c>
+      <c r="C4" t="n">
+        <v>249279</v>
+      </c>
+      <c r="D4" t="n">
+        <v>46783</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>REY SAID CASAS RAMOS</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>PAPALOTE TIJUANA</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>02-12-2025 17:39:24</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>02-02-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>399</v>
+      </c>
+      <c r="M4" t="n">
+        <v>5</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>31-05-2026 17:39:24</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
+        <v>37993</v>
+      </c>
+      <c r="Q4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="n">
+        <v>84880</v>
+      </c>
+      <c r="C5" t="n">
+        <v>127402</v>
+      </c>
+      <c r="D5" t="n">
+        <v>25075</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>NUBIA PATRICIA  RUIZ  BENCOMO</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>SENDERO CHIHUAHUA</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>29-12-2025 11:57:22</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>02-02-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>399</v>
+      </c>
+      <c r="M5" t="n">
+        <v>11</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>24-12-2026 11:57:22</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
+        <v>71334</v>
+      </c>
+      <c r="Q5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="n">
+        <v>83325</v>
+      </c>
+      <c r="C6" t="n">
+        <v>21709</v>
+      </c>
+      <c r="D6" t="n">
+        <v>20609</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>MIGUEL FRANCISCO ROJO GARCIA</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>SENDERO CULIACAN</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>03-12-2025 6:36:50</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>02-02-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>399</v>
+      </c>
+      <c r="M6" t="n">
+        <v>11</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>28-11-2026 6:36:50</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>2380</v>
+      </c>
+      <c r="Q6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" t="n">
+        <v>83410</v>
+      </c>
+      <c r="C7" t="n">
+        <v>172707</v>
+      </c>
+      <c r="D7" t="n">
+        <v>70226</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>LUIS ANGEL  FLORES MARTINEZ</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>PASEO LA PAZ</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>04-12-2025 5:25:36</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>02-02-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>399</v>
+      </c>
+      <c r="M7" t="n">
+        <v>11</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>29-11-2026 5:25:36</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>8022</v>
+      </c>
+      <c r="Q7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" t="n">
+        <v>83440</v>
+      </c>
+      <c r="C8" t="n">
+        <v>190835</v>
+      </c>
+      <c r="D8" t="n">
+        <v>88342</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>PERLA CORAL LUCERO  AGUILAR</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>PASEO LA PAZ</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>04-12-2025 17:40:44</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>02-02-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>499</v>
+      </c>
+      <c r="M8" t="n">
+        <v>11</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>29-11-2026 17:40:44</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P8" t="n">
+        <v>68138</v>
+      </c>
+      <c r="Q8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" t="n">
+        <v>84806</v>
+      </c>
+      <c r="C9" t="n">
+        <v>326368</v>
+      </c>
+      <c r="D9" t="n">
+        <v>23307</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>PEDRO MIGUEL  QUINTERO CUEVAS</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>CARROUSEL TIJUANA</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>28-12-2025 10:09:30</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>02-02-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>399</v>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
+        <v>83261</v>
+      </c>
+      <c r="Q9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" t="n">
+        <v>83302</v>
+      </c>
+      <c r="C10" t="n">
+        <v>326491</v>
+      </c>
+      <c r="D10" t="n">
+        <v>23430</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>ANA CECILIA  RENTERIA  HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>SENDERO CULIACAN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>02-12-2025 18:13:37</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>02-02-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>549</v>
+      </c>
+      <c r="M10" t="n">
+        <v>2</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>02-03-2026 18:13:37</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>83301</v>
+      </c>
+      <c r="Q10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" t="n">
+        <v>83154</v>
+      </c>
+      <c r="C11" t="n">
+        <v>319772</v>
+      </c>
+      <c r="D11" t="n">
+        <v>17269</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>ADRIAN ALEJANDRO ESCUTIA MUÑIZ</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>INSURGENTES</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>01-12-2025 12:03:42</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>28-01-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>599</v>
+      </c>
+      <c r="M11" t="n">
+        <v>11</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>26-11-2026 12:03:42</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>80928</v>
+      </c>
+      <c r="Q11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" t="n">
+        <v>84640</v>
+      </c>
+      <c r="C12" t="n">
+        <v>326127</v>
+      </c>
+      <c r="D12" t="n">
+        <v>23066</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>ISABEL ESPINOZA  VALENZUELA</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>MISION ENSENADA</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>23-12-2025 16:48:33</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>01-02-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>499</v>
+      </c>
+      <c r="M12" t="n">
+        <v>11</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>18-12-2026 16:48:33</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>83140</v>
+      </c>
+      <c r="Q12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" t="n">
+        <v>85072</v>
+      </c>
+      <c r="C13" t="n">
+        <v>18849</v>
+      </c>
+      <c r="D13" t="n">
+        <v>17752</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>REYNA GABRIELA CASTAÑEDA  PACHECO</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>TEC MEXICALI</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>30-12-2025 12:26:35</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>02-02-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>399</v>
+      </c>
+      <c r="M13" t="n">
+        <v>11</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>25-12-2026 12:26:35</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>71103</v>
+      </c>
+      <c r="Q13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Reporte generado: 02-01-2026 03:24 p. m.</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/descargas/cargos_recurrentes.xlsx
+++ b/data/descargas/cargos_recurrentes.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q14"/>
+  <dimension ref="A1:Q87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -603,27 +603,27 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>84502</v>
+        <v>83302</v>
       </c>
       <c r="C3" t="n">
-        <v>290990</v>
+        <v>326491</v>
       </c>
       <c r="D3" t="n">
-        <v>88488</v>
+        <v>23430</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>CLAUDIA ANTONIETA SALGADO MENDOZA</t>
+          <t>ANA CECILIA  RENTERIA  HERNANDEZ</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>MISION ENSENADA</t>
+          <t>SENDERO CULIACAN</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>22-12-2025 7:48:13</t>
+          <t>02-12-2025 18:13:37</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -645,14 +645,14 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>499</v>
+        <v>549</v>
       </c>
       <c r="M3" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>17-12-2026 7:48:13</t>
+          <t>02-03-2026 18:13:37</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -661,7 +661,7 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>65133</v>
+        <v>83301</v>
       </c>
       <c r="Q3" t="inlineStr"/>
     </row>
@@ -670,27 +670,27 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>83298</v>
+        <v>84806</v>
       </c>
       <c r="C4" t="n">
-        <v>249279</v>
+        <v>326368</v>
       </c>
       <c r="D4" t="n">
-        <v>46783</v>
+        <v>23307</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>REY SAID CASAS RAMOS</t>
+          <t>PEDRO MIGUEL  QUINTERO CUEVAS</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>PAPALOTE TIJUANA</t>
+          <t>CARROUSEL TIJUANA</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>02-12-2025 17:39:24</t>
+          <t>28-12-2025 10:09:30</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -714,21 +714,19 @@
       <c r="L4" t="n">
         <v>399</v>
       </c>
-      <c r="M4" t="n">
-        <v>5</v>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>31-05-2026 17:39:24</t>
-        </is>
-      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Domiciliado</t>
+          <t>Recurrente</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>37993</v>
+        <v>83261</v>
       </c>
       <c r="Q4" t="inlineStr"/>
     </row>
@@ -737,27 +735,27 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>84880</v>
+        <v>85342</v>
       </c>
       <c r="C5" t="n">
-        <v>127402</v>
+        <v>331486</v>
       </c>
       <c r="D5" t="n">
-        <v>25075</v>
+        <v>16540</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>NUBIA PATRICIA  RUIZ  BENCOMO</t>
+          <t>LETICIA DE LEON OLGUIN</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>SENDERO CHIHUAHUA</t>
+          <t>TEC MEXICALI</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>29-12-2025 11:57:22</t>
+          <t>02-01-2026 10:56:44</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -775,18 +773,18 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>RENOVACIÓN</t>
+          <t>NUEVO</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>399</v>
+        <v>549</v>
       </c>
       <c r="M5" t="n">
         <v>11</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>24-12-2026 11:57:22</t>
+          <t>28-12-2026 10:56:44</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -794,9 +792,7 @@
           <t>Domiciliado</t>
         </is>
       </c>
-      <c r="P5" t="n">
-        <v>71334</v>
-      </c>
+      <c r="P5" t="inlineStr"/>
       <c r="Q5" t="inlineStr"/>
     </row>
     <row r="6">
@@ -804,32 +800,32 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>83325</v>
+        <v>85355</v>
       </c>
       <c r="C6" t="n">
-        <v>21709</v>
+        <v>271763</v>
       </c>
       <c r="D6" t="n">
-        <v>20609</v>
+        <v>69265</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>MIGUEL FRANCISCO ROJO GARCIA</t>
+          <t>EDGAR ALARCON BARRIOS</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>SENDERO CULIACAN</t>
+          <t>AZAHARES CULIACAN</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>03-12-2025 6:36:50</t>
+          <t>02-01-2026 11:34:18</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>02-02-2026 23:59:59</t>
+          <t>06-02-2026 23:59:59</t>
         </is>
       </c>
       <c r="I6" t="n">
@@ -846,23 +842,21 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>399</v>
-      </c>
-      <c r="M6" t="n">
-        <v>11</v>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>28-11-2026 6:36:50</t>
-        </is>
-      </c>
+        <v>599</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Domiciliado</t>
+          <t>Recurrente</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>2380</v>
+        <v>52241</v>
       </c>
       <c r="Q6" t="inlineStr"/>
     </row>
@@ -871,27 +865,27 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>83410</v>
+        <v>85356</v>
       </c>
       <c r="C7" t="n">
-        <v>172707</v>
+        <v>38424</v>
       </c>
       <c r="D7" t="n">
-        <v>70226</v>
+        <v>36301</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>LUIS ANGEL  FLORES MARTINEZ</t>
+          <t>BRYAN  SOQUI VERDUZCO</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>PASEO LA PAZ</t>
+          <t>MISION ENSENADA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>04-12-2025 5:25:36</t>
+          <t>02-01-2026 11:34:33</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -909,28 +903,24 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>RENOVACIÓN</t>
+          <t>NUEVO</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>399</v>
-      </c>
-      <c r="M7" t="n">
-        <v>11</v>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>29-11-2026 5:25:36</t>
-        </is>
-      </c>
+        <v>649</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Domiciliado</t>
-        </is>
-      </c>
-      <c r="P7" t="n">
-        <v>8022</v>
-      </c>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr"/>
       <c r="Q7" t="inlineStr"/>
     </row>
     <row r="8">
@@ -938,27 +928,27 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>83440</v>
+        <v>85373</v>
       </c>
       <c r="C8" t="n">
-        <v>190835</v>
+        <v>331533</v>
       </c>
       <c r="D8" t="n">
-        <v>88342</v>
+        <v>16587</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>PERLA CORAL LUCERO  AGUILAR</t>
+          <t>JORGE JESUS  SERNA  CORREA</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>PASEO LA PAZ</t>
+          <t>METEPEC</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>04-12-2025 17:40:44</t>
+          <t>02-01-2026 13:12:58</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -976,18 +966,18 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>RENOVACIÓN</t>
+          <t>NUEVO</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>499</v>
+        <v>649</v>
       </c>
       <c r="M8" t="n">
         <v>11</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>29-11-2026 17:40:44</t>
+          <t>28-12-2026 13:12:58</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -995,9 +985,7 @@
           <t>Domiciliado</t>
         </is>
       </c>
-      <c r="P8" t="n">
-        <v>68138</v>
-      </c>
+      <c r="P8" t="inlineStr"/>
       <c r="Q8" t="inlineStr"/>
     </row>
     <row r="9">
@@ -1005,27 +993,27 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>84806</v>
+        <v>85374</v>
       </c>
       <c r="C9" t="n">
-        <v>326368</v>
+        <v>232207</v>
       </c>
       <c r="D9" t="n">
-        <v>23307</v>
+        <v>29712</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>PEDRO MIGUEL  QUINTERO CUEVAS</t>
+          <t>KRISTEL LORENA MAYORQUIN  ORDOÑEZ</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CARROUSEL TIJUANA</t>
+          <t>SENDERO CULIACAN</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>28-12-2025 10:09:30</t>
+          <t>02-01-2026 13:19:02</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1043,11 +1031,11 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>RENOVACIÓN</t>
+          <t>NUEVO</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>399</v>
+        <v>649</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -1060,9 +1048,7 @@
           <t>Recurrente</t>
         </is>
       </c>
-      <c r="P9" t="n">
-        <v>83261</v>
-      </c>
+      <c r="P9" t="inlineStr"/>
       <c r="Q9" t="inlineStr"/>
     </row>
     <row r="10">
@@ -1070,27 +1056,27 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>83302</v>
+        <v>85391</v>
       </c>
       <c r="C10" t="n">
-        <v>326491</v>
+        <v>75444</v>
       </c>
       <c r="D10" t="n">
-        <v>23430</v>
+        <v>73258</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>ANA CECILIA  RENTERIA  HERNANDEZ</t>
+          <t>DAYANNA  LOPEZ CASTELO</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>SENDERO CULIACAN</t>
+          <t>AZAHARES CULIACAN</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>02-12-2025 18:13:37</t>
+          <t>02-01-2026 14:20:50</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1112,14 +1098,14 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>549</v>
+        <v>749</v>
       </c>
       <c r="M10" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>02-03-2026 18:13:37</t>
+          <t>28-12-2026 14:20:50</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1128,7 +1114,7 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>83301</v>
+        <v>37414</v>
       </c>
       <c r="Q10" t="inlineStr"/>
     </row>
@@ -1137,17 +1123,17 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>83154</v>
+        <v>85392</v>
       </c>
       <c r="C11" t="n">
-        <v>319772</v>
+        <v>331553</v>
       </c>
       <c r="D11" t="n">
-        <v>17269</v>
+        <v>16607</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>ADRIAN ALEJANDRO ESCUTIA MUÑIZ</t>
+          <t>KENIA LISETH RODRIGUEZ  ROMERO</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1157,12 +1143,12 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>01-12-2025 12:03:42</t>
+          <t>02-01-2026 14:22:50</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>28-01-2026 23:59:59</t>
+          <t>02-02-2026 23:59:59</t>
         </is>
       </c>
       <c r="I11" t="n">
@@ -1175,18 +1161,18 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>RENOVACIÓN</t>
+          <t>NUEVO</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>599</v>
+        <v>649</v>
       </c>
       <c r="M11" t="n">
         <v>11</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>26-11-2026 12:03:42</t>
+          <t>28-12-2026 14:22:50</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1194,9 +1180,7 @@
           <t>Domiciliado</t>
         </is>
       </c>
-      <c r="P11" t="n">
-        <v>80928</v>
-      </c>
+      <c r="P11" t="inlineStr"/>
       <c r="Q11" t="inlineStr"/>
     </row>
     <row r="12">
@@ -1204,32 +1188,32 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>84640</v>
+        <v>85405</v>
       </c>
       <c r="C12" t="n">
-        <v>326127</v>
+        <v>331581</v>
       </c>
       <c r="D12" t="n">
-        <v>23066</v>
+        <v>16635</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ISABEL ESPINOZA  VALENZUELA</t>
+          <t>KARINA  GARCIA GOMEZ</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>MISION ENSENADA</t>
+          <t>SALTILLO VILLALTA</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>23-12-2025 16:48:33</t>
+          <t>02-01-2026 15:41:24</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>01-02-2026 23:59:59</t>
+          <t>02-02-2026 23:59:59</t>
         </is>
       </c>
       <c r="I12" t="n">
@@ -1242,18 +1226,18 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>RENOVACIÓN</t>
+          <t>NUEVO</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>499</v>
+        <v>649</v>
       </c>
       <c r="M12" t="n">
         <v>11</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>18-12-2026 16:48:33</t>
+          <t>28-12-2026 15:41:24</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1261,9 +1245,7 @@
           <t>Domiciliado</t>
         </is>
       </c>
-      <c r="P12" t="n">
-        <v>83140</v>
-      </c>
+      <c r="P12" t="inlineStr"/>
       <c r="Q12" t="inlineStr"/>
     </row>
     <row r="13">
@@ -1271,90 +1253,4851 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
+        <v>85406</v>
+      </c>
+      <c r="C13" t="n">
+        <v>331586</v>
+      </c>
+      <c r="D13" t="n">
+        <v>16640</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>LUIS JAVIER MARTINEZ CELIS</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>CARROUSEL TIJUANA</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>02-01-2026 15:49:07</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>02-02-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>649</v>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" t="n">
+        <v>85409</v>
+      </c>
+      <c r="C14" t="n">
+        <v>180662</v>
+      </c>
+      <c r="D14" t="n">
+        <v>78169</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>MARIA AZUCENA ANASTASIO ROMUALDO</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>CARROUSEL TIJUANA</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>02-01-2026 16:00:08</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>02-02-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
+        <v>749</v>
+      </c>
+      <c r="M14" t="n">
+        <v>11</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>28-12-2026 16:00:08</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>45199</v>
+      </c>
+      <c r="Q14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" t="n">
+        <v>85183</v>
+      </c>
+      <c r="C15" t="n">
+        <v>241364</v>
+      </c>
+      <c r="D15" t="n">
+        <v>38869</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>JESUS RUBEN FERNANDEZ NUÑEZ</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>TEC MEXICALI</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>30-12-2025 18:27:28</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>01-02-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Activado</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>CANCELADO</t>
+        </is>
+      </c>
+      <c r="L15" t="n">
+        <v>499</v>
+      </c>
+      <c r="M15" t="n">
+        <v>11</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>25-12-2026 18:27:28</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>83190</v>
+      </c>
+      <c r="Q15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" t="n">
+        <v>85349</v>
+      </c>
+      <c r="C16" t="n">
+        <v>331493</v>
+      </c>
+      <c r="D16" t="n">
+        <v>16547</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>BENJAMIN  GOMEZ  PONCE</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>TLALNEPANTLA</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>02-01-2026 11:13:00</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>02-02-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L16" t="n">
+        <v>549</v>
+      </c>
+      <c r="M16" t="n">
+        <v>11</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>28-12-2026 11:13:00</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" t="n">
+        <v>85364</v>
+      </c>
+      <c r="C17" t="n">
+        <v>217170</v>
+      </c>
+      <c r="D17" t="n">
+        <v>14678</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>GABRIELA GUERRERO ORANTES</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>SENDERO MEXICALI</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>02-01-2026 12:16:54</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>02-02-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L17" t="n">
+        <v>749</v>
+      </c>
+      <c r="M17" t="n">
+        <v>11</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>28-12-2026 12:16:54</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>15273</v>
+      </c>
+      <c r="Q17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" t="n">
+        <v>85366</v>
+      </c>
+      <c r="C18" t="n">
+        <v>319301</v>
+      </c>
+      <c r="D18" t="n">
+        <v>16798</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>IRVING OMAR LANDA ALONSO</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>PAPALOTE TIJUANA</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>02-01-2026 12:26:52</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>02-02-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L18" t="n">
+        <v>649</v>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" t="n">
+        <v>85381</v>
+      </c>
+      <c r="C19" t="n">
+        <v>242032</v>
+      </c>
+      <c r="D19" t="n">
+        <v>39537</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>JOSE ALEJANDRO GARCIA VELAZQUEZ</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>PAPALOTE TIJUANA</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>02-01-2026 13:42:51</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>02-02-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L19" t="n">
+        <v>749</v>
+      </c>
+      <c r="M19" t="n">
+        <v>11</v>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>28-12-2026 13:42:51</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
+        <v>31243</v>
+      </c>
+      <c r="Q19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" t="n">
+        <v>85398</v>
+      </c>
+      <c r="C20" t="n">
+        <v>331574</v>
+      </c>
+      <c r="D20" t="n">
+        <v>16628</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>ALONSO  GARCIA  RAMOS</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>INSURGENTES</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>02-01-2026 15:19:01</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>02-02-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L20" t="n">
+        <v>649</v>
+      </c>
+      <c r="M20" t="n">
+        <v>11</v>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>28-12-2026 15:19:01</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" t="n">
+        <v>85415</v>
+      </c>
+      <c r="C21" t="n">
+        <v>331592</v>
+      </c>
+      <c r="D21" t="n">
+        <v>16646</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>EMILIOALONSO BARCENAS REYES</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>INSURGENTES</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>02-01-2026 16:30:03</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>02-02-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L21" t="n">
+        <v>649</v>
+      </c>
+      <c r="M21" t="n">
+        <v>11</v>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>28-12-2026 16:30:03</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" t="n">
+        <v>85417</v>
+      </c>
+      <c r="C22" t="n">
+        <v>331598</v>
+      </c>
+      <c r="D22" t="n">
+        <v>16652</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>ISLAS BERENICE DIAZ  BARRIGA</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>TLALNEPANTLA</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>02-01-2026 16:41:33</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>02-02-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L22" t="n">
+        <v>549</v>
+      </c>
+      <c r="M22" t="n">
+        <v>11</v>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>28-12-2026 16:41:33</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" t="n">
+        <v>85430</v>
+      </c>
+      <c r="C23" t="n">
+        <v>283380</v>
+      </c>
+      <c r="D23" t="n">
+        <v>80881</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>BRIANDA LIZETH TAMAYO URQUIDEZ</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>VILLA VERDE MEXICALI</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>02-01-2026 18:52:42</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>02-02-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L23" t="n">
+        <v>549</v>
+      </c>
+      <c r="M23" t="n">
+        <v>11</v>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>28-12-2026 18:52:42</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>22</v>
+      </c>
+      <c r="B24" t="n">
+        <v>85434</v>
+      </c>
+      <c r="C24" t="n">
+        <v>331655</v>
+      </c>
+      <c r="D24" t="n">
+        <v>16709</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>JOSE ISRAEL  VARGAS  VALDEZ</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>SENDERO CULIACAN</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>02-01-2026 19:47:46</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>02-02-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L24" t="n">
+        <v>649</v>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>23</v>
+      </c>
+      <c r="B25" t="n">
+        <v>83287</v>
+      </c>
+      <c r="C25" t="n">
+        <v>234869</v>
+      </c>
+      <c r="D25" t="n">
+        <v>32374</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>NARCEDALIA URIARTE ROCHA</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>SENDERO CULIACAN</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>02-12-2025 16:52:24</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>20-01-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L25" t="n">
+        <v>499</v>
+      </c>
+      <c r="M25" t="n">
+        <v>11</v>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>27-11-2026 16:52:24</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P25" t="n">
+        <v>80346</v>
+      </c>
+      <c r="Q25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>24</v>
+      </c>
+      <c r="B26" t="n">
+        <v>83298</v>
+      </c>
+      <c r="C26" t="n">
+        <v>249279</v>
+      </c>
+      <c r="D26" t="n">
+        <v>46783</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>REY SAID CASAS RAMOS</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>PAPALOTE TIJUANA</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>02-12-2025 17:39:24</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>02-02-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L26" t="n">
+        <v>399</v>
+      </c>
+      <c r="M26" t="n">
+        <v>5</v>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>31-05-2026 17:39:24</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P26" t="n">
+        <v>37993</v>
+      </c>
+      <c r="Q26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>25</v>
+      </c>
+      <c r="B27" t="n">
+        <v>84502</v>
+      </c>
+      <c r="C27" t="n">
+        <v>290990</v>
+      </c>
+      <c r="D27" t="n">
+        <v>88488</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>CLAUDIA ANTONIETA SALGADO MENDOZA</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>MISION ENSENADA</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>22-12-2025 7:48:13</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>02-02-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L27" t="n">
+        <v>499</v>
+      </c>
+      <c r="M27" t="n">
+        <v>11</v>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>17-12-2026 7:48:13</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P27" t="n">
+        <v>65133</v>
+      </c>
+      <c r="Q27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>26</v>
+      </c>
+      <c r="B28" t="n">
+        <v>85352</v>
+      </c>
+      <c r="C28" t="n">
+        <v>331501</v>
+      </c>
+      <c r="D28" t="n">
+        <v>16555</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>MARIA MAGDALENA PALACIOS GAONA</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>SALTILLO VILLALTA</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>02-01-2026 11:30:38</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>02-02-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L28" t="n">
+        <v>649</v>
+      </c>
+      <c r="M28" t="n">
+        <v>11</v>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>28-12-2026 11:30:38</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>27</v>
+      </c>
+      <c r="B29" t="n">
+        <v>85384</v>
+      </c>
+      <c r="C29" t="n">
+        <v>331545</v>
+      </c>
+      <c r="D29" t="n">
+        <v>16599</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>FRANCISCO KEVIN PLANCARTE GARCIA</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>INSURGENTES</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>02-01-2026 13:55:56</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L29" t="n">
+        <v>1549</v>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>28</v>
+      </c>
+      <c r="B30" t="n">
+        <v>85395</v>
+      </c>
+      <c r="C30" t="n">
+        <v>331566</v>
+      </c>
+      <c r="D30" t="n">
+        <v>16620</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>HIRAM MORA VARGAS</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>INSURGENTES</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>02-01-2026 15:04:56</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L30" t="n">
+        <v>1549</v>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>29</v>
+      </c>
+      <c r="B31" t="n">
+        <v>85402</v>
+      </c>
+      <c r="C31" t="n">
+        <v>331576</v>
+      </c>
+      <c r="D31" t="n">
+        <v>16630</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>LUIS RODRIGO TORRES SANCHEZ</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>SALTILLO VILLALTA</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>02-01-2026 15:27:25</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>02-02-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L31" t="n">
+        <v>649</v>
+      </c>
+      <c r="M31" t="n">
+        <v>11</v>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>28-12-2026 15:27:25</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>30</v>
+      </c>
+      <c r="B32" t="n">
+        <v>85420</v>
+      </c>
+      <c r="C32" t="n">
+        <v>30767</v>
+      </c>
+      <c r="D32" t="n">
+        <v>28697</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>BERENICE ALFARO ESPINOSA</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>LOMA BONITA</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>02-01-2026 17:02:21</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>02-02-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L32" t="n">
+        <v>399</v>
+      </c>
+      <c r="M32" t="n">
+        <v>11</v>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>28-12-2026 17:02:21</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P32" t="n">
+        <v>28737</v>
+      </c>
+      <c r="Q32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>31</v>
+      </c>
+      <c r="B33" t="n">
+        <v>83154</v>
+      </c>
+      <c r="C33" t="n">
+        <v>319772</v>
+      </c>
+      <c r="D33" t="n">
+        <v>17269</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>ADRIAN ALEJANDRO ESCUTIA MUÑIZ</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>INSURGENTES</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>01-12-2025 12:03:42</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>28-01-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L33" t="n">
+        <v>599</v>
+      </c>
+      <c r="M33" t="n">
+        <v>11</v>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>26-11-2026 12:03:42</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P33" t="n">
+        <v>80928</v>
+      </c>
+      <c r="Q33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>32</v>
+      </c>
+      <c r="B34" t="n">
+        <v>85351</v>
+      </c>
+      <c r="C34" t="n">
+        <v>331489</v>
+      </c>
+      <c r="D34" t="n">
+        <v>16543</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>ADRIANA VELASCO  RAMIREZ</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>TLALNEPANTLA</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>02-01-2026 11:23:45</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>02-02-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L34" t="n">
+        <v>549</v>
+      </c>
+      <c r="M34" t="n">
+        <v>11</v>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>28-12-2026 11:23:45</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>33</v>
+      </c>
+      <c r="B35" t="n">
+        <v>85353</v>
+      </c>
+      <c r="C35" t="n">
+        <v>331504</v>
+      </c>
+      <c r="D35" t="n">
+        <v>16558</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>ANGEL  DURAN  VIZUET</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>TLALNEPANTLA</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>02-01-2026 11:33:22</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>02-02-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I35" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L35" t="n">
+        <v>549</v>
+      </c>
+      <c r="M35" t="n">
+        <v>11</v>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>28-12-2026 11:33:22</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>34</v>
+      </c>
+      <c r="B36" t="n">
+        <v>85362</v>
+      </c>
+      <c r="C36" t="n">
+        <v>114321</v>
+      </c>
+      <c r="D36" t="n">
+        <v>12050</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>NELLY SOFIA  GONZALEZ  OLIVARES</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>SANTA CATARINA</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>02-01-2026 12:02:44</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>02-02-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L36" t="n">
+        <v>549</v>
+      </c>
+      <c r="M36" t="n">
+        <v>11</v>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>28-12-2026 12:02:44</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>35</v>
+      </c>
+      <c r="B37" t="n">
+        <v>85387</v>
+      </c>
+      <c r="C37" t="n">
+        <v>331550</v>
+      </c>
+      <c r="D37" t="n">
+        <v>16604</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>ADRIAN ANTONIO CORDERO CALDERON</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>SENDERO CHIHUAHUA</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>02-01-2026 14:09:47</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>02-02-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L37" t="n">
+        <v>549</v>
+      </c>
+      <c r="M37" t="n">
+        <v>11</v>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>28-12-2026 14:09:47</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>36</v>
+      </c>
+      <c r="B38" t="n">
+        <v>85419</v>
+      </c>
+      <c r="C38" t="n">
+        <v>331608</v>
+      </c>
+      <c r="D38" t="n">
+        <v>16662</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>MARIA ANTONIETA  GERARDO PEREZ DE ALBA</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>SENDERO MEXICALI</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>02-01-2026 16:56:39</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>02-02-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I38" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L38" t="n">
+        <v>549</v>
+      </c>
+      <c r="M38" t="n">
+        <v>11</v>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>28-12-2026 16:56:39</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr"/>
+      <c r="Q38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>37</v>
+      </c>
+      <c r="B39" t="n">
+        <v>85421</v>
+      </c>
+      <c r="C39" t="n">
+        <v>96568</v>
+      </c>
+      <c r="D39" t="n">
+        <v>94327</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>CARLOS HERNANDEZ YEPIZ</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>SENDERO MEXICALI</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>02-01-2026 17:09:17</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>02-02-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I39" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L39" t="n">
+        <v>549</v>
+      </c>
+      <c r="M39" t="n">
+        <v>11</v>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>28-12-2026 17:09:17</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>38</v>
+      </c>
+      <c r="B40" t="n">
+        <v>85428</v>
+      </c>
+      <c r="C40" t="n">
+        <v>331623</v>
+      </c>
+      <c r="D40" t="n">
+        <v>16677</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>DANIEL  SALINAS  HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>TLALNEPANTLA</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>02-01-2026 17:58:49</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>02-02-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I40" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L40" t="n">
+        <v>549</v>
+      </c>
+      <c r="M40" t="n">
+        <v>11</v>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>28-12-2026 17:58:49</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr"/>
+      <c r="Q40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>39</v>
+      </c>
+      <c r="B41" t="n">
+        <v>83440</v>
+      </c>
+      <c r="C41" t="n">
+        <v>190835</v>
+      </c>
+      <c r="D41" t="n">
+        <v>88342</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>PERLA CORAL LUCERO  AGUILAR</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>PASEO LA PAZ</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>04-12-2025 17:40:44</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>02-02-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I41" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L41" t="n">
+        <v>499</v>
+      </c>
+      <c r="M41" t="n">
+        <v>11</v>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>29-11-2026 17:40:44</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P41" t="n">
+        <v>68138</v>
+      </c>
+      <c r="Q41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>40</v>
+      </c>
+      <c r="B42" t="n">
+        <v>85346</v>
+      </c>
+      <c r="C42" t="n">
+        <v>207168</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>04676</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>HERIBERTO JAVIER RAMIREZ LOZA</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>VILLAS DEL REY</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>02-01-2026 11:10:52</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>02-02-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I42" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L42" t="n">
+        <v>549</v>
+      </c>
+      <c r="M42" t="n">
+        <v>11</v>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>28-12-2026 11:10:52</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr"/>
+      <c r="Q42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>41</v>
+      </c>
+      <c r="B43" t="n">
+        <v>85369</v>
+      </c>
+      <c r="C43" t="n">
+        <v>34556</v>
+      </c>
+      <c r="D43" t="n">
+        <v>32470</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>ALAN STEPHEN VEGA CHACON</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>SENDERO MEXICALI</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>02-01-2026 12:29:38</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>02-02-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L43" t="n">
+        <v>649</v>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr"/>
+      <c r="Q43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>42</v>
+      </c>
+      <c r="B44" t="n">
+        <v>85376</v>
+      </c>
+      <c r="C44" t="n">
+        <v>331536</v>
+      </c>
+      <c r="D44" t="n">
+        <v>16590</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>GABRIELA OLIVERA MAYEN</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>TLALNEPANTLA</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>02-01-2026 13:21:19</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>02-02-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I44" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L44" t="n">
+        <v>549</v>
+      </c>
+      <c r="M44" t="n">
+        <v>11</v>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>28-12-2026 13:21:19</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr"/>
+      <c r="Q44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>43</v>
+      </c>
+      <c r="B45" t="n">
+        <v>85401</v>
+      </c>
+      <c r="C45" t="n">
+        <v>227928</v>
+      </c>
+      <c r="D45" t="n">
+        <v>25433</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>YOSSIRY MONSERRAT  REYES  MENDOZA</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>IXTAPALUCA</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>02-01-2026 15:26:49</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>02-02-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I45" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L45" t="n">
+        <v>549</v>
+      </c>
+      <c r="M45" t="n">
+        <v>11</v>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>28-12-2026 15:26:49</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr"/>
+      <c r="Q45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>44</v>
+      </c>
+      <c r="B46" t="n">
+        <v>85403</v>
+      </c>
+      <c r="C46" t="n">
+        <v>331580</v>
+      </c>
+      <c r="D46" t="n">
+        <v>16634</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>IRVIN ROBERTO RUBIO CASTELLANOS</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>PASEO 2000</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>02-01-2026 15:32:38</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>02-02-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I46" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L46" t="n">
+        <v>549</v>
+      </c>
+      <c r="M46" t="n">
+        <v>11</v>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>28-12-2026 15:32:38</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr"/>
+      <c r="Q46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>45</v>
+      </c>
+      <c r="B47" t="n">
+        <v>85410</v>
+      </c>
+      <c r="C47" t="n">
+        <v>331587</v>
+      </c>
+      <c r="D47" t="n">
+        <v>16641</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>JANARA ELIZABETH SAENZ GARCIA</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>VILLAS DEL REY</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>02-01-2026 16:05:09</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>02-02-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I47" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L47" t="n">
+        <v>549</v>
+      </c>
+      <c r="M47" t="n">
+        <v>11</v>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>28-12-2026 16:05:09</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr"/>
+      <c r="Q47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>46</v>
+      </c>
+      <c r="B48" t="n">
+        <v>85435</v>
+      </c>
+      <c r="C48" t="n">
+        <v>331665</v>
+      </c>
+      <c r="D48" t="n">
+        <v>16719</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>JOAQUIN GLORIA CASILLAS</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>CARROUSEL TIJUANA</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>02-01-2026 20:32:36</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>02-02-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L48" t="n">
+        <v>649</v>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr"/>
+      <c r="Q48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>47</v>
+      </c>
+      <c r="B49" t="n">
+        <v>85343</v>
+      </c>
+      <c r="C49" t="n">
+        <v>237668</v>
+      </c>
+      <c r="D49" t="n">
+        <v>35173</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>AARON RUIZ  MARTINEZ</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>SAN LUIS</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>02-01-2026 10:58:21</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>02-02-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I49" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L49" t="n">
+        <v>549</v>
+      </c>
+      <c r="M49" t="n">
+        <v>11</v>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>28-12-2026 10:58:21</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr"/>
+      <c r="Q49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>48</v>
+      </c>
+      <c r="B50" t="n">
+        <v>85354</v>
+      </c>
+      <c r="C50" t="n">
+        <v>331482</v>
+      </c>
+      <c r="D50" t="n">
+        <v>16536</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>DORA ARACELI DIAZ  VILLARREAL</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>SALTILLO VILLALTA</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>02-01-2026 11:34:09</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>02-02-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L50" t="n">
+        <v>649</v>
+      </c>
+      <c r="M50" t="n">
+        <v>11</v>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>28-12-2026 11:34:09</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr"/>
+      <c r="Q50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>49</v>
+      </c>
+      <c r="B51" t="n">
+        <v>85361</v>
+      </c>
+      <c r="C51" t="n">
+        <v>147484</v>
+      </c>
+      <c r="D51" t="n">
+        <v>45060</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>STEPHANYA PEREZ FERNANDEZ</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>PASEO LA PAZ</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>02-01-2026 11:58:21</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I51" t="n">
+        <v>0</v>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L51" t="n">
+        <v>1449</v>
+      </c>
+      <c r="M51" t="n">
+        <v>9</v>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>28-12-2026 11:58:21</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr"/>
+      <c r="Q51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>50</v>
+      </c>
+      <c r="B52" t="n">
+        <v>85368</v>
+      </c>
+      <c r="C52" t="n">
+        <v>331520</v>
+      </c>
+      <c r="D52" t="n">
+        <v>16574</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>KARLA EDITH TOVAR ROSALES</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>SALTILLO VILLALTA</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>02-01-2026 12:28:57</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>02-02-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I52" t="n">
+        <v>0</v>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L52" t="n">
+        <v>649</v>
+      </c>
+      <c r="M52" t="n">
+        <v>11</v>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>28-12-2026 12:28:57</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr"/>
+      <c r="Q52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>51</v>
+      </c>
+      <c r="B53" t="n">
+        <v>85379</v>
+      </c>
+      <c r="C53" t="n">
+        <v>331543</v>
+      </c>
+      <c r="D53" t="n">
+        <v>16597</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>JESUS  LUNA ORTIZ</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>INSURGENTES</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>02-01-2026 13:33:07</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I53" t="n">
+        <v>0</v>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L53" t="n">
+        <v>1549</v>
+      </c>
+      <c r="M53" t="n">
+        <v>9</v>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>28-12-2026 13:33:07</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr"/>
+      <c r="Q53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>52</v>
+      </c>
+      <c r="B54" t="n">
+        <v>85386</v>
+      </c>
+      <c r="C54" t="n">
+        <v>331546</v>
+      </c>
+      <c r="D54" t="n">
+        <v>16600</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>ITZETL QUIROZ SANTANA</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>METEPEC</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>02-01-2026 14:03:16</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>02-02-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I54" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L54" t="n">
+        <v>649</v>
+      </c>
+      <c r="M54" t="n">
+        <v>11</v>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>28-12-2026 14:03:16</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr"/>
+      <c r="Q54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>53</v>
+      </c>
+      <c r="B55" t="n">
+        <v>85393</v>
+      </c>
+      <c r="C55" t="n">
+        <v>200198</v>
+      </c>
+      <c r="D55" t="n">
+        <v>97705</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>MARCO ANTONIO GONZALEZ  HERRERA</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>SENDERO CHIHUAHUA</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>02-01-2026 14:34:57</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>02-02-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I55" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L55" t="n">
+        <v>549</v>
+      </c>
+      <c r="M55" t="n">
+        <v>11</v>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>28-12-2026 14:34:57</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr"/>
+      <c r="Q55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>54</v>
+      </c>
+      <c r="B56" t="n">
+        <v>85404</v>
+      </c>
+      <c r="C56" t="n">
+        <v>7025</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>05960</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>LUIS ANDRES  FRAUSTO HERRERA</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>VILLA VERDE MEXICALI</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>02-01-2026 15:36:10</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I56" t="n">
+        <v>0</v>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L56" t="n">
+        <v>1449</v>
+      </c>
+      <c r="M56" t="n">
+        <v>9</v>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>28-12-2026 15:36:10</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr"/>
+      <c r="Q56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>55</v>
+      </c>
+      <c r="B57" t="n">
+        <v>85418</v>
+      </c>
+      <c r="C57" t="n">
+        <v>331600</v>
+      </c>
+      <c r="D57" t="n">
+        <v>16654</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>ALEJANDRA RUIZ JAIME</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>INSURGENTES</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>02-01-2026 16:45:31</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I57" t="n">
+        <v>0</v>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L57" t="n">
+        <v>1549</v>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr"/>
+      <c r="Q57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>56</v>
+      </c>
+      <c r="B58" t="n">
+        <v>85429</v>
+      </c>
+      <c r="C58" t="n">
+        <v>331631</v>
+      </c>
+      <c r="D58" t="n">
+        <v>16685</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>AZAET RIVERA BOLAÑOS</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>PASEO 2000</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>02-01-2026 18:05:40</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>02-02-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I58" t="n">
+        <v>0</v>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L58" t="n">
+        <v>549</v>
+      </c>
+      <c r="M58" t="n">
+        <v>11</v>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>28-12-2026 18:05:40</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr"/>
+      <c r="Q58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>57</v>
+      </c>
+      <c r="B59" t="n">
+        <v>85436</v>
+      </c>
+      <c r="C59" t="n">
+        <v>287987</v>
+      </c>
+      <c r="D59" t="n">
+        <v>85485</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>JOSUE ALFONZO PEREZ CASTILLON</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>VILLAS DEL REY</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>02-01-2026 20:56:57</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>02-02-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I59" t="n">
+        <v>0</v>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L59" t="n">
+        <v>749</v>
+      </c>
+      <c r="M59" t="n">
+        <v>11</v>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>28-12-2026 20:56:57</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P59" t="n">
+        <v>63526</v>
+      </c>
+      <c r="Q59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>58</v>
+      </c>
+      <c r="B60" t="n">
+        <v>83325</v>
+      </c>
+      <c r="C60" t="n">
+        <v>21709</v>
+      </c>
+      <c r="D60" t="n">
+        <v>20609</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>MIGUEL FRANCISCO ROJO GARCIA</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>SENDERO CULIACAN</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>03-12-2025 6:36:50</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>02-02-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I60" t="n">
+        <v>0</v>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L60" t="n">
+        <v>399</v>
+      </c>
+      <c r="M60" t="n">
+        <v>11</v>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>28-11-2026 6:36:50</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P60" t="n">
+        <v>2380</v>
+      </c>
+      <c r="Q60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>59</v>
+      </c>
+      <c r="B61" t="n">
+        <v>83410</v>
+      </c>
+      <c r="C61" t="n">
+        <v>172707</v>
+      </c>
+      <c r="D61" t="n">
+        <v>70226</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>LUIS ANGEL  FLORES MARTINEZ</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>PASEO LA PAZ</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>04-12-2025 5:25:36</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>02-02-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I61" t="n">
+        <v>0</v>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L61" t="n">
+        <v>399</v>
+      </c>
+      <c r="M61" t="n">
+        <v>11</v>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>29-11-2026 5:25:36</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P61" t="n">
+        <v>8022</v>
+      </c>
+      <c r="Q61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>60</v>
+      </c>
+      <c r="B62" t="n">
+        <v>84880</v>
+      </c>
+      <c r="C62" t="n">
+        <v>127402</v>
+      </c>
+      <c r="D62" t="n">
+        <v>25075</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>NUBIA PATRICIA  RUIZ  BENCOMO</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>SENDERO CHIHUAHUA</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>29-12-2025 11:57:22</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>02-02-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I62" t="n">
+        <v>0</v>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L62" t="n">
+        <v>399</v>
+      </c>
+      <c r="M62" t="n">
+        <v>11</v>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>24-12-2026 11:57:22</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P62" t="n">
+        <v>71334</v>
+      </c>
+      <c r="Q62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>61</v>
+      </c>
+      <c r="B63" t="n">
+        <v>85348</v>
+      </c>
+      <c r="C63" t="n">
+        <v>331494</v>
+      </c>
+      <c r="D63" t="n">
+        <v>16548</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>SAMUEL FUENTES HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>METEPEC</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>02-01-2026 11:12:24</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>02-02-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I63" t="n">
+        <v>0</v>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L63" t="n">
+        <v>649</v>
+      </c>
+      <c r="M63" t="n">
+        <v>11</v>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>28-12-2026 11:12:24</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr"/>
+      <c r="Q63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>62</v>
+      </c>
+      <c r="B64" t="n">
+        <v>85350</v>
+      </c>
+      <c r="C64" t="n">
+        <v>331491</v>
+      </c>
+      <c r="D64" t="n">
+        <v>16545</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>ELIAS  GOMEZ  PONCE</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>TLALNEPANTLA</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>02-01-2026 11:18:18</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>02-02-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I64" t="n">
+        <v>0</v>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L64" t="n">
+        <v>549</v>
+      </c>
+      <c r="M64" t="n">
+        <v>11</v>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>28-12-2026 11:18:18</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr"/>
+      <c r="Q64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>63</v>
+      </c>
+      <c r="B65" t="n">
+        <v>85365</v>
+      </c>
+      <c r="C65" t="n">
+        <v>329705</v>
+      </c>
+      <c r="D65" t="n">
+        <v>14759</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>ESMERALDA MARTINEZ MEZA</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>PASEO LA PAZ</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>02-01-2026 12:23:37</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I65" t="n">
+        <v>0</v>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L65" t="n">
+        <v>1449</v>
+      </c>
+      <c r="M65" t="n">
+        <v>9</v>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>28-12-2026 12:23:37</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr"/>
+      <c r="Q65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>64</v>
+      </c>
+      <c r="B66" t="n">
+        <v>85367</v>
+      </c>
+      <c r="C66" t="n">
+        <v>329706</v>
+      </c>
+      <c r="D66" t="n">
+        <v>14760</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>MANUEL EZEQUIEL RAMIREZ BUSTOS</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>PASEO LA PAZ</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>02-01-2026 12:27:10</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>02-02-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I66" t="n">
+        <v>0</v>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L66" t="n">
+        <v>649</v>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr"/>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr"/>
+      <c r="Q66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>65</v>
+      </c>
+      <c r="B67" t="n">
+        <v>85380</v>
+      </c>
+      <c r="C67" t="n">
+        <v>249607</v>
+      </c>
+      <c r="D67" t="n">
+        <v>47111</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>ALEXIS FLORES GONZALEZ</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>PASEO LA PAZ</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>02-01-2026 13:40:00</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>02-02-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I67" t="n">
+        <v>0</v>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L67" t="n">
+        <v>749</v>
+      </c>
+      <c r="M67" t="n">
+        <v>11</v>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>28-12-2026 13:40:00</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P67" t="n">
+        <v>53883</v>
+      </c>
+      <c r="Q67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>66</v>
+      </c>
+      <c r="B68" t="n">
+        <v>85397</v>
+      </c>
+      <c r="C68" t="n">
+        <v>331571</v>
+      </c>
+      <c r="D68" t="n">
+        <v>16625</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>DIANA BERENICE  BAZAN  GARRIDO</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>INSURGENTES</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>02-01-2026 15:13:00</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I68" t="n">
+        <v>0</v>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L68" t="n">
+        <v>1549</v>
+      </c>
+      <c r="M68" t="n">
+        <v>9</v>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>28-12-2026 15:13:00</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr"/>
+      <c r="Q68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>67</v>
+      </c>
+      <c r="B69" t="n">
+        <v>85399</v>
+      </c>
+      <c r="C69" t="n">
+        <v>331578</v>
+      </c>
+      <c r="D69" t="n">
+        <v>16632</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>ALEX RICARDO PINTO URIBE</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>PASEO 2000</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>02-01-2026 15:21:15</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>02-02-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I69" t="n">
+        <v>0</v>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L69" t="n">
+        <v>549</v>
+      </c>
+      <c r="M69" t="n">
+        <v>11</v>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>28-12-2026 15:21:15</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr"/>
+      <c r="Q69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>68</v>
+      </c>
+      <c r="B70" t="n">
+        <v>85416</v>
+      </c>
+      <c r="C70" t="n">
+        <v>331597</v>
+      </c>
+      <c r="D70" t="n">
+        <v>16651</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>KARLA FABIOLA  GONZALEZ ALMEIDA</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>PASEO 2000</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>02-01-2026 16:36:43</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I70" t="n">
+        <v>0</v>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L70" t="n">
+        <v>1449</v>
+      </c>
+      <c r="M70" t="n">
+        <v>9</v>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>28-12-2026 16:36:43</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr"/>
+      <c r="Q70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>69</v>
+      </c>
+      <c r="B71" t="n">
+        <v>85433</v>
+      </c>
+      <c r="C71" t="n">
+        <v>331652</v>
+      </c>
+      <c r="D71" t="n">
+        <v>16706</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>LIZETH CECILIA  SANDOVAL  YAMASHIRO</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>SENDERO CULIACAN</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>02-01-2026 19:44:46</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>02-02-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I71" t="n">
+        <v>0</v>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L71" t="n">
+        <v>649</v>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr"/>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr"/>
+      <c r="Q71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>70</v>
+      </c>
+      <c r="B72" t="n">
+        <v>84640</v>
+      </c>
+      <c r="C72" t="n">
+        <v>326127</v>
+      </c>
+      <c r="D72" t="n">
+        <v>23066</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>ISABEL ESPINOZA  VALENZUELA</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>MISION ENSENADA</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>23-12-2025 16:48:33</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>01-02-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I72" t="n">
+        <v>0</v>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L72" t="n">
+        <v>499</v>
+      </c>
+      <c r="M72" t="n">
+        <v>11</v>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>18-12-2026 16:48:33</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P72" t="n">
+        <v>83140</v>
+      </c>
+      <c r="Q72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>71</v>
+      </c>
+      <c r="B73" t="n">
+        <v>83568</v>
+      </c>
+      <c r="C73" t="n">
+        <v>138456</v>
+      </c>
+      <c r="D73" t="n">
+        <v>36094</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>BRAYAN GAEL BALDERAS CONTRERAS</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>SENDERO SALTILLO</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>08-12-2025 7:50:26</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>02-02-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I73" t="n">
+        <v>0</v>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L73" t="n">
+        <v>549</v>
+      </c>
+      <c r="M73" t="n">
+        <v>5</v>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>06-06-2026 7:50:26</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P73" t="n">
+        <v>70999</v>
+      </c>
+      <c r="Q73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>72</v>
+      </c>
+      <c r="B74" t="n">
         <v>85072</v>
       </c>
-      <c r="C13" t="n">
+      <c r="C74" t="n">
         <v>18849</v>
       </c>
-      <c r="D13" t="n">
+      <c r="D74" t="n">
         <v>17752</v>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E74" t="inlineStr">
         <is>
           <t>REYNA GABRIELA CASTAÑEDA  PACHECO</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F74" t="inlineStr">
         <is>
           <t>TEC MEXICALI</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G74" t="inlineStr">
         <is>
           <t>30-12-2025 12:26:35</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>02-02-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>Sin filtro</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>02-02-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I74" t="n">
+        <v>0</v>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
         <is>
           <t>RENOVACIÓN</t>
         </is>
       </c>
-      <c r="L13" t="n">
+      <c r="L74" t="n">
         <v>399</v>
       </c>
-      <c r="M13" t="n">
+      <c r="M74" t="n">
         <v>11</v>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="N74" t="inlineStr">
         <is>
           <t>25-12-2026 12:26:35</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>Domiciliado</t>
-        </is>
-      </c>
-      <c r="P13" t="n">
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P74" t="n">
         <v>71103</v>
       </c>
-      <c r="Q13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Reporte generado: 02-01-2026 03:24 p. m.</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr"/>
+      <c r="Q74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>73</v>
+      </c>
+      <c r="B75" t="n">
+        <v>85357</v>
+      </c>
+      <c r="C75" t="n">
+        <v>331506</v>
+      </c>
+      <c r="D75" t="n">
+        <v>16560</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>OMAR ANTONIO  HERNANDEZ HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>TLALNEPANTLA</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>02-01-2026 11:40:03</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>02-02-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>0</v>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L75" t="n">
+        <v>549</v>
+      </c>
+      <c r="M75" t="n">
+        <v>11</v>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>28-12-2026 11:40:03</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr"/>
+      <c r="Q75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>74</v>
+      </c>
+      <c r="B76" t="n">
+        <v>85358</v>
+      </c>
+      <c r="C76" t="n">
+        <v>331497</v>
+      </c>
+      <c r="D76" t="n">
+        <v>16551</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>AMERICA YANDELLI PALACIOS GAONA</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>SALTILLO VILLALTA</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>02-01-2026 11:42:53</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>02-02-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I76" t="n">
+        <v>0</v>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L76" t="n">
+        <v>649</v>
+      </c>
+      <c r="M76" t="n">
+        <v>11</v>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>28-12-2026 11:42:53</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr"/>
+      <c r="Q76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>75</v>
+      </c>
+      <c r="B77" t="n">
+        <v>85372</v>
+      </c>
+      <c r="C77" t="n">
+        <v>331528</v>
+      </c>
+      <c r="D77" t="n">
+        <v>16582</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>EDGAR MANUEL GONZALEZ RUBIO GARCIA</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>PASEO LA PAZ</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>02-01-2026 12:58:52</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>02-02-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I77" t="n">
+        <v>0</v>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L77" t="n">
+        <v>549</v>
+      </c>
+      <c r="M77" t="n">
+        <v>11</v>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>28-12-2026 12:58:52</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr"/>
+      <c r="Q77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>76</v>
+      </c>
+      <c r="B78" t="n">
+        <v>85375</v>
+      </c>
+      <c r="C78" t="n">
+        <v>331524</v>
+      </c>
+      <c r="D78" t="n">
+        <v>16578</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>MAYRA GUADALUPE PARRA  RIVERA</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>SENDERO SALTILLO</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>02-01-2026 13:19:59</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>02-02-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I78" t="n">
+        <v>0</v>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L78" t="n">
+        <v>549</v>
+      </c>
+      <c r="M78" t="n">
+        <v>11</v>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>28-12-2026 13:19:59</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr"/>
+      <c r="Q78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>77</v>
+      </c>
+      <c r="B79" t="n">
+        <v>85389</v>
+      </c>
+      <c r="C79" t="n">
+        <v>331555</v>
+      </c>
+      <c r="D79" t="n">
+        <v>16609</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>RICARDO  URIAS  QUINTERO</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>SENDERO CULIACAN</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>02-01-2026 14:20:20</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>02-02-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I79" t="n">
+        <v>0</v>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L79" t="n">
+        <v>649</v>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr"/>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr"/>
+      <c r="Q79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>78</v>
+      </c>
+      <c r="B80" t="n">
+        <v>85390</v>
+      </c>
+      <c r="C80" t="n">
+        <v>329954</v>
+      </c>
+      <c r="D80" t="n">
+        <v>15008</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>VIRIDIANA  GONZALEZ PULIDO</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>PASEO 2000</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>02-01-2026 14:20:33</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>02-02-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I80" t="n">
+        <v>0</v>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L80" t="n">
+        <v>549</v>
+      </c>
+      <c r="M80" t="n">
+        <v>11</v>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>28-12-2026 14:20:33</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr"/>
+      <c r="Q80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>79</v>
+      </c>
+      <c r="B81" t="n">
+        <v>85407</v>
+      </c>
+      <c r="C81" t="n">
+        <v>331583</v>
+      </c>
+      <c r="D81" t="n">
+        <v>16637</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>RENATA GONZALEZ GOMEZ</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>SALTILLO VILLALTA</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>02-01-2026 15:51:20</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>02-02-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I81" t="n">
+        <v>0</v>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L81" t="n">
+        <v>649</v>
+      </c>
+      <c r="M81" t="n">
+        <v>11</v>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>28-12-2026 15:51:20</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr"/>
+      <c r="Q81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>80</v>
+      </c>
+      <c r="B82" t="n">
+        <v>85408</v>
+      </c>
+      <c r="C82" t="n">
+        <v>331588</v>
+      </c>
+      <c r="D82" t="n">
+        <v>16642</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>ROMINA SOSA SOLIS</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>SALTILLO VILLALTA</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>02-01-2026 15:58:45</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>02-02-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I82" t="n">
+        <v>0</v>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L82" t="n">
+        <v>649</v>
+      </c>
+      <c r="M82" t="n">
+        <v>11</v>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>28-12-2026 15:58:45</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr"/>
+      <c r="Q82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>81</v>
+      </c>
+      <c r="B83" t="n">
+        <v>85422</v>
+      </c>
+      <c r="C83" t="n">
+        <v>323721</v>
+      </c>
+      <c r="D83" t="n">
+        <v>20660</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>JAVIER HERNÁNDEZ CHÁVEZ</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>INSURGENTES</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>02-01-2026 17:09:25</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>02-02-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I83" t="n">
+        <v>0</v>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L83" t="n">
+        <v>649</v>
+      </c>
+      <c r="M83" t="n">
+        <v>11</v>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>28-12-2026 17:09:25</t>
+        </is>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr"/>
+      <c r="Q83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>82</v>
+      </c>
+      <c r="B84" t="n">
+        <v>85425</v>
+      </c>
+      <c r="C84" t="n">
+        <v>234864</v>
+      </c>
+      <c r="D84" t="n">
+        <v>32369</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>SARAH  MORENO URIARTE</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>SENDERO CULIACAN</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>02-01-2026 17:35:16</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>02-02-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I84" t="n">
+        <v>0</v>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L84" t="n">
+        <v>549</v>
+      </c>
+      <c r="M84" t="n">
+        <v>11</v>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>28-12-2026 17:35:16</t>
+        </is>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr"/>
+      <c r="Q84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>83</v>
+      </c>
+      <c r="B85" t="n">
+        <v>85439</v>
+      </c>
+      <c r="C85" t="n">
+        <v>331457</v>
+      </c>
+      <c r="D85" t="n">
+        <v>16511</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>CESAR BELLO LAGUNEZ</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>PASEO 2000</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>03-01-2026 6:29:18</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>03-02-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I85" t="n">
+        <v>0</v>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L85" t="n">
+        <v>549</v>
+      </c>
+      <c r="M85" t="n">
+        <v>11</v>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>29-12-2026 6:29:18</t>
+        </is>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P85" t="inlineStr"/>
+      <c r="Q85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>84</v>
+      </c>
+      <c r="B86" t="n">
+        <v>85440</v>
+      </c>
+      <c r="C86" t="n">
+        <v>331680</v>
+      </c>
+      <c r="D86" t="n">
+        <v>16734</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>GUADALUPE MARGARITA MENDOZA  HUERTA</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>PASEO LA PAZ</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>03-01-2026 7:10:20</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>03-02-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I86" t="n">
+        <v>0</v>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L86" t="n">
+        <v>549</v>
+      </c>
+      <c r="M86" t="n">
+        <v>11</v>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>29-12-2026 7:10:20</t>
+        </is>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P86" t="inlineStr"/>
+      <c r="Q86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Reporte generado: 03-01-2026 03:23 p. m.</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr"/>
+      <c r="C87" t="inlineStr"/>
+      <c r="D87" t="inlineStr"/>
+      <c r="E87" t="inlineStr"/>
+      <c r="F87" t="inlineStr"/>
+      <c r="G87" t="inlineStr"/>
+      <c r="H87" t="inlineStr"/>
+      <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr"/>
+      <c r="N87" t="inlineStr"/>
+      <c r="O87" t="inlineStr"/>
+      <c r="P87" t="inlineStr"/>
+      <c r="Q87" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/descargas/cargos_recurrentes.xlsx
+++ b/data/descargas/cargos_recurrentes.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q87"/>
+  <dimension ref="A1:Q149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -603,32 +603,32 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>83302</v>
+        <v>83406</v>
       </c>
       <c r="C3" t="n">
-        <v>326491</v>
+        <v>281541</v>
       </c>
       <c r="D3" t="n">
-        <v>23430</v>
+        <v>79042</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>ANA CECILIA  RENTERIA  HERNANDEZ</t>
+          <t>SILVIA ANGELICA  ARMENTA  MARQUEZ</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>SENDERO CULIACAN</t>
+          <t>SANTA FE</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>02-12-2025 18:13:37</t>
+          <t>03-12-2025 20:54:59</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>02-02-2026 23:59:59</t>
+          <t>03-02-2026 23:59:59</t>
         </is>
       </c>
       <c r="I3" t="n">
@@ -648,11 +648,11 @@
         <v>549</v>
       </c>
       <c r="M3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>02-03-2026 18:13:37</t>
+          <t>01-06-2026 20:54:59</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -661,7 +661,7 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>83301</v>
+        <v>59341</v>
       </c>
       <c r="Q3" t="inlineStr"/>
     </row>
@@ -670,27 +670,27 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>84806</v>
+        <v>83440</v>
       </c>
       <c r="C4" t="n">
-        <v>326368</v>
+        <v>190835</v>
       </c>
       <c r="D4" t="n">
-        <v>23307</v>
+        <v>88342</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>PEDRO MIGUEL  QUINTERO CUEVAS</t>
+          <t>PERLA CORAL LUCERO  AGUILAR</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>CARROUSEL TIJUANA</t>
+          <t>PASEO LA PAZ</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>28-12-2025 10:09:30</t>
+          <t>04-12-2025 17:40:44</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -712,21 +712,23 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>399</v>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>Indefinido</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
+        <v>499</v>
+      </c>
+      <c r="M4" t="n">
+        <v>11</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>29-11-2026 17:40:44</t>
+        </is>
+      </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Recurrente</t>
+          <t>Domiciliado</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>83261</v>
+        <v>68138</v>
       </c>
       <c r="Q4" t="inlineStr"/>
     </row>
@@ -735,17 +737,19 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85342</v>
+        <v>85069</v>
       </c>
       <c r="C5" t="n">
-        <v>331486</v>
-      </c>
-      <c r="D5" t="n">
-        <v>16540</v>
+        <v>204602</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>02110</t>
+        </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>LETICIA DE LEON OLGUIN</t>
+          <t>ABRAHAM BRAVO TORRES</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -755,12 +759,12 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>02-01-2026 10:56:44</t>
+          <t>30-12-2025 12:24:45</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>02-02-2026 23:59:59</t>
+          <t>03-02-2026 23:59:59</t>
         </is>
       </c>
       <c r="I5" t="n">
@@ -773,18 +777,18 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>NUEVO</t>
+          <t>RENOVACIÓN</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>549</v>
+        <v>399</v>
       </c>
       <c r="M5" t="n">
         <v>11</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>28-12-2026 10:56:44</t>
+          <t>25-12-2026 12:24:45</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -792,7 +796,9 @@
           <t>Domiciliado</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr"/>
+      <c r="P5" t="n">
+        <v>71171</v>
+      </c>
       <c r="Q5" t="inlineStr"/>
     </row>
     <row r="6">
@@ -800,32 +806,34 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>85355</v>
+        <v>85346</v>
       </c>
       <c r="C6" t="n">
-        <v>271763</v>
-      </c>
-      <c r="D6" t="n">
-        <v>69265</v>
+        <v>207168</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>04676</t>
+        </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>EDGAR ALARCON BARRIOS</t>
+          <t>HERIBERTO JAVIER RAMIREZ LOZA</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>AZAHARES CULIACAN</t>
+          <t>VILLAS DEL REY</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>02-01-2026 11:34:18</t>
+          <t>02-01-2026 11:10:52</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>06-02-2026 23:59:59</t>
+          <t>02-02-2026 23:59:59</t>
         </is>
       </c>
       <c r="I6" t="n">
@@ -838,26 +846,26 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>RENOVACIÓN</t>
+          <t>NUEVO</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>599</v>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>Indefinido</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
+        <v>549</v>
+      </c>
+      <c r="M6" t="n">
+        <v>11</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>28-12-2026 11:10:52</t>
+        </is>
+      </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Recurrente</t>
-        </is>
-      </c>
-      <c r="P6" t="n">
-        <v>52241</v>
-      </c>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr"/>
     </row>
     <row r="7">
@@ -865,27 +873,27 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>85356</v>
+        <v>85369</v>
       </c>
       <c r="C7" t="n">
-        <v>38424</v>
+        <v>34556</v>
       </c>
       <c r="D7" t="n">
-        <v>36301</v>
+        <v>32470</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>BRYAN  SOQUI VERDUZCO</t>
+          <t>ALAN STEPHEN VEGA CHACON</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>MISION ENSENADA</t>
+          <t>SENDERO MEXICALI</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>02-01-2026 11:34:33</t>
+          <t>02-01-2026 12:29:38</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -928,27 +936,27 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>85373</v>
+        <v>85376</v>
       </c>
       <c r="C8" t="n">
-        <v>331533</v>
+        <v>331536</v>
       </c>
       <c r="D8" t="n">
-        <v>16587</v>
+        <v>16590</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>JORGE JESUS  SERNA  CORREA</t>
+          <t>GABRIELA OLIVERA MAYEN</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>METEPEC</t>
+          <t>TLALNEPANTLA</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>02-01-2026 13:12:58</t>
+          <t>02-01-2026 13:21:19</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -970,14 +978,14 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>649</v>
+        <v>549</v>
       </c>
       <c r="M8" t="n">
         <v>11</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>28-12-2026 13:12:58</t>
+          <t>28-12-2026 13:21:19</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -993,27 +1001,27 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85374</v>
+        <v>85401</v>
       </c>
       <c r="C9" t="n">
-        <v>232207</v>
+        <v>227928</v>
       </c>
       <c r="D9" t="n">
-        <v>29712</v>
+        <v>25433</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>KRISTEL LORENA MAYORQUIN  ORDOÑEZ</t>
+          <t>YOSSIRY MONSERRAT  REYES  MENDOZA</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>SENDERO CULIACAN</t>
+          <t>IXTAPALUCA</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>02-01-2026 13:19:02</t>
+          <t>02-01-2026 15:26:49</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1035,17 +1043,19 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>649</v>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>Indefinido</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
+        <v>549</v>
+      </c>
+      <c r="M9" t="n">
+        <v>11</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>28-12-2026 15:26:49</t>
+        </is>
+      </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Recurrente</t>
+          <t>Domiciliado</t>
         </is>
       </c>
       <c r="P9" t="inlineStr"/>
@@ -1056,27 +1066,27 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>85391</v>
+        <v>85403</v>
       </c>
       <c r="C10" t="n">
-        <v>75444</v>
+        <v>331580</v>
       </c>
       <c r="D10" t="n">
-        <v>73258</v>
+        <v>16634</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>DAYANNA  LOPEZ CASTELO</t>
+          <t>IRVIN ROBERTO RUBIO CASTELLANOS</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>AZAHARES CULIACAN</t>
+          <t>PASEO 2000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>02-01-2026 14:20:50</t>
+          <t>02-01-2026 15:32:38</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1094,18 +1104,18 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>RENOVACIÓN</t>
+          <t>NUEVO</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>749</v>
+        <v>549</v>
       </c>
       <c r="M10" t="n">
         <v>11</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>28-12-2026 14:20:50</t>
+          <t>28-12-2026 15:32:38</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1113,9 +1123,7 @@
           <t>Domiciliado</t>
         </is>
       </c>
-      <c r="P10" t="n">
-        <v>37414</v>
-      </c>
+      <c r="P10" t="inlineStr"/>
       <c r="Q10" t="inlineStr"/>
     </row>
     <row r="11">
@@ -1123,27 +1131,27 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>85392</v>
+        <v>85410</v>
       </c>
       <c r="C11" t="n">
-        <v>331553</v>
+        <v>331587</v>
       </c>
       <c r="D11" t="n">
-        <v>16607</v>
+        <v>16641</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>KENIA LISETH RODRIGUEZ  ROMERO</t>
+          <t>JANARA ELIZABETH SAENZ GARCIA</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>INSURGENTES</t>
+          <t>VILLAS DEL REY</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>02-01-2026 14:22:50</t>
+          <t>02-01-2026 16:05:09</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1165,14 +1173,14 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>649</v>
+        <v>549</v>
       </c>
       <c r="M11" t="n">
         <v>11</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>28-12-2026 14:22:50</t>
+          <t>28-12-2026 16:05:09</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1188,27 +1196,27 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>85405</v>
+        <v>85435</v>
       </c>
       <c r="C12" t="n">
-        <v>331581</v>
+        <v>331665</v>
       </c>
       <c r="D12" t="n">
-        <v>16635</v>
+        <v>16719</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>KARINA  GARCIA GOMEZ</t>
+          <t>JOAQUIN GLORIA CASILLAS</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>SALTILLO VILLALTA</t>
+          <t>CARROUSEL TIJUANA</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>02-01-2026 15:41:24</t>
+          <t>02-01-2026 20:32:36</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1232,17 +1240,15 @@
       <c r="L12" t="n">
         <v>649</v>
       </c>
-      <c r="M12" t="n">
-        <v>11</v>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>28-12-2026 15:41:24</t>
-        </is>
-      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Domiciliado</t>
+          <t>Recurrente</t>
         </is>
       </c>
       <c r="P12" t="inlineStr"/>
@@ -1253,32 +1259,32 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>85406</v>
+        <v>85444</v>
       </c>
       <c r="C13" t="n">
-        <v>331586</v>
+        <v>331691</v>
       </c>
       <c r="D13" t="n">
-        <v>16640</v>
+        <v>16745</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>LUIS JAVIER MARTINEZ CELIS</t>
+          <t>DANIELA GISELLE URZUA NAVARRO</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CARROUSEL TIJUANA</t>
+          <t>MISION ENSENADA</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>02-01-2026 15:49:07</t>
+          <t>03-01-2026 8:58:51</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>02-02-2026 23:59:59</t>
+          <t>03-02-2026 23:59:59</t>
         </is>
       </c>
       <c r="I13" t="n">
@@ -1316,32 +1322,32 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>85409</v>
+        <v>85446</v>
       </c>
       <c r="C14" t="n">
-        <v>180662</v>
+        <v>147839</v>
       </c>
       <c r="D14" t="n">
-        <v>78169</v>
+        <v>45415</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>MARIA AZUCENA ANASTASIO ROMUALDO</t>
+          <t>LIDIA YARELY FAVELA  VERDUZCO</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>CARROUSEL TIJUANA</t>
+          <t>SENDERO CULIACAN</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>02-01-2026 16:00:08</t>
+          <t>03-01-2026 9:25:47</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>02-02-2026 23:59:59</t>
+          <t>03-02-2026 23:59:59</t>
         </is>
       </c>
       <c r="I14" t="n">
@@ -1354,28 +1360,24 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>RENOVACIÓN</t>
+          <t>NUEVO</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>749</v>
-      </c>
-      <c r="M14" t="n">
-        <v>11</v>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>28-12-2026 16:00:08</t>
-        </is>
-      </c>
+        <v>649</v>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Domiciliado</t>
-        </is>
-      </c>
-      <c r="P14" t="n">
-        <v>45199</v>
-      </c>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr"/>
       <c r="Q14" t="inlineStr"/>
     </row>
     <row r="15">
@@ -1383,32 +1385,32 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>85183</v>
+        <v>85469</v>
       </c>
       <c r="C15" t="n">
-        <v>241364</v>
+        <v>331733</v>
       </c>
       <c r="D15" t="n">
-        <v>38869</v>
+        <v>16787</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>JESUS RUBEN FERNANDEZ NUÑEZ</t>
+          <t>BLANCA  REYES  GARCIA</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>TEC MEXICALI</t>
+          <t>METEPEC</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>30-12-2025 18:27:28</t>
+          <t>03-01-2026 12:07:33</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>01-02-2026 23:59:59</t>
+          <t>03-02-2026 23:59:59</t>
         </is>
       </c>
       <c r="I15" t="n">
@@ -1416,23 +1418,23 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Activado</t>
+          <t>Sin filtro</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>CANCELADO</t>
+          <t>NUEVO</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>499</v>
+        <v>649</v>
       </c>
       <c r="M15" t="n">
         <v>11</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>25-12-2026 18:27:28</t>
+          <t>29-12-2026 12:07:33</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -1440,9 +1442,7 @@
           <t>Domiciliado</t>
         </is>
       </c>
-      <c r="P15" t="n">
-        <v>83190</v>
-      </c>
+      <c r="P15" t="inlineStr"/>
       <c r="Q15" t="inlineStr"/>
     </row>
     <row r="16">
@@ -1450,17 +1450,17 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>85349</v>
+        <v>85471</v>
       </c>
       <c r="C16" t="n">
-        <v>331493</v>
+        <v>331734</v>
       </c>
       <c r="D16" t="n">
-        <v>16547</v>
+        <v>16788</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>BENJAMIN  GOMEZ  PONCE</t>
+          <t>MIGUEL DE JESUS SOLACHE ZAMORANO</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1470,12 +1470,12 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>02-01-2026 11:13:00</t>
+          <t>03-01-2026 12:35:49</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>02-02-2026 23:59:59</t>
+          <t>03-02-2026 23:59:59</t>
         </is>
       </c>
       <c r="I16" t="n">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>28-12-2026 11:13:00</t>
+          <t>29-12-2026 12:35:49</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -1515,32 +1515,32 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>85364</v>
+        <v>85476</v>
       </c>
       <c r="C17" t="n">
-        <v>217170</v>
+        <v>331736</v>
       </c>
       <c r="D17" t="n">
-        <v>14678</v>
+        <v>16790</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>GABRIELA GUERRERO ORANTES</t>
+          <t>CARLOS ALBERTO NAJERA YUTANI</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>SENDERO MEXICALI</t>
+          <t>SALTILLO VILLALTA</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>02-01-2026 12:16:54</t>
+          <t>03-01-2026 12:44:58</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>02-02-2026 23:59:59</t>
+          <t>03-02-2026 23:59:59</t>
         </is>
       </c>
       <c r="I17" t="n">
@@ -1553,18 +1553,18 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>RENOVACIÓN</t>
+          <t>NUEVO</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>749</v>
+        <v>649</v>
       </c>
       <c r="M17" t="n">
         <v>11</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>28-12-2026 12:16:54</t>
+          <t>29-12-2026 12:44:58</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -1572,9 +1572,7 @@
           <t>Domiciliado</t>
         </is>
       </c>
-      <c r="P17" t="n">
-        <v>15273</v>
-      </c>
+      <c r="P17" t="inlineStr"/>
       <c r="Q17" t="inlineStr"/>
     </row>
     <row r="18">
@@ -1582,32 +1580,32 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>85366</v>
+        <v>85478</v>
       </c>
       <c r="C18" t="n">
-        <v>319301</v>
+        <v>331738</v>
       </c>
       <c r="D18" t="n">
-        <v>16798</v>
+        <v>16792</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>IRVING OMAR LANDA ALONSO</t>
+          <t>YEIMI ANAHI ALVARADO RODRIGUEZ</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>PAPALOTE TIJUANA</t>
+          <t>SENDERO SALTILLO</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>02-01-2026 12:26:52</t>
+          <t>03-01-2026 12:49:14</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>02-02-2026 23:59:59</t>
+          <t>03-02-2026 23:59:59</t>
         </is>
       </c>
       <c r="I18" t="n">
@@ -1624,17 +1622,19 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>649</v>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>Indefinido</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
+        <v>549</v>
+      </c>
+      <c r="M18" t="n">
+        <v>11</v>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>29-12-2026 12:49:14</t>
+        </is>
+      </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Recurrente</t>
+          <t>Domiciliado</t>
         </is>
       </c>
       <c r="P18" t="inlineStr"/>
@@ -1645,32 +1645,32 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>85381</v>
+        <v>85480</v>
       </c>
       <c r="C19" t="n">
-        <v>242032</v>
+        <v>331740</v>
       </c>
       <c r="D19" t="n">
-        <v>39537</v>
+        <v>16794</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>JOSE ALEJANDRO GARCIA VELAZQUEZ</t>
+          <t>EDGAR ALAHAN ESTRADA  HURTADO</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>PAPALOTE TIJUANA</t>
+          <t>SALTILLO VILLALTA</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>02-01-2026 13:42:51</t>
+          <t>03-01-2026 12:56:15</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>02-02-2026 23:59:59</t>
+          <t>03-02-2026 23:59:59</t>
         </is>
       </c>
       <c r="I19" t="n">
@@ -1683,18 +1683,18 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>RENOVACIÓN</t>
+          <t>NUEVO</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>749</v>
+        <v>649</v>
       </c>
       <c r="M19" t="n">
         <v>11</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>28-12-2026 13:42:51</t>
+          <t>29-12-2026 12:56:15</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -1702,9 +1702,7 @@
           <t>Domiciliado</t>
         </is>
       </c>
-      <c r="P19" t="n">
-        <v>31243</v>
-      </c>
+      <c r="P19" t="inlineStr"/>
       <c r="Q19" t="inlineStr"/>
     </row>
     <row r="20">
@@ -1712,32 +1710,32 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>85398</v>
+        <v>85501</v>
       </c>
       <c r="C20" t="n">
-        <v>331574</v>
+        <v>331771</v>
       </c>
       <c r="D20" t="n">
-        <v>16628</v>
+        <v>16575</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>ALONSO  GARCIA  RAMOS</t>
+          <t>GUSTAVO MARIO MENDOZA  ORTIZ</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>INSURGENTES</t>
+          <t>METEPEC</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>02-01-2026 15:19:01</t>
+          <t>03-01-2026 17:53:35</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>02-02-2026 23:59:59</t>
+          <t>03-02-2026 23:59:59</t>
         </is>
       </c>
       <c r="I20" t="n">
@@ -1761,7 +1759,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>28-12-2026 15:19:01</t>
+          <t>29-12-2026 17:53:35</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -1777,27 +1775,27 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>85415</v>
+        <v>84502</v>
       </c>
       <c r="C21" t="n">
-        <v>331592</v>
+        <v>290990</v>
       </c>
       <c r="D21" t="n">
-        <v>16646</v>
+        <v>88488</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>EMILIOALONSO BARCENAS REYES</t>
+          <t>CLAUDIA ANTONIETA SALGADO MENDOZA</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>INSURGENTES</t>
+          <t>MISION ENSENADA</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>02-01-2026 16:30:03</t>
+          <t>22-12-2025 7:48:13</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1815,18 +1813,18 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>NUEVO</t>
+          <t>RENOVACIÓN</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>649</v>
+        <v>499</v>
       </c>
       <c r="M21" t="n">
         <v>11</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>28-12-2026 16:30:03</t>
+          <t>17-12-2026 7:48:13</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -1834,7 +1832,9 @@
           <t>Domiciliado</t>
         </is>
       </c>
-      <c r="P21" t="inlineStr"/>
+      <c r="P21" t="n">
+        <v>65133</v>
+      </c>
       <c r="Q21" t="inlineStr"/>
     </row>
     <row r="22">
@@ -1842,32 +1842,32 @@
         <v>20</v>
       </c>
       <c r="B22" t="n">
-        <v>85417</v>
+        <v>85202</v>
       </c>
       <c r="C22" t="n">
-        <v>331598</v>
+        <v>154009</v>
       </c>
       <c r="D22" t="n">
-        <v>16652</v>
+        <v>51565</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>ISLAS BERENICE DIAZ  BARRIGA</t>
+          <t>AXEL LEONARDO BIBIANO GARCIA</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>TLALNEPANTLA</t>
+          <t>VILLAS DEL REY</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>02-01-2026 16:41:33</t>
+          <t>30-12-2025 19:23:24</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>02-02-2026 23:59:59</t>
+          <t>03-02-2026 23:59:59</t>
         </is>
       </c>
       <c r="I22" t="n">
@@ -1880,18 +1880,18 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>NUEVO</t>
+          <t>RENOVACIÓN</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>549</v>
+        <v>449</v>
       </c>
       <c r="M22" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>28-12-2026 16:41:33</t>
+          <t>28-06-2026 19:23:24</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -1899,7 +1899,9 @@
           <t>Domiciliado</t>
         </is>
       </c>
-      <c r="P22" t="inlineStr"/>
+      <c r="P22" t="n">
+        <v>49646</v>
+      </c>
       <c r="Q22" t="inlineStr"/>
     </row>
     <row r="23">
@@ -1907,27 +1909,27 @@
         <v>21</v>
       </c>
       <c r="B23" t="n">
-        <v>85430</v>
+        <v>85352</v>
       </c>
       <c r="C23" t="n">
-        <v>283380</v>
+        <v>331501</v>
       </c>
       <c r="D23" t="n">
-        <v>80881</v>
+        <v>16555</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>BRIANDA LIZETH TAMAYO URQUIDEZ</t>
+          <t>MARIA MAGDALENA PALACIOS GAONA</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>VILLA VERDE MEXICALI</t>
+          <t>SALTILLO VILLALTA</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>02-01-2026 18:52:42</t>
+          <t>02-01-2026 11:30:38</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1949,14 +1951,14 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>549</v>
+        <v>649</v>
       </c>
       <c r="M23" t="n">
         <v>11</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>28-12-2026 18:52:42</t>
+          <t>28-12-2026 11:30:38</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -1972,17 +1974,17 @@
         <v>22</v>
       </c>
       <c r="B24" t="n">
-        <v>85434</v>
+        <v>83287</v>
       </c>
       <c r="C24" t="n">
-        <v>331655</v>
+        <v>234869</v>
       </c>
       <c r="D24" t="n">
-        <v>16709</v>
+        <v>32374</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>JOSE ISRAEL  VARGAS  VALDEZ</t>
+          <t>NARCEDALIA URIARTE ROCHA</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1992,12 +1994,12 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>02-01-2026 19:47:46</t>
+          <t>02-12-2025 16:52:24</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>02-02-2026 23:59:59</t>
+          <t>20-01-2026 23:59:59</t>
         </is>
       </c>
       <c r="I24" t="n">
@@ -2010,24 +2012,28 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>NUEVO</t>
+          <t>RENOVACIÓN</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>649</v>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>Indefinido</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
+        <v>499</v>
+      </c>
+      <c r="M24" t="n">
+        <v>11</v>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>27-11-2026 16:52:24</t>
+        </is>
+      </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>Recurrente</t>
-        </is>
-      </c>
-      <c r="P24" t="inlineStr"/>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P24" t="n">
+        <v>80346</v>
+      </c>
       <c r="Q24" t="inlineStr"/>
     </row>
     <row r="25">
@@ -2035,32 +2041,32 @@
         <v>23</v>
       </c>
       <c r="B25" t="n">
-        <v>83287</v>
+        <v>83298</v>
       </c>
       <c r="C25" t="n">
-        <v>234869</v>
+        <v>249279</v>
       </c>
       <c r="D25" t="n">
-        <v>32374</v>
+        <v>46783</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>NARCEDALIA URIARTE ROCHA</t>
+          <t>REY SAID CASAS RAMOS</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>SENDERO CULIACAN</t>
+          <t>PAPALOTE TIJUANA</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>02-12-2025 16:52:24</t>
+          <t>02-12-2025 17:39:24</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>20-01-2026 23:59:59</t>
+          <t>02-02-2026 23:59:59</t>
         </is>
       </c>
       <c r="I25" t="n">
@@ -2077,14 +2083,14 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>499</v>
+        <v>399</v>
       </c>
       <c r="M25" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>27-11-2026 16:52:24</t>
+          <t>31-05-2026 17:39:24</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
@@ -2093,7 +2099,7 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>80346</v>
+        <v>37993</v>
       </c>
       <c r="Q25" t="inlineStr"/>
     </row>
@@ -2102,27 +2108,27 @@
         <v>24</v>
       </c>
       <c r="B26" t="n">
-        <v>83298</v>
+        <v>85377</v>
       </c>
       <c r="C26" t="n">
-        <v>249279</v>
+        <v>331540</v>
       </c>
       <c r="D26" t="n">
-        <v>46783</v>
+        <v>16594</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>REY SAID CASAS RAMOS</t>
+          <t>FRIDA PATRICIA PALACIOS MARTINEZ</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>PAPALOTE TIJUANA</t>
+          <t>PASEO 2000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>02-12-2025 17:39:24</t>
+          <t>02-01-2026 13:25:01</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2140,28 +2146,24 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>RENOVACIÓN</t>
+          <t>NUEVO</t>
         </is>
       </c>
       <c r="L26" t="n">
-        <v>399</v>
-      </c>
-      <c r="M26" t="n">
-        <v>5</v>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>31-05-2026 17:39:24</t>
-        </is>
-      </c>
+        <v>649</v>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr">
         <is>
-          <t>Domiciliado</t>
-        </is>
-      </c>
-      <c r="P26" t="n">
-        <v>37993</v>
-      </c>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr"/>
       <c r="Q26" t="inlineStr"/>
     </row>
     <row r="27">
@@ -2169,32 +2171,32 @@
         <v>25</v>
       </c>
       <c r="B27" t="n">
-        <v>84502</v>
+        <v>85384</v>
       </c>
       <c r="C27" t="n">
-        <v>290990</v>
+        <v>331545</v>
       </c>
       <c r="D27" t="n">
-        <v>88488</v>
+        <v>16599</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>CLAUDIA ANTONIETA SALGADO MENDOZA</t>
+          <t>FRANCISCO KEVIN PLANCARTE GARCIA</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>MISION ENSENADA</t>
+          <t>INSURGENTES</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>22-12-2025 7:48:13</t>
+          <t>02-01-2026 13:55:56</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>02-02-2026 23:59:59</t>
+          <t>02-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="I27" t="n">
@@ -2207,28 +2209,24 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>RENOVACIÓN</t>
+          <t>NUEVO</t>
         </is>
       </c>
       <c r="L27" t="n">
-        <v>499</v>
-      </c>
-      <c r="M27" t="n">
-        <v>11</v>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>17-12-2026 7:48:13</t>
-        </is>
-      </c>
+        <v>1549</v>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr">
         <is>
-          <t>Domiciliado</t>
-        </is>
-      </c>
-      <c r="P27" t="n">
-        <v>65133</v>
-      </c>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr"/>
       <c r="Q27" t="inlineStr"/>
     </row>
     <row r="28">
@@ -2236,32 +2234,32 @@
         <v>26</v>
       </c>
       <c r="B28" t="n">
-        <v>85352</v>
+        <v>85395</v>
       </c>
       <c r="C28" t="n">
-        <v>331501</v>
+        <v>331566</v>
       </c>
       <c r="D28" t="n">
-        <v>16555</v>
+        <v>16620</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>MARIA MAGDALENA PALACIOS GAONA</t>
+          <t>HIRAM MORA VARGAS</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>SALTILLO VILLALTA</t>
+          <t>INSURGENTES</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>02-01-2026 11:30:38</t>
+          <t>02-01-2026 15:04:56</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>02-02-2026 23:59:59</t>
+          <t>02-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="I28" t="n">
@@ -2278,19 +2276,17 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>649</v>
-      </c>
-      <c r="M28" t="n">
-        <v>11</v>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>28-12-2026 11:30:38</t>
-        </is>
-      </c>
+        <v>1549</v>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr">
         <is>
-          <t>Domiciliado</t>
+          <t>Recurrente</t>
         </is>
       </c>
       <c r="P28" t="inlineStr"/>
@@ -2301,32 +2297,32 @@
         <v>27</v>
       </c>
       <c r="B29" t="n">
-        <v>85384</v>
+        <v>85402</v>
       </c>
       <c r="C29" t="n">
-        <v>331545</v>
+        <v>331576</v>
       </c>
       <c r="D29" t="n">
-        <v>16599</v>
+        <v>16630</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>FRANCISCO KEVIN PLANCARTE GARCIA</t>
+          <t>LUIS RODRIGO TORRES SANCHEZ</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>INSURGENTES</t>
+          <t>SALTILLO VILLALTA</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>02-01-2026 13:55:56</t>
+          <t>02-01-2026 15:27:25</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>02-02-2026 23:59:59</t>
         </is>
       </c>
       <c r="I29" t="n">
@@ -2343,17 +2339,19 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1549</v>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>Indefinido</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
+        <v>649</v>
+      </c>
+      <c r="M29" t="n">
+        <v>11</v>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>28-12-2026 15:27:25</t>
+        </is>
+      </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>Recurrente</t>
+          <t>Domiciliado</t>
         </is>
       </c>
       <c r="P29" t="inlineStr"/>
@@ -2364,32 +2362,32 @@
         <v>28</v>
       </c>
       <c r="B30" t="n">
-        <v>85395</v>
+        <v>85420</v>
       </c>
       <c r="C30" t="n">
-        <v>331566</v>
+        <v>30767</v>
       </c>
       <c r="D30" t="n">
-        <v>16620</v>
+        <v>28697</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>HIRAM MORA VARGAS</t>
+          <t>BERENICE ALFARO ESPINOSA</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>INSURGENTES</t>
+          <t>LOMA BONITA</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>02-01-2026 15:04:56</t>
+          <t>02-01-2026 17:02:21</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>02-02-2026 23:59:59</t>
         </is>
       </c>
       <c r="I30" t="n">
@@ -2402,24 +2400,28 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>NUEVO</t>
+          <t>RENOVACIÓN</t>
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1549</v>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>Indefinido</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
+        <v>399</v>
+      </c>
+      <c r="M30" t="n">
+        <v>11</v>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>28-12-2026 17:02:21</t>
+        </is>
+      </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>Recurrente</t>
-        </is>
-      </c>
-      <c r="P30" t="inlineStr"/>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P30" t="n">
+        <v>28737</v>
+      </c>
       <c r="Q30" t="inlineStr"/>
     </row>
     <row r="31">
@@ -2427,32 +2429,32 @@
         <v>29</v>
       </c>
       <c r="B31" t="n">
-        <v>85402</v>
+        <v>85445</v>
       </c>
       <c r="C31" t="n">
-        <v>331576</v>
+        <v>331472</v>
       </c>
       <c r="D31" t="n">
-        <v>16630</v>
+        <v>16526</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>LUIS RODRIGO TORRES SANCHEZ</t>
+          <t>MARIA ISABEL DIAZ  DOMINGUEZ</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>SALTILLO VILLALTA</t>
+          <t>INSURGENTES</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>02-01-2026 15:27:25</t>
+          <t>03-01-2026 9:06:17</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>02-02-2026 23:59:59</t>
+          <t>03-02-2026 23:59:59</t>
         </is>
       </c>
       <c r="I31" t="n">
@@ -2476,7 +2478,7 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>28-12-2026 15:27:25</t>
+          <t>29-12-2026 9:06:17</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
@@ -2492,32 +2494,32 @@
         <v>30</v>
       </c>
       <c r="B32" t="n">
-        <v>85420</v>
+        <v>85452</v>
       </c>
       <c r="C32" t="n">
-        <v>30767</v>
+        <v>331709</v>
       </c>
       <c r="D32" t="n">
-        <v>28697</v>
+        <v>16763</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>BERENICE ALFARO ESPINOSA</t>
+          <t>MARIA ALEJANDRA JACOBO RODRIGUEZ</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>LOMA BONITA</t>
+          <t>SALTILLO VILLALTA</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>02-01-2026 17:02:21</t>
+          <t>03-01-2026 10:36:00</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>02-02-2026 23:59:59</t>
+          <t>03-02-2026 23:59:59</t>
         </is>
       </c>
       <c r="I32" t="n">
@@ -2530,18 +2532,18 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>RENOVACIÓN</t>
+          <t>NUEVO</t>
         </is>
       </c>
       <c r="L32" t="n">
-        <v>399</v>
+        <v>649</v>
       </c>
       <c r="M32" t="n">
         <v>11</v>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>28-12-2026 17:02:21</t>
+          <t>29-12-2026 10:36:00</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
@@ -2549,9 +2551,7 @@
           <t>Domiciliado</t>
         </is>
       </c>
-      <c r="P32" t="n">
-        <v>28737</v>
-      </c>
+      <c r="P32" t="inlineStr"/>
       <c r="Q32" t="inlineStr"/>
     </row>
     <row r="33">
@@ -2559,32 +2559,32 @@
         <v>31</v>
       </c>
       <c r="B33" t="n">
-        <v>83154</v>
+        <v>85463</v>
       </c>
       <c r="C33" t="n">
-        <v>319772</v>
+        <v>74211</v>
       </c>
       <c r="D33" t="n">
-        <v>17269</v>
+        <v>72027</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>ADRIAN ALEJANDRO ESCUTIA MUÑIZ</t>
+          <t>ERIC OLMEDO TREVIÑO</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>INSURGENTES</t>
+          <t>PASEO 2000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>01-12-2025 12:03:42</t>
+          <t>03-01-2026 11:31:36</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>28-01-2026 23:59:59</t>
+          <t>03-02-2026 23:59:59</t>
         </is>
       </c>
       <c r="I33" t="n">
@@ -2597,18 +2597,18 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>RENOVACIÓN</t>
+          <t>NUEVO</t>
         </is>
       </c>
       <c r="L33" t="n">
-        <v>599</v>
+        <v>549</v>
       </c>
       <c r="M33" t="n">
         <v>11</v>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>26-11-2026 12:03:42</t>
+          <t>29-12-2026 11:31:36</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
@@ -2616,9 +2616,7 @@
           <t>Domiciliado</t>
         </is>
       </c>
-      <c r="P33" t="n">
-        <v>80928</v>
-      </c>
+      <c r="P33" t="inlineStr"/>
       <c r="Q33" t="inlineStr"/>
     </row>
     <row r="34">
@@ -2626,32 +2624,32 @@
         <v>32</v>
       </c>
       <c r="B34" t="n">
-        <v>85351</v>
+        <v>85470</v>
       </c>
       <c r="C34" t="n">
-        <v>331489</v>
+        <v>255404</v>
       </c>
       <c r="D34" t="n">
-        <v>16543</v>
+        <v>52908</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>ADRIANA VELASCO  RAMIREZ</t>
+          <t>MARIANA SOFIA PIÑON  SALGADO</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>TLALNEPANTLA</t>
+          <t>VILLAS DEL REY</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>02-01-2026 11:23:45</t>
+          <t>03-01-2026 12:34:31</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>02-02-2026 23:59:59</t>
+          <t>03-02-2026 23:59:59</t>
         </is>
       </c>
       <c r="I34" t="n">
@@ -2675,7 +2673,7 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>28-12-2026 11:23:45</t>
+          <t>29-12-2026 12:34:31</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
@@ -2691,32 +2689,32 @@
         <v>33</v>
       </c>
       <c r="B35" t="n">
-        <v>85353</v>
+        <v>85477</v>
       </c>
       <c r="C35" t="n">
-        <v>331504</v>
+        <v>331732</v>
       </c>
       <c r="D35" t="n">
-        <v>16558</v>
+        <v>16786</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>ANGEL  DURAN  VIZUET</t>
+          <t>ABRAHAM  NAVARRO HERNANDEZ</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>TLALNEPANTLA</t>
+          <t>TEC MEXICALI</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>02-01-2026 11:33:22</t>
+          <t>03-01-2026 12:47:49</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>02-02-2026 23:59:59</t>
+          <t>03-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="I35" t="n">
@@ -2733,14 +2731,14 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>549</v>
+        <v>1449</v>
       </c>
       <c r="M35" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>28-12-2026 11:33:22</t>
+          <t>29-12-2026 12:47:49</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
@@ -2756,32 +2754,32 @@
         <v>34</v>
       </c>
       <c r="B36" t="n">
-        <v>85362</v>
+        <v>85488</v>
       </c>
       <c r="C36" t="n">
-        <v>114321</v>
+        <v>179365</v>
       </c>
       <c r="D36" t="n">
-        <v>12050</v>
+        <v>76872</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>NELLY SOFIA  GONZALEZ  OLIVARES</t>
+          <t>NOREYDA MARINTIA  MEDINA  GARCIA</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>SANTA CATARINA</t>
+          <t>VILLAS DEL REY</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>02-01-2026 12:02:44</t>
+          <t>03-01-2026 13:50:21</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>02-02-2026 23:59:59</t>
+          <t>03-02-2026 23:59:59</t>
         </is>
       </c>
       <c r="I36" t="n">
@@ -2794,18 +2792,18 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>NUEVO</t>
+          <t>RENOVACIÓN</t>
         </is>
       </c>
       <c r="L36" t="n">
-        <v>549</v>
+        <v>749</v>
       </c>
       <c r="M36" t="n">
         <v>11</v>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>28-12-2026 12:02:44</t>
+          <t>29-12-2026 13:50:21</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
@@ -2813,7 +2811,9 @@
           <t>Domiciliado</t>
         </is>
       </c>
-      <c r="P36" t="inlineStr"/>
+      <c r="P36" t="n">
+        <v>65906</v>
+      </c>
       <c r="Q36" t="inlineStr"/>
     </row>
     <row r="37">
@@ -2821,32 +2821,32 @@
         <v>35</v>
       </c>
       <c r="B37" t="n">
-        <v>85387</v>
+        <v>85495</v>
       </c>
       <c r="C37" t="n">
-        <v>331550</v>
+        <v>331761</v>
       </c>
       <c r="D37" t="n">
-        <v>16604</v>
+        <v>16815</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>ADRIAN ANTONIO CORDERO CALDERON</t>
+          <t>NORMA TUÑON NAVA</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>SENDERO CHIHUAHUA</t>
+          <t>METEPEC</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>02-01-2026 14:09:47</t>
+          <t>03-01-2026 15:31:18</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>02-02-2026 23:59:59</t>
+          <t>03-02-2026 23:59:59</t>
         </is>
       </c>
       <c r="I37" t="n">
@@ -2863,14 +2863,14 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>549</v>
+        <v>649</v>
       </c>
       <c r="M37" t="n">
         <v>11</v>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>28-12-2026 14:09:47</t>
+          <t>29-12-2026 15:31:18</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
@@ -2886,32 +2886,34 @@
         <v>36</v>
       </c>
       <c r="B38" t="n">
-        <v>85419</v>
+        <v>83680</v>
       </c>
       <c r="C38" t="n">
-        <v>331608</v>
-      </c>
-      <c r="D38" t="n">
-        <v>16662</v>
+        <v>4797</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>03735</t>
+        </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>MARIA ANTONIETA  GERARDO PEREZ DE ALBA</t>
+          <t>FAUSTO GILBERTO MOLINA  LUGO</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>SENDERO MEXICALI</t>
+          <t>VILLA VERDE MEXICALI</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>02-01-2026 16:56:39</t>
+          <t>08-12-2025 20:20:20</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>02-02-2026 23:59:59</t>
+          <t>03-02-2026 23:59:59</t>
         </is>
       </c>
       <c r="I38" t="n">
@@ -2924,18 +2926,18 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>NUEVO</t>
+          <t>RENOVACIÓN</t>
         </is>
       </c>
       <c r="L38" t="n">
-        <v>549</v>
+        <v>499</v>
       </c>
       <c r="M38" t="n">
         <v>11</v>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>28-12-2026 16:56:39</t>
+          <t>03-12-2026 20:20:20</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
@@ -2943,7 +2945,9 @@
           <t>Domiciliado</t>
         </is>
       </c>
-      <c r="P38" t="inlineStr"/>
+      <c r="P38" t="n">
+        <v>59323</v>
+      </c>
       <c r="Q38" t="inlineStr"/>
     </row>
     <row r="39">
@@ -2951,32 +2955,32 @@
         <v>37</v>
       </c>
       <c r="B39" t="n">
-        <v>85421</v>
+        <v>84313</v>
       </c>
       <c r="C39" t="n">
-        <v>96568</v>
+        <v>301685</v>
       </c>
       <c r="D39" t="n">
-        <v>94327</v>
+        <v>99183</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>CARLOS HERNANDEZ YEPIZ</t>
+          <t>JAZMIN ARACELY MARTINEZ MAQUEDA</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>SENDERO MEXICALI</t>
+          <t>CARROUSEL TIJUANA</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>02-01-2026 17:09:17</t>
+          <t>17-12-2025 19:29:11</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>02-02-2026 23:59:59</t>
+          <t>03-02-2026 23:59:59</t>
         </is>
       </c>
       <c r="I39" t="n">
@@ -2989,18 +2993,18 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>NUEVO</t>
+          <t>RENOVACIÓN</t>
         </is>
       </c>
       <c r="L39" t="n">
-        <v>549</v>
+        <v>499</v>
       </c>
       <c r="M39" t="n">
         <v>11</v>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>28-12-2026 17:09:17</t>
+          <t>12-12-2026 19:29:11</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
@@ -3008,7 +3012,9 @@
           <t>Domiciliado</t>
         </is>
       </c>
-      <c r="P39" t="inlineStr"/>
+      <c r="P39" t="n">
+        <v>71154</v>
+      </c>
       <c r="Q39" t="inlineStr"/>
     </row>
     <row r="40">
@@ -3016,32 +3022,32 @@
         <v>38</v>
       </c>
       <c r="B40" t="n">
-        <v>85428</v>
+        <v>84347</v>
       </c>
       <c r="C40" t="n">
-        <v>331623</v>
+        <v>277320</v>
       </c>
       <c r="D40" t="n">
-        <v>16677</v>
+        <v>74821</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>DANIEL  SALINAS  HERNANDEZ</t>
+          <t>JOSE MANUEL PEREZ RICO</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>TLALNEPANTLA</t>
+          <t>SENDERO MEXICALI</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>02-01-2026 17:58:49</t>
+          <t>18-12-2025 12:38:51</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>02-02-2026 23:59:59</t>
+          <t>26-01-2026 23:59:59</t>
         </is>
       </c>
       <c r="I40" t="n">
@@ -3054,18 +3060,18 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>NUEVO</t>
+          <t>RENOVACIÓN</t>
         </is>
       </c>
       <c r="L40" t="n">
-        <v>549</v>
+        <v>499</v>
       </c>
       <c r="M40" t="n">
         <v>11</v>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>28-12-2026 17:58:49</t>
+          <t>13-12-2026 12:38:51</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
@@ -3073,7 +3079,9 @@
           <t>Domiciliado</t>
         </is>
       </c>
-      <c r="P40" t="inlineStr"/>
+      <c r="P40" t="n">
+        <v>61746</v>
+      </c>
       <c r="Q40" t="inlineStr"/>
     </row>
     <row r="41">
@@ -3081,32 +3089,32 @@
         <v>39</v>
       </c>
       <c r="B41" t="n">
-        <v>83440</v>
+        <v>83377</v>
       </c>
       <c r="C41" t="n">
-        <v>190835</v>
+        <v>200836</v>
       </c>
       <c r="D41" t="n">
-        <v>88342</v>
+        <v>98343</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>PERLA CORAL LUCERO  AGUILAR</t>
+          <t>LUIS JOSUE DE LA CRUZ ESTEBAN</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>PASEO LA PAZ</t>
+          <t>SANTA CATARINA</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>04-12-2025 17:40:44</t>
+          <t>03-12-2025 16:49:24</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>02-02-2026 23:59:59</t>
+          <t>03-02-2026 23:59:59</t>
         </is>
       </c>
       <c r="I41" t="n">
@@ -3123,23 +3131,21 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>499</v>
-      </c>
-      <c r="M41" t="n">
-        <v>11</v>
-      </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>29-11-2026 17:40:44</t>
-        </is>
-      </c>
+        <v>599</v>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="O41" t="inlineStr">
         <is>
-          <t>Domiciliado</t>
+          <t>Recurrente</t>
         </is>
       </c>
       <c r="P41" t="n">
-        <v>68138</v>
+        <v>62574</v>
       </c>
       <c r="Q41" t="inlineStr"/>
     </row>
@@ -3148,34 +3154,32 @@
         <v>40</v>
       </c>
       <c r="B42" t="n">
-        <v>85346</v>
+        <v>85183</v>
       </c>
       <c r="C42" t="n">
-        <v>207168</v>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>04676</t>
-        </is>
+        <v>241364</v>
+      </c>
+      <c r="D42" t="n">
+        <v>38869</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>HERIBERTO JAVIER RAMIREZ LOZA</t>
+          <t>JESUS RUBEN FERNANDEZ NUÑEZ</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>VILLAS DEL REY</t>
+          <t>TEC MEXICALI</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>02-01-2026 11:10:52</t>
+          <t>30-12-2025 18:27:28</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>02-02-2026 23:59:59</t>
+          <t>01-02-2026 23:59:59</t>
         </is>
       </c>
       <c r="I42" t="n">
@@ -3183,23 +3187,23 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Sin filtro</t>
+          <t>Activado</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>NUEVO</t>
+          <t>CANCELADO</t>
         </is>
       </c>
       <c r="L42" t="n">
-        <v>549</v>
+        <v>499</v>
       </c>
       <c r="M42" t="n">
         <v>11</v>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>28-12-2026 11:10:52</t>
+          <t>25-12-2026 18:27:28</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
@@ -3207,7 +3211,9 @@
           <t>Domiciliado</t>
         </is>
       </c>
-      <c r="P42" t="inlineStr"/>
+      <c r="P42" t="n">
+        <v>83190</v>
+      </c>
       <c r="Q42" t="inlineStr"/>
     </row>
     <row r="43">
@@ -3215,32 +3221,32 @@
         <v>41</v>
       </c>
       <c r="B43" t="n">
-        <v>85369</v>
+        <v>85347</v>
       </c>
       <c r="C43" t="n">
-        <v>34556</v>
+        <v>331466</v>
       </c>
       <c r="D43" t="n">
-        <v>32470</v>
+        <v>16520</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>ALAN STEPHEN VEGA CHACON</t>
+          <t>JESMIN GUADALUPE  GUTIERREZ HERNANDEZ</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>SENDERO MEXICALI</t>
+          <t>SENDERO CHIHUAHUA</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>02-01-2026 12:29:38</t>
+          <t>02-01-2026 11:11:29</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>02-02-2026 23:59:59</t>
+          <t>03-02-2026 23:59:59</t>
         </is>
       </c>
       <c r="I43" t="n">
@@ -3253,21 +3259,23 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>NUEVO</t>
+          <t>CANCELADO</t>
         </is>
       </c>
       <c r="L43" t="n">
-        <v>649</v>
-      </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>Indefinido</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr"/>
+        <v>549</v>
+      </c>
+      <c r="M43" t="n">
+        <v>11</v>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>28-12-2026 11:11:29</t>
+        </is>
+      </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>Recurrente</t>
+          <t>Domiciliado</t>
         </is>
       </c>
       <c r="P43" t="inlineStr"/>
@@ -3278,17 +3286,17 @@
         <v>42</v>
       </c>
       <c r="B44" t="n">
-        <v>85376</v>
+        <v>85349</v>
       </c>
       <c r="C44" t="n">
-        <v>331536</v>
+        <v>331493</v>
       </c>
       <c r="D44" t="n">
-        <v>16590</v>
+        <v>16547</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>GABRIELA OLIVERA MAYEN</t>
+          <t>BENJAMIN  GOMEZ  PONCE</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -3298,7 +3306,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>02-01-2026 13:21:19</t>
+          <t>02-01-2026 11:13:00</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3327,7 +3335,7 @@
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>28-12-2026 13:21:19</t>
+          <t>28-12-2026 11:13:00</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
@@ -3343,27 +3351,27 @@
         <v>43</v>
       </c>
       <c r="B45" t="n">
-        <v>85401</v>
+        <v>85364</v>
       </c>
       <c r="C45" t="n">
-        <v>227928</v>
+        <v>217170</v>
       </c>
       <c r="D45" t="n">
-        <v>25433</v>
+        <v>14678</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>YOSSIRY MONSERRAT  REYES  MENDOZA</t>
+          <t>GABRIELA GUERRERO ORANTES</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>IXTAPALUCA</t>
+          <t>SENDERO MEXICALI</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>02-01-2026 15:26:49</t>
+          <t>02-01-2026 12:16:54</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3381,18 +3389,18 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>NUEVO</t>
+          <t>RENOVACIÓN</t>
         </is>
       </c>
       <c r="L45" t="n">
-        <v>549</v>
+        <v>749</v>
       </c>
       <c r="M45" t="n">
         <v>11</v>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>28-12-2026 15:26:49</t>
+          <t>28-12-2026 12:16:54</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
@@ -3400,7 +3408,9 @@
           <t>Domiciliado</t>
         </is>
       </c>
-      <c r="P45" t="inlineStr"/>
+      <c r="P45" t="n">
+        <v>15273</v>
+      </c>
       <c r="Q45" t="inlineStr"/>
     </row>
     <row r="46">
@@ -3408,27 +3418,27 @@
         <v>44</v>
       </c>
       <c r="B46" t="n">
-        <v>85403</v>
+        <v>85366</v>
       </c>
       <c r="C46" t="n">
-        <v>331580</v>
+        <v>319301</v>
       </c>
       <c r="D46" t="n">
-        <v>16634</v>
+        <v>16798</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>IRVIN ROBERTO RUBIO CASTELLANOS</t>
+          <t>IRVING OMAR LANDA ALONSO</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>PASEO 2000</t>
+          <t>PAPALOTE TIJUANA</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>02-01-2026 15:32:38</t>
+          <t>02-01-2026 12:26:52</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3450,19 +3460,17 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>549</v>
-      </c>
-      <c r="M46" t="n">
-        <v>11</v>
-      </c>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>28-12-2026 15:32:38</t>
-        </is>
-      </c>
+        <v>649</v>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="O46" t="inlineStr">
         <is>
-          <t>Domiciliado</t>
+          <t>Recurrente</t>
         </is>
       </c>
       <c r="P46" t="inlineStr"/>
@@ -3473,27 +3481,27 @@
         <v>45</v>
       </c>
       <c r="B47" t="n">
-        <v>85410</v>
+        <v>85381</v>
       </c>
       <c r="C47" t="n">
-        <v>331587</v>
+        <v>242032</v>
       </c>
       <c r="D47" t="n">
-        <v>16641</v>
+        <v>39537</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>JANARA ELIZABETH SAENZ GARCIA</t>
+          <t>JOSE ALEJANDRO GARCIA VELAZQUEZ</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>VILLAS DEL REY</t>
+          <t>PAPALOTE TIJUANA</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>02-01-2026 16:05:09</t>
+          <t>02-01-2026 13:42:51</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3511,18 +3519,18 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>NUEVO</t>
+          <t>RENOVACIÓN</t>
         </is>
       </c>
       <c r="L47" t="n">
-        <v>549</v>
+        <v>749</v>
       </c>
       <c r="M47" t="n">
         <v>11</v>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>28-12-2026 16:05:09</t>
+          <t>28-12-2026 13:42:51</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
@@ -3530,7 +3538,9 @@
           <t>Domiciliado</t>
         </is>
       </c>
-      <c r="P47" t="inlineStr"/>
+      <c r="P47" t="n">
+        <v>31243</v>
+      </c>
       <c r="Q47" t="inlineStr"/>
     </row>
     <row r="48">
@@ -3538,27 +3548,27 @@
         <v>46</v>
       </c>
       <c r="B48" t="n">
-        <v>85435</v>
+        <v>85398</v>
       </c>
       <c r="C48" t="n">
-        <v>331665</v>
+        <v>331574</v>
       </c>
       <c r="D48" t="n">
-        <v>16719</v>
+        <v>16628</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>JOAQUIN GLORIA CASILLAS</t>
+          <t>ALONSO  GARCIA  RAMOS</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>CARROUSEL TIJUANA</t>
+          <t>INSURGENTES</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>02-01-2026 20:32:36</t>
+          <t>02-01-2026 15:19:01</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3582,15 +3592,17 @@
       <c r="L48" t="n">
         <v>649</v>
       </c>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>Indefinido</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr"/>
+      <c r="M48" t="n">
+        <v>11</v>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>28-12-2026 15:19:01</t>
+        </is>
+      </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>Recurrente</t>
+          <t>Domiciliado</t>
         </is>
       </c>
       <c r="P48" t="inlineStr"/>
@@ -3601,27 +3613,27 @@
         <v>47</v>
       </c>
       <c r="B49" t="n">
-        <v>85343</v>
+        <v>85415</v>
       </c>
       <c r="C49" t="n">
-        <v>237668</v>
+        <v>331592</v>
       </c>
       <c r="D49" t="n">
-        <v>35173</v>
+        <v>16646</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AARON RUIZ  MARTINEZ</t>
+          <t>EMILIOALONSO BARCENAS REYES</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>SAN LUIS</t>
+          <t>INSURGENTES</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>02-01-2026 10:58:21</t>
+          <t>02-01-2026 16:30:03</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -3643,14 +3655,14 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>549</v>
+        <v>649</v>
       </c>
       <c r="M49" t="n">
         <v>11</v>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>28-12-2026 10:58:21</t>
+          <t>28-12-2026 16:30:03</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
@@ -3666,27 +3678,27 @@
         <v>48</v>
       </c>
       <c r="B50" t="n">
-        <v>85354</v>
+        <v>85417</v>
       </c>
       <c r="C50" t="n">
-        <v>331482</v>
+        <v>331598</v>
       </c>
       <c r="D50" t="n">
-        <v>16536</v>
+        <v>16652</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>DORA ARACELI DIAZ  VILLARREAL</t>
+          <t>ISLAS BERENICE DIAZ  BARRIGA</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>SALTILLO VILLALTA</t>
+          <t>TLALNEPANTLA</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>02-01-2026 11:34:09</t>
+          <t>02-01-2026 16:41:33</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3708,14 +3720,14 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>649</v>
+        <v>549</v>
       </c>
       <c r="M50" t="n">
         <v>11</v>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>28-12-2026 11:34:09</t>
+          <t>28-12-2026 16:41:33</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
@@ -3731,32 +3743,32 @@
         <v>49</v>
       </c>
       <c r="B51" t="n">
-        <v>85361</v>
+        <v>85430</v>
       </c>
       <c r="C51" t="n">
-        <v>147484</v>
+        <v>283380</v>
       </c>
       <c r="D51" t="n">
-        <v>45060</v>
+        <v>80881</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>STEPHANYA PEREZ FERNANDEZ</t>
+          <t>BRIANDA LIZETH TAMAYO URQUIDEZ</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>PASEO LA PAZ</t>
+          <t>VILLA VERDE MEXICALI</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>02-01-2026 11:58:21</t>
+          <t>02-01-2026 18:52:42</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>02-02-2026 23:59:59</t>
         </is>
       </c>
       <c r="I51" t="n">
@@ -3773,14 +3785,14 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>1449</v>
+        <v>549</v>
       </c>
       <c r="M51" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>28-12-2026 11:58:21</t>
+          <t>28-12-2026 18:52:42</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
@@ -3796,27 +3808,27 @@
         <v>50</v>
       </c>
       <c r="B52" t="n">
-        <v>85368</v>
+        <v>85434</v>
       </c>
       <c r="C52" t="n">
-        <v>331520</v>
+        <v>331655</v>
       </c>
       <c r="D52" t="n">
-        <v>16574</v>
+        <v>16709</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>KARLA EDITH TOVAR ROSALES</t>
+          <t>JOSE ISRAEL  VARGAS  VALDEZ</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>SALTILLO VILLALTA</t>
+          <t>SENDERO CULIACAN</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>02-01-2026 12:28:57</t>
+          <t>02-01-2026 19:47:46</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3840,17 +3852,15 @@
       <c r="L52" t="n">
         <v>649</v>
       </c>
-      <c r="M52" t="n">
-        <v>11</v>
-      </c>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t>28-12-2026 12:28:57</t>
-        </is>
-      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="O52" t="inlineStr">
         <is>
-          <t>Domiciliado</t>
+          <t>Recurrente</t>
         </is>
       </c>
       <c r="P52" t="inlineStr"/>
@@ -3861,32 +3871,32 @@
         <v>51</v>
       </c>
       <c r="B53" t="n">
-        <v>85379</v>
+        <v>85447</v>
       </c>
       <c r="C53" t="n">
-        <v>331543</v>
+        <v>289813</v>
       </c>
       <c r="D53" t="n">
-        <v>16597</v>
+        <v>87311</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>JESUS  LUNA ORTIZ</t>
+          <t>JOSE  GONZALEZ TORRES</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>INSURGENTES</t>
+          <t>VILLA VERDE MEXICALI</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>02-01-2026 13:33:07</t>
+          <t>03-01-2026 10:07:28</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>03-02-2026 23:59:59</t>
         </is>
       </c>
       <c r="I53" t="n">
@@ -3899,18 +3909,18 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>NUEVO</t>
+          <t>RENOVACIÓN</t>
         </is>
       </c>
       <c r="L53" t="n">
-        <v>1549</v>
+        <v>749</v>
       </c>
       <c r="M53" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>28-12-2026 13:33:07</t>
+          <t>29-12-2026 10:07:28</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
@@ -3918,7 +3928,9 @@
           <t>Domiciliado</t>
         </is>
       </c>
-      <c r="P53" t="inlineStr"/>
+      <c r="P53" t="n">
+        <v>64519</v>
+      </c>
       <c r="Q53" t="inlineStr"/>
     </row>
     <row r="54">
@@ -3926,32 +3938,32 @@
         <v>52</v>
       </c>
       <c r="B54" t="n">
-        <v>85386</v>
+        <v>85449</v>
       </c>
       <c r="C54" t="n">
-        <v>331546</v>
+        <v>276028</v>
       </c>
       <c r="D54" t="n">
-        <v>16600</v>
+        <v>73530</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>ITZETL QUIROZ SANTANA</t>
+          <t>DANIEL SAID  BARRAZA MARTINEZ</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>METEPEC</t>
+          <t>SENDERO CHIHUAHUA</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>02-01-2026 14:03:16</t>
+          <t>03-01-2026 10:28:41</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>02-02-2026 23:59:59</t>
+          <t>03-02-2026 23:59:59</t>
         </is>
       </c>
       <c r="I54" t="n">
@@ -3968,14 +3980,14 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>649</v>
+        <v>549</v>
       </c>
       <c r="M54" t="n">
         <v>11</v>
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>28-12-2026 14:03:16</t>
+          <t>29-12-2026 10:28:41</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
@@ -3991,32 +4003,32 @@
         <v>53</v>
       </c>
       <c r="B55" t="n">
-        <v>85393</v>
+        <v>85464</v>
       </c>
       <c r="C55" t="n">
-        <v>200198</v>
+        <v>331726</v>
       </c>
       <c r="D55" t="n">
-        <v>97705</v>
+        <v>16780</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>MARCO ANTONIO GONZALEZ  HERRERA</t>
+          <t>DIEGO EDUARDO  RODRIGUEZ ANDRES</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>SENDERO CHIHUAHUA</t>
+          <t>TLALNEPANTLA</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>02-01-2026 14:34:57</t>
+          <t>03-01-2026 11:45:32</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>02-02-2026 23:59:59</t>
+          <t>03-02-2026 23:59:59</t>
         </is>
       </c>
       <c r="I55" t="n">
@@ -4040,7 +4052,7 @@
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>28-12-2026 14:34:57</t>
+          <t>29-12-2026 11:45:32</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
@@ -4056,34 +4068,32 @@
         <v>54</v>
       </c>
       <c r="B56" t="n">
-        <v>85404</v>
+        <v>85466</v>
       </c>
       <c r="C56" t="n">
-        <v>7025</v>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>05960</t>
-        </is>
+        <v>331729</v>
+      </c>
+      <c r="D56" t="n">
+        <v>16783</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>LUIS ANDRES  FRAUSTO HERRERA</t>
+          <t>ARTURO DARIO COLIN ARRIAGA</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>VILLA VERDE MEXICALI</t>
+          <t>METEPEC</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>02-01-2026 15:36:10</t>
+          <t>03-01-2026 11:57:25</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>03-02-2026 23:59:59</t>
         </is>
       </c>
       <c r="I56" t="n">
@@ -4100,14 +4110,14 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>1449</v>
+        <v>649</v>
       </c>
       <c r="M56" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>28-12-2026 15:36:10</t>
+          <t>29-12-2026 11:57:25</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
@@ -4123,32 +4133,32 @@
         <v>55</v>
       </c>
       <c r="B57" t="n">
-        <v>85418</v>
+        <v>85481</v>
       </c>
       <c r="C57" t="n">
-        <v>331600</v>
+        <v>331741</v>
       </c>
       <c r="D57" t="n">
-        <v>16654</v>
+        <v>16795</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>ALEJANDRA RUIZ JAIME</t>
+          <t>JESUS DAMIAN  ESTRADA GALINDO</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>INSURGENTES</t>
+          <t>SALTILLO VILLALTA</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>02-01-2026 16:45:31</t>
+          <t>03-01-2026 13:02:29</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>03-02-2026 23:59:59</t>
         </is>
       </c>
       <c r="I57" t="n">
@@ -4165,17 +4175,19 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>1549</v>
-      </c>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>Indefinido</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr"/>
+        <v>649</v>
+      </c>
+      <c r="M57" t="n">
+        <v>11</v>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>29-12-2026 13:02:29</t>
+        </is>
+      </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>Recurrente</t>
+          <t>Domiciliado</t>
         </is>
       </c>
       <c r="P57" t="inlineStr"/>
@@ -4186,32 +4198,32 @@
         <v>56</v>
       </c>
       <c r="B58" t="n">
-        <v>85429</v>
+        <v>85498</v>
       </c>
       <c r="C58" t="n">
-        <v>331631</v>
+        <v>331767</v>
       </c>
       <c r="D58" t="n">
-        <v>16685</v>
+        <v>16571</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AZAET RIVERA BOLAÑOS</t>
+          <t>ZOLEDI JAQUELINE  AZAMAR  MORALES</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>PASEO 2000</t>
+          <t>CARROUSEL TIJUANA</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>02-01-2026 18:05:40</t>
+          <t>03-01-2026 16:13:54</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>02-02-2026 23:59:59</t>
+          <t>03-02-2026 23:59:59</t>
         </is>
       </c>
       <c r="I58" t="n">
@@ -4228,19 +4240,17 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>549</v>
-      </c>
-      <c r="M58" t="n">
-        <v>11</v>
-      </c>
-      <c r="N58" t="inlineStr">
-        <is>
-          <t>28-12-2026 18:05:40</t>
-        </is>
-      </c>
+        <v>649</v>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr"/>
       <c r="O58" t="inlineStr">
         <is>
-          <t>Domiciliado</t>
+          <t>Recurrente</t>
         </is>
       </c>
       <c r="P58" t="inlineStr"/>
@@ -4251,32 +4261,32 @@
         <v>57</v>
       </c>
       <c r="B59" t="n">
-        <v>85436</v>
+        <v>85500</v>
       </c>
       <c r="C59" t="n">
-        <v>287987</v>
+        <v>331769</v>
       </c>
       <c r="D59" t="n">
-        <v>85485</v>
+        <v>16573</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>JOSUE ALFONZO PEREZ CASTILLON</t>
+          <t>CARLOS  OCAÑA PONCE</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>VILLAS DEL REY</t>
+          <t>METEPEC</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>02-01-2026 20:56:57</t>
+          <t>03-01-2026 16:56:25</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>02-02-2026 23:59:59</t>
+          <t>03-02-2026 23:59:59</t>
         </is>
       </c>
       <c r="I59" t="n">
@@ -4289,18 +4299,18 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>RENOVACIÓN</t>
+          <t>NUEVO</t>
         </is>
       </c>
       <c r="L59" t="n">
-        <v>749</v>
+        <v>649</v>
       </c>
       <c r="M59" t="n">
         <v>11</v>
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>28-12-2026 20:56:57</t>
+          <t>29-12-2026 16:56:25</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
@@ -4308,9 +4318,7 @@
           <t>Domiciliado</t>
         </is>
       </c>
-      <c r="P59" t="n">
-        <v>63526</v>
-      </c>
+      <c r="P59" t="inlineStr"/>
       <c r="Q59" t="inlineStr"/>
     </row>
     <row r="60">
@@ -4318,27 +4326,27 @@
         <v>58</v>
       </c>
       <c r="B60" t="n">
-        <v>83325</v>
+        <v>84806</v>
       </c>
       <c r="C60" t="n">
-        <v>21709</v>
+        <v>326368</v>
       </c>
       <c r="D60" t="n">
-        <v>20609</v>
+        <v>23307</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>MIGUEL FRANCISCO ROJO GARCIA</t>
+          <t>PEDRO MIGUEL  QUINTERO CUEVAS</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>SENDERO CULIACAN</t>
+          <t>CARROUSEL TIJUANA</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>03-12-2025 6:36:50</t>
+          <t>28-12-2025 10:09:30</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4362,21 +4370,19 @@
       <c r="L60" t="n">
         <v>399</v>
       </c>
-      <c r="M60" t="n">
-        <v>11</v>
-      </c>
-      <c r="N60" t="inlineStr">
-        <is>
-          <t>28-11-2026 6:36:50</t>
-        </is>
-      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr"/>
       <c r="O60" t="inlineStr">
         <is>
-          <t>Domiciliado</t>
+          <t>Recurrente</t>
         </is>
       </c>
       <c r="P60" t="n">
-        <v>2380</v>
+        <v>83261</v>
       </c>
       <c r="Q60" t="inlineStr"/>
     </row>
@@ -4385,27 +4391,27 @@
         <v>59</v>
       </c>
       <c r="B61" t="n">
-        <v>83410</v>
+        <v>85342</v>
       </c>
       <c r="C61" t="n">
-        <v>172707</v>
+        <v>331486</v>
       </c>
       <c r="D61" t="n">
-        <v>70226</v>
+        <v>16540</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>LUIS ANGEL  FLORES MARTINEZ</t>
+          <t>LETICIA DE LEON OLGUIN</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>PASEO LA PAZ</t>
+          <t>TEC MEXICALI</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>04-12-2025 5:25:36</t>
+          <t>02-01-2026 10:56:44</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4423,18 +4429,18 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>RENOVACIÓN</t>
+          <t>NUEVO</t>
         </is>
       </c>
       <c r="L61" t="n">
-        <v>399</v>
+        <v>549</v>
       </c>
       <c r="M61" t="n">
         <v>11</v>
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>29-11-2026 5:25:36</t>
+          <t>28-12-2026 10:56:44</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
@@ -4442,9 +4448,7 @@
           <t>Domiciliado</t>
         </is>
       </c>
-      <c r="P61" t="n">
-        <v>8022</v>
-      </c>
+      <c r="P61" t="inlineStr"/>
       <c r="Q61" t="inlineStr"/>
     </row>
     <row r="62">
@@ -4452,32 +4456,32 @@
         <v>60</v>
       </c>
       <c r="B62" t="n">
-        <v>84880</v>
+        <v>85355</v>
       </c>
       <c r="C62" t="n">
-        <v>127402</v>
+        <v>271763</v>
       </c>
       <c r="D62" t="n">
-        <v>25075</v>
+        <v>69265</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>NUBIA PATRICIA  RUIZ  BENCOMO</t>
+          <t>EDGAR ALARCON BARRIOS</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>SENDERO CHIHUAHUA</t>
+          <t>AZAHARES CULIACAN</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>29-12-2025 11:57:22</t>
+          <t>02-01-2026 11:34:18</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>02-02-2026 23:59:59</t>
+          <t>06-02-2026 23:59:59</t>
         </is>
       </c>
       <c r="I62" t="n">
@@ -4494,23 +4498,21 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>399</v>
-      </c>
-      <c r="M62" t="n">
-        <v>11</v>
-      </c>
-      <c r="N62" t="inlineStr">
-        <is>
-          <t>24-12-2026 11:57:22</t>
-        </is>
-      </c>
+        <v>599</v>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr"/>
       <c r="O62" t="inlineStr">
         <is>
-          <t>Domiciliado</t>
+          <t>Recurrente</t>
         </is>
       </c>
       <c r="P62" t="n">
-        <v>71334</v>
+        <v>52241</v>
       </c>
       <c r="Q62" t="inlineStr"/>
     </row>
@@ -4519,27 +4521,27 @@
         <v>61</v>
       </c>
       <c r="B63" t="n">
-        <v>85348</v>
+        <v>85356</v>
       </c>
       <c r="C63" t="n">
-        <v>331494</v>
+        <v>38424</v>
       </c>
       <c r="D63" t="n">
-        <v>16548</v>
+        <v>36301</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>SAMUEL FUENTES HERNANDEZ</t>
+          <t>BRYAN  SOQUI VERDUZCO</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>METEPEC</t>
+          <t>MISION ENSENADA</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>02-01-2026 11:12:24</t>
+          <t>02-01-2026 11:34:33</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4563,17 +4565,15 @@
       <c r="L63" t="n">
         <v>649</v>
       </c>
-      <c r="M63" t="n">
-        <v>11</v>
-      </c>
-      <c r="N63" t="inlineStr">
-        <is>
-          <t>28-12-2026 11:12:24</t>
-        </is>
-      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr"/>
       <c r="O63" t="inlineStr">
         <is>
-          <t>Domiciliado</t>
+          <t>Recurrente</t>
         </is>
       </c>
       <c r="P63" t="inlineStr"/>
@@ -4584,27 +4584,27 @@
         <v>62</v>
       </c>
       <c r="B64" t="n">
-        <v>85350</v>
+        <v>85373</v>
       </c>
       <c r="C64" t="n">
-        <v>331491</v>
+        <v>331533</v>
       </c>
       <c r="D64" t="n">
-        <v>16545</v>
+        <v>16587</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>ELIAS  GOMEZ  PONCE</t>
+          <t>JORGE JESUS  SERNA  CORREA</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>TLALNEPANTLA</t>
+          <t>METEPEC</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>02-01-2026 11:18:18</t>
+          <t>02-01-2026 13:12:58</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -4626,14 +4626,14 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>549</v>
+        <v>649</v>
       </c>
       <c r="M64" t="n">
         <v>11</v>
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>28-12-2026 11:18:18</t>
+          <t>28-12-2026 13:12:58</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
@@ -4649,32 +4649,32 @@
         <v>63</v>
       </c>
       <c r="B65" t="n">
-        <v>85365</v>
+        <v>85374</v>
       </c>
       <c r="C65" t="n">
-        <v>329705</v>
+        <v>232207</v>
       </c>
       <c r="D65" t="n">
-        <v>14759</v>
+        <v>29712</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>ESMERALDA MARTINEZ MEZA</t>
+          <t>KRISTEL LORENA MAYORQUIN  ORDOÑEZ</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>PASEO LA PAZ</t>
+          <t>SENDERO CULIACAN</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>02-01-2026 12:23:37</t>
+          <t>02-01-2026 13:19:02</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>02-02-2026 23:59:59</t>
         </is>
       </c>
       <c r="I65" t="n">
@@ -4691,19 +4691,17 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>1449</v>
-      </c>
-      <c r="M65" t="n">
-        <v>9</v>
-      </c>
-      <c r="N65" t="inlineStr">
-        <is>
-          <t>28-12-2026 12:23:37</t>
-        </is>
-      </c>
+        <v>649</v>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr"/>
       <c r="O65" t="inlineStr">
         <is>
-          <t>Domiciliado</t>
+          <t>Recurrente</t>
         </is>
       </c>
       <c r="P65" t="inlineStr"/>
@@ -4714,27 +4712,27 @@
         <v>64</v>
       </c>
       <c r="B66" t="n">
-        <v>85367</v>
+        <v>85391</v>
       </c>
       <c r="C66" t="n">
-        <v>329706</v>
+        <v>75444</v>
       </c>
       <c r="D66" t="n">
-        <v>14760</v>
+        <v>73258</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>MANUEL EZEQUIEL RAMIREZ BUSTOS</t>
+          <t>DAYANNA  LOPEZ CASTELO</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>PASEO LA PAZ</t>
+          <t>AZAHARES CULIACAN</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>02-01-2026 12:27:10</t>
+          <t>02-01-2026 14:20:50</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -4752,24 +4750,28 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>NUEVO</t>
+          <t>RENOVACIÓN</t>
         </is>
       </c>
       <c r="L66" t="n">
-        <v>649</v>
-      </c>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>Indefinido</t>
-        </is>
-      </c>
-      <c r="N66" t="inlineStr"/>
+        <v>749</v>
+      </c>
+      <c r="M66" t="n">
+        <v>11</v>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>28-12-2026 14:20:50</t>
+        </is>
+      </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>Recurrente</t>
-        </is>
-      </c>
-      <c r="P66" t="inlineStr"/>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P66" t="n">
+        <v>37414</v>
+      </c>
       <c r="Q66" t="inlineStr"/>
     </row>
     <row r="67">
@@ -4777,27 +4779,27 @@
         <v>65</v>
       </c>
       <c r="B67" t="n">
-        <v>85380</v>
+        <v>85392</v>
       </c>
       <c r="C67" t="n">
-        <v>249607</v>
+        <v>331553</v>
       </c>
       <c r="D67" t="n">
-        <v>47111</v>
+        <v>16607</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>ALEXIS FLORES GONZALEZ</t>
+          <t>KENIA LISETH RODRIGUEZ  ROMERO</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>PASEO LA PAZ</t>
+          <t>INSURGENTES</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>02-01-2026 13:40:00</t>
+          <t>02-01-2026 14:22:50</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -4815,18 +4817,18 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>RENOVACIÓN</t>
+          <t>NUEVO</t>
         </is>
       </c>
       <c r="L67" t="n">
-        <v>749</v>
+        <v>649</v>
       </c>
       <c r="M67" t="n">
         <v>11</v>
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>28-12-2026 13:40:00</t>
+          <t>28-12-2026 14:22:50</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
@@ -4834,9 +4836,7 @@
           <t>Domiciliado</t>
         </is>
       </c>
-      <c r="P67" t="n">
-        <v>53883</v>
-      </c>
+      <c r="P67" t="inlineStr"/>
       <c r="Q67" t="inlineStr"/>
     </row>
     <row r="68">
@@ -4844,32 +4844,32 @@
         <v>66</v>
       </c>
       <c r="B68" t="n">
-        <v>85397</v>
+        <v>85405</v>
       </c>
       <c r="C68" t="n">
-        <v>331571</v>
+        <v>331581</v>
       </c>
       <c r="D68" t="n">
-        <v>16625</v>
+        <v>16635</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>DIANA BERENICE  BAZAN  GARRIDO</t>
+          <t>KARINA  GARCIA GOMEZ</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>INSURGENTES</t>
+          <t>SALTILLO VILLALTA</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>02-01-2026 15:13:00</t>
+          <t>02-01-2026 15:41:24</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>02-02-2026 23:59:59</t>
         </is>
       </c>
       <c r="I68" t="n">
@@ -4886,14 +4886,14 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>1549</v>
+        <v>649</v>
       </c>
       <c r="M68" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>28-12-2026 15:13:00</t>
+          <t>28-12-2026 15:41:24</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
@@ -4909,27 +4909,27 @@
         <v>67</v>
       </c>
       <c r="B69" t="n">
-        <v>85399</v>
+        <v>85406</v>
       </c>
       <c r="C69" t="n">
-        <v>331578</v>
+        <v>331586</v>
       </c>
       <c r="D69" t="n">
-        <v>16632</v>
+        <v>16640</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>ALEX RICARDO PINTO URIBE</t>
+          <t>LUIS JAVIER MARTINEZ CELIS</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>PASEO 2000</t>
+          <t>CARROUSEL TIJUANA</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>02-01-2026 15:21:15</t>
+          <t>02-01-2026 15:49:07</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -4951,19 +4951,17 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>549</v>
-      </c>
-      <c r="M69" t="n">
-        <v>11</v>
-      </c>
-      <c r="N69" t="inlineStr">
-        <is>
-          <t>28-12-2026 15:21:15</t>
-        </is>
-      </c>
+        <v>649</v>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr"/>
       <c r="O69" t="inlineStr">
         <is>
-          <t>Domiciliado</t>
+          <t>Recurrente</t>
         </is>
       </c>
       <c r="P69" t="inlineStr"/>
@@ -4974,32 +4972,32 @@
         <v>68</v>
       </c>
       <c r="B70" t="n">
-        <v>85416</v>
+        <v>85409</v>
       </c>
       <c r="C70" t="n">
-        <v>331597</v>
+        <v>180662</v>
       </c>
       <c r="D70" t="n">
-        <v>16651</v>
+        <v>78169</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>KARLA FABIOLA  GONZALEZ ALMEIDA</t>
+          <t>MARIA AZUCENA ANASTASIO ROMUALDO</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>PASEO 2000</t>
+          <t>CARROUSEL TIJUANA</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>02-01-2026 16:36:43</t>
+          <t>02-01-2026 16:00:08</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>02-02-2026 23:59:59</t>
         </is>
       </c>
       <c r="I70" t="n">
@@ -5012,18 +5010,18 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>NUEVO</t>
+          <t>RENOVACIÓN</t>
         </is>
       </c>
       <c r="L70" t="n">
-        <v>1449</v>
+        <v>749</v>
       </c>
       <c r="M70" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>28-12-2026 16:36:43</t>
+          <t>28-12-2026 16:00:08</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
@@ -5031,7 +5029,9 @@
           <t>Domiciliado</t>
         </is>
       </c>
-      <c r="P70" t="inlineStr"/>
+      <c r="P70" t="n">
+        <v>45199</v>
+      </c>
       <c r="Q70" t="inlineStr"/>
     </row>
     <row r="71">
@@ -5039,17 +5039,17 @@
         <v>69</v>
       </c>
       <c r="B71" t="n">
-        <v>85433</v>
+        <v>83302</v>
       </c>
       <c r="C71" t="n">
-        <v>331652</v>
+        <v>326491</v>
       </c>
       <c r="D71" t="n">
-        <v>16706</v>
+        <v>23430</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>LIZETH CECILIA  SANDOVAL  YAMASHIRO</t>
+          <t>ANA CECILIA  RENTERIA  HERNANDEZ</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -5059,7 +5059,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>02-01-2026 19:44:46</t>
+          <t>02-12-2025 18:13:37</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -5077,24 +5077,28 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>NUEVO</t>
+          <t>RENOVACIÓN</t>
         </is>
       </c>
       <c r="L71" t="n">
-        <v>649</v>
-      </c>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>Indefinido</t>
-        </is>
-      </c>
-      <c r="N71" t="inlineStr"/>
+        <v>549</v>
+      </c>
+      <c r="M71" t="n">
+        <v>2</v>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>02-03-2026 18:13:37</t>
+        </is>
+      </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>Recurrente</t>
-        </is>
-      </c>
-      <c r="P71" t="inlineStr"/>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P71" t="n">
+        <v>83301</v>
+      </c>
       <c r="Q71" t="inlineStr"/>
     </row>
     <row r="72">
@@ -5102,32 +5106,32 @@
         <v>70</v>
       </c>
       <c r="B72" t="n">
-        <v>84640</v>
+        <v>85441</v>
       </c>
       <c r="C72" t="n">
-        <v>326127</v>
+        <v>331466</v>
       </c>
       <c r="D72" t="n">
-        <v>23066</v>
+        <v>16520</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>ISABEL ESPINOZA  VALENZUELA</t>
+          <t>JESMIN GUADALUPE  GUTIERREZ HERNANDEZ</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>MISION ENSENADA</t>
+          <t>SENDERO CHIHUAHUA</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>23-12-2025 16:48:33</t>
+          <t>03-01-2026 7:59:33</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>01-02-2026 23:59:59</t>
+          <t>03-02-2026 23:59:59</t>
         </is>
       </c>
       <c r="I72" t="n">
@@ -5140,18 +5144,18 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>RENOVACIÓN</t>
+          <t>NUEVO</t>
         </is>
       </c>
       <c r="L72" t="n">
-        <v>499</v>
+        <v>549</v>
       </c>
       <c r="M72" t="n">
         <v>11</v>
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>18-12-2026 16:48:33</t>
+          <t>29-12-2026 7:59:33</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
@@ -5159,9 +5163,7 @@
           <t>Domiciliado</t>
         </is>
       </c>
-      <c r="P72" t="n">
-        <v>83140</v>
-      </c>
+      <c r="P72" t="inlineStr"/>
       <c r="Q72" t="inlineStr"/>
     </row>
     <row r="73">
@@ -5169,32 +5171,32 @@
         <v>71</v>
       </c>
       <c r="B73" t="n">
-        <v>83568</v>
+        <v>85456</v>
       </c>
       <c r="C73" t="n">
-        <v>138456</v>
+        <v>331714</v>
       </c>
       <c r="D73" t="n">
-        <v>36094</v>
+        <v>16768</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>BRAYAN GAEL BALDERAS CONTRERAS</t>
+          <t>BELEN CECILIA ARCE VILLAVICENCIO</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>SENDERO SALTILLO</t>
+          <t>PASEO LA PAZ</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>08-12-2025 7:50:26</t>
+          <t>03-01-2026 10:43:52</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>02-02-2026 23:59:59</t>
+          <t>03-02-2026 23:59:59</t>
         </is>
       </c>
       <c r="I73" t="n">
@@ -5207,28 +5209,24 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>RENOVACIÓN</t>
+          <t>NUEVO</t>
         </is>
       </c>
       <c r="L73" t="n">
-        <v>549</v>
-      </c>
-      <c r="M73" t="n">
-        <v>5</v>
-      </c>
-      <c r="N73" t="inlineStr">
-        <is>
-          <t>06-06-2026 7:50:26</t>
-        </is>
-      </c>
+        <v>649</v>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr"/>
       <c r="O73" t="inlineStr">
         <is>
-          <t>Domiciliado</t>
-        </is>
-      </c>
-      <c r="P73" t="n">
-        <v>70999</v>
-      </c>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr"/>
       <c r="Q73" t="inlineStr"/>
     </row>
     <row r="74">
@@ -5236,32 +5234,32 @@
         <v>72</v>
       </c>
       <c r="B74" t="n">
-        <v>85072</v>
+        <v>85459</v>
       </c>
       <c r="C74" t="n">
-        <v>18849</v>
+        <v>331719</v>
       </c>
       <c r="D74" t="n">
-        <v>17752</v>
+        <v>16773</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>REYNA GABRIELA CASTAÑEDA  PACHECO</t>
+          <t>NAOMI ESCALERA  HERNANDEZ</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>TEC MEXICALI</t>
+          <t>IXTAPALUCA</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>30-12-2025 12:26:35</t>
+          <t>03-01-2026 11:08:08</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>02-02-2026 23:59:59</t>
+          <t>03-02-2026 23:59:59</t>
         </is>
       </c>
       <c r="I74" t="n">
@@ -5274,18 +5272,18 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>RENOVACIÓN</t>
+          <t>NUEVO</t>
         </is>
       </c>
       <c r="L74" t="n">
-        <v>399</v>
+        <v>549</v>
       </c>
       <c r="M74" t="n">
         <v>11</v>
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>25-12-2026 12:26:35</t>
+          <t>29-12-2026 11:08:08</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
@@ -5293,9 +5291,7 @@
           <t>Domiciliado</t>
         </is>
       </c>
-      <c r="P74" t="n">
-        <v>71103</v>
-      </c>
+      <c r="P74" t="inlineStr"/>
       <c r="Q74" t="inlineStr"/>
     </row>
     <row r="75">
@@ -5303,17 +5299,17 @@
         <v>73</v>
       </c>
       <c r="B75" t="n">
-        <v>85357</v>
+        <v>85473</v>
       </c>
       <c r="C75" t="n">
-        <v>331506</v>
+        <v>331735</v>
       </c>
       <c r="D75" t="n">
-        <v>16560</v>
+        <v>16789</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>OMAR ANTONIO  HERNANDEZ HERNANDEZ</t>
+          <t>EMILIANO SOLACHE  VILCHIS</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -5323,12 +5319,12 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>02-01-2026 11:40:03</t>
+          <t>03-01-2026 12:44:05</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>02-02-2026 23:59:59</t>
+          <t>03-02-2026 23:59:59</t>
         </is>
       </c>
       <c r="I75" t="n">
@@ -5352,7 +5348,7 @@
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>28-12-2026 11:40:03</t>
+          <t>29-12-2026 12:44:05</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
@@ -5368,32 +5364,32 @@
         <v>74</v>
       </c>
       <c r="B76" t="n">
-        <v>85358</v>
+        <v>85474</v>
       </c>
       <c r="C76" t="n">
-        <v>331497</v>
+        <v>331737</v>
       </c>
       <c r="D76" t="n">
-        <v>16551</v>
+        <v>16791</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AMERICA YANDELLI PALACIOS GAONA</t>
+          <t>ZULEMA MONTSERRAT SILLER RIVERA</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>SALTILLO VILLALTA</t>
+          <t>SENDERO SALTILLO</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>02-01-2026 11:42:53</t>
+          <t>03-01-2026 12:44:09</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>02-02-2026 23:59:59</t>
+          <t>03-02-2026 23:59:59</t>
         </is>
       </c>
       <c r="I76" t="n">
@@ -5410,14 +5406,14 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>649</v>
+        <v>549</v>
       </c>
       <c r="M76" t="n">
         <v>11</v>
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>28-12-2026 11:42:53</t>
+          <t>29-12-2026 12:44:09</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
@@ -5433,32 +5429,34 @@
         <v>75</v>
       </c>
       <c r="B77" t="n">
-        <v>85372</v>
+        <v>85491</v>
       </c>
       <c r="C77" t="n">
-        <v>331528</v>
-      </c>
-      <c r="D77" t="n">
-        <v>16582</v>
+        <v>307515</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>05014</t>
+        </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>EDGAR MANUEL GONZALEZ RUBIO GARCIA</t>
+          <t>MARIA ISABEL SANCHEZ JIMENEZ</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>PASEO LA PAZ</t>
+          <t>INDEPENDENCIA</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>02-01-2026 12:58:52</t>
+          <t>03-01-2026 14:15:42</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>02-02-2026 23:59:59</t>
+          <t>03-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="I77" t="n">
@@ -5475,14 +5473,14 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>549</v>
+        <v>1449</v>
       </c>
       <c r="M77" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>28-12-2026 12:58:52</t>
+          <t>29-12-2026 14:15:42</t>
         </is>
       </c>
       <c r="O77" t="inlineStr">
@@ -5498,32 +5496,32 @@
         <v>76</v>
       </c>
       <c r="B78" t="n">
-        <v>85375</v>
+        <v>85492</v>
       </c>
       <c r="C78" t="n">
-        <v>331524</v>
+        <v>331757</v>
       </c>
       <c r="D78" t="n">
-        <v>16578</v>
+        <v>16811</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>MAYRA GUADALUPE PARRA  RIVERA</t>
+          <t>VICTOR ALFONSO SANTOSCOY AVILA</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>SENDERO SALTILLO</t>
+          <t>SALTILLO VILLALTA</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>02-01-2026 13:19:59</t>
+          <t>03-01-2026 14:43:56</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>02-02-2026 23:59:59</t>
+          <t>03-02-2026 23:59:59</t>
         </is>
       </c>
       <c r="I78" t="n">
@@ -5540,14 +5538,14 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>549</v>
+        <v>649</v>
       </c>
       <c r="M78" t="n">
         <v>11</v>
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>28-12-2026 13:19:59</t>
+          <t>29-12-2026 14:43:56</t>
         </is>
       </c>
       <c r="O78" t="inlineStr">
@@ -5563,32 +5561,32 @@
         <v>77</v>
       </c>
       <c r="B79" t="n">
-        <v>85389</v>
+        <v>83154</v>
       </c>
       <c r="C79" t="n">
-        <v>331555</v>
+        <v>319772</v>
       </c>
       <c r="D79" t="n">
-        <v>16609</v>
+        <v>17269</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>RICARDO  URIAS  QUINTERO</t>
+          <t>ADRIAN ALEJANDRO ESCUTIA MUÑIZ</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>SENDERO CULIACAN</t>
+          <t>INSURGENTES</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>02-01-2026 14:20:20</t>
+          <t>01-12-2025 12:03:42</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>02-02-2026 23:59:59</t>
+          <t>28-01-2026 23:59:59</t>
         </is>
       </c>
       <c r="I79" t="n">
@@ -5601,24 +5599,28 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>NUEVO</t>
+          <t>RENOVACIÓN</t>
         </is>
       </c>
       <c r="L79" t="n">
-        <v>649</v>
-      </c>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>Indefinido</t>
-        </is>
-      </c>
-      <c r="N79" t="inlineStr"/>
+        <v>599</v>
+      </c>
+      <c r="M79" t="n">
+        <v>11</v>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>26-11-2026 12:03:42</t>
+        </is>
+      </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>Recurrente</t>
-        </is>
-      </c>
-      <c r="P79" t="inlineStr"/>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P79" t="n">
+        <v>80928</v>
+      </c>
       <c r="Q79" t="inlineStr"/>
     </row>
     <row r="80">
@@ -5626,32 +5628,32 @@
         <v>78</v>
       </c>
       <c r="B80" t="n">
-        <v>85390</v>
+        <v>83379</v>
       </c>
       <c r="C80" t="n">
-        <v>329954</v>
+        <v>230054</v>
       </c>
       <c r="D80" t="n">
-        <v>15008</v>
+        <v>27559</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>VIRIDIANA  GONZALEZ PULIDO</t>
+          <t>JUDITH  CERECEDO HERNANDEZ</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>PASEO 2000</t>
+          <t>SANTA CATARINA</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>02-01-2026 14:20:33</t>
+          <t>03-12-2025 16:51:46</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>02-02-2026 23:59:59</t>
+          <t>03-02-2026 23:59:59</t>
         </is>
       </c>
       <c r="I80" t="n">
@@ -5664,26 +5666,26 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>NUEVO</t>
+          <t>RENOVACIÓN</t>
         </is>
       </c>
       <c r="L80" t="n">
-        <v>549</v>
-      </c>
-      <c r="M80" t="n">
-        <v>11</v>
-      </c>
-      <c r="N80" t="inlineStr">
-        <is>
-          <t>28-12-2026 14:20:33</t>
-        </is>
-      </c>
+        <v>599</v>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr"/>
       <c r="O80" t="inlineStr">
         <is>
-          <t>Domiciliado</t>
-        </is>
-      </c>
-      <c r="P80" t="inlineStr"/>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P80" t="n">
+        <v>62572</v>
+      </c>
       <c r="Q80" t="inlineStr"/>
     </row>
     <row r="81">
@@ -5691,27 +5693,27 @@
         <v>79</v>
       </c>
       <c r="B81" t="n">
-        <v>85407</v>
+        <v>85351</v>
       </c>
       <c r="C81" t="n">
-        <v>331583</v>
+        <v>331489</v>
       </c>
       <c r="D81" t="n">
-        <v>16637</v>
+        <v>16543</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RENATA GONZALEZ GOMEZ</t>
+          <t>ADRIANA VELASCO  RAMIREZ</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>SALTILLO VILLALTA</t>
+          <t>TLALNEPANTLA</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>02-01-2026 15:51:20</t>
+          <t>02-01-2026 11:23:45</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -5733,14 +5735,14 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>649</v>
+        <v>549</v>
       </c>
       <c r="M81" t="n">
         <v>11</v>
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>28-12-2026 15:51:20</t>
+          <t>28-12-2026 11:23:45</t>
         </is>
       </c>
       <c r="O81" t="inlineStr">
@@ -5756,27 +5758,27 @@
         <v>80</v>
       </c>
       <c r="B82" t="n">
-        <v>85408</v>
+        <v>85353</v>
       </c>
       <c r="C82" t="n">
-        <v>331588</v>
+        <v>331504</v>
       </c>
       <c r="D82" t="n">
-        <v>16642</v>
+        <v>16558</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>ROMINA SOSA SOLIS</t>
+          <t>ANGEL  DURAN  VIZUET</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>SALTILLO VILLALTA</t>
+          <t>TLALNEPANTLA</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>02-01-2026 15:58:45</t>
+          <t>02-01-2026 11:33:22</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -5798,14 +5800,14 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>649</v>
+        <v>549</v>
       </c>
       <c r="M82" t="n">
         <v>11</v>
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>28-12-2026 15:58:45</t>
+          <t>28-12-2026 11:33:22</t>
         </is>
       </c>
       <c r="O82" t="inlineStr">
@@ -5821,27 +5823,27 @@
         <v>81</v>
       </c>
       <c r="B83" t="n">
-        <v>85422</v>
+        <v>85362</v>
       </c>
       <c r="C83" t="n">
-        <v>323721</v>
+        <v>114321</v>
       </c>
       <c r="D83" t="n">
-        <v>20660</v>
+        <v>12050</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>JAVIER HERNÁNDEZ CHÁVEZ</t>
+          <t>NELLY SOFIA  GONZALEZ  OLIVARES</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>INSURGENTES</t>
+          <t>SANTA CATARINA</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>02-01-2026 17:09:25</t>
+          <t>02-01-2026 12:02:44</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -5863,14 +5865,14 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>649</v>
+        <v>549</v>
       </c>
       <c r="M83" t="n">
         <v>11</v>
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>28-12-2026 17:09:25</t>
+          <t>28-12-2026 12:02:44</t>
         </is>
       </c>
       <c r="O83" t="inlineStr">
@@ -5886,27 +5888,27 @@
         <v>82</v>
       </c>
       <c r="B84" t="n">
-        <v>85425</v>
+        <v>85387</v>
       </c>
       <c r="C84" t="n">
-        <v>234864</v>
+        <v>331550</v>
       </c>
       <c r="D84" t="n">
-        <v>32369</v>
+        <v>16604</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>SARAH  MORENO URIARTE</t>
+          <t>ADRIAN ANTONIO CORDERO CALDERON</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>SENDERO CULIACAN</t>
+          <t>SENDERO CHIHUAHUA</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>02-01-2026 17:35:16</t>
+          <t>02-01-2026 14:09:47</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -5935,7 +5937,7 @@
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>28-12-2026 17:35:16</t>
+          <t>28-12-2026 14:09:47</t>
         </is>
       </c>
       <c r="O84" t="inlineStr">
@@ -5951,32 +5953,32 @@
         <v>83</v>
       </c>
       <c r="B85" t="n">
-        <v>85439</v>
+        <v>85419</v>
       </c>
       <c r="C85" t="n">
-        <v>331457</v>
+        <v>331608</v>
       </c>
       <c r="D85" t="n">
-        <v>16511</v>
+        <v>16662</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>CESAR BELLO LAGUNEZ</t>
+          <t>MARIA ANTONIETA  GERARDO PEREZ DE ALBA</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>PASEO 2000</t>
+          <t>SENDERO MEXICALI</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>03-01-2026 6:29:18</t>
+          <t>02-01-2026 16:56:39</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>03-02-2026 23:59:59</t>
+          <t>02-02-2026 23:59:59</t>
         </is>
       </c>
       <c r="I85" t="n">
@@ -6000,7 +6002,7 @@
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>29-12-2026 6:29:18</t>
+          <t>28-12-2026 16:56:39</t>
         </is>
       </c>
       <c r="O85" t="inlineStr">
@@ -6016,32 +6018,32 @@
         <v>84</v>
       </c>
       <c r="B86" t="n">
-        <v>85440</v>
+        <v>85421</v>
       </c>
       <c r="C86" t="n">
-        <v>331680</v>
+        <v>96568</v>
       </c>
       <c r="D86" t="n">
-        <v>16734</v>
+        <v>94327</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>GUADALUPE MARGARITA MENDOZA  HUERTA</t>
+          <t>CARLOS HERNANDEZ YEPIZ</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>PASEO LA PAZ</t>
+          <t>SENDERO MEXICALI</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>03-01-2026 7:10:20</t>
+          <t>02-01-2026 17:09:17</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>03-02-2026 23:59:59</t>
+          <t>02-02-2026 23:59:59</t>
         </is>
       </c>
       <c r="I86" t="n">
@@ -6065,7 +6067,7 @@
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>29-12-2026 7:10:20</t>
+          <t>28-12-2026 17:09:17</t>
         </is>
       </c>
       <c r="O86" t="inlineStr">
@@ -6077,27 +6079,4063 @@
       <c r="Q86" t="inlineStr"/>
     </row>
     <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>Reporte generado: 03-01-2026 03:23 p. m.</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr"/>
-      <c r="C87" t="inlineStr"/>
-      <c r="D87" t="inlineStr"/>
-      <c r="E87" t="inlineStr"/>
-      <c r="F87" t="inlineStr"/>
-      <c r="G87" t="inlineStr"/>
-      <c r="H87" t="inlineStr"/>
-      <c r="I87" t="inlineStr"/>
-      <c r="J87" t="inlineStr"/>
-      <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
-      <c r="M87" t="inlineStr"/>
-      <c r="N87" t="inlineStr"/>
-      <c r="O87" t="inlineStr"/>
+      <c r="A87" t="n">
+        <v>85</v>
+      </c>
+      <c r="B87" t="n">
+        <v>85428</v>
+      </c>
+      <c r="C87" t="n">
+        <v>331623</v>
+      </c>
+      <c r="D87" t="n">
+        <v>16677</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>DANIEL  SALINAS  HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>TLALNEPANTLA</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>02-01-2026 17:58:49</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>02-02-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I87" t="n">
+        <v>0</v>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L87" t="n">
+        <v>549</v>
+      </c>
+      <c r="M87" t="n">
+        <v>11</v>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>28-12-2026 17:58:49</t>
+        </is>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr"/>
       <c r="Q87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>86</v>
+      </c>
+      <c r="B88" t="n">
+        <v>85451</v>
+      </c>
+      <c r="C88" t="n">
+        <v>287597</v>
+      </c>
+      <c r="D88" t="n">
+        <v>85095</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>MIGUEL EDUARDO DIAZ ROMERO</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>VILLAS DEL REY</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>03-01-2026 10:32:05</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>03-02-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I88" t="n">
+        <v>0</v>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L88" t="n">
+        <v>749</v>
+      </c>
+      <c r="M88" t="n">
+        <v>11</v>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>29-12-2026 10:32:05</t>
+        </is>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P88" t="n">
+        <v>63779</v>
+      </c>
+      <c r="Q88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>87</v>
+      </c>
+      <c r="B89" t="n">
+        <v>85453</v>
+      </c>
+      <c r="C89" t="n">
+        <v>331700</v>
+      </c>
+      <c r="D89" t="n">
+        <v>16754</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>ITZEL YOCELIN  SANCHEZ URBINA</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>TLALNEPANTLA</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>03-01-2026 10:36:15</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>03-02-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I89" t="n">
+        <v>0</v>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L89" t="n">
+        <v>549</v>
+      </c>
+      <c r="M89" t="n">
+        <v>11</v>
+      </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>29-12-2026 10:36:15</t>
+        </is>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P89" t="inlineStr"/>
+      <c r="Q89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>88</v>
+      </c>
+      <c r="B90" t="n">
+        <v>85455</v>
+      </c>
+      <c r="C90" t="n">
+        <v>331703</v>
+      </c>
+      <c r="D90" t="n">
+        <v>16757</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>HORTENCIA URBINA  LOPEZ</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>TLALNEPANTLA</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>03-01-2026 10:40:35</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>03-02-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I90" t="n">
+        <v>0</v>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L90" t="n">
+        <v>549</v>
+      </c>
+      <c r="M90" t="n">
+        <v>11</v>
+      </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>29-12-2026 10:40:35</t>
+        </is>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P90" t="inlineStr"/>
+      <c r="Q90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>89</v>
+      </c>
+      <c r="B91" t="n">
+        <v>85485</v>
+      </c>
+      <c r="C91" t="n">
+        <v>141866</v>
+      </c>
+      <c r="D91" t="n">
+        <v>39484</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>PERLA VIRIDIANA MARTINEZ BELTRAN</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>PASEO LA PAZ</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>03-01-2026 13:25:41</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>03-02-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I91" t="n">
+        <v>0</v>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L91" t="n">
+        <v>649</v>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr"/>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P91" t="inlineStr"/>
+      <c r="Q91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>90</v>
+      </c>
+      <c r="B92" t="n">
+        <v>85487</v>
+      </c>
+      <c r="C92" t="n">
+        <v>331748</v>
+      </c>
+      <c r="D92" t="n">
+        <v>16802</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>DANNA ALEJANDRA VAZQUEZ MARTINEZ</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>PASEO LA PAZ</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>03-01-2026 13:33:40</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>03-02-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I92" t="n">
+        <v>0</v>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L92" t="n">
+        <v>649</v>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr"/>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P92" t="inlineStr"/>
+      <c r="Q92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>91</v>
+      </c>
+      <c r="B93" t="n">
+        <v>85494</v>
+      </c>
+      <c r="C93" t="n">
+        <v>331759</v>
+      </c>
+      <c r="D93" t="n">
+        <v>16813</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>ABRAHAM  REYES  GONZALEZ</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>METEPEC</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>03-01-2026 15:17:09</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>03-02-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I93" t="n">
+        <v>0</v>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L93" t="n">
+        <v>649</v>
+      </c>
+      <c r="M93" t="n">
+        <v>11</v>
+      </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>29-12-2026 15:17:09</t>
+        </is>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P93" t="inlineStr"/>
+      <c r="Q93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>92</v>
+      </c>
+      <c r="B94" t="n">
+        <v>85496</v>
+      </c>
+      <c r="C94" t="n">
+        <v>331763</v>
+      </c>
+      <c r="D94" t="n">
+        <v>16817</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>RODRIGO  AVILA  LOBATO</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>METEPEC</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>03-01-2026 16:03:10</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>03-02-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I94" t="n">
+        <v>0</v>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L94" t="n">
+        <v>649</v>
+      </c>
+      <c r="M94" t="n">
+        <v>11</v>
+      </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>29-12-2026 16:03:10</t>
+        </is>
+      </c>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P94" t="inlineStr"/>
+      <c r="Q94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>93</v>
+      </c>
+      <c r="B95" t="n">
+        <v>84880</v>
+      </c>
+      <c r="C95" t="n">
+        <v>127402</v>
+      </c>
+      <c r="D95" t="n">
+        <v>25075</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>NUBIA PATRICIA  RUIZ  BENCOMO</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>SENDERO CHIHUAHUA</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>29-12-2025 11:57:22</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>02-02-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I95" t="n">
+        <v>0</v>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L95" t="n">
+        <v>399</v>
+      </c>
+      <c r="M95" t="n">
+        <v>11</v>
+      </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>24-12-2026 11:57:22</t>
+        </is>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P95" t="n">
+        <v>71334</v>
+      </c>
+      <c r="Q95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>94</v>
+      </c>
+      <c r="B96" t="n">
+        <v>83325</v>
+      </c>
+      <c r="C96" t="n">
+        <v>21709</v>
+      </c>
+      <c r="D96" t="n">
+        <v>20609</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>MIGUEL FRANCISCO ROJO GARCIA</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>SENDERO CULIACAN</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>03-12-2025 6:36:50</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>02-02-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I96" t="n">
+        <v>0</v>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L96" t="n">
+        <v>399</v>
+      </c>
+      <c r="M96" t="n">
+        <v>11</v>
+      </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>28-11-2026 6:36:50</t>
+        </is>
+      </c>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P96" t="n">
+        <v>2380</v>
+      </c>
+      <c r="Q96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>95</v>
+      </c>
+      <c r="B97" t="n">
+        <v>83410</v>
+      </c>
+      <c r="C97" t="n">
+        <v>172707</v>
+      </c>
+      <c r="D97" t="n">
+        <v>70226</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>LUIS ANGEL  FLORES MARTINEZ</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>PASEO LA PAZ</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>04-12-2025 5:25:36</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>02-02-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I97" t="n">
+        <v>0</v>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L97" t="n">
+        <v>399</v>
+      </c>
+      <c r="M97" t="n">
+        <v>11</v>
+      </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>29-11-2026 5:25:36</t>
+        </is>
+      </c>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P97" t="n">
+        <v>8022</v>
+      </c>
+      <c r="Q97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>96</v>
+      </c>
+      <c r="B98" t="n">
+        <v>85348</v>
+      </c>
+      <c r="C98" t="n">
+        <v>331494</v>
+      </c>
+      <c r="D98" t="n">
+        <v>16548</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>SAMUEL FUENTES HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>METEPEC</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>02-01-2026 11:12:24</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>02-02-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I98" t="n">
+        <v>0</v>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L98" t="n">
+        <v>649</v>
+      </c>
+      <c r="M98" t="n">
+        <v>11</v>
+      </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>28-12-2026 11:12:24</t>
+        </is>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P98" t="inlineStr"/>
+      <c r="Q98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>97</v>
+      </c>
+      <c r="B99" t="n">
+        <v>85350</v>
+      </c>
+      <c r="C99" t="n">
+        <v>331491</v>
+      </c>
+      <c r="D99" t="n">
+        <v>16545</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>ELIAS  GOMEZ  PONCE</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>TLALNEPANTLA</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>02-01-2026 11:18:18</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>02-02-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I99" t="n">
+        <v>0</v>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L99" t="n">
+        <v>549</v>
+      </c>
+      <c r="M99" t="n">
+        <v>11</v>
+      </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>28-12-2026 11:18:18</t>
+        </is>
+      </c>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P99" t="inlineStr"/>
+      <c r="Q99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>98</v>
+      </c>
+      <c r="B100" t="n">
+        <v>85365</v>
+      </c>
+      <c r="C100" t="n">
+        <v>329705</v>
+      </c>
+      <c r="D100" t="n">
+        <v>14759</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>ESMERALDA MARTINEZ MEZA</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>PASEO LA PAZ</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>02-01-2026 12:23:37</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I100" t="n">
+        <v>0</v>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L100" t="n">
+        <v>1449</v>
+      </c>
+      <c r="M100" t="n">
+        <v>9</v>
+      </c>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>28-12-2026 12:23:37</t>
+        </is>
+      </c>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P100" t="inlineStr"/>
+      <c r="Q100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>99</v>
+      </c>
+      <c r="B101" t="n">
+        <v>85367</v>
+      </c>
+      <c r="C101" t="n">
+        <v>329706</v>
+      </c>
+      <c r="D101" t="n">
+        <v>14760</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>MANUEL EZEQUIEL RAMIREZ BUSTOS</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>PASEO LA PAZ</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>02-01-2026 12:27:10</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>02-02-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I101" t="n">
+        <v>0</v>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L101" t="n">
+        <v>649</v>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr"/>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P101" t="inlineStr"/>
+      <c r="Q101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>100</v>
+      </c>
+      <c r="B102" t="n">
+        <v>85380</v>
+      </c>
+      <c r="C102" t="n">
+        <v>249607</v>
+      </c>
+      <c r="D102" t="n">
+        <v>47111</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>ALEXIS FLORES GONZALEZ</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>PASEO LA PAZ</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>02-01-2026 13:40:00</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>02-02-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I102" t="n">
+        <v>0</v>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L102" t="n">
+        <v>749</v>
+      </c>
+      <c r="M102" t="n">
+        <v>11</v>
+      </c>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>28-12-2026 13:40:00</t>
+        </is>
+      </c>
+      <c r="O102" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P102" t="n">
+        <v>53883</v>
+      </c>
+      <c r="Q102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>101</v>
+      </c>
+      <c r="B103" t="n">
+        <v>85397</v>
+      </c>
+      <c r="C103" t="n">
+        <v>331571</v>
+      </c>
+      <c r="D103" t="n">
+        <v>16625</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>DIANA BERENICE  BAZAN  GARRIDO</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>INSURGENTES</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>02-01-2026 15:13:00</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I103" t="n">
+        <v>0</v>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L103" t="n">
+        <v>1549</v>
+      </c>
+      <c r="M103" t="n">
+        <v>9</v>
+      </c>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>28-12-2026 15:13:00</t>
+        </is>
+      </c>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P103" t="inlineStr"/>
+      <c r="Q103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>102</v>
+      </c>
+      <c r="B104" t="n">
+        <v>85399</v>
+      </c>
+      <c r="C104" t="n">
+        <v>331578</v>
+      </c>
+      <c r="D104" t="n">
+        <v>16632</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>ALEX RICARDO PINTO URIBE</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>PASEO 2000</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>02-01-2026 15:21:15</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>02-02-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I104" t="n">
+        <v>0</v>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L104" t="n">
+        <v>549</v>
+      </c>
+      <c r="M104" t="n">
+        <v>11</v>
+      </c>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>28-12-2026 15:21:15</t>
+        </is>
+      </c>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P104" t="inlineStr"/>
+      <c r="Q104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>103</v>
+      </c>
+      <c r="B105" t="n">
+        <v>85416</v>
+      </c>
+      <c r="C105" t="n">
+        <v>331597</v>
+      </c>
+      <c r="D105" t="n">
+        <v>16651</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>KARLA FABIOLA  GONZALEZ ALMEIDA</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>PASEO 2000</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>02-01-2026 16:36:43</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I105" t="n">
+        <v>0</v>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L105" t="n">
+        <v>1449</v>
+      </c>
+      <c r="M105" t="n">
+        <v>9</v>
+      </c>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>28-12-2026 16:36:43</t>
+        </is>
+      </c>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P105" t="inlineStr"/>
+      <c r="Q105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>104</v>
+      </c>
+      <c r="B106" t="n">
+        <v>85433</v>
+      </c>
+      <c r="C106" t="n">
+        <v>331652</v>
+      </c>
+      <c r="D106" t="n">
+        <v>16706</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>LIZETH CECILIA  SANDOVAL  YAMASHIRO</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>SENDERO CULIACAN</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>02-01-2026 19:44:46</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>02-02-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I106" t="n">
+        <v>0</v>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L106" t="n">
+        <v>649</v>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr"/>
+      <c r="O106" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P106" t="inlineStr"/>
+      <c r="Q106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>105</v>
+      </c>
+      <c r="B107" t="n">
+        <v>85448</v>
+      </c>
+      <c r="C107" t="n">
+        <v>217427</v>
+      </c>
+      <c r="D107" t="n">
+        <v>14935</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>DALILA  GONZALEZ GONZALEZ</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>PABELLON ROSARITO</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>03-01-2026 10:22:02</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>05-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I107" t="n">
+        <v>0</v>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L107" t="n">
+        <v>1449</v>
+      </c>
+      <c r="M107" t="n">
+        <v>9</v>
+      </c>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t>29-12-2026 10:22:02</t>
+        </is>
+      </c>
+      <c r="O107" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P107" t="inlineStr"/>
+      <c r="Q107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>106</v>
+      </c>
+      <c r="B108" t="n">
+        <v>85450</v>
+      </c>
+      <c r="C108" t="n">
+        <v>331704</v>
+      </c>
+      <c r="D108" t="n">
+        <v>16758</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>AHATZIN AMEYALLI  SANCHEZ URBINA</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>TLALNEPANTLA</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>03-01-2026 10:29:49</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>03-02-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I108" t="n">
+        <v>0</v>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L108" t="n">
+        <v>549</v>
+      </c>
+      <c r="M108" t="n">
+        <v>11</v>
+      </c>
+      <c r="N108" t="inlineStr">
+        <is>
+          <t>29-12-2026 10:29:49</t>
+        </is>
+      </c>
+      <c r="O108" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P108" t="inlineStr"/>
+      <c r="Q108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>107</v>
+      </c>
+      <c r="B109" t="n">
+        <v>85465</v>
+      </c>
+      <c r="C109" t="n">
+        <v>331727</v>
+      </c>
+      <c r="D109" t="n">
+        <v>16781</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>MARIA ISABEL  CASTILLO HEREDIA</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>PASEO 2000</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>03-01-2026 11:47:29</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>03-02-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I109" t="n">
+        <v>0</v>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L109" t="n">
+        <v>649</v>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N109" t="inlineStr"/>
+      <c r="O109" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P109" t="inlineStr"/>
+      <c r="Q109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>108</v>
+      </c>
+      <c r="B110" t="n">
+        <v>85467</v>
+      </c>
+      <c r="C110" t="n">
+        <v>300838</v>
+      </c>
+      <c r="D110" t="n">
+        <v>98336</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>ARMANDO  ARAIZA  SANCHEZ</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>IXTAPALUCA</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>03-01-2026 12:01:14</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I110" t="n">
+        <v>0</v>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L110" t="n">
+        <v>1449</v>
+      </c>
+      <c r="M110" t="n">
+        <v>9</v>
+      </c>
+      <c r="N110" t="inlineStr">
+        <is>
+          <t>29-12-2026 12:01:14</t>
+        </is>
+      </c>
+      <c r="O110" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P110" t="inlineStr"/>
+      <c r="Q110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>109</v>
+      </c>
+      <c r="B111" t="n">
+        <v>85497</v>
+      </c>
+      <c r="C111" t="n">
+        <v>331765</v>
+      </c>
+      <c r="D111" t="n">
+        <v>16569</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>JESSICA ELIZABETH  CALDERON  BRICEÑO</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>CARROUSEL TIJUANA</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>03-01-2026 16:06:29</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>03-02-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I111" t="n">
+        <v>0</v>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L111" t="n">
+        <v>649</v>
+      </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N111" t="inlineStr"/>
+      <c r="O111" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P111" t="inlineStr"/>
+      <c r="Q111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>110</v>
+      </c>
+      <c r="B112" t="n">
+        <v>85499</v>
+      </c>
+      <c r="C112" t="n">
+        <v>331766</v>
+      </c>
+      <c r="D112" t="n">
+        <v>16570</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>JAIME  MACEDO PATIÑO</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>METEPEC</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>03-01-2026 16:18:11</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>03-02-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I112" t="n">
+        <v>0</v>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L112" t="n">
+        <v>649</v>
+      </c>
+      <c r="M112" t="n">
+        <v>11</v>
+      </c>
+      <c r="N112" t="inlineStr">
+        <is>
+          <t>29-12-2026 16:18:11</t>
+        </is>
+      </c>
+      <c r="O112" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P112" t="inlineStr"/>
+      <c r="Q112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>111</v>
+      </c>
+      <c r="B113" t="n">
+        <v>85343</v>
+      </c>
+      <c r="C113" t="n">
+        <v>237668</v>
+      </c>
+      <c r="D113" t="n">
+        <v>35173</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>AARON RUIZ  MARTINEZ</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>SAN LUIS</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>02-01-2026 10:58:21</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>02-02-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I113" t="n">
+        <v>0</v>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L113" t="n">
+        <v>549</v>
+      </c>
+      <c r="M113" t="n">
+        <v>11</v>
+      </c>
+      <c r="N113" t="inlineStr">
+        <is>
+          <t>28-12-2026 10:58:21</t>
+        </is>
+      </c>
+      <c r="O113" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P113" t="inlineStr"/>
+      <c r="Q113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>112</v>
+      </c>
+      <c r="B114" t="n">
+        <v>85354</v>
+      </c>
+      <c r="C114" t="n">
+        <v>331482</v>
+      </c>
+      <c r="D114" t="n">
+        <v>16536</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>DORA ARACELI DIAZ  VILLARREAL</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>SALTILLO VILLALTA</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>02-01-2026 11:34:09</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>02-02-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I114" t="n">
+        <v>0</v>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L114" t="n">
+        <v>649</v>
+      </c>
+      <c r="M114" t="n">
+        <v>11</v>
+      </c>
+      <c r="N114" t="inlineStr">
+        <is>
+          <t>28-12-2026 11:34:09</t>
+        </is>
+      </c>
+      <c r="O114" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P114" t="inlineStr"/>
+      <c r="Q114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>113</v>
+      </c>
+      <c r="B115" t="n">
+        <v>85361</v>
+      </c>
+      <c r="C115" t="n">
+        <v>147484</v>
+      </c>
+      <c r="D115" t="n">
+        <v>45060</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>STEPHANYA PEREZ FERNANDEZ</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>PASEO LA PAZ</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>02-01-2026 11:58:21</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I115" t="n">
+        <v>0</v>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L115" t="n">
+        <v>1449</v>
+      </c>
+      <c r="M115" t="n">
+        <v>9</v>
+      </c>
+      <c r="N115" t="inlineStr">
+        <is>
+          <t>28-12-2026 11:58:21</t>
+        </is>
+      </c>
+      <c r="O115" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P115" t="inlineStr"/>
+      <c r="Q115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>114</v>
+      </c>
+      <c r="B116" t="n">
+        <v>85368</v>
+      </c>
+      <c r="C116" t="n">
+        <v>331520</v>
+      </c>
+      <c r="D116" t="n">
+        <v>16574</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>KARLA EDITH TOVAR ROSALES</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>SALTILLO VILLALTA</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>02-01-2026 12:28:57</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>02-02-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I116" t="n">
+        <v>0</v>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L116" t="n">
+        <v>649</v>
+      </c>
+      <c r="M116" t="n">
+        <v>11</v>
+      </c>
+      <c r="N116" t="inlineStr">
+        <is>
+          <t>28-12-2026 12:28:57</t>
+        </is>
+      </c>
+      <c r="O116" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P116" t="inlineStr"/>
+      <c r="Q116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>115</v>
+      </c>
+      <c r="B117" t="n">
+        <v>85379</v>
+      </c>
+      <c r="C117" t="n">
+        <v>331543</v>
+      </c>
+      <c r="D117" t="n">
+        <v>16597</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>JESUS  LUNA ORTIZ</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>INSURGENTES</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>02-01-2026 13:33:07</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I117" t="n">
+        <v>0</v>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L117" t="n">
+        <v>1549</v>
+      </c>
+      <c r="M117" t="n">
+        <v>9</v>
+      </c>
+      <c r="N117" t="inlineStr">
+        <is>
+          <t>28-12-2026 13:33:07</t>
+        </is>
+      </c>
+      <c r="O117" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P117" t="inlineStr"/>
+      <c r="Q117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>116</v>
+      </c>
+      <c r="B118" t="n">
+        <v>85386</v>
+      </c>
+      <c r="C118" t="n">
+        <v>331546</v>
+      </c>
+      <c r="D118" t="n">
+        <v>16600</v>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>ITZETL QUIROZ SANTANA</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>METEPEC</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>02-01-2026 14:03:16</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>02-02-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I118" t="n">
+        <v>0</v>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L118" t="n">
+        <v>649</v>
+      </c>
+      <c r="M118" t="n">
+        <v>11</v>
+      </c>
+      <c r="N118" t="inlineStr">
+        <is>
+          <t>28-12-2026 14:03:16</t>
+        </is>
+      </c>
+      <c r="O118" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P118" t="inlineStr"/>
+      <c r="Q118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>117</v>
+      </c>
+      <c r="B119" t="n">
+        <v>85393</v>
+      </c>
+      <c r="C119" t="n">
+        <v>200198</v>
+      </c>
+      <c r="D119" t="n">
+        <v>97705</v>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>MARCO ANTONIO GONZALEZ  HERRERA</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>SENDERO CHIHUAHUA</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>02-01-2026 14:34:57</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>02-02-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I119" t="n">
+        <v>0</v>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L119" t="n">
+        <v>549</v>
+      </c>
+      <c r="M119" t="n">
+        <v>11</v>
+      </c>
+      <c r="N119" t="inlineStr">
+        <is>
+          <t>28-12-2026 14:34:57</t>
+        </is>
+      </c>
+      <c r="O119" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P119" t="inlineStr"/>
+      <c r="Q119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>118</v>
+      </c>
+      <c r="B120" t="n">
+        <v>85404</v>
+      </c>
+      <c r="C120" t="n">
+        <v>7025</v>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>05960</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>LUIS ANDRES  FRAUSTO HERRERA</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>VILLA VERDE MEXICALI</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>02-01-2026 15:36:10</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I120" t="n">
+        <v>0</v>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L120" t="n">
+        <v>1449</v>
+      </c>
+      <c r="M120" t="n">
+        <v>9</v>
+      </c>
+      <c r="N120" t="inlineStr">
+        <is>
+          <t>28-12-2026 15:36:10</t>
+        </is>
+      </c>
+      <c r="O120" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P120" t="inlineStr"/>
+      <c r="Q120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>119</v>
+      </c>
+      <c r="B121" t="n">
+        <v>85418</v>
+      </c>
+      <c r="C121" t="n">
+        <v>331600</v>
+      </c>
+      <c r="D121" t="n">
+        <v>16654</v>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>ALEJANDRA RUIZ JAIME</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>INSURGENTES</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>02-01-2026 16:45:31</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I121" t="n">
+        <v>0</v>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L121" t="n">
+        <v>1549</v>
+      </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N121" t="inlineStr"/>
+      <c r="O121" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P121" t="inlineStr"/>
+      <c r="Q121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>120</v>
+      </c>
+      <c r="B122" t="n">
+        <v>85429</v>
+      </c>
+      <c r="C122" t="n">
+        <v>331631</v>
+      </c>
+      <c r="D122" t="n">
+        <v>16685</v>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>AZAET RIVERA BOLAÑOS</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>PASEO 2000</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>02-01-2026 18:05:40</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>02-02-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I122" t="n">
+        <v>0</v>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L122" t="n">
+        <v>549</v>
+      </c>
+      <c r="M122" t="n">
+        <v>11</v>
+      </c>
+      <c r="N122" t="inlineStr">
+        <is>
+          <t>28-12-2026 18:05:40</t>
+        </is>
+      </c>
+      <c r="O122" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P122" t="inlineStr"/>
+      <c r="Q122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>121</v>
+      </c>
+      <c r="B123" t="n">
+        <v>85436</v>
+      </c>
+      <c r="C123" t="n">
+        <v>287987</v>
+      </c>
+      <c r="D123" t="n">
+        <v>85485</v>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>JOSUE ALFONZO PEREZ CASTILLON</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>VILLAS DEL REY</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>02-01-2026 20:56:57</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>02-02-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I123" t="n">
+        <v>0</v>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L123" t="n">
+        <v>749</v>
+      </c>
+      <c r="M123" t="n">
+        <v>11</v>
+      </c>
+      <c r="N123" t="inlineStr">
+        <is>
+          <t>28-12-2026 20:56:57</t>
+        </is>
+      </c>
+      <c r="O123" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P123" t="n">
+        <v>63526</v>
+      </c>
+      <c r="Q123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>122</v>
+      </c>
+      <c r="B124" t="n">
+        <v>85443</v>
+      </c>
+      <c r="C124" t="n">
+        <v>207621</v>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>05129</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>ALMA ANGELICA ROMERO ALVAREZ</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>IXTAPALUCA</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>03-01-2026 8:40:38</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>03-02-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I124" t="n">
+        <v>0</v>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L124" t="n">
+        <v>549</v>
+      </c>
+      <c r="M124" t="n">
+        <v>11</v>
+      </c>
+      <c r="N124" t="inlineStr">
+        <is>
+          <t>29-12-2026 8:40:38</t>
+        </is>
+      </c>
+      <c r="O124" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P124" t="inlineStr"/>
+      <c r="Q124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>123</v>
+      </c>
+      <c r="B125" t="n">
+        <v>85454</v>
+      </c>
+      <c r="C125" t="n">
+        <v>331706</v>
+      </c>
+      <c r="D125" t="n">
+        <v>16760</v>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>ROGELIO  SUAREZ CARRASCO</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>TLALNEPANTLA</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>03-01-2026 10:38:44</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>03-02-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I125" t="n">
+        <v>0</v>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L125" t="n">
+        <v>549</v>
+      </c>
+      <c r="M125" t="n">
+        <v>11</v>
+      </c>
+      <c r="N125" t="inlineStr">
+        <is>
+          <t>29-12-2026 10:38:44</t>
+        </is>
+      </c>
+      <c r="O125" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P125" t="inlineStr"/>
+      <c r="Q125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>124</v>
+      </c>
+      <c r="B126" t="n">
+        <v>85461</v>
+      </c>
+      <c r="C126" t="n">
+        <v>114641</v>
+      </c>
+      <c r="D126" t="n">
+        <v>12369</v>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>DANIELA  PADILLA MORENO</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>LOMA BONITA</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>03-01-2026 11:23:28</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>03-02-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I126" t="n">
+        <v>0</v>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L126" t="n">
+        <v>749</v>
+      </c>
+      <c r="M126" t="n">
+        <v>11</v>
+      </c>
+      <c r="N126" t="inlineStr">
+        <is>
+          <t>29-12-2026 11:23:28</t>
+        </is>
+      </c>
+      <c r="O126" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P126" t="n">
+        <v>31163</v>
+      </c>
+      <c r="Q126" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>125</v>
+      </c>
+      <c r="B127" t="n">
+        <v>85468</v>
+      </c>
+      <c r="C127" t="n">
+        <v>331728</v>
+      </c>
+      <c r="D127" t="n">
+        <v>16782</v>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>ISMAEL HIRAM  SAUCEDO OLIVERA</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>TLALNEPANTLA</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>03-01-2026 12:03:25</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>03-02-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I127" t="n">
+        <v>0</v>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L127" t="n">
+        <v>549</v>
+      </c>
+      <c r="M127" t="n">
+        <v>11</v>
+      </c>
+      <c r="N127" t="inlineStr">
+        <is>
+          <t>29-12-2026 12:03:25</t>
+        </is>
+      </c>
+      <c r="O127" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P127" t="inlineStr"/>
+      <c r="Q127" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>126</v>
+      </c>
+      <c r="B128" t="n">
+        <v>85479</v>
+      </c>
+      <c r="C128" t="n">
+        <v>331739</v>
+      </c>
+      <c r="D128" t="n">
+        <v>16793</v>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>SHARON HAYDE CABRERA HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>PAPALOTE TIJUANA</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>03-01-2026 12:54:57</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>03-02-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I128" t="n">
+        <v>0</v>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L128" t="n">
+        <v>649</v>
+      </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N128" t="inlineStr"/>
+      <c r="O128" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P128" t="inlineStr"/>
+      <c r="Q128" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>127</v>
+      </c>
+      <c r="B129" t="n">
+        <v>85486</v>
+      </c>
+      <c r="C129" t="n">
+        <v>220221</v>
+      </c>
+      <c r="D129" t="n">
+        <v>17728</v>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>JOSE MANUEL URIBE PONCE</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>SENDERO MEXICALI</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>03-01-2026 13:27:52</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>03-02-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I129" t="n">
+        <v>0</v>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L129" t="n">
+        <v>549</v>
+      </c>
+      <c r="M129" t="n">
+        <v>11</v>
+      </c>
+      <c r="N129" t="inlineStr">
+        <is>
+          <t>29-12-2026 13:27:52</t>
+        </is>
+      </c>
+      <c r="O129" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P129" t="inlineStr"/>
+      <c r="Q129" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>128</v>
+      </c>
+      <c r="B130" t="n">
+        <v>85493</v>
+      </c>
+      <c r="C130" t="n">
+        <v>331758</v>
+      </c>
+      <c r="D130" t="n">
+        <v>16812</v>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>LUIS MARTIN SANTOSCOY AVILA</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>SALTILLO VILLALTA</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>03-01-2026 14:52:23</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>03-02-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I130" t="n">
+        <v>0</v>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L130" t="n">
+        <v>649</v>
+      </c>
+      <c r="M130" t="n">
+        <v>11</v>
+      </c>
+      <c r="N130" t="inlineStr">
+        <is>
+          <t>29-12-2026 14:52:23</t>
+        </is>
+      </c>
+      <c r="O130" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P130" t="inlineStr"/>
+      <c r="Q130" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>129</v>
+      </c>
+      <c r="B131" t="n">
+        <v>84640</v>
+      </c>
+      <c r="C131" t="n">
+        <v>326127</v>
+      </c>
+      <c r="D131" t="n">
+        <v>23066</v>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>ISABEL ESPINOZA  VALENZUELA</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>MISION ENSENADA</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>23-12-2025 16:48:33</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>01-02-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I131" t="n">
+        <v>0</v>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L131" t="n">
+        <v>499</v>
+      </c>
+      <c r="M131" t="n">
+        <v>11</v>
+      </c>
+      <c r="N131" t="inlineStr">
+        <is>
+          <t>18-12-2026 16:48:33</t>
+        </is>
+      </c>
+      <c r="O131" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P131" t="n">
+        <v>83140</v>
+      </c>
+      <c r="Q131" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>130</v>
+      </c>
+      <c r="B132" t="n">
+        <v>85072</v>
+      </c>
+      <c r="C132" t="n">
+        <v>18849</v>
+      </c>
+      <c r="D132" t="n">
+        <v>17752</v>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>REYNA GABRIELA CASTAÑEDA  PACHECO</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>TEC MEXICALI</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>30-12-2025 12:26:35</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>02-02-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I132" t="n">
+        <v>0</v>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L132" t="n">
+        <v>399</v>
+      </c>
+      <c r="M132" t="n">
+        <v>11</v>
+      </c>
+      <c r="N132" t="inlineStr">
+        <is>
+          <t>25-12-2026 12:26:35</t>
+        </is>
+      </c>
+      <c r="O132" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P132" t="n">
+        <v>71103</v>
+      </c>
+      <c r="Q132" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>131</v>
+      </c>
+      <c r="B133" t="n">
+        <v>85357</v>
+      </c>
+      <c r="C133" t="n">
+        <v>331506</v>
+      </c>
+      <c r="D133" t="n">
+        <v>16560</v>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>OMAR ANTONIO  HERNANDEZ HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>TLALNEPANTLA</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>02-01-2026 11:40:03</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>02-02-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I133" t="n">
+        <v>0</v>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L133" t="n">
+        <v>549</v>
+      </c>
+      <c r="M133" t="n">
+        <v>11</v>
+      </c>
+      <c r="N133" t="inlineStr">
+        <is>
+          <t>28-12-2026 11:40:03</t>
+        </is>
+      </c>
+      <c r="O133" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P133" t="inlineStr"/>
+      <c r="Q133" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>132</v>
+      </c>
+      <c r="B134" t="n">
+        <v>85358</v>
+      </c>
+      <c r="C134" t="n">
+        <v>331497</v>
+      </c>
+      <c r="D134" t="n">
+        <v>16551</v>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>AMERICA YANDELLI PALACIOS GAONA</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>SALTILLO VILLALTA</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>02-01-2026 11:42:53</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>02-02-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I134" t="n">
+        <v>0</v>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L134" t="n">
+        <v>649</v>
+      </c>
+      <c r="M134" t="n">
+        <v>11</v>
+      </c>
+      <c r="N134" t="inlineStr">
+        <is>
+          <t>28-12-2026 11:42:53</t>
+        </is>
+      </c>
+      <c r="O134" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P134" t="inlineStr"/>
+      <c r="Q134" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>133</v>
+      </c>
+      <c r="B135" t="n">
+        <v>85372</v>
+      </c>
+      <c r="C135" t="n">
+        <v>331528</v>
+      </c>
+      <c r="D135" t="n">
+        <v>16582</v>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>EDGAR MANUEL GONZALEZ RUBIO GARCIA</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>PASEO LA PAZ</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>02-01-2026 12:58:52</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>02-02-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I135" t="n">
+        <v>0</v>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L135" t="n">
+        <v>549</v>
+      </c>
+      <c r="M135" t="n">
+        <v>11</v>
+      </c>
+      <c r="N135" t="inlineStr">
+        <is>
+          <t>28-12-2026 12:58:52</t>
+        </is>
+      </c>
+      <c r="O135" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P135" t="inlineStr"/>
+      <c r="Q135" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>134</v>
+      </c>
+      <c r="B136" t="n">
+        <v>85375</v>
+      </c>
+      <c r="C136" t="n">
+        <v>331524</v>
+      </c>
+      <c r="D136" t="n">
+        <v>16578</v>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>MAYRA GUADALUPE PARRA  RIVERA</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>SENDERO SALTILLO</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>02-01-2026 13:19:59</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>02-02-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I136" t="n">
+        <v>0</v>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L136" t="n">
+        <v>549</v>
+      </c>
+      <c r="M136" t="n">
+        <v>11</v>
+      </c>
+      <c r="N136" t="inlineStr">
+        <is>
+          <t>28-12-2026 13:19:59</t>
+        </is>
+      </c>
+      <c r="O136" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P136" t="inlineStr"/>
+      <c r="Q136" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>135</v>
+      </c>
+      <c r="B137" t="n">
+        <v>85389</v>
+      </c>
+      <c r="C137" t="n">
+        <v>331555</v>
+      </c>
+      <c r="D137" t="n">
+        <v>16609</v>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>RICARDO  URIAS  QUINTERO</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>SENDERO CULIACAN</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>02-01-2026 14:20:20</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>02-02-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I137" t="n">
+        <v>0</v>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L137" t="n">
+        <v>649</v>
+      </c>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N137" t="inlineStr"/>
+      <c r="O137" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P137" t="inlineStr"/>
+      <c r="Q137" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>136</v>
+      </c>
+      <c r="B138" t="n">
+        <v>85390</v>
+      </c>
+      <c r="C138" t="n">
+        <v>329954</v>
+      </c>
+      <c r="D138" t="n">
+        <v>15008</v>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>VIRIDIANA  GONZALEZ PULIDO</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>PASEO 2000</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>02-01-2026 14:20:33</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>02-02-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I138" t="n">
+        <v>0</v>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L138" t="n">
+        <v>549</v>
+      </c>
+      <c r="M138" t="n">
+        <v>11</v>
+      </c>
+      <c r="N138" t="inlineStr">
+        <is>
+          <t>28-12-2026 14:20:33</t>
+        </is>
+      </c>
+      <c r="O138" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P138" t="inlineStr"/>
+      <c r="Q138" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>137</v>
+      </c>
+      <c r="B139" t="n">
+        <v>85407</v>
+      </c>
+      <c r="C139" t="n">
+        <v>331583</v>
+      </c>
+      <c r="D139" t="n">
+        <v>16637</v>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>RENATA GONZALEZ GOMEZ</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>SALTILLO VILLALTA</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>02-01-2026 15:51:20</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>02-02-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I139" t="n">
+        <v>0</v>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L139" t="n">
+        <v>649</v>
+      </c>
+      <c r="M139" t="n">
+        <v>11</v>
+      </c>
+      <c r="N139" t="inlineStr">
+        <is>
+          <t>28-12-2026 15:51:20</t>
+        </is>
+      </c>
+      <c r="O139" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P139" t="inlineStr"/>
+      <c r="Q139" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>138</v>
+      </c>
+      <c r="B140" t="n">
+        <v>83568</v>
+      </c>
+      <c r="C140" t="n">
+        <v>138456</v>
+      </c>
+      <c r="D140" t="n">
+        <v>36094</v>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>BRAYAN GAEL BALDERAS CONTRERAS</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>SENDERO SALTILLO</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>08-12-2025 7:50:26</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>02-02-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I140" t="n">
+        <v>0</v>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L140" t="n">
+        <v>549</v>
+      </c>
+      <c r="M140" t="n">
+        <v>5</v>
+      </c>
+      <c r="N140" t="inlineStr">
+        <is>
+          <t>06-06-2026 7:50:26</t>
+        </is>
+      </c>
+      <c r="O140" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P140" t="n">
+        <v>70999</v>
+      </c>
+      <c r="Q140" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>139</v>
+      </c>
+      <c r="B141" t="n">
+        <v>85408</v>
+      </c>
+      <c r="C141" t="n">
+        <v>331588</v>
+      </c>
+      <c r="D141" t="n">
+        <v>16642</v>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>ROMINA SOSA SOLIS</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>SALTILLO VILLALTA</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>02-01-2026 15:58:45</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>02-02-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I141" t="n">
+        <v>0</v>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L141" t="n">
+        <v>649</v>
+      </c>
+      <c r="M141" t="n">
+        <v>11</v>
+      </c>
+      <c r="N141" t="inlineStr">
+        <is>
+          <t>28-12-2026 15:58:45</t>
+        </is>
+      </c>
+      <c r="O141" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P141" t="inlineStr"/>
+      <c r="Q141" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>140</v>
+      </c>
+      <c r="B142" t="n">
+        <v>85422</v>
+      </c>
+      <c r="C142" t="n">
+        <v>323721</v>
+      </c>
+      <c r="D142" t="n">
+        <v>20660</v>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>JAVIER HERNÁNDEZ CHÁVEZ</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>INSURGENTES</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>02-01-2026 17:09:25</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>02-02-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I142" t="n">
+        <v>0</v>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L142" t="n">
+        <v>649</v>
+      </c>
+      <c r="M142" t="n">
+        <v>11</v>
+      </c>
+      <c r="N142" t="inlineStr">
+        <is>
+          <t>28-12-2026 17:09:25</t>
+        </is>
+      </c>
+      <c r="O142" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P142" t="inlineStr"/>
+      <c r="Q142" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>141</v>
+      </c>
+      <c r="B143" t="n">
+        <v>85425</v>
+      </c>
+      <c r="C143" t="n">
+        <v>234864</v>
+      </c>
+      <c r="D143" t="n">
+        <v>32369</v>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>SARAH  MORENO URIARTE</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>SENDERO CULIACAN</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>02-01-2026 17:35:16</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>02-02-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I143" t="n">
+        <v>0</v>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L143" t="n">
+        <v>549</v>
+      </c>
+      <c r="M143" t="n">
+        <v>11</v>
+      </c>
+      <c r="N143" t="inlineStr">
+        <is>
+          <t>28-12-2026 17:35:16</t>
+        </is>
+      </c>
+      <c r="O143" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P143" t="inlineStr"/>
+      <c r="Q143" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>142</v>
+      </c>
+      <c r="B144" t="n">
+        <v>85439</v>
+      </c>
+      <c r="C144" t="n">
+        <v>331457</v>
+      </c>
+      <c r="D144" t="n">
+        <v>16511</v>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>CESAR BELLO LAGUNEZ</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>PASEO 2000</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>03-01-2026 6:29:18</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>03-02-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I144" t="n">
+        <v>0</v>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L144" t="n">
+        <v>549</v>
+      </c>
+      <c r="M144" t="n">
+        <v>11</v>
+      </c>
+      <c r="N144" t="inlineStr">
+        <is>
+          <t>29-12-2026 6:29:18</t>
+        </is>
+      </c>
+      <c r="O144" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P144" t="inlineStr"/>
+      <c r="Q144" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>143</v>
+      </c>
+      <c r="B145" t="n">
+        <v>85440</v>
+      </c>
+      <c r="C145" t="n">
+        <v>331680</v>
+      </c>
+      <c r="D145" t="n">
+        <v>16734</v>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>GUADALUPE MARGARITA MENDOZA  HUERTA</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>PASEO LA PAZ</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>03-01-2026 7:10:20</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>03-02-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I145" t="n">
+        <v>0</v>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L145" t="n">
+        <v>549</v>
+      </c>
+      <c r="M145" t="n">
+        <v>11</v>
+      </c>
+      <c r="N145" t="inlineStr">
+        <is>
+          <t>29-12-2026 7:10:20</t>
+        </is>
+      </c>
+      <c r="O145" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P145" t="inlineStr"/>
+      <c r="Q145" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>144</v>
+      </c>
+      <c r="B146" t="n">
+        <v>85458</v>
+      </c>
+      <c r="C146" t="n">
+        <v>331716</v>
+      </c>
+      <c r="D146" t="n">
+        <v>16770</v>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>JOSE ARTURO GONZALEZ MARTINEZ</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>SALTILLO VILLALTA</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>03-01-2026 10:51:44</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>03-02-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I146" t="n">
+        <v>0</v>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L146" t="n">
+        <v>649</v>
+      </c>
+      <c r="M146" t="n">
+        <v>11</v>
+      </c>
+      <c r="N146" t="inlineStr">
+        <is>
+          <t>29-12-2026 10:51:44</t>
+        </is>
+      </c>
+      <c r="O146" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P146" t="inlineStr"/>
+      <c r="Q146" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>145</v>
+      </c>
+      <c r="B147" t="n">
+        <v>85489</v>
+      </c>
+      <c r="C147" t="n">
+        <v>331751</v>
+      </c>
+      <c r="D147" t="n">
+        <v>16805</v>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>YOLANDA VILLA MORENO</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>PASEO 2000</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>03-01-2026 13:51:12</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I147" t="n">
+        <v>0</v>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L147" t="n">
+        <v>1449</v>
+      </c>
+      <c r="M147" t="n">
+        <v>9</v>
+      </c>
+      <c r="N147" t="inlineStr">
+        <is>
+          <t>29-12-2026 13:51:12</t>
+        </is>
+      </c>
+      <c r="O147" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P147" t="inlineStr"/>
+      <c r="Q147" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>146</v>
+      </c>
+      <c r="B148" t="n">
+        <v>85490</v>
+      </c>
+      <c r="C148" t="n">
+        <v>331756</v>
+      </c>
+      <c r="D148" t="n">
+        <v>16810</v>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>LEONILA DEL PILAR LUNA MADRIGAL</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>SANTA FE</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>03-01-2026 14:10:49</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>03-02-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I148" t="n">
+        <v>0</v>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L148" t="n">
+        <v>549</v>
+      </c>
+      <c r="M148" t="n">
+        <v>11</v>
+      </c>
+      <c r="N148" t="inlineStr">
+        <is>
+          <t>29-12-2026 14:10:49</t>
+        </is>
+      </c>
+      <c r="O148" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P148" t="inlineStr"/>
+      <c r="Q148" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Reporte generado: 04-01-2026 03:23 p. m.</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr"/>
+      <c r="C149" t="inlineStr"/>
+      <c r="D149" t="inlineStr"/>
+      <c r="E149" t="inlineStr"/>
+      <c r="F149" t="inlineStr"/>
+      <c r="G149" t="inlineStr"/>
+      <c r="H149" t="inlineStr"/>
+      <c r="I149" t="inlineStr"/>
+      <c r="J149" t="inlineStr"/>
+      <c r="K149" t="inlineStr"/>
+      <c r="L149" t="inlineStr"/>
+      <c r="M149" t="inlineStr"/>
+      <c r="N149" t="inlineStr"/>
+      <c r="O149" t="inlineStr"/>
+      <c r="P149" t="inlineStr"/>
+      <c r="Q149" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/descargas/cargos_recurrentes.xlsx
+++ b/data/descargas/cargos_recurrentes.xlsx
@@ -601,7 +601,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reporte generado: 01-02-2026 07:52 a. m. </t>
+          <t>Reporte generado: 01-02-2026 03:27 p. m.</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>

--- a/data/descargas/cargos_recurrentes.xlsx
+++ b/data/descargas/cargos_recurrentes.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q3"/>
+  <dimension ref="A1:Q67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -599,27 +599,4199 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Reporte generado: 01-02-2026 03:27 p. m.</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="n">
+        <v>87410</v>
+      </c>
+      <c r="C3" t="n">
+        <v>307274</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>04773</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>ESMERALDA GUADALUPE RANGEL ESQUIVEL</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>SEND SALTILLO</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>13-01-2026 18:27:00</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>02-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>499</v>
+      </c>
+      <c r="M3" t="n">
+        <v>11</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>08-01-2027 18:27:00</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P3" t="n">
+        <v>73961</v>
+      </c>
       <c r="Q3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="n">
+        <v>91211</v>
+      </c>
+      <c r="C4" t="n">
+        <v>321040</v>
+      </c>
+      <c r="D4" t="n">
+        <v>17979</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>JOSE RAMON VAZQUEZ REYNA</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>SEND SALTILLO</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>01-02-2026 8:48:32</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>01-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>499</v>
+      </c>
+      <c r="M4" t="n">
+        <v>11</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>27-01-2027 8:48:32</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="n">
+        <v>91218</v>
+      </c>
+      <c r="C5" t="n">
+        <v>339750</v>
+      </c>
+      <c r="D5" t="n">
+        <v>17568</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>AGUSTIN JAVIER HERNANDEZ RODRIGUEZ</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>SALTILLO VILLALTA</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>01-02-2026 9:43:06</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>01-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>649</v>
+      </c>
+      <c r="M5" t="n">
+        <v>11</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>27-01-2027 9:43:06</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="n">
+        <v>91229</v>
+      </c>
+      <c r="C6" t="n">
+        <v>332111</v>
+      </c>
+      <c r="D6" t="n">
+        <v>16915</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>EMILIO SEBASTIAN HERNANDEZ LOPEZ</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>INSURGENTES</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>01-02-2026 10:32:54</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>01-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>1549</v>
+      </c>
+      <c r="M6" t="n">
+        <v>9</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>27-01-2027 10:32:54</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" t="n">
+        <v>91243</v>
+      </c>
+      <c r="C7" t="n">
+        <v>339799</v>
+      </c>
+      <c r="D7" t="n">
+        <v>17617</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>ADRIANA MARTINEZ GARCIA</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>SALTILLO VILLALTA</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>01-02-2026 12:19:57</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>01-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>649</v>
+      </c>
+      <c r="M7" t="n">
+        <v>11</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>27-01-2027 12:19:57</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" t="n">
+        <v>91254</v>
+      </c>
+      <c r="C8" t="n">
+        <v>315164</v>
+      </c>
+      <c r="D8" t="n">
+        <v>12663</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>BENJAMIN ELISEO SANTANA RIESTRA</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>PASEO LA PAZ</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>01-02-2026 13:26:29</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>01-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>499</v>
+      </c>
+      <c r="M8" t="n">
+        <v>11</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>27-01-2027 13:26:29</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" t="n">
+        <v>91261</v>
+      </c>
+      <c r="C9" t="n">
+        <v>339185</v>
+      </c>
+      <c r="D9" t="n">
+        <v>17003</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>ROBERTO DE JESUS APARICIO  RODRIGUEZ</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>SEND MXL</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>01-02-2026 15:04:11</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>01-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>499</v>
+      </c>
+      <c r="M9" t="n">
+        <v>11</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>27-01-2027 15:04:11</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" t="n">
+        <v>91268</v>
+      </c>
+      <c r="C10" t="n">
+        <v>139369</v>
+      </c>
+      <c r="D10" t="n">
+        <v>37001</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>LANIA YEROBBY GARCIA ARAUJO</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>SEND CUL</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>02-02-2026 6:11:48</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>03-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>499</v>
+      </c>
+      <c r="M10" t="n">
+        <v>11</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>28-01-2027 6:11:48</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" t="n">
+        <v>90836</v>
+      </c>
+      <c r="C11" t="n">
+        <v>243346</v>
+      </c>
+      <c r="D11" t="n">
+        <v>40851</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>DANYA ESTEFANIA OLACHEA  CESEÑA</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>PASEO LA PAZ</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>29-01-2026 21:28:17</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>04-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>549</v>
+      </c>
+      <c r="M11" t="n">
+        <v>11</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>24-01-2027 21:28:17</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>68365</v>
+      </c>
+      <c r="Q11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" t="n">
+        <v>91220</v>
+      </c>
+      <c r="C12" t="n">
+        <v>338953</v>
+      </c>
+      <c r="D12" t="n">
+        <v>16771</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>FABIOLA  MARTINEZ  PLATA</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>IXTAPALUCA</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>01-02-2026 9:51:00</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>01-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>499</v>
+      </c>
+      <c r="M12" t="n">
+        <v>11</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>27-01-2027 9:51:00</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" t="n">
+        <v>91227</v>
+      </c>
+      <c r="C13" t="n">
+        <v>339764</v>
+      </c>
+      <c r="D13" t="n">
+        <v>17582</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>WILIAM ULISES  CASTRO LOPEZ</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>PASEO LA PAZ</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>01-02-2026 10:25:23</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>01-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>499</v>
+      </c>
+      <c r="M13" t="n">
+        <v>11</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>27-01-2027 10:25:23</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" t="n">
+        <v>91234</v>
+      </c>
+      <c r="C14" t="n">
+        <v>339780</v>
+      </c>
+      <c r="D14" t="n">
+        <v>17598</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>JUAN MANUEL  RODRIGUEZ RODRIGUEZ</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>METEPEC</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>01-02-2026 11:09:46</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>01-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
+        <v>649</v>
+      </c>
+      <c r="M14" t="n">
+        <v>11</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>27-01-2027 11:09:46</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" t="n">
+        <v>91252</v>
+      </c>
+      <c r="C15" t="n">
+        <v>339816</v>
+      </c>
+      <c r="D15" t="n">
+        <v>17634</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>LUIS DIEGO  GARCIA  VAZQUEZ</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>INSURGENTES</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>01-02-2026 13:19:28</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>01-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L15" t="n">
+        <v>1549</v>
+      </c>
+      <c r="M15" t="n">
+        <v>9</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>27-01-2027 13:19:28</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" t="n">
+        <v>91259</v>
+      </c>
+      <c r="C16" t="n">
+        <v>273415</v>
+      </c>
+      <c r="D16" t="n">
+        <v>70917</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>FRANCISCO MANUEL CORAL  CORRAL</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>MISION ENS</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>01-02-2026 14:25:39</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>01-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L16" t="n">
+        <v>649</v>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" t="n">
+        <v>90516</v>
+      </c>
+      <c r="C17" t="n">
+        <v>182631</v>
+      </c>
+      <c r="D17" t="n">
+        <v>80138</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>RICARDO RAFAEL  ROJO SILVA</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>PASEO LA PAZ</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>28-01-2026 13:27:50</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>01-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L17" t="n">
+        <v>399</v>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>56255</v>
+      </c>
+      <c r="Q17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" t="n">
+        <v>91214</v>
+      </c>
+      <c r="C18" t="n">
+        <v>339314</v>
+      </c>
+      <c r="D18" t="n">
+        <v>17132</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>JOSE FRANCISCO CEPEDA CEPEDA</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>SEND SALTILLO</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>01-02-2026 8:58:12</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>01-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L18" t="n">
+        <v>549</v>
+      </c>
+      <c r="M18" t="n">
+        <v>11</v>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>27-01-2027 8:58:12</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" t="n">
+        <v>91216</v>
+      </c>
+      <c r="C19" t="n">
+        <v>308838</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>06337</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>BRYAN IRVIN RIVERA RANGEL</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>SEND SALTILLO</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>01-02-2026 9:16:06</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>01-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L19" t="n">
+        <v>549</v>
+      </c>
+      <c r="M19" t="n">
+        <v>11</v>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>27-01-2027 9:16:06</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" t="n">
+        <v>91231</v>
+      </c>
+      <c r="C20" t="n">
+        <v>338984</v>
+      </c>
+      <c r="D20" t="n">
+        <v>16802</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>CHRISTIAN GAEL CABRERA GONZÁLEZ</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>SALTILLO VILLALTA</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>01-02-2026 10:41:13</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>01-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L20" t="n">
+        <v>549</v>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" t="n">
+        <v>91246</v>
+      </c>
+      <c r="C21" t="n">
+        <v>99736</v>
+      </c>
+      <c r="D21" t="n">
+        <v>97491</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>LUIS ENRIQUE VALENZUELA CAZAREZ</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>AZAHARES CUL</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>01-02-2026 12:46:55</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>02-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L21" t="n">
+        <v>449</v>
+      </c>
+      <c r="M21" t="n">
+        <v>11</v>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>27-01-2027 12:46:55</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P21" t="n">
+        <v>12228</v>
+      </c>
+      <c r="Q21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" t="n">
+        <v>91248</v>
+      </c>
+      <c r="C22" t="n">
+        <v>337631</v>
+      </c>
+      <c r="D22" t="n">
+        <v>15450</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>EDUARDO  ARIAS TREVIZO</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>SALTILLO VILLALTA</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>01-02-2026 13:03:49</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>01-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L22" t="n">
+        <v>649</v>
+      </c>
+      <c r="M22" t="n">
+        <v>11</v>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>27-01-2027 13:03:49</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" t="n">
+        <v>91250</v>
+      </c>
+      <c r="C23" t="n">
+        <v>339721</v>
+      </c>
+      <c r="D23" t="n">
+        <v>17539</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>YOYOTL IXCHEL  SANCHEZ VAZQUEZ</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>METEPEC</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>01-02-2026 13:12:51</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>01-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L23" t="n">
+        <v>649</v>
+      </c>
+      <c r="M23" t="n">
+        <v>11</v>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>27-01-2027 13:12:51</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>22</v>
+      </c>
+      <c r="B24" t="n">
+        <v>91263</v>
+      </c>
+      <c r="C24" t="n">
+        <v>339848</v>
+      </c>
+      <c r="D24" t="n">
+        <v>17666</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>CECILIA CRUZ ISIDRO</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>SEND MXL</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>02-02-2026 5:12:43</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>02-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L24" t="n">
+        <v>499</v>
+      </c>
+      <c r="M24" t="n">
+        <v>11</v>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>28-01-2027 5:12:43</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>23</v>
+      </c>
+      <c r="B25" t="n">
+        <v>88245</v>
+      </c>
+      <c r="C25" t="n">
+        <v>255291</v>
+      </c>
+      <c r="D25" t="n">
+        <v>52795</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>ANDRES  VILLEGAS ESPINOZA</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>SAN LUIS</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>17-01-2026 11:27:38</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>02-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L25" t="n">
+        <v>399</v>
+      </c>
+      <c r="M25" t="n">
+        <v>11</v>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>12-01-2027 11:27:38</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P25" t="n">
+        <v>42806</v>
+      </c>
+      <c r="Q25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>24</v>
+      </c>
+      <c r="B26" t="n">
+        <v>91217</v>
+      </c>
+      <c r="C26" t="n">
+        <v>339743</v>
+      </c>
+      <c r="D26" t="n">
+        <v>17561</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>JOSE ELIAS  PERALES GAONA</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>SALTILLO VILLALTA</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>01-02-2026 9:16:50</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>01-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L26" t="n">
+        <v>799</v>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>25</v>
+      </c>
+      <c r="B27" t="n">
+        <v>91219</v>
+      </c>
+      <c r="C27" t="n">
+        <v>339749</v>
+      </c>
+      <c r="D27" t="n">
+        <v>17567</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>IRMA LETICIA DE LA PEÑA  RETOLAZA</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>SALTILLO VILLALTA</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>01-02-2026 9:47:26</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>01-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L27" t="n">
+        <v>649</v>
+      </c>
+      <c r="M27" t="n">
+        <v>11</v>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>27-01-2027 9:47:26</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>26</v>
+      </c>
+      <c r="B28" t="n">
+        <v>91228</v>
+      </c>
+      <c r="C28" t="n">
+        <v>339768</v>
+      </c>
+      <c r="D28" t="n">
+        <v>17586</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>EFRAIN OMAR DURAN GUEVARA</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>SALTILLO VILLALTA</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>01-02-2026 10:28:30</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>01-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L28" t="n">
+        <v>649</v>
+      </c>
+      <c r="M28" t="n">
+        <v>11</v>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>27-01-2027 10:28:30</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>27</v>
+      </c>
+      <c r="B29" t="n">
+        <v>91251</v>
+      </c>
+      <c r="C29" t="n">
+        <v>339814</v>
+      </c>
+      <c r="D29" t="n">
+        <v>17632</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>VICTOR ADRIAN  GARCIA  BENAVIDEZ</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>INSURGENTES</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>01-02-2026 13:14:43</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>01-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L29" t="n">
+        <v>1549</v>
+      </c>
+      <c r="M29" t="n">
+        <v>9</v>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>27-01-2027 13:14:43</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>28</v>
+      </c>
+      <c r="B30" t="n">
+        <v>91253</v>
+      </c>
+      <c r="C30" t="n">
+        <v>339817</v>
+      </c>
+      <c r="D30" t="n">
+        <v>17635</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>NOEL ALEJANDRO  GARCIA  VAZQUEZ</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>INSURGENTES</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>01-02-2026 13:24:17</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>01-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L30" t="n">
+        <v>1549</v>
+      </c>
+      <c r="M30" t="n">
+        <v>9</v>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>27-01-2027 13:24:17</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>29</v>
+      </c>
+      <c r="B31" t="n">
+        <v>91260</v>
+      </c>
+      <c r="C31" t="n">
+        <v>339183</v>
+      </c>
+      <c r="D31" t="n">
+        <v>17001</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>TANIA YAZMIN RODRIGUEZ ESTELA</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>SEND MXL</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>01-02-2026 15:01:31</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>01-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L31" t="n">
+        <v>499</v>
+      </c>
+      <c r="M31" t="n">
+        <v>11</v>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>27-01-2027 15:01:31</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>30</v>
+      </c>
+      <c r="B32" t="n">
+        <v>91262</v>
+      </c>
+      <c r="C32" t="n">
+        <v>339831</v>
+      </c>
+      <c r="D32" t="n">
+        <v>17649</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>CARLO ANDRE VILLANUEVA TORRES</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>MISION ENS</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>01-02-2026 15:49:47</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>01-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L32" t="n">
+        <v>649</v>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>31</v>
+      </c>
+      <c r="B33" t="n">
+        <v>87457</v>
+      </c>
+      <c r="C33" t="n">
+        <v>60433</v>
+      </c>
+      <c r="D33" t="n">
+        <v>58274</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>HERIBERTO MEZA  ASTORGA</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>SEND MXL</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>13-01-2026 21:26:04</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>02-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L33" t="n">
+        <v>449</v>
+      </c>
+      <c r="M33" t="n">
+        <v>5</v>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>12-07-2026 21:26:04</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P33" t="n">
+        <v>49504</v>
+      </c>
+      <c r="Q33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>32</v>
+      </c>
+      <c r="B34" t="n">
+        <v>91212</v>
+      </c>
+      <c r="C34" t="n">
+        <v>339740</v>
+      </c>
+      <c r="D34" t="n">
+        <v>17558</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>JOSE RAMON  VAZQUEZ  ORTA</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>SEND SALTILLO</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>01-02-2026 8:48:47</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>01-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L34" t="n">
+        <v>499</v>
+      </c>
+      <c r="M34" t="n">
+        <v>11</v>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>27-01-2027 8:48:47</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>33</v>
+      </c>
+      <c r="B35" t="n">
+        <v>91237</v>
+      </c>
+      <c r="C35" t="n">
+        <v>282333</v>
+      </c>
+      <c r="D35" t="n">
+        <v>79834</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>JOSE ALBERTO MOYEDA HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>SEND SALTILLO</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>01-02-2026 11:44:17</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>01-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I35" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L35" t="n">
+        <v>749</v>
+      </c>
+      <c r="M35" t="n">
+        <v>11</v>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>27-01-2027 11:44:17</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P35" t="n">
+        <v>59914</v>
+      </c>
+      <c r="Q35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>34</v>
+      </c>
+      <c r="B36" t="n">
+        <v>91242</v>
+      </c>
+      <c r="C36" t="n">
+        <v>339800</v>
+      </c>
+      <c r="D36" t="n">
+        <v>17618</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>BRIAN MIGUEL AISPURO CORTEZ</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>VILLAS DEL REY</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>01-02-2026 12:07:33</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>01-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L36" t="n">
+        <v>499</v>
+      </c>
+      <c r="M36" t="n">
+        <v>11</v>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>27-01-2027 12:07:33</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>35</v>
+      </c>
+      <c r="B37" t="n">
+        <v>91267</v>
+      </c>
+      <c r="C37" t="n">
+        <v>339860</v>
+      </c>
+      <c r="D37" t="n">
+        <v>17678</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>BEATRIZ ADRIANA RAMIREZ GALVAN</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>PASEO 2000</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>02-02-2026 6:11:32</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>02-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L37" t="n">
+        <v>649</v>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>36</v>
+      </c>
+      <c r="B38" t="n">
+        <v>91276</v>
+      </c>
+      <c r="C38" t="n">
+        <v>339879</v>
+      </c>
+      <c r="D38" t="n">
+        <v>17697</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>ANGELICA MARIA PEREZ HIGUERA</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>PAPALOTE TJ</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>02-02-2026 7:31:50</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>02-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I38" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L38" t="n">
+        <v>1449</v>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr"/>
+      <c r="Q38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>37</v>
+      </c>
+      <c r="B39" t="n">
+        <v>90376</v>
+      </c>
+      <c r="C39" t="n">
+        <v>109059</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>06800</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>ROBERTO ELIAS DURON SORIANO</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>STA CATARINA</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>27-01-2026 17:29:26</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>02-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I39" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L39" t="n">
+        <v>399</v>
+      </c>
+      <c r="M39" t="n">
+        <v>11</v>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>22-01-2027 17:29:26</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P39" t="n">
+        <v>6706</v>
+      </c>
+      <c r="Q39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>38</v>
+      </c>
+      <c r="B40" t="n">
+        <v>85394</v>
+      </c>
+      <c r="C40" t="n">
+        <v>241364</v>
+      </c>
+      <c r="D40" t="n">
+        <v>38869</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>JESUS RUBEN FERNANDEZ NUÑEZ</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>TEC MXL</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>02-01-2026 14:54:50</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>01-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I40" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L40" t="n">
+        <v>499</v>
+      </c>
+      <c r="M40" t="n">
+        <v>11</v>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>28-12-2026 14:54:50</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P40" t="n">
+        <v>85183</v>
+      </c>
+      <c r="Q40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>39</v>
+      </c>
+      <c r="B41" t="n">
+        <v>85460</v>
+      </c>
+      <c r="C41" t="n">
+        <v>128574</v>
+      </c>
+      <c r="D41" t="n">
+        <v>26243</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>JOSE JUAN GODINES IBARRA</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>SEND SALTILLO</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>03-01-2026 11:08:11</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>02-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I41" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L41" t="n">
+        <v>449</v>
+      </c>
+      <c r="M41" t="n">
+        <v>5</v>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>02-07-2026 11:08:11</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P41" t="n">
+        <v>49334</v>
+      </c>
+      <c r="Q41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>40</v>
+      </c>
+      <c r="B42" t="n">
+        <v>86416</v>
+      </c>
+      <c r="C42" t="n">
+        <v>295868</v>
+      </c>
+      <c r="D42" t="n">
+        <v>93366</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>JUAN CARLOS CALVO RUIZ</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>SEND MXL</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>08-01-2026 13:04:20</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>02-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I42" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L42" t="n">
+        <v>549</v>
+      </c>
+      <c r="M42" t="n">
+        <v>5</v>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>07-07-2026 13:04:20</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P42" t="n">
+        <v>68042</v>
+      </c>
+      <c r="Q42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>41</v>
+      </c>
+      <c r="B43" t="n">
+        <v>86654</v>
+      </c>
+      <c r="C43" t="n">
+        <v>44470</v>
+      </c>
+      <c r="D43" t="n">
+        <v>42333</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>JAVIER FRUTERO LOPEZ</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>SANTA FE</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>09-01-2026 20:52:01</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>02-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L43" t="n">
+        <v>599</v>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P43" t="n">
+        <v>71003</v>
+      </c>
+      <c r="Q43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>42</v>
+      </c>
+      <c r="B44" t="n">
+        <v>91215</v>
+      </c>
+      <c r="C44" t="n">
+        <v>339078</v>
+      </c>
+      <c r="D44" t="n">
+        <v>16896</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>PEDRO  MORALEZ  ESPARZA</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>SALTILLO VILLALTA</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>01-02-2026 9:01:18</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>01-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I44" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L44" t="n">
+        <v>649</v>
+      </c>
+      <c r="M44" t="n">
+        <v>11</v>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>27-01-2027 9:01:18</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr"/>
+      <c r="Q44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>43</v>
+      </c>
+      <c r="B45" t="n">
+        <v>91230</v>
+      </c>
+      <c r="C45" t="n">
+        <v>339766</v>
+      </c>
+      <c r="D45" t="n">
+        <v>17584</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>PEDRO PABLO  PONS HINOJOSA</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>METEPEC</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>01-02-2026 10:35:11</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>01-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I45" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L45" t="n">
+        <v>649</v>
+      </c>
+      <c r="M45" t="n">
+        <v>11</v>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>27-01-2027 10:35:11</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr"/>
+      <c r="Q45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>44</v>
+      </c>
+      <c r="B46" t="n">
+        <v>91232</v>
+      </c>
+      <c r="C46" t="n">
+        <v>339777</v>
+      </c>
+      <c r="D46" t="n">
+        <v>17595</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>GISSEL LILIAN RODRIGUEZ SILVA</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>SAN LUIS</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>01-02-2026 10:52:55</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>01-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I46" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L46" t="n">
+        <v>649</v>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr"/>
+      <c r="Q46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>45</v>
+      </c>
+      <c r="B47" t="n">
+        <v>91247</v>
+      </c>
+      <c r="C47" t="n">
+        <v>337632</v>
+      </c>
+      <c r="D47" t="n">
+        <v>15451</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>MIRNA  RODRIGUEZ  REYES</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>SALTILLO VILLALTA</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>01-02-2026 13:00:49</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>01-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I47" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L47" t="n">
+        <v>649</v>
+      </c>
+      <c r="M47" t="n">
+        <v>11</v>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>27-01-2027 13:00:49</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr"/>
+      <c r="Q47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>46</v>
+      </c>
+      <c r="B48" t="n">
+        <v>91249</v>
+      </c>
+      <c r="C48" t="n">
+        <v>339720</v>
+      </c>
+      <c r="D48" t="n">
+        <v>17538</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>ROCIO   DAVALOS  SANTIAGO</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>METEPEC</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>01-02-2026 13:05:41</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>01-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L48" t="n">
+        <v>649</v>
+      </c>
+      <c r="M48" t="n">
+        <v>11</v>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>27-01-2027 13:05:41</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr"/>
+      <c r="Q48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>47</v>
+      </c>
+      <c r="B49" t="n">
+        <v>91266</v>
+      </c>
+      <c r="C49" t="n">
+        <v>339854</v>
+      </c>
+      <c r="D49" t="n">
+        <v>17672</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>DIEGO ARMANDO MEDINA PIEDRA</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>SAN LUIS</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>02-02-2026 5:45:55</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>02-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I49" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L49" t="n">
+        <v>999</v>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr"/>
+      <c r="Q49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>48</v>
+      </c>
+      <c r="B50" t="n">
+        <v>88741</v>
+      </c>
+      <c r="C50" t="n">
+        <v>254</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>00254</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>ARMANDO DEL REAL RODRIGUEZ</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>SEND MXL</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>19-01-2026 20:25:53</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>02-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L50" t="n">
+        <v>449</v>
+      </c>
+      <c r="M50" t="n">
+        <v>5</v>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>18-07-2026 20:25:53</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P50" t="n">
+        <v>49492</v>
+      </c>
+      <c r="Q50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>49</v>
+      </c>
+      <c r="B51" t="n">
+        <v>86018</v>
+      </c>
+      <c r="C51" t="n">
+        <v>301022</v>
+      </c>
+      <c r="D51" t="n">
+        <v>98520</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>IRIS GABRIELA  MEDINA  PEREZA</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>PABELLON RTO</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>06-01-2026 11:00:27</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>02-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I51" t="n">
+        <v>0</v>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L51" t="n">
+        <v>349</v>
+      </c>
+      <c r="M51" t="n">
+        <v>5</v>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>05-07-2026 11:00:27</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P51" t="n">
+        <v>77058</v>
+      </c>
+      <c r="Q51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>50</v>
+      </c>
+      <c r="B52" t="n">
+        <v>91221</v>
+      </c>
+      <c r="C52" t="n">
+        <v>339753</v>
+      </c>
+      <c r="D52" t="n">
+        <v>17571</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>FEDERICO  AMARO DAVILA</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>STA CATARINA</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>01-02-2026 9:51:56</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>01-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I52" t="n">
+        <v>0</v>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L52" t="n">
+        <v>499</v>
+      </c>
+      <c r="M52" t="n">
+        <v>11</v>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>27-01-2027 9:51:56</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr"/>
+      <c r="Q52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>51</v>
+      </c>
+      <c r="B53" t="n">
+        <v>91222</v>
+      </c>
+      <c r="C53" t="n">
+        <v>339752</v>
+      </c>
+      <c r="D53" t="n">
+        <v>17570</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>SONIA MURILLO ZIRANDA</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>TLALNEPANTLA</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>01-02-2026 9:54:30</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>01-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I53" t="n">
+        <v>0</v>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L53" t="n">
+        <v>649</v>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr"/>
+      <c r="Q53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>52</v>
+      </c>
+      <c r="B54" t="n">
+        <v>91239</v>
+      </c>
+      <c r="C54" t="n">
+        <v>338518</v>
+      </c>
+      <c r="D54" t="n">
+        <v>16336</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>ARIANE CHAVEZ FIGEROA</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>SALTILLO VILLALTA</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>01-02-2026 11:51:20</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>01-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I54" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L54" t="n">
+        <v>799</v>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr"/>
+      <c r="Q54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>53</v>
+      </c>
+      <c r="B55" t="n">
+        <v>91257</v>
+      </c>
+      <c r="C55" t="n">
+        <v>339827</v>
+      </c>
+      <c r="D55" t="n">
+        <v>17645</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>GERARDO ALEXIS TAPIA  TELLEZ</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>STA CATARINA</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>01-02-2026 14:02:02</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>01-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I55" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L55" t="n">
+        <v>1449</v>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr"/>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr"/>
+      <c r="Q55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>54</v>
+      </c>
+      <c r="B56" t="n">
+        <v>91258</v>
+      </c>
+      <c r="C56" t="n">
+        <v>339828</v>
+      </c>
+      <c r="D56" t="n">
+        <v>17646</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>WENDERLEIN HERMIDA NAVARRO</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>PASEO 2000</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>01-02-2026 14:24:04</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>01-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I56" t="n">
+        <v>0</v>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L56" t="n">
+        <v>649</v>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr"/>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr"/>
+      <c r="Q56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>55</v>
+      </c>
+      <c r="B57" t="n">
+        <v>91271</v>
+      </c>
+      <c r="C57" t="n">
+        <v>339868</v>
+      </c>
+      <c r="D57" t="n">
+        <v>17686</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>AILANI ABIGAIL CORONADO  DE LA ROCHA</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>SEND SALTILLO</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>02-02-2026 6:42:46</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>02-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I57" t="n">
+        <v>0</v>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L57" t="n">
+        <v>499</v>
+      </c>
+      <c r="M57" t="n">
+        <v>11</v>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>28-01-2027 6:42:46</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr"/>
+      <c r="Q57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>56</v>
+      </c>
+      <c r="B58" t="n">
+        <v>91272</v>
+      </c>
+      <c r="C58" t="n">
+        <v>173355</v>
+      </c>
+      <c r="D58" t="n">
+        <v>70863</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>CYNTHIA LILIAN OLIVAS  SANCHEZ</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>SANTA FE</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>02-02-2026 6:54:18</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>10-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I58" t="n">
+        <v>0</v>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L58" t="n">
+        <v>449</v>
+      </c>
+      <c r="M58" t="n">
+        <v>11</v>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>28-01-2027 6:54:18</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P58" t="n">
+        <v>62206</v>
+      </c>
+      <c r="Q58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>57</v>
+      </c>
+      <c r="B59" t="n">
+        <v>91275</v>
+      </c>
+      <c r="C59" t="n">
+        <v>87627</v>
+      </c>
+      <c r="D59" t="n">
+        <v>85407</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>ARIATNE SCARLET BAEZ PEREZ</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>SAN ISIDRO CUL</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>02-02-2026 7:06:56</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>02-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I59" t="n">
+        <v>0</v>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L59" t="n">
+        <v>1449</v>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr"/>
+      <c r="Q59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>58</v>
+      </c>
+      <c r="B60" t="n">
+        <v>87297</v>
+      </c>
+      <c r="C60" t="n">
+        <v>326372</v>
+      </c>
+      <c r="D60" t="n">
+        <v>23311</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>ANA LAURA  CALDERON VELA</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>SEND CHIH</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>13-01-2026 14:31:16</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>02-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I60" t="n">
+        <v>0</v>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L60" t="n">
+        <v>499</v>
+      </c>
+      <c r="M60" t="n">
+        <v>11</v>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>08-01-2027 14:31:16</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P60" t="n">
+        <v>84089</v>
+      </c>
+      <c r="Q60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>59</v>
+      </c>
+      <c r="B61" t="n">
+        <v>91223</v>
+      </c>
+      <c r="C61" t="n">
+        <v>339751</v>
+      </c>
+      <c r="D61" t="n">
+        <v>17569</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>GILBERTO GUTIERREZ VALDES</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>SALTILLO VILLALTA</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>01-02-2026 9:54:38</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>01-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I61" t="n">
+        <v>0</v>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L61" t="n">
+        <v>649</v>
+      </c>
+      <c r="M61" t="n">
+        <v>11</v>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>27-01-2027 9:54:38</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr"/>
+      <c r="Q61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>60</v>
+      </c>
+      <c r="B62" t="n">
+        <v>91224</v>
+      </c>
+      <c r="C62" t="n">
+        <v>338952</v>
+      </c>
+      <c r="D62" t="n">
+        <v>16770</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>ANABEL  MARTINEZ  PLATA</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>IXTAPALUCA</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>01-02-2026 9:59:59</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>01-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I62" t="n">
+        <v>0</v>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L62" t="n">
+        <v>499</v>
+      </c>
+      <c r="M62" t="n">
+        <v>11</v>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>27-01-2027 9:59:59</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr"/>
+      <c r="Q62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>61</v>
+      </c>
+      <c r="B63" t="n">
+        <v>91238</v>
+      </c>
+      <c r="C63" t="n">
+        <v>339793</v>
+      </c>
+      <c r="D63" t="n">
+        <v>17611</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>DANIEL NAJERA YUTANI</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>SALTILLO VILLALTA</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>01-02-2026 11:46:05</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>01-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I63" t="n">
+        <v>0</v>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L63" t="n">
+        <v>649</v>
+      </c>
+      <c r="M63" t="n">
+        <v>11</v>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>27-01-2027 11:46:05</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr"/>
+      <c r="Q63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>62</v>
+      </c>
+      <c r="B64" t="n">
+        <v>91256</v>
+      </c>
+      <c r="C64" t="n">
+        <v>339825</v>
+      </c>
+      <c r="D64" t="n">
+        <v>17643</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>PEDRO ALFREDO VILLARRUEL RIVERA</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>STA CATARINA</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>01-02-2026 13:57:54</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>01-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I64" t="n">
+        <v>0</v>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L64" t="n">
+        <v>1449</v>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr"/>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr"/>
+      <c r="Q64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>63</v>
+      </c>
+      <c r="B65" t="n">
+        <v>90637</v>
+      </c>
+      <c r="C65" t="n">
+        <v>281528</v>
+      </c>
+      <c r="D65" t="n">
+        <v>79029</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>VANESSA CRISTAL OLIVARES CASTILLO</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>SEND SALTILLO</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>29-01-2026 4:57:02</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>02-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I65" t="n">
+        <v>0</v>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L65" t="n">
+        <v>499</v>
+      </c>
+      <c r="M65" t="n">
+        <v>11</v>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>24-01-2027 4:57:02</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P65" t="n">
+        <v>59557</v>
+      </c>
+      <c r="Q65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>64</v>
+      </c>
+      <c r="B66" t="n">
+        <v>85558</v>
+      </c>
+      <c r="C66" t="n">
+        <v>326457</v>
+      </c>
+      <c r="D66" t="n">
+        <v>23396</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>ISABEL CARRIZOSA IDELFONSO</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>INSURGENTES</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>05-01-2026 4:01:21</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>02-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I66" t="n">
+        <v>0</v>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L66" t="n">
+        <v>649</v>
+      </c>
+      <c r="M66" t="n">
+        <v>11</v>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>31-12-2026 4:01:21</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P66" t="n">
+        <v>83293</v>
+      </c>
+      <c r="Q66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Reporte generado: 02-02-2026 03:42 p. m.</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr"/>
+      <c r="C67" t="inlineStr"/>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr"/>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
+      <c r="O67" t="inlineStr"/>
+      <c r="P67" t="inlineStr"/>
+      <c r="Q67" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/descargas/cargos_recurrentes.xlsx
+++ b/data/descargas/cargos_recurrentes.xlsx
@@ -601,7 +601,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reporte generado: 01-03-2026 07:22 a. m. </t>
+          <t xml:space="preserve">Reporte generado: 01-03-2026 07:49 a. m. </t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>

--- a/data/descargas/cargos_recurrentes.xlsx
+++ b/data/descargas/cargos_recurrentes.xlsx
@@ -601,7 +601,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reporte generado: 01-03-2026 07:49 a. m. </t>
+          <t>Reporte generado: 01-03-2026 03:26 p. m.</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>

--- a/data/descargas/cargos_recurrentes.xlsx
+++ b/data/descargas/cargos_recurrentes.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q3"/>
+  <dimension ref="A1:Q83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -599,27 +599,5257 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Reporte generado: 01-03-2026 03:26 p. m.</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="n">
+        <v>93900</v>
+      </c>
+      <c r="C3" t="n">
+        <v>339720</v>
+      </c>
+      <c r="D3" t="n">
+        <v>17538</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>ROCIO   DAVALOS  SANTIAGO</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>METEPEC</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>17-02-2026 16:46:14</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>01-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>649</v>
+      </c>
+      <c r="M3" t="n">
+        <v>11</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>12-02-2027 16:46:14</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P3" t="n">
+        <v>91249</v>
+      </c>
       <c r="Q3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="n">
+        <v>95329</v>
+      </c>
+      <c r="C4" t="n">
+        <v>347294</v>
+      </c>
+      <c r="D4" t="n">
+        <v>89459</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>KANNAN VINODHINI VINODHINI</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>SALTILLO VILLALTA</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>01-03-2026 10:16:36</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>01-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>649</v>
+      </c>
+      <c r="M4" t="n">
+        <v>11</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>24-02-2027 10:16:36</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="n">
+        <v>95331</v>
+      </c>
+      <c r="C5" t="n">
+        <v>347297</v>
+      </c>
+      <c r="D5" t="n">
+        <v>89462</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>HUGO RAUL HERNANDEZ ANGULO</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>PAPALOTE TJ</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>01-03-2026 10:30:23</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>01-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>649</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="n">
+        <v>95338</v>
+      </c>
+      <c r="C6" t="n">
+        <v>347312</v>
+      </c>
+      <c r="D6" t="n">
+        <v>89477</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>DAGOBERTO  GARZA MORENO</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>SALTILLO VILLALTA</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>01-03-2026 11:04:52</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>01-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>649</v>
+      </c>
+      <c r="M6" t="n">
+        <v>11</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>24-02-2027 11:04:52</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" t="n">
+        <v>95340</v>
+      </c>
+      <c r="C7" t="n">
+        <v>347320</v>
+      </c>
+      <c r="D7" t="n">
+        <v>89485</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>DANIA ALEXIA  RODRIGUEZ ESTRADA</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>TLALNEPANTLA</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>01-03-2026 11:31:04</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>01-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>549</v>
+      </c>
+      <c r="M7" t="n">
+        <v>11</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>24-02-2027 11:31:04</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" t="n">
+        <v>95363</v>
+      </c>
+      <c r="C8" t="n">
+        <v>234570</v>
+      </c>
+      <c r="D8" t="n">
+        <v>32075</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>JESUS ALEJANDRO SANCHEZ VALENCIA</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>SEND MXL</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>01-03-2026 15:08:34</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>01-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>499</v>
+      </c>
+      <c r="M8" t="n">
+        <v>11</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>24-02-2027 15:08:34</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P8" t="n">
+        <v>27299</v>
+      </c>
+      <c r="Q8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" t="n">
+        <v>95365</v>
+      </c>
+      <c r="C9" t="n">
+        <v>73348</v>
+      </c>
+      <c r="D9" t="n">
+        <v>71166</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>EDGAR EDUARDO  MARTINEZ  SOTO</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>STA CATARINA</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>02-03-2026 3:10:19</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>649</v>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" t="n">
+        <v>95370</v>
+      </c>
+      <c r="C10" t="n">
+        <v>305341</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>02840</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>GERARDO RAFAEL MONARRES MASCORRO</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>SEND SALTILLO</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>02-03-2026 4:34:20</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>549</v>
+      </c>
+      <c r="M10" t="n">
+        <v>11</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>25-02-2027 4:34:20</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" t="n">
+        <v>95395</v>
+      </c>
+      <c r="C11" t="n">
+        <v>207110</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>04618</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>YULIANA ELIBETH SERRANO CASTELLANOS</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>PABELLON RTO</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>02-03-2026 7:12:52</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>02-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>1449</v>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" t="n">
+        <v>90192</v>
+      </c>
+      <c r="C12" t="n">
+        <v>310982</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>08481</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>MICHELLE JAZMIN ARAGÓN LOZANO NA NA</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>INDEPENDENCIA</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>26-01-2026 20:29:28</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>26-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>599</v>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>76333</v>
+      </c>
+      <c r="Q12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" t="n">
+        <v>91899</v>
+      </c>
+      <c r="C13" t="n">
+        <v>124893</v>
+      </c>
+      <c r="D13" t="n">
+        <v>22569</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>JENNIFER  BARBAY XXX</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>TEC MXL</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>04-02-2026 12:34:42</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>449</v>
+      </c>
+      <c r="M13" t="n">
+        <v>11</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>30-01-2027 12:34:42</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>65571</v>
+      </c>
+      <c r="Q13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" t="n">
+        <v>95275</v>
+      </c>
+      <c r="C14" t="n">
+        <v>268123</v>
+      </c>
+      <c r="D14" t="n">
+        <v>65626</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>JOEL CARREON CUELLAR</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>SEND CHIH</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>28-02-2026 11:28:33</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
+        <v>449</v>
+      </c>
+      <c r="M14" t="n">
+        <v>5</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>27-08-2026 11:28:33</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>49343</v>
+      </c>
+      <c r="Q14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" t="n">
+        <v>95324</v>
+      </c>
+      <c r="C15" t="n">
+        <v>347277</v>
+      </c>
+      <c r="D15" t="n">
+        <v>89442</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>HUMBERTO BADILLO VALENCIA</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>TLALNEPANTLA</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>01-03-2026 9:02:59</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>01-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L15" t="n">
+        <v>549</v>
+      </c>
+      <c r="M15" t="n">
+        <v>11</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>24-02-2027 9:02:59</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" t="n">
+        <v>95326</v>
+      </c>
+      <c r="C16" t="n">
+        <v>347287</v>
+      </c>
+      <c r="D16" t="n">
+        <v>89452</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>KONDURAM  SANKARPANDI SANKARPANDI</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>SALTILLO VILLALTA</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>01-03-2026 9:59:47</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>01-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L16" t="n">
+        <v>649</v>
+      </c>
+      <c r="M16" t="n">
+        <v>11</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>24-02-2027 9:59:47</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" t="n">
+        <v>95343</v>
+      </c>
+      <c r="C17" t="n">
+        <v>347322</v>
+      </c>
+      <c r="D17" t="n">
+        <v>89487</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>OSCAR DANIEL  HERNANDEZ  CARRIZOSA</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>INSURGENTES</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>01-03-2026 11:46:09</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>01-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L17" t="n">
+        <v>649</v>
+      </c>
+      <c r="M17" t="n">
+        <v>11</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>24-02-2027 11:46:09</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" t="n">
+        <v>95358</v>
+      </c>
+      <c r="C18" t="n">
+        <v>153046</v>
+      </c>
+      <c r="D18" t="n">
+        <v>50605</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>PERLA  AGUIRRE  PIÑON</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>SEND MXL</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>01-03-2026 13:53:08</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>01-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L18" t="n">
+        <v>499</v>
+      </c>
+      <c r="M18" t="n">
+        <v>11</v>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>24-02-2027 13:53:08</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P18" t="n">
+        <v>78587</v>
+      </c>
+      <c r="Q18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" t="n">
+        <v>95360</v>
+      </c>
+      <c r="C19" t="n">
+        <v>347356</v>
+      </c>
+      <c r="D19" t="n">
+        <v>89521</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>MAGDIELA RADAIN  CORONADO  CASTILLO</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>CARROUSEL TJ</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>01-03-2026 14:41:50</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>01-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L19" t="n">
+        <v>549</v>
+      </c>
+      <c r="M19" t="n">
+        <v>11</v>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>24-02-2027 14:41:50</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" t="n">
+        <v>95375</v>
+      </c>
+      <c r="C20" t="n">
+        <v>347380</v>
+      </c>
+      <c r="D20" t="n">
+        <v>89545</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>OMAR BARRAZA AYON</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>SAN ISIDRO CUL</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>02-03-2026 5:17:00</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>02-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L20" t="n">
+        <v>1449</v>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" t="n">
+        <v>95377</v>
+      </c>
+      <c r="C21" t="n">
+        <v>347316</v>
+      </c>
+      <c r="D21" t="n">
+        <v>89481</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>EDUARD LOPEZ ALVAREZ</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>METEPEC</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>02-03-2026 5:21:41</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L21" t="n">
+        <v>649</v>
+      </c>
+      <c r="M21" t="n">
+        <v>11</v>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>25-02-2027 5:21:41</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" t="n">
+        <v>91599</v>
+      </c>
+      <c r="C22" t="n">
+        <v>3167</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>02168</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>MANUEL ALFREDO NIEBLA  INZUNZA</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>SEND MXL</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>03-02-2026 10:07:39</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L22" t="n">
+        <v>449</v>
+      </c>
+      <c r="M22" t="n">
+        <v>11</v>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>29-01-2027 10:07:39</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P22" t="n">
+        <v>91323</v>
+      </c>
+      <c r="Q22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" t="n">
+        <v>95075</v>
+      </c>
+      <c r="C23" t="n">
+        <v>231664</v>
+      </c>
+      <c r="D23" t="n">
+        <v>29169</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>RAUL HERNEY CHARA PEREZ</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>SANTA FE</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>27-02-2026 5:34:34</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>01-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L23" t="n">
+        <v>549</v>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P23" t="n">
+        <v>49241</v>
+      </c>
+      <c r="Q23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>22</v>
+      </c>
+      <c r="B24" t="n">
+        <v>95345</v>
+      </c>
+      <c r="C24" t="n">
+        <v>202450</v>
+      </c>
+      <c r="D24" t="n">
+        <v>99957</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>YULIANA SANTIAGO GARCIA</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>SEND MXL</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>01-03-2026 12:12:02</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>01-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L24" t="n">
+        <v>499</v>
+      </c>
+      <c r="M24" t="n">
+        <v>11</v>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>24-02-2027 12:12:02</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P24" t="n">
+        <v>67081</v>
+      </c>
+      <c r="Q24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>23</v>
+      </c>
+      <c r="B25" t="n">
+        <v>95347</v>
+      </c>
+      <c r="C25" t="n">
+        <v>347323</v>
+      </c>
+      <c r="D25" t="n">
+        <v>89488</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>MARIA ANTONIETA MADRIGAL  ARROYO</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>TLALNEPANTLA</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>01-03-2026 12:21:47</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>01-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L25" t="n">
+        <v>549</v>
+      </c>
+      <c r="M25" t="n">
+        <v>11</v>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>24-02-2027 12:21:47</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>24</v>
+      </c>
+      <c r="B26" t="n">
+        <v>95354</v>
+      </c>
+      <c r="C26" t="n">
+        <v>347345</v>
+      </c>
+      <c r="D26" t="n">
+        <v>89510</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>KAREN NAOMI MENDIETA  HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>METEPEC</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>01-03-2026 13:08:09</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>01-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L26" t="n">
+        <v>549</v>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>25</v>
+      </c>
+      <c r="B27" t="n">
+        <v>95356</v>
+      </c>
+      <c r="C27" t="n">
+        <v>221787</v>
+      </c>
+      <c r="D27" t="n">
+        <v>19294</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>YESSICA GUADALUPE GARCIA CASTRO</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>SAN LUIS</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>01-03-2026 13:32:56</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>01-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L27" t="n">
+        <v>549</v>
+      </c>
+      <c r="M27" t="n">
+        <v>11</v>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>24-02-2027 13:32:56</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>26</v>
+      </c>
+      <c r="B28" t="n">
+        <v>95379</v>
+      </c>
+      <c r="C28" t="n">
+        <v>347395</v>
+      </c>
+      <c r="D28" t="n">
+        <v>89560</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>FERNANDA MITCHELL  OCHOA RIESTRA</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>SALTILLO VILLALTA</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>02-03-2026 6:07:47</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L28" t="n">
+        <v>799</v>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>27</v>
+      </c>
+      <c r="B29" t="n">
+        <v>95381</v>
+      </c>
+      <c r="C29" t="n">
+        <v>225936</v>
+      </c>
+      <c r="D29" t="n">
+        <v>23443</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>EVELIN AMEYALI SANCHEZ HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>SEND SALTILLO</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>02-03-2026 6:17:04</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L29" t="n">
+        <v>499</v>
+      </c>
+      <c r="M29" t="n">
+        <v>11</v>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>25-02-2027 6:17:04</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P29" t="n">
+        <v>21527</v>
+      </c>
+      <c r="Q29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>28</v>
+      </c>
+      <c r="B30" t="n">
+        <v>93114</v>
+      </c>
+      <c r="C30" t="n">
+        <v>105268</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>03013</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>KAREN YAMILETH MENDEZ RUEDA</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>MISION ENS</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>12-02-2026 8:23:05</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L30" t="n">
+        <v>549</v>
+      </c>
+      <c r="M30" t="n">
+        <v>11</v>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>07-02-2027 8:23:05</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P30" t="n">
+        <v>91280</v>
+      </c>
+      <c r="Q30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>29</v>
+      </c>
+      <c r="B31" t="n">
+        <v>93373</v>
+      </c>
+      <c r="C31" t="n">
+        <v>343681</v>
+      </c>
+      <c r="D31" t="n">
+        <v>21498</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>LUIS JESUS  DEBEZ NIETO</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>METEPEC</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>14-02-2026 10:10:26</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>14-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L31" t="n">
+        <v>649</v>
+      </c>
+      <c r="M31" t="n">
+        <v>11</v>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>09-02-2027 10:10:26</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>30</v>
+      </c>
+      <c r="B32" t="n">
+        <v>91537</v>
+      </c>
+      <c r="C32" t="n">
+        <v>261466</v>
+      </c>
+      <c r="D32" t="n">
+        <v>58970</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>JOSE ANGEL GUTIERREZ DIAZ</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>TEC MXL</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>02-02-2026 21:04:40</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>01-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L32" t="n">
+        <v>599</v>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P32" t="n">
+        <v>65120</v>
+      </c>
+      <c r="Q32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>31</v>
+      </c>
+      <c r="B33" t="n">
+        <v>91988</v>
+      </c>
+      <c r="C33" t="n">
+        <v>271360</v>
+      </c>
+      <c r="D33" t="n">
+        <v>68862</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>CLAUDIA ANGELICA CALDERA YAÑEZ</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>SANTA FE</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>04-02-2026 19:05:14</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L33" t="n">
+        <v>549</v>
+      </c>
+      <c r="M33" t="n">
+        <v>5</v>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>03-08-2026 19:05:14</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P33" t="n">
+        <v>51939</v>
+      </c>
+      <c r="Q33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>32</v>
+      </c>
+      <c r="B34" t="n">
+        <v>95328</v>
+      </c>
+      <c r="C34" t="n">
+        <v>347290</v>
+      </c>
+      <c r="D34" t="n">
+        <v>89455</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>VELLADURAI  KIRUTHIKA KIRUTHIKA</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>SALTILLO VILLALTA</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>01-03-2026 10:08:26</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>01-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L34" t="n">
+        <v>649</v>
+      </c>
+      <c r="M34" t="n">
+        <v>11</v>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>24-02-2027 10:08:26</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>33</v>
+      </c>
+      <c r="B35" t="n">
+        <v>95332</v>
+      </c>
+      <c r="C35" t="n">
+        <v>347298</v>
+      </c>
+      <c r="D35" t="n">
+        <v>89463</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>ROBERTO AARON GALINDO  JIMENEZ</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>METEPEC</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>01-03-2026 10:30:37</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>01-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I35" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L35" t="n">
+        <v>799</v>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>34</v>
+      </c>
+      <c r="B36" t="n">
+        <v>95339</v>
+      </c>
+      <c r="C36" t="n">
+        <v>347317</v>
+      </c>
+      <c r="D36" t="n">
+        <v>89482</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>ARMANDO ALEJANDRO SALAZAR  AGUILAR</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>METEPEC</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>01-03-2026 11:17:37</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>01-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L36" t="n">
+        <v>649</v>
+      </c>
+      <c r="M36" t="n">
+        <v>11</v>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>24-02-2027 11:17:37</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>35</v>
+      </c>
+      <c r="B37" t="n">
+        <v>95346</v>
+      </c>
+      <c r="C37" t="n">
+        <v>347333</v>
+      </c>
+      <c r="D37" t="n">
+        <v>89498</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>ERIKA JAZMIN  RIOS VALDESPINO</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>METEPEC</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>01-03-2026 12:19:40</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>01-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L37" t="n">
+        <v>549</v>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>36</v>
+      </c>
+      <c r="B38" t="n">
+        <v>95353</v>
+      </c>
+      <c r="C38" t="n">
+        <v>316183</v>
+      </c>
+      <c r="D38" t="n">
+        <v>13682</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>ARACELY GOMEZ PIZZARRO</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>SEND CHIH</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>01-03-2026 13:02:15</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>01-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I38" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L38" t="n">
+        <v>549</v>
+      </c>
+      <c r="M38" t="n">
+        <v>11</v>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>24-02-2027 13:02:15</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr"/>
+      <c r="Q38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>37</v>
+      </c>
+      <c r="B39" t="n">
+        <v>95357</v>
+      </c>
+      <c r="C39" t="n">
+        <v>347167</v>
+      </c>
+      <c r="D39" t="n">
+        <v>89332</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>AYLIN CAMPOY DURAN</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>SANTA FE</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>01-03-2026 13:50:09</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>01-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I39" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L39" t="n">
+        <v>649</v>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>38</v>
+      </c>
+      <c r="B40" t="n">
+        <v>95364</v>
+      </c>
+      <c r="C40" t="n">
+        <v>73349</v>
+      </c>
+      <c r="D40" t="n">
+        <v>71167</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>LUCERO VIRIDIANA  LEAL  GUERRERO</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>STA CATARINA</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>02-03-2026 3:08:16</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I40" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L40" t="n">
+        <v>649</v>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr"/>
+      <c r="Q40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>39</v>
+      </c>
+      <c r="B41" t="n">
+        <v>95371</v>
+      </c>
+      <c r="C41" t="n">
+        <v>347371</v>
+      </c>
+      <c r="D41" t="n">
+        <v>89536</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>ALBERTO ORTIGOZA  PEREZ</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>INSURGENTES</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>02-03-2026 4:39:54</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I41" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L41" t="n">
+        <v>549</v>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr"/>
+      <c r="Q41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>40</v>
+      </c>
+      <c r="B42" t="n">
+        <v>95382</v>
+      </c>
+      <c r="C42" t="n">
+        <v>225937</v>
+      </c>
+      <c r="D42" t="n">
+        <v>23444</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>LUIS RAUL VALENCIA CABRERA</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>SEND SALTILLO</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>02-03-2026 6:22:42</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I42" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L42" t="n">
+        <v>499</v>
+      </c>
+      <c r="M42" t="n">
+        <v>11</v>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>25-02-2027 6:22:42</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P42" t="n">
+        <v>21526</v>
+      </c>
+      <c r="Q42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>41</v>
+      </c>
+      <c r="B43" t="n">
+        <v>95389</v>
+      </c>
+      <c r="C43" t="n">
+        <v>347405</v>
+      </c>
+      <c r="D43" t="n">
+        <v>89570</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>ITZEL KARINA GAXIOLA VALENCIA</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>PASEO 2000</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>02-03-2026 6:38:46</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L43" t="n">
+        <v>549</v>
+      </c>
+      <c r="M43" t="n">
+        <v>11</v>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>25-02-2027 6:38:46</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr"/>
+      <c r="Q43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>42</v>
+      </c>
+      <c r="B44" t="n">
+        <v>95396</v>
+      </c>
+      <c r="C44" t="n">
+        <v>346395</v>
+      </c>
+      <c r="D44" t="n">
+        <v>88560</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>DAVID ALBERTO GONZALEZ GALVAN</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>STA CATARINA</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>02-03-2026 7:14:40</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I44" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L44" t="n">
+        <v>499</v>
+      </c>
+      <c r="M44" t="n">
+        <v>11</v>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>25-02-2027 7:14:40</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr"/>
+      <c r="Q44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>43</v>
+      </c>
+      <c r="B45" t="n">
+        <v>93903</v>
+      </c>
+      <c r="C45" t="n">
+        <v>227245</v>
+      </c>
+      <c r="D45" t="n">
+        <v>24750</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>CAROLINA MANRIQUE RODRIGUEZ</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>SANTA FE</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>17-02-2026 16:47:11</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>01-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I45" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L45" t="n">
+        <v>549</v>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P45" t="n">
+        <v>21990</v>
+      </c>
+      <c r="Q45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>44</v>
+      </c>
+      <c r="B46" t="n">
+        <v>94217</v>
+      </c>
+      <c r="C46" t="n">
+        <v>301684</v>
+      </c>
+      <c r="D46" t="n">
+        <v>99182</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>RICARDO ALONSO ANGULO SALAZAR</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>INDEPENDENCIA</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>19-02-2026 20:57:08</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>01-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I46" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L46" t="n">
+        <v>499</v>
+      </c>
+      <c r="M46" t="n">
+        <v>11</v>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>14-02-2027 20:57:08</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P46" t="n">
+        <v>70989</v>
+      </c>
+      <c r="Q46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>45</v>
+      </c>
+      <c r="B47" t="n">
+        <v>95325</v>
+      </c>
+      <c r="C47" t="n">
+        <v>347284</v>
+      </c>
+      <c r="D47" t="n">
+        <v>89449</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>EMMANUEL  MARTINEZ BARRERA</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>METEPEC</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>01-03-2026 9:34:02</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>01-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I47" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L47" t="n">
+        <v>649</v>
+      </c>
+      <c r="M47" t="n">
+        <v>11</v>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>24-02-2027 9:34:02</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr"/>
+      <c r="Q47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>46</v>
+      </c>
+      <c r="B48" t="n">
+        <v>95327</v>
+      </c>
+      <c r="C48" t="n">
+        <v>279008</v>
+      </c>
+      <c r="D48" t="n">
+        <v>76509</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>KARINA ZAVALA FLORES</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>STA CATARINA</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>01-03-2026 10:07:58</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>01-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L48" t="n">
+        <v>499</v>
+      </c>
+      <c r="M48" t="n">
+        <v>11</v>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>24-02-2027 10:07:58</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P48" t="n">
+        <v>76927</v>
+      </c>
+      <c r="Q48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>47</v>
+      </c>
+      <c r="B49" t="n">
+        <v>95344</v>
+      </c>
+      <c r="C49" t="n">
+        <v>347328</v>
+      </c>
+      <c r="D49" t="n">
+        <v>89493</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>BERTHA JIMENEZ RODRIGUEZ</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>METEPEC</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>01-03-2026 12:07:18</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>01-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I49" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L49" t="n">
+        <v>799</v>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr"/>
+      <c r="Q49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>48</v>
+      </c>
+      <c r="B50" t="n">
+        <v>95359</v>
+      </c>
+      <c r="C50" t="n">
+        <v>67454</v>
+      </c>
+      <c r="D50" t="n">
+        <v>65285</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>RICARDO ORLANDO CRUZ RAMOS</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>SEND CUL</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>01-03-2026 14:14:05</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>01-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L50" t="n">
+        <v>649</v>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr"/>
+      <c r="Q50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>49</v>
+      </c>
+      <c r="B51" t="n">
+        <v>95374</v>
+      </c>
+      <c r="C51" t="n">
+        <v>309789</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>07288</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>ALMA GAMBOA MORENO</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>STA CATARINA</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>02-03-2026 5:14:32</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>02-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I51" t="n">
+        <v>0</v>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L51" t="n">
+        <v>1449</v>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr"/>
+      <c r="Q51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>50</v>
+      </c>
+      <c r="B52" t="n">
+        <v>95378</v>
+      </c>
+      <c r="C52" t="n">
+        <v>261134</v>
+      </c>
+      <c r="D52" t="n">
+        <v>58638</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>ADRIANA LOPEZ HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>SEND SALTILLO</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>02-03-2026 5:46:48</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I52" t="n">
+        <v>0</v>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L52" t="n">
+        <v>549</v>
+      </c>
+      <c r="M52" t="n">
+        <v>11</v>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>25-02-2027 5:46:48</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr"/>
+      <c r="Q52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>51</v>
+      </c>
+      <c r="B53" t="n">
+        <v>95393</v>
+      </c>
+      <c r="C53" t="n">
+        <v>117484</v>
+      </c>
+      <c r="D53" t="n">
+        <v>15199</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>GUADALUPE  NALLELY GARCIA CASTRO</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>SEND SALTILLO</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>02-03-2026 7:04:56</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I53" t="n">
+        <v>0</v>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L53" t="n">
+        <v>649</v>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr"/>
+      <c r="Q53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>52</v>
+      </c>
+      <c r="B54" t="n">
+        <v>91049</v>
+      </c>
+      <c r="C54" t="n">
+        <v>259574</v>
+      </c>
+      <c r="D54" t="n">
+        <v>57078</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>ADRIANA SELENE MONROY PRADO</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>IXTAPALUCA</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>31-01-2026 6:34:54</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>01-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I54" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L54" t="n">
+        <v>399</v>
+      </c>
+      <c r="M54" t="n">
+        <v>11</v>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>26-01-2027 6:34:54</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P54" t="n">
+        <v>43061</v>
+      </c>
+      <c r="Q54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>53</v>
+      </c>
+      <c r="B55" t="n">
+        <v>91021</v>
+      </c>
+      <c r="C55" t="n">
+        <v>248642</v>
+      </c>
+      <c r="D55" t="n">
+        <v>46146</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>JOAQUIN EDUARDO  DE LOS SANTOS  RODRIGUEZ</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>IXTAPALUCA</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>30-01-2026 19:30:18</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>28-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I55" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L55" t="n">
+        <v>449</v>
+      </c>
+      <c r="M55" t="n">
+        <v>5</v>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>29-07-2026 19:30:18</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P55" t="n">
+        <v>49337</v>
+      </c>
+      <c r="Q55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>54</v>
+      </c>
+      <c r="B56" t="n">
+        <v>95333</v>
+      </c>
+      <c r="C56" t="n">
+        <v>331341</v>
+      </c>
+      <c r="D56" t="n">
+        <v>16395</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>CINTHIA SUSANA ORNELAS ZARATE</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>PAPALOTE TJ</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>01-03-2026 10:36:52</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>01-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I56" t="n">
+        <v>0</v>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L56" t="n">
+        <v>499</v>
+      </c>
+      <c r="M56" t="n">
+        <v>11</v>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>24-02-2027 10:36:52</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P56" t="n">
+        <v>85265</v>
+      </c>
+      <c r="Q56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>55</v>
+      </c>
+      <c r="B57" t="n">
+        <v>95334</v>
+      </c>
+      <c r="C57" t="n">
+        <v>347300</v>
+      </c>
+      <c r="D57" t="n">
+        <v>89465</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>IRMA  ALBARRAN  CALDERON</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>METEPEC</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>01-03-2026 10:43:49</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>01-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I57" t="n">
+        <v>0</v>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L57" t="n">
+        <v>649</v>
+      </c>
+      <c r="M57" t="n">
+        <v>11</v>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>24-02-2027 10:43:49</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr"/>
+      <c r="Q57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>56</v>
+      </c>
+      <c r="B58" t="n">
+        <v>95352</v>
+      </c>
+      <c r="C58" t="n">
+        <v>347338</v>
+      </c>
+      <c r="D58" t="n">
+        <v>89503</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>JAIR JOCSAN  YBARRA CORTES</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>INSURGENTES</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>01-03-2026 12:40:23</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>01-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I58" t="n">
+        <v>0</v>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L58" t="n">
+        <v>1549</v>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr"/>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr"/>
+      <c r="Q58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>57</v>
+      </c>
+      <c r="B59" t="n">
+        <v>95366</v>
+      </c>
+      <c r="C59" t="n">
+        <v>256268</v>
+      </c>
+      <c r="D59" t="n">
+        <v>53772</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>GUSTAVO ADOLFO GAONA ORTIZ</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>SEND SALTILLO</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>02-03-2026 4:04:32</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I59" t="n">
+        <v>0</v>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L59" t="n">
+        <v>499</v>
+      </c>
+      <c r="M59" t="n">
+        <v>11</v>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>25-02-2027 4:04:32</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P59" t="n">
+        <v>40764</v>
+      </c>
+      <c r="Q59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>58</v>
+      </c>
+      <c r="B60" t="n">
+        <v>95383</v>
+      </c>
+      <c r="C60" t="n">
+        <v>406</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>00406</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>MANUEL DE JESUS LOPEZ CHEVEZ</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>SEND MXL</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>02-03-2026 6:23:10</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I60" t="n">
+        <v>0</v>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L60" t="n">
+        <v>499</v>
+      </c>
+      <c r="M60" t="n">
+        <v>11</v>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>25-02-2027 6:23:10</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P60" t="n">
+        <v>18678</v>
+      </c>
+      <c r="Q60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>59</v>
+      </c>
+      <c r="B61" t="n">
+        <v>95384</v>
+      </c>
+      <c r="C61" t="n">
+        <v>346074</v>
+      </c>
+      <c r="D61" t="n">
+        <v>88239</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>CARLOS JACINTO  DEL ANGEL BALLESTEROS</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>METEPEC</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>02-03-2026 6:27:05</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I61" t="n">
+        <v>0</v>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L61" t="n">
+        <v>649</v>
+      </c>
+      <c r="M61" t="n">
+        <v>11</v>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>25-02-2027 6:27:05</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr"/>
+      <c r="Q61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>60</v>
+      </c>
+      <c r="B62" t="n">
+        <v>88131</v>
+      </c>
+      <c r="C62" t="n">
+        <v>318071</v>
+      </c>
+      <c r="D62" t="n">
+        <v>15568</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>MARIA DE LOS ANGELES BUSTOS MONTES DE OCA</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>INSURGENTES</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>16-01-2026 15:28:41</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>20-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I62" t="n">
+        <v>0</v>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L62" t="n">
+        <v>599</v>
+      </c>
+      <c r="M62" t="n">
+        <v>11</v>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>11-01-2027 15:28:41</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P62" t="n">
+        <v>79786</v>
+      </c>
+      <c r="Q62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>61</v>
+      </c>
+      <c r="B63" t="n">
+        <v>94415</v>
+      </c>
+      <c r="C63" t="n">
+        <v>166858</v>
+      </c>
+      <c r="D63" t="n">
+        <v>64391</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>MIGUEL ANGEL OLGUIN ORDUÑO</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>CARROUSEL TJ</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>23-02-2026 9:43:06</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>01-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I63" t="n">
+        <v>0</v>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L63" t="n">
+        <v>399</v>
+      </c>
+      <c r="M63" t="n">
+        <v>11</v>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>18-02-2027 9:43:06</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P63" t="n">
+        <v>2303</v>
+      </c>
+      <c r="Q63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>62</v>
+      </c>
+      <c r="B64" t="n">
+        <v>94416</v>
+      </c>
+      <c r="C64" t="n">
+        <v>166857</v>
+      </c>
+      <c r="D64" t="n">
+        <v>64390</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>ANAHI ROMO ACOSTA</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>CARROUSEL TJ</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>23-02-2026 9:45:26</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>01-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I64" t="n">
+        <v>0</v>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L64" t="n">
+        <v>399</v>
+      </c>
+      <c r="M64" t="n">
+        <v>11</v>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>18-02-2027 9:45:26</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P64" t="n">
+        <v>2306</v>
+      </c>
+      <c r="Q64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>63</v>
+      </c>
+      <c r="B65" t="n">
+        <v>94701</v>
+      </c>
+      <c r="C65" t="n">
+        <v>226030</v>
+      </c>
+      <c r="D65" t="n">
+        <v>23537</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>MARIA DEL PILAR ROSAS TERRONES</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>INDEPENDENCIA</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>24-02-2026 12:15:57</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I65" t="n">
+        <v>0</v>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L65" t="n">
+        <v>399</v>
+      </c>
+      <c r="M65" t="n">
+        <v>11</v>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>19-02-2027 12:15:57</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P65" t="n">
+        <v>39955</v>
+      </c>
+      <c r="Q65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>64</v>
+      </c>
+      <c r="B66" t="n">
+        <v>92547</v>
+      </c>
+      <c r="C66" t="n">
+        <v>312043</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>09542</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>YULISSA KARYME GUITRON OSORIO</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>MISION ENS</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>09-02-2026 16:11:05</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>01-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I66" t="n">
+        <v>0</v>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L66" t="n">
+        <v>599</v>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr"/>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P66" t="n">
+        <v>81210</v>
+      </c>
+      <c r="Q66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>65</v>
+      </c>
+      <c r="B67" t="n">
+        <v>95330</v>
+      </c>
+      <c r="C67" t="n">
+        <v>347295</v>
+      </c>
+      <c r="D67" t="n">
+        <v>89460</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>BABU AJITH KUMAR</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>SALTILLO VILLALTA</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>01-03-2026 10:24:48</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>01-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I67" t="n">
+        <v>0</v>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L67" t="n">
+        <v>649</v>
+      </c>
+      <c r="M67" t="n">
+        <v>11</v>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>24-02-2027 10:24:48</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr"/>
+      <c r="Q67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>66</v>
+      </c>
+      <c r="B68" t="n">
+        <v>95337</v>
+      </c>
+      <c r="C68" t="n">
+        <v>278003</v>
+      </c>
+      <c r="D68" t="n">
+        <v>75504</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>CARLOS CESAR  SORIANO  CARRANZA</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>IXTAPALUCA</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>01-03-2026 11:04:13</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>01-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I68" t="n">
+        <v>0</v>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L68" t="n">
+        <v>499</v>
+      </c>
+      <c r="M68" t="n">
+        <v>11</v>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>24-02-2027 11:04:13</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr"/>
+      <c r="Q68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>67</v>
+      </c>
+      <c r="B69" t="n">
+        <v>95348</v>
+      </c>
+      <c r="C69" t="n">
+        <v>347334</v>
+      </c>
+      <c r="D69" t="n">
+        <v>89499</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>MARIA DOLORES MADRIGAL ARROYO</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>TLALNEPANTLA</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>01-03-2026 12:29:56</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>01-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I69" t="n">
+        <v>0</v>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L69" t="n">
+        <v>549</v>
+      </c>
+      <c r="M69" t="n">
+        <v>11</v>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>24-02-2027 12:29:56</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr"/>
+      <c r="Q69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>68</v>
+      </c>
+      <c r="B70" t="n">
+        <v>95355</v>
+      </c>
+      <c r="C70" t="n">
+        <v>347033</v>
+      </c>
+      <c r="D70" t="n">
+        <v>89198</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>VALERIA ALEJANDRA  PADILLA  CASE</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>INSURGENTES</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>01-03-2026 13:23:47</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>01-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I70" t="n">
+        <v>0</v>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L70" t="n">
+        <v>549</v>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr"/>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr"/>
+      <c r="Q70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>69</v>
+      </c>
+      <c r="B71" t="n">
+        <v>95362</v>
+      </c>
+      <c r="C71" t="n">
+        <v>61767</v>
+      </c>
+      <c r="D71" t="n">
+        <v>59606</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>DIEGO SANCHEZ MARTINN</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>SEND MXL</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>01-03-2026 15:06:11</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>01-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I71" t="n">
+        <v>0</v>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L71" t="n">
+        <v>499</v>
+      </c>
+      <c r="M71" t="n">
+        <v>11</v>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>24-02-2027 15:06:11</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P71" t="n">
+        <v>27301</v>
+      </c>
+      <c r="Q71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>70</v>
+      </c>
+      <c r="B72" t="n">
+        <v>95398</v>
+      </c>
+      <c r="C72" t="n">
+        <v>175739</v>
+      </c>
+      <c r="D72" t="n">
+        <v>73246</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>ABRAHAM ENRIQUE  VALENZUELA  BELTRAN</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>SEND CUL</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>02-03-2026 7:24:40</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I72" t="n">
+        <v>0</v>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L72" t="n">
+        <v>499</v>
+      </c>
+      <c r="M72" t="n">
+        <v>11</v>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>25-02-2027 7:24:40</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P72" t="n">
+        <v>23621</v>
+      </c>
+      <c r="Q72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>71</v>
+      </c>
+      <c r="B73" t="n">
+        <v>94569</v>
+      </c>
+      <c r="C73" t="n">
+        <v>295894</v>
+      </c>
+      <c r="D73" t="n">
+        <v>93392</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>AITZA MIRENA GUTIERREZ  BLANCARTE</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>VILLAS DEL REY</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>23-02-2026 18:10:10</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I73" t="n">
+        <v>0</v>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L73" t="n">
+        <v>499</v>
+      </c>
+      <c r="M73" t="n">
+        <v>11</v>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>18-02-2027 18:10:10</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P73" t="n">
+        <v>80852</v>
+      </c>
+      <c r="Q73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>72</v>
+      </c>
+      <c r="B74" t="n">
+        <v>95250</v>
+      </c>
+      <c r="C74" t="n">
+        <v>347165</v>
+      </c>
+      <c r="D74" t="n">
+        <v>89330</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>AGUSTIN TOLEDO ALMAZAN</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>METEPEC</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>28-02-2026 9:50:05</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>28-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I74" t="n">
+        <v>0</v>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L74" t="n">
+        <v>799</v>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr"/>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr"/>
+      <c r="Q74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>73</v>
+      </c>
+      <c r="B75" t="n">
+        <v>95336</v>
+      </c>
+      <c r="C75" t="n">
+        <v>347304</v>
+      </c>
+      <c r="D75" t="n">
+        <v>89469</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>DANIEL GARZA MORENO</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>SALTILLO VILLALTA</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>01-03-2026 10:59:52</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>01-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>0</v>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L75" t="n">
+        <v>649</v>
+      </c>
+      <c r="M75" t="n">
+        <v>11</v>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>24-02-2027 10:59:52</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr"/>
+      <c r="Q75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>74</v>
+      </c>
+      <c r="B76" t="n">
+        <v>95349</v>
+      </c>
+      <c r="C76" t="n">
+        <v>346388</v>
+      </c>
+      <c r="D76" t="n">
+        <v>88553</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>RAISA ITZEL  MONTERO  MARTINEZ</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>INSURGENTES</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>01-03-2026 12:35:15</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>01-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I76" t="n">
+        <v>0</v>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L76" t="n">
+        <v>1549</v>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr"/>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr"/>
+      <c r="Q76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>75</v>
+      </c>
+      <c r="B77" t="n">
+        <v>95350</v>
+      </c>
+      <c r="C77" t="n">
+        <v>347336</v>
+      </c>
+      <c r="D77" t="n">
+        <v>89501</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>ALAIDE INES ANGELES  MADRIGAL</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>TLALNEPANTLA</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>01-03-2026 12:36:10</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>01-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I77" t="n">
+        <v>0</v>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L77" t="n">
+        <v>549</v>
+      </c>
+      <c r="M77" t="n">
+        <v>11</v>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>24-02-2027 12:36:10</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr"/>
+      <c r="Q77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>76</v>
+      </c>
+      <c r="B78" t="n">
+        <v>95368</v>
+      </c>
+      <c r="C78" t="n">
+        <v>291777</v>
+      </c>
+      <c r="D78" t="n">
+        <v>89275</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>MARIA ELENA  CAMPOS  VALENCIA</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>AZAHARES CUL</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>02-03-2026 4:23:22</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I78" t="n">
+        <v>0</v>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L78" t="n">
+        <v>549</v>
+      </c>
+      <c r="M78" t="n">
+        <v>11</v>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>25-02-2027 4:23:22</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr"/>
+      <c r="Q78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>77</v>
+      </c>
+      <c r="B79" t="n">
+        <v>95385</v>
+      </c>
+      <c r="C79" t="n">
+        <v>346076</v>
+      </c>
+      <c r="D79" t="n">
+        <v>88241</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>JAVIERDE JESUS GARCIA ALCANTARÁ</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>METEPEC</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>02-03-2026 6:33:27</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I79" t="n">
+        <v>0</v>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L79" t="n">
+        <v>649</v>
+      </c>
+      <c r="M79" t="n">
+        <v>11</v>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>25-02-2027 6:33:27</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr"/>
+      <c r="Q79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>78</v>
+      </c>
+      <c r="B80" t="n">
+        <v>95386</v>
+      </c>
+      <c r="C80" t="n">
+        <v>34610</v>
+      </c>
+      <c r="D80" t="n">
+        <v>32524</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>MARIA DEL CARMEN JIMENEZ CRIOLLO</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>PASEO 2000</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>02-03-2026 6:33:46</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I80" t="n">
+        <v>0</v>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L80" t="n">
+        <v>499</v>
+      </c>
+      <c r="M80" t="n">
+        <v>11</v>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>25-02-2027 6:33:46</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P80" t="n">
+        <v>20553</v>
+      </c>
+      <c r="Q80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>79</v>
+      </c>
+      <c r="B81" t="n">
+        <v>95399</v>
+      </c>
+      <c r="C81" t="n">
+        <v>346084</v>
+      </c>
+      <c r="D81" t="n">
+        <v>88249</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>ADILENE LIZETH GUZMAN  MARINO</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>SANTA FE</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>02-03-2026 7:27:14</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I81" t="n">
+        <v>0</v>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L81" t="n">
+        <v>549</v>
+      </c>
+      <c r="M81" t="n">
+        <v>11</v>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>25-02-2027 7:27:14</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr"/>
+      <c r="Q81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>80</v>
+      </c>
+      <c r="B82" t="n">
+        <v>95400</v>
+      </c>
+      <c r="C82" t="n">
+        <v>347418</v>
+      </c>
+      <c r="D82" t="n">
+        <v>89583</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>MARIA ALEJANDRA HERNANDEZ SARABIA</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>SAN ISIDRO CUL</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>02-03-2026 7:27:34</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I82" t="n">
+        <v>0</v>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L82" t="n">
+        <v>549</v>
+      </c>
+      <c r="M82" t="n">
+        <v>11</v>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>25-02-2027 7:27:34</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr"/>
+      <c r="Q82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Reporte generado: 02-03-2026 03:45 p. m.</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr"/>
+      <c r="C83" t="inlineStr"/>
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" t="inlineStr"/>
+      <c r="F83" t="inlineStr"/>
+      <c r="G83" t="inlineStr"/>
+      <c r="H83" t="inlineStr"/>
+      <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr"/>
+      <c r="N83" t="inlineStr"/>
+      <c r="O83" t="inlineStr"/>
+      <c r="P83" t="inlineStr"/>
+      <c r="Q83" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/descargas/cargos_recurrentes.xlsx
+++ b/data/descargas/cargos_recurrentes.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q3"/>
+  <dimension ref="A1:Q15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -599,27 +599,821 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Reporte generado: 01-04-2026 08:25 a. m. </t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="n">
+        <v>97974</v>
+      </c>
+      <c r="C3" t="n">
+        <v>312043</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>09542</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>YULISSA KARYME GUITRON OSORIO</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>MISION ENS</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>27-03-2026 13:38:44</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>01-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>599</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P3" t="n">
+        <v>92547</v>
+      </c>
       <c r="Q3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="n">
+        <v>95401</v>
+      </c>
+      <c r="C4" t="n">
+        <v>202026</v>
+      </c>
+      <c r="D4" t="n">
+        <v>99533</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>GABRIELA MARIA SOTO VIELLEDENT</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>VILLA VERDE</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>02-03-2026 7:51:41</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>01-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>499</v>
+      </c>
+      <c r="M4" t="n">
+        <v>11</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>25-02-2027 7:51:41</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
+        <v>76934</v>
+      </c>
+      <c r="Q4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="n">
+        <v>98378</v>
+      </c>
+      <c r="C5" t="n">
+        <v>234373</v>
+      </c>
+      <c r="D5" t="n">
+        <v>31878</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>ANDREA  ESTAÑOL CUESTA</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>SEND MXL</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>01-04-2026 5:10:38</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>01-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>549</v>
+      </c>
+      <c r="M5" t="n">
+        <v>11</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>27-03-2027 5:10:38</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="n">
+        <v>98380</v>
+      </c>
+      <c r="C6" t="n">
+        <v>218531</v>
+      </c>
+      <c r="D6" t="n">
+        <v>16039</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>MARIA EUUGENIA CUESTA GUERRERRO</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>SEND MXL</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>01-04-2026 5:54:51</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>01-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>499</v>
+      </c>
+      <c r="M6" t="n">
+        <v>11</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>27-03-2027 5:54:51</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>16036</v>
+      </c>
+      <c r="Q6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" t="n">
+        <v>98382</v>
+      </c>
+      <c r="C7" t="n">
+        <v>10048</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>08977</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>JORGE HUMBERTO ROBLES BURGUEÑO</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>PABELLON RTO</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>01-04-2026 6:55:06</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>01-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>549</v>
+      </c>
+      <c r="M7" t="n">
+        <v>11</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>27-03-2027 6:55:06</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" t="n">
+        <v>96508</v>
+      </c>
+      <c r="C8" t="n">
+        <v>324178</v>
+      </c>
+      <c r="D8" t="n">
+        <v>21117</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>EDNA PRICILA  HERRERA  LOPEZ</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>INDEPENDENCIA</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>10-03-2026 14:42:50</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>01-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>399</v>
+      </c>
+      <c r="M8" t="n">
+        <v>11</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>05-03-2027 14:42:50</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P8" t="n">
+        <v>83239</v>
+      </c>
+      <c r="Q8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" t="n">
+        <v>95681</v>
+      </c>
+      <c r="C9" t="n">
+        <v>276079</v>
+      </c>
+      <c r="D9" t="n">
+        <v>73581</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>RAMON  SANCHEZ  RODRIGUEZ</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>MISION ENS</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>03-03-2026 5:53:34</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>01-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>399</v>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
+        <v>67204</v>
+      </c>
+      <c r="Q9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" t="n">
+        <v>98066</v>
+      </c>
+      <c r="C10" t="n">
+        <v>316321</v>
+      </c>
+      <c r="D10" t="n">
+        <v>13819</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>JESSICA LIZETH RODRIGUEZ GRIJALVA</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>SEND CHIH</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>29-03-2026 13:48:23</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>01-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>549</v>
+      </c>
+      <c r="M10" t="n">
+        <v>5</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>25-09-2026 13:48:23</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>79196</v>
+      </c>
+      <c r="Q10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" t="n">
+        <v>98379</v>
+      </c>
+      <c r="C11" t="n">
+        <v>353959</v>
+      </c>
+      <c r="D11" t="n">
+        <v>96123</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>RICARDO ALEXIS CARMONA  HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>IXTAPALUCA</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>01-04-2026 5:24:50</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>01-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>549</v>
+      </c>
+      <c r="M11" t="n">
+        <v>11</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>27-03-2027 5:24:50</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" t="n">
+        <v>97965</v>
+      </c>
+      <c r="C12" t="n">
+        <v>70411</v>
+      </c>
+      <c r="D12" t="n">
+        <v>68233</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>CYNTHIA IVETH GARCIA  MORENO</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>SEND MXL</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>27-03-2026 11:58:41</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>01-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>449</v>
+      </c>
+      <c r="M12" t="n">
+        <v>11</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>22-03-2027 11:58:41</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>31636</v>
+      </c>
+      <c r="Q12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" t="n">
+        <v>95361</v>
+      </c>
+      <c r="C13" t="n">
+        <v>237196</v>
+      </c>
+      <c r="D13" t="n">
+        <v>34701</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>PAULINA ELIZABETH FLORES HINOJOSA</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>SANTA FE</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>01-03-2026 14:42:48</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>01-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>449</v>
+      </c>
+      <c r="M13" t="n">
+        <v>5</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>28-08-2026 14:42:48</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>39905</v>
+      </c>
+      <c r="Q13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" t="n">
+        <v>98376</v>
+      </c>
+      <c r="C14" t="n">
+        <v>330015</v>
+      </c>
+      <c r="D14" t="n">
+        <v>15069</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>NOEL GALLEGOS VARELA</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>SEND CHIH</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>01-04-2026 5:07:31</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>01-07-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
+        <v>1449</v>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Reporte generado: 01-04-2026 01:57 p. m.</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/descargas/cargos_recurrentes.xlsx
+++ b/data/descargas/cargos_recurrentes.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q15"/>
+  <dimension ref="A1:Q18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -603,29 +603,27 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>97974</v>
+        <v>98066</v>
       </c>
       <c r="C3" t="n">
-        <v>312043</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>09542</t>
-        </is>
+        <v>316321</v>
+      </c>
+      <c r="D3" t="n">
+        <v>13819</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>YULISSA KARYME GUITRON OSORIO</t>
+          <t>JESSICA LIZETH RODRIGUEZ GRIJALVA</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>MISION ENS</t>
+          <t>SEND CHIH</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>27-03-2026 13:38:44</t>
+          <t>29-03-2026 13:48:23</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -647,21 +645,23 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>599</v>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>Indefinido</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+        <v>549</v>
+      </c>
+      <c r="M3" t="n">
+        <v>5</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>25-09-2026 13:48:23</t>
+        </is>
+      </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Recurrente</t>
+          <t>Domiciliado</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>92547</v>
+        <v>79196</v>
       </c>
       <c r="Q3" t="inlineStr"/>
     </row>
@@ -670,27 +670,27 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>95401</v>
+        <v>98383</v>
       </c>
       <c r="C4" t="n">
-        <v>202026</v>
+        <v>290244</v>
       </c>
       <c r="D4" t="n">
-        <v>99533</v>
+        <v>87742</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>GABRIELA MARIA SOTO VIELLEDENT</t>
+          <t>ALMA GUADALUPE AGUILAR  DIAZ</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>VILLA VERDE</t>
+          <t>IXTAPALUCA</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>02-03-2026 7:51:41</t>
+          <t>01-04-2026 7:28:15</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -708,18 +708,18 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>RENOVACIÓN</t>
+          <t>NUEVO</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>499</v>
+        <v>549</v>
       </c>
       <c r="M4" t="n">
         <v>11</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>25-02-2027 7:51:41</t>
+          <t>27-03-2027 7:28:15</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -727,9 +727,7 @@
           <t>Domiciliado</t>
         </is>
       </c>
-      <c r="P4" t="n">
-        <v>76934</v>
-      </c>
+      <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr"/>
     </row>
     <row r="5">
@@ -737,27 +735,29 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>98378</v>
+        <v>97974</v>
       </c>
       <c r="C5" t="n">
-        <v>234373</v>
-      </c>
-      <c r="D5" t="n">
-        <v>31878</v>
+        <v>312043</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>09542</t>
+        </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>ANDREA  ESTAÑOL CUESTA</t>
+          <t>YULISSA KARYME GUITRON OSORIO</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>SEND MXL</t>
+          <t>MISION ENS</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>01-04-2026 5:10:38</t>
+          <t>27-03-2026 13:38:44</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -775,26 +775,26 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>NUEVO</t>
+          <t>RENOVACIÓN</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>549</v>
-      </c>
-      <c r="M5" t="n">
-        <v>11</v>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>27-03-2027 5:10:38</t>
-        </is>
-      </c>
+        <v>599</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Domiciliado</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr"/>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
+        <v>92547</v>
+      </c>
       <c r="Q5" t="inlineStr"/>
     </row>
     <row r="6">
@@ -802,27 +802,27 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>98380</v>
+        <v>95401</v>
       </c>
       <c r="C6" t="n">
-        <v>218531</v>
+        <v>202026</v>
       </c>
       <c r="D6" t="n">
-        <v>16039</v>
+        <v>99533</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>MARIA EUUGENIA CUESTA GUERRERRO</t>
+          <t>GABRIELA MARIA SOTO VIELLEDENT</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>SEND MXL</t>
+          <t>VILLA VERDE</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>01-04-2026 5:54:51</t>
+          <t>02-03-2026 7:51:41</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -851,7 +851,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>27-03-2027 5:54:51</t>
+          <t>25-02-2027 7:51:41</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -860,7 +860,7 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>16036</v>
+        <v>76934</v>
       </c>
       <c r="Q6" t="inlineStr"/>
     </row>
@@ -869,29 +869,27 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>98382</v>
+        <v>98378</v>
       </c>
       <c r="C7" t="n">
-        <v>10048</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>08977</t>
-        </is>
+        <v>234373</v>
+      </c>
+      <c r="D7" t="n">
+        <v>31878</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>JORGE HUMBERTO ROBLES BURGUEÑO</t>
+          <t>ANDREA  ESTAÑOL CUESTA</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>PABELLON RTO</t>
+          <t>SEND MXL</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>01-04-2026 6:55:06</t>
+          <t>01-04-2026 5:10:38</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -920,7 +918,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>27-03-2027 6:55:06</t>
+          <t>27-03-2027 5:10:38</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -936,27 +934,27 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>96508</v>
+        <v>98380</v>
       </c>
       <c r="C8" t="n">
-        <v>324178</v>
+        <v>218531</v>
       </c>
       <c r="D8" t="n">
-        <v>21117</v>
+        <v>16039</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>EDNA PRICILA  HERRERA  LOPEZ</t>
+          <t>MARIA EUUGENIA CUESTA GUERRERRO</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>INDEPENDENCIA</t>
+          <t>SEND MXL</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>10-03-2026 14:42:50</t>
+          <t>01-04-2026 5:54:51</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -978,14 +976,14 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>399</v>
+        <v>499</v>
       </c>
       <c r="M8" t="n">
         <v>11</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>05-03-2027 14:42:50</t>
+          <t>27-03-2027 5:54:51</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -994,7 +992,7 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>83239</v>
+        <v>16036</v>
       </c>
       <c r="Q8" t="inlineStr"/>
     </row>
@@ -1003,27 +1001,29 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>95681</v>
+        <v>98382</v>
       </c>
       <c r="C9" t="n">
-        <v>276079</v>
-      </c>
-      <c r="D9" t="n">
-        <v>73581</v>
+        <v>10048</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>08977</t>
+        </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAMON  SANCHEZ  RODRIGUEZ</t>
+          <t>JORGE HUMBERTO ROBLES BURGUEÑO</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>MISION ENS</t>
+          <t>PABELLON RTO</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>03-03-2026 5:53:34</t>
+          <t>01-04-2026 6:55:06</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1041,26 +1041,26 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>RENOVACIÓN</t>
+          <t>NUEVO</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>399</v>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>Indefinido</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
+        <v>549</v>
+      </c>
+      <c r="M9" t="n">
+        <v>11</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>27-03-2027 6:55:06</t>
+        </is>
+      </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Recurrente</t>
-        </is>
-      </c>
-      <c r="P9" t="n">
-        <v>67204</v>
-      </c>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr"/>
       <c r="Q9" t="inlineStr"/>
     </row>
     <row r="10">
@@ -1068,27 +1068,27 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>98066</v>
+        <v>96508</v>
       </c>
       <c r="C10" t="n">
-        <v>316321</v>
+        <v>324178</v>
       </c>
       <c r="D10" t="n">
-        <v>13819</v>
+        <v>21117</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>JESSICA LIZETH RODRIGUEZ GRIJALVA</t>
+          <t>EDNA PRICILA  HERRERA  LOPEZ</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>SEND CHIH</t>
+          <t>INDEPENDENCIA</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>29-03-2026 13:48:23</t>
+          <t>10-03-2026 14:42:50</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1110,14 +1110,14 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>549</v>
+        <v>399</v>
       </c>
       <c r="M10" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>25-09-2026 13:48:23</t>
+          <t>05-03-2027 14:42:50</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1126,7 +1126,7 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>79196</v>
+        <v>83239</v>
       </c>
       <c r="Q10" t="inlineStr"/>
     </row>
@@ -1135,27 +1135,27 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>98379</v>
+        <v>97965</v>
       </c>
       <c r="C11" t="n">
-        <v>353959</v>
+        <v>70411</v>
       </c>
       <c r="D11" t="n">
-        <v>96123</v>
+        <v>68233</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RICARDO ALEXIS CARMONA  HERNANDEZ</t>
+          <t>CYNTHIA IVETH GARCIA  MORENO</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>IXTAPALUCA</t>
+          <t>SEND MXL</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>01-04-2026 5:24:50</t>
+          <t>27-03-2026 11:58:41</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1173,18 +1173,18 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>NUEVO</t>
+          <t>RENOVACIÓN</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>549</v>
+        <v>449</v>
       </c>
       <c r="M11" t="n">
         <v>11</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>27-03-2027 5:24:50</t>
+          <t>22-03-2027 11:58:41</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1192,7 +1192,9 @@
           <t>Domiciliado</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr"/>
+      <c r="P11" t="n">
+        <v>31636</v>
+      </c>
       <c r="Q11" t="inlineStr"/>
     </row>
     <row r="12">
@@ -1200,27 +1202,27 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>97965</v>
+        <v>95361</v>
       </c>
       <c r="C12" t="n">
-        <v>70411</v>
+        <v>237196</v>
       </c>
       <c r="D12" t="n">
-        <v>68233</v>
+        <v>34701</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CYNTHIA IVETH GARCIA  MORENO</t>
+          <t>PAULINA ELIZABETH FLORES HINOJOSA</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>SEND MXL</t>
+          <t>SANTA FE</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>27-03-2026 11:58:41</t>
+          <t>01-03-2026 14:42:48</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1245,11 +1247,11 @@
         <v>449</v>
       </c>
       <c r="M12" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>22-03-2027 11:58:41</t>
+          <t>28-08-2026 14:42:48</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1258,7 +1260,7 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>31636</v>
+        <v>39905</v>
       </c>
       <c r="Q12" t="inlineStr"/>
     </row>
@@ -1267,27 +1269,29 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>95361</v>
+        <v>98384</v>
       </c>
       <c r="C13" t="n">
-        <v>237196</v>
-      </c>
-      <c r="D13" t="n">
-        <v>34701</v>
+        <v>3040</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>02041</t>
+        </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>PAULINA ELIZABETH FLORES HINOJOSA</t>
+          <t>LISBETH MAGALLI GARCIA VERDUZCO</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>SANTA FE</t>
+          <t>SEND MXL</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>01-03-2026 14:42:48</t>
+          <t>01-04-2026 7:50:45</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1305,18 +1309,18 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>RENOVACIÓN</t>
+          <t>NUEVO</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>449</v>
+        <v>549</v>
       </c>
       <c r="M13" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>28-08-2026 14:42:48</t>
+          <t>27-03-2027 7:50:45</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1324,9 +1328,7 @@
           <t>Domiciliado</t>
         </is>
       </c>
-      <c r="P13" t="n">
-        <v>39905</v>
-      </c>
+      <c r="P13" t="inlineStr"/>
       <c r="Q13" t="inlineStr"/>
     </row>
     <row r="14">
@@ -1334,32 +1336,32 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C14" t="n">
-        <v>330015</v>
+        <v>353959</v>
       </c>
       <c r="D14" t="n">
-        <v>15069</v>
+        <v>96123</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>NOEL GALLEGOS VARELA</t>
+          <t>RICARDO ALEXIS CARMONA  HERNANDEZ</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>SEND CHIH</t>
+          <t>IXTAPALUCA</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>01-04-2026 5:07:31</t>
+          <t>01-04-2026 5:24:50</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>01-07-2026 23:59:59</t>
+          <t>01-05-2026 23:59:59</t>
         </is>
       </c>
       <c r="I14" t="n">
@@ -1376,44 +1378,237 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1449</v>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>Indefinido</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
+        <v>549</v>
+      </c>
+      <c r="M14" t="n">
+        <v>11</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>27-03-2027 5:24:50</t>
+        </is>
+      </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Recurrente</t>
+          <t>Domiciliado</t>
         </is>
       </c>
       <c r="P14" t="inlineStr"/>
       <c r="Q14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Reporte generado: 01-04-2026 01:57 p. m.</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
+      <c r="A15" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" t="n">
+        <v>98387</v>
+      </c>
+      <c r="C15" t="n">
+        <v>340681</v>
+      </c>
+      <c r="D15" t="n">
+        <v>18499</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>ALEXIS BENITEZ DEGOLLADO</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>METEPEC</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>01-04-2026 8:57:28</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>01-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L15" t="n">
+        <v>549</v>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr"/>
       <c r="Q15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" t="n">
+        <v>95681</v>
+      </c>
+      <c r="C16" t="n">
+        <v>276079</v>
+      </c>
+      <c r="D16" t="n">
+        <v>73581</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>RAMON  SANCHEZ  RODRIGUEZ</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>MISION ENS</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>03-03-2026 5:53:34</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>01-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L16" t="n">
+        <v>399</v>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>67204</v>
+      </c>
+      <c r="Q16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" t="n">
+        <v>98376</v>
+      </c>
+      <c r="C17" t="n">
+        <v>330015</v>
+      </c>
+      <c r="D17" t="n">
+        <v>15069</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>NOEL GALLEGOS VARELA</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>SEND CHIH</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>01-04-2026 5:07:31</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>01-07-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L17" t="n">
+        <v>1449</v>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Reporte generado: 01-04-2026 04:10 p. m.</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/descargas/cargos_recurrentes.xlsx
+++ b/data/descargas/cargos_recurrentes.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q18"/>
+  <dimension ref="A1:Q84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -603,27 +603,27 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>98066</v>
+        <v>98383</v>
       </c>
       <c r="C3" t="n">
-        <v>316321</v>
+        <v>290244</v>
       </c>
       <c r="D3" t="n">
-        <v>13819</v>
+        <v>87742</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>JESSICA LIZETH RODRIGUEZ GRIJALVA</t>
+          <t>ALMA GUADALUPE AGUILAR  DIAZ</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>SEND CHIH</t>
+          <t>IXTAPALUCA</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>29-03-2026 13:48:23</t>
+          <t>01-04-2026 7:28:15</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -641,18 +641,18 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>RENOVACIÓN</t>
+          <t>NUEVO</t>
         </is>
       </c>
       <c r="L3" t="n">
         <v>549</v>
       </c>
       <c r="M3" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>25-09-2026 13:48:23</t>
+          <t>27-03-2027 7:28:15</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -660,9 +660,7 @@
           <t>Domiciliado</t>
         </is>
       </c>
-      <c r="P3" t="n">
-        <v>79196</v>
-      </c>
+      <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr"/>
     </row>
     <row r="4">
@@ -670,27 +668,27 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>98383</v>
+        <v>98400</v>
       </c>
       <c r="C4" t="n">
-        <v>290244</v>
+        <v>116328</v>
       </c>
       <c r="D4" t="n">
-        <v>87742</v>
+        <v>14043</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>ALMA GUADALUPE AGUILAR  DIAZ</t>
+          <t>ELENA ALEXIS CARRILLO RODRIGUEZ</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>IXTAPALUCA</t>
+          <t>SAN LUIS</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>01-04-2026 7:28:15</t>
+          <t>01-04-2026 12:37:06</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -708,18 +706,18 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>NUEVO</t>
+          <t>RENOVACIÓN</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>549</v>
+        <v>499</v>
       </c>
       <c r="M4" t="n">
         <v>11</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>27-03-2027 7:28:15</t>
+          <t>27-03-2027 12:37:06</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -727,7 +725,9 @@
           <t>Domiciliado</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr"/>
+      <c r="P4" t="n">
+        <v>4911</v>
+      </c>
       <c r="Q4" t="inlineStr"/>
     </row>
     <row r="5">
@@ -735,29 +735,27 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>97974</v>
+        <v>98402</v>
       </c>
       <c r="C5" t="n">
-        <v>312043</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>09542</t>
-        </is>
+        <v>354836</v>
+      </c>
+      <c r="D5" t="n">
+        <v>97000</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>YULISSA KARYME GUITRON OSORIO</t>
+          <t>ERICK OSWALDO ESPINOZA  CARREON</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>MISION ENS</t>
+          <t>PASEO LA PAZ</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>27-03-2026 13:38:44</t>
+          <t>01-04-2026 12:55:02</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -775,26 +773,26 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>RENOVACIÓN</t>
+          <t>NUEVO</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>599</v>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>Indefinido</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
+        <v>999</v>
+      </c>
+      <c r="M5" t="n">
+        <v>11</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>27-03-2027 12:55:02</t>
+        </is>
+      </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Recurrente</t>
-        </is>
-      </c>
-      <c r="P5" t="n">
-        <v>92547</v>
-      </c>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr"/>
       <c r="Q5" t="inlineStr"/>
     </row>
     <row r="6">
@@ -802,27 +800,27 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>95401</v>
+        <v>98417</v>
       </c>
       <c r="C6" t="n">
-        <v>202026</v>
+        <v>354294</v>
       </c>
       <c r="D6" t="n">
-        <v>99533</v>
+        <v>96458</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>GABRIELA MARIA SOTO VIELLEDENT</t>
+          <t>MARIO ALBERTO RODRIGUEZ MENDOZA</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>VILLA VERDE</t>
+          <t>SEND CHIH</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>02-03-2026 7:51:41</t>
+          <t>01-04-2026 16:41:16</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -840,28 +838,24 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>RENOVACIÓN</t>
+          <t>NUEVO</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>499</v>
-      </c>
-      <c r="M6" t="n">
-        <v>11</v>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>25-02-2027 7:51:41</t>
-        </is>
-      </c>
+        <v>649</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Domiciliado</t>
-        </is>
-      </c>
-      <c r="P6" t="n">
-        <v>76934</v>
-      </c>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr"/>
     </row>
     <row r="7">
@@ -869,27 +863,27 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>98378</v>
+        <v>98419</v>
       </c>
       <c r="C7" t="n">
-        <v>234373</v>
+        <v>354709</v>
       </c>
       <c r="D7" t="n">
-        <v>31878</v>
+        <v>96873</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>ANDREA  ESTAÑOL CUESTA</t>
+          <t>ALEXANDER  DIMAS  GONZALEZ</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>SEND MXL</t>
+          <t>INSURGENTES</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>01-04-2026 5:10:38</t>
+          <t>01-04-2026 17:39:19</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -913,17 +907,15 @@
       <c r="L7" t="n">
         <v>549</v>
       </c>
-      <c r="M7" t="n">
-        <v>11</v>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>27-03-2027 5:10:38</t>
-        </is>
-      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Domiciliado</t>
+          <t>Recurrente</t>
         </is>
       </c>
       <c r="P7" t="inlineStr"/>
@@ -934,27 +926,27 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>98380</v>
+        <v>98434</v>
       </c>
       <c r="C8" t="n">
-        <v>218531</v>
+        <v>354927</v>
       </c>
       <c r="D8" t="n">
-        <v>16039</v>
+        <v>97091</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>MARIA EUUGENIA CUESTA GUERRERRO</t>
+          <t>LUZ MARIA  MORA  MARTINEZ</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>SEND MXL</t>
+          <t>LOMA BONITA</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>01-04-2026 5:54:51</t>
+          <t>01-04-2026 19:01:18</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -972,18 +964,18 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>RENOVACIÓN</t>
+          <t>NUEVO</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>499</v>
+        <v>549</v>
       </c>
       <c r="M8" t="n">
         <v>11</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>27-03-2027 5:54:51</t>
+          <t>27-03-2027 19:01:18</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -991,9 +983,7 @@
           <t>Domiciliado</t>
         </is>
       </c>
-      <c r="P8" t="n">
-        <v>16036</v>
-      </c>
+      <c r="P8" t="inlineStr"/>
       <c r="Q8" t="inlineStr"/>
     </row>
     <row r="9">
@@ -1001,29 +991,27 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>98382</v>
+        <v>98436</v>
       </c>
       <c r="C9" t="n">
-        <v>10048</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>08977</t>
-        </is>
+        <v>353944</v>
+      </c>
+      <c r="D9" t="n">
+        <v>96108</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>JORGE HUMBERTO ROBLES BURGUEÑO</t>
+          <t>CESAR EMILIANO OCHOA CHAPARRO</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>PABELLON RTO</t>
+          <t>INSURGENTES</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>01-04-2026 6:55:06</t>
+          <t>01-04-2026 19:03:51</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1045,14 +1033,14 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>549</v>
+        <v>649</v>
       </c>
       <c r="M9" t="n">
         <v>11</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>27-03-2027 6:55:06</t>
+          <t>27-03-2027 19:03:51</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1068,27 +1056,27 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>96508</v>
+        <v>98449</v>
       </c>
       <c r="C10" t="n">
-        <v>324178</v>
+        <v>354459</v>
       </c>
       <c r="D10" t="n">
-        <v>21117</v>
+        <v>96623</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>EDNA PRICILA  HERRERA  LOPEZ</t>
+          <t>MARCO ANTONIO LOZA GUTIERREZ</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>INDEPENDENCIA</t>
+          <t>VILLA VERDE</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>10-03-2026 14:42:50</t>
+          <t>01-04-2026 21:22:40</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1106,18 +1094,18 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>RENOVACIÓN</t>
+          <t>NUEVO</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>399</v>
+        <v>549</v>
       </c>
       <c r="M10" t="n">
         <v>11</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>05-03-2027 14:42:50</t>
+          <t>27-03-2027 21:22:40</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1125,9 +1113,7 @@
           <t>Domiciliado</t>
         </is>
       </c>
-      <c r="P10" t="n">
-        <v>83239</v>
-      </c>
+      <c r="P10" t="inlineStr"/>
       <c r="Q10" t="inlineStr"/>
     </row>
     <row r="11">
@@ -1135,32 +1121,32 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>97965</v>
+        <v>98451</v>
       </c>
       <c r="C11" t="n">
-        <v>70411</v>
+        <v>44701</v>
       </c>
       <c r="D11" t="n">
-        <v>68233</v>
+        <v>42564</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>CYNTHIA IVETH GARCIA  MORENO</t>
+          <t>KARINA YESENIA ZUÑIGA CAMEZ</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>SEND MXL</t>
+          <t>VILLA VERDE</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>27-03-2026 11:58:41</t>
+          <t>02-04-2026 5:10:41</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>01-05-2026 23:59:59</t>
+          <t>07-05-2026 23:59:59</t>
         </is>
       </c>
       <c r="I11" t="n">
@@ -1177,14 +1163,14 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>449</v>
+        <v>499</v>
       </c>
       <c r="M11" t="n">
         <v>11</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>22-03-2027 11:58:41</t>
+          <t>28-03-2027 5:10:41</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1193,7 +1179,7 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>31636</v>
+        <v>65871</v>
       </c>
       <c r="Q11" t="inlineStr"/>
     </row>
@@ -1202,32 +1188,32 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>95361</v>
+        <v>98453</v>
       </c>
       <c r="C12" t="n">
-        <v>237196</v>
+        <v>143046</v>
       </c>
       <c r="D12" t="n">
-        <v>34701</v>
+        <v>40662</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>PAULINA ELIZABETH FLORES HINOJOSA</t>
+          <t>LYZEIDY VALENZUELA  RUELAS</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>SANTA FE</t>
+          <t>VILLAS DEL REY</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>01-03-2026 14:42:48</t>
+          <t>02-04-2026 7:09:39</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>01-05-2026 23:59:59</t>
+          <t>02-05-2026 23:59:59</t>
         </is>
       </c>
       <c r="I12" t="n">
@@ -1240,18 +1226,18 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>RENOVACIÓN</t>
+          <t>NUEVO</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>449</v>
+        <v>549</v>
       </c>
       <c r="M12" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>28-08-2026 14:42:48</t>
+          <t>28-03-2027 7:09:39</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1259,9 +1245,7 @@
           <t>Domiciliado</t>
         </is>
       </c>
-      <c r="P12" t="n">
-        <v>39905</v>
-      </c>
+      <c r="P12" t="inlineStr"/>
       <c r="Q12" t="inlineStr"/>
     </row>
     <row r="13">
@@ -1269,34 +1253,32 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>98384</v>
+        <v>95945</v>
       </c>
       <c r="C13" t="n">
-        <v>3040</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>02041</t>
-        </is>
+        <v>331588</v>
+      </c>
+      <c r="D13" t="n">
+        <v>16642</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>LISBETH MAGALLI GARCIA VERDUZCO</t>
+          <t>ROMINA SOSA SOLIS</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>SEND MXL</t>
+          <t>SALTILLO VILLALTA</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>01-04-2026 7:50:45</t>
+          <t>04-03-2026 16:58:11</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>01-05-2026 23:59:59</t>
+          <t>02-05-2026 23:59:59</t>
         </is>
       </c>
       <c r="I13" t="n">
@@ -1309,18 +1291,18 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>NUEVO</t>
+          <t>RENOVACIÓN</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>549</v>
+        <v>649</v>
       </c>
       <c r="M13" t="n">
         <v>11</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>27-03-2027 7:50:45</t>
+          <t>27-02-2027 16:58:11</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1328,7 +1310,9 @@
           <t>Domiciliado</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr"/>
+      <c r="P13" t="n">
+        <v>85408</v>
+      </c>
       <c r="Q13" t="inlineStr"/>
     </row>
     <row r="14">
@@ -1336,27 +1320,27 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>98379</v>
+        <v>98066</v>
       </c>
       <c r="C14" t="n">
-        <v>353959</v>
+        <v>316321</v>
       </c>
       <c r="D14" t="n">
-        <v>96123</v>
+        <v>13819</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RICARDO ALEXIS CARMONA  HERNANDEZ</t>
+          <t>JESSICA LIZETH RODRIGUEZ GRIJALVA</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>IXTAPALUCA</t>
+          <t>SEND CHIH</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>01-04-2026 5:24:50</t>
+          <t>29-03-2026 13:48:23</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1374,18 +1358,18 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>NUEVO</t>
+          <t>RENOVACIÓN</t>
         </is>
       </c>
       <c r="L14" t="n">
         <v>549</v>
       </c>
       <c r="M14" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>27-03-2027 5:24:50</t>
+          <t>25-09-2026 13:48:23</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -1393,7 +1377,9 @@
           <t>Domiciliado</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr"/>
+      <c r="P14" t="n">
+        <v>79196</v>
+      </c>
       <c r="Q14" t="inlineStr"/>
     </row>
     <row r="15">
@@ -1401,27 +1387,27 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>98387</v>
+        <v>95401</v>
       </c>
       <c r="C15" t="n">
-        <v>340681</v>
+        <v>202026</v>
       </c>
       <c r="D15" t="n">
-        <v>18499</v>
+        <v>99533</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>ALEXIS BENITEZ DEGOLLADO</t>
+          <t>GABRIELA MARIA SOTO VIELLEDENT</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>METEPEC</t>
+          <t>VILLA VERDE</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>01-04-2026 8:57:28</t>
+          <t>02-03-2026 7:51:41</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1439,24 +1425,28 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>NUEVO</t>
+          <t>RENOVACIÓN</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>549</v>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>Indefinido</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
+        <v>499</v>
+      </c>
+      <c r="M15" t="n">
+        <v>11</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>25-02-2027 7:51:41</t>
+        </is>
+      </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Recurrente</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr"/>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>76934</v>
+      </c>
       <c r="Q15" t="inlineStr"/>
     </row>
     <row r="16">
@@ -1464,32 +1454,32 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>95681</v>
+        <v>95416</v>
       </c>
       <c r="C16" t="n">
-        <v>276079</v>
+        <v>93948</v>
       </c>
       <c r="D16" t="n">
-        <v>73581</v>
+        <v>91707</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAMON  SANCHEZ  RODRIGUEZ</t>
+          <t>ANA RAFAELA GALVAN LOPEZ</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>MISION ENS</t>
+          <t>SEND SALTILLO</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>03-03-2026 5:53:34</t>
+          <t>02-03-2026 9:03:29</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>01-05-2026 23:59:59</t>
+          <t>02-05-2026 23:59:59</t>
         </is>
       </c>
       <c r="I16" t="n">
@@ -1506,21 +1496,23 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>399</v>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>Indefinido</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
+        <v>499</v>
+      </c>
+      <c r="M16" t="n">
+        <v>11</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>25-02-2027 9:03:29</t>
+        </is>
+      </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Recurrente</t>
+          <t>Domiciliado</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>67204</v>
+        <v>95415</v>
       </c>
       <c r="Q16" t="inlineStr"/>
     </row>
@@ -1529,32 +1521,32 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>98376</v>
+        <v>95451</v>
       </c>
       <c r="C17" t="n">
-        <v>330015</v>
+        <v>339837</v>
       </c>
       <c r="D17" t="n">
-        <v>15069</v>
+        <v>17655</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>NOEL GALLEGOS VARELA</t>
+          <t>CRISTIAN ALEXIS RUIZ AGUILAR</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>SEND CHIH</t>
+          <t>INSURGENTES</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>01-04-2026 5:07:31</t>
+          <t>02-03-2026 11:39:41</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>01-07-2026 23:59:59</t>
+          <t>02-05-2026 23:59:59</t>
         </is>
       </c>
       <c r="I17" t="n">
@@ -1567,48 +1559,4356 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L17" t="n">
+        <v>649</v>
+      </c>
+      <c r="M17" t="n">
+        <v>11</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>25-02-2027 11:39:41</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>91337</v>
+      </c>
+      <c r="Q17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" t="n">
+        <v>98391</v>
+      </c>
+      <c r="C18" t="n">
+        <v>354812</v>
+      </c>
+      <c r="D18" t="n">
+        <v>96976</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>ALAN  ESCOBEDO  BAEZ</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>INSURGENTES</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>01-04-2026 10:47:30</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>01-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
           <t>NUEVO</t>
         </is>
       </c>
-      <c r="L17" t="n">
-        <v>1449</v>
-      </c>
-      <c r="M17" t="inlineStr">
+      <c r="L18" t="n">
+        <v>549</v>
+      </c>
+      <c r="M18" t="inlineStr">
         <is>
           <t>Indefinido</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr">
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr">
         <is>
           <t>Recurrente</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Reporte generado: 01-04-2026 04:10 p. m.</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr"/>
       <c r="Q18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" t="n">
+        <v>98392</v>
+      </c>
+      <c r="C19" t="n">
+        <v>354811</v>
+      </c>
+      <c r="D19" t="n">
+        <v>96975</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>XIMENA PAOLA SANCHEZ RAMIREZ</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>TLALNEPANTLA</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>01-04-2026 10:48:46</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>01-07-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L19" t="n">
+        <v>1449</v>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" t="n">
+        <v>98409</v>
+      </c>
+      <c r="C20" t="n">
+        <v>164157</v>
+      </c>
+      <c r="D20" t="n">
+        <v>61690</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>BERTHA ALICIA GARCIA HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>SEND MXL</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>01-04-2026 15:01:11</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>01-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L20" t="n">
+        <v>499</v>
+      </c>
+      <c r="M20" t="n">
+        <v>11</v>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>27-03-2027 15:01:11</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P20" t="n">
+        <v>62356</v>
+      </c>
+      <c r="Q20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" t="n">
+        <v>98410</v>
+      </c>
+      <c r="C21" t="n">
+        <v>354869</v>
+      </c>
+      <c r="D21" t="n">
+        <v>97033</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>JULIO ARIZMENDI MORENO</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>METEPEC</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>01-04-2026 15:08:38</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>01-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L21" t="n">
+        <v>549</v>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" t="n">
+        <v>98427</v>
+      </c>
+      <c r="C22" t="n">
+        <v>352177</v>
+      </c>
+      <c r="D22" t="n">
+        <v>94341</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>JUANA FRIAS GARCIA</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>CARROUSEL TJ</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>01-04-2026 18:05:19</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>01-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L22" t="n">
+        <v>649</v>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" t="n">
+        <v>98428</v>
+      </c>
+      <c r="C23" t="n">
+        <v>354917</v>
+      </c>
+      <c r="D23" t="n">
+        <v>97081</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>MARLO ANDRE OCAMPO GARCIA</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>INSURGENTES</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>01-04-2026 18:06:23</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>01-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L23" t="n">
+        <v>649</v>
+      </c>
+      <c r="M23" t="n">
+        <v>11</v>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>27-03-2027 18:06:23</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>22</v>
+      </c>
+      <c r="B24" t="n">
+        <v>98441</v>
+      </c>
+      <c r="C24" t="n">
+        <v>151482</v>
+      </c>
+      <c r="D24" t="n">
+        <v>49047</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>ALAN HERIBERTO ESPINOZA ALIRE</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>INDEPENDENCIA</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>01-04-2026 20:05:11</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>01-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L24" t="n">
+        <v>649</v>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>23</v>
+      </c>
+      <c r="B25" t="n">
+        <v>98442</v>
+      </c>
+      <c r="C25" t="n">
+        <v>354954</v>
+      </c>
+      <c r="D25" t="n">
+        <v>97118</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>MARTA  CRUZ ALVARADO</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>CARROUSEL TJ</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>01-04-2026 20:24:50</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>01-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L25" t="n">
+        <v>649</v>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>24</v>
+      </c>
+      <c r="B26" t="n">
+        <v>95669</v>
+      </c>
+      <c r="C26" t="n">
+        <v>165787</v>
+      </c>
+      <c r="D26" t="n">
+        <v>63320</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>ALISSON ABRIL ROMERO LARA</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>TEC MXL</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>02-03-2026 21:15:34</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>30-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L26" t="n">
+        <v>499</v>
+      </c>
+      <c r="M26" t="n">
+        <v>11</v>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>25-02-2027 21:15:34</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P26" t="n">
+        <v>70751</v>
+      </c>
+      <c r="Q26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>25</v>
+      </c>
+      <c r="B27" t="n">
+        <v>97974</v>
+      </c>
+      <c r="C27" t="n">
+        <v>312043</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>09542</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>YULISSA KARYME GUITRON OSORIO</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>MISION ENS</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>27-03-2026 13:38:44</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>01-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L27" t="n">
+        <v>599</v>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P27" t="n">
+        <v>92547</v>
+      </c>
+      <c r="Q27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>26</v>
+      </c>
+      <c r="B28" t="n">
+        <v>98379</v>
+      </c>
+      <c r="C28" t="n">
+        <v>353959</v>
+      </c>
+      <c r="D28" t="n">
+        <v>96123</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>RICARDO ALEXIS CARMONA  HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>IXTAPALUCA</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>01-04-2026 5:24:50</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>01-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L28" t="n">
+        <v>549</v>
+      </c>
+      <c r="M28" t="n">
+        <v>11</v>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>27-03-2027 5:24:50</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>27</v>
+      </c>
+      <c r="B29" t="n">
+        <v>98397</v>
+      </c>
+      <c r="C29" t="n">
+        <v>354168</v>
+      </c>
+      <c r="D29" t="n">
+        <v>96332</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>JESSICA  AMADOR MARTINEZ</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>PASEO 2000</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>01-04-2026 12:05:06</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>01-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L29" t="n">
+        <v>649</v>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>28</v>
+      </c>
+      <c r="B30" t="n">
+        <v>98404</v>
+      </c>
+      <c r="C30" t="n">
+        <v>339346</v>
+      </c>
+      <c r="D30" t="n">
+        <v>17164</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>ANA RUT MARTINEZ  BALDERAS</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>SALTILLO VILLALTA</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>01-04-2026 13:19:32</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>01-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L30" t="n">
+        <v>549</v>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>29</v>
+      </c>
+      <c r="B31" t="n">
+        <v>98415</v>
+      </c>
+      <c r="C31" t="n">
+        <v>354891</v>
+      </c>
+      <c r="D31" t="n">
+        <v>97055</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>JUAN PABLO  CASTILLO  MENDOZAA</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>CARROUSEL TJ</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>01-04-2026 16:25:57</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>01-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L31" t="n">
+        <v>649</v>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>30</v>
+      </c>
+      <c r="B32" t="n">
+        <v>98429</v>
+      </c>
+      <c r="C32" t="n">
+        <v>347152</v>
+      </c>
+      <c r="D32" t="n">
+        <v>89317</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>AMADO  CORDOVA  SORIA</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>SALTILLO VILLALTA</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>01-04-2026 18:36:29</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>01-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L32" t="n">
+        <v>649</v>
+      </c>
+      <c r="M32" t="n">
+        <v>11</v>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>27-03-2027 18:36:29</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>31</v>
+      </c>
+      <c r="B33" t="n">
+        <v>98440</v>
+      </c>
+      <c r="C33" t="n">
+        <v>236970</v>
+      </c>
+      <c r="D33" t="n">
+        <v>34475</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>MARCOS  EDUARDO MINJAREZ</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>PAPALOTE TJ</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>01-04-2026 19:54:42</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>01-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L33" t="n">
+        <v>499</v>
+      </c>
+      <c r="M33" t="n">
+        <v>11</v>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>27-03-2027 19:54:42</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P33" t="n">
+        <v>81791</v>
+      </c>
+      <c r="Q33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>32</v>
+      </c>
+      <c r="B34" t="n">
+        <v>98447</v>
+      </c>
+      <c r="C34" t="n">
+        <v>147739</v>
+      </c>
+      <c r="D34" t="n">
+        <v>45315</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>CARLOS ALEJANDRO GIJON BURGOIN</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>PASEO LA PAZ</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>01-04-2026 20:57:51</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>01-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L34" t="n">
+        <v>549</v>
+      </c>
+      <c r="M34" t="n">
+        <v>11</v>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>27-03-2027 20:57:51</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>33</v>
+      </c>
+      <c r="B35" t="n">
+        <v>96825</v>
+      </c>
+      <c r="C35" t="n">
+        <v>131946</v>
+      </c>
+      <c r="D35" t="n">
+        <v>29604</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>CHRISTOFER ISAAC RAMIREZ MARTINEZ</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>PAPALOTE TJ</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>14-03-2026 11:57:25</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>02-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I35" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L35" t="n">
+        <v>399</v>
+      </c>
+      <c r="M35" t="n">
+        <v>11</v>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>09-03-2027 11:57:25</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P35" t="n">
+        <v>21366</v>
+      </c>
+      <c r="Q35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>34</v>
+      </c>
+      <c r="B36" t="n">
+        <v>95681</v>
+      </c>
+      <c r="C36" t="n">
+        <v>276079</v>
+      </c>
+      <c r="D36" t="n">
+        <v>73581</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>RAMON  SANCHEZ  RODRIGUEZ</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>MISION ENS</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>03-03-2026 5:53:34</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>01-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L36" t="n">
+        <v>399</v>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P36" t="n">
+        <v>67204</v>
+      </c>
+      <c r="Q36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>35</v>
+      </c>
+      <c r="B37" t="n">
+        <v>98387</v>
+      </c>
+      <c r="C37" t="n">
+        <v>340681</v>
+      </c>
+      <c r="D37" t="n">
+        <v>18499</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>ALEXIS BENITEZ DEGOLLADO</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>METEPEC</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>01-04-2026 8:57:28</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>01-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L37" t="n">
+        <v>549</v>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>36</v>
+      </c>
+      <c r="B38" t="n">
+        <v>98389</v>
+      </c>
+      <c r="C38" t="n">
+        <v>354805</v>
+      </c>
+      <c r="D38" t="n">
+        <v>96969</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>GUSTAVO CHAPA DAVALOS</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>TLALNEPANTLA</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>01-04-2026 10:29:44</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>01-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I38" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L38" t="n">
+        <v>549</v>
+      </c>
+      <c r="M38" t="n">
+        <v>11</v>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>27-03-2027 10:29:44</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr"/>
+      <c r="Q38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>37</v>
+      </c>
+      <c r="B39" t="n">
+        <v>98398</v>
+      </c>
+      <c r="C39" t="n">
+        <v>289580</v>
+      </c>
+      <c r="D39" t="n">
+        <v>87078</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>GRACIELAGLORIA GONZALEZ MARTÍNEZ</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>SAN LUIS</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>01-04-2026 12:11:54</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>01-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I39" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L39" t="n">
+        <v>549</v>
+      </c>
+      <c r="M39" t="n">
+        <v>11</v>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>27-03-2027 12:11:54</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>38</v>
+      </c>
+      <c r="B40" t="n">
+        <v>98421</v>
+      </c>
+      <c r="C40" t="n">
+        <v>181296</v>
+      </c>
+      <c r="D40" t="n">
+        <v>78803</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>KAMILA  RODRIGUES DE MENEZES</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>CARROUSEL TJ</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>01-04-2026 17:44:14</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>01-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I40" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L40" t="n">
+        <v>549</v>
+      </c>
+      <c r="M40" t="n">
+        <v>11</v>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>27-03-2027 17:44:14</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr"/>
+      <c r="Q40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>39</v>
+      </c>
+      <c r="B41" t="n">
+        <v>98423</v>
+      </c>
+      <c r="C41" t="n">
+        <v>354845</v>
+      </c>
+      <c r="D41" t="n">
+        <v>97009</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>MONICA PAMELA CHAPA  RODRIGUEZ</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>STA CATARINA</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>01-04-2026 13:28:58</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>01-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I41" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L41" t="n">
+        <v>549</v>
+      </c>
+      <c r="M41" t="n">
+        <v>11</v>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>27-03-2027 13:28:58</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr"/>
+      <c r="Q41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>40</v>
+      </c>
+      <c r="B42" t="n">
+        <v>98430</v>
+      </c>
+      <c r="C42" t="n">
+        <v>98152</v>
+      </c>
+      <c r="D42" t="n">
+        <v>95909</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>IRMA  CASTAÑON ROMAN</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>LOMA BONITA</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>01-04-2026 18:53:00</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>01-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I42" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L42" t="n">
+        <v>549</v>
+      </c>
+      <c r="M42" t="n">
+        <v>11</v>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>27-03-2027 18:53:00</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr"/>
+      <c r="Q42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>41</v>
+      </c>
+      <c r="B43" t="n">
+        <v>98432</v>
+      </c>
+      <c r="C43" t="n">
+        <v>338829</v>
+      </c>
+      <c r="D43" t="n">
+        <v>16647</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>ROSA TELLEZ GUADARRAMA</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>INSURGENTES</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>01-04-2026 18:55:11</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>02-07-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L43" t="n">
+        <v>1549</v>
+      </c>
+      <c r="M43" t="n">
+        <v>9</v>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>27-03-2027 18:55:11</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr"/>
+      <c r="Q43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>42</v>
+      </c>
+      <c r="B44" t="n">
+        <v>98455</v>
+      </c>
+      <c r="C44" t="n">
+        <v>354979</v>
+      </c>
+      <c r="D44" t="n">
+        <v>97143</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>MARIA VIANNEY OLVERA RODRIGUEZ</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>PASEO 2000</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>02-04-2026 7:52:12</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>02-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I44" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L44" t="n">
+        <v>549</v>
+      </c>
+      <c r="M44" t="n">
+        <v>11</v>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>28-03-2027 7:52:12</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr"/>
+      <c r="Q44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>43</v>
+      </c>
+      <c r="B45" t="n">
+        <v>96824</v>
+      </c>
+      <c r="C45" t="n">
+        <v>295993</v>
+      </c>
+      <c r="D45" t="n">
+        <v>93491</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>MIGUEL ANGEL  ASTUDILLO MARIN</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>CARROUSEL TJ</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>14-03-2026 11:57:18</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>02-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I45" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L45" t="n">
+        <v>499</v>
+      </c>
+      <c r="M45" t="n">
+        <v>11</v>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>09-03-2027 11:57:18</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P45" t="n">
+        <v>76896</v>
+      </c>
+      <c r="Q45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>44</v>
+      </c>
+      <c r="B46" t="n">
+        <v>98089</v>
+      </c>
+      <c r="C46" t="n">
+        <v>354084</v>
+      </c>
+      <c r="D46" t="n">
+        <v>96248</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>ROSALBA DOMINGO PARRA</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>TLALNEPANTLA</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>30-03-2026 8:23:13</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>30-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I46" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L46" t="n">
+        <v>549</v>
+      </c>
+      <c r="M46" t="n">
+        <v>11</v>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>25-03-2027 8:23:13</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr"/>
+      <c r="Q46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>45</v>
+      </c>
+      <c r="B47" t="n">
+        <v>95361</v>
+      </c>
+      <c r="C47" t="n">
+        <v>237196</v>
+      </c>
+      <c r="D47" t="n">
+        <v>34701</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>PAULINA ELIZABETH FLORES HINOJOSA</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>SANTA FE</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>01-03-2026 14:42:48</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>01-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I47" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L47" t="n">
+        <v>449</v>
+      </c>
+      <c r="M47" t="n">
+        <v>5</v>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>28-08-2026 14:42:48</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P47" t="n">
+        <v>39905</v>
+      </c>
+      <c r="Q47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>46</v>
+      </c>
+      <c r="B48" t="n">
+        <v>98384</v>
+      </c>
+      <c r="C48" t="n">
+        <v>3040</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>02041</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>LISBETH MAGALLI GARCIA VERDUZCO</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>SEND MXL</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>01-04-2026 7:50:45</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>01-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L48" t="n">
+        <v>549</v>
+      </c>
+      <c r="M48" t="n">
+        <v>11</v>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>27-03-2027 7:50:45</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr"/>
+      <c r="Q48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>47</v>
+      </c>
+      <c r="B49" t="n">
+        <v>98399</v>
+      </c>
+      <c r="C49" t="n">
+        <v>150909</v>
+      </c>
+      <c r="D49" t="n">
+        <v>48475</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>KARINA LIZBETH FLORES SILVA</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>SAN LUIS</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>01-04-2026 12:30:40</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>01-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I49" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L49" t="n">
+        <v>499</v>
+      </c>
+      <c r="M49" t="n">
+        <v>11</v>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>27-03-2027 12:30:40</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P49" t="n">
+        <v>83695</v>
+      </c>
+      <c r="Q49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>48</v>
+      </c>
+      <c r="B50" t="n">
+        <v>98403</v>
+      </c>
+      <c r="C50" t="n">
+        <v>354838</v>
+      </c>
+      <c r="D50" t="n">
+        <v>97002</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>ROCIO GUADALUPE ROCHA PADRON</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>IXTAPALUCA</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>01-04-2026 13:06:47</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>01-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L50" t="n">
+        <v>649</v>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr"/>
+      <c r="Q50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>49</v>
+      </c>
+      <c r="B51" t="n">
+        <v>98416</v>
+      </c>
+      <c r="C51" t="n">
+        <v>354894</v>
+      </c>
+      <c r="D51" t="n">
+        <v>97058</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>ANGEL ISMAEL VENCES  OCHOA</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>SEND MXL</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>01-04-2026 16:28:22</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>01-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I51" t="n">
+        <v>0</v>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L51" t="n">
+        <v>549</v>
+      </c>
+      <c r="M51" t="n">
+        <v>11</v>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>27-03-2027 16:28:22</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr"/>
+      <c r="Q51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>50</v>
+      </c>
+      <c r="B52" t="n">
+        <v>98433</v>
+      </c>
+      <c r="C52" t="n">
+        <v>240369</v>
+      </c>
+      <c r="D52" t="n">
+        <v>37874</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>ALEXIS RAYMUNDO  CAMPOS  JUAREZ</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>SANTA FE</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>01-04-2026 18:56:46</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>01-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I52" t="n">
+        <v>0</v>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L52" t="n">
+        <v>499</v>
+      </c>
+      <c r="M52" t="n">
+        <v>11</v>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>27-03-2027 18:56:46</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P52" t="n">
+        <v>80953</v>
+      </c>
+      <c r="Q52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>51</v>
+      </c>
+      <c r="B53" t="n">
+        <v>98450</v>
+      </c>
+      <c r="C53" t="n">
+        <v>36331</v>
+      </c>
+      <c r="D53" t="n">
+        <v>34235</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>YOSELYN MICHEL SALAZAR  FIGUEROA</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>SANTA FE</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>01-04-2026 21:41:21</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>01-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I53" t="n">
+        <v>0</v>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L53" t="n">
+        <v>649</v>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr"/>
+      <c r="Q53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>52</v>
+      </c>
+      <c r="B54" t="n">
+        <v>98452</v>
+      </c>
+      <c r="C54" t="n">
+        <v>244777</v>
+      </c>
+      <c r="D54" t="n">
+        <v>42282</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>NANCY  HERNÁNDEZ GONZALEZ</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>SEND SALTILLO</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>02-04-2026 6:26:04</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>02-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I54" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L54" t="n">
+        <v>999</v>
+      </c>
+      <c r="M54" t="n">
+        <v>11</v>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>28-03-2027 6:26:04</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr"/>
+      <c r="Q54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>53</v>
+      </c>
+      <c r="B55" t="n">
+        <v>97112</v>
+      </c>
+      <c r="C55" t="n">
+        <v>307274</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>04773</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>ESMERALDA GUADALUPE RANGEL ESQUIVEL</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>SEND SALTILLO</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>17-03-2026 18:17:30</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>02-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I55" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L55" t="n">
+        <v>499</v>
+      </c>
+      <c r="M55" t="n">
+        <v>11</v>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>12-03-2027 18:17:30</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P55" t="n">
+        <v>87410</v>
+      </c>
+      <c r="Q55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>54</v>
+      </c>
+      <c r="B56" t="n">
+        <v>97214</v>
+      </c>
+      <c r="C56" t="n">
+        <v>227607</v>
+      </c>
+      <c r="D56" t="n">
+        <v>25112</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>NUBIA LORENA BUCIO CASTILLO</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>PAPALOTE TJ</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>18-03-2026 16:31:25</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>02-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I56" t="n">
+        <v>0</v>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L56" t="n">
+        <v>449</v>
+      </c>
+      <c r="M56" t="n">
+        <v>5</v>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>14-09-2026 16:31:25</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P56" t="n">
+        <v>50707</v>
+      </c>
+      <c r="Q56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>55</v>
+      </c>
+      <c r="B57" t="n">
+        <v>97965</v>
+      </c>
+      <c r="C57" t="n">
+        <v>70411</v>
+      </c>
+      <c r="D57" t="n">
+        <v>68233</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>CYNTHIA IVETH GARCIA  MORENO</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>SEND MXL</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>27-03-2026 11:58:41</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>01-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I57" t="n">
+        <v>0</v>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L57" t="n">
+        <v>449</v>
+      </c>
+      <c r="M57" t="n">
+        <v>11</v>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>22-03-2027 11:58:41</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P57" t="n">
+        <v>31636</v>
+      </c>
+      <c r="Q57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>56</v>
+      </c>
+      <c r="B58" t="n">
+        <v>98406</v>
+      </c>
+      <c r="C58" t="n">
+        <v>354852</v>
+      </c>
+      <c r="D58" t="n">
+        <v>97016</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>ROBERTO EMILIANO BAEZ  GONZALEZ</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>INSURGENTES</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>01-04-2026 14:27:45</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>01-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I58" t="n">
+        <v>0</v>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L58" t="n">
+        <v>649</v>
+      </c>
+      <c r="M58" t="n">
+        <v>11</v>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>27-03-2027 14:27:45</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr"/>
+      <c r="Q58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>57</v>
+      </c>
+      <c r="B59" t="n">
+        <v>98413</v>
+      </c>
+      <c r="C59" t="n">
+        <v>253549</v>
+      </c>
+      <c r="D59" t="n">
+        <v>51053</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>ROSA MARINA LOPEZ ESPINOSA</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>CARROUSEL TJ</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>01-04-2026 15:44:33</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>01-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I59" t="n">
+        <v>0</v>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L59" t="n">
+        <v>499</v>
+      </c>
+      <c r="M59" t="n">
+        <v>11</v>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>27-03-2027 15:44:33</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P59" t="n">
+        <v>38535</v>
+      </c>
+      <c r="Q59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>58</v>
+      </c>
+      <c r="B60" t="n">
+        <v>98431</v>
+      </c>
+      <c r="C60" t="n">
+        <v>133972</v>
+      </c>
+      <c r="D60" t="n">
+        <v>31622</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>EDGAR ALI JIMENEZ LOPEZ</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>PASEO 2000</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>01-04-2026 18:54:53</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>01-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I60" t="n">
+        <v>0</v>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L60" t="n">
+        <v>499</v>
+      </c>
+      <c r="M60" t="n">
+        <v>11</v>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>27-03-2027 18:54:53</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P60" t="n">
+        <v>21825</v>
+      </c>
+      <c r="Q60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>59</v>
+      </c>
+      <c r="B61" t="n">
+        <v>98438</v>
+      </c>
+      <c r="C61" t="n">
+        <v>340018</v>
+      </c>
+      <c r="D61" t="n">
+        <v>17836</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>ANDRES AVILA ROJAS</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>MISION ENS</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>01-04-2026 19:36:58</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>02-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I61" t="n">
+        <v>0</v>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L61" t="n">
+        <v>549</v>
+      </c>
+      <c r="M61" t="n">
+        <v>11</v>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>27-03-2027 19:36:58</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P61" t="n">
+        <v>91348</v>
+      </c>
+      <c r="Q61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>60</v>
+      </c>
+      <c r="B62" t="n">
+        <v>98456</v>
+      </c>
+      <c r="C62" t="n">
+        <v>354538</v>
+      </c>
+      <c r="D62" t="n">
+        <v>96702</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>MARIA NALLELY ROMAN ESPINOZA</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>VILLA VERDE</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>02-04-2026 8:39:43</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>02-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I62" t="n">
+        <v>0</v>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L62" t="n">
+        <v>549</v>
+      </c>
+      <c r="M62" t="n">
+        <v>11</v>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>28-03-2027 8:39:43</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr"/>
+      <c r="Q62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>61</v>
+      </c>
+      <c r="B63" t="n">
+        <v>95816</v>
+      </c>
+      <c r="C63" t="n">
+        <v>26874</v>
+      </c>
+      <c r="D63" t="n">
+        <v>24813</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>JESUS  NUÑEZ CHICUATE</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>TEC MXL</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>03-03-2026 18:01:45</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>02-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I63" t="n">
+        <v>0</v>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L63" t="n">
+        <v>449</v>
+      </c>
+      <c r="M63" t="n">
+        <v>5</v>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>30-08-2026 18:01:45</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P63" t="n">
+        <v>51181</v>
+      </c>
+      <c r="Q63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>62</v>
+      </c>
+      <c r="B64" t="n">
+        <v>97995</v>
+      </c>
+      <c r="C64" t="n">
+        <v>295894</v>
+      </c>
+      <c r="D64" t="n">
+        <v>93392</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>AITZA MIRENA GUTIERREZ  BLANCARTE</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>VILLAS DEL REY</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>27-03-2026 16:22:41</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>02-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I64" t="n">
+        <v>0</v>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L64" t="n">
+        <v>499</v>
+      </c>
+      <c r="M64" t="n">
+        <v>11</v>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>22-03-2027 16:22:41</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P64" t="n">
+        <v>94569</v>
+      </c>
+      <c r="Q64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>63</v>
+      </c>
+      <c r="B65" t="n">
+        <v>98378</v>
+      </c>
+      <c r="C65" t="n">
+        <v>234373</v>
+      </c>
+      <c r="D65" t="n">
+        <v>31878</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>ANDREA  ESTAÑOL CUESTA</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>SEND MXL</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>01-04-2026 5:10:38</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>01-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I65" t="n">
+        <v>0</v>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L65" t="n">
+        <v>549</v>
+      </c>
+      <c r="M65" t="n">
+        <v>11</v>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>27-03-2027 5:10:38</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr"/>
+      <c r="Q65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>64</v>
+      </c>
+      <c r="B66" t="n">
+        <v>98380</v>
+      </c>
+      <c r="C66" t="n">
+        <v>218531</v>
+      </c>
+      <c r="D66" t="n">
+        <v>16039</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>MARIA EUUGENIA CUESTA GUERRERRO</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>SEND MXL</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>01-04-2026 5:54:51</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>01-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I66" t="n">
+        <v>0</v>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L66" t="n">
+        <v>499</v>
+      </c>
+      <c r="M66" t="n">
+        <v>11</v>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>27-03-2027 5:54:51</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P66" t="n">
+        <v>16036</v>
+      </c>
+      <c r="Q66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>65</v>
+      </c>
+      <c r="B67" t="n">
+        <v>98382</v>
+      </c>
+      <c r="C67" t="n">
+        <v>10048</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>08977</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>JORGE HUMBERTO ROBLES BURGUEÑO</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>PABELLON RTO</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>01-04-2026 6:55:06</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>01-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I67" t="n">
+        <v>0</v>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L67" t="n">
+        <v>549</v>
+      </c>
+      <c r="M67" t="n">
+        <v>11</v>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>27-03-2027 6:55:06</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr"/>
+      <c r="Q67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>66</v>
+      </c>
+      <c r="B68" t="n">
+        <v>98405</v>
+      </c>
+      <c r="C68" t="n">
+        <v>71326</v>
+      </c>
+      <c r="D68" t="n">
+        <v>69147</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>LEONEL  NUÑEZ  MENDOZA</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>SAN LUIS</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>01-04-2026 14:07:16</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>01-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I68" t="n">
+        <v>0</v>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L68" t="n">
+        <v>499</v>
+      </c>
+      <c r="M68" t="n">
+        <v>11</v>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>27-03-2027 14:07:16</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P68" t="n">
+        <v>19720</v>
+      </c>
+      <c r="Q68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>67</v>
+      </c>
+      <c r="B69" t="n">
+        <v>98407</v>
+      </c>
+      <c r="C69" t="n">
+        <v>354856</v>
+      </c>
+      <c r="D69" t="n">
+        <v>97020</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>GUILLERMINA  REYES  R</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>MISION ENS</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>01-04-2026 14:28:19</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>01-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I69" t="n">
+        <v>0</v>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L69" t="n">
+        <v>549</v>
+      </c>
+      <c r="M69" t="n">
+        <v>11</v>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>27-03-2027 14:28:19</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr"/>
+      <c r="Q69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>68</v>
+      </c>
+      <c r="B70" t="n">
+        <v>98412</v>
+      </c>
+      <c r="C70" t="n">
+        <v>354877</v>
+      </c>
+      <c r="D70" t="n">
+        <v>97041</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>JAQUELINE TORRES MARTINEZ</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>SEND MXL</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>01-04-2026 15:27:35</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>01-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I70" t="n">
+        <v>0</v>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L70" t="n">
+        <v>649</v>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr"/>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr"/>
+      <c r="Q70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>69</v>
+      </c>
+      <c r="B71" t="n">
+        <v>98414</v>
+      </c>
+      <c r="C71" t="n">
+        <v>351183</v>
+      </c>
+      <c r="D71" t="n">
+        <v>93347</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>KENNETH ROSEMBERG VILLA FRANCO</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>IXTAPALUCA</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>01-04-2026 15:47:30</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>01-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I71" t="n">
+        <v>0</v>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L71" t="n">
+        <v>549</v>
+      </c>
+      <c r="M71" t="n">
+        <v>11</v>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>27-03-2027 15:47:30</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr"/>
+      <c r="Q71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>70</v>
+      </c>
+      <c r="B72" t="n">
+        <v>98437</v>
+      </c>
+      <c r="C72" t="n">
+        <v>354929</v>
+      </c>
+      <c r="D72" t="n">
+        <v>97093</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>JOSE EDUARDO  CUEN  RENTERIA</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>SEND MXL</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>01-04-2026 19:09:05</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>01-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I72" t="n">
+        <v>0</v>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L72" t="n">
+        <v>649</v>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr"/>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr"/>
+      <c r="Q72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>71</v>
+      </c>
+      <c r="B73" t="n">
+        <v>98448</v>
+      </c>
+      <c r="C73" t="n">
+        <v>348011</v>
+      </c>
+      <c r="D73" t="n">
+        <v>90176</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>LARISSA IVETTE LOZA  CUETO</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>VILLA VERDE</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>01-04-2026 21:18:05</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>01-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I73" t="n">
+        <v>0</v>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L73" t="n">
+        <v>549</v>
+      </c>
+      <c r="M73" t="n">
+        <v>11</v>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>27-03-2027 21:18:05</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr"/>
+      <c r="Q73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>72</v>
+      </c>
+      <c r="B74" t="n">
+        <v>95699</v>
+      </c>
+      <c r="C74" t="n">
+        <v>250359</v>
+      </c>
+      <c r="D74" t="n">
+        <v>47863</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>LENE  RODRIGUEZ CORRALES</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>SAN LUIS</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>03-03-2026 8:11:05</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>02-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I74" t="n">
+        <v>0</v>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L74" t="n">
+        <v>549</v>
+      </c>
+      <c r="M74" t="n">
+        <v>5</v>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>30-08-2026 8:11:05</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P74" t="n">
+        <v>76998</v>
+      </c>
+      <c r="Q74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>73</v>
+      </c>
+      <c r="B75" t="n">
+        <v>96508</v>
+      </c>
+      <c r="C75" t="n">
+        <v>324178</v>
+      </c>
+      <c r="D75" t="n">
+        <v>21117</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>EDNA PRICILA  HERRERA  LOPEZ</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>INDEPENDENCIA</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>10-03-2026 14:42:50</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>01-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>0</v>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L75" t="n">
+        <v>399</v>
+      </c>
+      <c r="M75" t="n">
+        <v>11</v>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>05-03-2027 14:42:50</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P75" t="n">
+        <v>83239</v>
+      </c>
+      <c r="Q75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>74</v>
+      </c>
+      <c r="B76" t="n">
+        <v>98376</v>
+      </c>
+      <c r="C76" t="n">
+        <v>330015</v>
+      </c>
+      <c r="D76" t="n">
+        <v>15069</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>NOEL GALLEGOS VARELA</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>SEND CHIH</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>01-04-2026 5:07:31</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>01-07-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I76" t="n">
+        <v>0</v>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L76" t="n">
+        <v>1449</v>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr"/>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr"/>
+      <c r="Q76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>75</v>
+      </c>
+      <c r="B77" t="n">
+        <v>98393</v>
+      </c>
+      <c r="C77" t="n">
+        <v>354818</v>
+      </c>
+      <c r="D77" t="n">
+        <v>96982</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>ISIDRO  MENDEZ  JARAMILLO</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>SALTILLO VILLALTA</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>01-04-2026 10:58:42</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>01-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I77" t="n">
+        <v>0</v>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L77" t="n">
+        <v>799</v>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr"/>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr"/>
+      <c r="Q77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>76</v>
+      </c>
+      <c r="B78" t="n">
+        <v>98411</v>
+      </c>
+      <c r="C78" t="n">
+        <v>354867</v>
+      </c>
+      <c r="D78" t="n">
+        <v>97031</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>SEBASTIAN IBAÑEZ RAMIREZ</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>INSURGENTES</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>01-04-2026 15:15:54</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>01-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I78" t="n">
+        <v>0</v>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L78" t="n">
+        <v>649</v>
+      </c>
+      <c r="M78" t="n">
+        <v>11</v>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>27-03-2027 15:15:54</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr"/>
+      <c r="Q78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>77</v>
+      </c>
+      <c r="B79" t="n">
+        <v>98425</v>
+      </c>
+      <c r="C79" t="n">
+        <v>352652</v>
+      </c>
+      <c r="D79" t="n">
+        <v>94816</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>MARCO VEGA DUARTE</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>TEC MXL</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>01-04-2026 18:03:42</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>01-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I79" t="n">
+        <v>0</v>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L79" t="n">
+        <v>549</v>
+      </c>
+      <c r="M79" t="n">
+        <v>11</v>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>27-03-2027 18:03:42</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr"/>
+      <c r="Q79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>78</v>
+      </c>
+      <c r="B80" t="n">
+        <v>98426</v>
+      </c>
+      <c r="C80" t="n">
+        <v>183909</v>
+      </c>
+      <c r="D80" t="n">
+        <v>81416</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>FELIPE ARTURO HERNANDEZ VALDEZ</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>CARROUSEL TJ</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>01-04-2026 18:03:51</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>01-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I80" t="n">
+        <v>0</v>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L80" t="n">
+        <v>399</v>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr"/>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P80" t="n">
+        <v>43588</v>
+      </c>
+      <c r="Q80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>79</v>
+      </c>
+      <c r="B81" t="n">
+        <v>98443</v>
+      </c>
+      <c r="C81" t="n">
+        <v>257769</v>
+      </c>
+      <c r="D81" t="n">
+        <v>55273</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>JUANA ISABEL DOMINGUEZ MATA</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>LOMA BONITA</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>01-04-2026 20:24:55</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>01-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I81" t="n">
+        <v>0</v>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L81" t="n">
+        <v>549</v>
+      </c>
+      <c r="M81" t="n">
+        <v>11</v>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>27-03-2027 20:24:55</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr"/>
+      <c r="Q81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>80</v>
+      </c>
+      <c r="B82" t="n">
+        <v>98444</v>
+      </c>
+      <c r="C82" t="n">
+        <v>280981</v>
+      </c>
+      <c r="D82" t="n">
+        <v>78482</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>JOSE DANIEL  CASTRO DE LOS REYES</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>SAN LUIS</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>01-04-2026 20:33:23</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>01-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I82" t="n">
+        <v>0</v>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L82" t="n">
+        <v>649</v>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr"/>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr"/>
+      <c r="Q82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>81</v>
+      </c>
+      <c r="B83" t="n">
+        <v>98458</v>
+      </c>
+      <c r="C83" t="n">
+        <v>355001</v>
+      </c>
+      <c r="D83" t="n">
+        <v>97165</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>MARIA ELODIA SALVADOR MORALES</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>PASEO 2000</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>02-04-2026 8:58:21</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>02-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I83" t="n">
+        <v>0</v>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L83" t="n">
+        <v>549</v>
+      </c>
+      <c r="M83" t="n">
+        <v>11</v>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>28-03-2027 8:58:21</t>
+        </is>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr"/>
+      <c r="Q83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Reporte generado: 02-04-2026 04:04 p. m.</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr"/>
+      <c r="C84" t="inlineStr"/>
+      <c r="D84" t="inlineStr"/>
+      <c r="E84" t="inlineStr"/>
+      <c r="F84" t="inlineStr"/>
+      <c r="G84" t="inlineStr"/>
+      <c r="H84" t="inlineStr"/>
+      <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr"/>
+      <c r="N84" t="inlineStr"/>
+      <c r="O84" t="inlineStr"/>
+      <c r="P84" t="inlineStr"/>
+      <c r="Q84" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/descargas/cargos_recurrentes.xlsx
+++ b/data/descargas/cargos_recurrentes.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q84"/>
+  <dimension ref="A1:Q133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1253,27 +1253,27 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>95945</v>
+        <v>98483</v>
       </c>
       <c r="C13" t="n">
-        <v>331588</v>
+        <v>355127</v>
       </c>
       <c r="D13" t="n">
-        <v>16642</v>
+        <v>97291</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>ROMINA SOSA SOLIS</t>
+          <t>EDUARDO  PALACIOS GONZALEZ</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>SALTILLO VILLALTA</t>
+          <t>METEPEC</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>04-03-2026 16:58:11</t>
+          <t>02-04-2026 16:02:53</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>RENOVACIÓN</t>
+          <t>NUEVO</t>
         </is>
       </c>
       <c r="L13" t="n">
@@ -1302,7 +1302,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>27-02-2027 16:58:11</t>
+          <t>28-03-2027 16:02:53</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1310,9 +1310,7 @@
           <t>Domiciliado</t>
         </is>
       </c>
-      <c r="P13" t="n">
-        <v>85408</v>
-      </c>
+      <c r="P13" t="inlineStr"/>
       <c r="Q13" t="inlineStr"/>
     </row>
     <row r="14">
@@ -1320,32 +1318,32 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>98066</v>
+        <v>98485</v>
       </c>
       <c r="C14" t="n">
-        <v>316321</v>
+        <v>355129</v>
       </c>
       <c r="D14" t="n">
-        <v>13819</v>
+        <v>97293</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>JESSICA LIZETH RODRIGUEZ GRIJALVA</t>
+          <t>JANET BERENICE ESTRADA LABASTIDA</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>SEND CHIH</t>
+          <t>METEPEC</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>29-03-2026 13:48:23</t>
+          <t>02-04-2026 16:11:59</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>01-05-2026 23:59:59</t>
+          <t>02-05-2026 23:59:59</t>
         </is>
       </c>
       <c r="I14" t="n">
@@ -1358,18 +1356,18 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>RENOVACIÓN</t>
+          <t>NUEVO</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>549</v>
+        <v>649</v>
       </c>
       <c r="M14" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>25-09-2026 13:48:23</t>
+          <t>28-03-2027 16:11:59</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -1377,9 +1375,7 @@
           <t>Domiciliado</t>
         </is>
       </c>
-      <c r="P14" t="n">
-        <v>79196</v>
-      </c>
+      <c r="P14" t="inlineStr"/>
       <c r="Q14" t="inlineStr"/>
     </row>
     <row r="15">
@@ -1387,32 +1383,32 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>95401</v>
+        <v>98500</v>
       </c>
       <c r="C15" t="n">
-        <v>202026</v>
+        <v>147601</v>
       </c>
       <c r="D15" t="n">
-        <v>99533</v>
+        <v>45177</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>GABRIELA MARIA SOTO VIELLEDENT</t>
+          <t>JUAN ERNESTO MIRANDA ORTEGA</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>VILLA VERDE</t>
+          <t>PASEO LA PAZ</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>02-03-2026 7:51:41</t>
+          <t>02-04-2026 18:33:21</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>01-05-2026 23:59:59</t>
+          <t>02-05-2026 23:59:59</t>
         </is>
       </c>
       <c r="I15" t="n">
@@ -1425,18 +1421,18 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>RENOVACIÓN</t>
+          <t>NUEVO</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>499</v>
+        <v>549</v>
       </c>
       <c r="M15" t="n">
         <v>11</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>25-02-2027 7:51:41</t>
+          <t>28-03-2027 18:33:21</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -1444,9 +1440,7 @@
           <t>Domiciliado</t>
         </is>
       </c>
-      <c r="P15" t="n">
-        <v>76934</v>
-      </c>
+      <c r="P15" t="inlineStr"/>
       <c r="Q15" t="inlineStr"/>
     </row>
     <row r="16">
@@ -1454,27 +1448,27 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>95416</v>
+        <v>98502</v>
       </c>
       <c r="C16" t="n">
-        <v>93948</v>
+        <v>355205</v>
       </c>
       <c r="D16" t="n">
-        <v>91707</v>
+        <v>97369</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>ANA RAFAELA GALVAN LOPEZ</t>
+          <t>CRISTOFER KEVIN  OSNAYA RODRIGUEZ</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>SEND SALTILLO</t>
+          <t>SALTILLO VILLALTA</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>02-03-2026 9:03:29</t>
+          <t>02-04-2026 19:19:45</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1492,18 +1486,18 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>RENOVACIÓN</t>
+          <t>NUEVO</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>499</v>
+        <v>649</v>
       </c>
       <c r="M16" t="n">
         <v>11</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>25-02-2027 9:03:29</t>
+          <t>28-03-2027 19:19:45</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -1511,9 +1505,7 @@
           <t>Domiciliado</t>
         </is>
       </c>
-      <c r="P16" t="n">
-        <v>95415</v>
-      </c>
+      <c r="P16" t="inlineStr"/>
       <c r="Q16" t="inlineStr"/>
     </row>
     <row r="17">
@@ -1521,27 +1513,27 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>95451</v>
+        <v>95945</v>
       </c>
       <c r="C17" t="n">
-        <v>339837</v>
+        <v>331588</v>
       </c>
       <c r="D17" t="n">
-        <v>17655</v>
+        <v>16642</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>CRISTIAN ALEXIS RUIZ AGUILAR</t>
+          <t>ROMINA SOSA SOLIS</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>INSURGENTES</t>
+          <t>SALTILLO VILLALTA</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>02-03-2026 11:39:41</t>
+          <t>04-03-2026 16:58:11</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1570,7 +1562,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>25-02-2027 11:39:41</t>
+          <t>27-02-2027 16:58:11</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -1579,7 +1571,7 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>91337</v>
+        <v>85408</v>
       </c>
       <c r="Q17" t="inlineStr"/>
     </row>
@@ -1588,32 +1580,32 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>98391</v>
+        <v>95996</v>
       </c>
       <c r="C18" t="n">
-        <v>354812</v>
+        <v>36383</v>
       </c>
       <c r="D18" t="n">
-        <v>96976</v>
+        <v>34287</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>ALAN  ESCOBEDO  BAEZ</t>
+          <t>CECILIA LLAMAS VALTIERRRA</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>INSURGENTES</t>
+          <t>TEC MXL</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>01-04-2026 10:47:30</t>
+          <t>04-03-2026 22:02:57</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>01-05-2026 23:59:59</t>
+          <t>03-05-2026 23:59:59</t>
         </is>
       </c>
       <c r="I18" t="n">
@@ -1626,24 +1618,28 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>NUEVO</t>
+          <t>RENOVACIÓN</t>
         </is>
       </c>
       <c r="L18" t="n">
         <v>549</v>
       </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>Indefinido</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
+      <c r="M18" t="n">
+        <v>11</v>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>27-02-2027 22:02:57</t>
+        </is>
+      </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Recurrente</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr"/>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P18" t="n">
+        <v>95856</v>
+      </c>
       <c r="Q18" t="inlineStr"/>
     </row>
     <row r="19">
@@ -1651,32 +1647,32 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>98392</v>
+        <v>98049</v>
       </c>
       <c r="C19" t="n">
-        <v>354811</v>
+        <v>87282</v>
       </c>
       <c r="D19" t="n">
-        <v>96975</v>
+        <v>85063</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>XIMENA PAOLA SANCHEZ RAMIREZ</t>
+          <t>NOMAR EDUARDO BARRAZA  VALENZUELA</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>TLALNEPANTLA</t>
+          <t>INDEPENDENCIA</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>01-04-2026 10:48:46</t>
+          <t>28-03-2026 13:08:47</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>01-07-2026 23:59:59</t>
+          <t>03-05-2026 23:59:59</t>
         </is>
       </c>
       <c r="I19" t="n">
@@ -1689,11 +1685,11 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>NUEVO</t>
+          <t>RENOVACIÓN</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1449</v>
+        <v>399</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -1706,7 +1702,9 @@
           <t>Recurrente</t>
         </is>
       </c>
-      <c r="P19" t="inlineStr"/>
+      <c r="P19" t="n">
+        <v>85359</v>
+      </c>
       <c r="Q19" t="inlineStr"/>
     </row>
     <row r="20">
@@ -1714,27 +1712,27 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>98409</v>
+        <v>98066</v>
       </c>
       <c r="C20" t="n">
-        <v>164157</v>
+        <v>316321</v>
       </c>
       <c r="D20" t="n">
-        <v>61690</v>
+        <v>13819</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>BERTHA ALICIA GARCIA HERNANDEZ</t>
+          <t>JESSICA LIZETH RODRIGUEZ GRIJALVA</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>SEND MXL</t>
+          <t>SEND CHIH</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>01-04-2026 15:01:11</t>
+          <t>29-03-2026 13:48:23</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1756,14 +1754,14 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>499</v>
+        <v>549</v>
       </c>
       <c r="M20" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>27-03-2027 15:01:11</t>
+          <t>25-09-2026 13:48:23</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -1772,7 +1770,7 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>62356</v>
+        <v>79196</v>
       </c>
       <c r="Q20" t="inlineStr"/>
     </row>
@@ -1781,32 +1779,32 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>98410</v>
+        <v>95699</v>
       </c>
       <c r="C21" t="n">
-        <v>354869</v>
+        <v>250359</v>
       </c>
       <c r="D21" t="n">
-        <v>97033</v>
+        <v>47863</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>JULIO ARIZMENDI MORENO</t>
+          <t>LENE  RODRIGUEZ CORRALES</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>METEPEC</t>
+          <t>SAN LUIS</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>01-04-2026 15:08:38</t>
+          <t>03-03-2026 8:11:05</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>01-05-2026 23:59:59</t>
+          <t>02-05-2026 23:59:59</t>
         </is>
       </c>
       <c r="I21" t="n">
@@ -1819,24 +1817,28 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>NUEVO</t>
+          <t>RENOVACIÓN</t>
         </is>
       </c>
       <c r="L21" t="n">
         <v>549</v>
       </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>Indefinido</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
+      <c r="M21" t="n">
+        <v>5</v>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>30-08-2026 8:11:05</t>
+        </is>
+      </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Recurrente</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr"/>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P21" t="n">
+        <v>76998</v>
+      </c>
       <c r="Q21" t="inlineStr"/>
     </row>
     <row r="22">
@@ -1844,27 +1846,27 @@
         <v>20</v>
       </c>
       <c r="B22" t="n">
-        <v>98427</v>
+        <v>98378</v>
       </c>
       <c r="C22" t="n">
-        <v>352177</v>
+        <v>234373</v>
       </c>
       <c r="D22" t="n">
-        <v>94341</v>
+        <v>31878</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>JUANA FRIAS GARCIA</t>
+          <t>ANDREA  ESTAÑOL CUESTA</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>CARROUSEL TJ</t>
+          <t>SEND MXL</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>01-04-2026 18:05:19</t>
+          <t>01-04-2026 5:10:38</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1886,17 +1888,19 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>649</v>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>Indefinido</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
+        <v>549</v>
+      </c>
+      <c r="M22" t="n">
+        <v>11</v>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>27-03-2027 5:10:38</t>
+        </is>
+      </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Recurrente</t>
+          <t>Domiciliado</t>
         </is>
       </c>
       <c r="P22" t="inlineStr"/>
@@ -1907,27 +1911,27 @@
         <v>21</v>
       </c>
       <c r="B23" t="n">
-        <v>98428</v>
+        <v>98380</v>
       </c>
       <c r="C23" t="n">
-        <v>354917</v>
+        <v>218531</v>
       </c>
       <c r="D23" t="n">
-        <v>97081</v>
+        <v>16039</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>MARLO ANDRE OCAMPO GARCIA</t>
+          <t>MARIA EUUGENIA CUESTA GUERRERRO</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>INSURGENTES</t>
+          <t>SEND MXL</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>01-04-2026 18:06:23</t>
+          <t>01-04-2026 5:54:51</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1945,18 +1949,18 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>NUEVO</t>
+          <t>RENOVACIÓN</t>
         </is>
       </c>
       <c r="L23" t="n">
-        <v>649</v>
+        <v>499</v>
       </c>
       <c r="M23" t="n">
         <v>11</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>27-03-2027 18:06:23</t>
+          <t>27-03-2027 5:54:51</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -1964,7 +1968,9 @@
           <t>Domiciliado</t>
         </is>
       </c>
-      <c r="P23" t="inlineStr"/>
+      <c r="P23" t="n">
+        <v>16036</v>
+      </c>
       <c r="Q23" t="inlineStr"/>
     </row>
     <row r="24">
@@ -1972,27 +1978,29 @@
         <v>22</v>
       </c>
       <c r="B24" t="n">
-        <v>98441</v>
+        <v>98382</v>
       </c>
       <c r="C24" t="n">
-        <v>151482</v>
-      </c>
-      <c r="D24" t="n">
-        <v>49047</v>
+        <v>10048</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>08977</t>
+        </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>ALAN HERIBERTO ESPINOZA ALIRE</t>
+          <t>JORGE HUMBERTO ROBLES BURGUEÑO</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>INDEPENDENCIA</t>
+          <t>PABELLON RTO</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>01-04-2026 20:05:11</t>
+          <t>01-04-2026 6:55:06</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2014,17 +2022,19 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>649</v>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>Indefinido</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
+        <v>549</v>
+      </c>
+      <c r="M24" t="n">
+        <v>11</v>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>27-03-2027 6:55:06</t>
+        </is>
+      </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>Recurrente</t>
+          <t>Domiciliado</t>
         </is>
       </c>
       <c r="P24" t="inlineStr"/>
@@ -2035,27 +2045,27 @@
         <v>23</v>
       </c>
       <c r="B25" t="n">
-        <v>98442</v>
+        <v>98405</v>
       </c>
       <c r="C25" t="n">
-        <v>354954</v>
+        <v>71326</v>
       </c>
       <c r="D25" t="n">
-        <v>97118</v>
+        <v>69147</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>MARTA  CRUZ ALVARADO</t>
+          <t>LEONEL  NUÑEZ  MENDOZA</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>CARROUSEL TJ</t>
+          <t>SAN LUIS</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>01-04-2026 20:24:50</t>
+          <t>01-04-2026 14:07:16</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2073,24 +2083,28 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>NUEVO</t>
+          <t>RENOVACIÓN</t>
         </is>
       </c>
       <c r="L25" t="n">
-        <v>649</v>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>Indefinido</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
+        <v>499</v>
+      </c>
+      <c r="M25" t="n">
+        <v>11</v>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>27-03-2027 14:07:16</t>
+        </is>
+      </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>Recurrente</t>
-        </is>
-      </c>
-      <c r="P25" t="inlineStr"/>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P25" t="n">
+        <v>19720</v>
+      </c>
       <c r="Q25" t="inlineStr"/>
     </row>
     <row r="26">
@@ -2098,32 +2112,32 @@
         <v>24</v>
       </c>
       <c r="B26" t="n">
-        <v>95669</v>
+        <v>98407</v>
       </c>
       <c r="C26" t="n">
-        <v>165787</v>
+        <v>354856</v>
       </c>
       <c r="D26" t="n">
-        <v>63320</v>
+        <v>97020</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>ALISSON ABRIL ROMERO LARA</t>
+          <t>GUILLERMINA  REYES  R</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>TEC MXL</t>
+          <t>MISION ENS</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>02-03-2026 21:15:34</t>
+          <t>01-04-2026 14:28:19</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>30-04-2026 23:59:59</t>
+          <t>01-05-2026 23:59:59</t>
         </is>
       </c>
       <c r="I26" t="n">
@@ -2136,18 +2150,18 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>RENOVACIÓN</t>
+          <t>NUEVO</t>
         </is>
       </c>
       <c r="L26" t="n">
-        <v>499</v>
+        <v>549</v>
       </c>
       <c r="M26" t="n">
         <v>11</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>25-02-2027 21:15:34</t>
+          <t>27-03-2027 14:28:19</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
@@ -2155,9 +2169,7 @@
           <t>Domiciliado</t>
         </is>
       </c>
-      <c r="P26" t="n">
-        <v>70751</v>
-      </c>
+      <c r="P26" t="inlineStr"/>
       <c r="Q26" t="inlineStr"/>
     </row>
     <row r="27">
@@ -2165,29 +2177,27 @@
         <v>25</v>
       </c>
       <c r="B27" t="n">
-        <v>97974</v>
+        <v>98412</v>
       </c>
       <c r="C27" t="n">
-        <v>312043</v>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>09542</t>
-        </is>
+        <v>354877</v>
+      </c>
+      <c r="D27" t="n">
+        <v>97041</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>YULISSA KARYME GUITRON OSORIO</t>
+          <t>JAQUELINE TORRES MARTINEZ</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>MISION ENS</t>
+          <t>SEND MXL</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>27-03-2026 13:38:44</t>
+          <t>01-04-2026 15:27:35</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2205,11 +2215,11 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>RENOVACIÓN</t>
+          <t>NUEVO</t>
         </is>
       </c>
       <c r="L27" t="n">
-        <v>599</v>
+        <v>649</v>
       </c>
       <c r="M27" t="inlineStr">
         <is>
@@ -2222,9 +2232,7 @@
           <t>Recurrente</t>
         </is>
       </c>
-      <c r="P27" t="n">
-        <v>92547</v>
-      </c>
+      <c r="P27" t="inlineStr"/>
       <c r="Q27" t="inlineStr"/>
     </row>
     <row r="28">
@@ -2232,17 +2240,17 @@
         <v>26</v>
       </c>
       <c r="B28" t="n">
-        <v>98379</v>
+        <v>98414</v>
       </c>
       <c r="C28" t="n">
-        <v>353959</v>
+        <v>351183</v>
       </c>
       <c r="D28" t="n">
-        <v>96123</v>
+        <v>93347</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RICARDO ALEXIS CARMONA  HERNANDEZ</t>
+          <t>KENNETH ROSEMBERG VILLA FRANCO</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -2252,7 +2260,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>01-04-2026 5:24:50</t>
+          <t>01-04-2026 15:47:30</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2281,7 +2289,7 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>27-03-2027 5:24:50</t>
+          <t>27-03-2027 15:47:30</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
@@ -2297,27 +2305,27 @@
         <v>27</v>
       </c>
       <c r="B29" t="n">
-        <v>98397</v>
+        <v>98437</v>
       </c>
       <c r="C29" t="n">
-        <v>354168</v>
+        <v>354929</v>
       </c>
       <c r="D29" t="n">
-        <v>96332</v>
+        <v>97093</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>JESSICA  AMADOR MARTINEZ</t>
+          <t>JOSE EDUARDO  CUEN  RENTERIA</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>PASEO 2000</t>
+          <t>SEND MXL</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>01-04-2026 12:05:06</t>
+          <t>01-04-2026 19:09:05</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2360,27 +2368,27 @@
         <v>28</v>
       </c>
       <c r="B30" t="n">
-        <v>98404</v>
+        <v>98448</v>
       </c>
       <c r="C30" t="n">
-        <v>339346</v>
+        <v>348011</v>
       </c>
       <c r="D30" t="n">
-        <v>17164</v>
+        <v>90176</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>ANA RUT MARTINEZ  BALDERAS</t>
+          <t>LARISSA IVETTE LOZA  CUETO</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>SALTILLO VILLALTA</t>
+          <t>VILLA VERDE</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>01-04-2026 13:19:32</t>
+          <t>01-04-2026 21:18:05</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2404,15 +2412,17 @@
       <c r="L30" t="n">
         <v>549</v>
       </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>Indefinido</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
+      <c r="M30" t="n">
+        <v>11</v>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>27-03-2027 21:18:05</t>
+        </is>
+      </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>Recurrente</t>
+          <t>Domiciliado</t>
         </is>
       </c>
       <c r="P30" t="inlineStr"/>
@@ -2423,32 +2433,32 @@
         <v>29</v>
       </c>
       <c r="B31" t="n">
-        <v>98415</v>
+        <v>98471</v>
       </c>
       <c r="C31" t="n">
-        <v>354891</v>
+        <v>354849</v>
       </c>
       <c r="D31" t="n">
-        <v>97055</v>
+        <v>97013</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>JUAN PABLO  CASTILLO  MENDOZAA</t>
+          <t>ILEANA LORELEI ANGELES CALLEJA</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>CARROUSEL TJ</t>
+          <t>METEPEC</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>01-04-2026 16:25:57</t>
+          <t>02-04-2026 12:32:40</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>01-05-2026 23:59:59</t>
+          <t>02-05-2026 23:59:59</t>
         </is>
       </c>
       <c r="I31" t="n">
@@ -2467,15 +2477,17 @@
       <c r="L31" t="n">
         <v>649</v>
       </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>Indefinido</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
+      <c r="M31" t="n">
+        <v>11</v>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>28-03-2027 12:32:40</t>
+        </is>
+      </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>Recurrente</t>
+          <t>Domiciliado</t>
         </is>
       </c>
       <c r="P31" t="inlineStr"/>
@@ -2486,32 +2498,32 @@
         <v>30</v>
       </c>
       <c r="B32" t="n">
-        <v>98429</v>
+        <v>98473</v>
       </c>
       <c r="C32" t="n">
-        <v>347152</v>
+        <v>355073</v>
       </c>
       <c r="D32" t="n">
-        <v>89317</v>
+        <v>97237</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AMADO  CORDOVA  SORIA</t>
+          <t>STEPHANIE CADENA CORDOVA</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>SALTILLO VILLALTA</t>
+          <t>METEPEC</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>01-04-2026 18:36:29</t>
+          <t>02-04-2026 12:57:11</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>01-05-2026 23:59:59</t>
+          <t>02-05-2026 23:59:59</t>
         </is>
       </c>
       <c r="I32" t="n">
@@ -2535,7 +2547,7 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>27-03-2027 18:36:29</t>
+          <t>28-03-2027 12:57:11</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
@@ -2551,32 +2563,32 @@
         <v>31</v>
       </c>
       <c r="B33" t="n">
-        <v>98440</v>
+        <v>98480</v>
       </c>
       <c r="C33" t="n">
-        <v>236970</v>
+        <v>355094</v>
       </c>
       <c r="D33" t="n">
-        <v>34475</v>
+        <v>97258</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>MARCOS  EDUARDO MINJAREZ</t>
+          <t>MARIA JOSE  GARCIA  RAMOS</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>PAPALOTE TJ</t>
+          <t>INSURGENTES</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>01-04-2026 19:54:42</t>
+          <t>02-04-2026 14:00:25</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>01-05-2026 23:59:59</t>
+          <t>02-05-2026 23:59:59</t>
         </is>
       </c>
       <c r="I33" t="n">
@@ -2589,28 +2601,24 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>RENOVACIÓN</t>
+          <t>NUEVO</t>
         </is>
       </c>
       <c r="L33" t="n">
-        <v>499</v>
-      </c>
-      <c r="M33" t="n">
-        <v>11</v>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>27-03-2027 19:54:42</t>
-        </is>
-      </c>
+        <v>549</v>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="O33" t="inlineStr">
         <is>
-          <t>Domiciliado</t>
-        </is>
-      </c>
-      <c r="P33" t="n">
-        <v>81791</v>
-      </c>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr"/>
       <c r="Q33" t="inlineStr"/>
     </row>
     <row r="34">
@@ -2618,32 +2626,32 @@
         <v>32</v>
       </c>
       <c r="B34" t="n">
-        <v>98447</v>
+        <v>98482</v>
       </c>
       <c r="C34" t="n">
-        <v>147739</v>
+        <v>355131</v>
       </c>
       <c r="D34" t="n">
-        <v>45315</v>
+        <v>97295</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>CARLOS ALEJANDRO GIJON BURGOIN</t>
+          <t>YOLANDA LAURA ZUBER RASGADO</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>PASEO LA PAZ</t>
+          <t>METEPEC</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>01-04-2026 20:57:51</t>
+          <t>02-04-2026 15:59:25</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>01-05-2026 23:59:59</t>
+          <t>02-05-2026 23:59:59</t>
         </is>
       </c>
       <c r="I34" t="n">
@@ -2660,14 +2668,14 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>549</v>
+        <v>649</v>
       </c>
       <c r="M34" t="n">
         <v>11</v>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>27-03-2027 20:57:51</t>
+          <t>28-03-2027 15:59:25</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
@@ -2683,27 +2691,27 @@
         <v>33</v>
       </c>
       <c r="B35" t="n">
-        <v>96825</v>
+        <v>98505</v>
       </c>
       <c r="C35" t="n">
-        <v>131946</v>
+        <v>355223</v>
       </c>
       <c r="D35" t="n">
-        <v>29604</v>
+        <v>97387</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>CHRISTOFER ISAAC RAMIREZ MARTINEZ</t>
+          <t>NORMA SARAHI VEGA SAUCEDA</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>PAPALOTE TJ</t>
+          <t>SAN ISIDRO CUL</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>14-03-2026 11:57:25</t>
+          <t>02-04-2026 19:51:57</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2721,18 +2729,18 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>RENOVACIÓN</t>
+          <t>NUEVO</t>
         </is>
       </c>
       <c r="L35" t="n">
-        <v>399</v>
+        <v>549</v>
       </c>
       <c r="M35" t="n">
         <v>11</v>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>09-03-2027 11:57:25</t>
+          <t>28-03-2027 19:51:57</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
@@ -2740,9 +2748,7 @@
           <t>Domiciliado</t>
         </is>
       </c>
-      <c r="P35" t="n">
-        <v>21366</v>
-      </c>
+      <c r="P35" t="inlineStr"/>
       <c r="Q35" t="inlineStr"/>
     </row>
     <row r="36">
@@ -2750,32 +2756,32 @@
         <v>34</v>
       </c>
       <c r="B36" t="n">
-        <v>95681</v>
+        <v>98507</v>
       </c>
       <c r="C36" t="n">
-        <v>276079</v>
+        <v>355236</v>
       </c>
       <c r="D36" t="n">
-        <v>73581</v>
+        <v>97400</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RAMON  SANCHEZ  RODRIGUEZ</t>
+          <t>KEVEN BRAYAN MEJIA BOHORQUEZ</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>MISION ENS</t>
+          <t>VILLAS DEL REY</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>03-03-2026 5:53:34</t>
+          <t>02-04-2026 20:52:15</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>01-05-2026 23:59:59</t>
+          <t>02-05-2026 23:59:59</t>
         </is>
       </c>
       <c r="I36" t="n">
@@ -2788,11 +2794,11 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>RENOVACIÓN</t>
+          <t>NUEVO</t>
         </is>
       </c>
       <c r="L36" t="n">
-        <v>399</v>
+        <v>649</v>
       </c>
       <c r="M36" t="inlineStr">
         <is>
@@ -2805,9 +2811,7 @@
           <t>Recurrente</t>
         </is>
       </c>
-      <c r="P36" t="n">
-        <v>67204</v>
-      </c>
+      <c r="P36" t="inlineStr"/>
       <c r="Q36" t="inlineStr"/>
     </row>
     <row r="37">
@@ -2815,32 +2819,32 @@
         <v>35</v>
       </c>
       <c r="B37" t="n">
-        <v>98387</v>
+        <v>98512</v>
       </c>
       <c r="C37" t="n">
-        <v>340681</v>
+        <v>291223</v>
       </c>
       <c r="D37" t="n">
-        <v>18499</v>
+        <v>88721</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>ALEXIS BENITEZ DEGOLLADO</t>
+          <t>EVA TERESA  ARTEAGA RUEDAS</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>METEPEC</t>
+          <t>SANTA FE</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>01-04-2026 8:57:28</t>
+          <t>03-04-2026 8:32:54</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>01-05-2026 23:59:59</t>
+          <t>04-05-2026 23:59:59</t>
         </is>
       </c>
       <c r="I37" t="n">
@@ -2853,24 +2857,28 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>NUEVO</t>
+          <t>RENOVACIÓN</t>
         </is>
       </c>
       <c r="L37" t="n">
         <v>549</v>
       </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>Indefinido</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
+      <c r="M37" t="n">
+        <v>5</v>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>30-09-2026 8:32:54</t>
+        </is>
+      </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>Recurrente</t>
-        </is>
-      </c>
-      <c r="P37" t="inlineStr"/>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P37" t="n">
+        <v>65250</v>
+      </c>
       <c r="Q37" t="inlineStr"/>
     </row>
     <row r="38">
@@ -2878,27 +2886,27 @@
         <v>36</v>
       </c>
       <c r="B38" t="n">
-        <v>98389</v>
+        <v>96508</v>
       </c>
       <c r="C38" t="n">
-        <v>354805</v>
+        <v>324178</v>
       </c>
       <c r="D38" t="n">
-        <v>96969</v>
+        <v>21117</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>GUSTAVO CHAPA DAVALOS</t>
+          <t>EDNA PRICILA  HERRERA  LOPEZ</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>TLALNEPANTLA</t>
+          <t>INDEPENDENCIA</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>01-04-2026 10:29:44</t>
+          <t>10-03-2026 14:42:50</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2916,18 +2924,18 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>NUEVO</t>
+          <t>RENOVACIÓN</t>
         </is>
       </c>
       <c r="L38" t="n">
-        <v>549</v>
+        <v>399</v>
       </c>
       <c r="M38" t="n">
         <v>11</v>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>27-03-2027 10:29:44</t>
+          <t>05-03-2027 14:42:50</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
@@ -2935,7 +2943,9 @@
           <t>Domiciliado</t>
         </is>
       </c>
-      <c r="P38" t="inlineStr"/>
+      <c r="P38" t="n">
+        <v>83239</v>
+      </c>
       <c r="Q38" t="inlineStr"/>
     </row>
     <row r="39">
@@ -2943,27 +2953,27 @@
         <v>37</v>
       </c>
       <c r="B39" t="n">
-        <v>98398</v>
+        <v>98379</v>
       </c>
       <c r="C39" t="n">
-        <v>289580</v>
+        <v>353959</v>
       </c>
       <c r="D39" t="n">
-        <v>87078</v>
+        <v>96123</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>GRACIELAGLORIA GONZALEZ MARTÍNEZ</t>
+          <t>RICARDO ALEXIS CARMONA  HERNANDEZ</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>SAN LUIS</t>
+          <t>IXTAPALUCA</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>01-04-2026 12:11:54</t>
+          <t>01-04-2026 5:24:50</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2992,7 +3002,7 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>27-03-2027 12:11:54</t>
+          <t>27-03-2027 5:24:50</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
@@ -3008,27 +3018,27 @@
         <v>38</v>
       </c>
       <c r="B40" t="n">
-        <v>98421</v>
+        <v>98397</v>
       </c>
       <c r="C40" t="n">
-        <v>181296</v>
+        <v>354168</v>
       </c>
       <c r="D40" t="n">
-        <v>78803</v>
+        <v>96332</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>KAMILA  RODRIGUES DE MENEZES</t>
+          <t>JESSICA  AMADOR MARTINEZ</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>CARROUSEL TJ</t>
+          <t>PASEO 2000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>01-04-2026 17:44:14</t>
+          <t>01-04-2026 12:05:06</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -3050,19 +3060,17 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>549</v>
-      </c>
-      <c r="M40" t="n">
-        <v>11</v>
-      </c>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>27-03-2027 17:44:14</t>
-        </is>
-      </c>
+        <v>649</v>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="O40" t="inlineStr">
         <is>
-          <t>Domiciliado</t>
+          <t>Recurrente</t>
         </is>
       </c>
       <c r="P40" t="inlineStr"/>
@@ -3073,27 +3081,27 @@
         <v>39</v>
       </c>
       <c r="B41" t="n">
-        <v>98423</v>
+        <v>98404</v>
       </c>
       <c r="C41" t="n">
-        <v>354845</v>
+        <v>339346</v>
       </c>
       <c r="D41" t="n">
-        <v>97009</v>
+        <v>17164</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>MONICA PAMELA CHAPA  RODRIGUEZ</t>
+          <t>ANA RUT MARTINEZ  BALDERAS</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>STA CATARINA</t>
+          <t>SALTILLO VILLALTA</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>01-04-2026 13:28:58</t>
+          <t>01-04-2026 13:19:32</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3117,17 +3125,15 @@
       <c r="L41" t="n">
         <v>549</v>
       </c>
-      <c r="M41" t="n">
-        <v>11</v>
-      </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>27-03-2027 13:28:58</t>
-        </is>
-      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="O41" t="inlineStr">
         <is>
-          <t>Domiciliado</t>
+          <t>Recurrente</t>
         </is>
       </c>
       <c r="P41" t="inlineStr"/>
@@ -3138,27 +3144,27 @@
         <v>40</v>
       </c>
       <c r="B42" t="n">
-        <v>98430</v>
+        <v>98415</v>
       </c>
       <c r="C42" t="n">
-        <v>98152</v>
+        <v>354891</v>
       </c>
       <c r="D42" t="n">
-        <v>95909</v>
+        <v>97055</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>IRMA  CASTAÑON ROMAN</t>
+          <t>JUAN PABLO  CASTILLO  MENDOZAA</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>LOMA BONITA</t>
+          <t>CARROUSEL TJ</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>01-04-2026 18:53:00</t>
+          <t>01-04-2026 16:25:57</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3180,19 +3186,17 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>549</v>
-      </c>
-      <c r="M42" t="n">
-        <v>11</v>
-      </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>27-03-2027 18:53:00</t>
-        </is>
-      </c>
+        <v>649</v>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="O42" t="inlineStr">
         <is>
-          <t>Domiciliado</t>
+          <t>Recurrente</t>
         </is>
       </c>
       <c r="P42" t="inlineStr"/>
@@ -3203,32 +3207,32 @@
         <v>41</v>
       </c>
       <c r="B43" t="n">
-        <v>98432</v>
+        <v>98429</v>
       </c>
       <c r="C43" t="n">
-        <v>338829</v>
+        <v>347152</v>
       </c>
       <c r="D43" t="n">
-        <v>16647</v>
+        <v>89317</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>ROSA TELLEZ GUADARRAMA</t>
+          <t>AMADO  CORDOVA  SORIA</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>INSURGENTES</t>
+          <t>SALTILLO VILLALTA</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>01-04-2026 18:55:11</t>
+          <t>01-04-2026 18:36:29</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>02-07-2026 23:59:59</t>
+          <t>01-05-2026 23:59:59</t>
         </is>
       </c>
       <c r="I43" t="n">
@@ -3245,14 +3249,14 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1549</v>
+        <v>649</v>
       </c>
       <c r="M43" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>27-03-2027 18:55:11</t>
+          <t>27-03-2027 18:36:29</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
@@ -3268,32 +3272,32 @@
         <v>42</v>
       </c>
       <c r="B44" t="n">
-        <v>98455</v>
+        <v>98440</v>
       </c>
       <c r="C44" t="n">
-        <v>354979</v>
+        <v>236970</v>
       </c>
       <c r="D44" t="n">
-        <v>97143</v>
+        <v>34475</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>MARIA VIANNEY OLVERA RODRIGUEZ</t>
+          <t>MARCOS  EDUARDO MINJAREZ</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>PASEO 2000</t>
+          <t>PAPALOTE TJ</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>02-04-2026 7:52:12</t>
+          <t>01-04-2026 19:54:42</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>02-05-2026 23:59:59</t>
+          <t>01-05-2026 23:59:59</t>
         </is>
       </c>
       <c r="I44" t="n">
@@ -3306,18 +3310,18 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>NUEVO</t>
+          <t>RENOVACIÓN</t>
         </is>
       </c>
       <c r="L44" t="n">
-        <v>549</v>
+        <v>499</v>
       </c>
       <c r="M44" t="n">
         <v>11</v>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>28-03-2027 7:52:12</t>
+          <t>27-03-2027 19:54:42</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
@@ -3325,7 +3329,9 @@
           <t>Domiciliado</t>
         </is>
       </c>
-      <c r="P44" t="inlineStr"/>
+      <c r="P44" t="n">
+        <v>81791</v>
+      </c>
       <c r="Q44" t="inlineStr"/>
     </row>
     <row r="45">
@@ -3333,32 +3339,32 @@
         <v>43</v>
       </c>
       <c r="B45" t="n">
-        <v>96824</v>
+        <v>98447</v>
       </c>
       <c r="C45" t="n">
-        <v>295993</v>
+        <v>147739</v>
       </c>
       <c r="D45" t="n">
-        <v>93491</v>
+        <v>45315</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>MIGUEL ANGEL  ASTUDILLO MARIN</t>
+          <t>CARLOS ALEJANDRO GIJON BURGOIN</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>CARROUSEL TJ</t>
+          <t>PASEO LA PAZ</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>14-03-2026 11:57:18</t>
+          <t>01-04-2026 20:57:51</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>02-05-2026 23:59:59</t>
+          <t>01-05-2026 23:59:59</t>
         </is>
       </c>
       <c r="I45" t="n">
@@ -3371,18 +3377,18 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>RENOVACIÓN</t>
+          <t>NUEVO</t>
         </is>
       </c>
       <c r="L45" t="n">
-        <v>499</v>
+        <v>549</v>
       </c>
       <c r="M45" t="n">
         <v>11</v>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>09-03-2027 11:57:18</t>
+          <t>27-03-2027 20:57:51</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
@@ -3390,9 +3396,7 @@
           <t>Domiciliado</t>
         </is>
       </c>
-      <c r="P45" t="n">
-        <v>76896</v>
-      </c>
+      <c r="P45" t="inlineStr"/>
       <c r="Q45" t="inlineStr"/>
     </row>
     <row r="46">
@@ -3400,32 +3404,32 @@
         <v>44</v>
       </c>
       <c r="B46" t="n">
-        <v>98089</v>
+        <v>98472</v>
       </c>
       <c r="C46" t="n">
-        <v>354084</v>
+        <v>355075</v>
       </c>
       <c r="D46" t="n">
-        <v>96248</v>
+        <v>97239</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>ROSALBA DOMINGO PARRA</t>
+          <t>VIOLETA BANDA VALDEZ</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>TLALNEPANTLA</t>
+          <t>SALTILLO VILLALTA</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>30-03-2026 8:23:13</t>
+          <t>02-04-2026 12:45:08</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>30-04-2026 23:59:59</t>
+          <t>02-05-2026 23:59:59</t>
         </is>
       </c>
       <c r="I46" t="n">
@@ -3444,17 +3448,15 @@
       <c r="L46" t="n">
         <v>549</v>
       </c>
-      <c r="M46" t="n">
-        <v>11</v>
-      </c>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>25-03-2027 8:23:13</t>
-        </is>
-      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="O46" t="inlineStr">
         <is>
-          <t>Domiciliado</t>
+          <t>Recurrente</t>
         </is>
       </c>
       <c r="P46" t="inlineStr"/>
@@ -3465,32 +3467,32 @@
         <v>45</v>
       </c>
       <c r="B47" t="n">
-        <v>95361</v>
+        <v>98479</v>
       </c>
       <c r="C47" t="n">
-        <v>237196</v>
+        <v>340561</v>
       </c>
       <c r="D47" t="n">
-        <v>34701</v>
+        <v>18379</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>PAULINA ELIZABETH FLORES HINOJOSA</t>
+          <t>EMMANUEL AGUIRRE LOPEZ</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>SANTA FE</t>
+          <t>SALTILLO VILLALTA</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>01-03-2026 14:42:48</t>
+          <t>02-04-2026 13:47:53</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>01-05-2026 23:59:59</t>
+          <t>02-05-2026 23:59:59</t>
         </is>
       </c>
       <c r="I47" t="n">
@@ -3503,28 +3505,24 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>RENOVACIÓN</t>
+          <t>NUEVO</t>
         </is>
       </c>
       <c r="L47" t="n">
-        <v>449</v>
-      </c>
-      <c r="M47" t="n">
-        <v>5</v>
-      </c>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>28-08-2026 14:42:48</t>
-        </is>
-      </c>
+        <v>549</v>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
       <c r="O47" t="inlineStr">
         <is>
-          <t>Domiciliado</t>
-        </is>
-      </c>
-      <c r="P47" t="n">
-        <v>39905</v>
-      </c>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr"/>
       <c r="Q47" t="inlineStr"/>
     </row>
     <row r="48">
@@ -3532,34 +3530,32 @@
         <v>46</v>
       </c>
       <c r="B48" t="n">
-        <v>98384</v>
+        <v>98490</v>
       </c>
       <c r="C48" t="n">
-        <v>3040</v>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>02041</t>
-        </is>
+        <v>252992</v>
+      </c>
+      <c r="D48" t="n">
+        <v>50496</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>LISBETH MAGALLI GARCIA VERDUZCO</t>
+          <t>MARICELA ITZELL MENDOZA QUIROGA</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>SEND MXL</t>
+          <t>SEND SALTILLO</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>01-04-2026 7:50:45</t>
+          <t>02-04-2026 17:14:29</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>01-05-2026 23:59:59</t>
+          <t>02-05-2026 23:59:59</t>
         </is>
       </c>
       <c r="I48" t="n">
@@ -3583,7 +3579,7 @@
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>27-03-2027 7:50:45</t>
+          <t>28-03-2027 17:14:29</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
@@ -3599,32 +3595,32 @@
         <v>47</v>
       </c>
       <c r="B49" t="n">
-        <v>98399</v>
+        <v>98497</v>
       </c>
       <c r="C49" t="n">
-        <v>150909</v>
+        <v>355189</v>
       </c>
       <c r="D49" t="n">
-        <v>48475</v>
+        <v>97353</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>KARINA LIZBETH FLORES SILVA</t>
+          <t>VALERIA ANTONIO LOPEZ</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>SAN LUIS</t>
+          <t>SEND SALTILLO</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>01-04-2026 12:30:40</t>
+          <t>02-04-2026 18:29:08</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>01-05-2026 23:59:59</t>
+          <t>02-05-2026 23:59:59</t>
         </is>
       </c>
       <c r="I49" t="n">
@@ -3637,18 +3633,18 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>RENOVACIÓN</t>
+          <t>NUEVO</t>
         </is>
       </c>
       <c r="L49" t="n">
-        <v>499</v>
+        <v>549</v>
       </c>
       <c r="M49" t="n">
         <v>11</v>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>27-03-2027 12:30:40</t>
+          <t>28-03-2027 18:29:08</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
@@ -3656,9 +3652,7 @@
           <t>Domiciliado</t>
         </is>
       </c>
-      <c r="P49" t="n">
-        <v>83695</v>
-      </c>
+      <c r="P49" t="inlineStr"/>
       <c r="Q49" t="inlineStr"/>
     </row>
     <row r="50">
@@ -3666,32 +3660,32 @@
         <v>48</v>
       </c>
       <c r="B50" t="n">
-        <v>98403</v>
+        <v>98504</v>
       </c>
       <c r="C50" t="n">
-        <v>354838</v>
+        <v>343928</v>
       </c>
       <c r="D50" t="n">
-        <v>97002</v>
+        <v>21745</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>ROCIO GUADALUPE ROCHA PADRON</t>
+          <t>CLAUDIA LIZETH HERNANDEZ ROBLES</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>IXTAPALUCA</t>
+          <t>SANTA FE</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>01-04-2026 13:06:47</t>
+          <t>02-04-2026 19:48:38</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>01-05-2026 23:59:59</t>
+          <t>02-05-2026 23:59:59</t>
         </is>
       </c>
       <c r="I50" t="n">
@@ -3708,17 +3702,19 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>649</v>
-      </c>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>Indefinido</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr"/>
+        <v>549</v>
+      </c>
+      <c r="M50" t="n">
+        <v>11</v>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>28-03-2027 19:48:38</t>
+        </is>
+      </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>Recurrente</t>
+          <t>Domiciliado</t>
         </is>
       </c>
       <c r="P50" t="inlineStr"/>
@@ -3729,32 +3725,32 @@
         <v>49</v>
       </c>
       <c r="B51" t="n">
-        <v>98416</v>
+        <v>96825</v>
       </c>
       <c r="C51" t="n">
-        <v>354894</v>
+        <v>131946</v>
       </c>
       <c r="D51" t="n">
-        <v>97058</v>
+        <v>29604</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>ANGEL ISMAEL VENCES  OCHOA</t>
+          <t>CHRISTOFER ISAAC RAMIREZ MARTINEZ</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>SEND MXL</t>
+          <t>PAPALOTE TJ</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>01-04-2026 16:28:22</t>
+          <t>14-03-2026 11:57:25</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>01-05-2026 23:59:59</t>
+          <t>02-05-2026 23:59:59</t>
         </is>
       </c>
       <c r="I51" t="n">
@@ -3767,18 +3763,18 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>NUEVO</t>
+          <t>RENOVACIÓN</t>
         </is>
       </c>
       <c r="L51" t="n">
-        <v>549</v>
+        <v>399</v>
       </c>
       <c r="M51" t="n">
         <v>11</v>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>27-03-2027 16:28:22</t>
+          <t>09-03-2027 11:57:25</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
@@ -3786,7 +3782,9 @@
           <t>Domiciliado</t>
         </is>
       </c>
-      <c r="P51" t="inlineStr"/>
+      <c r="P51" t="n">
+        <v>21366</v>
+      </c>
       <c r="Q51" t="inlineStr"/>
     </row>
     <row r="52">
@@ -3794,27 +3792,27 @@
         <v>50</v>
       </c>
       <c r="B52" t="n">
-        <v>98433</v>
+        <v>95401</v>
       </c>
       <c r="C52" t="n">
-        <v>240369</v>
+        <v>202026</v>
       </c>
       <c r="D52" t="n">
-        <v>37874</v>
+        <v>99533</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>ALEXIS RAYMUNDO  CAMPOS  JUAREZ</t>
+          <t>GABRIELA MARIA SOTO VIELLEDENT</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>SANTA FE</t>
+          <t>VILLA VERDE</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>01-04-2026 18:56:46</t>
+          <t>02-03-2026 7:51:41</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3843,7 +3841,7 @@
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>27-03-2027 18:56:46</t>
+          <t>25-02-2027 7:51:41</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
@@ -3852,7 +3850,7 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>80953</v>
+        <v>76934</v>
       </c>
       <c r="Q52" t="inlineStr"/>
     </row>
@@ -3861,32 +3859,32 @@
         <v>51</v>
       </c>
       <c r="B53" t="n">
-        <v>98450</v>
+        <v>95416</v>
       </c>
       <c r="C53" t="n">
-        <v>36331</v>
+        <v>93948</v>
       </c>
       <c r="D53" t="n">
-        <v>34235</v>
+        <v>91707</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>YOSELYN MICHEL SALAZAR  FIGUEROA</t>
+          <t>ANA RAFAELA GALVAN LOPEZ</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>SANTA FE</t>
+          <t>SEND SALTILLO</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>01-04-2026 21:41:21</t>
+          <t>02-03-2026 9:03:29</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>01-05-2026 23:59:59</t>
+          <t>02-05-2026 23:59:59</t>
         </is>
       </c>
       <c r="I53" t="n">
@@ -3899,24 +3897,28 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>NUEVO</t>
+          <t>RENOVACIÓN</t>
         </is>
       </c>
       <c r="L53" t="n">
-        <v>649</v>
-      </c>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>Indefinido</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr"/>
+        <v>499</v>
+      </c>
+      <c r="M53" t="n">
+        <v>11</v>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>25-02-2027 9:03:29</t>
+        </is>
+      </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>Recurrente</t>
-        </is>
-      </c>
-      <c r="P53" t="inlineStr"/>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P53" t="n">
+        <v>95415</v>
+      </c>
       <c r="Q53" t="inlineStr"/>
     </row>
     <row r="54">
@@ -3924,27 +3926,27 @@
         <v>52</v>
       </c>
       <c r="B54" t="n">
-        <v>98452</v>
+        <v>95451</v>
       </c>
       <c r="C54" t="n">
-        <v>244777</v>
+        <v>339837</v>
       </c>
       <c r="D54" t="n">
-        <v>42282</v>
+        <v>17655</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>NANCY  HERNÁNDEZ GONZALEZ</t>
+          <t>CRISTIAN ALEXIS RUIZ AGUILAR</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>SEND SALTILLO</t>
+          <t>INSURGENTES</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>02-04-2026 6:26:04</t>
+          <t>02-03-2026 11:39:41</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3962,18 +3964,18 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>NUEVO</t>
+          <t>RENOVACIÓN</t>
         </is>
       </c>
       <c r="L54" t="n">
-        <v>999</v>
+        <v>649</v>
       </c>
       <c r="M54" t="n">
         <v>11</v>
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>28-03-2027 6:26:04</t>
+          <t>25-02-2027 11:39:41</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
@@ -3981,7 +3983,9 @@
           <t>Domiciliado</t>
         </is>
       </c>
-      <c r="P54" t="inlineStr"/>
+      <c r="P54" t="n">
+        <v>91337</v>
+      </c>
       <c r="Q54" t="inlineStr"/>
     </row>
     <row r="55">
@@ -3989,34 +3993,32 @@
         <v>53</v>
       </c>
       <c r="B55" t="n">
-        <v>97112</v>
+        <v>95669</v>
       </c>
       <c r="C55" t="n">
-        <v>307274</v>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>04773</t>
-        </is>
+        <v>165787</v>
+      </c>
+      <c r="D55" t="n">
+        <v>63320</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>ESMERALDA GUADALUPE RANGEL ESQUIVEL</t>
+          <t>ALISSON ABRIL ROMERO LARA</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>SEND SALTILLO</t>
+          <t>TEC MXL</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>17-03-2026 18:17:30</t>
+          <t>02-03-2026 21:15:34</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>02-05-2026 23:59:59</t>
+          <t>30-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="I55" t="n">
@@ -4040,7 +4042,7 @@
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>12-03-2027 18:17:30</t>
+          <t>25-02-2027 21:15:34</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
@@ -4049,7 +4051,7 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>87410</v>
+        <v>70751</v>
       </c>
       <c r="Q55" t="inlineStr"/>
     </row>
@@ -4058,32 +4060,32 @@
         <v>54</v>
       </c>
       <c r="B56" t="n">
-        <v>97214</v>
+        <v>98391</v>
       </c>
       <c r="C56" t="n">
-        <v>227607</v>
+        <v>354812</v>
       </c>
       <c r="D56" t="n">
-        <v>25112</v>
+        <v>96976</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>NUBIA LORENA BUCIO CASTILLO</t>
+          <t>ALAN  ESCOBEDO  BAEZ</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>PAPALOTE TJ</t>
+          <t>INSURGENTES</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>18-03-2026 16:31:25</t>
+          <t>01-04-2026 10:47:30</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>02-05-2026 23:59:59</t>
+          <t>01-05-2026 23:59:59</t>
         </is>
       </c>
       <c r="I56" t="n">
@@ -4096,28 +4098,24 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>RENOVACIÓN</t>
+          <t>NUEVO</t>
         </is>
       </c>
       <c r="L56" t="n">
-        <v>449</v>
-      </c>
-      <c r="M56" t="n">
-        <v>5</v>
-      </c>
-      <c r="N56" t="inlineStr">
-        <is>
-          <t>14-09-2026 16:31:25</t>
-        </is>
-      </c>
+        <v>549</v>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr"/>
       <c r="O56" t="inlineStr">
         <is>
-          <t>Domiciliado</t>
-        </is>
-      </c>
-      <c r="P56" t="n">
-        <v>50707</v>
-      </c>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr"/>
       <c r="Q56" t="inlineStr"/>
     </row>
     <row r="57">
@@ -4125,32 +4123,32 @@
         <v>55</v>
       </c>
       <c r="B57" t="n">
-        <v>97965</v>
+        <v>98392</v>
       </c>
       <c r="C57" t="n">
-        <v>70411</v>
+        <v>354811</v>
       </c>
       <c r="D57" t="n">
-        <v>68233</v>
+        <v>96975</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>CYNTHIA IVETH GARCIA  MORENO</t>
+          <t>XIMENA PAOLA SANCHEZ RAMIREZ</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>SEND MXL</t>
+          <t>TLALNEPANTLA</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>27-03-2026 11:58:41</t>
+          <t>01-04-2026 10:48:46</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>01-05-2026 23:59:59</t>
+          <t>01-07-2026 23:59:59</t>
         </is>
       </c>
       <c r="I57" t="n">
@@ -4163,28 +4161,24 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>RENOVACIÓN</t>
+          <t>NUEVO</t>
         </is>
       </c>
       <c r="L57" t="n">
-        <v>449</v>
-      </c>
-      <c r="M57" t="n">
-        <v>11</v>
-      </c>
-      <c r="N57" t="inlineStr">
-        <is>
-          <t>22-03-2027 11:58:41</t>
-        </is>
-      </c>
+        <v>1449</v>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
       <c r="O57" t="inlineStr">
         <is>
-          <t>Domiciliado</t>
-        </is>
-      </c>
-      <c r="P57" t="n">
-        <v>31636</v>
-      </c>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr"/>
       <c r="Q57" t="inlineStr"/>
     </row>
     <row r="58">
@@ -4192,27 +4186,27 @@
         <v>56</v>
       </c>
       <c r="B58" t="n">
-        <v>98406</v>
+        <v>98409</v>
       </c>
       <c r="C58" t="n">
-        <v>354852</v>
+        <v>164157</v>
       </c>
       <c r="D58" t="n">
-        <v>97016</v>
+        <v>61690</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>ROBERTO EMILIANO BAEZ  GONZALEZ</t>
+          <t>BERTHA ALICIA GARCIA HERNANDEZ</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>INSURGENTES</t>
+          <t>SEND MXL</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>01-04-2026 14:27:45</t>
+          <t>01-04-2026 15:01:11</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -4230,18 +4224,18 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>NUEVO</t>
+          <t>RENOVACIÓN</t>
         </is>
       </c>
       <c r="L58" t="n">
-        <v>649</v>
+        <v>499</v>
       </c>
       <c r="M58" t="n">
         <v>11</v>
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>27-03-2027 14:27:45</t>
+          <t>27-03-2027 15:01:11</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
@@ -4249,7 +4243,9 @@
           <t>Domiciliado</t>
         </is>
       </c>
-      <c r="P58" t="inlineStr"/>
+      <c r="P58" t="n">
+        <v>62356</v>
+      </c>
       <c r="Q58" t="inlineStr"/>
     </row>
     <row r="59">
@@ -4257,27 +4253,27 @@
         <v>57</v>
       </c>
       <c r="B59" t="n">
-        <v>98413</v>
+        <v>98410</v>
       </c>
       <c r="C59" t="n">
-        <v>253549</v>
+        <v>354869</v>
       </c>
       <c r="D59" t="n">
-        <v>51053</v>
+        <v>97033</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>ROSA MARINA LOPEZ ESPINOSA</t>
+          <t>JULIO ARIZMENDI MORENO</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>CARROUSEL TJ</t>
+          <t>METEPEC</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>01-04-2026 15:44:33</t>
+          <t>01-04-2026 15:08:38</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4295,28 +4291,24 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>RENOVACIÓN</t>
+          <t>NUEVO</t>
         </is>
       </c>
       <c r="L59" t="n">
-        <v>499</v>
-      </c>
-      <c r="M59" t="n">
-        <v>11</v>
-      </c>
-      <c r="N59" t="inlineStr">
-        <is>
-          <t>27-03-2027 15:44:33</t>
-        </is>
-      </c>
+        <v>549</v>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
       <c r="O59" t="inlineStr">
         <is>
-          <t>Domiciliado</t>
-        </is>
-      </c>
-      <c r="P59" t="n">
-        <v>38535</v>
-      </c>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr"/>
       <c r="Q59" t="inlineStr"/>
     </row>
     <row r="60">
@@ -4324,27 +4316,27 @@
         <v>58</v>
       </c>
       <c r="B60" t="n">
-        <v>98431</v>
+        <v>98427</v>
       </c>
       <c r="C60" t="n">
-        <v>133972</v>
+        <v>352177</v>
       </c>
       <c r="D60" t="n">
-        <v>31622</v>
+        <v>94341</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>EDGAR ALI JIMENEZ LOPEZ</t>
+          <t>JUANA FRIAS GARCIA</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>PASEO 2000</t>
+          <t>CARROUSEL TJ</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>01-04-2026 18:54:53</t>
+          <t>01-04-2026 18:05:19</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4362,28 +4354,24 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>RENOVACIÓN</t>
+          <t>NUEVO</t>
         </is>
       </c>
       <c r="L60" t="n">
-        <v>499</v>
-      </c>
-      <c r="M60" t="n">
-        <v>11</v>
-      </c>
-      <c r="N60" t="inlineStr">
-        <is>
-          <t>27-03-2027 18:54:53</t>
-        </is>
-      </c>
+        <v>649</v>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr"/>
       <c r="O60" t="inlineStr">
         <is>
-          <t>Domiciliado</t>
-        </is>
-      </c>
-      <c r="P60" t="n">
-        <v>21825</v>
-      </c>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr"/>
       <c r="Q60" t="inlineStr"/>
     </row>
     <row r="61">
@@ -4391,32 +4379,32 @@
         <v>59</v>
       </c>
       <c r="B61" t="n">
-        <v>98438</v>
+        <v>98428</v>
       </c>
       <c r="C61" t="n">
-        <v>340018</v>
+        <v>354917</v>
       </c>
       <c r="D61" t="n">
-        <v>17836</v>
+        <v>97081</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>ANDRES AVILA ROJAS</t>
+          <t>MARLO ANDRE OCAMPO GARCIA</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>MISION ENS</t>
+          <t>INSURGENTES</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>01-04-2026 19:36:58</t>
+          <t>01-04-2026 18:06:23</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>02-05-2026 23:59:59</t>
+          <t>01-05-2026 23:59:59</t>
         </is>
       </c>
       <c r="I61" t="n">
@@ -4429,18 +4417,18 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>RENOVACIÓN</t>
+          <t>NUEVO</t>
         </is>
       </c>
       <c r="L61" t="n">
-        <v>549</v>
+        <v>649</v>
       </c>
       <c r="M61" t="n">
         <v>11</v>
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>27-03-2027 19:36:58</t>
+          <t>27-03-2027 18:06:23</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
@@ -4448,9 +4436,7 @@
           <t>Domiciliado</t>
         </is>
       </c>
-      <c r="P61" t="n">
-        <v>91348</v>
-      </c>
+      <c r="P61" t="inlineStr"/>
       <c r="Q61" t="inlineStr"/>
     </row>
     <row r="62">
@@ -4458,32 +4444,32 @@
         <v>60</v>
       </c>
       <c r="B62" t="n">
-        <v>98456</v>
+        <v>98441</v>
       </c>
       <c r="C62" t="n">
-        <v>354538</v>
+        <v>151482</v>
       </c>
       <c r="D62" t="n">
-        <v>96702</v>
+        <v>49047</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>MARIA NALLELY ROMAN ESPINOZA</t>
+          <t>ALAN HERIBERTO ESPINOZA ALIRE</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>VILLA VERDE</t>
+          <t>INDEPENDENCIA</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>02-04-2026 8:39:43</t>
+          <t>01-04-2026 20:05:11</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>02-05-2026 23:59:59</t>
+          <t>01-05-2026 23:59:59</t>
         </is>
       </c>
       <c r="I62" t="n">
@@ -4500,19 +4486,17 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>549</v>
-      </c>
-      <c r="M62" t="n">
-        <v>11</v>
-      </c>
-      <c r="N62" t="inlineStr">
-        <is>
-          <t>28-03-2027 8:39:43</t>
-        </is>
-      </c>
+        <v>649</v>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr"/>
       <c r="O62" t="inlineStr">
         <is>
-          <t>Domiciliado</t>
+          <t>Recurrente</t>
         </is>
       </c>
       <c r="P62" t="inlineStr"/>
@@ -4523,32 +4507,32 @@
         <v>61</v>
       </c>
       <c r="B63" t="n">
-        <v>95816</v>
+        <v>98442</v>
       </c>
       <c r="C63" t="n">
-        <v>26874</v>
+        <v>354954</v>
       </c>
       <c r="D63" t="n">
-        <v>24813</v>
+        <v>97118</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>JESUS  NUÑEZ CHICUATE</t>
+          <t>MARTA  CRUZ ALVARADO</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>TEC MXL</t>
+          <t>CARROUSEL TJ</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>03-03-2026 18:01:45</t>
+          <t>01-04-2026 20:24:50</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>02-05-2026 23:59:59</t>
+          <t>01-05-2026 23:59:59</t>
         </is>
       </c>
       <c r="I63" t="n">
@@ -4561,28 +4545,24 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>RENOVACIÓN</t>
+          <t>NUEVO</t>
         </is>
       </c>
       <c r="L63" t="n">
-        <v>449</v>
-      </c>
-      <c r="M63" t="n">
-        <v>5</v>
-      </c>
-      <c r="N63" t="inlineStr">
-        <is>
-          <t>30-08-2026 18:01:45</t>
-        </is>
-      </c>
+        <v>649</v>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr"/>
       <c r="O63" t="inlineStr">
         <is>
-          <t>Domiciliado</t>
-        </is>
-      </c>
-      <c r="P63" t="n">
-        <v>51181</v>
-      </c>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr"/>
       <c r="Q63" t="inlineStr"/>
     </row>
     <row r="64">
@@ -4590,27 +4570,27 @@
         <v>62</v>
       </c>
       <c r="B64" t="n">
-        <v>97995</v>
+        <v>98459</v>
       </c>
       <c r="C64" t="n">
-        <v>295894</v>
+        <v>355000</v>
       </c>
       <c r="D64" t="n">
-        <v>93392</v>
+        <v>97164</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AITZA MIRENA GUTIERREZ  BLANCARTE</t>
+          <t>RAFAEL  DELA VARA  VALDEZ</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>VILLAS DEL REY</t>
+          <t>TEC MXL</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>27-03-2026 16:22:41</t>
+          <t>02-04-2026 9:06:49</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -4628,18 +4608,18 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>RENOVACIÓN</t>
+          <t>NUEVO</t>
         </is>
       </c>
       <c r="L64" t="n">
-        <v>499</v>
+        <v>549</v>
       </c>
       <c r="M64" t="n">
         <v>11</v>
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>22-03-2027 16:22:41</t>
+          <t>28-03-2027 9:06:49</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
@@ -4647,9 +4627,7 @@
           <t>Domiciliado</t>
         </is>
       </c>
-      <c r="P64" t="n">
-        <v>94569</v>
-      </c>
+      <c r="P64" t="inlineStr"/>
       <c r="Q64" t="inlineStr"/>
     </row>
     <row r="65">
@@ -4657,32 +4635,32 @@
         <v>63</v>
       </c>
       <c r="B65" t="n">
-        <v>98378</v>
+        <v>98460</v>
       </c>
       <c r="C65" t="n">
-        <v>234373</v>
+        <v>355009</v>
       </c>
       <c r="D65" t="n">
-        <v>31878</v>
+        <v>97173</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>ANDREA  ESTAÑOL CUESTA</t>
+          <t>FATIMA  LOPEZ  MACHADO</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>SEND MXL</t>
+          <t>CARROUSEL TJ</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>01-04-2026 5:10:38</t>
+          <t>02-04-2026 9:20:58</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>01-05-2026 23:59:59</t>
+          <t>02-05-2026 23:59:59</t>
         </is>
       </c>
       <c r="I65" t="n">
@@ -4706,7 +4684,7 @@
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>27-03-2027 5:10:38</t>
+          <t>28-03-2027 9:20:58</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
@@ -4722,32 +4700,32 @@
         <v>64</v>
       </c>
       <c r="B66" t="n">
-        <v>98380</v>
+        <v>98478</v>
       </c>
       <c r="C66" t="n">
-        <v>218531</v>
+        <v>140360</v>
       </c>
       <c r="D66" t="n">
-        <v>16039</v>
+        <v>37987</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>MARIA EUUGENIA CUESTA GUERRERRO</t>
+          <t>ALONDRA MITCHELL PEREZ  RAZO</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>SEND MXL</t>
+          <t>VILLA VERDE</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>01-04-2026 5:54:51</t>
+          <t>02-04-2026 13:38:22</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>01-05-2026 23:59:59</t>
+          <t>03-05-2026 23:59:59</t>
         </is>
       </c>
       <c r="I66" t="n">
@@ -4771,7 +4749,7 @@
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>27-03-2027 5:54:51</t>
+          <t>28-03-2027 13:38:22</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
@@ -4780,7 +4758,7 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>16036</v>
+        <v>81216</v>
       </c>
       <c r="Q66" t="inlineStr"/>
     </row>
@@ -4789,34 +4767,32 @@
         <v>65</v>
       </c>
       <c r="B67" t="n">
-        <v>98382</v>
+        <v>98492</v>
       </c>
       <c r="C67" t="n">
-        <v>10048</v>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>08977</t>
-        </is>
+        <v>355159</v>
+      </c>
+      <c r="D67" t="n">
+        <v>97323</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>JORGE HUMBERTO ROBLES BURGUEÑO</t>
+          <t>VALERIA FLORES GANDUR</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>PABELLON RTO</t>
+          <t>INSURGENTES</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>01-04-2026 6:55:06</t>
+          <t>02-04-2026 17:31:38</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>01-05-2026 23:59:59</t>
+          <t>02-05-2026 23:59:59</t>
         </is>
       </c>
       <c r="I67" t="n">
@@ -4833,19 +4809,17 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>549</v>
-      </c>
-      <c r="M67" t="n">
-        <v>11</v>
-      </c>
-      <c r="N67" t="inlineStr">
-        <is>
-          <t>27-03-2027 6:55:06</t>
-        </is>
-      </c>
+        <v>799</v>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr"/>
       <c r="O67" t="inlineStr">
         <is>
-          <t>Domiciliado</t>
+          <t>Recurrente</t>
         </is>
       </c>
       <c r="P67" t="inlineStr"/>
@@ -4856,32 +4830,34 @@
         <v>66</v>
       </c>
       <c r="B68" t="n">
-        <v>98405</v>
+        <v>98509</v>
       </c>
       <c r="C68" t="n">
-        <v>71326</v>
-      </c>
-      <c r="D68" t="n">
-        <v>69147</v>
+        <v>2053</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>01054</t>
+        </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>LEONEL  NUÑEZ  MENDOZA</t>
+          <t>CLARISA LORENA VALERIO  LOPEZ</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>SAN LUIS</t>
+          <t>SEND MXL</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>01-04-2026 14:07:16</t>
+          <t>03-04-2026 7:45:54</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>01-05-2026 23:59:59</t>
+          <t>03-05-2026 23:59:59</t>
         </is>
       </c>
       <c r="I68" t="n">
@@ -4894,28 +4870,24 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>RENOVACIÓN</t>
+          <t>NUEVO</t>
         </is>
       </c>
       <c r="L68" t="n">
-        <v>499</v>
-      </c>
-      <c r="M68" t="n">
-        <v>11</v>
-      </c>
-      <c r="N68" t="inlineStr">
-        <is>
-          <t>27-03-2027 14:07:16</t>
-        </is>
-      </c>
+        <v>649</v>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr"/>
       <c r="O68" t="inlineStr">
         <is>
-          <t>Domiciliado</t>
-        </is>
-      </c>
-      <c r="P68" t="n">
-        <v>19720</v>
-      </c>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr"/>
       <c r="Q68" t="inlineStr"/>
     </row>
     <row r="69">
@@ -4923,17 +4895,19 @@
         <v>67</v>
       </c>
       <c r="B69" t="n">
-        <v>98407</v>
+        <v>97974</v>
       </c>
       <c r="C69" t="n">
-        <v>354856</v>
-      </c>
-      <c r="D69" t="n">
-        <v>97020</v>
+        <v>312043</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>09542</t>
+        </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>GUILLERMINA  REYES  R</t>
+          <t>YULISSA KARYME GUITRON OSORIO</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -4943,7 +4917,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>01-04-2026 14:28:19</t>
+          <t>27-03-2026 13:38:44</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -4961,26 +4935,26 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>NUEVO</t>
+          <t>RENOVACIÓN</t>
         </is>
       </c>
       <c r="L69" t="n">
-        <v>549</v>
-      </c>
-      <c r="M69" t="n">
-        <v>11</v>
-      </c>
-      <c r="N69" t="inlineStr">
-        <is>
-          <t>27-03-2027 14:28:19</t>
-        </is>
-      </c>
+        <v>599</v>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr"/>
       <c r="O69" t="inlineStr">
         <is>
-          <t>Domiciliado</t>
-        </is>
-      </c>
-      <c r="P69" t="inlineStr"/>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P69" t="n">
+        <v>92547</v>
+      </c>
       <c r="Q69" t="inlineStr"/>
     </row>
     <row r="70">
@@ -4988,27 +4962,27 @@
         <v>68</v>
       </c>
       <c r="B70" t="n">
-        <v>98412</v>
+        <v>98387</v>
       </c>
       <c r="C70" t="n">
-        <v>354877</v>
+        <v>340681</v>
       </c>
       <c r="D70" t="n">
-        <v>97041</v>
+        <v>18499</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>JAQUELINE TORRES MARTINEZ</t>
+          <t>ALEXIS BENITEZ DEGOLLADO</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>SEND MXL</t>
+          <t>METEPEC</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>01-04-2026 15:27:35</t>
+          <t>01-04-2026 8:57:28</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -5030,7 +5004,7 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>649</v>
+        <v>549</v>
       </c>
       <c r="M70" t="inlineStr">
         <is>
@@ -5051,27 +5025,27 @@
         <v>69</v>
       </c>
       <c r="B71" t="n">
-        <v>98414</v>
+        <v>98389</v>
       </c>
       <c r="C71" t="n">
-        <v>351183</v>
+        <v>354805</v>
       </c>
       <c r="D71" t="n">
-        <v>93347</v>
+        <v>96969</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>KENNETH ROSEMBERG VILLA FRANCO</t>
+          <t>GUSTAVO CHAPA DAVALOS</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>IXTAPALUCA</t>
+          <t>TLALNEPANTLA</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>01-04-2026 15:47:30</t>
+          <t>01-04-2026 10:29:44</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -5100,7 +5074,7 @@
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>27-03-2027 15:47:30</t>
+          <t>27-03-2027 10:29:44</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
@@ -5116,27 +5090,27 @@
         <v>70</v>
       </c>
       <c r="B72" t="n">
-        <v>98437</v>
+        <v>98398</v>
       </c>
       <c r="C72" t="n">
-        <v>354929</v>
+        <v>289580</v>
       </c>
       <c r="D72" t="n">
-        <v>97093</v>
+        <v>87078</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>JOSE EDUARDO  CUEN  RENTERIA</t>
+          <t>GRACIELAGLORIA GONZALEZ MARTÍNEZ</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>SEND MXL</t>
+          <t>SAN LUIS</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>01-04-2026 19:09:05</t>
+          <t>01-04-2026 12:11:54</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -5158,17 +5132,19 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>649</v>
-      </c>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>Indefinido</t>
-        </is>
-      </c>
-      <c r="N72" t="inlineStr"/>
+        <v>549</v>
+      </c>
+      <c r="M72" t="n">
+        <v>11</v>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>27-03-2027 12:11:54</t>
+        </is>
+      </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>Recurrente</t>
+          <t>Domiciliado</t>
         </is>
       </c>
       <c r="P72" t="inlineStr"/>
@@ -5179,27 +5155,27 @@
         <v>71</v>
       </c>
       <c r="B73" t="n">
-        <v>98448</v>
+        <v>98421</v>
       </c>
       <c r="C73" t="n">
-        <v>348011</v>
+        <v>181296</v>
       </c>
       <c r="D73" t="n">
-        <v>90176</v>
+        <v>78803</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>LARISSA IVETTE LOZA  CUETO</t>
+          <t>KAMILA  RODRIGUES DE MENEZES</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>VILLA VERDE</t>
+          <t>CARROUSEL TJ</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>01-04-2026 21:18:05</t>
+          <t>01-04-2026 17:44:14</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -5228,7 +5204,7 @@
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>27-03-2027 21:18:05</t>
+          <t>27-03-2027 17:44:14</t>
         </is>
       </c>
       <c r="O73" t="inlineStr">
@@ -5244,32 +5220,32 @@
         <v>72</v>
       </c>
       <c r="B74" t="n">
-        <v>95699</v>
+        <v>98423</v>
       </c>
       <c r="C74" t="n">
-        <v>250359</v>
+        <v>354845</v>
       </c>
       <c r="D74" t="n">
-        <v>47863</v>
+        <v>97009</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>LENE  RODRIGUEZ CORRALES</t>
+          <t>MONICA PAMELA CHAPA  RODRIGUEZ</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>SAN LUIS</t>
+          <t>STA CATARINA</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>03-03-2026 8:11:05</t>
+          <t>01-04-2026 13:28:58</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>02-05-2026 23:59:59</t>
+          <t>01-05-2026 23:59:59</t>
         </is>
       </c>
       <c r="I74" t="n">
@@ -5282,18 +5258,18 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>RENOVACIÓN</t>
+          <t>NUEVO</t>
         </is>
       </c>
       <c r="L74" t="n">
         <v>549</v>
       </c>
       <c r="M74" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>30-08-2026 8:11:05</t>
+          <t>27-03-2027 13:28:58</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
@@ -5301,9 +5277,7 @@
           <t>Domiciliado</t>
         </is>
       </c>
-      <c r="P74" t="n">
-        <v>76998</v>
-      </c>
+      <c r="P74" t="inlineStr"/>
       <c r="Q74" t="inlineStr"/>
     </row>
     <row r="75">
@@ -5311,27 +5285,27 @@
         <v>73</v>
       </c>
       <c r="B75" t="n">
-        <v>96508</v>
+        <v>98430</v>
       </c>
       <c r="C75" t="n">
-        <v>324178</v>
+        <v>98152</v>
       </c>
       <c r="D75" t="n">
-        <v>21117</v>
+        <v>95909</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>EDNA PRICILA  HERRERA  LOPEZ</t>
+          <t>IRMA  CASTAÑON ROMAN</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>INDEPENDENCIA</t>
+          <t>LOMA BONITA</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>10-03-2026 14:42:50</t>
+          <t>01-04-2026 18:53:00</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -5349,18 +5323,18 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>RENOVACIÓN</t>
+          <t>NUEVO</t>
         </is>
       </c>
       <c r="L75" t="n">
-        <v>399</v>
+        <v>549</v>
       </c>
       <c r="M75" t="n">
         <v>11</v>
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>05-03-2027 14:42:50</t>
+          <t>27-03-2027 18:53:00</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
@@ -5368,9 +5342,7 @@
           <t>Domiciliado</t>
         </is>
       </c>
-      <c r="P75" t="n">
-        <v>83239</v>
-      </c>
+      <c r="P75" t="inlineStr"/>
       <c r="Q75" t="inlineStr"/>
     </row>
     <row r="76">
@@ -5378,32 +5350,32 @@
         <v>74</v>
       </c>
       <c r="B76" t="n">
-        <v>98376</v>
+        <v>98432</v>
       </c>
       <c r="C76" t="n">
-        <v>330015</v>
+        <v>338829</v>
       </c>
       <c r="D76" t="n">
-        <v>15069</v>
+        <v>16647</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>NOEL GALLEGOS VARELA</t>
+          <t>ROSA TELLEZ GUADARRAMA</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>SEND CHIH</t>
+          <t>INSURGENTES</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>01-04-2026 5:07:31</t>
+          <t>01-04-2026 18:55:11</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>01-07-2026 23:59:59</t>
+          <t>02-07-2026 23:59:59</t>
         </is>
       </c>
       <c r="I76" t="n">
@@ -5420,17 +5392,19 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>1449</v>
-      </c>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>Indefinido</t>
-        </is>
-      </c>
-      <c r="N76" t="inlineStr"/>
+        <v>1549</v>
+      </c>
+      <c r="M76" t="n">
+        <v>9</v>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>27-03-2027 18:55:11</t>
+        </is>
+      </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>Recurrente</t>
+          <t>Domiciliado</t>
         </is>
       </c>
       <c r="P76" t="inlineStr"/>
@@ -5441,32 +5415,32 @@
         <v>75</v>
       </c>
       <c r="B77" t="n">
-        <v>98393</v>
+        <v>98455</v>
       </c>
       <c r="C77" t="n">
-        <v>354818</v>
+        <v>354979</v>
       </c>
       <c r="D77" t="n">
-        <v>96982</v>
+        <v>97143</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>ISIDRO  MENDEZ  JARAMILLO</t>
+          <t>MARIA VIANNEY OLVERA RODRIGUEZ</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>SALTILLO VILLALTA</t>
+          <t>PASEO 2000</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>01-04-2026 10:58:42</t>
+          <t>02-04-2026 7:52:12</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>01-05-2026 23:59:59</t>
+          <t>02-05-2026 23:59:59</t>
         </is>
       </c>
       <c r="I77" t="n">
@@ -5483,17 +5457,19 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>799</v>
-      </c>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>Indefinido</t>
-        </is>
-      </c>
-      <c r="N77" t="inlineStr"/>
+        <v>549</v>
+      </c>
+      <c r="M77" t="n">
+        <v>11</v>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>28-03-2027 7:52:12</t>
+        </is>
+      </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>Recurrente</t>
+          <t>Domiciliado</t>
         </is>
       </c>
       <c r="P77" t="inlineStr"/>
@@ -5504,17 +5480,17 @@
         <v>76</v>
       </c>
       <c r="B78" t="n">
-        <v>98411</v>
+        <v>98464</v>
       </c>
       <c r="C78" t="n">
-        <v>354867</v>
+        <v>354913</v>
       </c>
       <c r="D78" t="n">
-        <v>97031</v>
+        <v>97077</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>SEBASTIAN IBAÑEZ RAMIREZ</t>
+          <t>KARINA SANCHEZ DIAZ</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -5524,12 +5500,12 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>01-04-2026 15:15:54</t>
+          <t>02-04-2026 10:53:54</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>01-05-2026 23:59:59</t>
+          <t>02-05-2026 23:59:59</t>
         </is>
       </c>
       <c r="I78" t="n">
@@ -5546,19 +5522,17 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>649</v>
-      </c>
-      <c r="M78" t="n">
-        <v>11</v>
-      </c>
-      <c r="N78" t="inlineStr">
-        <is>
-          <t>27-03-2027 15:15:54</t>
-        </is>
-      </c>
+        <v>799</v>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr"/>
       <c r="O78" t="inlineStr">
         <is>
-          <t>Domiciliado</t>
+          <t>Recurrente</t>
         </is>
       </c>
       <c r="P78" t="inlineStr"/>
@@ -5569,32 +5543,32 @@
         <v>77</v>
       </c>
       <c r="B79" t="n">
-        <v>98425</v>
+        <v>98487</v>
       </c>
       <c r="C79" t="n">
-        <v>352652</v>
+        <v>85428</v>
       </c>
       <c r="D79" t="n">
-        <v>94816</v>
+        <v>83211</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>MARCO VEGA DUARTE</t>
+          <t>ROBERTO  LOPEZ  ROSALES</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>TEC MXL</t>
+          <t>STA CATARINA</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>01-04-2026 18:03:42</t>
+          <t>02-04-2026 16:48:55</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>01-05-2026 23:59:59</t>
+          <t>02-05-2026 23:59:59</t>
         </is>
       </c>
       <c r="I79" t="n">
@@ -5618,7 +5592,7 @@
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>27-03-2027 18:03:42</t>
+          <t>28-03-2027 16:48:55</t>
         </is>
       </c>
       <c r="O79" t="inlineStr">
@@ -5634,32 +5608,32 @@
         <v>78</v>
       </c>
       <c r="B80" t="n">
-        <v>98426</v>
+        <v>98489</v>
       </c>
       <c r="C80" t="n">
-        <v>183909</v>
+        <v>343045</v>
       </c>
       <c r="D80" t="n">
-        <v>81416</v>
+        <v>20862</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>FELIPE ARTURO HERNANDEZ VALDEZ</t>
+          <t>LUISA MARÍA MALDONADO AMARO</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>CARROUSEL TJ</t>
+          <t>TLALNEPANTLA</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>01-04-2026 18:03:51</t>
+          <t>02-04-2026 16:57:12</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>01-05-2026 23:59:59</t>
+          <t>02-05-2026 23:59:59</t>
         </is>
       </c>
       <c r="I80" t="n">
@@ -5672,11 +5646,11 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>RENOVACIÓN</t>
+          <t>NUEVO</t>
         </is>
       </c>
       <c r="L80" t="n">
-        <v>399</v>
+        <v>649</v>
       </c>
       <c r="M80" t="inlineStr">
         <is>
@@ -5689,9 +5663,7 @@
           <t>Recurrente</t>
         </is>
       </c>
-      <c r="P80" t="n">
-        <v>43588</v>
-      </c>
+      <c r="P80" t="inlineStr"/>
       <c r="Q80" t="inlineStr"/>
     </row>
     <row r="81">
@@ -5699,32 +5671,32 @@
         <v>79</v>
       </c>
       <c r="B81" t="n">
-        <v>98443</v>
+        <v>98496</v>
       </c>
       <c r="C81" t="n">
-        <v>257769</v>
+        <v>352673</v>
       </c>
       <c r="D81" t="n">
-        <v>55273</v>
+        <v>94837</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>JUANA ISABEL DOMINGUEZ MATA</t>
+          <t>CHRISTIAN  VALDEZ  ORTEGA</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>LOMA BONITA</t>
+          <t>METEPEC</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>01-04-2026 20:24:55</t>
+          <t>02-04-2026 18:16:33</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>01-05-2026 23:59:59</t>
+          <t>02-05-2026 23:59:59</t>
         </is>
       </c>
       <c r="I81" t="n">
@@ -5743,17 +5715,15 @@
       <c r="L81" t="n">
         <v>549</v>
       </c>
-      <c r="M81" t="n">
-        <v>11</v>
-      </c>
-      <c r="N81" t="inlineStr">
-        <is>
-          <t>27-03-2027 20:24:55</t>
-        </is>
-      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr"/>
       <c r="O81" t="inlineStr">
         <is>
-          <t>Domiciliado</t>
+          <t>Recurrente</t>
         </is>
       </c>
       <c r="P81" t="inlineStr"/>
@@ -5764,32 +5734,32 @@
         <v>80</v>
       </c>
       <c r="B82" t="n">
-        <v>98444</v>
+        <v>98498</v>
       </c>
       <c r="C82" t="n">
-        <v>280981</v>
+        <v>355061</v>
       </c>
       <c r="D82" t="n">
-        <v>78482</v>
+        <v>97225</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>JOSE DANIEL  CASTRO DE LOS REYES</t>
+          <t>ADRIÁN ALEJANDRO DE LEÓN  VIGIL</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>SAN LUIS</t>
+          <t>STA CATARINA</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>01-04-2026 20:33:23</t>
+          <t>02-04-2026 12:07:04</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>01-05-2026 23:59:59</t>
+          <t>02-05-2026 23:59:59</t>
         </is>
       </c>
       <c r="I82" t="n">
@@ -5806,17 +5776,19 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>649</v>
-      </c>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>Indefinido</t>
-        </is>
-      </c>
-      <c r="N82" t="inlineStr"/>
+        <v>549</v>
+      </c>
+      <c r="M82" t="n">
+        <v>11</v>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>28-03-2027 12:07:04</t>
+        </is>
+      </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>Recurrente</t>
+          <t>Domiciliado</t>
         </is>
       </c>
       <c r="P82" t="inlineStr"/>
@@ -5827,88 +5799,3291 @@
         <v>81</v>
       </c>
       <c r="B83" t="n">
+        <v>95681</v>
+      </c>
+      <c r="C83" t="n">
+        <v>276079</v>
+      </c>
+      <c r="D83" t="n">
+        <v>73581</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>RAMON  SANCHEZ  RODRIGUEZ</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>MISION ENS</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>03-03-2026 5:53:34</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>01-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I83" t="n">
+        <v>0</v>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L83" t="n">
+        <v>399</v>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr"/>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P83" t="n">
+        <v>67204</v>
+      </c>
+      <c r="Q83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>82</v>
+      </c>
+      <c r="B84" t="n">
+        <v>97185</v>
+      </c>
+      <c r="C84" t="n">
+        <v>18432</v>
+      </c>
+      <c r="D84" t="n">
+        <v>17335</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>GABRIELA GONZALEZ FIERRO</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>PAPALOTE TJ</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>18-03-2026 10:09:52</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>03-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I84" t="n">
+        <v>0</v>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L84" t="n">
+        <v>449</v>
+      </c>
+      <c r="M84" t="n">
+        <v>5</v>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>14-09-2026 10:09:52</t>
+        </is>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P84" t="n">
+        <v>51754</v>
+      </c>
+      <c r="Q84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>83</v>
+      </c>
+      <c r="B85" t="n">
+        <v>96824</v>
+      </c>
+      <c r="C85" t="n">
+        <v>295993</v>
+      </c>
+      <c r="D85" t="n">
+        <v>93491</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>MIGUEL ANGEL  ASTUDILLO MARIN</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>CARROUSEL TJ</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>14-03-2026 11:57:18</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>02-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I85" t="n">
+        <v>0</v>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L85" t="n">
+        <v>499</v>
+      </c>
+      <c r="M85" t="n">
+        <v>11</v>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>09-03-2027 11:57:18</t>
+        </is>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P85" t="n">
+        <v>76896</v>
+      </c>
+      <c r="Q85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>84</v>
+      </c>
+      <c r="B86" t="n">
+        <v>98089</v>
+      </c>
+      <c r="C86" t="n">
+        <v>354084</v>
+      </c>
+      <c r="D86" t="n">
+        <v>96248</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>ROSALBA DOMINGO PARRA</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>TLALNEPANTLA</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>30-03-2026 8:23:13</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>30-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I86" t="n">
+        <v>0</v>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L86" t="n">
+        <v>549</v>
+      </c>
+      <c r="M86" t="n">
+        <v>11</v>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>25-03-2027 8:23:13</t>
+        </is>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P86" t="inlineStr"/>
+      <c r="Q86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>85</v>
+      </c>
+      <c r="B87" t="n">
+        <v>98406</v>
+      </c>
+      <c r="C87" t="n">
+        <v>354852</v>
+      </c>
+      <c r="D87" t="n">
+        <v>97016</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>ROBERTO EMILIANO BAEZ  GONZALEZ</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>INSURGENTES</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>01-04-2026 14:27:45</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>01-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I87" t="n">
+        <v>0</v>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L87" t="n">
+        <v>649</v>
+      </c>
+      <c r="M87" t="n">
+        <v>11</v>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>27-03-2027 14:27:45</t>
+        </is>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P87" t="inlineStr"/>
+      <c r="Q87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>86</v>
+      </c>
+      <c r="B88" t="n">
+        <v>98413</v>
+      </c>
+      <c r="C88" t="n">
+        <v>253549</v>
+      </c>
+      <c r="D88" t="n">
+        <v>51053</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>ROSA MARINA LOPEZ ESPINOSA</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>CARROUSEL TJ</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>01-04-2026 15:44:33</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>01-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I88" t="n">
+        <v>0</v>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L88" t="n">
+        <v>499</v>
+      </c>
+      <c r="M88" t="n">
+        <v>11</v>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>27-03-2027 15:44:33</t>
+        </is>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P88" t="n">
+        <v>38535</v>
+      </c>
+      <c r="Q88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>87</v>
+      </c>
+      <c r="B89" t="n">
+        <v>98431</v>
+      </c>
+      <c r="C89" t="n">
+        <v>133972</v>
+      </c>
+      <c r="D89" t="n">
+        <v>31622</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>EDGAR ALI JIMENEZ LOPEZ</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>PASEO 2000</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>01-04-2026 18:54:53</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>01-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I89" t="n">
+        <v>0</v>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L89" t="n">
+        <v>499</v>
+      </c>
+      <c r="M89" t="n">
+        <v>11</v>
+      </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>27-03-2027 18:54:53</t>
+        </is>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P89" t="n">
+        <v>21825</v>
+      </c>
+      <c r="Q89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>88</v>
+      </c>
+      <c r="B90" t="n">
+        <v>98438</v>
+      </c>
+      <c r="C90" t="n">
+        <v>340018</v>
+      </c>
+      <c r="D90" t="n">
+        <v>17836</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>ANDRES AVILA ROJAS</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>MISION ENS</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>01-04-2026 19:36:58</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>02-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I90" t="n">
+        <v>0</v>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L90" t="n">
+        <v>549</v>
+      </c>
+      <c r="M90" t="n">
+        <v>11</v>
+      </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>27-03-2027 19:36:58</t>
+        </is>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P90" t="n">
+        <v>91348</v>
+      </c>
+      <c r="Q90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>89</v>
+      </c>
+      <c r="B91" t="n">
+        <v>98456</v>
+      </c>
+      <c r="C91" t="n">
+        <v>354538</v>
+      </c>
+      <c r="D91" t="n">
+        <v>96702</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>MARIA NALLELY ROMAN ESPINOZA</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>VILLA VERDE</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>02-04-2026 8:39:43</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>02-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I91" t="n">
+        <v>0</v>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L91" t="n">
+        <v>549</v>
+      </c>
+      <c r="M91" t="n">
+        <v>11</v>
+      </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>28-03-2027 8:39:43</t>
+        </is>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P91" t="inlineStr"/>
+      <c r="Q91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>90</v>
+      </c>
+      <c r="B92" t="n">
+        <v>98463</v>
+      </c>
+      <c r="C92" t="n">
+        <v>355033</v>
+      </c>
+      <c r="D92" t="n">
+        <v>97197</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>JOSE ALFREDO HERRERA LOPEZ</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>CARROUSEL TJ</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>02-04-2026 10:35:56</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>02-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I92" t="n">
+        <v>0</v>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L92" t="n">
+        <v>549</v>
+      </c>
+      <c r="M92" t="n">
+        <v>11</v>
+      </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>28-03-2027 10:35:56</t>
+        </is>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P92" t="inlineStr"/>
+      <c r="Q92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>91</v>
+      </c>
+      <c r="B93" t="n">
+        <v>98474</v>
+      </c>
+      <c r="C93" t="n">
+        <v>355074</v>
+      </c>
+      <c r="D93" t="n">
+        <v>97238</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>CAMILA ELISA RAMIREZ  CADENA</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>METEPEC</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>02-04-2026 13:01:12</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>02-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I93" t="n">
+        <v>0</v>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L93" t="n">
+        <v>549</v>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr"/>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P93" t="inlineStr"/>
+      <c r="Q93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>92</v>
+      </c>
+      <c r="B94" t="n">
+        <v>98481</v>
+      </c>
+      <c r="C94" t="n">
+        <v>97060</v>
+      </c>
+      <c r="D94" t="n">
+        <v>94819</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>LILIAN  ROSILES CAMACHO</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>TEC MXL</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>02-04-2026 15:32:05</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>02-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I94" t="n">
+        <v>0</v>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L94" t="n">
+        <v>549</v>
+      </c>
+      <c r="M94" t="n">
+        <v>11</v>
+      </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>28-03-2027 15:32:05</t>
+        </is>
+      </c>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P94" t="inlineStr"/>
+      <c r="Q94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>93</v>
+      </c>
+      <c r="B95" t="n">
+        <v>98488</v>
+      </c>
+      <c r="C95" t="n">
+        <v>355143</v>
+      </c>
+      <c r="D95" t="n">
+        <v>97307</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>ALEJANDRO  MEJIA  GONZALEZ</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>METEPEC</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>02-04-2026 16:56:01</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>02-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I95" t="n">
+        <v>0</v>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L95" t="n">
+        <v>549</v>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr"/>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P95" t="inlineStr"/>
+      <c r="Q95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>94</v>
+      </c>
+      <c r="B96" t="n">
+        <v>98495</v>
+      </c>
+      <c r="C96" t="n">
+        <v>355174</v>
+      </c>
+      <c r="D96" t="n">
+        <v>97338</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>LEGNA MICHEL CRUZ  LOPEZ</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>SAN LUIS</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>02-04-2026 18:08:51</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>02-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I96" t="n">
+        <v>0</v>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L96" t="n">
+        <v>549</v>
+      </c>
+      <c r="M96" t="n">
+        <v>11</v>
+      </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>28-03-2027 18:08:51</t>
+        </is>
+      </c>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P96" t="inlineStr"/>
+      <c r="Q96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>95</v>
+      </c>
+      <c r="B97" t="n">
+        <v>98506</v>
+      </c>
+      <c r="C97" t="n">
+        <v>301801</v>
+      </c>
+      <c r="D97" t="n">
+        <v>99299</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>NUBIA VANESSA ACOSTA ZAVALA</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>MISION ENS</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>02-04-2026 20:03:24</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>02-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I97" t="n">
+        <v>0</v>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L97" t="n">
+        <v>549</v>
+      </c>
+      <c r="M97" t="n">
+        <v>11</v>
+      </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>28-03-2027 20:03:24</t>
+        </is>
+      </c>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P97" t="inlineStr"/>
+      <c r="Q97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>96</v>
+      </c>
+      <c r="B98" t="n">
+        <v>95816</v>
+      </c>
+      <c r="C98" t="n">
+        <v>26874</v>
+      </c>
+      <c r="D98" t="n">
+        <v>24813</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>JESUS  NUÑEZ CHICUATE</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>TEC MXL</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>03-03-2026 18:01:45</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>02-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I98" t="n">
+        <v>0</v>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L98" t="n">
+        <v>449</v>
+      </c>
+      <c r="M98" t="n">
+        <v>5</v>
+      </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>30-08-2026 18:01:45</t>
+        </is>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P98" t="n">
+        <v>51181</v>
+      </c>
+      <c r="Q98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>97</v>
+      </c>
+      <c r="B99" t="n">
+        <v>96066</v>
+      </c>
+      <c r="C99" t="n">
+        <v>262306</v>
+      </c>
+      <c r="D99" t="n">
+        <v>59810</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>MONICA  BAÑALES  COSSIO</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>PASEO LA PAZ</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>05-03-2026 18:35:11</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>03-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I99" t="n">
+        <v>0</v>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L99" t="n">
+        <v>499</v>
+      </c>
+      <c r="M99" t="n">
+        <v>11</v>
+      </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>28-02-2027 18:35:11</t>
+        </is>
+      </c>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P99" t="n">
+        <v>91681</v>
+      </c>
+      <c r="Q99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>98</v>
+      </c>
+      <c r="B100" t="n">
+        <v>97995</v>
+      </c>
+      <c r="C100" t="n">
+        <v>295894</v>
+      </c>
+      <c r="D100" t="n">
+        <v>93392</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>AITZA MIRENA GUTIERREZ  BLANCARTE</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>VILLAS DEL REY</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>27-03-2026 16:22:41</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>02-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I100" t="n">
+        <v>0</v>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L100" t="n">
+        <v>499</v>
+      </c>
+      <c r="M100" t="n">
+        <v>11</v>
+      </c>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>22-03-2027 16:22:41</t>
+        </is>
+      </c>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P100" t="n">
+        <v>94569</v>
+      </c>
+      <c r="Q100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>99</v>
+      </c>
+      <c r="B101" t="n">
+        <v>95361</v>
+      </c>
+      <c r="C101" t="n">
+        <v>237196</v>
+      </c>
+      <c r="D101" t="n">
+        <v>34701</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>PAULINA ELIZABETH FLORES HINOJOSA</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>SANTA FE</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>01-03-2026 14:42:48</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>01-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I101" t="n">
+        <v>0</v>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L101" t="n">
+        <v>449</v>
+      </c>
+      <c r="M101" t="n">
+        <v>5</v>
+      </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>28-08-2026 14:42:48</t>
+        </is>
+      </c>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P101" t="n">
+        <v>39905</v>
+      </c>
+      <c r="Q101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>100</v>
+      </c>
+      <c r="B102" t="n">
+        <v>98384</v>
+      </c>
+      <c r="C102" t="n">
+        <v>3040</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>02041</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>LISBETH MAGALLI GARCIA VERDUZCO</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>SEND MXL</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>01-04-2026 7:50:45</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>01-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I102" t="n">
+        <v>0</v>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L102" t="n">
+        <v>549</v>
+      </c>
+      <c r="M102" t="n">
+        <v>11</v>
+      </c>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>27-03-2027 7:50:45</t>
+        </is>
+      </c>
+      <c r="O102" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P102" t="inlineStr"/>
+      <c r="Q102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>101</v>
+      </c>
+      <c r="B103" t="n">
+        <v>98399</v>
+      </c>
+      <c r="C103" t="n">
+        <v>150909</v>
+      </c>
+      <c r="D103" t="n">
+        <v>48475</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>KARINA LIZBETH FLORES SILVA</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>SAN LUIS</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>01-04-2026 12:30:40</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>01-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I103" t="n">
+        <v>0</v>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L103" t="n">
+        <v>499</v>
+      </c>
+      <c r="M103" t="n">
+        <v>11</v>
+      </c>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>27-03-2027 12:30:40</t>
+        </is>
+      </c>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P103" t="n">
+        <v>83695</v>
+      </c>
+      <c r="Q103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>102</v>
+      </c>
+      <c r="B104" t="n">
+        <v>98403</v>
+      </c>
+      <c r="C104" t="n">
+        <v>354838</v>
+      </c>
+      <c r="D104" t="n">
+        <v>97002</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>ROCIO GUADALUPE ROCHA PADRON</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>IXTAPALUCA</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>01-04-2026 13:06:47</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>01-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I104" t="n">
+        <v>0</v>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L104" t="n">
+        <v>649</v>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N104" t="inlineStr"/>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P104" t="inlineStr"/>
+      <c r="Q104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>103</v>
+      </c>
+      <c r="B105" t="n">
+        <v>98416</v>
+      </c>
+      <c r="C105" t="n">
+        <v>354894</v>
+      </c>
+      <c r="D105" t="n">
+        <v>97058</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>ANGEL ISMAEL VENCES  OCHOA</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>SEND MXL</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>01-04-2026 16:28:22</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>01-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I105" t="n">
+        <v>0</v>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L105" t="n">
+        <v>549</v>
+      </c>
+      <c r="M105" t="n">
+        <v>11</v>
+      </c>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>27-03-2027 16:28:22</t>
+        </is>
+      </c>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P105" t="inlineStr"/>
+      <c r="Q105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>104</v>
+      </c>
+      <c r="B106" t="n">
+        <v>98433</v>
+      </c>
+      <c r="C106" t="n">
+        <v>240369</v>
+      </c>
+      <c r="D106" t="n">
+        <v>37874</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>ALEXIS RAYMUNDO  CAMPOS  JUAREZ</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>SANTA FE</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>01-04-2026 18:56:46</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>01-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I106" t="n">
+        <v>0</v>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L106" t="n">
+        <v>499</v>
+      </c>
+      <c r="M106" t="n">
+        <v>11</v>
+      </c>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>27-03-2027 18:56:46</t>
+        </is>
+      </c>
+      <c r="O106" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P106" t="n">
+        <v>80953</v>
+      </c>
+      <c r="Q106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>105</v>
+      </c>
+      <c r="B107" t="n">
+        <v>98450</v>
+      </c>
+      <c r="C107" t="n">
+        <v>36331</v>
+      </c>
+      <c r="D107" t="n">
+        <v>34235</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>YOSELYN MICHEL SALAZAR  FIGUEROA</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>SANTA FE</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>01-04-2026 21:41:21</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>01-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I107" t="n">
+        <v>0</v>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L107" t="n">
+        <v>649</v>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N107" t="inlineStr"/>
+      <c r="O107" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P107" t="inlineStr"/>
+      <c r="Q107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>106</v>
+      </c>
+      <c r="B108" t="n">
+        <v>98452</v>
+      </c>
+      <c r="C108" t="n">
+        <v>244777</v>
+      </c>
+      <c r="D108" t="n">
+        <v>42282</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>NANCY  HERNÁNDEZ GONZALEZ</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>SEND SALTILLO</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>02-04-2026 6:26:04</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>02-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I108" t="n">
+        <v>0</v>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L108" t="n">
+        <v>999</v>
+      </c>
+      <c r="M108" t="n">
+        <v>11</v>
+      </c>
+      <c r="N108" t="inlineStr">
+        <is>
+          <t>28-03-2027 6:26:04</t>
+        </is>
+      </c>
+      <c r="O108" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P108" t="inlineStr"/>
+      <c r="Q108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>107</v>
+      </c>
+      <c r="B109" t="n">
+        <v>98469</v>
+      </c>
+      <c r="C109" t="n">
+        <v>331727</v>
+      </c>
+      <c r="D109" t="n">
+        <v>16781</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>MARIA ISABEL  CASTILLO HEREDIA</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>PASEO 2000</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>02-04-2026 12:09:11</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>03-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I109" t="n">
+        <v>0</v>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L109" t="n">
+        <v>649</v>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N109" t="inlineStr"/>
+      <c r="O109" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P109" t="n">
+        <v>85465</v>
+      </c>
+      <c r="Q109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>108</v>
+      </c>
+      <c r="B110" t="n">
+        <v>98484</v>
+      </c>
+      <c r="C110" t="n">
+        <v>355128</v>
+      </c>
+      <c r="D110" t="n">
+        <v>97292</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>EDUARDO PALACIOS ESTRADA</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>METEPEC</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>02-04-2026 16:07:22</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>02-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I110" t="n">
+        <v>0</v>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L110" t="n">
+        <v>549</v>
+      </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N110" t="inlineStr"/>
+      <c r="O110" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P110" t="inlineStr"/>
+      <c r="Q110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>109</v>
+      </c>
+      <c r="B111" t="n">
+        <v>98486</v>
+      </c>
+      <c r="C111" t="n">
+        <v>354495</v>
+      </c>
+      <c r="D111" t="n">
+        <v>96659</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>NURI GUADALUPE QUINTERO LOPEZ</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>PASEO 2000</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>02-04-2026 16:37:14</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>02-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I111" t="n">
+        <v>0</v>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L111" t="n">
+        <v>549</v>
+      </c>
+      <c r="M111" t="n">
+        <v>11</v>
+      </c>
+      <c r="N111" t="inlineStr">
+        <is>
+          <t>28-03-2027 16:37:14</t>
+        </is>
+      </c>
+      <c r="O111" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P111" t="inlineStr"/>
+      <c r="Q111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>110</v>
+      </c>
+      <c r="B112" t="n">
+        <v>98501</v>
+      </c>
+      <c r="C112" t="n">
+        <v>91450</v>
+      </c>
+      <c r="D112" t="n">
+        <v>89221</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>SHEILA LAZARIN HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>VILLA VERDE</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>02-04-2026 18:59:08</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>02-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I112" t="n">
+        <v>0</v>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L112" t="n">
+        <v>649</v>
+      </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N112" t="inlineStr"/>
+      <c r="O112" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P112" t="inlineStr"/>
+      <c r="Q112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>111</v>
+      </c>
+      <c r="B113" t="n">
+        <v>98503</v>
+      </c>
+      <c r="C113" t="n">
+        <v>284389</v>
+      </c>
+      <c r="D113" t="n">
+        <v>81890</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>OSIEL ALEJANDRO ZAVALA GALAVIZ</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>SEND SALTILLO</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>02-04-2026 19:25:17</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>02-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I113" t="n">
+        <v>0</v>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L113" t="n">
+        <v>499</v>
+      </c>
+      <c r="M113" t="n">
+        <v>11</v>
+      </c>
+      <c r="N113" t="inlineStr">
+        <is>
+          <t>28-03-2027 19:25:17</t>
+        </is>
+      </c>
+      <c r="O113" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P113" t="n">
+        <v>61223</v>
+      </c>
+      <c r="Q113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>112</v>
+      </c>
+      <c r="B114" t="n">
+        <v>95729</v>
+      </c>
+      <c r="C114" t="n">
+        <v>271470</v>
+      </c>
+      <c r="D114" t="n">
+        <v>68972</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>DANIELA MEDINA PARTIDA</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>SANTA FE</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>03-03-2026 10:30:22</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>03-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I114" t="n">
+        <v>0</v>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L114" t="n">
+        <v>599</v>
+      </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N114" t="inlineStr"/>
+      <c r="O114" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P114" t="n">
+        <v>52010</v>
+      </c>
+      <c r="Q114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>113</v>
+      </c>
+      <c r="B115" t="n">
+        <v>95842</v>
+      </c>
+      <c r="C115" t="n">
+        <v>194058</v>
+      </c>
+      <c r="D115" t="n">
+        <v>91565</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>FRANCISCO JAVIER CABIEDES HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>MISION ENS</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>03-03-2026 19:39:24</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>03-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I115" t="n">
+        <v>0</v>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L115" t="n">
+        <v>399</v>
+      </c>
+      <c r="M115" t="n">
+        <v>11</v>
+      </c>
+      <c r="N115" t="inlineStr">
+        <is>
+          <t>26-02-2027 19:39:24</t>
+        </is>
+      </c>
+      <c r="O115" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P115" t="n">
+        <v>81606</v>
+      </c>
+      <c r="Q115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>114</v>
+      </c>
+      <c r="B116" t="n">
+        <v>95859</v>
+      </c>
+      <c r="C116" t="n">
+        <v>101890</v>
+      </c>
+      <c r="D116" t="n">
+        <v>99642</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>ELIZABETH RODRIGUEZ CASTRO</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>CARROUSEL TJ</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>03-03-2026 20:59:15</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>03-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I116" t="n">
+        <v>0</v>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L116" t="n">
+        <v>549</v>
+      </c>
+      <c r="M116" t="n">
+        <v>5</v>
+      </c>
+      <c r="N116" t="inlineStr">
+        <is>
+          <t>30-08-2026 20:59:15</t>
+        </is>
+      </c>
+      <c r="O116" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P116" t="n">
+        <v>59304</v>
+      </c>
+      <c r="Q116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>115</v>
+      </c>
+      <c r="B117" t="n">
+        <v>97112</v>
+      </c>
+      <c r="C117" t="n">
+        <v>307274</v>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>04773</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>ESMERALDA GUADALUPE RANGEL ESQUIVEL</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>SEND SALTILLO</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>17-03-2026 18:17:30</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>02-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I117" t="n">
+        <v>0</v>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L117" t="n">
+        <v>499</v>
+      </c>
+      <c r="M117" t="n">
+        <v>11</v>
+      </c>
+      <c r="N117" t="inlineStr">
+        <is>
+          <t>12-03-2027 18:17:30</t>
+        </is>
+      </c>
+      <c r="O117" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P117" t="n">
+        <v>87410</v>
+      </c>
+      <c r="Q117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>116</v>
+      </c>
+      <c r="B118" t="n">
+        <v>97214</v>
+      </c>
+      <c r="C118" t="n">
+        <v>227607</v>
+      </c>
+      <c r="D118" t="n">
+        <v>25112</v>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>NUBIA LORENA BUCIO CASTILLO</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>PAPALOTE TJ</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>18-03-2026 16:31:25</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>02-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I118" t="n">
+        <v>0</v>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L118" t="n">
+        <v>449</v>
+      </c>
+      <c r="M118" t="n">
+        <v>5</v>
+      </c>
+      <c r="N118" t="inlineStr">
+        <is>
+          <t>14-09-2026 16:31:25</t>
+        </is>
+      </c>
+      <c r="O118" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P118" t="n">
+        <v>50707</v>
+      </c>
+      <c r="Q118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>117</v>
+      </c>
+      <c r="B119" t="n">
+        <v>97965</v>
+      </c>
+      <c r="C119" t="n">
+        <v>70411</v>
+      </c>
+      <c r="D119" t="n">
+        <v>68233</v>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>CYNTHIA IVETH GARCIA  MORENO</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>SEND MXL</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>27-03-2026 11:58:41</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>01-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I119" t="n">
+        <v>0</v>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L119" t="n">
+        <v>449</v>
+      </c>
+      <c r="M119" t="n">
+        <v>11</v>
+      </c>
+      <c r="N119" t="inlineStr">
+        <is>
+          <t>22-03-2027 11:58:41</t>
+        </is>
+      </c>
+      <c r="O119" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P119" t="n">
+        <v>31636</v>
+      </c>
+      <c r="Q119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>118</v>
+      </c>
+      <c r="B120" t="n">
+        <v>98376</v>
+      </c>
+      <c r="C120" t="n">
+        <v>330015</v>
+      </c>
+      <c r="D120" t="n">
+        <v>15069</v>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>NOEL GALLEGOS VARELA</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>SEND CHIH</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>01-04-2026 5:07:31</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>01-07-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I120" t="n">
+        <v>0</v>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L120" t="n">
+        <v>1449</v>
+      </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N120" t="inlineStr"/>
+      <c r="O120" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P120" t="inlineStr"/>
+      <c r="Q120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>119</v>
+      </c>
+      <c r="B121" t="n">
+        <v>98393</v>
+      </c>
+      <c r="C121" t="n">
+        <v>354818</v>
+      </c>
+      <c r="D121" t="n">
+        <v>96982</v>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>ISIDRO  MENDEZ  JARAMILLO</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>SALTILLO VILLALTA</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>01-04-2026 10:58:42</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>01-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I121" t="n">
+        <v>0</v>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L121" t="n">
+        <v>799</v>
+      </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N121" t="inlineStr"/>
+      <c r="O121" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P121" t="inlineStr"/>
+      <c r="Q121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>120</v>
+      </c>
+      <c r="B122" t="n">
+        <v>98411</v>
+      </c>
+      <c r="C122" t="n">
+        <v>354867</v>
+      </c>
+      <c r="D122" t="n">
+        <v>97031</v>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>SEBASTIAN IBAÑEZ RAMIREZ</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>INSURGENTES</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>01-04-2026 15:15:54</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>01-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I122" t="n">
+        <v>0</v>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L122" t="n">
+        <v>649</v>
+      </c>
+      <c r="M122" t="n">
+        <v>11</v>
+      </c>
+      <c r="N122" t="inlineStr">
+        <is>
+          <t>27-03-2027 15:15:54</t>
+        </is>
+      </c>
+      <c r="O122" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P122" t="inlineStr"/>
+      <c r="Q122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>121</v>
+      </c>
+      <c r="B123" t="n">
+        <v>98425</v>
+      </c>
+      <c r="C123" t="n">
+        <v>352652</v>
+      </c>
+      <c r="D123" t="n">
+        <v>94816</v>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>MARCO VEGA DUARTE</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>TEC MXL</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>01-04-2026 18:03:42</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>01-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I123" t="n">
+        <v>0</v>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L123" t="n">
+        <v>549</v>
+      </c>
+      <c r="M123" t="n">
+        <v>11</v>
+      </c>
+      <c r="N123" t="inlineStr">
+        <is>
+          <t>27-03-2027 18:03:42</t>
+        </is>
+      </c>
+      <c r="O123" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P123" t="inlineStr"/>
+      <c r="Q123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>122</v>
+      </c>
+      <c r="B124" t="n">
+        <v>98426</v>
+      </c>
+      <c r="C124" t="n">
+        <v>183909</v>
+      </c>
+      <c r="D124" t="n">
+        <v>81416</v>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>FELIPE ARTURO HERNANDEZ VALDEZ</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>CARROUSEL TJ</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>01-04-2026 18:03:51</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>01-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I124" t="n">
+        <v>0</v>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L124" t="n">
+        <v>399</v>
+      </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N124" t="inlineStr"/>
+      <c r="O124" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P124" t="n">
+        <v>43588</v>
+      </c>
+      <c r="Q124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>123</v>
+      </c>
+      <c r="B125" t="n">
+        <v>98443</v>
+      </c>
+      <c r="C125" t="n">
+        <v>257769</v>
+      </c>
+      <c r="D125" t="n">
+        <v>55273</v>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>JUANA ISABEL DOMINGUEZ MATA</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>LOMA BONITA</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>01-04-2026 20:24:55</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>01-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I125" t="n">
+        <v>0</v>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L125" t="n">
+        <v>549</v>
+      </c>
+      <c r="M125" t="n">
+        <v>11</v>
+      </c>
+      <c r="N125" t="inlineStr">
+        <is>
+          <t>27-03-2027 20:24:55</t>
+        </is>
+      </c>
+      <c r="O125" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P125" t="inlineStr"/>
+      <c r="Q125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>124</v>
+      </c>
+      <c r="B126" t="n">
+        <v>98444</v>
+      </c>
+      <c r="C126" t="n">
+        <v>280981</v>
+      </c>
+      <c r="D126" t="n">
+        <v>78482</v>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>JOSE DANIEL  CASTRO DE LOS REYES</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>SAN LUIS</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>01-04-2026 20:33:23</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>01-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I126" t="n">
+        <v>0</v>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L126" t="n">
+        <v>649</v>
+      </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N126" t="inlineStr"/>
+      <c r="O126" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P126" t="inlineStr"/>
+      <c r="Q126" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>125</v>
+      </c>
+      <c r="B127" t="n">
         <v>98458</v>
       </c>
-      <c r="C83" t="n">
+      <c r="C127" t="n">
         <v>355001</v>
       </c>
-      <c r="D83" t="n">
+      <c r="D127" t="n">
         <v>97165</v>
       </c>
-      <c r="E83" t="inlineStr">
+      <c r="E127" t="inlineStr">
         <is>
           <t>MARIA ELODIA SALVADOR MORALES</t>
         </is>
       </c>
-      <c r="F83" t="inlineStr">
+      <c r="F127" t="inlineStr">
         <is>
           <t>PASEO 2000</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr">
+      <c r="G127" t="inlineStr">
         <is>
           <t>02-04-2026 8:58:21</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
+      <c r="H127" t="inlineStr">
         <is>
           <t>02-05-2026 23:59:59</t>
         </is>
       </c>
-      <c r="I83" t="n">
-        <v>0</v>
-      </c>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>Sin filtro</t>
-        </is>
-      </c>
-      <c r="K83" t="inlineStr">
+      <c r="I127" t="n">
+        <v>0</v>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
         <is>
           <t>NUEVO</t>
         </is>
       </c>
-      <c r="L83" t="n">
+      <c r="L127" t="n">
         <v>549</v>
       </c>
-      <c r="M83" t="n">
+      <c r="M127" t="n">
         <v>11</v>
       </c>
-      <c r="N83" t="inlineStr">
+      <c r="N127" t="inlineStr">
         <is>
           <t>28-03-2027 8:58:21</t>
         </is>
       </c>
-      <c r="O83" t="inlineStr">
+      <c r="O127" t="inlineStr">
         <is>
           <t>Domiciliado</t>
         </is>
       </c>
-      <c r="P83" t="inlineStr"/>
-      <c r="Q83" t="inlineStr"/>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>Reporte generado: 02-04-2026 04:04 p. m.</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr"/>
-      <c r="C84" t="inlineStr"/>
-      <c r="D84" t="inlineStr"/>
-      <c r="E84" t="inlineStr"/>
-      <c r="F84" t="inlineStr"/>
-      <c r="G84" t="inlineStr"/>
-      <c r="H84" t="inlineStr"/>
-      <c r="I84" t="inlineStr"/>
-      <c r="J84" t="inlineStr"/>
-      <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr"/>
-      <c r="N84" t="inlineStr"/>
-      <c r="O84" t="inlineStr"/>
-      <c r="P84" t="inlineStr"/>
-      <c r="Q84" t="inlineStr"/>
+      <c r="P127" t="inlineStr"/>
+      <c r="Q127" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>126</v>
+      </c>
+      <c r="B128" t="n">
+        <v>98461</v>
+      </c>
+      <c r="C128" t="n">
+        <v>355011</v>
+      </c>
+      <c r="D128" t="n">
+        <v>97175</v>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>MARCO ANTONIO ALVARADO MANDUJANO</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>SEND SALTILLO</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>02-04-2026 9:22:00</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>02-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I128" t="n">
+        <v>0</v>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L128" t="n">
+        <v>549</v>
+      </c>
+      <c r="M128" t="n">
+        <v>11</v>
+      </c>
+      <c r="N128" t="inlineStr">
+        <is>
+          <t>28-03-2027 9:22:00</t>
+        </is>
+      </c>
+      <c r="O128" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P128" t="inlineStr"/>
+      <c r="Q128" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>127</v>
+      </c>
+      <c r="B129" t="n">
+        <v>98475</v>
+      </c>
+      <c r="C129" t="n">
+        <v>355078</v>
+      </c>
+      <c r="D129" t="n">
+        <v>97242</v>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>MARIAN CADENA CORDOVA</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>METEPEC</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>02-04-2026 13:04:29</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>02-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I129" t="n">
+        <v>0</v>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L129" t="n">
+        <v>649</v>
+      </c>
+      <c r="M129" t="n">
+        <v>11</v>
+      </c>
+      <c r="N129" t="inlineStr">
+        <is>
+          <t>28-03-2027 13:04:29</t>
+        </is>
+      </c>
+      <c r="O129" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P129" t="inlineStr"/>
+      <c r="Q129" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>128</v>
+      </c>
+      <c r="B130" t="n">
+        <v>98493</v>
+      </c>
+      <c r="C130" t="n">
+        <v>354661</v>
+      </c>
+      <c r="D130" t="n">
+        <v>96825</v>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>ARYAM SUSANA CONTRERAS CORTES</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>SALTILLO VILLALTA</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>02-04-2026 17:35:38</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>02-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I130" t="n">
+        <v>0</v>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L130" t="n">
+        <v>799</v>
+      </c>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N130" t="inlineStr"/>
+      <c r="O130" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P130" t="inlineStr"/>
+      <c r="Q130" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>129</v>
+      </c>
+      <c r="B131" t="n">
+        <v>98494</v>
+      </c>
+      <c r="C131" t="n">
+        <v>355165</v>
+      </c>
+      <c r="D131" t="n">
+        <v>97329</v>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>MARIA FERNANDA GUZMAN FUENTES</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>PAPALOTE TJ</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>02-04-2026 17:59:11</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>02-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I131" t="n">
+        <v>0</v>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L131" t="n">
+        <v>649</v>
+      </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N131" t="inlineStr"/>
+      <c r="O131" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P131" t="inlineStr"/>
+      <c r="Q131" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>130</v>
+      </c>
+      <c r="B132" t="n">
+        <v>98511</v>
+      </c>
+      <c r="C132" t="n">
+        <v>291224</v>
+      </c>
+      <c r="D132" t="n">
+        <v>88722</v>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>JULIO CESAR  PEREZ  HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>SANTA FE</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>03-04-2026 8:29:05</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>04-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I132" t="n">
+        <v>0</v>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L132" t="n">
+        <v>549</v>
+      </c>
+      <c r="M132" t="n">
+        <v>5</v>
+      </c>
+      <c r="N132" t="inlineStr">
+        <is>
+          <t>30-09-2026 8:29:05</t>
+        </is>
+      </c>
+      <c r="O132" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P132" t="n">
+        <v>97678</v>
+      </c>
+      <c r="Q132" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Reporte generado: 03-04-2026 03:43 p. m.</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr"/>
+      <c r="C133" t="inlineStr"/>
+      <c r="D133" t="inlineStr"/>
+      <c r="E133" t="inlineStr"/>
+      <c r="F133" t="inlineStr"/>
+      <c r="G133" t="inlineStr"/>
+      <c r="H133" t="inlineStr"/>
+      <c r="I133" t="inlineStr"/>
+      <c r="J133" t="inlineStr"/>
+      <c r="K133" t="inlineStr"/>
+      <c r="L133" t="inlineStr"/>
+      <c r="M133" t="inlineStr"/>
+      <c r="N133" t="inlineStr"/>
+      <c r="O133" t="inlineStr"/>
+      <c r="P133" t="inlineStr"/>
+      <c r="Q133" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/descargas/cargos_recurrentes.xlsx
+++ b/data/descargas/cargos_recurrentes.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q3"/>
+  <dimension ref="A1:Q19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -599,27 +599,1083 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Reporte generado: 01-05-2026 09:11 a. m. </t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="n">
+        <v>99056</v>
+      </c>
+      <c r="C3" t="n">
+        <v>76774</v>
+      </c>
+      <c r="D3" t="n">
+        <v>74576</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>CESAR DANIEL  PEREYRA  CONTRERAS</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>VILLA VERDE</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>10-04-2026 17:32:18</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>01-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>399</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P3" t="n">
+        <v>24188</v>
+      </c>
       <c r="Q3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="n">
+        <v>98454</v>
+      </c>
+      <c r="C4" t="n">
+        <v>65078</v>
+      </c>
+      <c r="D4" t="n">
+        <v>62916</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>ALEJANDRO MAGALLAN  LOPEZ</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>SEND CUL</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>02-04-2026 7:19:31</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>01-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>350</v>
+      </c>
+      <c r="M4" t="n">
+        <v>5</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>29-09-2026 7:19:31</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
+        <v>76842</v>
+      </c>
+      <c r="Q4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="n">
+        <v>98465</v>
+      </c>
+      <c r="C5" t="n">
+        <v>312044</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>09543</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>NIRVANA FERNANDA  SALADO  SANCHEZ</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>MISION ENS</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>02-04-2026 11:24:30</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>01-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>499</v>
+      </c>
+      <c r="M5" t="n">
+        <v>11</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>28-03-2027 11:24:30</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
+        <v>76811</v>
+      </c>
+      <c r="Q5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="n">
+        <v>100177</v>
+      </c>
+      <c r="C6" t="n">
+        <v>194060</v>
+      </c>
+      <c r="D6" t="n">
+        <v>91567</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>ELISA ELENA PAREDES HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>TEC MXL</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>27-04-2026 8:15:35</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>01-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>499</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>4813</v>
+      </c>
+      <c r="Q6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" t="n">
+        <v>100484</v>
+      </c>
+      <c r="C7" t="n">
+        <v>42885</v>
+      </c>
+      <c r="D7" t="n">
+        <v>40755</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>LUZ ADRIANA ALARCON  GONZALEZ</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>PASEO 2000</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>01-05-2026 8:55:06</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>01-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>649</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" t="n">
+        <v>99080</v>
+      </c>
+      <c r="C8" t="n">
+        <v>326105</v>
+      </c>
+      <c r="D8" t="n">
+        <v>23044</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>MONICA DANIELA  ORDUÑO PEREZ</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>SEND CUL</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>11-04-2026 10:17:07</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>01-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>599</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P8" t="n">
+        <v>83122</v>
+      </c>
+      <c r="Q8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" t="n">
+        <v>97892</v>
+      </c>
+      <c r="C9" t="n">
+        <v>151685</v>
+      </c>
+      <c r="D9" t="n">
+        <v>49250</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>SUSAN ELIZABETH SOTO PIÑA</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>SEND CUL</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>26-03-2026 13:42:06</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>01-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>399</v>
+      </c>
+      <c r="M9" t="n">
+        <v>11</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>21-03-2027 13:42:06</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
+        <v>2308</v>
+      </c>
+      <c r="Q9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" t="n">
+        <v>100331</v>
+      </c>
+      <c r="C10" t="n">
+        <v>22791</v>
+      </c>
+      <c r="D10" t="n">
+        <v>21685</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>JUAN JOSE  PACHECO  FLORES</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>CARROUSEL TJ</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>28-04-2026 13:00:52</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>01-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>399</v>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>79141</v>
+      </c>
+      <c r="Q10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99846</v>
+      </c>
+      <c r="C11" t="n">
+        <v>253406</v>
+      </c>
+      <c r="D11" t="n">
+        <v>50910</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>BRISEIDA ISABEL ENRIQUEZ ZEPEDA</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>PAPALOTE TJ</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>20-04-2026 21:29:56</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>01-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>499</v>
+      </c>
+      <c r="M11" t="n">
+        <v>11</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>15-04-2027 21:29:56</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>79273</v>
+      </c>
+      <c r="Q11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" t="n">
+        <v>98466</v>
+      </c>
+      <c r="C12" t="n">
+        <v>205081</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>02589</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>ISRAEL CRESPO RIOS</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>MISION ENS</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>02-04-2026 11:27:04</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>01-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>499</v>
+      </c>
+      <c r="M12" t="n">
+        <v>11</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>28-03-2027 11:27:04</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>76809</v>
+      </c>
+      <c r="Q12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" t="n">
+        <v>98583</v>
+      </c>
+      <c r="C13" t="n">
+        <v>114721</v>
+      </c>
+      <c r="D13" t="n">
+        <v>12446</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>JESUS ANTONIO ABRIL CAMPOS</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>SAN LUIS</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>06-04-2026 5:30:30</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>01-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>399</v>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>11835</v>
+      </c>
+      <c r="Q13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" t="n">
+        <v>99840</v>
+      </c>
+      <c r="C14" t="n">
+        <v>178067</v>
+      </c>
+      <c r="D14" t="n">
+        <v>75574</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>ALMA ANGELICA  PEREZ  MIRANDA</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>SANTA FE</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>20-04-2026 20:14:31</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>01-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
+        <v>449</v>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>74406</v>
+      </c>
+      <c r="Q14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" t="n">
+        <v>98369</v>
+      </c>
+      <c r="C15" t="n">
+        <v>56575</v>
+      </c>
+      <c r="D15" t="n">
+        <v>54426</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>LARISSA DENISSE LOPEZ BURGOS</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>TEC MXL</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>31-03-2026 20:18:54</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>01-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L15" t="n">
+        <v>499</v>
+      </c>
+      <c r="M15" t="n">
+        <v>11</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>26-03-2027 20:18:54</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>91270</v>
+      </c>
+      <c r="Q15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" t="n">
+        <v>100480</v>
+      </c>
+      <c r="C16" t="n">
+        <v>360840</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>03005</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>TANIA ELIZABETH VILLAREAL PEREDA</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>INSURGENTES</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>01-05-2026 7:38:40</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>01-08-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L16" t="n">
+        <v>1549</v>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" t="n">
+        <v>100483</v>
+      </c>
+      <c r="C17" t="n">
+        <v>360852</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>03017</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>ELIUD RAMIREZ BELMARES</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>SALTILLO VILLALTA</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>01-05-2026 8:37:34</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>01-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L17" t="n">
+        <v>649</v>
+      </c>
+      <c r="M17" t="n">
+        <v>11</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>26-04-2027 8:37:34</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" t="n">
+        <v>98943</v>
+      </c>
+      <c r="C18" t="n">
+        <v>37106</v>
+      </c>
+      <c r="D18" t="n">
+        <v>34985</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>JUAN FRANCISCO PITONES NORIEGA</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>SEND MXL</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>08-04-2026 20:42:26</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>01-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L18" t="n">
+        <v>399</v>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P18" t="n">
+        <v>96274</v>
+      </c>
+      <c r="Q18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Reporte generado: 01-05-2026 04:01 p. m.</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/descargas/cargos_recurrentes.xlsx
+++ b/data/descargas/cargos_recurrentes.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q19"/>
+  <dimension ref="A1:Q47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -603,27 +603,29 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>99056</v>
+        <v>100493</v>
       </c>
       <c r="C3" t="n">
-        <v>76774</v>
-      </c>
-      <c r="D3" t="n">
-        <v>74576</v>
+        <v>360045</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>02210</t>
+        </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>CESAR DANIEL  PEREYRA  CONTRERAS</t>
+          <t>BALTAZAR VILLASEÑOR  CRUZ</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>VILLA VERDE</t>
+          <t>METEPEC</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>10-04-2026 17:32:18</t>
+          <t>01-05-2026 11:51:52</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -641,11 +643,11 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>RENOVACIÓN</t>
+          <t>NUEVO</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>399</v>
+        <v>799</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -658,9 +660,7 @@
           <t>Recurrente</t>
         </is>
       </c>
-      <c r="P3" t="n">
-        <v>24188</v>
-      </c>
+      <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr"/>
     </row>
     <row r="4">
@@ -668,27 +668,27 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>98454</v>
+        <v>100495</v>
       </c>
       <c r="C4" t="n">
-        <v>65078</v>
+        <v>349026</v>
       </c>
       <c r="D4" t="n">
-        <v>62916</v>
+        <v>91191</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>ALEJANDRO MAGALLAN  LOPEZ</t>
+          <t>CESAR OMAR OBREGON ESTRELLLO</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>SEND CUL</t>
+          <t>SALTILLO VILLALTA</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>02-04-2026 7:19:31</t>
+          <t>01-05-2026 12:28:55</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -706,18 +706,18 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>RENOVACIÓN</t>
+          <t>NUEVO</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>350</v>
+        <v>649</v>
       </c>
       <c r="M4" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>29-09-2026 7:19:31</t>
+          <t>26-04-2027 12:28:55</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -725,9 +725,7 @@
           <t>Domiciliado</t>
         </is>
       </c>
-      <c r="P4" t="n">
-        <v>76842</v>
-      </c>
+      <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr"/>
     </row>
     <row r="5">
@@ -735,34 +733,34 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>98465</v>
+        <v>100502</v>
       </c>
       <c r="C5" t="n">
-        <v>312044</v>
+        <v>205459</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>09543</t>
+          <t>02967</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>NIRVANA FERNANDA  SALADO  SANCHEZ</t>
+          <t>ANTONIO  LAMAS IRINEO</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>MISION ENS</t>
+          <t>SEND MXL</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>02-04-2026 11:24:30</t>
+          <t>01-05-2026 17:19:17</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>01-06-2026 23:59:59</t>
+          <t>30-05-2026 23:59:59</t>
         </is>
       </c>
       <c r="I5" t="n">
@@ -779,14 +777,14 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>499</v>
+        <v>399</v>
       </c>
       <c r="M5" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>28-03-2027 11:24:30</t>
+          <t>28-10-2026 17:19:17</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -795,7 +793,7 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>76811</v>
+        <v>38806</v>
       </c>
       <c r="Q5" t="inlineStr"/>
     </row>
@@ -804,17 +802,19 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>100177</v>
+        <v>100504</v>
       </c>
       <c r="C6" t="n">
-        <v>194060</v>
-      </c>
-      <c r="D6" t="n">
-        <v>91567</v>
+        <v>361003</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>03168</t>
+        </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>ELISA ELENA PAREDES HERNANDEZ</t>
+          <t>DEMIAN CORONADO LOPEZ</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>27-04-2026 8:15:35</t>
+          <t>01-05-2026 18:12:55</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -842,11 +842,11 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>RENOVACIÓN</t>
+          <t>NUEVO</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>499</v>
+        <v>649</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -859,9 +859,7 @@
           <t>Recurrente</t>
         </is>
       </c>
-      <c r="P6" t="n">
-        <v>4813</v>
-      </c>
+      <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr"/>
     </row>
     <row r="7">
@@ -869,17 +867,17 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>100484</v>
+        <v>100485</v>
       </c>
       <c r="C7" t="n">
-        <v>42885</v>
+        <v>283428</v>
       </c>
       <c r="D7" t="n">
-        <v>40755</v>
+        <v>80929</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>LUZ ADRIANA ALARCON  GONZALEZ</t>
+          <t>JOSE MANUEL OSUNA PEÑA</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -889,7 +887,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>01-05-2026 8:55:06</t>
+          <t>01-05-2026 9:28:55</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -907,24 +905,28 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>NUEVO</t>
+          <t>RENOVACIÓN</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>649</v>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>Indefinido</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
+        <v>699</v>
+      </c>
+      <c r="M7" t="n">
+        <v>11</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>26-04-2027 9:28:55</t>
+        </is>
+      </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Recurrente</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr"/>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>60636</v>
+      </c>
       <c r="Q7" t="inlineStr"/>
     </row>
     <row r="8">
@@ -932,27 +934,27 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>99080</v>
+        <v>100496</v>
       </c>
       <c r="C8" t="n">
-        <v>326105</v>
+        <v>241908</v>
       </c>
       <c r="D8" t="n">
-        <v>23044</v>
+        <v>39413</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>MONICA DANIELA  ORDUÑO PEREZ</t>
+          <t>DANIA FERNANDA MORENO BELLO</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>SEND CUL</t>
+          <t>TEC MXL</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>11-04-2026 10:17:07</t>
+          <t>01-05-2026 12:44:57</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -974,21 +976,23 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>599</v>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>Indefinido</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
+        <v>699</v>
+      </c>
+      <c r="M8" t="n">
+        <v>11</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>26-04-2027 12:44:57</t>
+        </is>
+      </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Recurrente</t>
+          <t>Domiciliado</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>83122</v>
+        <v>54257</v>
       </c>
       <c r="Q8" t="inlineStr"/>
     </row>
@@ -997,27 +1001,29 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>97892</v>
+        <v>100503</v>
       </c>
       <c r="C9" t="n">
-        <v>151685</v>
-      </c>
-      <c r="D9" t="n">
-        <v>49250</v>
+        <v>360991</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>03156</t>
+        </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>SUSAN ELIZABETH SOTO PIÑA</t>
+          <t>MARLENE  GARCIA AGUILAR</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>SEND CUL</t>
+          <t>VILLA VERDE</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>26-03-2026 13:42:06</t>
+          <t>01-05-2026 17:35:18</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1035,28 +1041,24 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>RENOVACIÓN</t>
+          <t>NUEVO</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>399</v>
-      </c>
-      <c r="M9" t="n">
-        <v>11</v>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>21-03-2027 13:42:06</t>
-        </is>
-      </c>
+        <v>649</v>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Domiciliado</t>
-        </is>
-      </c>
-      <c r="P9" t="n">
-        <v>2308</v>
-      </c>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr"/>
       <c r="Q9" t="inlineStr"/>
     </row>
     <row r="10">
@@ -1064,27 +1066,27 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>100331</v>
+        <v>99056</v>
       </c>
       <c r="C10" t="n">
-        <v>22791</v>
+        <v>76774</v>
       </c>
       <c r="D10" t="n">
-        <v>21685</v>
+        <v>74576</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>JUAN JOSE  PACHECO  FLORES</t>
+          <t>CESAR DANIEL  PEREYRA  CONTRERAS</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CARROUSEL TJ</t>
+          <t>VILLA VERDE</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>28-04-2026 13:00:52</t>
+          <t>10-04-2026 17:32:18</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1120,7 +1122,7 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>79141</v>
+        <v>24188</v>
       </c>
       <c r="Q10" t="inlineStr"/>
     </row>
@@ -1129,27 +1131,29 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>99846</v>
+        <v>100488</v>
       </c>
       <c r="C11" t="n">
-        <v>253406</v>
-      </c>
-      <c r="D11" t="n">
-        <v>50910</v>
+        <v>360887</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>03052</t>
+        </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>BRISEIDA ISABEL ENRIQUEZ ZEPEDA</t>
+          <t>MARIA DEL CARMEN JIMENEZ SANCHEZ</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>PAPALOTE TJ</t>
+          <t>SEND SALTILLO</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>20-04-2026 21:29:56</t>
+          <t>01-05-2026 10:34:42</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1167,18 +1171,18 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>RENOVACIÓN</t>
+          <t>NUEVO</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>499</v>
+        <v>549</v>
       </c>
       <c r="M11" t="n">
         <v>11</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>15-04-2027 21:29:56</t>
+          <t>26-04-2027 10:34:42</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1186,9 +1190,7 @@
           <t>Domiciliado</t>
         </is>
       </c>
-      <c r="P11" t="n">
-        <v>79273</v>
-      </c>
+      <c r="P11" t="inlineStr"/>
       <c r="Q11" t="inlineStr"/>
     </row>
     <row r="12">
@@ -1196,29 +1198,29 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>98466</v>
+        <v>100490</v>
       </c>
       <c r="C12" t="n">
-        <v>205081</v>
+        <v>360892</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>02589</t>
+          <t>03057</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ISRAEL CRESPO RIOS</t>
+          <t>ZARAKY RENE  ZENTENO  ORTIZ</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>MISION ENS</t>
+          <t>IXTAPALUCA</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>02-04-2026 11:27:04</t>
+          <t>01-05-2026 11:00:08</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1236,28 +1238,24 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>RENOVACIÓN</t>
+          <t>NUEVO</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>499</v>
-      </c>
-      <c r="M12" t="n">
-        <v>11</v>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>28-03-2027 11:27:04</t>
-        </is>
-      </c>
+        <v>649</v>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Domiciliado</t>
-        </is>
-      </c>
-      <c r="P12" t="n">
-        <v>76809</v>
-      </c>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr"/>
       <c r="Q12" t="inlineStr"/>
     </row>
     <row r="13">
@@ -1265,27 +1263,29 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>98583</v>
+        <v>100492</v>
       </c>
       <c r="C13" t="n">
-        <v>114721</v>
-      </c>
-      <c r="D13" t="n">
-        <v>12446</v>
+        <v>360904</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>03069</t>
+        </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>JESUS ANTONIO ABRIL CAMPOS</t>
+          <t>CARLA DANIELA MARTINEZ  GUILLEN</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>SAN LUIS</t>
+          <t>IXTAPALUCA</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>06-04-2026 5:30:30</t>
+          <t>01-05-2026 11:42:18</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1303,26 +1303,26 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>RENOVACIÓN</t>
+          <t>NUEVO</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>399</v>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>Indefinido</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
+        <v>549</v>
+      </c>
+      <c r="M13" t="n">
+        <v>11</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>26-04-2027 11:42:18</t>
+        </is>
+      </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Recurrente</t>
-        </is>
-      </c>
-      <c r="P13" t="n">
-        <v>11835</v>
-      </c>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr"/>
       <c r="Q13" t="inlineStr"/>
     </row>
     <row r="14">
@@ -1330,27 +1330,29 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>99840</v>
+        <v>100505</v>
       </c>
       <c r="C14" t="n">
-        <v>178067</v>
-      </c>
-      <c r="D14" t="n">
-        <v>75574</v>
+        <v>360757</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>02922</t>
+        </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>ALMA ANGELICA  PEREZ  MIRANDA</t>
+          <t>CARLOS EDUARDO  FLORES  SANCHEZ</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>SANTA FE</t>
+          <t>SEND MXL</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>20-04-2026 20:14:31</t>
+          <t>01-05-2026 18:17:42</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1368,26 +1370,26 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>RENOVACIÓN</t>
+          <t>NUEVO</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>449</v>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>Indefinido</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
+        <v>549</v>
+      </c>
+      <c r="M14" t="n">
+        <v>11</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>26-04-2027 18:17:42</t>
+        </is>
+      </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Recurrente</t>
-        </is>
-      </c>
-      <c r="P14" t="n">
-        <v>74406</v>
-      </c>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr"/>
       <c r="Q14" t="inlineStr"/>
     </row>
     <row r="15">
@@ -1395,27 +1397,27 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>98369</v>
+        <v>100507</v>
       </c>
       <c r="C15" t="n">
-        <v>56575</v>
+        <v>353643</v>
       </c>
       <c r="D15" t="n">
-        <v>54426</v>
+        <v>95807</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>LARISSA DENISSE LOPEZ BURGOS</t>
+          <t>MINERVA  GONZALEZ  MACEDO</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>TEC MXL</t>
+          <t>METEPEC</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>31-03-2026 20:18:54</t>
+          <t>01-05-2026 18:32:13</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1433,18 +1435,18 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>RENOVACIÓN</t>
+          <t>NUEVO</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>499</v>
+        <v>649</v>
       </c>
       <c r="M15" t="n">
         <v>11</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>26-03-2027 20:18:54</t>
+          <t>26-04-2027 18:32:13</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -1452,9 +1454,7 @@
           <t>Domiciliado</t>
         </is>
       </c>
-      <c r="P15" t="n">
-        <v>91270</v>
-      </c>
+      <c r="P15" t="inlineStr"/>
       <c r="Q15" t="inlineStr"/>
     </row>
     <row r="16">
@@ -1462,34 +1462,32 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>100480</v>
+        <v>98369</v>
       </c>
       <c r="C16" t="n">
-        <v>360840</v>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>03005</t>
-        </is>
+        <v>56575</v>
+      </c>
+      <c r="D16" t="n">
+        <v>54426</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>TANIA ELIZABETH VILLAREAL PEREDA</t>
+          <t>LARISSA DENISSE LOPEZ BURGOS</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>INSURGENTES</t>
+          <t>TEC MXL</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>01-05-2026 7:38:40</t>
+          <t>31-03-2026 20:18:54</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>01-08-2026 23:59:59</t>
+          <t>01-06-2026 23:59:59</t>
         </is>
       </c>
       <c r="I16" t="n">
@@ -1502,24 +1500,28 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>NUEVO</t>
+          <t>RENOVACIÓN</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1549</v>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>Indefinido</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
+        <v>499</v>
+      </c>
+      <c r="M16" t="n">
+        <v>11</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>26-03-2027 20:18:54</t>
+        </is>
+      </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Recurrente</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr"/>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>91270</v>
+      </c>
       <c r="Q16" t="inlineStr"/>
     </row>
     <row r="17">
@@ -1527,29 +1529,27 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>100483</v>
+        <v>100331</v>
       </c>
       <c r="C17" t="n">
-        <v>360852</v>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>03017</t>
-        </is>
+        <v>22791</v>
+      </c>
+      <c r="D17" t="n">
+        <v>21685</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>ELIUD RAMIREZ BELMARES</t>
+          <t>JUAN JOSE  PACHECO  FLORES</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>SALTILLO VILLALTA</t>
+          <t>CARROUSEL TJ</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>01-05-2026 8:37:34</t>
+          <t>28-04-2026 13:00:52</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1567,26 +1567,26 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>NUEVO</t>
+          <t>RENOVACIÓN</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>649</v>
-      </c>
-      <c r="M17" t="n">
-        <v>11</v>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>26-04-2027 8:37:34</t>
-        </is>
-      </c>
+        <v>399</v>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Domiciliado</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr"/>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>79141</v>
+      </c>
       <c r="Q17" t="inlineStr"/>
     </row>
     <row r="18">
@@ -1594,27 +1594,27 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>98943</v>
+        <v>100499</v>
       </c>
       <c r="C18" t="n">
-        <v>37106</v>
+        <v>79792</v>
       </c>
       <c r="D18" t="n">
-        <v>34985</v>
+        <v>77591</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>JUAN FRANCISCO PITONES NORIEGA</t>
+          <t>CHRISTIAN PRISCILA CARDONA BANDA</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>SEND MXL</t>
+          <t>STA CATARINA</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>08-04-2026 20:42:26</t>
+          <t>01-05-2026 16:18:47</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1632,50 +1632,1898 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>RENOVACIÓN</t>
+          <t>NUEVO</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>399</v>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>Indefinido</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
+        <v>549</v>
+      </c>
+      <c r="M18" t="n">
+        <v>11</v>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>26-04-2027 16:18:47</t>
+        </is>
+      </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Recurrente</t>
-        </is>
-      </c>
-      <c r="P18" t="n">
-        <v>96274</v>
-      </c>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr"/>
       <c r="Q18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Reporte generado: 01-05-2026 04:01 p. m.</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
+      <c r="A19" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" t="n">
+        <v>100514</v>
+      </c>
+      <c r="C19" t="n">
+        <v>361054</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>03219</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>ALAN IGNACIO  CORTES HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>SALTILLO VILLALTA</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>02-05-2026 7:36:52</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>02-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L19" t="n">
+        <v>649</v>
+      </c>
+      <c r="M19" t="n">
+        <v>11</v>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>27-04-2027 7:36:52</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr"/>
       <c r="Q19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" t="n">
+        <v>97892</v>
+      </c>
+      <c r="C20" t="n">
+        <v>151685</v>
+      </c>
+      <c r="D20" t="n">
+        <v>49250</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>SUSAN ELIZABETH SOTO PIÑA</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>SEND CUL</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>26-03-2026 13:42:06</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>01-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L20" t="n">
+        <v>399</v>
+      </c>
+      <c r="M20" t="n">
+        <v>11</v>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>21-03-2027 13:42:06</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P20" t="n">
+        <v>2308</v>
+      </c>
+      <c r="Q20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" t="n">
+        <v>99846</v>
+      </c>
+      <c r="C21" t="n">
+        <v>253406</v>
+      </c>
+      <c r="D21" t="n">
+        <v>50910</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>BRISEIDA ISABEL ENRIQUEZ ZEPEDA</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>PAPALOTE TJ</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>20-04-2026 21:29:56</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>01-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L21" t="n">
+        <v>499</v>
+      </c>
+      <c r="M21" t="n">
+        <v>11</v>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>15-04-2027 21:29:56</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P21" t="n">
+        <v>79273</v>
+      </c>
+      <c r="Q21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" t="n">
+        <v>100489</v>
+      </c>
+      <c r="C22" t="n">
+        <v>360888</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>03053</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>MARA FERNANDA LUNA MENDOZA</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>VILLA VERDE</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>01-05-2026 10:38:33</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>01-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L22" t="n">
+        <v>649</v>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" t="n">
+        <v>100491</v>
+      </c>
+      <c r="C23" t="n">
+        <v>56971</v>
+      </c>
+      <c r="D23" t="n">
+        <v>54822</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>NOEMI  RAMOS  DE LEON</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>CARROUSEL TJ</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>01-05-2026 11:15:25</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>04-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L23" t="n">
+        <v>449</v>
+      </c>
+      <c r="M23" t="n">
+        <v>11</v>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>26-04-2027 11:15:25</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P23" t="n">
+        <v>68495</v>
+      </c>
+      <c r="Q23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>22</v>
+      </c>
+      <c r="B24" t="n">
+        <v>100508</v>
+      </c>
+      <c r="C24" t="n">
+        <v>361018</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>03183</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>DENIS LILIANA AMEZCUA CRUZ</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>CARROUSEL TJ</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>01-05-2026 19:13:51</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>01-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L24" t="n">
+        <v>649</v>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>23</v>
+      </c>
+      <c r="B25" t="n">
+        <v>98466</v>
+      </c>
+      <c r="C25" t="n">
+        <v>205081</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>02589</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>ISRAEL CRESPO RIOS</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>MISION ENS</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>02-04-2026 11:27:04</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>01-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L25" t="n">
+        <v>499</v>
+      </c>
+      <c r="M25" t="n">
+        <v>11</v>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>28-03-2027 11:27:04</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P25" t="n">
+        <v>76809</v>
+      </c>
+      <c r="Q25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>24</v>
+      </c>
+      <c r="B26" t="n">
+        <v>98583</v>
+      </c>
+      <c r="C26" t="n">
+        <v>114721</v>
+      </c>
+      <c r="D26" t="n">
+        <v>12446</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>JESUS ANTONIO ABRIL CAMPOS</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>SAN LUIS</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>06-04-2026 5:30:30</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>01-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L26" t="n">
+        <v>399</v>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P26" t="n">
+        <v>11835</v>
+      </c>
+      <c r="Q26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>25</v>
+      </c>
+      <c r="B27" t="n">
+        <v>99840</v>
+      </c>
+      <c r="C27" t="n">
+        <v>178067</v>
+      </c>
+      <c r="D27" t="n">
+        <v>75574</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>ALMA ANGELICA  PEREZ  MIRANDA</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>SANTA FE</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>20-04-2026 20:14:31</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>01-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L27" t="n">
+        <v>449</v>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P27" t="n">
+        <v>74406</v>
+      </c>
+      <c r="Q27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>26</v>
+      </c>
+      <c r="B28" t="n">
+        <v>100487</v>
+      </c>
+      <c r="C28" t="n">
+        <v>48666</v>
+      </c>
+      <c r="D28" t="n">
+        <v>46524</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>ANA LUISA  HERNANDEZ  BELTRAN</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>AZAHARES CUL</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>01-05-2026 10:01:13</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>01-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L28" t="n">
+        <v>549</v>
+      </c>
+      <c r="M28" t="n">
+        <v>11</v>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>26-04-2027 10:01:13</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>27</v>
+      </c>
+      <c r="B29" t="n">
+        <v>100494</v>
+      </c>
+      <c r="C29" t="n">
+        <v>346010</v>
+      </c>
+      <c r="D29" t="n">
+        <v>88175</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>ANA FABIOLA FLORES CARMONA</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>PASEO 2000</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>01-05-2026 11:54:51</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>01-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L29" t="n">
+        <v>999</v>
+      </c>
+      <c r="M29" t="n">
+        <v>11</v>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>26-04-2027 11:54:51</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>28</v>
+      </c>
+      <c r="B30" t="n">
+        <v>100501</v>
+      </c>
+      <c r="C30" t="n">
+        <v>347090</v>
+      </c>
+      <c r="D30" t="n">
+        <v>89255</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>GUILLERMO GERARDO VAZQUEZ GARCIA</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>SEND MXL</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>01-05-2026 16:31:24</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>01-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L30" t="n">
+        <v>549</v>
+      </c>
+      <c r="M30" t="n">
+        <v>11</v>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>26-04-2027 16:31:24</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>29</v>
+      </c>
+      <c r="B31" t="n">
+        <v>100512</v>
+      </c>
+      <c r="C31" t="n">
+        <v>140437</v>
+      </c>
+      <c r="D31" t="n">
+        <v>38064</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>JUAN  FLORES  FELIX</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>AZAHARES CUL</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>01-05-2026 20:54:12</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>04-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L31" t="n">
+        <v>449</v>
+      </c>
+      <c r="M31" t="n">
+        <v>5</v>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>28-10-2026 20:54:12</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P31" t="n">
+        <v>55808</v>
+      </c>
+      <c r="Q31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>30</v>
+      </c>
+      <c r="B32" t="n">
+        <v>98454</v>
+      </c>
+      <c r="C32" t="n">
+        <v>65078</v>
+      </c>
+      <c r="D32" t="n">
+        <v>62916</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>ALEJANDRO MAGALLAN  LOPEZ</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>SEND CUL</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>02-04-2026 7:19:31</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>01-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L32" t="n">
+        <v>350</v>
+      </c>
+      <c r="M32" t="n">
+        <v>5</v>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>29-09-2026 7:19:31</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P32" t="n">
+        <v>76842</v>
+      </c>
+      <c r="Q32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>31</v>
+      </c>
+      <c r="B33" t="n">
+        <v>98465</v>
+      </c>
+      <c r="C33" t="n">
+        <v>312044</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>09543</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>NIRVANA FERNANDA  SALADO  SANCHEZ</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>MISION ENS</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>02-04-2026 11:24:30</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>01-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L33" t="n">
+        <v>499</v>
+      </c>
+      <c r="M33" t="n">
+        <v>11</v>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>28-03-2027 11:24:30</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P33" t="n">
+        <v>76811</v>
+      </c>
+      <c r="Q33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>32</v>
+      </c>
+      <c r="B34" t="n">
+        <v>95940</v>
+      </c>
+      <c r="C34" t="n">
+        <v>95151</v>
+      </c>
+      <c r="D34" t="n">
+        <v>92910</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>ANGELICA DEYANIRA SERRANO VALDEZ</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>PASEO 2000</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>04-03-2026 15:59:55</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>03-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L34" t="n">
+        <v>499</v>
+      </c>
+      <c r="M34" t="n">
+        <v>11</v>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>27-02-2027 15:59:55</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P34" t="n">
+        <v>52003</v>
+      </c>
+      <c r="Q34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>33</v>
+      </c>
+      <c r="B35" t="n">
+        <v>100177</v>
+      </c>
+      <c r="C35" t="n">
+        <v>194060</v>
+      </c>
+      <c r="D35" t="n">
+        <v>91567</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>ELISA ELENA PAREDES HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>TEC MXL</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>27-04-2026 8:15:35</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>01-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I35" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L35" t="n">
+        <v>499</v>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P35" t="n">
+        <v>4813</v>
+      </c>
+      <c r="Q35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>34</v>
+      </c>
+      <c r="B36" t="n">
+        <v>100443</v>
+      </c>
+      <c r="C36" t="n">
+        <v>354766</v>
+      </c>
+      <c r="D36" t="n">
+        <v>96930</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>JESUS ORLANDO OROZCO SEGOVIA</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>SEND MXL</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>30-04-2026 8:06:02</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>01-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L36" t="n">
+        <v>549</v>
+      </c>
+      <c r="M36" t="n">
+        <v>11</v>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>25-04-2027 8:06:02</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>35</v>
+      </c>
+      <c r="B37" t="n">
+        <v>100484</v>
+      </c>
+      <c r="C37" t="n">
+        <v>42885</v>
+      </c>
+      <c r="D37" t="n">
+        <v>40755</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>LUZ ADRIANA ALARCON  GONZALEZ</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>PASEO 2000</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>01-05-2026 8:55:06</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>01-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L37" t="n">
+        <v>649</v>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>36</v>
+      </c>
+      <c r="B38" t="n">
+        <v>100486</v>
+      </c>
+      <c r="C38" t="n">
+        <v>360869</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>03034</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>JOANNA VILLEGAS ORTIZ</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>MISION ENS</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>01-05-2026 9:43:16</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>01-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I38" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L38" t="n">
+        <v>649</v>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr"/>
+      <c r="Q38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>37</v>
+      </c>
+      <c r="B39" t="n">
+        <v>100509</v>
+      </c>
+      <c r="C39" t="n">
+        <v>141351</v>
+      </c>
+      <c r="D39" t="n">
+        <v>38969</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>JESUS ABELARDO RODRIGUEZ NAVARRO</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>CARROUSEL TJ</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>01-05-2026 20:01:10</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>01-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I39" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L39" t="n">
+        <v>699</v>
+      </c>
+      <c r="M39" t="n">
+        <v>11</v>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>26-04-2027 20:01:10</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P39" t="n">
+        <v>76258</v>
+      </c>
+      <c r="Q39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>38</v>
+      </c>
+      <c r="B40" t="n">
+        <v>100511</v>
+      </c>
+      <c r="C40" t="n">
+        <v>361026</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>03191</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>HILARY MONROY MORENO</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>CARROUSEL TJ</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>01-05-2026 20:07:30</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>01-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I40" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L40" t="n">
+        <v>649</v>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr"/>
+      <c r="Q40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>39</v>
+      </c>
+      <c r="B41" t="n">
+        <v>99080</v>
+      </c>
+      <c r="C41" t="n">
+        <v>326105</v>
+      </c>
+      <c r="D41" t="n">
+        <v>23044</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>MONICA DANIELA  ORDUÑO PEREZ</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>SEND CUL</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>11-04-2026 10:17:07</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>01-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I41" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L41" t="n">
+        <v>599</v>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P41" t="n">
+        <v>83122</v>
+      </c>
+      <c r="Q41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>40</v>
+      </c>
+      <c r="B42" t="n">
+        <v>100480</v>
+      </c>
+      <c r="C42" t="n">
+        <v>360840</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>03005</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>TANIA ELIZABETH VILLAREAL PEREDA</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>INSURGENTES</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>01-05-2026 7:38:40</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>01-08-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I42" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L42" t="n">
+        <v>1549</v>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr"/>
+      <c r="Q42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>41</v>
+      </c>
+      <c r="B43" t="n">
+        <v>100483</v>
+      </c>
+      <c r="C43" t="n">
+        <v>360852</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>03017</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>ELIUD RAMIREZ BELMARES</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>SALTILLO VILLALTA</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>01-05-2026 8:37:34</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>01-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L43" t="n">
+        <v>649</v>
+      </c>
+      <c r="M43" t="n">
+        <v>11</v>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>26-04-2027 8:37:34</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr"/>
+      <c r="Q43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>42</v>
+      </c>
+      <c r="B44" t="n">
+        <v>100515</v>
+      </c>
+      <c r="C44" t="n">
+        <v>361056</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>03221</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>GILBERTO  BARRIOS HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>SALTILLO VILLALTA</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>02-05-2026 7:46:19</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>02-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I44" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L44" t="n">
+        <v>649</v>
+      </c>
+      <c r="M44" t="n">
+        <v>11</v>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>27-04-2027 7:46:19</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr"/>
+      <c r="Q44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>43</v>
+      </c>
+      <c r="B45" t="n">
+        <v>98943</v>
+      </c>
+      <c r="C45" t="n">
+        <v>37106</v>
+      </c>
+      <c r="D45" t="n">
+        <v>34985</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>JUAN FRANCISCO PITONES NORIEGA</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>SEND MXL</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>08-04-2026 20:42:26</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>01-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I45" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L45" t="n">
+        <v>399</v>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P45" t="n">
+        <v>96274</v>
+      </c>
+      <c r="Q45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>44</v>
+      </c>
+      <c r="B46" t="n">
+        <v>100497</v>
+      </c>
+      <c r="C46" t="n">
+        <v>179725</v>
+      </c>
+      <c r="D46" t="n">
+        <v>77232</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>EBER  MAGDIEL  CASTILLEJA  BARROSO</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>SEND SALTILLO</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>01-05-2026 15:17:21</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>01-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I46" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L46" t="n">
+        <v>499</v>
+      </c>
+      <c r="M46" t="n">
+        <v>11</v>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>26-04-2027 15:17:21</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P46" t="n">
+        <v>4540</v>
+      </c>
+      <c r="Q46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Reporte generado: 02-05-2026 03:48 p. m.</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr"/>
+      <c r="C47" t="inlineStr"/>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
+      <c r="O47" t="inlineStr"/>
+      <c r="P47" t="inlineStr"/>
+      <c r="Q47" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/descargas/cargos_recurrentes.xlsx
+++ b/data/descargas/cargos_recurrentes.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q47"/>
+  <dimension ref="A1:Q67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -603,29 +603,27 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>100493</v>
+        <v>100485</v>
       </c>
       <c r="C3" t="n">
-        <v>360045</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>02210</t>
-        </is>
+        <v>283428</v>
+      </c>
+      <c r="D3" t="n">
+        <v>80929</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>BALTAZAR VILLASEÑOR  CRUZ</t>
+          <t>JOSE MANUEL OSUNA PEÑA</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>METEPEC</t>
+          <t>PASEO 2000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>01-05-2026 11:51:52</t>
+          <t>01-05-2026 9:28:55</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -643,24 +641,28 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>NUEVO</t>
+          <t>RENOVACIÓN</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>799</v>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>Indefinido</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+        <v>699</v>
+      </c>
+      <c r="M3" t="n">
+        <v>11</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>26-04-2027 9:28:55</t>
+        </is>
+      </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Recurrente</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr"/>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P3" t="n">
+        <v>60636</v>
+      </c>
       <c r="Q3" t="inlineStr"/>
     </row>
     <row r="4">
@@ -668,27 +670,27 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>100495</v>
+        <v>100496</v>
       </c>
       <c r="C4" t="n">
-        <v>349026</v>
+        <v>241908</v>
       </c>
       <c r="D4" t="n">
-        <v>91191</v>
+        <v>39413</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>CESAR OMAR OBREGON ESTRELLLO</t>
+          <t>DANIA FERNANDA MORENO BELLO</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>SALTILLO VILLALTA</t>
+          <t>TEC MXL</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>01-05-2026 12:28:55</t>
+          <t>01-05-2026 12:44:57</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -706,18 +708,18 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>NUEVO</t>
+          <t>RENOVACIÓN</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>649</v>
+        <v>699</v>
       </c>
       <c r="M4" t="n">
         <v>11</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>26-04-2027 12:28:55</t>
+          <t>26-04-2027 12:44:57</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -725,7 +727,9 @@
           <t>Domiciliado</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr"/>
+      <c r="P4" t="n">
+        <v>54257</v>
+      </c>
       <c r="Q4" t="inlineStr"/>
     </row>
     <row r="5">
@@ -733,34 +737,34 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>100502</v>
+        <v>100503</v>
       </c>
       <c r="C5" t="n">
-        <v>205459</v>
+        <v>360991</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>02967</t>
+          <t>03156</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>ANTONIO  LAMAS IRINEO</t>
+          <t>MARLENE  GARCIA AGUILAR</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>SEND MXL</t>
+          <t>VILLA VERDE</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>01-05-2026 17:19:17</t>
+          <t>01-05-2026 17:35:18</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>30-05-2026 23:59:59</t>
+          <t>01-06-2026 23:59:59</t>
         </is>
       </c>
       <c r="I5" t="n">
@@ -773,28 +777,24 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>RENOVACIÓN</t>
+          <t>NUEVO</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>399</v>
-      </c>
-      <c r="M5" t="n">
-        <v>5</v>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>28-10-2026 17:19:17</t>
-        </is>
-      </c>
+        <v>649</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Domiciliado</t>
-        </is>
-      </c>
-      <c r="P5" t="n">
-        <v>38806</v>
-      </c>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr"/>
       <c r="Q5" t="inlineStr"/>
     </row>
     <row r="6">
@@ -802,34 +802,32 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>100504</v>
+        <v>100521</v>
       </c>
       <c r="C6" t="n">
-        <v>361003</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>03168</t>
-        </is>
+        <v>266562</v>
+      </c>
+      <c r="D6" t="n">
+        <v>64066</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>DEMIAN CORONADO LOPEZ</t>
+          <t>NATALIA PADILLA RIVAS</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>TEC MXL</t>
+          <t>CARROUSEL TJ</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>01-05-2026 18:12:55</t>
+          <t>02-05-2026 13:06:35</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>01-06-2026 23:59:59</t>
+          <t>02-06-2026 23:59:59</t>
         </is>
       </c>
       <c r="I6" t="n">
@@ -846,17 +844,19 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>649</v>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>Indefinido</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
+        <v>499</v>
+      </c>
+      <c r="M6" t="n">
+        <v>11</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>27-04-2027 13:06:35</t>
+        </is>
+      </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Recurrente</t>
+          <t>Domiciliado</t>
         </is>
       </c>
       <c r="P6" t="inlineStr"/>
@@ -867,27 +867,27 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>100485</v>
+        <v>99056</v>
       </c>
       <c r="C7" t="n">
-        <v>283428</v>
+        <v>76774</v>
       </c>
       <c r="D7" t="n">
-        <v>80929</v>
+        <v>74576</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>JOSE MANUEL OSUNA PEÑA</t>
+          <t>CESAR DANIEL  PEREYRA  CONTRERAS</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>PASEO 2000</t>
+          <t>VILLA VERDE</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>01-05-2026 9:28:55</t>
+          <t>10-04-2026 17:32:18</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -909,23 +909,21 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>699</v>
-      </c>
-      <c r="M7" t="n">
-        <v>11</v>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>26-04-2027 9:28:55</t>
-        </is>
-      </c>
+        <v>399</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Domiciliado</t>
+          <t>Recurrente</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>60636</v>
+        <v>24188</v>
       </c>
       <c r="Q7" t="inlineStr"/>
     </row>
@@ -934,32 +932,32 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>100496</v>
+        <v>98510</v>
       </c>
       <c r="C8" t="n">
-        <v>241908</v>
+        <v>195783</v>
       </c>
       <c r="D8" t="n">
-        <v>39413</v>
+        <v>93290</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>DANIA FERNANDA MORENO BELLO</t>
+          <t>KEVIN AXEL VILLAREAL CUEN</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>TEC MXL</t>
+          <t>PABELLON RTO</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>01-05-2026 12:44:57</t>
+          <t>03-04-2026 8:20:41</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>01-06-2026 23:59:59</t>
+          <t>03-06-2026 23:59:59</t>
         </is>
       </c>
       <c r="I8" t="n">
@@ -976,14 +974,14 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>699</v>
+        <v>399</v>
       </c>
       <c r="M8" t="n">
         <v>11</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>26-04-2027 12:44:57</t>
+          <t>29-03-2027 8:20:41</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -992,7 +990,7 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>54257</v>
+        <v>41075</v>
       </c>
       <c r="Q8" t="inlineStr"/>
     </row>
@@ -1001,34 +999,32 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>100503</v>
+        <v>98541</v>
       </c>
       <c r="C9" t="n">
-        <v>360991</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>03156</t>
-        </is>
+        <v>25207</v>
+      </c>
+      <c r="D9" t="n">
+        <v>23149</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>MARLENE  GARCIA AGUILAR</t>
+          <t>YOSHIO JESUS  RINCON  MIRANDA</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>VILLA VERDE</t>
+          <t>CARROUSEL TJ</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>01-05-2026 17:35:18</t>
+          <t>03-04-2026 17:05:50</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>01-06-2026 23:59:59</t>
+          <t>02-06-2026 23:59:59</t>
         </is>
       </c>
       <c r="I9" t="n">
@@ -1041,24 +1037,28 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>NUEVO</t>
+          <t>RENOVACIÓN</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>649</v>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>Indefinido</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
+        <v>449</v>
+      </c>
+      <c r="M9" t="n">
+        <v>5</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>30-09-2026 17:05:50</t>
+        </is>
+      </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Recurrente</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr"/>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
+        <v>49403</v>
+      </c>
       <c r="Q9" t="inlineStr"/>
     </row>
     <row r="10">
@@ -1066,32 +1066,32 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>99056</v>
+        <v>98810</v>
       </c>
       <c r="C10" t="n">
-        <v>76774</v>
+        <v>59822</v>
       </c>
       <c r="D10" t="n">
-        <v>74576</v>
+        <v>57663</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>CESAR DANIEL  PEREYRA  CONTRERAS</t>
+          <t>LETICIA RUBIO VALENZUELA</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>VILLA VERDE</t>
+          <t>INDEPENDENCIA</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>10-04-2026 17:32:18</t>
+          <t>07-04-2026 17:54:05</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>01-06-2026 23:59:59</t>
+          <t>02-06-2026 23:59:59</t>
         </is>
       </c>
       <c r="I10" t="n">
@@ -1110,19 +1110,21 @@
       <c r="L10" t="n">
         <v>399</v>
       </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>Indefinido</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
+      <c r="M10" t="n">
+        <v>11</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>02-04-2027 17:54:05</t>
+        </is>
+      </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Recurrente</t>
+          <t>Domiciliado</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>24188</v>
+        <v>8024</v>
       </c>
       <c r="Q10" t="inlineStr"/>
     </row>
@@ -1131,29 +1133,27 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>100488</v>
+        <v>100331</v>
       </c>
       <c r="C11" t="n">
-        <v>360887</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>03052</t>
-        </is>
+        <v>22791</v>
+      </c>
+      <c r="D11" t="n">
+        <v>21685</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>MARIA DEL CARMEN JIMENEZ SANCHEZ</t>
+          <t>JUAN JOSE  PACHECO  FLORES</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>SEND SALTILLO</t>
+          <t>CARROUSEL TJ</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>01-05-2026 10:34:42</t>
+          <t>28-04-2026 13:00:52</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1171,26 +1171,26 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>NUEVO</t>
+          <t>RENOVACIÓN</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>549</v>
-      </c>
-      <c r="M11" t="n">
-        <v>11</v>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>26-04-2027 10:34:42</t>
-        </is>
-      </c>
+        <v>399</v>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Domiciliado</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr"/>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>79141</v>
+      </c>
       <c r="Q11" t="inlineStr"/>
     </row>
     <row r="12">
@@ -1198,29 +1198,27 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>100490</v>
+        <v>100499</v>
       </c>
       <c r="C12" t="n">
-        <v>360892</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>03057</t>
-        </is>
+        <v>79792</v>
+      </c>
+      <c r="D12" t="n">
+        <v>77591</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ZARAKY RENE  ZENTENO  ORTIZ</t>
+          <t>CHRISTIAN PRISCILA CARDONA BANDA</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>IXTAPALUCA</t>
+          <t>STA CATARINA</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>01-05-2026 11:00:08</t>
+          <t>01-05-2026 16:18:47</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1242,17 +1240,19 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>649</v>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>Indefinido</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
+        <v>549</v>
+      </c>
+      <c r="M12" t="n">
+        <v>11</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>26-04-2027 16:18:47</t>
+        </is>
+      </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Recurrente</t>
+          <t>Domiciliado</t>
         </is>
       </c>
       <c r="P12" t="inlineStr"/>
@@ -1263,34 +1263,34 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>100492</v>
+        <v>100514</v>
       </c>
       <c r="C13" t="n">
-        <v>360904</v>
+        <v>361054</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>03069</t>
+          <t>03219</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CARLA DANIELA MARTINEZ  GUILLEN</t>
+          <t>ALAN IGNACIO  CORTES HERNANDEZ</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>IXTAPALUCA</t>
+          <t>SALTILLO VILLALTA</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>01-05-2026 11:42:18</t>
+          <t>02-05-2026 7:36:52</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>01-06-2026 23:59:59</t>
+          <t>02-06-2026 23:59:59</t>
         </is>
       </c>
       <c r="I13" t="n">
@@ -1307,14 +1307,14 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>549</v>
+        <v>649</v>
       </c>
       <c r="M13" t="n">
         <v>11</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>26-04-2027 11:42:18</t>
+          <t>27-04-2027 7:36:52</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1330,34 +1330,32 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>100505</v>
+        <v>100517</v>
       </c>
       <c r="C14" t="n">
-        <v>360757</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>02922</t>
-        </is>
+        <v>348099</v>
+      </c>
+      <c r="D14" t="n">
+        <v>90264</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CARLOS EDUARDO  FLORES  SANCHEZ</t>
+          <t>DANIEL CASIO FLORENCIO</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>SEND MXL</t>
+          <t>SEND SALTILLO</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>01-05-2026 18:17:42</t>
+          <t>02-05-2026 10:04:52</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>01-06-2026 23:59:59</t>
+          <t>03-06-2026 23:59:59</t>
         </is>
       </c>
       <c r="I14" t="n">
@@ -1370,7 +1368,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>NUEVO</t>
+          <t>RENOVACIÓN</t>
         </is>
       </c>
       <c r="L14" t="n">
@@ -1381,7 +1379,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>26-04-2027 18:17:42</t>
+          <t>27-04-2027 10:04:52</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -1389,7 +1387,9 @@
           <t>Domiciliado</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr"/>
+      <c r="P14" t="n">
+        <v>95766</v>
+      </c>
       <c r="Q14" t="inlineStr"/>
     </row>
     <row r="15">
@@ -1397,32 +1397,32 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>100507</v>
+        <v>97773</v>
       </c>
       <c r="C15" t="n">
-        <v>353643</v>
+        <v>348244</v>
       </c>
       <c r="D15" t="n">
-        <v>95807</v>
+        <v>90409</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>MINERVA  GONZALEZ  MACEDO</t>
+          <t>DULCE NOHEMI SOTO MORENO</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>METEPEC</t>
+          <t>TEC MXL</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>01-05-2026 18:32:13</t>
+          <t>24-03-2026 20:48:40</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>01-06-2026 23:59:59</t>
+          <t>10-05-2026 23:59:59</t>
         </is>
       </c>
       <c r="I15" t="n">
@@ -1435,18 +1435,18 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>NUEVO</t>
+          <t>RENOVACIÓN</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>649</v>
+        <v>549</v>
       </c>
       <c r="M15" t="n">
         <v>11</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>26-04-2027 18:32:13</t>
+          <t>19-03-2027 20:48:40</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -1454,7 +1454,9 @@
           <t>Domiciliado</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr"/>
+      <c r="P15" t="n">
+        <v>97756</v>
+      </c>
       <c r="Q15" t="inlineStr"/>
     </row>
     <row r="16">
@@ -1462,27 +1464,27 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>98369</v>
+        <v>97892</v>
       </c>
       <c r="C16" t="n">
-        <v>56575</v>
+        <v>151685</v>
       </c>
       <c r="D16" t="n">
-        <v>54426</v>
+        <v>49250</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>LARISSA DENISSE LOPEZ BURGOS</t>
+          <t>SUSAN ELIZABETH SOTO PIÑA</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>TEC MXL</t>
+          <t>SEND CUL</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>31-03-2026 20:18:54</t>
+          <t>26-03-2026 13:42:06</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1504,14 +1506,14 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>499</v>
+        <v>399</v>
       </c>
       <c r="M16" t="n">
         <v>11</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>26-03-2027 20:18:54</t>
+          <t>21-03-2027 13:42:06</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -1520,7 +1522,7 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>91270</v>
+        <v>2308</v>
       </c>
       <c r="Q16" t="inlineStr"/>
     </row>
@@ -1529,27 +1531,27 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>100331</v>
+        <v>99846</v>
       </c>
       <c r="C17" t="n">
-        <v>22791</v>
+        <v>253406</v>
       </c>
       <c r="D17" t="n">
-        <v>21685</v>
+        <v>50910</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>JUAN JOSE  PACHECO  FLORES</t>
+          <t>BRISEIDA ISABEL ENRIQUEZ ZEPEDA</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>CARROUSEL TJ</t>
+          <t>PAPALOTE TJ</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>28-04-2026 13:00:52</t>
+          <t>20-04-2026 21:29:56</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1571,21 +1573,23 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>399</v>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>Indefinido</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
+        <v>499</v>
+      </c>
+      <c r="M17" t="n">
+        <v>11</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>15-04-2027 21:29:56</t>
+        </is>
+      </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Recurrente</t>
+          <t>Domiciliado</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>79141</v>
+        <v>79273</v>
       </c>
       <c r="Q17" t="inlineStr"/>
     </row>
@@ -1594,27 +1598,27 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>100499</v>
+        <v>98454</v>
       </c>
       <c r="C18" t="n">
-        <v>79792</v>
+        <v>65078</v>
       </c>
       <c r="D18" t="n">
-        <v>77591</v>
+        <v>62916</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>CHRISTIAN PRISCILA CARDONA BANDA</t>
+          <t>ALEJANDRO MAGALLAN  LOPEZ</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>STA CATARINA</t>
+          <t>SEND CUL</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>01-05-2026 16:18:47</t>
+          <t>02-04-2026 7:19:31</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1632,18 +1636,18 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>NUEVO</t>
+          <t>RENOVACIÓN</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>549</v>
+        <v>350</v>
       </c>
       <c r="M18" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>26-04-2027 16:18:47</t>
+          <t>29-09-2026 7:19:31</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -1651,7 +1655,9 @@
           <t>Domiciliado</t>
         </is>
       </c>
-      <c r="P18" t="inlineStr"/>
+      <c r="P18" t="n">
+        <v>76842</v>
+      </c>
       <c r="Q18" t="inlineStr"/>
     </row>
     <row r="19">
@@ -1659,34 +1665,34 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>100514</v>
+        <v>98465</v>
       </c>
       <c r="C19" t="n">
-        <v>361054</v>
+        <v>312044</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>03219</t>
+          <t>09543</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>ALAN IGNACIO  CORTES HERNANDEZ</t>
+          <t>NIRVANA FERNANDA  SALADO  SANCHEZ</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>SALTILLO VILLALTA</t>
+          <t>MISION ENS</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>02-05-2026 7:36:52</t>
+          <t>02-04-2026 11:24:30</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>02-06-2026 23:59:59</t>
+          <t>01-06-2026 23:59:59</t>
         </is>
       </c>
       <c r="I19" t="n">
@@ -1699,18 +1705,18 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>NUEVO</t>
+          <t>RENOVACIÓN</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>649</v>
+        <v>499</v>
       </c>
       <c r="M19" t="n">
         <v>11</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>27-04-2027 7:36:52</t>
+          <t>28-03-2027 11:24:30</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -1718,7 +1724,9 @@
           <t>Domiciliado</t>
         </is>
       </c>
-      <c r="P19" t="inlineStr"/>
+      <c r="P19" t="n">
+        <v>76811</v>
+      </c>
       <c r="Q19" t="inlineStr"/>
     </row>
     <row r="20">
@@ -1726,27 +1734,27 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>97892</v>
+        <v>100487</v>
       </c>
       <c r="C20" t="n">
-        <v>151685</v>
+        <v>48666</v>
       </c>
       <c r="D20" t="n">
-        <v>49250</v>
+        <v>46524</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>SUSAN ELIZABETH SOTO PIÑA</t>
+          <t>ANA LUISA  HERNANDEZ  BELTRAN</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>SEND CUL</t>
+          <t>AZAHARES CUL</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>26-03-2026 13:42:06</t>
+          <t>01-05-2026 10:01:13</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1764,18 +1772,18 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>RENOVACIÓN</t>
+          <t>NUEVO</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>399</v>
+        <v>549</v>
       </c>
       <c r="M20" t="n">
         <v>11</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>21-03-2027 13:42:06</t>
+          <t>26-04-2027 10:01:13</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -1783,9 +1791,7 @@
           <t>Domiciliado</t>
         </is>
       </c>
-      <c r="P20" t="n">
-        <v>2308</v>
-      </c>
+      <c r="P20" t="inlineStr"/>
       <c r="Q20" t="inlineStr"/>
     </row>
     <row r="21">
@@ -1793,27 +1799,27 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>99846</v>
+        <v>100494</v>
       </c>
       <c r="C21" t="n">
-        <v>253406</v>
+        <v>346010</v>
       </c>
       <c r="D21" t="n">
-        <v>50910</v>
+        <v>88175</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>BRISEIDA ISABEL ENRIQUEZ ZEPEDA</t>
+          <t>ANA FABIOLA FLORES CARMONA</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>PAPALOTE TJ</t>
+          <t>PASEO 2000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>20-04-2026 21:29:56</t>
+          <t>01-05-2026 11:54:51</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1831,18 +1837,18 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>RENOVACIÓN</t>
+          <t>NUEVO</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>499</v>
+        <v>999</v>
       </c>
       <c r="M21" t="n">
         <v>11</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>15-04-2027 21:29:56</t>
+          <t>26-04-2027 11:54:51</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -1850,9 +1856,7 @@
           <t>Domiciliado</t>
         </is>
       </c>
-      <c r="P21" t="n">
-        <v>79273</v>
-      </c>
+      <c r="P21" t="inlineStr"/>
       <c r="Q21" t="inlineStr"/>
     </row>
     <row r="22">
@@ -1860,29 +1864,27 @@
         <v>20</v>
       </c>
       <c r="B22" t="n">
-        <v>100489</v>
+        <v>100501</v>
       </c>
       <c r="C22" t="n">
-        <v>360888</v>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>03053</t>
-        </is>
+        <v>347090</v>
+      </c>
+      <c r="D22" t="n">
+        <v>89255</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>MARA FERNANDA LUNA MENDOZA</t>
+          <t>GUILLERMO GERARDO VAZQUEZ GARCIA</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>VILLA VERDE</t>
+          <t>SEND MXL</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>01-05-2026 10:38:33</t>
+          <t>01-05-2026 16:31:24</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1904,17 +1906,19 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>649</v>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>Indefinido</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
+        <v>549</v>
+      </c>
+      <c r="M22" t="n">
+        <v>11</v>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>26-04-2027 16:31:24</t>
+        </is>
+      </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Recurrente</t>
+          <t>Domiciliado</t>
         </is>
       </c>
       <c r="P22" t="inlineStr"/>
@@ -1925,27 +1929,27 @@
         <v>21</v>
       </c>
       <c r="B23" t="n">
-        <v>100491</v>
+        <v>100512</v>
       </c>
       <c r="C23" t="n">
-        <v>56971</v>
+        <v>140437</v>
       </c>
       <c r="D23" t="n">
-        <v>54822</v>
+        <v>38064</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>NOEMI  RAMOS  DE LEON</t>
+          <t>JUAN  FLORES  FELIX</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>CARROUSEL TJ</t>
+          <t>AZAHARES CUL</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>01-05-2026 11:15:25</t>
+          <t>01-05-2026 20:54:12</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1970,11 +1974,11 @@
         <v>449</v>
       </c>
       <c r="M23" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>26-04-2027 11:15:25</t>
+          <t>28-10-2026 20:54:12</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -1983,7 +1987,7 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>68495</v>
+        <v>55808</v>
       </c>
       <c r="Q23" t="inlineStr"/>
     </row>
@@ -1992,34 +1996,32 @@
         <v>22</v>
       </c>
       <c r="B24" t="n">
-        <v>100508</v>
+        <v>99047</v>
       </c>
       <c r="C24" t="n">
-        <v>361018</v>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>03183</t>
-        </is>
+        <v>38715</v>
+      </c>
+      <c r="D24" t="n">
+        <v>36587</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>DENIS LILIANA AMEZCUA CRUZ</t>
+          <t>ELOINA  REYNOSO  TERRONES</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>CARROUSEL TJ</t>
+          <t>PABELLON RTO</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>01-05-2026 19:13:51</t>
+          <t>10-04-2026 15:14:18</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>01-06-2026 23:59:59</t>
+          <t>02-06-2026 23:59:59</t>
         </is>
       </c>
       <c r="I24" t="n">
@@ -2032,11 +2034,11 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>NUEVO</t>
+          <t>RENOVACIÓN</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>649</v>
+        <v>399</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
@@ -2049,7 +2051,9 @@
           <t>Recurrente</t>
         </is>
       </c>
-      <c r="P24" t="inlineStr"/>
+      <c r="P24" t="n">
+        <v>57290</v>
+      </c>
       <c r="Q24" t="inlineStr"/>
     </row>
     <row r="25">
@@ -2057,29 +2061,27 @@
         <v>23</v>
       </c>
       <c r="B25" t="n">
-        <v>98466</v>
+        <v>100177</v>
       </c>
       <c r="C25" t="n">
-        <v>205081</v>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>02589</t>
-        </is>
+        <v>194060</v>
+      </c>
+      <c r="D25" t="n">
+        <v>91567</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>ISRAEL CRESPO RIOS</t>
+          <t>ELISA ELENA PAREDES HERNANDEZ</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>MISION ENS</t>
+          <t>TEC MXL</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>02-04-2026 11:27:04</t>
+          <t>27-04-2026 8:15:35</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2103,21 +2105,19 @@
       <c r="L25" t="n">
         <v>499</v>
       </c>
-      <c r="M25" t="n">
-        <v>11</v>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>28-03-2027 11:27:04</t>
-        </is>
-      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr">
         <is>
-          <t>Domiciliado</t>
+          <t>Recurrente</t>
         </is>
       </c>
       <c r="P25" t="n">
-        <v>76809</v>
+        <v>4813</v>
       </c>
       <c r="Q25" t="inlineStr"/>
     </row>
@@ -2126,27 +2126,27 @@
         <v>24</v>
       </c>
       <c r="B26" t="n">
-        <v>98583</v>
+        <v>100443</v>
       </c>
       <c r="C26" t="n">
-        <v>114721</v>
+        <v>354766</v>
       </c>
       <c r="D26" t="n">
-        <v>12446</v>
+        <v>96930</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>JESUS ANTONIO ABRIL CAMPOS</t>
+          <t>JESUS ORLANDO OROZCO SEGOVIA</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>SAN LUIS</t>
+          <t>SEND MXL</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>06-04-2026 5:30:30</t>
+          <t>30-04-2026 8:06:02</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2164,26 +2164,26 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>RENOVACIÓN</t>
+          <t>NUEVO</t>
         </is>
       </c>
       <c r="L26" t="n">
-        <v>399</v>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>Indefinido</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
+        <v>549</v>
+      </c>
+      <c r="M26" t="n">
+        <v>11</v>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>25-04-2027 8:06:02</t>
+        </is>
+      </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>Recurrente</t>
-        </is>
-      </c>
-      <c r="P26" t="n">
-        <v>11835</v>
-      </c>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr"/>
       <c r="Q26" t="inlineStr"/>
     </row>
     <row r="27">
@@ -2191,27 +2191,27 @@
         <v>25</v>
       </c>
       <c r="B27" t="n">
-        <v>99840</v>
+        <v>100484</v>
       </c>
       <c r="C27" t="n">
-        <v>178067</v>
+        <v>42885</v>
       </c>
       <c r="D27" t="n">
-        <v>75574</v>
+        <v>40755</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>ALMA ANGELICA  PEREZ  MIRANDA</t>
+          <t>LUZ ADRIANA ALARCON  GONZALEZ</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>SANTA FE</t>
+          <t>PASEO 2000</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>20-04-2026 20:14:31</t>
+          <t>01-05-2026 8:55:06</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2229,11 +2229,11 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>RENOVACIÓN</t>
+          <t>NUEVO</t>
         </is>
       </c>
       <c r="L27" t="n">
-        <v>449</v>
+        <v>649</v>
       </c>
       <c r="M27" t="inlineStr">
         <is>
@@ -2246,9 +2246,7 @@
           <t>Recurrente</t>
         </is>
       </c>
-      <c r="P27" t="n">
-        <v>74406</v>
-      </c>
+      <c r="P27" t="inlineStr"/>
       <c r="Q27" t="inlineStr"/>
     </row>
     <row r="28">
@@ -2256,27 +2254,29 @@
         <v>26</v>
       </c>
       <c r="B28" t="n">
-        <v>100487</v>
+        <v>100486</v>
       </c>
       <c r="C28" t="n">
-        <v>48666</v>
-      </c>
-      <c r="D28" t="n">
-        <v>46524</v>
+        <v>360869</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>03034</t>
+        </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>ANA LUISA  HERNANDEZ  BELTRAN</t>
+          <t>JOANNA VILLEGAS ORTIZ</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>AZAHARES CUL</t>
+          <t>MISION ENS</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>01-05-2026 10:01:13</t>
+          <t>01-05-2026 9:43:16</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2298,19 +2298,17 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>549</v>
-      </c>
-      <c r="M28" t="n">
-        <v>11</v>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>26-04-2027 10:01:13</t>
-        </is>
-      </c>
+        <v>649</v>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr">
         <is>
-          <t>Domiciliado</t>
+          <t>Recurrente</t>
         </is>
       </c>
       <c r="P28" t="inlineStr"/>
@@ -2321,27 +2319,27 @@
         <v>27</v>
       </c>
       <c r="B29" t="n">
-        <v>100494</v>
+        <v>100509</v>
       </c>
       <c r="C29" t="n">
-        <v>346010</v>
+        <v>141351</v>
       </c>
       <c r="D29" t="n">
-        <v>88175</v>
+        <v>38969</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>ANA FABIOLA FLORES CARMONA</t>
+          <t>JESUS ABELARDO RODRIGUEZ NAVARRO</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>PASEO 2000</t>
+          <t>CARROUSEL TJ</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>01-05-2026 11:54:51</t>
+          <t>01-05-2026 20:01:10</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2359,18 +2357,18 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>NUEVO</t>
+          <t>RENOVACIÓN</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>999</v>
+        <v>699</v>
       </c>
       <c r="M29" t="n">
         <v>11</v>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>26-04-2027 11:54:51</t>
+          <t>26-04-2027 20:01:10</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
@@ -2378,7 +2376,9 @@
           <t>Domiciliado</t>
         </is>
       </c>
-      <c r="P29" t="inlineStr"/>
+      <c r="P29" t="n">
+        <v>76258</v>
+      </c>
       <c r="Q29" t="inlineStr"/>
     </row>
     <row r="30">
@@ -2386,27 +2386,29 @@
         <v>28</v>
       </c>
       <c r="B30" t="n">
-        <v>100501</v>
+        <v>100511</v>
       </c>
       <c r="C30" t="n">
-        <v>347090</v>
-      </c>
-      <c r="D30" t="n">
-        <v>89255</v>
+        <v>361026</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>03191</t>
+        </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>GUILLERMO GERARDO VAZQUEZ GARCIA</t>
+          <t>HILARY MONROY MORENO</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>SEND MXL</t>
+          <t>CARROUSEL TJ</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>01-05-2026 16:31:24</t>
+          <t>01-05-2026 20:07:30</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2428,19 +2430,17 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>549</v>
-      </c>
-      <c r="M30" t="n">
-        <v>11</v>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>26-04-2027 16:31:24</t>
-        </is>
-      </c>
+        <v>649</v>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr">
         <is>
-          <t>Domiciliado</t>
+          <t>Recurrente</t>
         </is>
       </c>
       <c r="P30" t="inlineStr"/>
@@ -2451,32 +2451,32 @@
         <v>29</v>
       </c>
       <c r="B31" t="n">
-        <v>100512</v>
+        <v>100518</v>
       </c>
       <c r="C31" t="n">
-        <v>140437</v>
+        <v>348102</v>
       </c>
       <c r="D31" t="n">
-        <v>38064</v>
+        <v>90267</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>JUAN  FLORES  FELIX</t>
+          <t>CHRISTIAN IVETTE MARTINEZ  MORALES</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>AZAHARES CUL</t>
+          <t>SEND SALTILLO</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>01-05-2026 20:54:12</t>
+          <t>02-05-2026 10:06:29</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>04-06-2026 23:59:59</t>
+          <t>03-06-2026 23:59:59</t>
         </is>
       </c>
       <c r="I31" t="n">
@@ -2493,14 +2493,14 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>449</v>
+        <v>549</v>
       </c>
       <c r="M31" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>28-10-2026 20:54:12</t>
+          <t>27-04-2027 10:06:29</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
@@ -2509,7 +2509,7 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>55808</v>
+        <v>95767</v>
       </c>
       <c r="Q31" t="inlineStr"/>
     </row>
@@ -2518,40 +2518,40 @@
         <v>30</v>
       </c>
       <c r="B32" t="n">
-        <v>98454</v>
+        <v>95940</v>
       </c>
       <c r="C32" t="n">
-        <v>65078</v>
+        <v>95151</v>
       </c>
       <c r="D32" t="n">
-        <v>62916</v>
+        <v>92910</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>ALEJANDRO MAGALLAN  LOPEZ</t>
+          <t>ANGELICA DEYANIRA SERRANO VALDEZ</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>SEND CUL</t>
+          <t>PASEO 2000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>02-04-2026 7:19:31</t>
+          <t>04-03-2026 15:59:55</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>01-06-2026 23:59:59</t>
+          <t>03-05-2026 23:59:59</t>
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Sin filtro</t>
+          <t>Activado</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2560,14 +2560,14 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>350</v>
+        <v>499</v>
       </c>
       <c r="M32" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>29-09-2026 7:19:31</t>
+          <t>27-02-2027 15:59:55</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
@@ -2576,7 +2576,7 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>76842</v>
+        <v>52003</v>
       </c>
       <c r="Q32" t="inlineStr"/>
     </row>
@@ -2585,29 +2585,27 @@
         <v>31</v>
       </c>
       <c r="B33" t="n">
-        <v>98465</v>
+        <v>99080</v>
       </c>
       <c r="C33" t="n">
-        <v>312044</v>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>09543</t>
-        </is>
+        <v>326105</v>
+      </c>
+      <c r="D33" t="n">
+        <v>23044</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>NIRVANA FERNANDA  SALADO  SANCHEZ</t>
+          <t>MONICA DANIELA  ORDUÑO PEREZ</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>MISION ENS</t>
+          <t>SEND CUL</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>02-04-2026 11:24:30</t>
+          <t>11-04-2026 10:17:07</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2629,23 +2627,21 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>499</v>
-      </c>
-      <c r="M33" t="n">
-        <v>11</v>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>28-03-2027 11:24:30</t>
-        </is>
-      </c>
+        <v>599</v>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="O33" t="inlineStr">
         <is>
-          <t>Domiciliado</t>
+          <t>Recurrente</t>
         </is>
       </c>
       <c r="P33" t="n">
-        <v>76811</v>
+        <v>83122</v>
       </c>
       <c r="Q33" t="inlineStr"/>
     </row>
@@ -2654,32 +2650,34 @@
         <v>32</v>
       </c>
       <c r="B34" t="n">
-        <v>95940</v>
+        <v>98466</v>
       </c>
       <c r="C34" t="n">
-        <v>95151</v>
-      </c>
-      <c r="D34" t="n">
-        <v>92910</v>
+        <v>205081</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>02589</t>
+        </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>ANGELICA DEYANIRA SERRANO VALDEZ</t>
+          <t>ISRAEL CRESPO RIOS</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>PASEO 2000</t>
+          <t>MISION ENS</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>04-03-2026 15:59:55</t>
+          <t>02-04-2026 11:27:04</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>03-05-2026 23:59:59</t>
+          <t>01-06-2026 23:59:59</t>
         </is>
       </c>
       <c r="I34" t="n">
@@ -2703,7 +2701,7 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>27-02-2027 15:59:55</t>
+          <t>28-03-2027 11:27:04</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
@@ -2712,7 +2710,7 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>52003</v>
+        <v>76809</v>
       </c>
       <c r="Q34" t="inlineStr"/>
     </row>
@@ -2721,32 +2719,32 @@
         <v>33</v>
       </c>
       <c r="B35" t="n">
-        <v>100177</v>
+        <v>98517</v>
       </c>
       <c r="C35" t="n">
-        <v>194060</v>
+        <v>232630</v>
       </c>
       <c r="D35" t="n">
-        <v>91567</v>
+        <v>30135</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>ELISA ELENA PAREDES HERNANDEZ</t>
+          <t>JULIO CESAR VERDE  MANJARRES</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>TEC MXL</t>
+          <t>CARROUSEL TJ</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>27-04-2026 8:15:35</t>
+          <t>03-04-2026 10:04:26</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>01-06-2026 23:59:59</t>
+          <t>02-06-2026 23:59:59</t>
         </is>
       </c>
       <c r="I35" t="n">
@@ -2763,21 +2761,23 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>499</v>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>Indefinido</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
+        <v>449</v>
+      </c>
+      <c r="M35" t="n">
+        <v>5</v>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>30-09-2026 10:04:26</t>
+        </is>
+      </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>Recurrente</t>
+          <t>Domiciliado</t>
         </is>
       </c>
       <c r="P35" t="n">
-        <v>4813</v>
+        <v>49260</v>
       </c>
       <c r="Q35" t="inlineStr"/>
     </row>
@@ -2786,27 +2786,27 @@
         <v>34</v>
       </c>
       <c r="B36" t="n">
-        <v>100443</v>
+        <v>98583</v>
       </c>
       <c r="C36" t="n">
-        <v>354766</v>
+        <v>114721</v>
       </c>
       <c r="D36" t="n">
-        <v>96930</v>
+        <v>12446</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>JESUS ORLANDO OROZCO SEGOVIA</t>
+          <t>JESUS ANTONIO ABRIL CAMPOS</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>SEND MXL</t>
+          <t>SAN LUIS</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>30-04-2026 8:06:02</t>
+          <t>06-04-2026 5:30:30</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2824,26 +2824,26 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>NUEVO</t>
+          <t>RENOVACIÓN</t>
         </is>
       </c>
       <c r="L36" t="n">
-        <v>549</v>
-      </c>
-      <c r="M36" t="n">
-        <v>11</v>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>25-04-2027 8:06:02</t>
-        </is>
-      </c>
+        <v>399</v>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="O36" t="inlineStr">
         <is>
-          <t>Domiciliado</t>
-        </is>
-      </c>
-      <c r="P36" t="inlineStr"/>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P36" t="n">
+        <v>11835</v>
+      </c>
       <c r="Q36" t="inlineStr"/>
     </row>
     <row r="37">
@@ -2851,32 +2851,32 @@
         <v>35</v>
       </c>
       <c r="B37" t="n">
-        <v>100484</v>
+        <v>99889</v>
       </c>
       <c r="C37" t="n">
-        <v>42885</v>
+        <v>17586</v>
       </c>
       <c r="D37" t="n">
-        <v>40755</v>
+        <v>16499</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>LUZ ADRIANA ALARCON  GONZALEZ</t>
+          <t>ERIKA ADRIANA BERMUDEZ TALAVERA</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>PASEO 2000</t>
+          <t>MISION ENS</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>01-05-2026 8:55:06</t>
+          <t>21-04-2026 13:14:32</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>01-06-2026 23:59:59</t>
+          <t>02-06-2026 23:59:59</t>
         </is>
       </c>
       <c r="I37" t="n">
@@ -2889,24 +2889,28 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>NUEVO</t>
+          <t>RENOVACIÓN</t>
         </is>
       </c>
       <c r="L37" t="n">
-        <v>649</v>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>Indefinido</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
+        <v>499</v>
+      </c>
+      <c r="M37" t="n">
+        <v>11</v>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>16-04-2027 13:14:32</t>
+        </is>
+      </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>Recurrente</t>
-        </is>
-      </c>
-      <c r="P37" t="inlineStr"/>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P37" t="n">
+        <v>95586</v>
+      </c>
       <c r="Q37" t="inlineStr"/>
     </row>
     <row r="38">
@@ -2914,34 +2918,32 @@
         <v>36</v>
       </c>
       <c r="B38" t="n">
-        <v>100486</v>
+        <v>100457</v>
       </c>
       <c r="C38" t="n">
-        <v>360869</v>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>03034</t>
-        </is>
+        <v>98076</v>
+      </c>
+      <c r="D38" t="n">
+        <v>95835</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>JOANNA VILLEGAS ORTIZ</t>
+          <t>NORA FERNANDA CORTES MATUS</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>MISION ENS</t>
+          <t>SEND CUL</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>01-05-2026 9:43:16</t>
+          <t>30-04-2026 16:15:54</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>01-06-2026 23:59:59</t>
+          <t>03-06-2026 23:59:59</t>
         </is>
       </c>
       <c r="I38" t="n">
@@ -2954,7 +2956,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>NUEVO</t>
+          <t>RENOVACIÓN</t>
         </is>
       </c>
       <c r="L38" t="n">
@@ -2971,7 +2973,9 @@
           <t>Recurrente</t>
         </is>
       </c>
-      <c r="P38" t="inlineStr"/>
+      <c r="P38" t="n">
+        <v>91561</v>
+      </c>
       <c r="Q38" t="inlineStr"/>
     </row>
     <row r="39">
@@ -2979,27 +2983,29 @@
         <v>37</v>
       </c>
       <c r="B39" t="n">
-        <v>100509</v>
+        <v>100489</v>
       </c>
       <c r="C39" t="n">
-        <v>141351</v>
-      </c>
-      <c r="D39" t="n">
-        <v>38969</v>
+        <v>360888</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>03053</t>
+        </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>JESUS ABELARDO RODRIGUEZ NAVARRO</t>
+          <t>MARA FERNANDA LUNA MENDOZA</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>CARROUSEL TJ</t>
+          <t>VILLA VERDE</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>01-05-2026 20:01:10</t>
+          <t>01-05-2026 10:38:33</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -3017,28 +3023,24 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>RENOVACIÓN</t>
+          <t>NUEVO</t>
         </is>
       </c>
       <c r="L39" t="n">
-        <v>699</v>
-      </c>
-      <c r="M39" t="n">
-        <v>11</v>
-      </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>26-04-2027 20:01:10</t>
-        </is>
-      </c>
+        <v>649</v>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="O39" t="inlineStr">
         <is>
-          <t>Domiciliado</t>
-        </is>
-      </c>
-      <c r="P39" t="n">
-        <v>76258</v>
-      </c>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr"/>
       <c r="Q39" t="inlineStr"/>
     </row>
     <row r="40">
@@ -3046,19 +3048,17 @@
         <v>38</v>
       </c>
       <c r="B40" t="n">
-        <v>100511</v>
+        <v>100491</v>
       </c>
       <c r="C40" t="n">
-        <v>361026</v>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>03191</t>
-        </is>
+        <v>56971</v>
+      </c>
+      <c r="D40" t="n">
+        <v>54822</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>HILARY MONROY MORENO</t>
+          <t>NOEMI  RAMOS  DE LEON</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -3068,12 +3068,12 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>01-05-2026 20:07:30</t>
+          <t>01-05-2026 11:15:25</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>01-06-2026 23:59:59</t>
+          <t>04-06-2026 23:59:59</t>
         </is>
       </c>
       <c r="I40" t="n">
@@ -3086,24 +3086,28 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>NUEVO</t>
+          <t>RENOVACIÓN</t>
         </is>
       </c>
       <c r="L40" t="n">
-        <v>649</v>
-      </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>Indefinido</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
+        <v>449</v>
+      </c>
+      <c r="M40" t="n">
+        <v>11</v>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>26-04-2027 11:15:25</t>
+        </is>
+      </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>Recurrente</t>
-        </is>
-      </c>
-      <c r="P40" t="inlineStr"/>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P40" t="n">
+        <v>68495</v>
+      </c>
       <c r="Q40" t="inlineStr"/>
     </row>
     <row r="41">
@@ -3111,27 +3115,29 @@
         <v>39</v>
       </c>
       <c r="B41" t="n">
-        <v>99080</v>
+        <v>100508</v>
       </c>
       <c r="C41" t="n">
-        <v>326105</v>
-      </c>
-      <c r="D41" t="n">
-        <v>23044</v>
+        <v>361018</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>03183</t>
+        </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>MONICA DANIELA  ORDUÑO PEREZ</t>
+          <t>DENIS LILIANA AMEZCUA CRUZ</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>SEND CUL</t>
+          <t>CARROUSEL TJ</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>11-04-2026 10:17:07</t>
+          <t>01-05-2026 19:13:51</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3149,11 +3155,11 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>RENOVACIÓN</t>
+          <t>NUEVO</t>
         </is>
       </c>
       <c r="L41" t="n">
-        <v>599</v>
+        <v>649</v>
       </c>
       <c r="M41" t="inlineStr">
         <is>
@@ -3166,9 +3172,7 @@
           <t>Recurrente</t>
         </is>
       </c>
-      <c r="P41" t="n">
-        <v>83122</v>
-      </c>
+      <c r="P41" t="inlineStr"/>
       <c r="Q41" t="inlineStr"/>
     </row>
     <row r="42">
@@ -3176,34 +3180,32 @@
         <v>40</v>
       </c>
       <c r="B42" t="n">
-        <v>100480</v>
+        <v>100523</v>
       </c>
       <c r="C42" t="n">
-        <v>360840</v>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>03005</t>
-        </is>
+        <v>177956</v>
+      </c>
+      <c r="D42" t="n">
+        <v>75463</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>TANIA ELIZABETH VILLAREAL PEREDA</t>
+          <t>LUIS DAVID ROSAS  ALONSO</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>INSURGENTES</t>
+          <t>PASEO 2000</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>01-05-2026 7:38:40</t>
+          <t>02-05-2026 13:24:03</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>01-08-2026 23:59:59</t>
+          <t>02-06-2026 23:59:59</t>
         </is>
       </c>
       <c r="I42" t="n">
@@ -3216,24 +3218,28 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>NUEVO</t>
+          <t>RENOVACIÓN</t>
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1549</v>
-      </c>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>Indefinido</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr"/>
+        <v>499</v>
+      </c>
+      <c r="M42" t="n">
+        <v>11</v>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>27-04-2027 13:24:03</t>
+        </is>
+      </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>Recurrente</t>
-        </is>
-      </c>
-      <c r="P42" t="inlineStr"/>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P42" t="n">
+        <v>4701</v>
+      </c>
       <c r="Q42" t="inlineStr"/>
     </row>
     <row r="43">
@@ -3241,29 +3247,27 @@
         <v>41</v>
       </c>
       <c r="B43" t="n">
-        <v>100483</v>
+        <v>99840</v>
       </c>
       <c r="C43" t="n">
-        <v>360852</v>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>03017</t>
-        </is>
+        <v>178067</v>
+      </c>
+      <c r="D43" t="n">
+        <v>75574</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>ELIUD RAMIREZ BELMARES</t>
+          <t>ALMA ANGELICA  PEREZ  MIRANDA</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>SALTILLO VILLALTA</t>
+          <t>SANTA FE</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>01-05-2026 8:37:34</t>
+          <t>20-04-2026 20:14:31</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3281,26 +3285,26 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>NUEVO</t>
+          <t>RENOVACIÓN</t>
         </is>
       </c>
       <c r="L43" t="n">
-        <v>649</v>
-      </c>
-      <c r="M43" t="n">
-        <v>11</v>
-      </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>26-04-2027 8:37:34</t>
-        </is>
-      </c>
+        <v>449</v>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="O43" t="inlineStr">
         <is>
-          <t>Domiciliado</t>
-        </is>
-      </c>
-      <c r="P43" t="inlineStr"/>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P43" t="n">
+        <v>74406</v>
+      </c>
       <c r="Q43" t="inlineStr"/>
     </row>
     <row r="44">
@@ -3308,34 +3312,32 @@
         <v>42</v>
       </c>
       <c r="B44" t="n">
-        <v>100515</v>
+        <v>98369</v>
       </c>
       <c r="C44" t="n">
-        <v>361056</v>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>03221</t>
-        </is>
+        <v>56575</v>
+      </c>
+      <c r="D44" t="n">
+        <v>54426</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>GILBERTO  BARRIOS HERNANDEZ</t>
+          <t>LARISSA DENISSE LOPEZ BURGOS</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>SALTILLO VILLALTA</t>
+          <t>TEC MXL</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>02-05-2026 7:46:19</t>
+          <t>31-03-2026 20:18:54</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>02-06-2026 23:59:59</t>
+          <t>01-06-2026 23:59:59</t>
         </is>
       </c>
       <c r="I44" t="n">
@@ -3348,18 +3350,18 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>NUEVO</t>
+          <t>RENOVACIÓN</t>
         </is>
       </c>
       <c r="L44" t="n">
-        <v>649</v>
+        <v>499</v>
       </c>
       <c r="M44" t="n">
         <v>11</v>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>27-04-2027 7:46:19</t>
+          <t>26-03-2027 20:18:54</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
@@ -3367,7 +3369,9 @@
           <t>Domiciliado</t>
         </is>
       </c>
-      <c r="P44" t="inlineStr"/>
+      <c r="P44" t="n">
+        <v>91270</v>
+      </c>
       <c r="Q44" t="inlineStr"/>
     </row>
     <row r="45">
@@ -3375,32 +3379,32 @@
         <v>43</v>
       </c>
       <c r="B45" t="n">
-        <v>98943</v>
+        <v>98418</v>
       </c>
       <c r="C45" t="n">
-        <v>37106</v>
+        <v>346832</v>
       </c>
       <c r="D45" t="n">
-        <v>34985</v>
+        <v>88997</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>JUAN FRANCISCO PITONES NORIEGA</t>
+          <t>KARLA BERENICE GONZALEZ ESPINDOLA</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>SEND MXL</t>
+          <t>TLALNEPANTLA</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>08-04-2026 20:42:26</t>
+          <t>01-04-2026 17:36:56</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>01-06-2026 23:59:59</t>
+          <t>03-06-2026 23:59:59</t>
         </is>
       </c>
       <c r="I45" t="n">
@@ -3417,21 +3421,23 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>399</v>
-      </c>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>Indefinido</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
+        <v>549</v>
+      </c>
+      <c r="M45" t="n">
+        <v>11</v>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>27-03-2027 17:36:56</t>
+        </is>
+      </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>Recurrente</t>
+          <t>Domiciliado</t>
         </is>
       </c>
       <c r="P45" t="n">
-        <v>96274</v>
+        <v>95789</v>
       </c>
       <c r="Q45" t="inlineStr"/>
     </row>
@@ -3440,32 +3446,32 @@
         <v>44</v>
       </c>
       <c r="B46" t="n">
-        <v>100497</v>
+        <v>99890</v>
       </c>
       <c r="C46" t="n">
-        <v>179725</v>
+        <v>34927</v>
       </c>
       <c r="D46" t="n">
-        <v>77232</v>
+        <v>32841</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>EBER  MAGDIEL  CASTILLEJA  BARROSO</t>
+          <t>LILIAN RUVALCABA FIGUEROA</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>SEND SALTILLO</t>
+          <t>MISION ENS</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>01-05-2026 15:17:21</t>
+          <t>21-04-2026 13:16:43</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>01-06-2026 23:59:59</t>
+          <t>02-06-2026 23:59:59</t>
         </is>
       </c>
       <c r="I46" t="n">
@@ -3489,41 +3495,1365 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
+          <t>16-04-2027 13:16:43</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P46" t="n">
+        <v>95584</v>
+      </c>
+      <c r="Q46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>45</v>
+      </c>
+      <c r="B47" t="n">
+        <v>100107</v>
+      </c>
+      <c r="C47" t="n">
+        <v>312465</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>09964</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>GUADALUPE  CASTRO ROSAS</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>SEND MXL</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>24-04-2026 15:34:48</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>02-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I47" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L47" t="n">
+        <v>549</v>
+      </c>
+      <c r="M47" t="n">
+        <v>5</v>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>21-10-2026 15:34:48</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P47" t="n">
+        <v>77036</v>
+      </c>
+      <c r="Q47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>46</v>
+      </c>
+      <c r="B48" t="n">
+        <v>100488</v>
+      </c>
+      <c r="C48" t="n">
+        <v>360887</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>03052</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>MARIA DEL CARMEN JIMENEZ SANCHEZ</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>SEND SALTILLO</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>01-05-2026 10:34:42</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>01-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L48" t="n">
+        <v>549</v>
+      </c>
+      <c r="M48" t="n">
+        <v>11</v>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>26-04-2027 10:34:42</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr"/>
+      <c r="Q48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>47</v>
+      </c>
+      <c r="B49" t="n">
+        <v>100490</v>
+      </c>
+      <c r="C49" t="n">
+        <v>360892</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>03057</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>ZARAKY RENE  ZENTENO  ORTIZ</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>IXTAPALUCA</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>01-05-2026 11:00:08</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>01-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I49" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L49" t="n">
+        <v>649</v>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr"/>
+      <c r="Q49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>48</v>
+      </c>
+      <c r="B50" t="n">
+        <v>100492</v>
+      </c>
+      <c r="C50" t="n">
+        <v>360904</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>03069</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>CARLA DANIELA MARTINEZ  GUILLEN</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>IXTAPALUCA</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>01-05-2026 11:42:18</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>01-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L50" t="n">
+        <v>549</v>
+      </c>
+      <c r="M50" t="n">
+        <v>11</v>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>26-04-2027 11:42:18</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr"/>
+      <c r="Q50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>49</v>
+      </c>
+      <c r="B51" t="n">
+        <v>100505</v>
+      </c>
+      <c r="C51" t="n">
+        <v>360757</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>02922</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>CARLOS EDUARDO  FLORES  SANCHEZ</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>SEND MXL</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>01-05-2026 18:17:42</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>01-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I51" t="n">
+        <v>0</v>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L51" t="n">
+        <v>549</v>
+      </c>
+      <c r="M51" t="n">
+        <v>11</v>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>26-04-2027 18:17:42</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr"/>
+      <c r="Q51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>50</v>
+      </c>
+      <c r="B52" t="n">
+        <v>100507</v>
+      </c>
+      <c r="C52" t="n">
+        <v>353643</v>
+      </c>
+      <c r="D52" t="n">
+        <v>95807</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>MINERVA  GONZALEZ  MACEDO</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>METEPEC</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>01-05-2026 18:32:13</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>01-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I52" t="n">
+        <v>0</v>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L52" t="n">
+        <v>649</v>
+      </c>
+      <c r="M52" t="n">
+        <v>11</v>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>26-04-2027 18:32:13</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr"/>
+      <c r="Q52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>51</v>
+      </c>
+      <c r="B53" t="n">
+        <v>100522</v>
+      </c>
+      <c r="C53" t="n">
+        <v>360630</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>02795</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>EDUARDO  GONZALES FLORES</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>SALTILLO VILLALTA</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>02-05-2026 13:13:57</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>02-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I53" t="n">
+        <v>0</v>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L53" t="n">
+        <v>549</v>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr"/>
+      <c r="Q53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>52</v>
+      </c>
+      <c r="B54" t="n">
+        <v>96317</v>
+      </c>
+      <c r="C54" t="n">
+        <v>340665</v>
+      </c>
+      <c r="D54" t="n">
+        <v>18483</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>MONICA ROXANA ALDUNCIN FLETCHER</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>METEPEC</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>09-03-2026 16:06:01</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>03-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I54" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L54" t="n">
+        <v>649</v>
+      </c>
+      <c r="M54" t="n">
+        <v>11</v>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>04-03-2027 16:06:01</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P54" t="n">
+        <v>91727</v>
+      </c>
+      <c r="Q54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>53</v>
+      </c>
+      <c r="B55" t="n">
+        <v>98557</v>
+      </c>
+      <c r="C55" t="n">
+        <v>312669</v>
+      </c>
+      <c r="D55" t="n">
+        <v>10168</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>ROBERTO SALAZAR</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>CARROUSEL TJ</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>04-04-2026 12:48:33</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>03-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I55" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L55" t="n">
+        <v>599</v>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr"/>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P55" t="n">
+        <v>77181</v>
+      </c>
+      <c r="Q55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>54</v>
+      </c>
+      <c r="B56" t="n">
+        <v>100493</v>
+      </c>
+      <c r="C56" t="n">
+        <v>360045</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>02210</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>BALTAZAR VILLASEÑOR  CRUZ</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>METEPEC</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>01-05-2026 11:51:52</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>01-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I56" t="n">
+        <v>0</v>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L56" t="n">
+        <v>799</v>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr"/>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr"/>
+      <c r="Q56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>55</v>
+      </c>
+      <c r="B57" t="n">
+        <v>100495</v>
+      </c>
+      <c r="C57" t="n">
+        <v>349026</v>
+      </c>
+      <c r="D57" t="n">
+        <v>91191</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>CESAR OMAR OBREGON ESTRELLLO</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>SALTILLO VILLALTA</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>01-05-2026 12:28:55</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>01-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I57" t="n">
+        <v>0</v>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L57" t="n">
+        <v>649</v>
+      </c>
+      <c r="M57" t="n">
+        <v>11</v>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>26-04-2027 12:28:55</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr"/>
+      <c r="Q57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>56</v>
+      </c>
+      <c r="B58" t="n">
+        <v>100502</v>
+      </c>
+      <c r="C58" t="n">
+        <v>205459</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>02967</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>ANTONIO  LAMAS IRINEO</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>SEND MXL</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>01-05-2026 17:19:17</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>30-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I58" t="n">
+        <v>0</v>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L58" t="n">
+        <v>399</v>
+      </c>
+      <c r="M58" t="n">
+        <v>5</v>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>28-10-2026 17:19:17</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P58" t="n">
+        <v>38806</v>
+      </c>
+      <c r="Q58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>57</v>
+      </c>
+      <c r="B59" t="n">
+        <v>100504</v>
+      </c>
+      <c r="C59" t="n">
+        <v>361003</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>03168</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>DEMIAN CORONADO LOPEZ</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>TEC MXL</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>01-05-2026 18:12:55</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>01-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I59" t="n">
+        <v>0</v>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L59" t="n">
+        <v>649</v>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr"/>
+      <c r="Q59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>58</v>
+      </c>
+      <c r="B60" t="n">
+        <v>99332</v>
+      </c>
+      <c r="C60" t="n">
+        <v>257916</v>
+      </c>
+      <c r="D60" t="n">
+        <v>55420</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>FELIPE ALFONSO GUERRERO INZUNZA</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>SEND CUL</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>14-04-2026 12:19:40</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>02-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I60" t="n">
+        <v>0</v>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L60" t="n">
+        <v>399</v>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr"/>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P60" t="n">
+        <v>73999</v>
+      </c>
+      <c r="Q60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>59</v>
+      </c>
+      <c r="B61" t="n">
+        <v>96322</v>
+      </c>
+      <c r="C61" t="n">
+        <v>340658</v>
+      </c>
+      <c r="D61" t="n">
+        <v>18476</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>MONICA BERALD BERMUDEZ ALDUCIN</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>METEPEC</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>09-03-2026 16:14:08</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>03-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I61" t="n">
+        <v>0</v>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L61" t="n">
+        <v>649</v>
+      </c>
+      <c r="M61" t="n">
+        <v>11</v>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>04-03-2027 16:14:08</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P61" t="n">
+        <v>91712</v>
+      </c>
+      <c r="Q61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>60</v>
+      </c>
+      <c r="B62" t="n">
+        <v>100480</v>
+      </c>
+      <c r="C62" t="n">
+        <v>360840</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>03005</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>TANIA ELIZABETH VILLAREAL PEREDA</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>INSURGENTES</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>01-05-2026 7:38:40</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>01-08-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I62" t="n">
+        <v>0</v>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L62" t="n">
+        <v>1549</v>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr"/>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr"/>
+      <c r="Q62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>61</v>
+      </c>
+      <c r="B63" t="n">
+        <v>100483</v>
+      </c>
+      <c r="C63" t="n">
+        <v>360852</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>03017</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>ELIUD RAMIREZ BELMARES</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>SALTILLO VILLALTA</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>01-05-2026 8:37:34</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>01-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I63" t="n">
+        <v>0</v>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L63" t="n">
+        <v>649</v>
+      </c>
+      <c r="M63" t="n">
+        <v>11</v>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>26-04-2027 8:37:34</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr"/>
+      <c r="Q63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>62</v>
+      </c>
+      <c r="B64" t="n">
+        <v>100515</v>
+      </c>
+      <c r="C64" t="n">
+        <v>361056</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>03221</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>GILBERTO  BARRIOS HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>SALTILLO VILLALTA</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>02-05-2026 7:46:19</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>02-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I64" t="n">
+        <v>0</v>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L64" t="n">
+        <v>649</v>
+      </c>
+      <c r="M64" t="n">
+        <v>11</v>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>27-04-2027 7:46:19</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr"/>
+      <c r="Q64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>63</v>
+      </c>
+      <c r="B65" t="n">
+        <v>98943</v>
+      </c>
+      <c r="C65" t="n">
+        <v>37106</v>
+      </c>
+      <c r="D65" t="n">
+        <v>34985</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>JUAN FRANCISCO PITONES NORIEGA</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>SEND MXL</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>08-04-2026 20:42:26</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>01-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I65" t="n">
+        <v>0</v>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L65" t="n">
+        <v>399</v>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr"/>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P65" t="n">
+        <v>96274</v>
+      </c>
+      <c r="Q65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>64</v>
+      </c>
+      <c r="B66" t="n">
+        <v>100497</v>
+      </c>
+      <c r="C66" t="n">
+        <v>179725</v>
+      </c>
+      <c r="D66" t="n">
+        <v>77232</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>EBER  MAGDIEL  CASTILLEJA  BARROSO</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>SEND SALTILLO</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>01-05-2026 15:17:21</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>01-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I66" t="n">
+        <v>0</v>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L66" t="n">
+        <v>499</v>
+      </c>
+      <c r="M66" t="n">
+        <v>11</v>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
           <t>26-04-2027 15:17:21</t>
         </is>
       </c>
-      <c r="O46" t="inlineStr">
+      <c r="O66" t="inlineStr">
         <is>
           <t>Domiciliado</t>
         </is>
       </c>
-      <c r="P46" t="n">
+      <c r="P66" t="n">
         <v>4540</v>
       </c>
-      <c r="Q46" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>Reporte generado: 02-05-2026 03:48 p. m.</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr"/>
-      <c r="C47" t="inlineStr"/>
-      <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr"/>
-      <c r="F47" t="inlineStr"/>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
-      <c r="O47" t="inlineStr"/>
-      <c r="P47" t="inlineStr"/>
-      <c r="Q47" t="inlineStr"/>
+      <c r="Q66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Reporte generado: 03-05-2026 03:50 p. m.</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr"/>
+      <c r="C67" t="inlineStr"/>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr"/>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
+      <c r="O67" t="inlineStr"/>
+      <c r="P67" t="inlineStr"/>
+      <c r="Q67" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/descargas/cargos_recurrentes.xlsx
+++ b/data/descargas/cargos_recurrentes.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q67"/>
+  <dimension ref="A1:Q115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -603,17 +603,17 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>100485</v>
+        <v>95940</v>
       </c>
       <c r="C3" t="n">
-        <v>283428</v>
+        <v>95151</v>
       </c>
       <c r="D3" t="n">
-        <v>80929</v>
+        <v>92910</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>JOSE MANUEL OSUNA PEÑA</t>
+          <t>ANGELICA DEYANIRA SERRANO VALDEZ</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -623,12 +623,12 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>01-05-2026 9:28:55</t>
+          <t>04-03-2026 15:59:55</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>01-06-2026 23:59:59</t>
+          <t>03-06-2026 23:59:59</t>
         </is>
       </c>
       <c r="I3" t="n">
@@ -636,7 +636,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Sin filtro</t>
+          <t>Activado</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -645,14 +645,14 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>699</v>
+        <v>499</v>
       </c>
       <c r="M3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>26-04-2027 9:28:55</t>
+          <t>27-02-2027 15:59:55</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -661,7 +661,7 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>60636</v>
+        <v>52003</v>
       </c>
       <c r="Q3" t="inlineStr"/>
     </row>
@@ -670,17 +670,17 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>100496</v>
+        <v>100177</v>
       </c>
       <c r="C4" t="n">
-        <v>241908</v>
+        <v>194060</v>
       </c>
       <c r="D4" t="n">
-        <v>39413</v>
+        <v>91567</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>DANIA FERNANDA MORENO BELLO</t>
+          <t>ELISA ELENA PAREDES HERNANDEZ</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -690,7 +690,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>01-05-2026 12:44:57</t>
+          <t>27-04-2026 8:15:35</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -712,23 +712,21 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>699</v>
-      </c>
-      <c r="M4" t="n">
-        <v>11</v>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>26-04-2027 12:44:57</t>
-        </is>
-      </c>
+        <v>499</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Domiciliado</t>
+          <t>Recurrente</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>54257</v>
+        <v>4813</v>
       </c>
       <c r="Q4" t="inlineStr"/>
     </row>
@@ -737,29 +735,27 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>100503</v>
+        <v>99080</v>
       </c>
       <c r="C5" t="n">
-        <v>360991</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>03156</t>
-        </is>
+        <v>326105</v>
+      </c>
+      <c r="D5" t="n">
+        <v>23044</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>MARLENE  GARCIA AGUILAR</t>
+          <t>MONICA DANIELA  ORDUÑO PEREZ</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>VILLA VERDE</t>
+          <t>SEND CUL</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>01-05-2026 17:35:18</t>
+          <t>11-04-2026 10:17:07</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -777,11 +773,11 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>NUEVO</t>
+          <t>RENOVACIÓN</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>649</v>
+        <v>599</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -794,7 +790,9 @@
           <t>Recurrente</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr"/>
+      <c r="P5" t="n">
+        <v>83122</v>
+      </c>
       <c r="Q5" t="inlineStr"/>
     </row>
     <row r="6">
@@ -802,32 +800,32 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>100521</v>
+        <v>100443</v>
       </c>
       <c r="C6" t="n">
-        <v>266562</v>
+        <v>354766</v>
       </c>
       <c r="D6" t="n">
-        <v>64066</v>
+        <v>96930</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>NATALIA PADILLA RIVAS</t>
+          <t>JESUS ORLANDO OROZCO SEGOVIA</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>CARROUSEL TJ</t>
+          <t>SEND MXL</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>02-05-2026 13:06:35</t>
+          <t>30-04-2026 8:06:02</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>02-06-2026 23:59:59</t>
+          <t>01-06-2026 23:59:59</t>
         </is>
       </c>
       <c r="I6" t="n">
@@ -844,14 +842,14 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>499</v>
+        <v>549</v>
       </c>
       <c r="M6" t="n">
         <v>11</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>27-04-2027 13:06:35</t>
+          <t>25-04-2027 8:06:02</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -867,27 +865,27 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>99056</v>
+        <v>100484</v>
       </c>
       <c r="C7" t="n">
-        <v>76774</v>
+        <v>42885</v>
       </c>
       <c r="D7" t="n">
-        <v>74576</v>
+        <v>40755</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>CESAR DANIEL  PEREYRA  CONTRERAS</t>
+          <t>LUZ ADRIANA ALARCON  GONZALEZ</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>VILLA VERDE</t>
+          <t>PASEO 2000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>10-04-2026 17:32:18</t>
+          <t>01-05-2026 8:55:06</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -905,11 +903,11 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>RENOVACIÓN</t>
+          <t>NUEVO</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>399</v>
+        <v>649</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -922,9 +920,7 @@
           <t>Recurrente</t>
         </is>
       </c>
-      <c r="P7" t="n">
-        <v>24188</v>
-      </c>
+      <c r="P7" t="inlineStr"/>
       <c r="Q7" t="inlineStr"/>
     </row>
     <row r="8">
@@ -932,32 +928,34 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>98510</v>
+        <v>100486</v>
       </c>
       <c r="C8" t="n">
-        <v>195783</v>
-      </c>
-      <c r="D8" t="n">
-        <v>93290</v>
+        <v>360869</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>03034</t>
+        </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>KEVIN AXEL VILLAREAL CUEN</t>
+          <t>JOANNA VILLEGAS ORTIZ</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>PABELLON RTO</t>
+          <t>MISION ENS</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>03-04-2026 8:20:41</t>
+          <t>01-05-2026 9:43:16</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>03-06-2026 23:59:59</t>
+          <t>01-06-2026 23:59:59</t>
         </is>
       </c>
       <c r="I8" t="n">
@@ -970,28 +968,24 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>RENOVACIÓN</t>
+          <t>NUEVO</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>399</v>
-      </c>
-      <c r="M8" t="n">
-        <v>11</v>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>29-03-2027 8:20:41</t>
-        </is>
-      </c>
+        <v>649</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Domiciliado</t>
-        </is>
-      </c>
-      <c r="P8" t="n">
-        <v>41075</v>
-      </c>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr"/>
       <c r="Q8" t="inlineStr"/>
     </row>
     <row r="9">
@@ -999,17 +993,17 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>98541</v>
+        <v>100509</v>
       </c>
       <c r="C9" t="n">
-        <v>25207</v>
+        <v>141351</v>
       </c>
       <c r="D9" t="n">
-        <v>23149</v>
+        <v>38969</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>YOSHIO JESUS  RINCON  MIRANDA</t>
+          <t>JESUS ABELARDO RODRIGUEZ NAVARRO</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1019,12 +1013,12 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>03-04-2026 17:05:50</t>
+          <t>01-05-2026 20:01:10</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>02-06-2026 23:59:59</t>
+          <t>01-06-2026 23:59:59</t>
         </is>
       </c>
       <c r="I9" t="n">
@@ -1041,14 +1035,14 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>449</v>
+        <v>699</v>
       </c>
       <c r="M9" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>30-09-2026 17:05:50</t>
+          <t>26-04-2027 20:01:10</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1057,7 +1051,7 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>49403</v>
+        <v>76258</v>
       </c>
       <c r="Q9" t="inlineStr"/>
     </row>
@@ -1066,32 +1060,34 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>98810</v>
+        <v>100511</v>
       </c>
       <c r="C10" t="n">
-        <v>59822</v>
-      </c>
-      <c r="D10" t="n">
-        <v>57663</v>
+        <v>361026</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>03191</t>
+        </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>LETICIA RUBIO VALENZUELA</t>
+          <t>HILARY MONROY MORENO</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>INDEPENDENCIA</t>
+          <t>CARROUSEL TJ</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>07-04-2026 17:54:05</t>
+          <t>01-05-2026 20:07:30</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>02-06-2026 23:59:59</t>
+          <t>01-06-2026 23:59:59</t>
         </is>
       </c>
       <c r="I10" t="n">
@@ -1104,28 +1100,24 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>RENOVACIÓN</t>
+          <t>NUEVO</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>399</v>
-      </c>
-      <c r="M10" t="n">
-        <v>11</v>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>02-04-2027 17:54:05</t>
-        </is>
-      </c>
+        <v>649</v>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Domiciliado</t>
-        </is>
-      </c>
-      <c r="P10" t="n">
-        <v>8024</v>
-      </c>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr"/>
       <c r="Q10" t="inlineStr"/>
     </row>
     <row r="11">
@@ -1133,32 +1125,32 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>100331</v>
+        <v>100518</v>
       </c>
       <c r="C11" t="n">
-        <v>22791</v>
+        <v>348102</v>
       </c>
       <c r="D11" t="n">
-        <v>21685</v>
+        <v>90267</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>JUAN JOSE  PACHECO  FLORES</t>
+          <t>CHRISTIAN IVETTE MARTINEZ  MORALES</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CARROUSEL TJ</t>
+          <t>SEND SALTILLO</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>28-04-2026 13:00:52</t>
+          <t>02-05-2026 10:06:29</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>01-06-2026 23:59:59</t>
+          <t>03-06-2026 23:59:59</t>
         </is>
       </c>
       <c r="I11" t="n">
@@ -1175,21 +1167,23 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>399</v>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>Indefinido</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
+        <v>549</v>
+      </c>
+      <c r="M11" t="n">
+        <v>11</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>27-04-2027 10:06:29</t>
+        </is>
+      </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Recurrente</t>
+          <t>Domiciliado</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>79141</v>
+        <v>95767</v>
       </c>
       <c r="Q11" t="inlineStr"/>
     </row>
@@ -1198,32 +1192,34 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>100499</v>
+        <v>100543</v>
       </c>
       <c r="C12" t="n">
-        <v>79792</v>
-      </c>
-      <c r="D12" t="n">
-        <v>77591</v>
+        <v>361238</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>03403</t>
+        </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CHRISTIAN PRISCILA CARDONA BANDA</t>
+          <t>RENYCAN ALEJANDRO AVILA MARRUJO</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>STA CATARINA</t>
+          <t>VILLA VERDE</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>01-05-2026 16:18:47</t>
+          <t>04-05-2026 5:07:22</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>01-06-2026 23:59:59</t>
+          <t>04-06-2026 23:59:59</t>
         </is>
       </c>
       <c r="I12" t="n">
@@ -1247,7 +1243,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>26-04-2027 16:18:47</t>
+          <t>29-04-2027 5:07:22</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1263,34 +1259,34 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>100514</v>
+        <v>100545</v>
       </c>
       <c r="C13" t="n">
-        <v>361054</v>
+        <v>361245</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>03219</t>
+          <t>03410</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>ALAN IGNACIO  CORTES HERNANDEZ</t>
+          <t>JUAN CORONEL  PARRA</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>SALTILLO VILLALTA</t>
+          <t>SEND MXL</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>02-05-2026 7:36:52</t>
+          <t>04-05-2026 5:40:19</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>02-06-2026 23:59:59</t>
+          <t>04-06-2026 23:59:59</t>
         </is>
       </c>
       <c r="I13" t="n">
@@ -1307,14 +1303,14 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>649</v>
+        <v>549</v>
       </c>
       <c r="M13" t="n">
         <v>11</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>27-04-2027 7:36:52</t>
+          <t>29-04-2027 5:40:19</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1330,32 +1326,32 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>100517</v>
+        <v>100552</v>
       </c>
       <c r="C14" t="n">
-        <v>348099</v>
+        <v>124601</v>
       </c>
       <c r="D14" t="n">
-        <v>90264</v>
+        <v>22283</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>DANIEL CASIO FLORENCIO</t>
+          <t>VICTOR MANUEL FLORES ROMAN</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>SEND SALTILLO</t>
+          <t>VILLAS DEL REY</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>02-05-2026 10:04:52</t>
+          <t>04-05-2026 6:55:26</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>03-06-2026 23:59:59</t>
+          <t>04-06-2026 23:59:59</t>
         </is>
       </c>
       <c r="I14" t="n">
@@ -1372,14 +1368,14 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>549</v>
+        <v>499</v>
       </c>
       <c r="M14" t="n">
         <v>11</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>27-04-2027 10:04:52</t>
+          <t>29-04-2027 6:55:26</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -1388,7 +1384,7 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>95766</v>
+        <v>2090</v>
       </c>
       <c r="Q14" t="inlineStr"/>
     </row>
@@ -1397,17 +1393,17 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>97773</v>
+        <v>98369</v>
       </c>
       <c r="C15" t="n">
-        <v>348244</v>
+        <v>56575</v>
       </c>
       <c r="D15" t="n">
-        <v>90409</v>
+        <v>54426</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>DULCE NOHEMI SOTO MORENO</t>
+          <t>LARISSA DENISSE LOPEZ BURGOS</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1417,12 +1413,12 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>24-03-2026 20:48:40</t>
+          <t>31-03-2026 20:18:54</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>10-05-2026 23:59:59</t>
+          <t>01-06-2026 23:59:59</t>
         </is>
       </c>
       <c r="I15" t="n">
@@ -1439,14 +1435,14 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>549</v>
+        <v>499</v>
       </c>
       <c r="M15" t="n">
         <v>11</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>19-03-2027 20:48:40</t>
+          <t>26-03-2027 20:18:54</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -1455,7 +1451,7 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>97756</v>
+        <v>91270</v>
       </c>
       <c r="Q15" t="inlineStr"/>
     </row>
@@ -1464,32 +1460,32 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>97892</v>
+        <v>98418</v>
       </c>
       <c r="C16" t="n">
-        <v>151685</v>
+        <v>346832</v>
       </c>
       <c r="D16" t="n">
-        <v>49250</v>
+        <v>88997</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>SUSAN ELIZABETH SOTO PIÑA</t>
+          <t>KARLA BERENICE GONZALEZ ESPINDOLA</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>SEND CUL</t>
+          <t>TLALNEPANTLA</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>26-03-2026 13:42:06</t>
+          <t>01-04-2026 17:36:56</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>01-06-2026 23:59:59</t>
+          <t>03-06-2026 23:59:59</t>
         </is>
       </c>
       <c r="I16" t="n">
@@ -1506,14 +1502,14 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>399</v>
+        <v>549</v>
       </c>
       <c r="M16" t="n">
         <v>11</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>21-03-2027 13:42:06</t>
+          <t>27-03-2027 17:36:56</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -1522,7 +1518,7 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>2308</v>
+        <v>95789</v>
       </c>
       <c r="Q16" t="inlineStr"/>
     </row>
@@ -1531,32 +1527,32 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>99846</v>
+        <v>99890</v>
       </c>
       <c r="C17" t="n">
-        <v>253406</v>
+        <v>34927</v>
       </c>
       <c r="D17" t="n">
-        <v>50910</v>
+        <v>32841</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>BRISEIDA ISABEL ENRIQUEZ ZEPEDA</t>
+          <t>LILIAN RUVALCABA FIGUEROA</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>PAPALOTE TJ</t>
+          <t>MISION ENS</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>20-04-2026 21:29:56</t>
+          <t>21-04-2026 13:16:43</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>01-06-2026 23:59:59</t>
+          <t>02-06-2026 23:59:59</t>
         </is>
       </c>
       <c r="I17" t="n">
@@ -1580,7 +1576,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>15-04-2027 21:29:56</t>
+          <t>16-04-2027 13:16:43</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -1589,7 +1585,7 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>79273</v>
+        <v>95584</v>
       </c>
       <c r="Q17" t="inlineStr"/>
     </row>
@@ -1598,32 +1594,34 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>98454</v>
+        <v>100107</v>
       </c>
       <c r="C18" t="n">
-        <v>65078</v>
-      </c>
-      <c r="D18" t="n">
-        <v>62916</v>
+        <v>312465</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>09964</t>
+        </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>ALEJANDRO MAGALLAN  LOPEZ</t>
+          <t>GUADALUPE  CASTRO ROSAS</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>SEND CUL</t>
+          <t>SEND MXL</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>02-04-2026 7:19:31</t>
+          <t>24-04-2026 15:34:48</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>01-06-2026 23:59:59</t>
+          <t>02-06-2026 23:59:59</t>
         </is>
       </c>
       <c r="I18" t="n">
@@ -1640,14 +1638,14 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>350</v>
+        <v>549</v>
       </c>
       <c r="M18" t="n">
         <v>5</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>29-09-2026 7:19:31</t>
+          <t>21-10-2026 15:34:48</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -1656,7 +1654,7 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>76842</v>
+        <v>77036</v>
       </c>
       <c r="Q18" t="inlineStr"/>
     </row>
@@ -1665,29 +1663,29 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>98465</v>
+        <v>100488</v>
       </c>
       <c r="C19" t="n">
-        <v>312044</v>
+        <v>360887</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>09543</t>
+          <t>03052</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>NIRVANA FERNANDA  SALADO  SANCHEZ</t>
+          <t>MARIA DEL CARMEN JIMENEZ SANCHEZ</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>MISION ENS</t>
+          <t>SEND SALTILLO</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>02-04-2026 11:24:30</t>
+          <t>01-05-2026 10:34:42</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1705,18 +1703,18 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>RENOVACIÓN</t>
+          <t>NUEVO</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>499</v>
+        <v>549</v>
       </c>
       <c r="M19" t="n">
         <v>11</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>28-03-2027 11:24:30</t>
+          <t>26-04-2027 10:34:42</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -1724,9 +1722,7 @@
           <t>Domiciliado</t>
         </is>
       </c>
-      <c r="P19" t="n">
-        <v>76811</v>
-      </c>
+      <c r="P19" t="inlineStr"/>
       <c r="Q19" t="inlineStr"/>
     </row>
     <row r="20">
@@ -1734,27 +1730,29 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>100487</v>
+        <v>100490</v>
       </c>
       <c r="C20" t="n">
-        <v>48666</v>
-      </c>
-      <c r="D20" t="n">
-        <v>46524</v>
+        <v>360892</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>03057</t>
+        </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>ANA LUISA  HERNANDEZ  BELTRAN</t>
+          <t>ZARAKY RENE  ZENTENO  ORTIZ</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>AZAHARES CUL</t>
+          <t>IXTAPALUCA</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>01-05-2026 10:01:13</t>
+          <t>01-05-2026 11:00:08</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1776,19 +1774,17 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>549</v>
-      </c>
-      <c r="M20" t="n">
-        <v>11</v>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>26-04-2027 10:01:13</t>
-        </is>
-      </c>
+        <v>649</v>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Domiciliado</t>
+          <t>Recurrente</t>
         </is>
       </c>
       <c r="P20" t="inlineStr"/>
@@ -1799,27 +1795,29 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>100494</v>
+        <v>100492</v>
       </c>
       <c r="C21" t="n">
-        <v>346010</v>
-      </c>
-      <c r="D21" t="n">
-        <v>88175</v>
+        <v>360904</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>03069</t>
+        </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>ANA FABIOLA FLORES CARMONA</t>
+          <t>CARLA DANIELA MARTINEZ  GUILLEN</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>PASEO 2000</t>
+          <t>IXTAPALUCA</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>01-05-2026 11:54:51</t>
+          <t>01-05-2026 11:42:18</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1841,14 +1839,14 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>999</v>
+        <v>549</v>
       </c>
       <c r="M21" t="n">
         <v>11</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>26-04-2027 11:54:51</t>
+          <t>26-04-2027 11:42:18</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -1864,17 +1862,19 @@
         <v>20</v>
       </c>
       <c r="B22" t="n">
-        <v>100501</v>
+        <v>100505</v>
       </c>
       <c r="C22" t="n">
-        <v>347090</v>
-      </c>
-      <c r="D22" t="n">
-        <v>89255</v>
+        <v>360757</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>02922</t>
+        </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>GUILLERMO GERARDO VAZQUEZ GARCIA</t>
+          <t>CARLOS EDUARDO  FLORES  SANCHEZ</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1884,7 +1884,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>01-05-2026 16:31:24</t>
+          <t>01-05-2026 18:17:42</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1913,7 +1913,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>26-04-2027 16:31:24</t>
+          <t>26-04-2027 18:17:42</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -1929,32 +1929,32 @@
         <v>21</v>
       </c>
       <c r="B23" t="n">
-        <v>100512</v>
+        <v>100507</v>
       </c>
       <c r="C23" t="n">
-        <v>140437</v>
+        <v>353643</v>
       </c>
       <c r="D23" t="n">
-        <v>38064</v>
+        <v>95807</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>JUAN  FLORES  FELIX</t>
+          <t>MINERVA  GONZALEZ  MACEDO</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>AZAHARES CUL</t>
+          <t>METEPEC</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>01-05-2026 20:54:12</t>
+          <t>01-05-2026 18:32:13</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>04-06-2026 23:59:59</t>
+          <t>01-06-2026 23:59:59</t>
         </is>
       </c>
       <c r="I23" t="n">
@@ -1967,18 +1967,18 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>RENOVACIÓN</t>
+          <t>NUEVO</t>
         </is>
       </c>
       <c r="L23" t="n">
-        <v>449</v>
+        <v>649</v>
       </c>
       <c r="M23" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>28-10-2026 20:54:12</t>
+          <t>26-04-2027 18:32:13</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -1986,9 +1986,7 @@
           <t>Domiciliado</t>
         </is>
       </c>
-      <c r="P23" t="n">
-        <v>55808</v>
-      </c>
+      <c r="P23" t="inlineStr"/>
       <c r="Q23" t="inlineStr"/>
     </row>
     <row r="24">
@@ -1996,27 +1994,29 @@
         <v>22</v>
       </c>
       <c r="B24" t="n">
-        <v>99047</v>
+        <v>100522</v>
       </c>
       <c r="C24" t="n">
-        <v>38715</v>
-      </c>
-      <c r="D24" t="n">
-        <v>36587</v>
+        <v>360630</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>02795</t>
+        </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>ELOINA  REYNOSO  TERRONES</t>
+          <t>EDUARDO  GONZALES FLORES</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>PABELLON RTO</t>
+          <t>SALTILLO VILLALTA</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>10-04-2026 15:14:18</t>
+          <t>02-05-2026 13:13:57</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2034,11 +2034,11 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>RENOVACIÓN</t>
+          <t>NUEVO</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>399</v>
+        <v>549</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
@@ -2051,9 +2051,7 @@
           <t>Recurrente</t>
         </is>
       </c>
-      <c r="P24" t="n">
-        <v>57290</v>
-      </c>
+      <c r="P24" t="inlineStr"/>
       <c r="Q24" t="inlineStr"/>
     </row>
     <row r="25">
@@ -2061,32 +2059,34 @@
         <v>23</v>
       </c>
       <c r="B25" t="n">
-        <v>100177</v>
+        <v>100541</v>
       </c>
       <c r="C25" t="n">
-        <v>194060</v>
-      </c>
-      <c r="D25" t="n">
-        <v>91567</v>
+        <v>361236</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>03401</t>
+        </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>ELISA ELENA PAREDES HERNANDEZ</t>
+          <t>OSCAR ALFONSO GARCIA HUIZAR</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>TEC MXL</t>
+          <t>SEND SALTILLO</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>27-04-2026 8:15:35</t>
+          <t>04-05-2026 4:43:51</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>01-06-2026 23:59:59</t>
+          <t>04-06-2026 23:59:59</t>
         </is>
       </c>
       <c r="I25" t="n">
@@ -2099,26 +2099,26 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>RENOVACIÓN</t>
+          <t>NUEVO</t>
         </is>
       </c>
       <c r="L25" t="n">
-        <v>499</v>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>Indefinido</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
+        <v>549</v>
+      </c>
+      <c r="M25" t="n">
+        <v>11</v>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>29-04-2027 4:43:51</t>
+        </is>
+      </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>Recurrente</t>
-        </is>
-      </c>
-      <c r="P25" t="n">
-        <v>4813</v>
-      </c>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr"/>
       <c r="Q25" t="inlineStr"/>
     </row>
     <row r="26">
@@ -2126,32 +2126,34 @@
         <v>24</v>
       </c>
       <c r="B26" t="n">
-        <v>100443</v>
+        <v>100556</v>
       </c>
       <c r="C26" t="n">
-        <v>354766</v>
-      </c>
-      <c r="D26" t="n">
-        <v>96930</v>
+        <v>361264</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>03429</t>
+        </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>JESUS ORLANDO OROZCO SEGOVIA</t>
+          <t>GIOVANNA ZUGIA SOBRINO</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>SEND MXL</t>
+          <t>PASEO 2000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>30-04-2026 8:06:02</t>
+          <t>04-05-2026 7:25:48</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>01-06-2026 23:59:59</t>
+          <t>04-06-2026 23:59:59</t>
         </is>
       </c>
       <c r="I26" t="n">
@@ -2168,19 +2170,17 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>549</v>
-      </c>
-      <c r="M26" t="n">
-        <v>11</v>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>25-04-2027 8:06:02</t>
-        </is>
-      </c>
+        <v>649</v>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr">
         <is>
-          <t>Domiciliado</t>
+          <t>Recurrente</t>
         </is>
       </c>
       <c r="P26" t="inlineStr"/>
@@ -2191,32 +2191,34 @@
         <v>25</v>
       </c>
       <c r="B27" t="n">
-        <v>100484</v>
+        <v>100558</v>
       </c>
       <c r="C27" t="n">
-        <v>42885</v>
-      </c>
-      <c r="D27" t="n">
-        <v>40755</v>
+        <v>361266</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>03431</t>
+        </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>LUZ ADRIANA ALARCON  GONZALEZ</t>
+          <t>ROBERTO MORA FERNANDEZ</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>PASEO 2000</t>
+          <t>MISION ENS</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>01-05-2026 8:55:06</t>
+          <t>04-05-2026 7:36:43</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>01-06-2026 23:59:59</t>
+          <t>04-06-2026 23:59:59</t>
         </is>
       </c>
       <c r="I27" t="n">
@@ -2233,17 +2235,19 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>649</v>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>Indefinido</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
+        <v>549</v>
+      </c>
+      <c r="M27" t="n">
+        <v>11</v>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>29-04-2027 7:36:43</t>
+        </is>
+      </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>Recurrente</t>
+          <t>Domiciliado</t>
         </is>
       </c>
       <c r="P27" t="inlineStr"/>
@@ -2254,34 +2258,32 @@
         <v>26</v>
       </c>
       <c r="B28" t="n">
-        <v>100486</v>
+        <v>100573</v>
       </c>
       <c r="C28" t="n">
-        <v>360869</v>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>03034</t>
-        </is>
+        <v>156338</v>
+      </c>
+      <c r="D28" t="n">
+        <v>53885</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>JOANNA VILLEGAS ORTIZ</t>
+          <t>DIANA PAOLA PANDURO RODRIGUEZ</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>MISION ENS</t>
+          <t>SEND CHIH</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>01-05-2026 9:43:16</t>
+          <t>04-05-2026 9:45:16</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>01-06-2026 23:59:59</t>
+          <t>04-06-2026 23:59:59</t>
         </is>
       </c>
       <c r="I28" t="n">
@@ -2298,17 +2300,19 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>649</v>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>Indefinido</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
+        <v>499</v>
+      </c>
+      <c r="M28" t="n">
+        <v>5</v>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>31-10-2026 9:45:16</t>
+        </is>
+      </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>Recurrente</t>
+          <t>Domiciliado</t>
         </is>
       </c>
       <c r="P28" t="inlineStr"/>
@@ -2319,32 +2323,32 @@
         <v>27</v>
       </c>
       <c r="B29" t="n">
-        <v>100509</v>
+        <v>98510</v>
       </c>
       <c r="C29" t="n">
-        <v>141351</v>
+        <v>195783</v>
       </c>
       <c r="D29" t="n">
-        <v>38969</v>
+        <v>93290</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>JESUS ABELARDO RODRIGUEZ NAVARRO</t>
+          <t>KEVIN AXEL VILLAREAL CUEN</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>CARROUSEL TJ</t>
+          <t>PABELLON RTO</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>01-05-2026 20:01:10</t>
+          <t>03-04-2026 8:20:41</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>01-06-2026 23:59:59</t>
+          <t>03-06-2026 23:59:59</t>
         </is>
       </c>
       <c r="I29" t="n">
@@ -2361,14 +2365,14 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>699</v>
+        <v>399</v>
       </c>
       <c r="M29" t="n">
         <v>11</v>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>26-04-2027 20:01:10</t>
+          <t>29-03-2027 8:20:41</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
@@ -2377,7 +2381,7 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>76258</v>
+        <v>41075</v>
       </c>
       <c r="Q29" t="inlineStr"/>
     </row>
@@ -2386,19 +2390,17 @@
         <v>28</v>
       </c>
       <c r="B30" t="n">
-        <v>100511</v>
+        <v>98541</v>
       </c>
       <c r="C30" t="n">
-        <v>361026</v>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>03191</t>
-        </is>
+        <v>25207</v>
+      </c>
+      <c r="D30" t="n">
+        <v>23149</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>HILARY MONROY MORENO</t>
+          <t>YOSHIO JESUS  RINCON  MIRANDA</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -2408,12 +2410,12 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>01-05-2026 20:07:30</t>
+          <t>03-04-2026 17:05:50</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>01-06-2026 23:59:59</t>
+          <t>02-06-2026 23:59:59</t>
         </is>
       </c>
       <c r="I30" t="n">
@@ -2426,24 +2428,28 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>NUEVO</t>
+          <t>RENOVACIÓN</t>
         </is>
       </c>
       <c r="L30" t="n">
-        <v>649</v>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>Indefinido</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
+        <v>449</v>
+      </c>
+      <c r="M30" t="n">
+        <v>5</v>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>30-09-2026 17:05:50</t>
+        </is>
+      </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>Recurrente</t>
-        </is>
-      </c>
-      <c r="P30" t="inlineStr"/>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P30" t="n">
+        <v>49403</v>
+      </c>
       <c r="Q30" t="inlineStr"/>
     </row>
     <row r="31">
@@ -2451,32 +2457,32 @@
         <v>29</v>
       </c>
       <c r="B31" t="n">
-        <v>100518</v>
+        <v>99846</v>
       </c>
       <c r="C31" t="n">
-        <v>348102</v>
+        <v>253406</v>
       </c>
       <c r="D31" t="n">
-        <v>90267</v>
+        <v>50910</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>CHRISTIAN IVETTE MARTINEZ  MORALES</t>
+          <t>BRISEIDA ISABEL ENRIQUEZ ZEPEDA</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>SEND SALTILLO</t>
+          <t>PAPALOTE TJ</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>02-05-2026 10:06:29</t>
+          <t>20-04-2026 21:29:56</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>03-06-2026 23:59:59</t>
+          <t>01-06-2026 23:59:59</t>
         </is>
       </c>
       <c r="I31" t="n">
@@ -2493,14 +2499,14 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>549</v>
+        <v>499</v>
       </c>
       <c r="M31" t="n">
         <v>11</v>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>27-04-2027 10:06:29</t>
+          <t>15-04-2027 21:29:56</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
@@ -2509,7 +2515,7 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>95767</v>
+        <v>79273</v>
       </c>
       <c r="Q31" t="inlineStr"/>
     </row>
@@ -2518,40 +2524,40 @@
         <v>30</v>
       </c>
       <c r="B32" t="n">
-        <v>95940</v>
+        <v>98810</v>
       </c>
       <c r="C32" t="n">
-        <v>95151</v>
+        <v>59822</v>
       </c>
       <c r="D32" t="n">
-        <v>92910</v>
+        <v>57663</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>ANGELICA DEYANIRA SERRANO VALDEZ</t>
+          <t>LETICIA RUBIO VALENZUELA</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>PASEO 2000</t>
+          <t>INDEPENDENCIA</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>04-03-2026 15:59:55</t>
+          <t>07-04-2026 17:54:05</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>03-05-2026 23:59:59</t>
+          <t>02-06-2026 23:59:59</t>
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Activado</t>
+          <t>Sin filtro</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2560,14 +2566,14 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>499</v>
+        <v>399</v>
       </c>
       <c r="M32" t="n">
         <v>11</v>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>27-02-2027 15:59:55</t>
+          <t>02-04-2027 17:54:05</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
@@ -2576,7 +2582,7 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>52003</v>
+        <v>8024</v>
       </c>
       <c r="Q32" t="inlineStr"/>
     </row>
@@ -2585,32 +2591,32 @@
         <v>31</v>
       </c>
       <c r="B33" t="n">
-        <v>99080</v>
+        <v>97773</v>
       </c>
       <c r="C33" t="n">
-        <v>326105</v>
+        <v>348244</v>
       </c>
       <c r="D33" t="n">
-        <v>23044</v>
+        <v>90409</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>MONICA DANIELA  ORDUÑO PEREZ</t>
+          <t>DULCE NOHEMI SOTO MORENO</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>SEND CUL</t>
+          <t>TEC MXL</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>11-04-2026 10:17:07</t>
+          <t>24-03-2026 20:48:40</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>01-06-2026 23:59:59</t>
+          <t>10-05-2026 23:59:59</t>
         </is>
       </c>
       <c r="I33" t="n">
@@ -2627,21 +2633,23 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>599</v>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>Indefinido</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
+        <v>549</v>
+      </c>
+      <c r="M33" t="n">
+        <v>11</v>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>19-03-2027 20:48:40</t>
+        </is>
+      </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>Recurrente</t>
+          <t>Domiciliado</t>
         </is>
       </c>
       <c r="P33" t="n">
-        <v>83122</v>
+        <v>97756</v>
       </c>
       <c r="Q33" t="inlineStr"/>
     </row>
@@ -2650,29 +2658,27 @@
         <v>32</v>
       </c>
       <c r="B34" t="n">
-        <v>98466</v>
+        <v>97892</v>
       </c>
       <c r="C34" t="n">
-        <v>205081</v>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>02589</t>
-        </is>
+        <v>151685</v>
+      </c>
+      <c r="D34" t="n">
+        <v>49250</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>ISRAEL CRESPO RIOS</t>
+          <t>SUSAN ELIZABETH SOTO PIÑA</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>MISION ENS</t>
+          <t>SEND CUL</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>02-04-2026 11:27:04</t>
+          <t>26-03-2026 13:42:06</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2694,14 +2700,14 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>499</v>
+        <v>399</v>
       </c>
       <c r="M34" t="n">
         <v>11</v>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>28-03-2027 11:27:04</t>
+          <t>21-03-2027 13:42:06</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
@@ -2710,7 +2716,7 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>76809</v>
+        <v>2308</v>
       </c>
       <c r="Q34" t="inlineStr"/>
     </row>
@@ -2719,17 +2725,17 @@
         <v>33</v>
       </c>
       <c r="B35" t="n">
-        <v>98517</v>
+        <v>100331</v>
       </c>
       <c r="C35" t="n">
-        <v>232630</v>
+        <v>22791</v>
       </c>
       <c r="D35" t="n">
-        <v>30135</v>
+        <v>21685</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>JULIO CESAR VERDE  MANJARRES</t>
+          <t>JUAN JOSE  PACHECO  FLORES</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -2739,12 +2745,12 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>03-04-2026 10:04:26</t>
+          <t>28-04-2026 13:00:52</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>02-06-2026 23:59:59</t>
+          <t>01-06-2026 23:59:59</t>
         </is>
       </c>
       <c r="I35" t="n">
@@ -2761,23 +2767,21 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>449</v>
-      </c>
-      <c r="M35" t="n">
-        <v>5</v>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>30-09-2026 10:04:26</t>
-        </is>
-      </c>
+        <v>399</v>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="O35" t="inlineStr">
         <is>
-          <t>Domiciliado</t>
+          <t>Recurrente</t>
         </is>
       </c>
       <c r="P35" t="n">
-        <v>49260</v>
+        <v>79141</v>
       </c>
       <c r="Q35" t="inlineStr"/>
     </row>
@@ -2786,27 +2790,27 @@
         <v>34</v>
       </c>
       <c r="B36" t="n">
-        <v>98583</v>
+        <v>100499</v>
       </c>
       <c r="C36" t="n">
-        <v>114721</v>
+        <v>79792</v>
       </c>
       <c r="D36" t="n">
-        <v>12446</v>
+        <v>77591</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>JESUS ANTONIO ABRIL CAMPOS</t>
+          <t>CHRISTIAN PRISCILA CARDONA BANDA</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>SAN LUIS</t>
+          <t>STA CATARINA</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>06-04-2026 5:30:30</t>
+          <t>01-05-2026 16:18:47</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2824,26 +2828,26 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>RENOVACIÓN</t>
+          <t>NUEVO</t>
         </is>
       </c>
       <c r="L36" t="n">
-        <v>399</v>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>Indefinido</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
+        <v>549</v>
+      </c>
+      <c r="M36" t="n">
+        <v>11</v>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>26-04-2027 16:18:47</t>
+        </is>
+      </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>Recurrente</t>
-        </is>
-      </c>
-      <c r="P36" t="n">
-        <v>11835</v>
-      </c>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr"/>
       <c r="Q36" t="inlineStr"/>
     </row>
     <row r="37">
@@ -2851,27 +2855,29 @@
         <v>35</v>
       </c>
       <c r="B37" t="n">
-        <v>99889</v>
+        <v>100514</v>
       </c>
       <c r="C37" t="n">
-        <v>17586</v>
-      </c>
-      <c r="D37" t="n">
-        <v>16499</v>
+        <v>361054</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>03219</t>
+        </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>ERIKA ADRIANA BERMUDEZ TALAVERA</t>
+          <t>ALAN IGNACIO  CORTES HERNANDEZ</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>MISION ENS</t>
+          <t>SALTILLO VILLALTA</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>21-04-2026 13:14:32</t>
+          <t>02-05-2026 7:36:52</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2889,18 +2895,18 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>RENOVACIÓN</t>
+          <t>NUEVO</t>
         </is>
       </c>
       <c r="L37" t="n">
-        <v>499</v>
+        <v>649</v>
       </c>
       <c r="M37" t="n">
         <v>11</v>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>16-04-2027 13:14:32</t>
+          <t>27-04-2027 7:36:52</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
@@ -2908,9 +2914,7 @@
           <t>Domiciliado</t>
         </is>
       </c>
-      <c r="P37" t="n">
-        <v>95586</v>
-      </c>
+      <c r="P37" t="inlineStr"/>
       <c r="Q37" t="inlineStr"/>
     </row>
     <row r="38">
@@ -2918,27 +2922,27 @@
         <v>36</v>
       </c>
       <c r="B38" t="n">
-        <v>100457</v>
+        <v>100517</v>
       </c>
       <c r="C38" t="n">
-        <v>98076</v>
+        <v>348099</v>
       </c>
       <c r="D38" t="n">
-        <v>95835</v>
+        <v>90264</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>NORA FERNANDA CORTES MATUS</t>
+          <t>DANIEL CASIO FLORENCIO</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>SEND CUL</t>
+          <t>SEND SALTILLO</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>30-04-2026 16:15:54</t>
+          <t>02-05-2026 10:04:52</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2960,21 +2964,23 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>649</v>
-      </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>Indefinido</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
+        <v>549</v>
+      </c>
+      <c r="M38" t="n">
+        <v>11</v>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>27-04-2027 10:04:52</t>
+        </is>
+      </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>Recurrente</t>
+          <t>Domiciliado</t>
         </is>
       </c>
       <c r="P38" t="n">
-        <v>91561</v>
+        <v>95766</v>
       </c>
       <c r="Q38" t="inlineStr"/>
     </row>
@@ -2983,34 +2989,34 @@
         <v>37</v>
       </c>
       <c r="B39" t="n">
-        <v>100489</v>
+        <v>100531</v>
       </c>
       <c r="C39" t="n">
-        <v>360888</v>
+        <v>361188</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>03053</t>
+          <t>03353</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>MARA FERNANDA LUNA MENDOZA</t>
+          <t>YURIDIA YAMILET ANOTA VEGA</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>VILLA VERDE</t>
+          <t>PASEO 2000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>01-05-2026 10:38:33</t>
+          <t>03-05-2026 12:36:11</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>01-06-2026 23:59:59</t>
+          <t>03-06-2026 23:59:59</t>
         </is>
       </c>
       <c r="I39" t="n">
@@ -3027,17 +3033,19 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>649</v>
-      </c>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>Indefinido</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
+        <v>549</v>
+      </c>
+      <c r="M39" t="n">
+        <v>11</v>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>28-04-2027 12:36:11</t>
+        </is>
+      </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>Recurrente</t>
+          <t>Domiciliado</t>
         </is>
       </c>
       <c r="P39" t="inlineStr"/>
@@ -3048,32 +3056,34 @@
         <v>38</v>
       </c>
       <c r="B40" t="n">
-        <v>100491</v>
+        <v>100532</v>
       </c>
       <c r="C40" t="n">
-        <v>56971</v>
-      </c>
-      <c r="D40" t="n">
-        <v>54822</v>
+        <v>361189</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>03354</t>
+        </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>NOEMI  RAMOS  DE LEON</t>
+          <t>XIMENA  DE LACRUZ ESQUIVEL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>CARROUSEL TJ</t>
+          <t>PASEO 2000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>01-05-2026 11:15:25</t>
+          <t>03-05-2026 12:43:23</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>04-06-2026 23:59:59</t>
+          <t>03-06-2026 23:59:59</t>
         </is>
       </c>
       <c r="I40" t="n">
@@ -3086,18 +3096,18 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>RENOVACIÓN</t>
+          <t>NUEVO</t>
         </is>
       </c>
       <c r="L40" t="n">
-        <v>449</v>
+        <v>549</v>
       </c>
       <c r="M40" t="n">
         <v>11</v>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>26-04-2027 11:15:25</t>
+          <t>28-04-2027 12:43:23</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
@@ -3105,9 +3115,7 @@
           <t>Domiciliado</t>
         </is>
       </c>
-      <c r="P40" t="n">
-        <v>68495</v>
-      </c>
+      <c r="P40" t="inlineStr"/>
       <c r="Q40" t="inlineStr"/>
     </row>
     <row r="41">
@@ -3115,34 +3123,34 @@
         <v>39</v>
       </c>
       <c r="B41" t="n">
-        <v>100508</v>
+        <v>100549</v>
       </c>
       <c r="C41" t="n">
-        <v>361018</v>
+        <v>361251</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>03183</t>
+          <t>03416</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>DENIS LILIANA AMEZCUA CRUZ</t>
+          <t>JEREMHY ALMEIDA OLMEDO</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>CARROUSEL TJ</t>
+          <t>PABELLON RTO</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>01-05-2026 19:13:51</t>
+          <t>04-05-2026 6:10:14</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>01-06-2026 23:59:59</t>
+          <t>04-06-2026 23:59:59</t>
         </is>
       </c>
       <c r="I41" t="n">
@@ -3159,17 +3167,19 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>649</v>
-      </c>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>Indefinido</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
+        <v>549</v>
+      </c>
+      <c r="M41" t="n">
+        <v>11</v>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>29-04-2027 6:10:14</t>
+        </is>
+      </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>Recurrente</t>
+          <t>Domiciliado</t>
         </is>
       </c>
       <c r="P41" t="inlineStr"/>
@@ -3180,32 +3190,34 @@
         <v>40</v>
       </c>
       <c r="B42" t="n">
-        <v>100523</v>
+        <v>100550</v>
       </c>
       <c r="C42" t="n">
-        <v>177956</v>
-      </c>
-      <c r="D42" t="n">
-        <v>75463</v>
+        <v>361250</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>03415</t>
+        </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>LUIS DAVID ROSAS  ALONSO</t>
+          <t>CARLOS ALBERTO CORPUS TELLES</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>PASEO 2000</t>
+          <t>SEND SALTILLO</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>02-05-2026 13:24:03</t>
+          <t>04-05-2026 6:10:26</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>02-06-2026 23:59:59</t>
+          <t>04-06-2026 23:59:59</t>
         </is>
       </c>
       <c r="I42" t="n">
@@ -3218,18 +3230,18 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>RENOVACIÓN</t>
+          <t>NUEVO</t>
         </is>
       </c>
       <c r="L42" t="n">
-        <v>499</v>
+        <v>549</v>
       </c>
       <c r="M42" t="n">
         <v>11</v>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>27-04-2027 13:24:03</t>
+          <t>29-04-2027 6:10:26</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
@@ -3237,9 +3249,7 @@
           <t>Domiciliado</t>
         </is>
       </c>
-      <c r="P42" t="n">
-        <v>4701</v>
-      </c>
+      <c r="P42" t="inlineStr"/>
       <c r="Q42" t="inlineStr"/>
     </row>
     <row r="43">
@@ -3247,32 +3257,34 @@
         <v>41</v>
       </c>
       <c r="B43" t="n">
-        <v>99840</v>
+        <v>100564</v>
       </c>
       <c r="C43" t="n">
-        <v>178067</v>
-      </c>
-      <c r="D43" t="n">
-        <v>75574</v>
+        <v>361278</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>03443</t>
+        </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>ALMA ANGELICA  PEREZ  MIRANDA</t>
+          <t>JOSE ALFREDO HIGUERA ENCINAS</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>SANTA FE</t>
+          <t>SEND MXL</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>20-04-2026 20:14:31</t>
+          <t>04-05-2026 8:28:46</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>01-06-2026 23:59:59</t>
+          <t>04-06-2026 23:59:59</t>
         </is>
       </c>
       <c r="I43" t="n">
@@ -3285,26 +3297,26 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>RENOVACIÓN</t>
+          <t>NUEVO</t>
         </is>
       </c>
       <c r="L43" t="n">
-        <v>449</v>
-      </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>Indefinido</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr"/>
+        <v>549</v>
+      </c>
+      <c r="M43" t="n">
+        <v>11</v>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>29-04-2027 8:28:46</t>
+        </is>
+      </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>Recurrente</t>
-        </is>
-      </c>
-      <c r="P43" t="n">
-        <v>74406</v>
-      </c>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr"/>
       <c r="Q43" t="inlineStr"/>
     </row>
     <row r="44">
@@ -3312,32 +3324,32 @@
         <v>42</v>
       </c>
       <c r="B44" t="n">
-        <v>98369</v>
+        <v>100567</v>
       </c>
       <c r="C44" t="n">
-        <v>56575</v>
+        <v>235274</v>
       </c>
       <c r="D44" t="n">
-        <v>54426</v>
+        <v>32779</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>LARISSA DENISSE LOPEZ BURGOS</t>
+          <t>PEDRO JAIR  PERALTA  ZARATE</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>TEC MXL</t>
+          <t>PABELLON RTO</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>31-03-2026 20:18:54</t>
+          <t>04-05-2026 8:59:44</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>01-06-2026 23:59:59</t>
+          <t>04-06-2026 23:59:59</t>
         </is>
       </c>
       <c r="I44" t="n">
@@ -3350,18 +3362,18 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>RENOVACIÓN</t>
+          <t>NUEVO</t>
         </is>
       </c>
       <c r="L44" t="n">
-        <v>499</v>
+        <v>549</v>
       </c>
       <c r="M44" t="n">
         <v>11</v>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>26-03-2027 20:18:54</t>
+          <t>29-04-2027 8:59:44</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
@@ -3369,9 +3381,7 @@
           <t>Domiciliado</t>
         </is>
       </c>
-      <c r="P44" t="n">
-        <v>91270</v>
-      </c>
+      <c r="P44" t="inlineStr"/>
       <c r="Q44" t="inlineStr"/>
     </row>
     <row r="45">
@@ -3379,32 +3389,32 @@
         <v>43</v>
       </c>
       <c r="B45" t="n">
-        <v>98418</v>
+        <v>98454</v>
       </c>
       <c r="C45" t="n">
-        <v>346832</v>
+        <v>65078</v>
       </c>
       <c r="D45" t="n">
-        <v>88997</v>
+        <v>62916</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>KARLA BERENICE GONZALEZ ESPINDOLA</t>
+          <t>ALEJANDRO MAGALLAN  LOPEZ</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>TLALNEPANTLA</t>
+          <t>SEND CUL</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>01-04-2026 17:36:56</t>
+          <t>02-04-2026 7:19:31</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>03-06-2026 23:59:59</t>
+          <t>01-06-2026 23:59:59</t>
         </is>
       </c>
       <c r="I45" t="n">
@@ -3421,14 +3431,14 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>549</v>
+        <v>350</v>
       </c>
       <c r="M45" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>27-03-2027 17:36:56</t>
+          <t>29-09-2026 7:19:31</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
@@ -3437,7 +3447,7 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>95789</v>
+        <v>76842</v>
       </c>
       <c r="Q45" t="inlineStr"/>
     </row>
@@ -3446,17 +3456,19 @@
         <v>44</v>
       </c>
       <c r="B46" t="n">
-        <v>99890</v>
+        <v>98465</v>
       </c>
       <c r="C46" t="n">
-        <v>34927</v>
-      </c>
-      <c r="D46" t="n">
-        <v>32841</v>
+        <v>312044</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>09543</t>
+        </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>LILIAN RUVALCABA FIGUEROA</t>
+          <t>NIRVANA FERNANDA  SALADO  SANCHEZ</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -3466,12 +3478,12 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>21-04-2026 13:16:43</t>
+          <t>02-04-2026 11:24:30</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>02-06-2026 23:59:59</t>
+          <t>01-06-2026 23:59:59</t>
         </is>
       </c>
       <c r="I46" t="n">
@@ -3495,7 +3507,7 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>16-04-2027 13:16:43</t>
+          <t>28-03-2027 11:24:30</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
@@ -3504,7 +3516,7 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>95584</v>
+        <v>76811</v>
       </c>
       <c r="Q46" t="inlineStr"/>
     </row>
@@ -3513,34 +3525,32 @@
         <v>45</v>
       </c>
       <c r="B47" t="n">
-        <v>100107</v>
+        <v>100169</v>
       </c>
       <c r="C47" t="n">
-        <v>312465</v>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>09964</t>
-        </is>
+        <v>74777</v>
+      </c>
+      <c r="D47" t="n">
+        <v>72592</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>GUADALUPE  CASTRO ROSAS</t>
+          <t>OLGA ALICIA  BARRAZA RIOS</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>SEND MXL</t>
+          <t>SEND CUL</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>24-04-2026 15:34:48</t>
+          <t>27-04-2026 5:45:57</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>02-06-2026 23:59:59</t>
+          <t>04-06-2026 23:59:59</t>
         </is>
       </c>
       <c r="I47" t="n">
@@ -3557,14 +3567,14 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>549</v>
+        <v>399</v>
       </c>
       <c r="M47" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>21-10-2026 15:34:48</t>
+          <t>22-04-2027 5:45:57</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
@@ -3573,7 +3583,7 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>77036</v>
+        <v>74295</v>
       </c>
       <c r="Q47" t="inlineStr"/>
     </row>
@@ -3582,34 +3592,32 @@
         <v>46</v>
       </c>
       <c r="B48" t="n">
-        <v>100488</v>
+        <v>99047</v>
       </c>
       <c r="C48" t="n">
-        <v>360887</v>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>03052</t>
-        </is>
+        <v>38715</v>
+      </c>
+      <c r="D48" t="n">
+        <v>36587</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>MARIA DEL CARMEN JIMENEZ SANCHEZ</t>
+          <t>ELOINA  REYNOSO  TERRONES</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>SEND SALTILLO</t>
+          <t>PABELLON RTO</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>01-05-2026 10:34:42</t>
+          <t>10-04-2026 15:14:18</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>01-06-2026 23:59:59</t>
+          <t>02-06-2026 23:59:59</t>
         </is>
       </c>
       <c r="I48" t="n">
@@ -3622,26 +3630,26 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>NUEVO</t>
+          <t>RENOVACIÓN</t>
         </is>
       </c>
       <c r="L48" t="n">
-        <v>549</v>
-      </c>
-      <c r="M48" t="n">
-        <v>11</v>
-      </c>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>26-04-2027 10:34:42</t>
-        </is>
-      </c>
+        <v>399</v>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
       <c r="O48" t="inlineStr">
         <is>
-          <t>Domiciliado</t>
-        </is>
-      </c>
-      <c r="P48" t="inlineStr"/>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P48" t="n">
+        <v>57290</v>
+      </c>
       <c r="Q48" t="inlineStr"/>
     </row>
     <row r="49">
@@ -3649,29 +3657,27 @@
         <v>47</v>
       </c>
       <c r="B49" t="n">
-        <v>100490</v>
+        <v>100487</v>
       </c>
       <c r="C49" t="n">
-        <v>360892</v>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>03057</t>
-        </is>
+        <v>48666</v>
+      </c>
+      <c r="D49" t="n">
+        <v>46524</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>ZARAKY RENE  ZENTENO  ORTIZ</t>
+          <t>ANA LUISA  HERNANDEZ  BELTRAN</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>IXTAPALUCA</t>
+          <t>AZAHARES CUL</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>01-05-2026 11:00:08</t>
+          <t>01-05-2026 10:01:13</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -3693,17 +3699,19 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>649</v>
-      </c>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>Indefinido</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr"/>
+        <v>549</v>
+      </c>
+      <c r="M49" t="n">
+        <v>11</v>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>26-04-2027 10:01:13</t>
+        </is>
+      </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>Recurrente</t>
+          <t>Domiciliado</t>
         </is>
       </c>
       <c r="P49" t="inlineStr"/>
@@ -3714,29 +3722,27 @@
         <v>48</v>
       </c>
       <c r="B50" t="n">
-        <v>100492</v>
+        <v>100494</v>
       </c>
       <c r="C50" t="n">
-        <v>360904</v>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>03069</t>
-        </is>
+        <v>346010</v>
+      </c>
+      <c r="D50" t="n">
+        <v>88175</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>CARLA DANIELA MARTINEZ  GUILLEN</t>
+          <t>ANA FABIOLA FLORES CARMONA</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>IXTAPALUCA</t>
+          <t>PASEO 2000</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>01-05-2026 11:42:18</t>
+          <t>01-05-2026 11:54:51</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3758,14 +3764,14 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>549</v>
+        <v>999</v>
       </c>
       <c r="M50" t="n">
         <v>11</v>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>26-04-2027 11:42:18</t>
+          <t>26-04-2027 11:54:51</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
@@ -3781,19 +3787,17 @@
         <v>49</v>
       </c>
       <c r="B51" t="n">
-        <v>100505</v>
+        <v>100501</v>
       </c>
       <c r="C51" t="n">
-        <v>360757</v>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>02922</t>
-        </is>
+        <v>347090</v>
+      </c>
+      <c r="D51" t="n">
+        <v>89255</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>CARLOS EDUARDO  FLORES  SANCHEZ</t>
+          <t>GUILLERMO GERARDO VAZQUEZ GARCIA</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -3803,7 +3807,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>01-05-2026 18:17:42</t>
+          <t>01-05-2026 16:31:24</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3832,7 +3836,7 @@
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>26-04-2027 18:17:42</t>
+          <t>26-04-2027 16:31:24</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
@@ -3848,32 +3852,32 @@
         <v>50</v>
       </c>
       <c r="B52" t="n">
-        <v>100507</v>
+        <v>100512</v>
       </c>
       <c r="C52" t="n">
-        <v>353643</v>
+        <v>140437</v>
       </c>
       <c r="D52" t="n">
-        <v>95807</v>
+        <v>38064</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>MINERVA  GONZALEZ  MACEDO</t>
+          <t>JUAN  FLORES  FELIX</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>METEPEC</t>
+          <t>AZAHARES CUL</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>01-05-2026 18:32:13</t>
+          <t>01-05-2026 20:54:12</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>01-06-2026 23:59:59</t>
+          <t>04-06-2026 23:59:59</t>
         </is>
       </c>
       <c r="I52" t="n">
@@ -3886,18 +3890,18 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>NUEVO</t>
+          <t>RENOVACIÓN</t>
         </is>
       </c>
       <c r="L52" t="n">
-        <v>649</v>
+        <v>449</v>
       </c>
       <c r="M52" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>26-04-2027 18:32:13</t>
+          <t>28-10-2026 20:54:12</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
@@ -3905,7 +3909,9 @@
           <t>Domiciliado</t>
         </is>
       </c>
-      <c r="P52" t="inlineStr"/>
+      <c r="P52" t="n">
+        <v>55808</v>
+      </c>
       <c r="Q52" t="inlineStr"/>
     </row>
     <row r="53">
@@ -3913,34 +3919,34 @@
         <v>51</v>
       </c>
       <c r="B53" t="n">
-        <v>100522</v>
+        <v>100526</v>
       </c>
       <c r="C53" t="n">
-        <v>360630</v>
+        <v>361153</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>02795</t>
+          <t>03318</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>EDUARDO  GONZALES FLORES</t>
+          <t>JESUS SALVATIERRA DE PAZ</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>SALTILLO VILLALTA</t>
+          <t>SEND CHIH</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>02-05-2026 13:13:57</t>
+          <t>03-05-2026 9:32:44</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>02-06-2026 23:59:59</t>
+          <t>03-08-2026 23:59:59</t>
         </is>
       </c>
       <c r="I53" t="n">
@@ -3957,7 +3963,7 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>549</v>
+        <v>1449</v>
       </c>
       <c r="M53" t="inlineStr">
         <is>
@@ -3978,27 +3984,29 @@
         <v>52</v>
       </c>
       <c r="B54" t="n">
-        <v>96317</v>
+        <v>100537</v>
       </c>
       <c r="C54" t="n">
-        <v>340665</v>
-      </c>
-      <c r="D54" t="n">
-        <v>18483</v>
+        <v>361195</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>03360</t>
+        </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>MONICA ROXANA ALDUNCIN FLETCHER</t>
+          <t>LESLY XIOMARA AGUILAR GUZMAN</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>METEPEC</t>
+          <t>SALTILLO VILLALTA</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>09-03-2026 16:06:01</t>
+          <t>03-05-2026 14:30:46</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -4016,7 +4024,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>RENOVACIÓN</t>
+          <t>NUEVO</t>
         </is>
       </c>
       <c r="L54" t="n">
@@ -4027,7 +4035,7 @@
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>04-03-2027 16:06:01</t>
+          <t>28-04-2027 14:30:46</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
@@ -4035,9 +4043,7 @@
           <t>Domiciliado</t>
         </is>
       </c>
-      <c r="P54" t="n">
-        <v>91727</v>
-      </c>
+      <c r="P54" t="inlineStr"/>
       <c r="Q54" t="inlineStr"/>
     </row>
     <row r="55">
@@ -4045,32 +4051,32 @@
         <v>53</v>
       </c>
       <c r="B55" t="n">
-        <v>98557</v>
+        <v>100544</v>
       </c>
       <c r="C55" t="n">
-        <v>312669</v>
+        <v>32222</v>
       </c>
       <c r="D55" t="n">
-        <v>10168</v>
+        <v>30145</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>ROBERTO SALAZAR</t>
+          <t>JOSE ARTURO LOPEZ FELIX</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>CARROUSEL TJ</t>
+          <t>TEC MXL</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>04-04-2026 12:48:33</t>
+          <t>04-05-2026 5:31:21</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>03-06-2026 23:59:59</t>
+          <t>04-06-2026 23:59:59</t>
         </is>
       </c>
       <c r="I55" t="n">
@@ -4083,26 +4089,26 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>RENOVACIÓN</t>
+          <t>NUEVO</t>
         </is>
       </c>
       <c r="L55" t="n">
-        <v>599</v>
-      </c>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>Indefinido</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr"/>
+        <v>549</v>
+      </c>
+      <c r="M55" t="n">
+        <v>11</v>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>29-04-2027 5:31:21</t>
+        </is>
+      </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>Recurrente</t>
-        </is>
-      </c>
-      <c r="P55" t="n">
-        <v>77181</v>
-      </c>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr"/>
       <c r="Q55" t="inlineStr"/>
     </row>
     <row r="56">
@@ -4110,34 +4116,34 @@
         <v>54</v>
       </c>
       <c r="B56" t="n">
-        <v>100493</v>
+        <v>100562</v>
       </c>
       <c r="C56" t="n">
-        <v>360045</v>
+        <v>4119</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>02210</t>
+          <t>03120</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>BALTAZAR VILLASEÑOR  CRUZ</t>
+          <t>MOISES  FLORES  HERRERA</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>METEPEC</t>
+          <t>SEND MXL</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>01-05-2026 11:51:52</t>
+          <t>04-05-2026 8:13:55</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>01-06-2026 23:59:59</t>
+          <t>04-06-2026 23:59:59</t>
         </is>
       </c>
       <c r="I56" t="n">
@@ -4154,7 +4160,7 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>799</v>
+        <v>649</v>
       </c>
       <c r="M56" t="inlineStr">
         <is>
@@ -4175,32 +4181,34 @@
         <v>55</v>
       </c>
       <c r="B57" t="n">
-        <v>100495</v>
+        <v>100569</v>
       </c>
       <c r="C57" t="n">
-        <v>349026</v>
-      </c>
-      <c r="D57" t="n">
-        <v>91191</v>
+        <v>361291</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>03456</t>
+        </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>CESAR OMAR OBREGON ESTRELLLO</t>
+          <t>FABIAN  LOPEZ RAMIREZ</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>SALTILLO VILLALTA</t>
+          <t>PASEO LA PAZ</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>01-05-2026 12:28:55</t>
+          <t>04-05-2026 9:17:56</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>01-06-2026 23:59:59</t>
+          <t>04-08-2026 23:59:59</t>
         </is>
       </c>
       <c r="I57" t="n">
@@ -4217,14 +4225,14 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>649</v>
+        <v>1449</v>
       </c>
       <c r="M57" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>26-04-2027 12:28:55</t>
+          <t>29-04-2027 9:17:56</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
@@ -4240,29 +4248,27 @@
         <v>56</v>
       </c>
       <c r="B58" t="n">
-        <v>100502</v>
+        <v>98183</v>
       </c>
       <c r="C58" t="n">
-        <v>205459</v>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>02967</t>
-        </is>
+        <v>301268</v>
+      </c>
+      <c r="D58" t="n">
+        <v>98766</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>ANTONIO  LAMAS IRINEO</t>
+          <t>DAYANARA ELIZABETH  MELGAREJO  CRUZ</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>SEND MXL</t>
+          <t>CARROUSEL TJ</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>01-05-2026 17:19:17</t>
+          <t>30-03-2026 18:05:51</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -4284,14 +4290,14 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>399</v>
+        <v>499</v>
       </c>
       <c r="M58" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>28-10-2026 17:19:17</t>
+          <t>25-03-2027 18:05:51</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
@@ -4300,7 +4306,7 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>38806</v>
+        <v>81114</v>
       </c>
       <c r="Q58" t="inlineStr"/>
     </row>
@@ -4309,29 +4315,29 @@
         <v>57</v>
       </c>
       <c r="B59" t="n">
-        <v>100504</v>
+        <v>98466</v>
       </c>
       <c r="C59" t="n">
-        <v>361003</v>
+        <v>205081</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>03168</t>
+          <t>02589</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>DEMIAN CORONADO LOPEZ</t>
+          <t>ISRAEL CRESPO RIOS</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>TEC MXL</t>
+          <t>MISION ENS</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>01-05-2026 18:12:55</t>
+          <t>02-04-2026 11:27:04</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4349,24 +4355,28 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>NUEVO</t>
+          <t>RENOVACIÓN</t>
         </is>
       </c>
       <c r="L59" t="n">
-        <v>649</v>
-      </c>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>Indefinido</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr"/>
+        <v>499</v>
+      </c>
+      <c r="M59" t="n">
+        <v>11</v>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>28-03-2027 11:27:04</t>
+        </is>
+      </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>Recurrente</t>
-        </is>
-      </c>
-      <c r="P59" t="inlineStr"/>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P59" t="n">
+        <v>76809</v>
+      </c>
       <c r="Q59" t="inlineStr"/>
     </row>
     <row r="60">
@@ -4374,27 +4384,27 @@
         <v>58</v>
       </c>
       <c r="B60" t="n">
-        <v>99332</v>
+        <v>98517</v>
       </c>
       <c r="C60" t="n">
-        <v>257916</v>
+        <v>232630</v>
       </c>
       <c r="D60" t="n">
-        <v>55420</v>
+        <v>30135</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>FELIPE ALFONSO GUERRERO INZUNZA</t>
+          <t>JULIO CESAR VERDE  MANJARRES</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>SEND CUL</t>
+          <t>CARROUSEL TJ</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>14-04-2026 12:19:40</t>
+          <t>03-04-2026 10:04:26</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4416,21 +4426,23 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>399</v>
-      </c>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>Indefinido</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr"/>
+        <v>449</v>
+      </c>
+      <c r="M60" t="n">
+        <v>5</v>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>30-09-2026 10:04:26</t>
+        </is>
+      </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>Recurrente</t>
+          <t>Domiciliado</t>
         </is>
       </c>
       <c r="P60" t="n">
-        <v>73999</v>
+        <v>49260</v>
       </c>
       <c r="Q60" t="inlineStr"/>
     </row>
@@ -4439,32 +4451,32 @@
         <v>59</v>
       </c>
       <c r="B61" t="n">
-        <v>96322</v>
+        <v>98583</v>
       </c>
       <c r="C61" t="n">
-        <v>340658</v>
+        <v>114721</v>
       </c>
       <c r="D61" t="n">
-        <v>18476</v>
+        <v>12446</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>MONICA BERALD BERMUDEZ ALDUCIN</t>
+          <t>JESUS ANTONIO ABRIL CAMPOS</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>METEPEC</t>
+          <t>SAN LUIS</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>09-03-2026 16:14:08</t>
+          <t>06-04-2026 5:30:30</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>03-06-2026 23:59:59</t>
+          <t>01-06-2026 23:59:59</t>
         </is>
       </c>
       <c r="I61" t="n">
@@ -4481,23 +4493,21 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>649</v>
-      </c>
-      <c r="M61" t="n">
-        <v>11</v>
-      </c>
-      <c r="N61" t="inlineStr">
-        <is>
-          <t>04-03-2027 16:14:08</t>
-        </is>
-      </c>
+        <v>399</v>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr"/>
       <c r="O61" t="inlineStr">
         <is>
-          <t>Domiciliado</t>
+          <t>Recurrente</t>
         </is>
       </c>
       <c r="P61" t="n">
-        <v>91712</v>
+        <v>11835</v>
       </c>
       <c r="Q61" t="inlineStr"/>
     </row>
@@ -4506,34 +4516,32 @@
         <v>60</v>
       </c>
       <c r="B62" t="n">
-        <v>100480</v>
+        <v>99840</v>
       </c>
       <c r="C62" t="n">
-        <v>360840</v>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>03005</t>
-        </is>
+        <v>178067</v>
+      </c>
+      <c r="D62" t="n">
+        <v>75574</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>TANIA ELIZABETH VILLAREAL PEREDA</t>
+          <t>ALMA ANGELICA  PEREZ  MIRANDA</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>INSURGENTES</t>
+          <t>SANTA FE</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>01-05-2026 7:38:40</t>
+          <t>20-04-2026 20:14:31</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>01-08-2026 23:59:59</t>
+          <t>01-06-2026 23:59:59</t>
         </is>
       </c>
       <c r="I62" t="n">
@@ -4546,11 +4554,11 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>NUEVO</t>
+          <t>RENOVACIÓN</t>
         </is>
       </c>
       <c r="L62" t="n">
-        <v>1549</v>
+        <v>449</v>
       </c>
       <c r="M62" t="inlineStr">
         <is>
@@ -4563,7 +4571,9 @@
           <t>Recurrente</t>
         </is>
       </c>
-      <c r="P62" t="inlineStr"/>
+      <c r="P62" t="n">
+        <v>74406</v>
+      </c>
       <c r="Q62" t="inlineStr"/>
     </row>
     <row r="63">
@@ -4571,34 +4581,32 @@
         <v>61</v>
       </c>
       <c r="B63" t="n">
-        <v>100483</v>
+        <v>99889</v>
       </c>
       <c r="C63" t="n">
-        <v>360852</v>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>03017</t>
-        </is>
+        <v>17586</v>
+      </c>
+      <c r="D63" t="n">
+        <v>16499</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>ELIUD RAMIREZ BELMARES</t>
+          <t>ERIKA ADRIANA BERMUDEZ TALAVERA</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>SALTILLO VILLALTA</t>
+          <t>MISION ENS</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>01-05-2026 8:37:34</t>
+          <t>21-04-2026 13:14:32</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>01-06-2026 23:59:59</t>
+          <t>02-06-2026 23:59:59</t>
         </is>
       </c>
       <c r="I63" t="n">
@@ -4611,18 +4619,18 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>NUEVO</t>
+          <t>RENOVACIÓN</t>
         </is>
       </c>
       <c r="L63" t="n">
-        <v>649</v>
+        <v>499</v>
       </c>
       <c r="M63" t="n">
         <v>11</v>
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>26-04-2027 8:37:34</t>
+          <t>16-04-2027 13:14:32</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
@@ -4630,7 +4638,9 @@
           <t>Domiciliado</t>
         </is>
       </c>
-      <c r="P63" t="inlineStr"/>
+      <c r="P63" t="n">
+        <v>95586</v>
+      </c>
       <c r="Q63" t="inlineStr"/>
     </row>
     <row r="64">
@@ -4638,34 +4648,32 @@
         <v>62</v>
       </c>
       <c r="B64" t="n">
-        <v>100515</v>
+        <v>100457</v>
       </c>
       <c r="C64" t="n">
-        <v>361056</v>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>03221</t>
-        </is>
+        <v>98076</v>
+      </c>
+      <c r="D64" t="n">
+        <v>95835</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>GILBERTO  BARRIOS HERNANDEZ</t>
+          <t>NORA FERNANDA CORTES MATUS</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>SALTILLO VILLALTA</t>
+          <t>SEND CUL</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>02-05-2026 7:46:19</t>
+          <t>30-04-2026 16:15:54</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>02-06-2026 23:59:59</t>
+          <t>03-06-2026 23:59:59</t>
         </is>
       </c>
       <c r="I64" t="n">
@@ -4678,26 +4686,26 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>NUEVO</t>
+          <t>RENOVACIÓN</t>
         </is>
       </c>
       <c r="L64" t="n">
         <v>649</v>
       </c>
-      <c r="M64" t="n">
-        <v>11</v>
-      </c>
-      <c r="N64" t="inlineStr">
-        <is>
-          <t>27-04-2027 7:46:19</t>
-        </is>
-      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr"/>
       <c r="O64" t="inlineStr">
         <is>
-          <t>Domiciliado</t>
-        </is>
-      </c>
-      <c r="P64" t="inlineStr"/>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P64" t="n">
+        <v>91561</v>
+      </c>
       <c r="Q64" t="inlineStr"/>
     </row>
     <row r="65">
@@ -4705,27 +4713,29 @@
         <v>63</v>
       </c>
       <c r="B65" t="n">
-        <v>98943</v>
+        <v>100489</v>
       </c>
       <c r="C65" t="n">
-        <v>37106</v>
-      </c>
-      <c r="D65" t="n">
-        <v>34985</v>
+        <v>360888</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>03053</t>
+        </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>JUAN FRANCISCO PITONES NORIEGA</t>
+          <t>MARA FERNANDA LUNA MENDOZA</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>SEND MXL</t>
+          <t>VILLA VERDE</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>08-04-2026 20:42:26</t>
+          <t>01-05-2026 10:38:33</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -4743,11 +4753,11 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>RENOVACIÓN</t>
+          <t>NUEVO</t>
         </is>
       </c>
       <c r="L65" t="n">
-        <v>399</v>
+        <v>649</v>
       </c>
       <c r="M65" t="inlineStr">
         <is>
@@ -4760,9 +4770,7 @@
           <t>Recurrente</t>
         </is>
       </c>
-      <c r="P65" t="n">
-        <v>96274</v>
-      </c>
+      <c r="P65" t="inlineStr"/>
       <c r="Q65" t="inlineStr"/>
     </row>
     <row r="66">
@@ -4770,32 +4778,32 @@
         <v>64</v>
       </c>
       <c r="B66" t="n">
-        <v>100497</v>
+        <v>100491</v>
       </c>
       <c r="C66" t="n">
-        <v>179725</v>
+        <v>56971</v>
       </c>
       <c r="D66" t="n">
-        <v>77232</v>
+        <v>54822</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>EBER  MAGDIEL  CASTILLEJA  BARROSO</t>
+          <t>NOEMI  RAMOS  DE LEON</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>SEND SALTILLO</t>
+          <t>CARROUSEL TJ</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>01-05-2026 15:17:21</t>
+          <t>01-05-2026 11:15:25</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>01-06-2026 23:59:59</t>
+          <t>04-06-2026 23:59:59</t>
         </is>
       </c>
       <c r="I66" t="n">
@@ -4812,14 +4820,14 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>499</v>
+        <v>449</v>
       </c>
       <c r="M66" t="n">
         <v>11</v>
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>26-04-2027 15:17:21</t>
+          <t>26-04-2027 11:15:25</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
@@ -4828,32 +4836,3202 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>4540</v>
+        <v>68495</v>
       </c>
       <c r="Q66" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>Reporte generado: 03-05-2026 03:50 p. m.</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr"/>
-      <c r="C67" t="inlineStr"/>
-      <c r="D67" t="inlineStr"/>
-      <c r="E67" t="inlineStr"/>
-      <c r="F67" t="inlineStr"/>
-      <c r="G67" t="inlineStr"/>
-      <c r="H67" t="inlineStr"/>
-      <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr"/>
+      <c r="A67" t="n">
+        <v>65</v>
+      </c>
+      <c r="B67" t="n">
+        <v>100508</v>
+      </c>
+      <c r="C67" t="n">
+        <v>361018</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>03183</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>DENIS LILIANA AMEZCUA CRUZ</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>CARROUSEL TJ</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>01-05-2026 19:13:51</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>01-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I67" t="n">
+        <v>0</v>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L67" t="n">
+        <v>649</v>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
       <c r="N67" t="inlineStr"/>
-      <c r="O67" t="inlineStr"/>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr"/>
       <c r="Q67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>66</v>
+      </c>
+      <c r="B68" t="n">
+        <v>100523</v>
+      </c>
+      <c r="C68" t="n">
+        <v>177956</v>
+      </c>
+      <c r="D68" t="n">
+        <v>75463</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>LUIS DAVID ROSAS  ALONSO</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>PASEO 2000</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>02-05-2026 13:24:03</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>02-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I68" t="n">
+        <v>0</v>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L68" t="n">
+        <v>499</v>
+      </c>
+      <c r="M68" t="n">
+        <v>11</v>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>27-04-2027 13:24:03</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P68" t="n">
+        <v>4701</v>
+      </c>
+      <c r="Q68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>67</v>
+      </c>
+      <c r="B69" t="n">
+        <v>100540</v>
+      </c>
+      <c r="C69" t="n">
+        <v>361235</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>03400</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>DAVID NAHUM RUBIO REYES</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>SALTILLO VILLALTA</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>04-05-2026 4:38:35</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>04-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I69" t="n">
+        <v>0</v>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L69" t="n">
+        <v>649</v>
+      </c>
+      <c r="M69" t="n">
+        <v>11</v>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>29-04-2027 4:38:35</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr"/>
+      <c r="Q69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>68</v>
+      </c>
+      <c r="B70" t="n">
+        <v>100542</v>
+      </c>
+      <c r="C70" t="n">
+        <v>251572</v>
+      </c>
+      <c r="D70" t="n">
+        <v>49076</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>GAEL ELIAS ARAIZA ANCHONDO</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>SEND CHIH</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>04-05-2026 4:45:50</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>04-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I70" t="n">
+        <v>0</v>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L70" t="n">
+        <v>549</v>
+      </c>
+      <c r="M70" t="n">
+        <v>11</v>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>29-04-2027 4:45:50</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr"/>
+      <c r="Q70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>69</v>
+      </c>
+      <c r="B71" t="n">
+        <v>100572</v>
+      </c>
+      <c r="C71" t="n">
+        <v>92514</v>
+      </c>
+      <c r="D71" t="n">
+        <v>90276</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>ALEJANDRO CERVANTES AVILES</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>SEND SALTILLO</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>04-05-2026 9:35:18</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>04-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I71" t="n">
+        <v>0</v>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L71" t="n">
+        <v>499</v>
+      </c>
+      <c r="M71" t="n">
+        <v>11</v>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>29-04-2027 9:35:18</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P71" t="n">
+        <v>45799</v>
+      </c>
+      <c r="Q71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>70</v>
+      </c>
+      <c r="B72" t="n">
+        <v>100574</v>
+      </c>
+      <c r="C72" t="n">
+        <v>361296</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>03461</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>DAILIN  LIMON ZARZOSA</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>SANTA FE</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>04-05-2026 9:47:35</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>04-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I72" t="n">
+        <v>0</v>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L72" t="n">
+        <v>649</v>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr"/>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr"/>
+      <c r="Q72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>71</v>
+      </c>
+      <c r="B73" t="n">
+        <v>98556</v>
+      </c>
+      <c r="C73" t="n">
+        <v>312668</v>
+      </c>
+      <c r="D73" t="n">
+        <v>10167</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>LILIANA QUEZADA MONTES</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>CARROUSEL TJ</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>04-04-2026 12:47:09</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>03-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I73" t="n">
+        <v>0</v>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L73" t="n">
+        <v>599</v>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr"/>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P73" t="n">
+        <v>77180</v>
+      </c>
+      <c r="Q73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>72</v>
+      </c>
+      <c r="B74" t="n">
+        <v>98631</v>
+      </c>
+      <c r="C74" t="n">
+        <v>7025</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>05960</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>LUIS ANDRES  FRAUSTO HERRERA</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>VILLA VERDE</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>06-04-2026 13:35:23</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>02-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I74" t="n">
+        <v>0</v>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L74" t="n">
+        <v>549</v>
+      </c>
+      <c r="M74" t="n">
+        <v>11</v>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>01-04-2027 13:35:23</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P74" t="n">
+        <v>85404</v>
+      </c>
+      <c r="Q74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>73</v>
+      </c>
+      <c r="B75" t="n">
+        <v>98856</v>
+      </c>
+      <c r="C75" t="n">
+        <v>151341</v>
+      </c>
+      <c r="D75" t="n">
+        <v>48906</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>CARLOS GUZMAN  ROBLES</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>SEND CUL</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>08-04-2026 5:49:32</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>04-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>0</v>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L75" t="n">
+        <v>549</v>
+      </c>
+      <c r="M75" t="n">
+        <v>11</v>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>03-04-2027 5:49:32</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P75" t="n">
+        <v>95870</v>
+      </c>
+      <c r="Q75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>74</v>
+      </c>
+      <c r="B76" t="n">
+        <v>99056</v>
+      </c>
+      <c r="C76" t="n">
+        <v>76774</v>
+      </c>
+      <c r="D76" t="n">
+        <v>74576</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>CESAR DANIEL  PEREYRA  CONTRERAS</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>VILLA VERDE</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>10-04-2026 17:32:18</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>01-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I76" t="n">
+        <v>0</v>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L76" t="n">
+        <v>399</v>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr"/>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P76" t="n">
+        <v>24188</v>
+      </c>
+      <c r="Q76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>75</v>
+      </c>
+      <c r="B77" t="n">
+        <v>100278</v>
+      </c>
+      <c r="C77" t="n">
+        <v>238071</v>
+      </c>
+      <c r="D77" t="n">
+        <v>35576</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>CARMEN GUADALUPE VAZQUEZ RODRIGUEZ</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>CARROUSEL TJ</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>27-04-2026 19:15:26</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>04-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I77" t="n">
+        <v>0</v>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L77" t="n">
+        <v>449</v>
+      </c>
+      <c r="M77" t="n">
+        <v>11</v>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>22-04-2027 19:15:26</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P77" t="n">
+        <v>56316</v>
+      </c>
+      <c r="Q77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>76</v>
+      </c>
+      <c r="B78" t="n">
+        <v>100485</v>
+      </c>
+      <c r="C78" t="n">
+        <v>283428</v>
+      </c>
+      <c r="D78" t="n">
+        <v>80929</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>JOSE MANUEL OSUNA PEÑA</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>PASEO 2000</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>01-05-2026 9:28:55</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>01-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I78" t="n">
+        <v>0</v>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L78" t="n">
+        <v>699</v>
+      </c>
+      <c r="M78" t="n">
+        <v>11</v>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>26-04-2027 9:28:55</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P78" t="n">
+        <v>60636</v>
+      </c>
+      <c r="Q78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>77</v>
+      </c>
+      <c r="B79" t="n">
+        <v>100496</v>
+      </c>
+      <c r="C79" t="n">
+        <v>241908</v>
+      </c>
+      <c r="D79" t="n">
+        <v>39413</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>DANIA FERNANDA MORENO BELLO</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>TEC MXL</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>01-05-2026 12:44:57</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>01-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I79" t="n">
+        <v>0</v>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L79" t="n">
+        <v>699</v>
+      </c>
+      <c r="M79" t="n">
+        <v>11</v>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>26-04-2027 12:44:57</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P79" t="n">
+        <v>54257</v>
+      </c>
+      <c r="Q79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>78</v>
+      </c>
+      <c r="B80" t="n">
+        <v>100503</v>
+      </c>
+      <c r="C80" t="n">
+        <v>360991</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>03156</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>MARLENE  GARCIA AGUILAR</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>VILLA VERDE</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>01-05-2026 17:35:18</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>01-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I80" t="n">
+        <v>0</v>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L80" t="n">
+        <v>649</v>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr"/>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr"/>
+      <c r="Q80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>79</v>
+      </c>
+      <c r="B81" t="n">
+        <v>100521</v>
+      </c>
+      <c r="C81" t="n">
+        <v>266562</v>
+      </c>
+      <c r="D81" t="n">
+        <v>64066</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>NATALIA PADILLA RIVAS</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>CARROUSEL TJ</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>02-05-2026 13:06:35</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>02-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I81" t="n">
+        <v>0</v>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L81" t="n">
+        <v>499</v>
+      </c>
+      <c r="M81" t="n">
+        <v>11</v>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>27-04-2027 13:06:35</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr"/>
+      <c r="Q81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>80</v>
+      </c>
+      <c r="B82" t="n">
+        <v>100528</v>
+      </c>
+      <c r="C82" t="n">
+        <v>361166</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>03331</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>DIANA MELISSA ALVAREZ MENDOZA</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>PASEO LA PAZ</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>03-05-2026 11:05:56</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>03-08-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I82" t="n">
+        <v>0</v>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L82" t="n">
+        <v>1449</v>
+      </c>
+      <c r="M82" t="n">
+        <v>9</v>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>28-04-2027 11:05:56</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr"/>
+      <c r="Q82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>81</v>
+      </c>
+      <c r="B83" t="n">
+        <v>100535</v>
+      </c>
+      <c r="C83" t="n">
+        <v>361192</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>03357</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>NORMA ORTENCIA  ZAMARRIPA  BARBOZA</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>SALTILLO VILLALTA</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>03-05-2026 14:07:48</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>03-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I83" t="n">
+        <v>0</v>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L83" t="n">
+        <v>649</v>
+      </c>
+      <c r="M83" t="n">
+        <v>11</v>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>28-04-2027 14:07:48</t>
+        </is>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr"/>
+      <c r="Q83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>82</v>
+      </c>
+      <c r="B84" t="n">
+        <v>100546</v>
+      </c>
+      <c r="C84" t="n">
+        <v>361246</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>03411</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>SAUL ZAZUETA ROCHA</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>SEND CUL</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>04-05-2026 5:48:24</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>04-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I84" t="n">
+        <v>0</v>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L84" t="n">
+        <v>649</v>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr"/>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr"/>
+      <c r="Q84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>83</v>
+      </c>
+      <c r="B85" t="n">
+        <v>100553</v>
+      </c>
+      <c r="C85" t="n">
+        <v>123402</v>
+      </c>
+      <c r="D85" t="n">
+        <v>21089</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>ANDRES DELGADO RODRIGUEZ</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>MISION ENS</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>04-05-2026 6:58:47</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>03-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I85" t="n">
+        <v>0</v>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L85" t="n">
+        <v>399</v>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr"/>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P85" t="n">
+        <v>11539</v>
+      </c>
+      <c r="Q85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>84</v>
+      </c>
+      <c r="B86" t="n">
+        <v>100560</v>
+      </c>
+      <c r="C86" t="n">
+        <v>361272</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>03437</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>NANCY ESPINOZA SANCHEZ</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>PABELLON RTO</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>04-05-2026 7:56:41</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>04-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I86" t="n">
+        <v>0</v>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L86" t="n">
+        <v>549</v>
+      </c>
+      <c r="M86" t="n">
+        <v>11</v>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>29-04-2027 7:56:41</t>
+        </is>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P86" t="inlineStr"/>
+      <c r="Q86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>85</v>
+      </c>
+      <c r="B87" t="n">
+        <v>100571</v>
+      </c>
+      <c r="C87" t="n">
+        <v>324133</v>
+      </c>
+      <c r="D87" t="n">
+        <v>21072</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>HORACIO OLIVA LOPEZ</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>INSURGENTES</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>04-05-2026 9:31:35</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>04-08-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I87" t="n">
+        <v>0</v>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L87" t="n">
+        <v>1549</v>
+      </c>
+      <c r="M87" t="n">
+        <v>9</v>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>29-04-2027 9:31:35</t>
+        </is>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P87" t="inlineStr"/>
+      <c r="Q87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>86</v>
+      </c>
+      <c r="B88" t="n">
+        <v>96317</v>
+      </c>
+      <c r="C88" t="n">
+        <v>340665</v>
+      </c>
+      <c r="D88" t="n">
+        <v>18483</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>MONICA ROXANA ALDUNCIN FLETCHER</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>METEPEC</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>09-03-2026 16:06:01</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>03-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I88" t="n">
+        <v>0</v>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L88" t="n">
+        <v>649</v>
+      </c>
+      <c r="M88" t="n">
+        <v>11</v>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>04-03-2027 16:06:01</t>
+        </is>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P88" t="n">
+        <v>91727</v>
+      </c>
+      <c r="Q88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>87</v>
+      </c>
+      <c r="B89" t="n">
+        <v>98557</v>
+      </c>
+      <c r="C89" t="n">
+        <v>312669</v>
+      </c>
+      <c r="D89" t="n">
+        <v>10168</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>ROBERTO SALAZAR</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>CARROUSEL TJ</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>04-04-2026 12:48:33</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>03-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I89" t="n">
+        <v>0</v>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L89" t="n">
+        <v>599</v>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr"/>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P89" t="n">
+        <v>77181</v>
+      </c>
+      <c r="Q89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>88</v>
+      </c>
+      <c r="B90" t="n">
+        <v>99332</v>
+      </c>
+      <c r="C90" t="n">
+        <v>257916</v>
+      </c>
+      <c r="D90" t="n">
+        <v>55420</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>FELIPE ALFONSO GUERRERO INZUNZA</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>SEND CUL</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>14-04-2026 12:19:40</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>02-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I90" t="n">
+        <v>0</v>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L90" t="n">
+        <v>399</v>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr"/>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P90" t="n">
+        <v>73999</v>
+      </c>
+      <c r="Q90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>89</v>
+      </c>
+      <c r="B91" t="n">
+        <v>100493</v>
+      </c>
+      <c r="C91" t="n">
+        <v>360045</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>02210</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>BALTAZAR VILLASEÑOR  CRUZ</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>METEPEC</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>01-05-2026 11:51:52</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>01-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I91" t="n">
+        <v>0</v>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L91" t="n">
+        <v>799</v>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr"/>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P91" t="inlineStr"/>
+      <c r="Q91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>90</v>
+      </c>
+      <c r="B92" t="n">
+        <v>100495</v>
+      </c>
+      <c r="C92" t="n">
+        <v>349026</v>
+      </c>
+      <c r="D92" t="n">
+        <v>91191</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>CESAR OMAR OBREGON ESTRELLLO</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>SALTILLO VILLALTA</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>01-05-2026 12:28:55</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>01-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I92" t="n">
+        <v>0</v>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L92" t="n">
+        <v>649</v>
+      </c>
+      <c r="M92" t="n">
+        <v>11</v>
+      </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>26-04-2027 12:28:55</t>
+        </is>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P92" t="inlineStr"/>
+      <c r="Q92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>91</v>
+      </c>
+      <c r="B93" t="n">
+        <v>100502</v>
+      </c>
+      <c r="C93" t="n">
+        <v>205459</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>02967</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>ANTONIO  LAMAS IRINEO</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>SEND MXL</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>01-05-2026 17:19:17</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>30-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I93" t="n">
+        <v>0</v>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L93" t="n">
+        <v>399</v>
+      </c>
+      <c r="M93" t="n">
+        <v>5</v>
+      </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>28-10-2026 17:19:17</t>
+        </is>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P93" t="n">
+        <v>38806</v>
+      </c>
+      <c r="Q93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>92</v>
+      </c>
+      <c r="B94" t="n">
+        <v>100504</v>
+      </c>
+      <c r="C94" t="n">
+        <v>361003</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>03168</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>DEMIAN CORONADO LOPEZ</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>TEC MXL</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>01-05-2026 18:12:55</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>01-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I94" t="n">
+        <v>0</v>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L94" t="n">
+        <v>649</v>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr"/>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P94" t="inlineStr"/>
+      <c r="Q94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>93</v>
+      </c>
+      <c r="B95" t="n">
+        <v>100529</v>
+      </c>
+      <c r="C95" t="n">
+        <v>361169</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>03334</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>SONIA LOPEZ  RUIZ</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>INSURGENTES</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>03-05-2026 11:20:21</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>03-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I95" t="n">
+        <v>0</v>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L95" t="n">
+        <v>799</v>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr"/>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P95" t="inlineStr"/>
+      <c r="Q95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>94</v>
+      </c>
+      <c r="B96" t="n">
+        <v>100534</v>
+      </c>
+      <c r="C96" t="n">
+        <v>149146</v>
+      </c>
+      <c r="D96" t="n">
+        <v>46718</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>HEIDI ALEXANDRA  ARELLANO  GONZALEZ</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>AZAHARES CUL</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>03-05-2026 13:06:02</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>03-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I96" t="n">
+        <v>0</v>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L96" t="n">
+        <v>499</v>
+      </c>
+      <c r="M96" t="n">
+        <v>11</v>
+      </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>28-04-2027 13:06:02</t>
+        </is>
+      </c>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P96" t="n">
+        <v>81275</v>
+      </c>
+      <c r="Q96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>95</v>
+      </c>
+      <c r="B97" t="n">
+        <v>100536</v>
+      </c>
+      <c r="C97" t="n">
+        <v>361145</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>03310</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>CHRISTHPER MILLAR  BENTACOURT</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>SALTILLO VILLALTA</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>03-05-2026 14:24:07</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>03-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I97" t="n">
+        <v>0</v>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L97" t="n">
+        <v>649</v>
+      </c>
+      <c r="M97" t="n">
+        <v>11</v>
+      </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>28-04-2027 14:24:07</t>
+        </is>
+      </c>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P97" t="inlineStr"/>
+      <c r="Q97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>96</v>
+      </c>
+      <c r="B98" t="n">
+        <v>100538</v>
+      </c>
+      <c r="C98" t="n">
+        <v>223303</v>
+      </c>
+      <c r="D98" t="n">
+        <v>20810</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>ALBERTO  CALZADA VELAZQUEZ</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>AZAHARES CUL</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>03-05-2026 14:46:26</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>05-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I98" t="n">
+        <v>0</v>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L98" t="n">
+        <v>449</v>
+      </c>
+      <c r="M98" t="n">
+        <v>11</v>
+      </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>28-04-2027 14:46:26</t>
+        </is>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P98" t="n">
+        <v>19839</v>
+      </c>
+      <c r="Q98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>97</v>
+      </c>
+      <c r="B99" t="n">
+        <v>100559</v>
+      </c>
+      <c r="C99" t="n">
+        <v>44466</v>
+      </c>
+      <c r="D99" t="n">
+        <v>42329</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>CECILIA GUADALUPE BELTRAN RODRIGUEZ</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>PASEO 2000</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>04-05-2026 7:50:27</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>04-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I99" t="n">
+        <v>0</v>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L99" t="n">
+        <v>649</v>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr"/>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P99" t="inlineStr"/>
+      <c r="Q99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>98</v>
+      </c>
+      <c r="B100" t="n">
+        <v>100561</v>
+      </c>
+      <c r="C100" t="n">
+        <v>361276</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>03441</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>MARIA DE LOS ANGELES  PEREZ  ARENAS</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>TEC MXL</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>04-05-2026 8:13:11</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>04-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I100" t="n">
+        <v>0</v>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L100" t="n">
+        <v>549</v>
+      </c>
+      <c r="M100" t="n">
+        <v>11</v>
+      </c>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>29-04-2027 8:13:11</t>
+        </is>
+      </c>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P100" t="inlineStr"/>
+      <c r="Q100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>99</v>
+      </c>
+      <c r="B101" t="n">
+        <v>100563</v>
+      </c>
+      <c r="C101" t="n">
+        <v>112854</v>
+      </c>
+      <c r="D101" t="n">
+        <v>10589</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>SERGIO MOISÉS  FLORES MÁRQUEZ</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>SEND MXL</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>04-05-2026 8:18:48</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>04-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I101" t="n">
+        <v>0</v>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L101" t="n">
+        <v>649</v>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr"/>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P101" t="inlineStr"/>
+      <c r="Q101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>100</v>
+      </c>
+      <c r="B102" t="n">
+        <v>100568</v>
+      </c>
+      <c r="C102" t="n">
+        <v>361268</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>03433</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>LIDIA LUCIA LOPEZ JERONIMO</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>PABELLON RTO</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>04-05-2026 9:06:03</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>04-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I102" t="n">
+        <v>0</v>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L102" t="n">
+        <v>549</v>
+      </c>
+      <c r="M102" t="n">
+        <v>11</v>
+      </c>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>29-04-2027 9:06:03</t>
+        </is>
+      </c>
+      <c r="O102" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P102" t="inlineStr"/>
+      <c r="Q102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>101</v>
+      </c>
+      <c r="B103" t="n">
+        <v>100570</v>
+      </c>
+      <c r="C103" t="n">
+        <v>227390</v>
+      </c>
+      <c r="D103" t="n">
+        <v>24895</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>NURY GUADALUPE  AVALOS  ESPARZA</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>SANTA FE</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>04-05-2026 9:24:12</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>01-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I103" t="n">
+        <v>0</v>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L103" t="n">
+        <v>449</v>
+      </c>
+      <c r="M103" t="n">
+        <v>11</v>
+      </c>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>29-04-2027 9:24:12</t>
+        </is>
+      </c>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P103" t="n">
+        <v>22080</v>
+      </c>
+      <c r="Q103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>102</v>
+      </c>
+      <c r="B104" t="n">
+        <v>96322</v>
+      </c>
+      <c r="C104" t="n">
+        <v>340658</v>
+      </c>
+      <c r="D104" t="n">
+        <v>18476</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>MONICA BERALD BERMUDEZ ALDUCIN</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>METEPEC</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>09-03-2026 16:14:08</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>03-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I104" t="n">
+        <v>0</v>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L104" t="n">
+        <v>649</v>
+      </c>
+      <c r="M104" t="n">
+        <v>11</v>
+      </c>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>04-03-2027 16:14:08</t>
+        </is>
+      </c>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P104" t="n">
+        <v>91712</v>
+      </c>
+      <c r="Q104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>103</v>
+      </c>
+      <c r="B105" t="n">
+        <v>98943</v>
+      </c>
+      <c r="C105" t="n">
+        <v>37106</v>
+      </c>
+      <c r="D105" t="n">
+        <v>34985</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>JUAN FRANCISCO PITONES NORIEGA</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>SEND MXL</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>08-04-2026 20:42:26</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>01-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I105" t="n">
+        <v>0</v>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L105" t="n">
+        <v>399</v>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N105" t="inlineStr"/>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P105" t="n">
+        <v>96274</v>
+      </c>
+      <c r="Q105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>104</v>
+      </c>
+      <c r="B106" t="n">
+        <v>100480</v>
+      </c>
+      <c r="C106" t="n">
+        <v>360840</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>03005</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>TANIA ELIZABETH VILLAREAL PEREDA</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>INSURGENTES</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>01-05-2026 7:38:40</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>01-08-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I106" t="n">
+        <v>0</v>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L106" t="n">
+        <v>1549</v>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr"/>
+      <c r="O106" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P106" t="inlineStr"/>
+      <c r="Q106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>105</v>
+      </c>
+      <c r="B107" t="n">
+        <v>100483</v>
+      </c>
+      <c r="C107" t="n">
+        <v>360852</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>03017</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>ELIUD RAMIREZ BELMARES</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>SALTILLO VILLALTA</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>01-05-2026 8:37:34</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>01-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I107" t="n">
+        <v>0</v>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L107" t="n">
+        <v>649</v>
+      </c>
+      <c r="M107" t="n">
+        <v>11</v>
+      </c>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t>26-04-2027 8:37:34</t>
+        </is>
+      </c>
+      <c r="O107" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P107" t="inlineStr"/>
+      <c r="Q107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>106</v>
+      </c>
+      <c r="B108" t="n">
+        <v>100515</v>
+      </c>
+      <c r="C108" t="n">
+        <v>361056</v>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>03221</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>GILBERTO  BARRIOS HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>SALTILLO VILLALTA</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>02-05-2026 7:46:19</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>02-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I108" t="n">
+        <v>0</v>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L108" t="n">
+        <v>649</v>
+      </c>
+      <c r="M108" t="n">
+        <v>11</v>
+      </c>
+      <c r="N108" t="inlineStr">
+        <is>
+          <t>27-04-2027 7:46:19</t>
+        </is>
+      </c>
+      <c r="O108" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P108" t="inlineStr"/>
+      <c r="Q108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>107</v>
+      </c>
+      <c r="B109" t="n">
+        <v>100530</v>
+      </c>
+      <c r="C109" t="n">
+        <v>361181</v>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>03346</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>ARGEL RODRIGUEZ CASTILLO</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>SEND CHIH</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>03-05-2026 11:59:19</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>03-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I109" t="n">
+        <v>0</v>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L109" t="n">
+        <v>649</v>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N109" t="inlineStr"/>
+      <c r="O109" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P109" t="inlineStr"/>
+      <c r="Q109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>108</v>
+      </c>
+      <c r="B110" t="n">
+        <v>100533</v>
+      </c>
+      <c r="C110" t="n">
+        <v>30229</v>
+      </c>
+      <c r="D110" t="n">
+        <v>28159</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>LARRY GERARDO ALFARO SUBIA</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>SANTA FE</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>03-05-2026 12:43:54</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>04-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I110" t="n">
+        <v>0</v>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L110" t="n">
+        <v>399</v>
+      </c>
+      <c r="M110" t="n">
+        <v>11</v>
+      </c>
+      <c r="N110" t="inlineStr">
+        <is>
+          <t>28-04-2027 12:43:54</t>
+        </is>
+      </c>
+      <c r="O110" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P110" t="n">
+        <v>6790</v>
+      </c>
+      <c r="Q110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>109</v>
+      </c>
+      <c r="B111" t="n">
+        <v>100547</v>
+      </c>
+      <c r="C111" t="n">
+        <v>253927</v>
+      </c>
+      <c r="D111" t="n">
+        <v>51431</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>ANGEL GIOVANNI VAZQUEZ MORALES</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>PABELLON RTO</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>04-05-2026 5:53:25</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>04-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I111" t="n">
+        <v>0</v>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L111" t="n">
+        <v>549</v>
+      </c>
+      <c r="M111" t="n">
+        <v>11</v>
+      </c>
+      <c r="N111" t="inlineStr">
+        <is>
+          <t>29-04-2027 5:53:25</t>
+        </is>
+      </c>
+      <c r="O111" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P111" t="inlineStr"/>
+      <c r="Q111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>110</v>
+      </c>
+      <c r="B112" t="n">
+        <v>100548</v>
+      </c>
+      <c r="C112" t="n">
+        <v>361249</v>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>03414</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>JULIO MARTIN ALMEDIA OLMEDO</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>PABELLON RTO</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>04-05-2026 6:01:54</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>04-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I112" t="n">
+        <v>0</v>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L112" t="n">
+        <v>549</v>
+      </c>
+      <c r="M112" t="n">
+        <v>11</v>
+      </c>
+      <c r="N112" t="inlineStr">
+        <is>
+          <t>29-04-2027 6:01:54</t>
+        </is>
+      </c>
+      <c r="O112" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P112" t="inlineStr"/>
+      <c r="Q112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>111</v>
+      </c>
+      <c r="B113" t="n">
+        <v>100566</v>
+      </c>
+      <c r="C113" t="n">
+        <v>216187</v>
+      </c>
+      <c r="D113" t="n">
+        <v>13695</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>MARIA FERNANDA SALDAÑA ARRIAGA</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>SEND SALTILLO</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>04-05-2026 8:59:02</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>04-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I113" t="n">
+        <v>0</v>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L113" t="n">
+        <v>549</v>
+      </c>
+      <c r="M113" t="n">
+        <v>11</v>
+      </c>
+      <c r="N113" t="inlineStr">
+        <is>
+          <t>29-04-2027 8:59:02</t>
+        </is>
+      </c>
+      <c r="O113" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P113" t="inlineStr"/>
+      <c r="Q113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>112</v>
+      </c>
+      <c r="B114" t="n">
+        <v>100497</v>
+      </c>
+      <c r="C114" t="n">
+        <v>179725</v>
+      </c>
+      <c r="D114" t="n">
+        <v>77232</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>EBER  MAGDIEL  CASTILLEJA  BARROSO</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>SEND SALTILLO</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>01-05-2026 15:17:21</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>01-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I114" t="n">
+        <v>0</v>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L114" t="n">
+        <v>499</v>
+      </c>
+      <c r="M114" t="n">
+        <v>11</v>
+      </c>
+      <c r="N114" t="inlineStr">
+        <is>
+          <t>26-04-2027 15:17:21</t>
+        </is>
+      </c>
+      <c r="O114" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P114" t="n">
+        <v>4540</v>
+      </c>
+      <c r="Q114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Reporte generado: 04-05-2026 04:49 p. m.</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr"/>
+      <c r="C115" t="inlineStr"/>
+      <c r="D115" t="inlineStr"/>
+      <c r="E115" t="inlineStr"/>
+      <c r="F115" t="inlineStr"/>
+      <c r="G115" t="inlineStr"/>
+      <c r="H115" t="inlineStr"/>
+      <c r="I115" t="inlineStr"/>
+      <c r="J115" t="inlineStr"/>
+      <c r="K115" t="inlineStr"/>
+      <c r="L115" t="inlineStr"/>
+      <c r="M115" t="inlineStr"/>
+      <c r="N115" t="inlineStr"/>
+      <c r="O115" t="inlineStr"/>
+      <c r="P115" t="inlineStr"/>
+      <c r="Q115" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/descargas/cargos_recurrentes.xlsx
+++ b/data/descargas/cargos_recurrentes.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q10"/>
+  <dimension ref="A1:Q56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -613,7 +613,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>VICTOR MANUEL  ORTIZ  CARRISOZA</t>
+          <t>CARLOS HERNAN CORTEZ CARRISOZA</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -668,34 +668,32 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>102657</v>
+        <v>102712</v>
       </c>
       <c r="C4" t="n">
-        <v>362251</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>04412</t>
-        </is>
+        <v>25650</v>
+      </c>
+      <c r="D4" t="n">
+        <v>23591</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RODRIGO ALEJANDRO  MARTINEZ  GARCIA</t>
+          <t>AZUCENA  CAMACHO  HERRERA</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>METEPEC</t>
+          <t>PABELLON RTO</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>01-06-2026 5:21:32</t>
+          <t>01-06-2026 12:20:27</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>01-07-2026 23:59:59</t>
+          <t>01-09-2026 23:59:59</t>
         </is>
       </c>
       <c r="I4" t="n">
@@ -712,7 +710,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>799</v>
+        <v>1449</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -733,17 +731,19 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>102656</v>
+        <v>102703</v>
       </c>
       <c r="C5" t="n">
-        <v>117076</v>
-      </c>
-      <c r="D5" t="n">
-        <v>14791</v>
+        <v>365950</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>08110</t>
+        </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>VIRGINIA VAZQUEZ CHAVEZ</t>
+          <t>CUAUHTEMOC RODRIGUEZ POSADA</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -753,12 +753,12 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>01-06-2026 5:10:04</t>
+          <t>01-06-2026 11:14:21</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>01-07-2026 23:59:59</t>
+          <t>01-09-2026 23:59:59</t>
         </is>
       </c>
       <c r="I5" t="n">
@@ -775,14 +775,14 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>549</v>
+        <v>1449</v>
       </c>
       <c r="M5" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>27-05-2027 5:10:04</t>
+          <t>27-05-2027 11:14:21</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -798,27 +798,29 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>102654</v>
+        <v>102675</v>
       </c>
       <c r="C6" t="n">
-        <v>282587</v>
-      </c>
-      <c r="D6" t="n">
-        <v>80088</v>
+        <v>365904</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>08064</t>
+        </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>MARIA DE JESUS PEREZ VAZQUEZ</t>
+          <t>REYNA CARMEN PADILLA VALDEZ</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>MISION ENS</t>
+          <t>VILLAS DEL REY</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>01-06-2026 5:05:38</t>
+          <t>01-06-2026 8:16:24</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -840,19 +842,17 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>549</v>
-      </c>
-      <c r="M6" t="n">
-        <v>11</v>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>27-05-2027 5:05:38</t>
-        </is>
-      </c>
+        <v>649</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Domiciliado</t>
+          <t>Recurrente</t>
         </is>
       </c>
       <c r="P6" t="inlineStr"/>
@@ -863,34 +863,34 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>102658</v>
+        <v>102699</v>
       </c>
       <c r="C7" t="n">
-        <v>210572</v>
+        <v>365932</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>08080</t>
+          <t>08092</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>JESUS ANTONIO VEGA GONZALEZ</t>
+          <t>CYNTHIA ANGELICA OSCOY CORIA</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>AZAHARES CUL</t>
+          <t>TLALNEPANTLA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>01-06-2026 5:23:11</t>
+          <t>01-06-2026 10:19:03</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>02-07-2026 23:59:59</t>
+          <t>01-07-2026 23:59:59</t>
         </is>
       </c>
       <c r="I7" t="n">
@@ -903,18 +903,18 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>RENOVACIÓN</t>
+          <t>NUEVO</t>
         </is>
       </c>
       <c r="L7" t="n">
         <v>549</v>
       </c>
       <c r="M7" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>28-11-2026 5:23:11</t>
+          <t>27-05-2027 10:19:03</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -922,9 +922,7 @@
           <t>Domiciliado</t>
         </is>
       </c>
-      <c r="P7" t="n">
-        <v>77078</v>
-      </c>
+      <c r="P7" t="inlineStr"/>
       <c r="Q7" t="inlineStr"/>
     </row>
     <row r="8">
@@ -932,34 +930,34 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>102660</v>
+        <v>102677</v>
       </c>
       <c r="C8" t="n">
-        <v>365876</v>
+        <v>365596</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>08036</t>
+          <t>07756</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>EDUARDO VALSECA RODRIGUEZ</t>
+          <t>NAHOMI RIVERA ARMENTA</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>TLALNEPANTLA</t>
+          <t>PABELLON RTO</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>01-06-2026 5:35:45</t>
+          <t>01-06-2026 8:23:45</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>01-07-2026 23:59:59</t>
+          <t>01-09-2026 23:59:59</t>
         </is>
       </c>
       <c r="I8" t="n">
@@ -976,19 +974,17 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>549</v>
-      </c>
-      <c r="M8" t="n">
-        <v>11</v>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>27-05-2027 5:35:45</t>
-        </is>
-      </c>
+        <v>1449</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Domiciliado</t>
+          <t>Recurrente</t>
         </is>
       </c>
       <c r="P8" t="inlineStr"/>
@@ -999,29 +995,29 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>102655</v>
+        <v>102684</v>
       </c>
       <c r="C9" t="n">
-        <v>365871</v>
+        <v>311162</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>08031</t>
+          <t>08661</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>FRIDA PAOLA HERNANDEZ VARGAS</t>
+          <t>SOFIA FERNANDEZ LUQUE</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>PASEO 2000</t>
+          <t>VILLA VERDE</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>01-06-2026 5:09:04</t>
+          <t>01-06-2026 8:52:55</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1043,44 +1039,3068 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>649</v>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>Indefinido</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
+        <v>499</v>
+      </c>
+      <c r="M9" t="n">
+        <v>5</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>28-11-2026 8:52:55</t>
+        </is>
+      </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Recurrente</t>
+          <t>Domiciliado</t>
         </is>
       </c>
       <c r="P9" t="inlineStr"/>
       <c r="Q9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Reporte generado: 01-06-2026 12:53 p. m.</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
+      <c r="A10" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" t="n">
+        <v>102693</v>
+      </c>
+      <c r="C10" t="n">
+        <v>156616</v>
+      </c>
+      <c r="D10" t="n">
+        <v>54161</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>CAMILA AMADOR RUELAS</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>TEC MXL</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>01-06-2026 10:04:01</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>01-07-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>499</v>
+      </c>
+      <c r="M10" t="n">
+        <v>5</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>28-11-2026 10:04:01</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr"/>
       <c r="Q10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" t="n">
+        <v>102700</v>
+      </c>
+      <c r="C11" t="n">
+        <v>365935</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>08095</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>CINTHIA IVETTE  CORDOVA CORONADO</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>SEND MXL</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>01-06-2026 10:21:04</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>01-07-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>649</v>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" t="n">
+        <v>102681</v>
+      </c>
+      <c r="C12" t="n">
+        <v>98920</v>
+      </c>
+      <c r="D12" t="n">
+        <v>96676</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>JAVIER SALCIDO MAYORAL</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>TEC MXL</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>01-06-2026 8:41:41</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>01-07-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>499</v>
+      </c>
+      <c r="M12" t="n">
+        <v>5</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>28-11-2026 8:41:41</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" t="n">
+        <v>102713</v>
+      </c>
+      <c r="C13" t="n">
+        <v>365971</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>08131</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>MARTA ROSA CERBON AMBRIZ</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>METEPEC</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>01-06-2026 12:27:24</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>01-07-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>649</v>
+      </c>
+      <c r="M13" t="n">
+        <v>11</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>27-05-2027 12:27:24</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" t="n">
+        <v>102685</v>
+      </c>
+      <c r="C14" t="n">
+        <v>365915</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>08075</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>MARTHA LORENA ANGULO VALENZUELA</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>PAPALOTE TJ</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>01-06-2026 9:08:16</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>02-07-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
+        <v>649</v>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" t="n">
+        <v>102671</v>
+      </c>
+      <c r="C15" t="n">
+        <v>32897</v>
+      </c>
+      <c r="D15" t="n">
+        <v>30820</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>CLAUDIO MARTINEZ DIAZ</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>SAN LUIS</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>01-06-2026 7:30:29</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>01-07-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L15" t="n">
+        <v>449</v>
+      </c>
+      <c r="M15" t="n">
+        <v>11</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>27-05-2027 7:30:29</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>15649</v>
+      </c>
+      <c r="Q15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" t="n">
+        <v>102686</v>
+      </c>
+      <c r="C16" t="n">
+        <v>365921</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>08081</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>CLAUDIA FERNANDA SILVA MOLINA</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>MISION ENS</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>01-06-2026 9:35:02</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>01-07-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L16" t="n">
+        <v>499</v>
+      </c>
+      <c r="M16" t="n">
+        <v>5</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>28-11-2026 9:35:02</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" t="n">
+        <v>102655</v>
+      </c>
+      <c r="C17" t="n">
+        <v>365871</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>08031</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>FRIDA PAOLA HERNANDEZ VARGAS</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>PASEO 2000</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>01-06-2026 5:09:04</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>01-07-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L17" t="n">
+        <v>649</v>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" t="n">
+        <v>102667</v>
+      </c>
+      <c r="C18" t="n">
+        <v>364877</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>07037</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>ANDREA JACQUELENE ASCENCIO RODRIGUEZ</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>PASEO LA PAZ</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>01-06-2026 6:51:06</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>01-07-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L18" t="n">
+        <v>549</v>
+      </c>
+      <c r="M18" t="n">
+        <v>11</v>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>27-05-2027 6:51:06</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" t="n">
+        <v>102701</v>
+      </c>
+      <c r="C19" t="n">
+        <v>258431</v>
+      </c>
+      <c r="D19" t="n">
+        <v>55935</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>ELIZABETH TOLENTINO HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>TEC MXL</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>01-06-2026 10:59:14</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>01-07-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L19" t="n">
+        <v>499</v>
+      </c>
+      <c r="M19" t="n">
+        <v>5</v>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>28-11-2026 10:59:14</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" t="n">
+        <v>102597</v>
+      </c>
+      <c r="C20" t="n">
+        <v>307208</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>04707</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>LUIS ANGEL VILDOSOLA ROMO</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>INDEPENDENCIA</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>30-05-2026 10:52:40</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>01-07-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L20" t="n">
+        <v>499</v>
+      </c>
+      <c r="M20" t="n">
+        <v>11</v>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>25-05-2027 10:52:40</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P20" t="n">
+        <v>81539</v>
+      </c>
+      <c r="Q20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" t="n">
+        <v>102690</v>
+      </c>
+      <c r="C21" t="n">
+        <v>365909</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>08069</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>FERNANDO ESTEBAN  SANTOS  MARTINEZ</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>TLALNEPANTLA</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>01-06-2026 9:55:32</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>01-07-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L21" t="n">
+        <v>649</v>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" t="n">
+        <v>102668</v>
+      </c>
+      <c r="C22" t="n">
+        <v>365890</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>08050</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>ROLANDO  JUAREZ MUÑOZ</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>METEPEC</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>01-06-2026 6:59:30</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>01-07-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L22" t="n">
+        <v>649</v>
+      </c>
+      <c r="M22" t="n">
+        <v>11</v>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>27-05-2027 6:59:30</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" t="n">
+        <v>102682</v>
+      </c>
+      <c r="C23" t="n">
+        <v>290065</v>
+      </c>
+      <c r="D23" t="n">
+        <v>87563</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>ZAIDA JEANETH AGUILAR ROMERO</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>SEND MXL</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>01-06-2026 8:44:35</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>01-07-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L23" t="n">
+        <v>649</v>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>22</v>
+      </c>
+      <c r="B24" t="n">
+        <v>100180</v>
+      </c>
+      <c r="C24" t="n">
+        <v>293308</v>
+      </c>
+      <c r="D24" t="n">
+        <v>90806</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>PATRICIA  CARMONA VILLALVA</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>PASEO 2000</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>27-04-2026 8:32:46</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>26-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>CANCELADO</t>
+        </is>
+      </c>
+      <c r="L24" t="n">
+        <v>549</v>
+      </c>
+      <c r="M24" t="n">
+        <v>11</v>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>22-04-2027 8:32:46</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P24" t="n">
+        <v>89837</v>
+      </c>
+      <c r="Q24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>23</v>
+      </c>
+      <c r="B25" t="n">
+        <v>102673</v>
+      </c>
+      <c r="C25" t="n">
+        <v>365901</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>08061</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>JENNIFER  GARIBAY  SAAVEDRA</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>SEND MXL</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>01-06-2026 8:00:14</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>01-07-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L25" t="n">
+        <v>549</v>
+      </c>
+      <c r="M25" t="n">
+        <v>11</v>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>27-05-2027 8:00:14</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>24</v>
+      </c>
+      <c r="B26" t="n">
+        <v>102706</v>
+      </c>
+      <c r="C26" t="n">
+        <v>365962</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>08122</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>JOSE ANGEL  PARRA LEON</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>SALTILLO VILLALTA</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>01-06-2026 11:47:54</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>01-07-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L26" t="n">
+        <v>799</v>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>25</v>
+      </c>
+      <c r="B27" t="n">
+        <v>102678</v>
+      </c>
+      <c r="C27" t="n">
+        <v>51159</v>
+      </c>
+      <c r="D27" t="n">
+        <v>49015</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>NATHALIA JAQUELINE ROMERO MARRUJO</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>AZAHARES CUL</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>01-06-2026 8:28:51</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>01-07-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L27" t="n">
+        <v>999</v>
+      </c>
+      <c r="M27" t="n">
+        <v>11</v>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>27-05-2027 8:28:51</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>26</v>
+      </c>
+      <c r="B28" t="n">
+        <v>102709</v>
+      </c>
+      <c r="C28" t="n">
+        <v>365967</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>08127</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>MARIAM YARENY SANZ MOLINA</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>MISION ENS</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>01-06-2026 12:11:53</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>01-07-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L28" t="n">
+        <v>499</v>
+      </c>
+      <c r="M28" t="n">
+        <v>5</v>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>28-11-2026 12:11:53</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>27</v>
+      </c>
+      <c r="B29" t="n">
+        <v>100831</v>
+      </c>
+      <c r="C29" t="n">
+        <v>124958</v>
+      </c>
+      <c r="D29" t="n">
+        <v>22634</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>ANDREA BERENICE  SOTO SOLIS</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>SEND CHIH</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>06-05-2026 8:19:34</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>01-07-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L29" t="n">
+        <v>399</v>
+      </c>
+      <c r="M29" t="n">
+        <v>11</v>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>01-05-2027 8:19:34</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P29" t="n">
+        <v>30724</v>
+      </c>
+      <c r="Q29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>28</v>
+      </c>
+      <c r="B30" t="n">
+        <v>102711</v>
+      </c>
+      <c r="C30" t="n">
+        <v>365970</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>08130</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>VIRIDIANA GUADALUPE MOLINA ALVAREZ</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>MISION ENS</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>01-06-2026 12:16:24</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>01-07-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L30" t="n">
+        <v>499</v>
+      </c>
+      <c r="M30" t="n">
+        <v>5</v>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>28-11-2026 12:16:24</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>29</v>
+      </c>
+      <c r="B31" t="n">
+        <v>102688</v>
+      </c>
+      <c r="C31" t="n">
+        <v>365923</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>08083</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>MAGALY  GONZALEZ ALVAREZ</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>AZAHARES CUL</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>01-06-2026 9:40:52</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>01-07-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L31" t="n">
+        <v>649</v>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>30</v>
+      </c>
+      <c r="B32" t="n">
+        <v>102657</v>
+      </c>
+      <c r="C32" t="n">
+        <v>362251</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>04412</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>RODRIGO ALEJANDRO  MARTINEZ  GARCIA</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>METEPEC</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>01-06-2026 5:21:32</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>01-07-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L32" t="n">
+        <v>799</v>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>31</v>
+      </c>
+      <c r="B33" t="n">
+        <v>102656</v>
+      </c>
+      <c r="C33" t="n">
+        <v>117076</v>
+      </c>
+      <c r="D33" t="n">
+        <v>14791</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>VIRGINIA VAZQUEZ CHAVEZ</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>MISION ENS</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>01-06-2026 5:10:04</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>01-07-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L33" t="n">
+        <v>549</v>
+      </c>
+      <c r="M33" t="n">
+        <v>11</v>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>27-05-2027 5:10:04</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>32</v>
+      </c>
+      <c r="B34" t="n">
+        <v>102669</v>
+      </c>
+      <c r="C34" t="n">
+        <v>365896</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>08056</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>MELANY FERNANDA BARRERAS  RODRIGUEZ</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>SEND MXL</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>01-06-2026 7:23:03</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>01-07-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L34" t="n">
+        <v>549</v>
+      </c>
+      <c r="M34" t="n">
+        <v>11</v>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>27-05-2027 7:23:03</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>33</v>
+      </c>
+      <c r="B35" t="n">
+        <v>102670</v>
+      </c>
+      <c r="C35" t="n">
+        <v>365893</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>08053</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>ORALIA MONTOYA GONZALEZ</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>METEPEC</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>01-06-2026 7:28:40</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>01-09-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I35" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L35" t="n">
+        <v>1549</v>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>34</v>
+      </c>
+      <c r="B36" t="n">
+        <v>102687</v>
+      </c>
+      <c r="C36" t="n">
+        <v>243723</v>
+      </c>
+      <c r="D36" t="n">
+        <v>41228</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>ALONSO  CERVANTES  AGUIAR</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>SEND MXL</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>01-06-2026 9:37:09</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>01-07-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L36" t="n">
+        <v>999</v>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P36" t="n">
+        <v>32648</v>
+      </c>
+      <c r="Q36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>35</v>
+      </c>
+      <c r="B37" t="n">
+        <v>102665</v>
+      </c>
+      <c r="C37" t="n">
+        <v>365884</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>08044</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>ROSA BRISEIDA SOLANO QUIRAZCO</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>PAPALOTE TJ</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>01-06-2026 6:13:16</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>01-07-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L37" t="n">
+        <v>649</v>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>36</v>
+      </c>
+      <c r="B38" t="n">
+        <v>102676</v>
+      </c>
+      <c r="C38" t="n">
+        <v>365906</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>08066</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>NIDELIN GISSELLE MARTINEZ</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>PASEO 2000</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>01-06-2026 8:20:46</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>01-07-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I38" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L38" t="n">
+        <v>649</v>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr"/>
+      <c r="Q38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>37</v>
+      </c>
+      <c r="B39" t="n">
+        <v>102708</v>
+      </c>
+      <c r="C39" t="n">
+        <v>360581</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>02746</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>JESSICA GONZALEZ  SAFONT</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>INSURGENTES</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>01-06-2026 12:05:12</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>01-09-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I39" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L39" t="n">
+        <v>1549</v>
+      </c>
+      <c r="M39" t="n">
+        <v>9</v>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>27-05-2027 12:05:12</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>38</v>
+      </c>
+      <c r="B40" t="n">
+        <v>102680</v>
+      </c>
+      <c r="C40" t="n">
+        <v>329287</v>
+      </c>
+      <c r="D40" t="n">
+        <v>14341</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>JASON JARIB ANTONIO ALBAÑIL</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>PASEO 2000</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>01-06-2026 8:41:12</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>01-07-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I40" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L40" t="n">
+        <v>649</v>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr"/>
+      <c r="Q40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>39</v>
+      </c>
+      <c r="B41" t="n">
+        <v>102666</v>
+      </c>
+      <c r="C41" t="n">
+        <v>365888</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>08048</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>EUDORO DE LA MORA AGUILAR</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>PAPALOTE TJ</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>01-06-2026 6:27:05</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>01-09-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I41" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L41" t="n">
+        <v>1449</v>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr"/>
+      <c r="Q41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>40</v>
+      </c>
+      <c r="B42" t="n">
+        <v>102654</v>
+      </c>
+      <c r="C42" t="n">
+        <v>282587</v>
+      </c>
+      <c r="D42" t="n">
+        <v>80088</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>MARIA DE JESUS PEREZ VAZQUEZ</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>MISION ENS</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>01-06-2026 5:05:38</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>01-07-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I42" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L42" t="n">
+        <v>549</v>
+      </c>
+      <c r="M42" t="n">
+        <v>11</v>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>27-05-2027 5:05:38</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr"/>
+      <c r="Q42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>41</v>
+      </c>
+      <c r="B43" t="n">
+        <v>102689</v>
+      </c>
+      <c r="C43" t="n">
+        <v>221420</v>
+      </c>
+      <c r="D43" t="n">
+        <v>18927</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>MARILU JAZMIN  CASTRO  ARAUJO</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>CARROUSEL TJ</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>01-06-2026 9:50:24</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>01-07-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L43" t="n">
+        <v>499</v>
+      </c>
+      <c r="M43" t="n">
+        <v>5</v>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>28-11-2026 9:50:24</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr"/>
+      <c r="Q43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>42</v>
+      </c>
+      <c r="B44" t="n">
+        <v>102679</v>
+      </c>
+      <c r="C44" t="n">
+        <v>78496</v>
+      </c>
+      <c r="D44" t="n">
+        <v>76298</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>MARIA VALENZUELA LOPEZ</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>AZAHARES CUL</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>01-06-2026 8:36:04</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>01-07-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I44" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L44" t="n">
+        <v>549</v>
+      </c>
+      <c r="M44" t="n">
+        <v>11</v>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>27-05-2027 8:36:04</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr"/>
+      <c r="Q44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>43</v>
+      </c>
+      <c r="B45" t="n">
+        <v>102694</v>
+      </c>
+      <c r="C45" t="n">
+        <v>365930</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>08090</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>DIANA LIZETH IBARRA GARIBO</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>PABELLON RTO</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>01-06-2026 10:07:05</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>01-07-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I45" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L45" t="n">
+        <v>649</v>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr"/>
+      <c r="Q45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>44</v>
+      </c>
+      <c r="B46" t="n">
+        <v>102698</v>
+      </c>
+      <c r="C46" t="n">
+        <v>365933</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>08093</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>LUIS ANGEL  BARRIOS DELGADO</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>SEND MXL</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>01-06-2026 10:17:08</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>01-07-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I46" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L46" t="n">
+        <v>649</v>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr"/>
+      <c r="Q46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>45</v>
+      </c>
+      <c r="B47" t="n">
+        <v>102705</v>
+      </c>
+      <c r="C47" t="n">
+        <v>190702</v>
+      </c>
+      <c r="D47" t="n">
+        <v>88209</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>DAYANA  PEREZ CARAVEO</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>LOMA BONITA</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>01-06-2026 11:24:58</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>01-07-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I47" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L47" t="n">
+        <v>499</v>
+      </c>
+      <c r="M47" t="n">
+        <v>5</v>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>28-11-2026 11:24:58</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr"/>
+      <c r="Q47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>46</v>
+      </c>
+      <c r="B48" t="n">
+        <v>102710</v>
+      </c>
+      <c r="C48" t="n">
+        <v>360582</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>02747</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>MARIA CAMILA GARCIA GONZALEZ</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>INSURGENTES</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>01-06-2026 12:15:54</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>01-07-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L48" t="n">
+        <v>549</v>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr"/>
+      <c r="Q48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>47</v>
+      </c>
+      <c r="B49" t="n">
+        <v>101699</v>
+      </c>
+      <c r="C49" t="n">
+        <v>307203</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>04702</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>ANGELICA ROMO TIRADO</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>INDEPENDENCIA</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>18-05-2026 18:11:14</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>01-07-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I49" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L49" t="n">
+        <v>499</v>
+      </c>
+      <c r="M49" t="n">
+        <v>11</v>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>13-05-2027 18:11:14</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P49" t="n">
+        <v>81538</v>
+      </c>
+      <c r="Q49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>48</v>
+      </c>
+      <c r="B50" t="n">
+        <v>102658</v>
+      </c>
+      <c r="C50" t="n">
+        <v>210572</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>08080</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>JESUS ANTONIO VEGA GONZALEZ</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>AZAHARES CUL</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>01-06-2026 5:23:11</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>02-07-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L50" t="n">
+        <v>549</v>
+      </c>
+      <c r="M50" t="n">
+        <v>5</v>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>28-11-2026 5:23:11</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P50" t="n">
+        <v>77078</v>
+      </c>
+      <c r="Q50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>49</v>
+      </c>
+      <c r="B51" t="n">
+        <v>102660</v>
+      </c>
+      <c r="C51" t="n">
+        <v>365876</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>08036</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>EDUARDO VALSECA RODRIGUEZ</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>TLALNEPANTLA</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>01-06-2026 5:35:45</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>01-07-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I51" t="n">
+        <v>0</v>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L51" t="n">
+        <v>549</v>
+      </c>
+      <c r="M51" t="n">
+        <v>11</v>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>27-05-2027 5:35:45</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr"/>
+      <c r="Q51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>50</v>
+      </c>
+      <c r="B52" t="n">
+        <v>102683</v>
+      </c>
+      <c r="C52" t="n">
+        <v>156787</v>
+      </c>
+      <c r="D52" t="n">
+        <v>54331</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>MIRNA PARRA PARRA</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>TEC MXL</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>01-06-2026 8:47:30</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>01-07-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I52" t="n">
+        <v>0</v>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L52" t="n">
+        <v>499</v>
+      </c>
+      <c r="M52" t="n">
+        <v>5</v>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>28-11-2026 8:47:30</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr"/>
+      <c r="Q52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>51</v>
+      </c>
+      <c r="B53" t="n">
+        <v>100481</v>
+      </c>
+      <c r="C53" t="n">
+        <v>232335</v>
+      </c>
+      <c r="D53" t="n">
+        <v>29840</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>MIRIAM SUSANA LIZARRAGA OROZCO</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>VILLA VERDE</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>01-05-2026 7:58:04</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>01-07-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I53" t="n">
+        <v>1</v>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L53" t="n">
+        <v>399</v>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P53" t="n">
+        <v>45917</v>
+      </c>
+      <c r="Q53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>52</v>
+      </c>
+      <c r="B54" t="n">
+        <v>102664</v>
+      </c>
+      <c r="C54" t="n">
+        <v>255326</v>
+      </c>
+      <c r="D54" t="n">
+        <v>52830</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>PAMELA GOMEZ RINCONES</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>PABELLON RTO</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>01-06-2026 5:59:17</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>01-09-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I54" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L54" t="n">
+        <v>1449</v>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr"/>
+      <c r="Q54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>53</v>
+      </c>
+      <c r="B55" t="n">
+        <v>102696</v>
+      </c>
+      <c r="C55" t="n">
+        <v>73246</v>
+      </c>
+      <c r="D55" t="n">
+        <v>71064</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>ANDREA JULIETA  LIZARRAGA  PEREZ</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>TEC MXL</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>01-06-2026 10:08:00</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>01-07-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I55" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L55" t="n">
+        <v>499</v>
+      </c>
+      <c r="M55" t="n">
+        <v>5</v>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>28-11-2026 10:08:00</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr"/>
+      <c r="Q55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Reporte generado: 01-06-2026 07:59 p. m.</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr"/>
+      <c r="C56" t="inlineStr"/>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
+      <c r="O56" t="inlineStr"/>
+      <c r="P56" t="inlineStr"/>
+      <c r="Q56" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/descargas/cargos_recurrentes.xlsx
+++ b/data/descargas/cargos_recurrentes.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q3"/>
+  <dimension ref="A1:Q18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -599,27 +599,1014 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Reporte generado: 01-07-2026 10:53 a. m. </t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="n">
+        <v>105014</v>
+      </c>
+      <c r="C3" t="n">
+        <v>307487</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>04986</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>ASHLEY ANGULO LAFARGA</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>VILLA VERDE</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>01-07-2026 5:55:03</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>01-08-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>549</v>
+      </c>
+      <c r="M3" t="n">
+        <v>11</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>26-06-2027 5:55:03</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="n">
+        <v>102843</v>
+      </c>
+      <c r="C4" t="n">
+        <v>218531</v>
+      </c>
+      <c r="D4" t="n">
+        <v>16039</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>MARIA EUGENIA CUESTA GUERRERRO</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>SEND MXL</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>02-06-2026 6:22:38</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>01-08-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>499</v>
+      </c>
+      <c r="M4" t="n">
+        <v>11</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>28-05-2027 6:22:38</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
+        <v>98380</v>
+      </c>
+      <c r="Q4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="n">
+        <v>105017</v>
+      </c>
+      <c r="C5" t="n">
+        <v>370242</v>
+      </c>
+      <c r="D5" t="n">
+        <v>12402</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>STEPHANIE  ALVAREZ TORRES</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>VILLAS DEL REY</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>01-07-2026 7:00:58</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>01-08-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>999</v>
+      </c>
+      <c r="M5" t="n">
+        <v>11</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>26-06-2027 7:00:58</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="n">
+        <v>102757</v>
+      </c>
+      <c r="C6" t="n">
+        <v>21014</v>
+      </c>
+      <c r="D6" t="n">
+        <v>19914</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>CARMEN ESTHER GARCIA VILLEGAS</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>VILLA VERDE</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>01-06-2026 17:29:42</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>01-08-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>449</v>
+      </c>
+      <c r="M6" t="n">
+        <v>5</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>28-11-2026 17:29:42</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>31697</v>
+      </c>
+      <c r="Q6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" t="n">
+        <v>105015</v>
+      </c>
+      <c r="C7" t="n">
+        <v>371316</v>
+      </c>
+      <c r="D7" t="n">
+        <v>13476</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>DIANA RAMIREZ TORES</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>PAPALOTE TJ</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>01-07-2026 6:38:27</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>01-08-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>649</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" t="n">
+        <v>105022</v>
+      </c>
+      <c r="C8" t="n">
+        <v>370013</v>
+      </c>
+      <c r="D8" t="n">
+        <v>12173</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>AILED MARCELA CANDELA CUEN</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>SAN LUIS</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>01-07-2026 10:15:31</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>01-08-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>649</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" t="n">
+        <v>105019</v>
+      </c>
+      <c r="C9" t="n">
+        <v>360779</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>02944</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>ARISBE  HERRERA  VALADES</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>SALTILLO VILLALTA</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>01-07-2026 7:10:32</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>01-08-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>649</v>
+      </c>
+      <c r="M9" t="n">
+        <v>11</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>26-06-2027 7:10:32</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" t="n">
+        <v>102987</v>
+      </c>
+      <c r="C10" t="n">
+        <v>68471</v>
+      </c>
+      <c r="D10" t="n">
+        <v>66299</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>JESUS MAURICIO VALTIERRA HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>MISION ENS</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>02-06-2026 21:42:32</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>01-08-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>499</v>
+      </c>
+      <c r="M10" t="n">
+        <v>11</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>28-05-2027 21:42:32</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>70979</v>
+      </c>
+      <c r="Q10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" t="n">
+        <v>104971</v>
+      </c>
+      <c r="C11" t="n">
+        <v>339162</v>
+      </c>
+      <c r="D11" t="n">
+        <v>16980</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>SHOPIA XIMENA  FLORES  DOMINGUEZ</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>INSURGENTES</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>30-06-2026 16:16:13</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>01-08-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>649</v>
+      </c>
+      <c r="M11" t="n">
+        <v>11</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>25-06-2027 16:16:13</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>90809</v>
+      </c>
+      <c r="Q11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" t="n">
+        <v>105016</v>
+      </c>
+      <c r="C12" t="n">
+        <v>369160</v>
+      </c>
+      <c r="D12" t="n">
+        <v>11320</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>ANDREA MONSERRAT ESPINOZA ANGUIS</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>SEND CUL</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>01-07-2026 6:58:08</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>01-08-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>649</v>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" t="n">
+        <v>103090</v>
+      </c>
+      <c r="C13" t="n">
+        <v>289981</v>
+      </c>
+      <c r="D13" t="n">
+        <v>87479</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>RICARDO HERNANDEZ CASTILLO</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>SEND SALTILLO</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>04-06-2026 10:32:04</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>01-08-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>499</v>
+      </c>
+      <c r="M13" t="n">
+        <v>11</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>30-05-2027 10:32:04</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>73652</v>
+      </c>
+      <c r="Q13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" t="n">
+        <v>102719</v>
+      </c>
+      <c r="C14" t="n">
+        <v>273408</v>
+      </c>
+      <c r="D14" t="n">
+        <v>70910</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>BLANCA ESTELA SOTELO DE LA CRUZ</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>IXTAPALUCA</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>01-06-2026 13:40:42</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>01-08-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
+        <v>599</v>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>78501</v>
+      </c>
+      <c r="Q14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" t="n">
+        <v>103652</v>
+      </c>
+      <c r="C15" t="n">
+        <v>29941</v>
+      </c>
+      <c r="D15" t="n">
+        <v>27871</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>CARLOS MARTIN ESPINOZA  BARRAZA</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>PASEO 2000</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>12-06-2026 17:10:07</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>01-08-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L15" t="n">
+        <v>399</v>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>10984</v>
+      </c>
+      <c r="Q15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" t="n">
+        <v>102001</v>
+      </c>
+      <c r="C16" t="n">
+        <v>345112</v>
+      </c>
+      <c r="D16" t="n">
+        <v>87277</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>ITZEL VIRIDIANA ALVAREZ FERRER</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>PASEO 2000</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>21-05-2026 18:42:20</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>19-07-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L16" t="n">
+        <v>499</v>
+      </c>
+      <c r="M16" t="n">
+        <v>11</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>16-05-2027 18:42:20</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>94178</v>
+      </c>
+      <c r="Q16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" t="n">
+        <v>104187</v>
+      </c>
+      <c r="C17" t="n">
+        <v>94293</v>
+      </c>
+      <c r="D17" t="n">
+        <v>92052</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>PERLA ALEJANDRA SILVA BAÑUELOS</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>SEND SALTILLO</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>19-06-2026 16:06:08</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>01-08-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L17" t="n">
+        <v>399</v>
+      </c>
+      <c r="M17" t="n">
+        <v>11</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>14-06-2027 16:06:08</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>4787</v>
+      </c>
+      <c r="Q17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Reporte generado: 01-07-2026 05:17 p. m.</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/descargas/cargos_recurrentes.xlsx
+++ b/data/descargas/cargos_recurrentes.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q18"/>
+  <dimension ref="A1:Q113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -603,29 +603,27 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>105014</v>
+        <v>105044</v>
       </c>
       <c r="C3" t="n">
-        <v>307487</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>04986</t>
-        </is>
+        <v>179187</v>
+      </c>
+      <c r="D3" t="n">
+        <v>76694</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>ASHLEY ANGULO LAFARGA</t>
+          <t>IVAN RAFAEL CASAS QUIÑONES</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>VILLA VERDE</t>
+          <t>SEND MXL</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>01-07-2026 5:55:03</t>
+          <t>01-07-2026 16:46:41</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -647,19 +645,17 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>549</v>
-      </c>
-      <c r="M3" t="n">
-        <v>11</v>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>26-06-2027 5:55:03</t>
-        </is>
-      </c>
+        <v>599</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Domiciliado</t>
+          <t>Recurrente</t>
         </is>
       </c>
       <c r="P3" t="inlineStr"/>
@@ -670,32 +666,32 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>102843</v>
+        <v>105118</v>
       </c>
       <c r="C4" t="n">
-        <v>218531</v>
+        <v>371412</v>
       </c>
       <c r="D4" t="n">
-        <v>16039</v>
+        <v>13572</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>MARIA EUGENIA CUESTA GUERRERRO</t>
+          <t>ISRAEL TORRES AMEZCUA</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>SEND MXL</t>
+          <t>VILLA VERDE</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>02-06-2026 6:22:38</t>
+          <t>02-07-2026 8:15:24</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>01-08-2026 23:59:59</t>
+          <t>02-08-2026 23:59:59</t>
         </is>
       </c>
       <c r="I4" t="n">
@@ -708,28 +704,24 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>RENOVACIÓN</t>
+          <t>NUEVO</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>499</v>
-      </c>
-      <c r="M4" t="n">
-        <v>11</v>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>28-05-2027 6:22:38</t>
-        </is>
-      </c>
+        <v>599</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Domiciliado</t>
-        </is>
-      </c>
-      <c r="P4" t="n">
-        <v>98380</v>
-      </c>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr"/>
     </row>
     <row r="5">
@@ -737,32 +729,32 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>105017</v>
+        <v>102463</v>
       </c>
       <c r="C5" t="n">
-        <v>370242</v>
+        <v>339000</v>
       </c>
       <c r="D5" t="n">
-        <v>12402</v>
+        <v>16818</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>STEPHANIE  ALVAREZ TORRES</t>
+          <t>LUIS ENRIQUE LAZOS CARRILLO</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>VILLAS DEL REY</t>
+          <t>SEND MXL</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>01-07-2026 7:00:58</t>
+          <t>28-05-2026 8:14:12</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>01-08-2026 23:59:59</t>
+          <t>28-07-2026 23:59:59</t>
         </is>
       </c>
       <c r="I5" t="n">
@@ -775,18 +767,18 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>NUEVO</t>
+          <t>RENOVACIÓN</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>999</v>
+        <v>499</v>
       </c>
       <c r="M5" t="n">
         <v>11</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>26-06-2027 7:00:58</t>
+          <t>23-05-2027 8:14:12</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -794,7 +786,9 @@
           <t>Domiciliado</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr"/>
+      <c r="P5" t="n">
+        <v>91197</v>
+      </c>
       <c r="Q5" t="inlineStr"/>
     </row>
     <row r="6">
@@ -802,27 +796,27 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>102757</v>
+        <v>105055</v>
       </c>
       <c r="C6" t="n">
-        <v>21014</v>
+        <v>269679</v>
       </c>
       <c r="D6" t="n">
-        <v>19914</v>
+        <v>67182</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>CARMEN ESTHER GARCIA VILLEGAS</t>
+          <t>ANGELY JATZIRI INZUNZA HERNANDEZ</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>VILLA VERDE</t>
+          <t>SEND CUL</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>01-06-2026 17:29:42</t>
+          <t>01-07-2026 17:36:28</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -844,23 +838,21 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>449</v>
-      </c>
-      <c r="M6" t="n">
-        <v>5</v>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>28-11-2026 17:29:42</t>
-        </is>
-      </c>
+        <v>999</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Domiciliado</t>
+          <t>Recurrente</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>31697</v>
+        <v>50859</v>
       </c>
       <c r="Q6" t="inlineStr"/>
     </row>
@@ -869,27 +861,27 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>105015</v>
+        <v>105089</v>
       </c>
       <c r="C7" t="n">
-        <v>371316</v>
+        <v>370483</v>
       </c>
       <c r="D7" t="n">
-        <v>13476</v>
+        <v>12643</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>DIANA RAMIREZ TORES</t>
+          <t>JOSE FEDERICO VEGA NABOR</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>PAPALOTE TJ</t>
+          <t>SAN LUIS</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>01-07-2026 6:38:27</t>
+          <t>01-07-2026 19:35:04</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -911,7 +903,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>649</v>
+        <v>599</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -932,32 +924,32 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>105022</v>
+        <v>105106</v>
       </c>
       <c r="C8" t="n">
-        <v>370013</v>
+        <v>42253</v>
       </c>
       <c r="D8" t="n">
-        <v>12173</v>
+        <v>40123</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AILED MARCELA CANDELA CUEN</t>
+          <t>JOSE FRANCISCO GARCIA ZUÑIGA</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>SAN LUIS</t>
+          <t>TEC MXL</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>01-07-2026 10:15:31</t>
+          <t>01-07-2026 20:47:25</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>01-08-2026 23:59:59</t>
+          <t>30-07-2026 23:59:59</t>
         </is>
       </c>
       <c r="I8" t="n">
@@ -970,24 +962,28 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>NUEVO</t>
+          <t>RENOVACIÓN</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>649</v>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>Indefinido</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
+        <v>399</v>
+      </c>
+      <c r="M8" t="n">
+        <v>5</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>28-12-2026 20:47:25</t>
+        </is>
+      </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Recurrente</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr"/>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P8" t="n">
+        <v>39497</v>
+      </c>
       <c r="Q8" t="inlineStr"/>
     </row>
     <row r="9">
@@ -995,29 +991,27 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>105019</v>
+        <v>105015</v>
       </c>
       <c r="C9" t="n">
-        <v>360779</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>02944</t>
-        </is>
+        <v>371316</v>
+      </c>
+      <c r="D9" t="n">
+        <v>13476</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>ARISBE  HERRERA  VALADES</t>
+          <t>DIANA RAMIREZ TORES</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>SALTILLO VILLALTA</t>
+          <t>PAPALOTE TJ</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>01-07-2026 7:10:32</t>
+          <t>01-07-2026 6:38:27</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1041,17 +1035,15 @@
       <c r="L9" t="n">
         <v>649</v>
       </c>
-      <c r="M9" t="n">
-        <v>11</v>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>26-06-2027 7:10:32</t>
-        </is>
-      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Domiciliado</t>
+          <t>Recurrente</t>
         </is>
       </c>
       <c r="P9" t="inlineStr"/>
@@ -1062,27 +1054,27 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>102987</v>
+        <v>105022</v>
       </c>
       <c r="C10" t="n">
-        <v>68471</v>
+        <v>370013</v>
       </c>
       <c r="D10" t="n">
-        <v>66299</v>
+        <v>12173</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>JESUS MAURICIO VALTIERRA HERNANDEZ</t>
+          <t>AILED MARCELA CANDELA CUEN</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>MISION ENS</t>
+          <t>SAN LUIS</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>02-06-2026 21:42:32</t>
+          <t>01-07-2026 10:15:31</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1100,28 +1092,24 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>RENOVACIÓN</t>
+          <t>NUEVO</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>499</v>
-      </c>
-      <c r="M10" t="n">
-        <v>11</v>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>28-05-2027 21:42:32</t>
-        </is>
-      </c>
+        <v>649</v>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Domiciliado</t>
-        </is>
-      </c>
-      <c r="P10" t="n">
-        <v>70979</v>
-      </c>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr"/>
       <c r="Q10" t="inlineStr"/>
     </row>
     <row r="11">
@@ -1129,27 +1117,27 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>104971</v>
+        <v>105072</v>
       </c>
       <c r="C11" t="n">
-        <v>339162</v>
+        <v>174193</v>
       </c>
       <c r="D11" t="n">
-        <v>16980</v>
+        <v>71701</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>SHOPIA XIMENA  FLORES  DOMINGUEZ</t>
+          <t>MARIA DE LOS ANGELES DE LA TOBA GARCIA</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>INSURGENTES</t>
+          <t>PASEO LA PAZ</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>30-06-2026 16:16:13</t>
+          <t>01-07-2026 18:23:46</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1167,18 +1155,18 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>RENOVACIÓN</t>
+          <t>NUEVO</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>649</v>
+        <v>999</v>
       </c>
       <c r="M11" t="n">
         <v>11</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>25-06-2027 16:16:13</t>
+          <t>26-06-2027 18:23:46</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1186,9 +1174,7 @@
           <t>Domiciliado</t>
         </is>
       </c>
-      <c r="P11" t="n">
-        <v>90809</v>
-      </c>
+      <c r="P11" t="inlineStr"/>
       <c r="Q11" t="inlineStr"/>
     </row>
     <row r="12">
@@ -1196,27 +1182,27 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>105016</v>
+        <v>105080</v>
       </c>
       <c r="C12" t="n">
-        <v>369160</v>
+        <v>371456</v>
       </c>
       <c r="D12" t="n">
-        <v>11320</v>
+        <v>13616</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ANDREA MONSERRAT ESPINOZA ANGUIS</t>
+          <t>JOEL CONTRERAS SAUCEDO</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>SEND CUL</t>
+          <t>TLALNEPANTLA</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>01-07-2026 6:58:08</t>
+          <t>01-07-2026 18:50:02</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1238,7 +1224,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>649</v>
+        <v>599</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -1259,27 +1245,27 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>103090</v>
+        <v>105082</v>
       </c>
       <c r="C13" t="n">
-        <v>289981</v>
+        <v>371476</v>
       </c>
       <c r="D13" t="n">
-        <v>87479</v>
+        <v>13636</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RICARDO HERNANDEZ CASTILLO</t>
+          <t>OSCAR GONZALEZ BALTAZAR</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>SEND SALTILLO</t>
+          <t>SANTA FE</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>04-06-2026 10:32:04</t>
+          <t>01-07-2026 19:09:56</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1297,28 +1283,24 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>RENOVACIÓN</t>
+          <t>NUEVO</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>499</v>
-      </c>
-      <c r="M13" t="n">
-        <v>11</v>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>30-05-2027 10:32:04</t>
-        </is>
-      </c>
+        <v>599</v>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Domiciliado</t>
-        </is>
-      </c>
-      <c r="P13" t="n">
-        <v>73652</v>
-      </c>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr"/>
       <c r="Q13" t="inlineStr"/>
     </row>
     <row r="14">
@@ -1326,27 +1308,29 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>102719</v>
+        <v>105019</v>
       </c>
       <c r="C14" t="n">
-        <v>273408</v>
-      </c>
-      <c r="D14" t="n">
-        <v>70910</v>
+        <v>360779</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>02944</t>
+        </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>BLANCA ESTELA SOTELO DE LA CRUZ</t>
+          <t>ARISBE  HERRERA  VALADES</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>IXTAPALUCA</t>
+          <t>SALTILLO VILLALTA</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>01-06-2026 13:40:42</t>
+          <t>01-07-2026 7:10:32</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1364,26 +1348,26 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>RENOVACIÓN</t>
+          <t>NUEVO</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>599</v>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>Indefinido</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
+        <v>649</v>
+      </c>
+      <c r="M14" t="n">
+        <v>11</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>26-06-2027 7:10:32</t>
+        </is>
+      </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Recurrente</t>
-        </is>
-      </c>
-      <c r="P14" t="n">
-        <v>78501</v>
-      </c>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr"/>
       <c r="Q14" t="inlineStr"/>
     </row>
     <row r="15">
@@ -1391,27 +1375,27 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>103652</v>
+        <v>105053</v>
       </c>
       <c r="C15" t="n">
-        <v>29941</v>
+        <v>371267</v>
       </c>
       <c r="D15" t="n">
-        <v>27871</v>
+        <v>13427</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>CARLOS MARTIN ESPINOZA  BARRAZA</t>
+          <t>ERNESTO BARRAZA URIARTE</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>PASEO 2000</t>
+          <t>VILLA VERDE</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>12-06-2026 17:10:07</t>
+          <t>01-07-2026 17:30:48</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1429,11 +1413,11 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>RENOVACIÓN</t>
+          <t>NUEVO</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>399</v>
+        <v>599</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -1446,9 +1430,7 @@
           <t>Recurrente</t>
         </is>
       </c>
-      <c r="P15" t="n">
-        <v>10984</v>
-      </c>
+      <c r="P15" t="inlineStr"/>
       <c r="Q15" t="inlineStr"/>
     </row>
     <row r="16">
@@ -1456,32 +1438,32 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>102001</v>
+        <v>105121</v>
       </c>
       <c r="C16" t="n">
-        <v>345112</v>
+        <v>371534</v>
       </c>
       <c r="D16" t="n">
-        <v>87277</v>
+        <v>13694</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>ITZEL VIRIDIANA ALVAREZ FERRER</t>
+          <t>JONATHAN GARCIA ZAMORA</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>PASEO 2000</t>
+          <t>VILLAS DEL REY</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>21-05-2026 18:42:20</t>
+          <t>02-07-2026 9:03:30</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>19-07-2026 23:59:59</t>
+          <t>02-08-2026 23:59:59</t>
         </is>
       </c>
       <c r="I16" t="n">
@@ -1494,28 +1476,24 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>RENOVACIÓN</t>
+          <t>NUEVO</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>499</v>
-      </c>
-      <c r="M16" t="n">
-        <v>11</v>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>16-05-2027 18:42:20</t>
-        </is>
-      </c>
+        <v>599</v>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Domiciliado</t>
-        </is>
-      </c>
-      <c r="P16" t="n">
-        <v>94178</v>
-      </c>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr"/>
       <c r="Q16" t="inlineStr"/>
     </row>
     <row r="17">
@@ -1523,27 +1501,27 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>104187</v>
+        <v>102987</v>
       </c>
       <c r="C17" t="n">
-        <v>94293</v>
+        <v>68471</v>
       </c>
       <c r="D17" t="n">
-        <v>92052</v>
+        <v>66299</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>PERLA ALEJANDRA SILVA BAÑUELOS</t>
+          <t>JESUS MAURICIO VALTIERRA HERNANDEZ</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>SEND SALTILLO</t>
+          <t>MISION ENS</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>19-06-2026 16:06:08</t>
+          <t>02-06-2026 21:42:32</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1565,14 +1543,14 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>399</v>
+        <v>499</v>
       </c>
       <c r="M17" t="n">
         <v>11</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>14-06-2027 16:06:08</t>
+          <t>28-05-2027 21:42:32</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -1581,32 +1559,6159 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>4787</v>
+        <v>70979</v>
       </c>
       <c r="Q17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Reporte generado: 01-07-2026 05:17 p. m.</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
+      <c r="A18" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" t="n">
+        <v>105093</v>
+      </c>
+      <c r="C18" t="n">
+        <v>371487</v>
+      </c>
+      <c r="D18" t="n">
+        <v>13647</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>RICARDO  CASTILLO  VALDIVIA</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>SEND SALTILLO</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>01-07-2026 19:48:46</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>01-08-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L18" t="n">
+        <v>599</v>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr"/>
       <c r="Q18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" t="n">
+        <v>105120</v>
+      </c>
+      <c r="C19" t="n">
+        <v>236764</v>
+      </c>
+      <c r="D19" t="n">
+        <v>34269</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>DANIEL SALAZAR NIEBLAS</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>VILLAS DEL REY</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>02-07-2026 8:31:41</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>02-08-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L19" t="n">
+        <v>599</v>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" t="n">
+        <v>105032</v>
+      </c>
+      <c r="C20" t="n">
+        <v>371373</v>
+      </c>
+      <c r="D20" t="n">
+        <v>13533</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>BERTA ALICIA SANCHEZ DUARTE</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>VILLA VERDE</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>01-07-2026 13:25:46</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>01-08-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L20" t="n">
+        <v>599</v>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" t="n">
+        <v>105092</v>
+      </c>
+      <c r="C21" t="n">
+        <v>70084</v>
+      </c>
+      <c r="D21" t="n">
+        <v>67906</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>GLORIA IVETTE CONTRERAS SEDANO</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>SAN ISIDRO CUL</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>01-07-2026 19:45:31</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>24-07-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L21" t="n">
+        <v>499</v>
+      </c>
+      <c r="M21" t="n">
+        <v>11</v>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>26-06-2027 19:45:31</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P21" t="n">
+        <v>94674</v>
+      </c>
+      <c r="Q21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" t="n">
+        <v>105033</v>
+      </c>
+      <c r="C22" t="n">
+        <v>371385</v>
+      </c>
+      <c r="D22" t="n">
+        <v>13545</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>JOSE LUIS MIYAR VILLANUEVA</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>SERRANIA</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>01-07-2026 14:34:38</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>01-08-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L22" t="n">
+        <v>849</v>
+      </c>
+      <c r="M22" t="n">
+        <v>11</v>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>26-06-2027 14:34:38</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" t="n">
+        <v>105058</v>
+      </c>
+      <c r="C23" t="n">
+        <v>371440</v>
+      </c>
+      <c r="D23" t="n">
+        <v>13600</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>MIGUEL ANGEL MENDOZA  SIERRA</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>SALTILLO VILLALTA</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>01-07-2026 17:54:09</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>01-08-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L23" t="n">
+        <v>549</v>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>22</v>
+      </c>
+      <c r="B24" t="n">
+        <v>105014</v>
+      </c>
+      <c r="C24" t="n">
+        <v>307487</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>04986</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>ASHLEY ANGULO LAFARGA</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>VILLA VERDE</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>01-07-2026 5:55:03</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>01-08-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L24" t="n">
+        <v>549</v>
+      </c>
+      <c r="M24" t="n">
+        <v>11</v>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>26-06-2027 5:55:03</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>23</v>
+      </c>
+      <c r="B25" t="n">
+        <v>105039</v>
+      </c>
+      <c r="C25" t="n">
+        <v>371405</v>
+      </c>
+      <c r="D25" t="n">
+        <v>13565</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>LUSI ERNESTO BORQUEZ  GUTIERREZ</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>PASEO LA PAZ</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>01-07-2026 16:07:19</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>01-08-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L25" t="n">
+        <v>599</v>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>24</v>
+      </c>
+      <c r="B26" t="n">
+        <v>105075</v>
+      </c>
+      <c r="C26" t="n">
+        <v>371439</v>
+      </c>
+      <c r="D26" t="n">
+        <v>13599</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>GABRIEL YAHIR SALGADO CORRALES</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>SEND MXL</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>01-07-2026 18:36:13</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>01-08-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L26" t="n">
+        <v>599</v>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>25</v>
+      </c>
+      <c r="B27" t="n">
+        <v>105027</v>
+      </c>
+      <c r="C27" t="n">
+        <v>371352</v>
+      </c>
+      <c r="D27" t="n">
+        <v>13512</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>MARIA GUADALUPE  SANCHEZ CARIDAD</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>PABELLON RTO</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>01-07-2026 12:11:43</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>01-08-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L27" t="n">
+        <v>599</v>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>26</v>
+      </c>
+      <c r="B28" t="n">
+        <v>103090</v>
+      </c>
+      <c r="C28" t="n">
+        <v>289981</v>
+      </c>
+      <c r="D28" t="n">
+        <v>87479</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>RICARDO HERNANDEZ CASTILLO</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>SEND SALTILLO</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>04-06-2026 10:32:04</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>01-08-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L28" t="n">
+        <v>499</v>
+      </c>
+      <c r="M28" t="n">
+        <v>11</v>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>30-05-2027 10:32:04</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P28" t="n">
+        <v>73652</v>
+      </c>
+      <c r="Q28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>27</v>
+      </c>
+      <c r="B29" t="n">
+        <v>105062</v>
+      </c>
+      <c r="C29" t="n">
+        <v>371445</v>
+      </c>
+      <c r="D29" t="n">
+        <v>13605</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>XIMENA MICHELLE  DELGADO  CONTRERAS</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>MISION ENS</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>01-07-2026 18:05:37</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>01-08-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L29" t="n">
+        <v>599</v>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>28</v>
+      </c>
+      <c r="B30" t="n">
+        <v>104658</v>
+      </c>
+      <c r="C30" t="n">
+        <v>347670</v>
+      </c>
+      <c r="D30" t="n">
+        <v>89835</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>NALLELI PATRICIA LORANT TORRES</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>TLALNEPANTLA</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>26-06-2026 17:10:02</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>02-08-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L30" t="n">
+        <v>549</v>
+      </c>
+      <c r="M30" t="n">
+        <v>11</v>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>21-06-2027 17:10:02</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P30" t="n">
+        <v>95522</v>
+      </c>
+      <c r="Q30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>29</v>
+      </c>
+      <c r="B31" t="n">
+        <v>104971</v>
+      </c>
+      <c r="C31" t="n">
+        <v>339162</v>
+      </c>
+      <c r="D31" t="n">
+        <v>16980</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>SHOPIA XIMENA  FLORES  DOMINGUEZ</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>INSURGENTES</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>30-06-2026 16:16:13</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>01-08-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L31" t="n">
+        <v>649</v>
+      </c>
+      <c r="M31" t="n">
+        <v>11</v>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>25-06-2027 16:16:13</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P31" t="n">
+        <v>90809</v>
+      </c>
+      <c r="Q31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>30</v>
+      </c>
+      <c r="B32" t="n">
+        <v>105025</v>
+      </c>
+      <c r="C32" t="n">
+        <v>371345</v>
+      </c>
+      <c r="D32" t="n">
+        <v>13505</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>MARTHA ILIANA  LEON VAZQUEZ</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>VILLAS DEL REY</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>01-07-2026 11:50:21</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>02-08-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L32" t="n">
+        <v>599</v>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>31</v>
+      </c>
+      <c r="B33" t="n">
+        <v>105064</v>
+      </c>
+      <c r="C33" t="n">
+        <v>371450</v>
+      </c>
+      <c r="D33" t="n">
+        <v>13610</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>MAZARI ASAEL LOPEZ ROSAS</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>IXTAPALUCA</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>01-07-2026 18:09:04</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>01-08-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L33" t="n">
+        <v>599</v>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>32</v>
+      </c>
+      <c r="B34" t="n">
+        <v>105066</v>
+      </c>
+      <c r="C34" t="n">
+        <v>371455</v>
+      </c>
+      <c r="D34" t="n">
+        <v>13615</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>MIGUEL ANGEL  HERRERA GARCIA</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>SALTILLO VILLALTA</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>01-07-2026 18:15:24</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>01-08-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L34" t="n">
+        <v>549</v>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>33</v>
+      </c>
+      <c r="B35" t="n">
+        <v>105063</v>
+      </c>
+      <c r="C35" t="n">
+        <v>371448</v>
+      </c>
+      <c r="D35" t="n">
+        <v>13608</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>ASHLEY MICHELLE ENCINAS MUJICA</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>MISION ENS</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>01-07-2026 18:07:13</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>01-08-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I35" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L35" t="n">
+        <v>599</v>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>34</v>
+      </c>
+      <c r="B36" t="n">
+        <v>104456</v>
+      </c>
+      <c r="C36" t="n">
+        <v>163216</v>
+      </c>
+      <c r="D36" t="n">
+        <v>60749</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>LIZETH LUCIA LARRETA RICO</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>VILLAS DEL REY</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>23-06-2026 14:48:17</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>02-08-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L36" t="n">
+        <v>449</v>
+      </c>
+      <c r="M36" t="n">
+        <v>11</v>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>18-06-2027 14:48:17</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P36" t="n">
+        <v>43648</v>
+      </c>
+      <c r="Q36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>35</v>
+      </c>
+      <c r="B37" t="n">
+        <v>102702</v>
+      </c>
+      <c r="C37" t="n">
+        <v>346842</v>
+      </c>
+      <c r="D37" t="n">
+        <v>89007</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>MARIANA LOPEZ GONZALEZ</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>TLALNEPANTLA</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>01-06-2026 11:01:35</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>02-08-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L37" t="n">
+        <v>549</v>
+      </c>
+      <c r="M37" t="n">
+        <v>11</v>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>27-05-2027 11:01:35</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P37" t="n">
+        <v>95452</v>
+      </c>
+      <c r="Q37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>36</v>
+      </c>
+      <c r="B38" t="n">
+        <v>105040</v>
+      </c>
+      <c r="C38" t="n">
+        <v>84969</v>
+      </c>
+      <c r="D38" t="n">
+        <v>82752</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>LUIS FERNANDO PAYAN  LOPEZ</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>SEND CUL</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>01-07-2026 16:08:35</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>01-08-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I38" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L38" t="n">
+        <v>599</v>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr"/>
+      <c r="Q38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>37</v>
+      </c>
+      <c r="B39" t="n">
+        <v>105090</v>
+      </c>
+      <c r="C39" t="n">
+        <v>371485</v>
+      </c>
+      <c r="D39" t="n">
+        <v>13645</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>GUSTAVO IGLESIAS BLANCAS</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>SANTA FE</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>01-07-2026 19:39:35</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>01-08-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I39" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L39" t="n">
+        <v>599</v>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>38</v>
+      </c>
+      <c r="B40" t="n">
+        <v>105016</v>
+      </c>
+      <c r="C40" t="n">
+        <v>369160</v>
+      </c>
+      <c r="D40" t="n">
+        <v>11320</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>ANDREA MONSERRAT ESPINOZA ANGUIS</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>SEND CUL</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>01-07-2026 6:58:08</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>01-08-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I40" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L40" t="n">
+        <v>649</v>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr"/>
+      <c r="Q40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>39</v>
+      </c>
+      <c r="B41" t="n">
+        <v>102542</v>
+      </c>
+      <c r="C41" t="n">
+        <v>319371</v>
+      </c>
+      <c r="D41" t="n">
+        <v>16868</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>REGINA ZAVALA  MEJIA</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>INSURGENTES</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>29-05-2026 11:54:18</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>20-07-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I41" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L41" t="n">
+        <v>599</v>
+      </c>
+      <c r="M41" t="n">
+        <v>11</v>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>24-05-2027 11:54:18</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P41" t="n">
+        <v>80316</v>
+      </c>
+      <c r="Q41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>40</v>
+      </c>
+      <c r="B42" t="n">
+        <v>105070</v>
+      </c>
+      <c r="C42" t="n">
+        <v>189843</v>
+      </c>
+      <c r="D42" t="n">
+        <v>87350</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>EDRUAN OBIER  RAMIREZ  GONZALEZ</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>SEND CUL</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>01-07-2026 18:21:35</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>01-08-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I42" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L42" t="n">
+        <v>549</v>
+      </c>
+      <c r="M42" t="n">
+        <v>11</v>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>26-06-2027 18:21:35</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr"/>
+      <c r="Q42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>41</v>
+      </c>
+      <c r="B43" t="n">
+        <v>105104</v>
+      </c>
+      <c r="C43" t="n">
+        <v>278026</v>
+      </c>
+      <c r="D43" t="n">
+        <v>75527</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>TEREZA MARGARITA ORTEGA  HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>IXTAPALUCA</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>01-07-2026 20:33:09</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>01-08-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L43" t="n">
+        <v>999</v>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr"/>
+      <c r="Q43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>42</v>
+      </c>
+      <c r="B44" t="n">
+        <v>102719</v>
+      </c>
+      <c r="C44" t="n">
+        <v>273408</v>
+      </c>
+      <c r="D44" t="n">
+        <v>70910</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>BLANCA ESTELA SOTELO DE LA CRUZ</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>IXTAPALUCA</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>01-06-2026 13:40:42</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>01-08-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I44" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L44" t="n">
+        <v>599</v>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P44" t="n">
+        <v>78501</v>
+      </c>
+      <c r="Q44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>43</v>
+      </c>
+      <c r="B45" t="n">
+        <v>104811</v>
+      </c>
+      <c r="C45" t="n">
+        <v>182978</v>
+      </c>
+      <c r="D45" t="n">
+        <v>80485</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>YADIRA RAMOS ARCINIEGA</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>CARROUSEL TJ</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>29-06-2026 16:29:22</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>02-08-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I45" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L45" t="n">
+        <v>499</v>
+      </c>
+      <c r="M45" t="n">
+        <v>11</v>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>24-06-2027 16:29:22</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P45" t="n">
+        <v>91385</v>
+      </c>
+      <c r="Q45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>44</v>
+      </c>
+      <c r="B46" t="n">
+        <v>105076</v>
+      </c>
+      <c r="C46" t="n">
+        <v>345883</v>
+      </c>
+      <c r="D46" t="n">
+        <v>88048</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>DULCE VALERIA GUTIÉRREZ RUIZ</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>INSURGENTES</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>01-07-2026 18:36:15</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>01-08-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I46" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L46" t="n">
+        <v>699</v>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr"/>
+      <c r="Q46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>45</v>
+      </c>
+      <c r="B47" t="n">
+        <v>105079</v>
+      </c>
+      <c r="C47" t="n">
+        <v>371465</v>
+      </c>
+      <c r="D47" t="n">
+        <v>13625</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>LITZY ROSALIA MEZA VALLEJO</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>SEND MXL</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>01-07-2026 18:49:35</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>01-08-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I47" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L47" t="n">
+        <v>599</v>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr"/>
+      <c r="Q47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>46</v>
+      </c>
+      <c r="B48" t="n">
+        <v>105111</v>
+      </c>
+      <c r="C48" t="n">
+        <v>371508</v>
+      </c>
+      <c r="D48" t="n">
+        <v>13668</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>JUAN FERNANDO SANCHEZ GARCIA</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>SEND SALTILLO</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>02-07-2026 6:15:28</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>02-08-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L48" t="n">
+        <v>599</v>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr"/>
+      <c r="Q48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>47</v>
+      </c>
+      <c r="B49" t="n">
+        <v>105100</v>
+      </c>
+      <c r="C49" t="n">
+        <v>278026</v>
+      </c>
+      <c r="D49" t="n">
+        <v>75527</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>TEREZA MARGARITA ORTEGA  HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>IXTAPALUCA</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>01-07-2026 20:18:59</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>01-08-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I49" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>CANCELADO</t>
+        </is>
+      </c>
+      <c r="L49" t="n">
+        <v>999</v>
+      </c>
+      <c r="M49" t="n">
+        <v>11</v>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>26-06-2027 20:18:59</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr"/>
+      <c r="Q49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>48</v>
+      </c>
+      <c r="B50" t="n">
+        <v>105038</v>
+      </c>
+      <c r="C50" t="n">
+        <v>371402</v>
+      </c>
+      <c r="D50" t="n">
+        <v>13562</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>JACQUELINE  MAYER CARRILLO</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>PASEO LA PAZ</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>01-07-2026 16:03:37</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>01-08-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L50" t="n">
+        <v>599</v>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr"/>
+      <c r="Q50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>49</v>
+      </c>
+      <c r="B51" t="n">
+        <v>105088</v>
+      </c>
+      <c r="C51" t="n">
+        <v>331975</v>
+      </c>
+      <c r="D51" t="n">
+        <v>16779</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>NAYELI ROMERO GOMEZ</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>TLALNEPANTLA</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>01-07-2026 19:34:41</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>01-08-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I51" t="n">
+        <v>0</v>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L51" t="n">
+        <v>599</v>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr"/>
+      <c r="Q51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>50</v>
+      </c>
+      <c r="B52" t="n">
+        <v>104588</v>
+      </c>
+      <c r="C52" t="n">
+        <v>347743</v>
+      </c>
+      <c r="D52" t="n">
+        <v>89908</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>FERNANDO  GARCIA LOPEZ</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>SALTILLO VILLALTA</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>25-06-2026 15:05:50</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>02-08-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I52" t="n">
+        <v>0</v>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L52" t="n">
+        <v>549</v>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P52" t="n">
+        <v>95570</v>
+      </c>
+      <c r="Q52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>51</v>
+      </c>
+      <c r="B53" t="n">
+        <v>104958</v>
+      </c>
+      <c r="C53" t="n">
+        <v>333288</v>
+      </c>
+      <c r="D53" t="n">
+        <v>17155</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>ALEJANDRO  MOLINA  SENA</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>SALTILLO VILLALTA</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>30-06-2026 14:32:41</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>09-08-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I53" t="n">
+        <v>0</v>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L53" t="n">
+        <v>649</v>
+      </c>
+      <c r="M53" t="n">
+        <v>11</v>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>25-06-2027 14:32:41</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P53" t="n">
+        <v>88865</v>
+      </c>
+      <c r="Q53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>52</v>
+      </c>
+      <c r="B54" t="n">
+        <v>105083</v>
+      </c>
+      <c r="C54" t="n">
+        <v>118175</v>
+      </c>
+      <c r="D54" t="n">
+        <v>15887</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>ROCIO GABRIELA LOPEZ TAMAYO</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>SAN ISIDRO CUL</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>01-07-2026 19:13:25</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>01-08-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I54" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L54" t="n">
+        <v>599</v>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr"/>
+      <c r="Q54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>53</v>
+      </c>
+      <c r="B55" t="n">
+        <v>102757</v>
+      </c>
+      <c r="C55" t="n">
+        <v>21014</v>
+      </c>
+      <c r="D55" t="n">
+        <v>19914</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>CARMEN ESTHER GARCIA VILLEGAS</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>VILLA VERDE</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>01-06-2026 17:29:42</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>01-08-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I55" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L55" t="n">
+        <v>449</v>
+      </c>
+      <c r="M55" t="n">
+        <v>5</v>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>28-11-2026 17:29:42</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P55" t="n">
+        <v>31697</v>
+      </c>
+      <c r="Q55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>54</v>
+      </c>
+      <c r="B56" t="n">
+        <v>105107</v>
+      </c>
+      <c r="C56" t="n">
+        <v>368391</v>
+      </c>
+      <c r="D56" t="n">
+        <v>10551</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>OSCAR HUGO  MAYA  MARTINEZ</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>TLALNEPANTLA</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>01-07-2026 20:47:33</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>01-08-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I56" t="n">
+        <v>0</v>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L56" t="n">
+        <v>549</v>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr"/>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr"/>
+      <c r="Q56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>55</v>
+      </c>
+      <c r="B57" t="n">
+        <v>105114</v>
+      </c>
+      <c r="C57" t="n">
+        <v>371397</v>
+      </c>
+      <c r="D57" t="n">
+        <v>13557</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>NANCY GONZALEZ ALCANTARA</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>IXTAPALUCA</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>02-07-2026 7:07:53</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>02-08-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I57" t="n">
+        <v>0</v>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L57" t="n">
+        <v>599</v>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr"/>
+      <c r="Q57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>56</v>
+      </c>
+      <c r="B58" t="n">
+        <v>105116</v>
+      </c>
+      <c r="C58" t="n">
+        <v>371521</v>
+      </c>
+      <c r="D58" t="n">
+        <v>13681</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>MARIO ANDRE FIGUEROA RUIZ</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>SEND CHIH</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>02-07-2026 7:36:45</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>02-08-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I58" t="n">
+        <v>0</v>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L58" t="n">
+        <v>999</v>
+      </c>
+      <c r="M58" t="n">
+        <v>11</v>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>27-06-2027 7:36:45</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr"/>
+      <c r="Q58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>57</v>
+      </c>
+      <c r="B59" t="n">
+        <v>105085</v>
+      </c>
+      <c r="C59" t="n">
+        <v>126817</v>
+      </c>
+      <c r="D59" t="n">
+        <v>24490</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>AMERICA  ROMAN  SOTO</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>SANTA FE</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>01-07-2026 19:18:20</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>01-08-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I59" t="n">
+        <v>0</v>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L59" t="n">
+        <v>599</v>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr"/>
+      <c r="Q59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>58</v>
+      </c>
+      <c r="B60" t="n">
+        <v>105077</v>
+      </c>
+      <c r="C60" t="n">
+        <v>371463</v>
+      </c>
+      <c r="D60" t="n">
+        <v>13623</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>SILVESTRE LEONARDO TORRES ROSALES</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>SALTILLO VILLALTA</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>01-07-2026 18:38:43</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>01-08-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I60" t="n">
+        <v>0</v>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L60" t="n">
+        <v>799</v>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr"/>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr"/>
+      <c r="Q60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>59</v>
+      </c>
+      <c r="B61" t="n">
+        <v>105113</v>
+      </c>
+      <c r="C61" t="n">
+        <v>362957</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>05117</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>DANIEL JEREMIAS FLORES MORALES</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>CARROUSEL TJ</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>02-07-2026 6:43:48</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>02-08-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I61" t="n">
+        <v>0</v>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L61" t="n">
+        <v>599</v>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr"/>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr"/>
+      <c r="Q61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>60</v>
+      </c>
+      <c r="B62" t="n">
+        <v>105026</v>
+      </c>
+      <c r="C62" t="n">
+        <v>110686</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>08424</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>JULIO ALBERTO  LOERA  QUIROZ</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>STA CATARINA</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>01-07-2026 12:06:22</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>01-08-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I62" t="n">
+        <v>0</v>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L62" t="n">
+        <v>599</v>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr"/>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr"/>
+      <c r="Q62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>61</v>
+      </c>
+      <c r="B63" t="n">
+        <v>105037</v>
+      </c>
+      <c r="C63" t="n">
+        <v>26588</v>
+      </c>
+      <c r="D63" t="n">
+        <v>24527</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>ROMAN PEREZ LOMAS</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>TEC MXL</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>01-07-2026 15:36:45</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>02-08-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I63" t="n">
+        <v>0</v>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L63" t="n">
+        <v>399</v>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr"/>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P63" t="n">
+        <v>71133</v>
+      </c>
+      <c r="Q63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>62</v>
+      </c>
+      <c r="B64" t="n">
+        <v>105052</v>
+      </c>
+      <c r="C64" t="n">
+        <v>266869</v>
+      </c>
+      <c r="D64" t="n">
+        <v>64373</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>MAR LIBERTAD VILLALOBOS ARMENDARIZ</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>SEND CHIH</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>01-07-2026 17:26:21</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>01-08-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I64" t="n">
+        <v>0</v>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L64" t="n">
+        <v>549</v>
+      </c>
+      <c r="M64" t="n">
+        <v>11</v>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>26-06-2027 17:26:21</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr"/>
+      <c r="Q64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>63</v>
+      </c>
+      <c r="B65" t="n">
+        <v>105084</v>
+      </c>
+      <c r="C65" t="n">
+        <v>371478</v>
+      </c>
+      <c r="D65" t="n">
+        <v>13638</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>ALEJANDRO  LUGO  CARRILLO</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>AZAHARES CUL</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>01-07-2026 19:14:35</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>01-08-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I65" t="n">
+        <v>0</v>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L65" t="n">
+        <v>599</v>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr"/>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr"/>
+      <c r="Q65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>64</v>
+      </c>
+      <c r="B66" t="n">
+        <v>105103</v>
+      </c>
+      <c r="C66" t="n">
+        <v>371101</v>
+      </c>
+      <c r="D66" t="n">
+        <v>13261</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>ROSA MARGARITA  HERNANDEZ  FIERRO</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>SEND CHIH</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>01-07-2026 20:25:14</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>01-08-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I66" t="n">
+        <v>0</v>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L66" t="n">
+        <v>999</v>
+      </c>
+      <c r="M66" t="n">
+        <v>11</v>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>26-06-2027 20:25:14</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr"/>
+      <c r="Q66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>65</v>
+      </c>
+      <c r="B67" t="n">
+        <v>105023</v>
+      </c>
+      <c r="C67" t="n">
+        <v>320546</v>
+      </c>
+      <c r="D67" t="n">
+        <v>17485</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>MARIA DE LOS ANGELES  BOLTOR  X</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>VILLAS DEL REY</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>01-07-2026 10:52:46</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>01-08-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I67" t="n">
+        <v>0</v>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L67" t="n">
+        <v>999</v>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr"/>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P67" t="n">
+        <v>80726</v>
+      </c>
+      <c r="Q67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>66</v>
+      </c>
+      <c r="B68" t="n">
+        <v>105091</v>
+      </c>
+      <c r="C68" t="n">
+        <v>310780</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>08279</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>AMALIA  QUIÑONEZ VALENZUELA</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>SEND CUL</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>01-07-2026 19:43:53</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>01-08-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I68" t="n">
+        <v>0</v>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L68" t="n">
+        <v>599</v>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr"/>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr"/>
+      <c r="Q68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>67</v>
+      </c>
+      <c r="B69" t="n">
+        <v>103652</v>
+      </c>
+      <c r="C69" t="n">
+        <v>29941</v>
+      </c>
+      <c r="D69" t="n">
+        <v>27871</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>CARLOS MARTIN ESPINOZA  BARRAZA</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>PASEO 2000</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>12-06-2026 17:10:07</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>01-08-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I69" t="n">
+        <v>0</v>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L69" t="n">
+        <v>399</v>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr"/>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P69" t="n">
+        <v>10984</v>
+      </c>
+      <c r="Q69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>68</v>
+      </c>
+      <c r="B70" t="n">
+        <v>105117</v>
+      </c>
+      <c r="C70" t="n">
+        <v>371523</v>
+      </c>
+      <c r="D70" t="n">
+        <v>13683</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>ANGEL ULISES TORRES OCHOA</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>SEND SALTILLO</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>02-07-2026 7:49:52</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>02-08-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I70" t="n">
+        <v>0</v>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L70" t="n">
+        <v>599</v>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr"/>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr"/>
+      <c r="Q70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>69</v>
+      </c>
+      <c r="B71" t="n">
+        <v>104163</v>
+      </c>
+      <c r="C71" t="n">
+        <v>340198</v>
+      </c>
+      <c r="D71" t="n">
+        <v>18016</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>ANETTE  IBARRA RODRIGUEZ</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>SEND SALTILLO</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>19-06-2026 7:07:23</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>02-08-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I71" t="n">
+        <v>0</v>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L71" t="n">
+        <v>499</v>
+      </c>
+      <c r="M71" t="n">
+        <v>11</v>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>14-06-2027 7:07:23</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P71" t="n">
+        <v>91431</v>
+      </c>
+      <c r="Q71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>70</v>
+      </c>
+      <c r="B72" t="n">
+        <v>102543</v>
+      </c>
+      <c r="C72" t="n">
+        <v>319373</v>
+      </c>
+      <c r="D72" t="n">
+        <v>16870</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>MARISOL  MEJIA GONZALEZ</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>INSURGENTES</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>29-05-2026 11:57:01</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>20-07-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I72" t="n">
+        <v>0</v>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L72" t="n">
+        <v>599</v>
+      </c>
+      <c r="M72" t="n">
+        <v>11</v>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>24-05-2027 11:57:01</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P72" t="n">
+        <v>80315</v>
+      </c>
+      <c r="Q72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>71</v>
+      </c>
+      <c r="B73" t="n">
+        <v>105050</v>
+      </c>
+      <c r="C73" t="n">
+        <v>152783</v>
+      </c>
+      <c r="D73" t="n">
+        <v>50342</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>SARA NICOLE MANRIQUEZ  JIMENEZ</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>PASEO LA PAZ</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>01-07-2026 17:10:49</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>01-08-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I73" t="n">
+        <v>0</v>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L73" t="n">
+        <v>599</v>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr"/>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr"/>
+      <c r="Q73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>72</v>
+      </c>
+      <c r="B74" t="n">
+        <v>105105</v>
+      </c>
+      <c r="C74" t="n">
+        <v>55485</v>
+      </c>
+      <c r="D74" t="n">
+        <v>53337</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>JESUS MANUEL  RIOS  HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>SANTA FE</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>01-07-2026 20:46:40</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>01-08-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I74" t="n">
+        <v>0</v>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L74" t="n">
+        <v>599</v>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr"/>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr"/>
+      <c r="Q74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>73</v>
+      </c>
+      <c r="B75" t="n">
+        <v>105045</v>
+      </c>
+      <c r="C75" t="n">
+        <v>179184</v>
+      </c>
+      <c r="D75" t="n">
+        <v>76691</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>JIMENA CASAS QUIÑONES</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>SEND MXL</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>01-07-2026 16:53:43</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>01-08-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>0</v>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L75" t="n">
+        <v>599</v>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr"/>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr"/>
+      <c r="Q75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>74</v>
+      </c>
+      <c r="B76" t="n">
+        <v>102001</v>
+      </c>
+      <c r="C76" t="n">
+        <v>345112</v>
+      </c>
+      <c r="D76" t="n">
+        <v>87277</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>ITZEL VIRIDIANA ALVAREZ FERRER</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>PASEO 2000</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>21-05-2026 18:42:20</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>19-07-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I76" t="n">
+        <v>0</v>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L76" t="n">
+        <v>499</v>
+      </c>
+      <c r="M76" t="n">
+        <v>11</v>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>16-05-2027 18:42:20</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P76" t="n">
+        <v>94178</v>
+      </c>
+      <c r="Q76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>75</v>
+      </c>
+      <c r="B77" t="n">
+        <v>105094</v>
+      </c>
+      <c r="C77" t="n">
+        <v>215951</v>
+      </c>
+      <c r="D77" t="n">
+        <v>13459</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>FABIOLA PATRICIA  VILLEGAS  SALAZAR</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>MISION ENS</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>01-07-2026 19:51:37</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>01-08-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I77" t="n">
+        <v>0</v>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L77" t="n">
+        <v>599</v>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr"/>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr"/>
+      <c r="Q77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>76</v>
+      </c>
+      <c r="B78" t="n">
+        <v>104187</v>
+      </c>
+      <c r="C78" t="n">
+        <v>94293</v>
+      </c>
+      <c r="D78" t="n">
+        <v>92052</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>PERLA ALEJANDRA SILVA BAÑUELOS</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>SEND SALTILLO</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>19-06-2026 16:06:08</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>01-08-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I78" t="n">
+        <v>0</v>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L78" t="n">
+        <v>399</v>
+      </c>
+      <c r="M78" t="n">
+        <v>11</v>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>14-06-2027 16:06:08</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P78" t="n">
+        <v>4787</v>
+      </c>
+      <c r="Q78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>77</v>
+      </c>
+      <c r="B79" t="n">
+        <v>105122</v>
+      </c>
+      <c r="C79" t="n">
+        <v>358608</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>00773</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>FERNANDO ALLAN BOLAÑOS ESTRADA</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>CARROUSEL TJ</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>02-07-2026 9:34:02</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>02-08-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I79" t="n">
+        <v>0</v>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L79" t="n">
+        <v>599</v>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr"/>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr"/>
+      <c r="Q79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>78</v>
+      </c>
+      <c r="B80" t="n">
+        <v>101482</v>
+      </c>
+      <c r="C80" t="n">
+        <v>319037</v>
+      </c>
+      <c r="D80" t="n">
+        <v>16534</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>JORGE EDUARDO LOPEZ AGUADO AMADOR</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>INSURGENTES</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>15-05-2026 9:46:06</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>20-07-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I80" t="n">
+        <v>0</v>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L80" t="n">
+        <v>599</v>
+      </c>
+      <c r="M80" t="n">
+        <v>11</v>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>10-05-2027 9:46:06</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P80" t="n">
+        <v>80192</v>
+      </c>
+      <c r="Q80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>79</v>
+      </c>
+      <c r="B81" t="n">
+        <v>105087</v>
+      </c>
+      <c r="C81" t="n">
+        <v>371482</v>
+      </c>
+      <c r="D81" t="n">
+        <v>13642</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>ANDRES ANTONIO SIFUENTES HERRERA</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>STA CATARINA</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>01-07-2026 19:24:53</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>01-08-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I81" t="n">
+        <v>0</v>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L81" t="n">
+        <v>599</v>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr"/>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr"/>
+      <c r="Q81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>80</v>
+      </c>
+      <c r="B82" t="n">
+        <v>105102</v>
+      </c>
+      <c r="C82" t="n">
+        <v>153290</v>
+      </c>
+      <c r="D82" t="n">
+        <v>50848</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>XIOMARA MICHELL URIAS  BENITEZ</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>SAN ISIDRO CUL</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>01-07-2026 20:24:25</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>03-08-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I82" t="n">
+        <v>0</v>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L82" t="n">
+        <v>499</v>
+      </c>
+      <c r="M82" t="n">
+        <v>11</v>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>26-06-2027 20:24:25</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P82" t="n">
+        <v>91721</v>
+      </c>
+      <c r="Q82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>81</v>
+      </c>
+      <c r="B83" t="n">
+        <v>105078</v>
+      </c>
+      <c r="C83" t="n">
+        <v>370765</v>
+      </c>
+      <c r="D83" t="n">
+        <v>12925</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>FEDERICO ISRAEL SALAZAR  JAIME</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>SALTILLO VILLALTA</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>01-07-2026 18:39:48</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>01-08-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I83" t="n">
+        <v>0</v>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L83" t="n">
+        <v>549</v>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr"/>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr"/>
+      <c r="Q83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>82</v>
+      </c>
+      <c r="B84" t="n">
+        <v>105110</v>
+      </c>
+      <c r="C84" t="n">
+        <v>302333</v>
+      </c>
+      <c r="D84" t="n">
+        <v>99831</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>ALEXA JUDITH MARTINEZ MARTINEZ</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>STA CATARINA</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>02-07-2026 6:09:05</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>02-08-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I84" t="n">
+        <v>0</v>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L84" t="n">
+        <v>999</v>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr"/>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P84" t="n">
+        <v>71656</v>
+      </c>
+      <c r="Q84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>83</v>
+      </c>
+      <c r="B85" t="n">
+        <v>105035</v>
+      </c>
+      <c r="C85" t="n">
+        <v>371390</v>
+      </c>
+      <c r="D85" t="n">
+        <v>13550</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>RODRIGO  DEL BOSQUE  BOONE</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>SALTILLO VILLALTA</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>01-07-2026 15:05:43</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>01-08-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I85" t="n">
+        <v>0</v>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L85" t="n">
+        <v>549</v>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr"/>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P85" t="inlineStr"/>
+      <c r="Q85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>84</v>
+      </c>
+      <c r="B86" t="n">
+        <v>105049</v>
+      </c>
+      <c r="C86" t="n">
+        <v>371422</v>
+      </c>
+      <c r="D86" t="n">
+        <v>13582</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>ANTONIO DE JESUS  MENDOZA  CUEVAS</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>SEND SALTILLO</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>01-07-2026 17:10:16</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>01-08-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I86" t="n">
+        <v>0</v>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L86" t="n">
+        <v>599</v>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr"/>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P86" t="inlineStr"/>
+      <c r="Q86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>85</v>
+      </c>
+      <c r="B87" t="n">
+        <v>105081</v>
+      </c>
+      <c r="C87" t="n">
+        <v>371475</v>
+      </c>
+      <c r="D87" t="n">
+        <v>13635</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>ARTURO JUNIOR HERNANDEZ MEZA</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>SEND MXL</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>01-07-2026 19:06:52</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>01-08-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I87" t="n">
+        <v>0</v>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L87" t="n">
+        <v>599</v>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr"/>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P87" t="inlineStr"/>
+      <c r="Q87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>86</v>
+      </c>
+      <c r="B88" t="n">
+        <v>105115</v>
+      </c>
+      <c r="C88" t="n">
+        <v>318179</v>
+      </c>
+      <c r="D88" t="n">
+        <v>15676</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>ERWIN ROMMEL SANCHEZ HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>PABELLON RTO</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>02-07-2026 7:09:16</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>02-08-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I88" t="n">
+        <v>0</v>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L88" t="n">
+        <v>599</v>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr"/>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P88" t="inlineStr"/>
+      <c r="Q88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>87</v>
+      </c>
+      <c r="B89" t="n">
+        <v>102843</v>
+      </c>
+      <c r="C89" t="n">
+        <v>218531</v>
+      </c>
+      <c r="D89" t="n">
+        <v>16039</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>MARIA EUGENIA CUESTA GUERRERRO</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>SEND MXL</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>02-06-2026 6:22:38</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>01-08-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I89" t="n">
+        <v>0</v>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L89" t="n">
+        <v>499</v>
+      </c>
+      <c r="M89" t="n">
+        <v>11</v>
+      </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>28-05-2027 6:22:38</t>
+        </is>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P89" t="n">
+        <v>98380</v>
+      </c>
+      <c r="Q89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>88</v>
+      </c>
+      <c r="B90" t="n">
+        <v>103010</v>
+      </c>
+      <c r="C90" t="n">
+        <v>140843</v>
+      </c>
+      <c r="D90" t="n">
+        <v>38469</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>MARIA DE JESUS RODRIGUEZ MICHEL</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>PABELLON RTO</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>03-06-2026 10:15:40</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>02-08-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I90" t="n">
+        <v>0</v>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L90" t="n">
+        <v>599</v>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr"/>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P90" t="n">
+        <v>51949</v>
+      </c>
+      <c r="Q90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>89</v>
+      </c>
+      <c r="B91" t="n">
+        <v>105073</v>
+      </c>
+      <c r="C91" t="n">
+        <v>355910</v>
+      </c>
+      <c r="D91" t="n">
+        <v>98074</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>MIGUEL ANGEL  HERRERA FARIAS</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>SALTILLO VILLALTA</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>01-07-2026 18:26:24</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>06-08-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I91" t="n">
+        <v>0</v>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L91" t="n">
+        <v>549</v>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr"/>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P91" t="n">
+        <v>105056</v>
+      </c>
+      <c r="Q91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>90</v>
+      </c>
+      <c r="B92" t="n">
+        <v>105017</v>
+      </c>
+      <c r="C92" t="n">
+        <v>370242</v>
+      </c>
+      <c r="D92" t="n">
+        <v>12402</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>STEPHANIE  ALVAREZ TORRES</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>VILLAS DEL REY</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>01-07-2026 7:00:58</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>01-08-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I92" t="n">
+        <v>0</v>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L92" t="n">
+        <v>999</v>
+      </c>
+      <c r="M92" t="n">
+        <v>11</v>
+      </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>26-06-2027 7:00:58</t>
+        </is>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P92" t="inlineStr"/>
+      <c r="Q92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>91</v>
+      </c>
+      <c r="B93" t="n">
+        <v>105036</v>
+      </c>
+      <c r="C93" t="n">
+        <v>365317</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>07477</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>ALEJANDRO  ROSALES SANTANA</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>PAPALOTE TJ</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>01-07-2026 15:25:25</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>01-08-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I93" t="n">
+        <v>0</v>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L93" t="n">
+        <v>599</v>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr"/>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P93" t="inlineStr"/>
+      <c r="Q93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>92</v>
+      </c>
+      <c r="B94" t="n">
+        <v>105051</v>
+      </c>
+      <c r="C94" t="n">
+        <v>371428</v>
+      </c>
+      <c r="D94" t="n">
+        <v>13588</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>JORDAN ALEJANDRA AVILA  RUIZ</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>AZAHARES CUL</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>01-07-2026 17:21:53</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>01-08-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I94" t="n">
+        <v>0</v>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L94" t="n">
+        <v>599</v>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr"/>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P94" t="inlineStr"/>
+      <c r="Q94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>93</v>
+      </c>
+      <c r="B95" t="n">
+        <v>105028</v>
+      </c>
+      <c r="C95" t="n">
+        <v>370848</v>
+      </c>
+      <c r="D95" t="n">
+        <v>13008</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>GILBERTO ISRAEL LAZCANO GUTIERREZ</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>VILLAS DEL REY</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>01-07-2026 12:49:38</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>01-08-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I95" t="n">
+        <v>0</v>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L95" t="n">
+        <v>599</v>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr"/>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P95" t="inlineStr"/>
+      <c r="Q95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>94</v>
+      </c>
+      <c r="B96" t="n">
+        <v>105059</v>
+      </c>
+      <c r="C96" t="n">
+        <v>371383</v>
+      </c>
+      <c r="D96" t="n">
+        <v>13543</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>ISAAC RENE BERNANDINO  HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>MISION ENS</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>01-07-2026 17:55:21</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>01-08-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I96" t="n">
+        <v>0</v>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L96" t="n">
+        <v>599</v>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr"/>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P96" t="inlineStr"/>
+      <c r="Q96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>95</v>
+      </c>
+      <c r="B97" t="n">
+        <v>105095</v>
+      </c>
+      <c r="C97" t="n">
+        <v>307917</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>05416</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>JAZMIN URESTI ESPINOZA</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>SEND SALTILLO</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>01-07-2026 19:56:19</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>01-08-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I97" t="n">
+        <v>0</v>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L97" t="n">
+        <v>599</v>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr"/>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P97" t="inlineStr"/>
+      <c r="Q97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>96</v>
+      </c>
+      <c r="B98" t="n">
+        <v>104994</v>
+      </c>
+      <c r="C98" t="n">
+        <v>311002</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>08501</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>KAREN MONTSERAT FARIAS RIVAS</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>SANTA FE</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>30-06-2026 18:49:41</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>02-08-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I98" t="n">
+        <v>0</v>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L98" t="n">
+        <v>499</v>
+      </c>
+      <c r="M98" t="n">
+        <v>11</v>
+      </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>25-06-2027 18:49:41</t>
+        </is>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P98" t="n">
+        <v>95585</v>
+      </c>
+      <c r="Q98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>97</v>
+      </c>
+      <c r="B99" t="n">
+        <v>105112</v>
+      </c>
+      <c r="C99" t="n">
+        <v>367119</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>09279</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>GILA MARISELA FUENTES ROCHA</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>PASEO LA PAZ</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>02-07-2026 6:35:56</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>07-08-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I99" t="n">
+        <v>0</v>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L99" t="n">
+        <v>649</v>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr"/>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P99" t="n">
+        <v>103188</v>
+      </c>
+      <c r="Q99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>98</v>
+      </c>
+      <c r="B100" t="n">
+        <v>105054</v>
+      </c>
+      <c r="C100" t="n">
+        <v>190066</v>
+      </c>
+      <c r="D100" t="n">
+        <v>87573</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>LEVI YESHUA ROCHA MARTINEZ</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>SAN LUIS</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>01-07-2026 17:31:14</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>01-08-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I100" t="n">
+        <v>0</v>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L100" t="n">
+        <v>999</v>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr"/>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P100" t="n">
+        <v>70529</v>
+      </c>
+      <c r="Q100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>99</v>
+      </c>
+      <c r="B101" t="n">
+        <v>105057</v>
+      </c>
+      <c r="C101" t="n">
+        <v>18207</v>
+      </c>
+      <c r="D101" t="n">
+        <v>17114</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>ELENA ISMERAI  NAVARRO AGUIRRE</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>MISION ENS</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>01-07-2026 17:48:01</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>01-08-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I101" t="n">
+        <v>0</v>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L101" t="n">
+        <v>599</v>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr"/>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P101" t="inlineStr"/>
+      <c r="Q101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>100</v>
+      </c>
+      <c r="B102" t="n">
+        <v>105098</v>
+      </c>
+      <c r="C102" t="n">
+        <v>371438</v>
+      </c>
+      <c r="D102" t="n">
+        <v>13598</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>JESUS ORLANDO ARMENTA MICKINNEY</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>PASEO 2000</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>01-07-2026 20:05:27</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>02-08-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I102" t="n">
+        <v>0</v>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L102" t="n">
+        <v>599</v>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N102" t="inlineStr"/>
+      <c r="O102" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P102" t="inlineStr"/>
+      <c r="Q102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>101</v>
+      </c>
+      <c r="B103" t="n">
+        <v>105123</v>
+      </c>
+      <c r="C103" t="n">
+        <v>371538</v>
+      </c>
+      <c r="D103" t="n">
+        <v>13698</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>KEVIN HERNANDEZ ALVAREZ</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>PAPALOTE TJ</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>02-07-2026 9:42:33</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>02-08-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I103" t="n">
+        <v>0</v>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L103" t="n">
+        <v>599</v>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N103" t="inlineStr"/>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P103" t="inlineStr"/>
+      <c r="Q103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>102</v>
+      </c>
+      <c r="B104" t="n">
+        <v>105042</v>
+      </c>
+      <c r="C104" t="n">
+        <v>371406</v>
+      </c>
+      <c r="D104" t="n">
+        <v>13566</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>MERIT SAMIRA CAMACHO VALENCIANO</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>SEND SALTILLO</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>01-07-2026 16:13:56</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>01-08-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I104" t="n">
+        <v>0</v>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L104" t="n">
+        <v>649</v>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N104" t="inlineStr"/>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P104" t="inlineStr"/>
+      <c r="Q104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>103</v>
+      </c>
+      <c r="B105" t="n">
+        <v>105074</v>
+      </c>
+      <c r="C105" t="n">
+        <v>194789</v>
+      </c>
+      <c r="D105" t="n">
+        <v>92296</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>ROXANA  REYES GARCIA</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>LOMA BONITA</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>01-07-2026 18:32:08</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>01-08-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I105" t="n">
+        <v>0</v>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L105" t="n">
+        <v>999</v>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N105" t="inlineStr"/>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P105" t="n">
+        <v>49758</v>
+      </c>
+      <c r="Q105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>104</v>
+      </c>
+      <c r="B106" t="n">
+        <v>105099</v>
+      </c>
+      <c r="C106" t="n">
+        <v>133363</v>
+      </c>
+      <c r="D106" t="n">
+        <v>31015</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>BERNABE  GARAY  VALLE</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>AZAHARES CUL</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>01-07-2026 20:05:52</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>01-08-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I106" t="n">
+        <v>0</v>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L106" t="n">
+        <v>599</v>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr"/>
+      <c r="O106" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P106" t="inlineStr"/>
+      <c r="Q106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>105</v>
+      </c>
+      <c r="B107" t="n">
+        <v>101975</v>
+      </c>
+      <c r="C107" t="n">
+        <v>347559</v>
+      </c>
+      <c r="D107" t="n">
+        <v>89724</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>ROSA MARIA RODRIGUEZ  AYALA</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>TEC MXL</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>21-05-2026 10:27:15</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>02-08-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I107" t="n">
+        <v>0</v>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L107" t="n">
+        <v>549</v>
+      </c>
+      <c r="M107" t="n">
+        <v>11</v>
+      </c>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t>16-05-2027 10:27:15</t>
+        </is>
+      </c>
+      <c r="O107" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P107" t="n">
+        <v>95471</v>
+      </c>
+      <c r="Q107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>106</v>
+      </c>
+      <c r="B108" t="n">
+        <v>105034</v>
+      </c>
+      <c r="C108" t="n">
+        <v>103534</v>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>01283</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>DALIA ELIZABETH RUIZ  MACEDO</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>SEND MXL</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>01-07-2026 15:00:15</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>01-08-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I108" t="n">
+        <v>0</v>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L108" t="n">
+        <v>549</v>
+      </c>
+      <c r="M108" t="n">
+        <v>11</v>
+      </c>
+      <c r="N108" t="inlineStr">
+        <is>
+          <t>26-06-2027 15:00:15</t>
+        </is>
+      </c>
+      <c r="O108" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P108" t="inlineStr"/>
+      <c r="Q108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>107</v>
+      </c>
+      <c r="B109" t="n">
+        <v>105068</v>
+      </c>
+      <c r="C109" t="n">
+        <v>258756</v>
+      </c>
+      <c r="D109" t="n">
+        <v>56260</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>OSCAR ARELLANO  LOPEZ</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>IXTAPALUCA</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>01-07-2026 18:21:24</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>01-08-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I109" t="n">
+        <v>0</v>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L109" t="n">
+        <v>599</v>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N109" t="inlineStr"/>
+      <c r="O109" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P109" t="inlineStr"/>
+      <c r="Q109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>108</v>
+      </c>
+      <c r="B110" t="n">
+        <v>105046</v>
+      </c>
+      <c r="C110" t="n">
+        <v>218346</v>
+      </c>
+      <c r="D110" t="n">
+        <v>15854</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>FERNANDO  TORRES  HERRERA</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>SEND CHIH</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>01-07-2026 16:58:47</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>01-08-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I110" t="n">
+        <v>0</v>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L110" t="n">
+        <v>999</v>
+      </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N110" t="inlineStr"/>
+      <c r="O110" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P110" t="n">
+        <v>86750</v>
+      </c>
+      <c r="Q110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>109</v>
+      </c>
+      <c r="B111" t="n">
+        <v>105060</v>
+      </c>
+      <c r="C111" t="n">
+        <v>371443</v>
+      </c>
+      <c r="D111" t="n">
+        <v>13603</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>JOSE ARMANDO ESCOBAR  FAUSTINOS</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>MISION ENS</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>01-07-2026 17:59:36</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>01-08-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I111" t="n">
+        <v>0</v>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L111" t="n">
+        <v>599</v>
+      </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N111" t="inlineStr"/>
+      <c r="O111" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P111" t="inlineStr"/>
+      <c r="Q111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>110</v>
+      </c>
+      <c r="B112" t="n">
+        <v>102973</v>
+      </c>
+      <c r="C112" t="n">
+        <v>71686</v>
+      </c>
+      <c r="D112" t="n">
+        <v>69505</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>ERICKA GONZALEZ NAVARRO</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>TEC MXL</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>02-06-2026 19:47:26</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>24-07-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I112" t="n">
+        <v>0</v>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L112" t="n">
+        <v>499</v>
+      </c>
+      <c r="M112" t="n">
+        <v>11</v>
+      </c>
+      <c r="N112" t="inlineStr">
+        <is>
+          <t>28-05-2027 19:47:26</t>
+        </is>
+      </c>
+      <c r="O112" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P112" t="n">
+        <v>97748</v>
+      </c>
+      <c r="Q112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Reporte generado: 02-07-2026 04:52 p. m.</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr"/>
+      <c r="C113" t="inlineStr"/>
+      <c r="D113" t="inlineStr"/>
+      <c r="E113" t="inlineStr"/>
+      <c r="F113" t="inlineStr"/>
+      <c r="G113" t="inlineStr"/>
+      <c r="H113" t="inlineStr"/>
+      <c r="I113" t="inlineStr"/>
+      <c r="J113" t="inlineStr"/>
+      <c r="K113" t="inlineStr"/>
+      <c r="L113" t="inlineStr"/>
+      <c r="M113" t="inlineStr"/>
+      <c r="N113" t="inlineStr"/>
+      <c r="O113" t="inlineStr"/>
+      <c r="P113" t="inlineStr"/>
+      <c r="Q113" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/descargas/cargos_recurrentes.xlsx
+++ b/data/descargas/cargos_recurrentes.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q3"/>
+  <dimension ref="A1:Q14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -599,27 +599,764 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Reporte generado: 01-08-2026 09:24 a. m. </t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="n">
+        <v>106958</v>
+      </c>
+      <c r="C3" t="n">
+        <v>33824</v>
+      </c>
+      <c r="D3" t="n">
+        <v>31740</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>JESUS OCTAVIO NAVARRETE RENTERIA</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>SAN LUIS</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>27-07-2026 8:47:58</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>01-09-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>449</v>
+      </c>
+      <c r="M3" t="n">
+        <v>11</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>22-07-2027 8:47:58</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P3" t="n">
+        <v>24603</v>
+      </c>
       <c r="Q3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="n">
+        <v>107324</v>
+      </c>
+      <c r="C4" t="n">
+        <v>258431</v>
+      </c>
+      <c r="D4" t="n">
+        <v>55935</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>ELIZABETH TOLENTINO HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>TEC MXL</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>29-07-2026 10:27:31</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>01-09-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>499</v>
+      </c>
+      <c r="M4" t="n">
+        <v>5</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>25-01-2027 10:27:31</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
+        <v>107157</v>
+      </c>
+      <c r="Q4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="n">
+        <v>105968</v>
+      </c>
+      <c r="C5" t="n">
+        <v>164157</v>
+      </c>
+      <c r="D5" t="n">
+        <v>61690</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>BERTHA ALICIA GARCIA HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>SEND MXL</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>13-07-2026 18:05:03</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>01-09-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>499</v>
+      </c>
+      <c r="M5" t="n">
+        <v>11</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>08-07-2027 18:05:03</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
+        <v>98409</v>
+      </c>
+      <c r="Q5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="n">
+        <v>106990</v>
+      </c>
+      <c r="C6" t="n">
+        <v>186227</v>
+      </c>
+      <c r="D6" t="n">
+        <v>83734</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>ALEJANDRA GUADALUPE  PUENTE  MARTINEZ</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>SEND SALTILLO</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>27-07-2026 13:11:58</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>06-05-2025 23:59:59</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>499</v>
+      </c>
+      <c r="M6" t="n">
+        <v>11</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>22-07-2027 13:11:58</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>52206</v>
+      </c>
+      <c r="Q6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" t="n">
+        <v>105143</v>
+      </c>
+      <c r="C7" t="n">
+        <v>307187</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>04686</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>MARIA GLORIA  SARABIA  CORONA</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>TEC MXL</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>02-07-2026 12:18:21</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>01-09-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>399</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>73904</v>
+      </c>
+      <c r="Q7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" t="n">
+        <v>105425</v>
+      </c>
+      <c r="C8" t="n">
+        <v>286072</v>
+      </c>
+      <c r="D8" t="n">
+        <v>83572</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>MARIEL ARIANA BARRAZA ARCE</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>TEC MXL</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>06-07-2026 18:05:56</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>01-09-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>499</v>
+      </c>
+      <c r="M8" t="n">
+        <v>11</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>01-07-2027 18:05:56</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P8" t="n">
+        <v>105424</v>
+      </c>
+      <c r="Q8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" t="n">
+        <v>107555</v>
+      </c>
+      <c r="C9" t="n">
+        <v>6276</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>05213</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>GERARDO HURTADO  BARON</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>MISION ENS</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>31-07-2026 10:23:25</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>01-09-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>399</v>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
+        <v>28862</v>
+      </c>
+      <c r="Q9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" t="n">
+        <v>105109</v>
+      </c>
+      <c r="C10" t="n">
+        <v>366026</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>08186</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>ERIK SALDAÑA  SANCHEZ</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>STA CATARINA</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>02-07-2026 4:23:57</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>01-09-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>499</v>
+      </c>
+      <c r="M10" t="n">
+        <v>5</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>29-12-2026 4:23:57</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>102797</v>
+      </c>
+      <c r="Q10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" t="n">
+        <v>105018</v>
+      </c>
+      <c r="C11" t="n">
+        <v>65078</v>
+      </c>
+      <c r="D11" t="n">
+        <v>62916</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>ALEJANDRO MAGALLAN  LOPEZ</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>SEND CUL</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>01-07-2026 7:04:56</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>01-09-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>350</v>
+      </c>
+      <c r="M11" t="n">
+        <v>5</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>28-12-2026 7:04:56</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>98454</v>
+      </c>
+      <c r="Q11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" t="n">
+        <v>107630</v>
+      </c>
+      <c r="C12" t="n">
+        <v>337648</v>
+      </c>
+      <c r="D12" t="n">
+        <v>15467</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>CHRISTIAN RIVERA ZAVALETA</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>INSURGENTES</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>01-08-2026 8:29:26</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>01-09-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>699</v>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" t="n">
+        <v>105173</v>
+      </c>
+      <c r="C13" t="n">
+        <v>312176</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>09675</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>KEVIN MICHAEL GONZALEZ ALCANTAR</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>PASEO 2000</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>02-07-2026 15:58:26</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>01-09-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>549</v>
+      </c>
+      <c r="M13" t="n">
+        <v>5</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>29-12-2026 15:58:26</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>76876</v>
+      </c>
+      <c r="Q13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Reporte generado: 01-08-2026 04:05 p. m.</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/descargas/cargos_recurrentes.xlsx
+++ b/data/descargas/cargos_recurrentes.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q14"/>
+  <dimension ref="A1:Q22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -603,32 +603,32 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>106958</v>
+        <v>106990</v>
       </c>
       <c r="C3" t="n">
-        <v>33824</v>
+        <v>186227</v>
       </c>
       <c r="D3" t="n">
-        <v>31740</v>
+        <v>83734</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>JESUS OCTAVIO NAVARRETE RENTERIA</t>
+          <t>ALEJANDRA GUADALUPE  PUENTE  MARTINEZ</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>SAN LUIS</t>
+          <t>SEND SALTILLO</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>27-07-2026 8:47:58</t>
+          <t>27-07-2026 13:11:58</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>01-09-2026 23:59:59</t>
+          <t>06-05-2025 23:59:59</t>
         </is>
       </c>
       <c r="I3" t="n">
@@ -645,14 +645,14 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>449</v>
+        <v>499</v>
       </c>
       <c r="M3" t="n">
         <v>11</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>22-07-2027 8:47:58</t>
+          <t>22-07-2027 13:11:58</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -661,7 +661,7 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>24603</v>
+        <v>52206</v>
       </c>
       <c r="Q3" t="inlineStr"/>
     </row>
@@ -670,27 +670,27 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>107324</v>
+        <v>106958</v>
       </c>
       <c r="C4" t="n">
-        <v>258431</v>
+        <v>33824</v>
       </c>
       <c r="D4" t="n">
-        <v>55935</v>
+        <v>31740</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>ELIZABETH TOLENTINO HERNANDEZ</t>
+          <t>JESUS OCTAVIO NAVARRETE RENTERIA</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>TEC MXL</t>
+          <t>SAN LUIS</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>29-07-2026 10:27:31</t>
+          <t>27-07-2026 8:47:58</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -712,14 +712,14 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>499</v>
+        <v>449</v>
       </c>
       <c r="M4" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>25-01-2027 10:27:31</t>
+          <t>22-07-2027 8:47:58</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -728,7 +728,7 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>107157</v>
+        <v>24603</v>
       </c>
       <c r="Q4" t="inlineStr"/>
     </row>
@@ -737,27 +737,27 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>105968</v>
+        <v>107324</v>
       </c>
       <c r="C5" t="n">
-        <v>164157</v>
+        <v>258431</v>
       </c>
       <c r="D5" t="n">
-        <v>61690</v>
+        <v>55935</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>BERTHA ALICIA GARCIA HERNANDEZ</t>
+          <t>ELIZABETH TOLENTINO HERNANDEZ</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>SEND MXL</t>
+          <t>TEC MXL</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>13-07-2026 18:05:03</t>
+          <t>29-07-2026 10:27:31</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -782,11 +782,11 @@
         <v>499</v>
       </c>
       <c r="M5" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>08-07-2027 18:05:03</t>
+          <t>25-01-2027 10:27:31</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -795,7 +795,7 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>98409</v>
+        <v>107157</v>
       </c>
       <c r="Q5" t="inlineStr"/>
     </row>
@@ -804,32 +804,32 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>106990</v>
+        <v>107631</v>
       </c>
       <c r="C6" t="n">
-        <v>186227</v>
+        <v>376815</v>
       </c>
       <c r="D6" t="n">
-        <v>83734</v>
+        <v>18975</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>ALEJANDRA GUADALUPE  PUENTE  MARTINEZ</t>
+          <t>RICARDO ALEJANDRO  CARRERA HERNANDEZ</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>SEND SALTILLO</t>
+          <t>PASEO LA PAZ</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>27-07-2026 13:11:58</t>
+          <t>01-08-2026 9:37:22</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>06-05-2025 23:59:59</t>
+          <t>01-09-2026 23:59:59</t>
         </is>
       </c>
       <c r="I6" t="n">
@@ -842,18 +842,18 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>RENOVACIÓN</t>
+          <t>NUEVO</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>499</v>
+        <v>999</v>
       </c>
       <c r="M6" t="n">
         <v>11</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>22-07-2027 13:11:58</t>
+          <t>27-07-2027 9:37:22</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -861,9 +861,7 @@
           <t>Domiciliado</t>
         </is>
       </c>
-      <c r="P6" t="n">
-        <v>52206</v>
-      </c>
+      <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr"/>
     </row>
     <row r="7">
@@ -871,29 +869,27 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>105143</v>
+        <v>107641</v>
       </c>
       <c r="C7" t="n">
-        <v>307187</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>04686</t>
-        </is>
+        <v>285430</v>
+      </c>
+      <c r="D7" t="n">
+        <v>82931</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>MARIA GLORIA  SARABIA  CORONA</t>
+          <t>ALMA BELIA GARCIA LARA</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>TEC MXL</t>
+          <t>SEND MXL</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>02-07-2026 12:18:21</t>
+          <t>01-08-2026 12:58:24</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -911,11 +907,11 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>RENOVACIÓN</t>
+          <t>NUEVO</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>399</v>
+        <v>599</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -928,9 +924,7 @@
           <t>Recurrente</t>
         </is>
       </c>
-      <c r="P7" t="n">
-        <v>73904</v>
-      </c>
+      <c r="P7" t="inlineStr"/>
       <c r="Q7" t="inlineStr"/>
     </row>
     <row r="8">
@@ -938,17 +932,17 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>105425</v>
+        <v>107639</v>
       </c>
       <c r="C8" t="n">
-        <v>286072</v>
+        <v>144840</v>
       </c>
       <c r="D8" t="n">
-        <v>83572</v>
+        <v>42434</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>MARIEL ARIANA BARRAZA ARCE</t>
+          <t>MARIA TERESA LOPEZ GARCIA</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -958,7 +952,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>06-07-2026 18:05:56</t>
+          <t>01-08-2026 12:34:01</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -976,28 +970,24 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>RENOVACIÓN</t>
+          <t>NUEVO</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>499</v>
-      </c>
-      <c r="M8" t="n">
-        <v>11</v>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>01-07-2027 18:05:56</t>
-        </is>
-      </c>
+        <v>599</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Domiciliado</t>
-        </is>
-      </c>
-      <c r="P8" t="n">
-        <v>105424</v>
-      </c>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr"/>
       <c r="Q8" t="inlineStr"/>
     </row>
     <row r="9">
@@ -1005,29 +995,27 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>107555</v>
+        <v>105968</v>
       </c>
       <c r="C9" t="n">
-        <v>6276</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>05213</t>
-        </is>
+        <v>164157</v>
+      </c>
+      <c r="D9" t="n">
+        <v>61690</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>GERARDO HURTADO  BARON</t>
+          <t>BERTHA ALICIA GARCIA HERNANDEZ</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>MISION ENS</t>
+          <t>SEND MXL</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>31-07-2026 10:23:25</t>
+          <t>13-07-2026 18:05:03</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1049,21 +1037,23 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>399</v>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>Indefinido</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
+        <v>499</v>
+      </c>
+      <c r="M9" t="n">
+        <v>11</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>08-07-2027 18:05:03</t>
+        </is>
+      </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Recurrente</t>
+          <t>Domiciliado</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>28862</v>
+        <v>98409</v>
       </c>
       <c r="Q9" t="inlineStr"/>
     </row>
@@ -1072,29 +1062,29 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>105109</v>
+        <v>105143</v>
       </c>
       <c r="C10" t="n">
-        <v>366026</v>
+        <v>307187</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>08186</t>
+          <t>04686</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>ERIK SALDAÑA  SANCHEZ</t>
+          <t>MARIA GLORIA  SARABIA  CORONA</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>STA CATARINA</t>
+          <t>TEC MXL</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>02-07-2026 4:23:57</t>
+          <t>02-07-2026 12:18:21</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1116,23 +1106,21 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>499</v>
-      </c>
-      <c r="M10" t="n">
-        <v>5</v>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>29-12-2026 4:23:57</t>
-        </is>
-      </c>
+        <v>399</v>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Domiciliado</t>
+          <t>Recurrente</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>102797</v>
+        <v>73904</v>
       </c>
       <c r="Q10" t="inlineStr"/>
     </row>
@@ -1141,27 +1129,29 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>105018</v>
+        <v>107555</v>
       </c>
       <c r="C11" t="n">
-        <v>65078</v>
-      </c>
-      <c r="D11" t="n">
-        <v>62916</v>
+        <v>6276</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>05213</t>
+        </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>ALEJANDRO MAGALLAN  LOPEZ</t>
+          <t>GERARDO HURTADO  BARON</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>SEND CUL</t>
+          <t>MISION ENS</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>01-07-2026 7:04:56</t>
+          <t>31-07-2026 10:23:25</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1183,23 +1173,21 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>350</v>
-      </c>
-      <c r="M11" t="n">
-        <v>5</v>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>28-12-2026 7:04:56</t>
-        </is>
-      </c>
+        <v>399</v>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Domiciliado</t>
+          <t>Recurrente</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>98454</v>
+        <v>28862</v>
       </c>
       <c r="Q11" t="inlineStr"/>
     </row>
@@ -1208,27 +1196,27 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>107630</v>
+        <v>105425</v>
       </c>
       <c r="C12" t="n">
-        <v>337648</v>
+        <v>286072</v>
       </c>
       <c r="D12" t="n">
-        <v>15467</v>
+        <v>83572</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CHRISTIAN RIVERA ZAVALETA</t>
+          <t>MARIEL ARIANA BARRAZA ARCE</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>INSURGENTES</t>
+          <t>TEC MXL</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>01-08-2026 8:29:26</t>
+          <t>06-07-2026 18:05:56</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1246,24 +1234,28 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>NUEVO</t>
+          <t>RENOVACIÓN</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>699</v>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>Indefinido</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
+        <v>499</v>
+      </c>
+      <c r="M12" t="n">
+        <v>11</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>01-07-2027 18:05:56</t>
+        </is>
+      </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Recurrente</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr"/>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>105424</v>
+      </c>
       <c r="Q12" t="inlineStr"/>
     </row>
     <row r="13">
@@ -1271,29 +1263,27 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>105173</v>
+        <v>107640</v>
       </c>
       <c r="C13" t="n">
-        <v>312176</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>09675</t>
-        </is>
+        <v>144848</v>
+      </c>
+      <c r="D13" t="n">
+        <v>42442</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>KEVIN MICHAEL GONZALEZ ALCANTAR</t>
+          <t>SARAHI  LOPEZ GARCIA</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>PASEO 2000</t>
+          <t>TEC MXL</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>02-07-2026 15:58:26</t>
+          <t>01-08-2026 12:38:22</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1311,52 +1301,572 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>599</v>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" t="n">
+        <v>107644</v>
+      </c>
+      <c r="C14" t="n">
+        <v>165704</v>
+      </c>
+      <c r="D14" t="n">
+        <v>63237</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>ESTEBAN ENRIQUE CALOCA  GOMEZ</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>CARROUSEL TJ</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>01-08-2026 15:29:54</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>01-09-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
           <t>RENOVACIÓN</t>
         </is>
       </c>
-      <c r="L13" t="n">
+      <c r="L14" t="n">
+        <v>999</v>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>51618</v>
+      </c>
+      <c r="Q14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" t="n">
+        <v>105109</v>
+      </c>
+      <c r="C15" t="n">
+        <v>366026</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>08186</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>ERIK SALDAÑA  SANCHEZ</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>STA CATARINA</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>02-07-2026 4:23:57</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>01-09-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L15" t="n">
+        <v>499</v>
+      </c>
+      <c r="M15" t="n">
+        <v>5</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>29-12-2026 4:23:57</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>102797</v>
+      </c>
+      <c r="Q15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" t="n">
+        <v>107636</v>
+      </c>
+      <c r="C16" t="n">
+        <v>36616</v>
+      </c>
+      <c r="D16" t="n">
+        <v>34520</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>KEVYN URIAS SOTO</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>TEC MXL</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>01-08-2026 10:08:11</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>01-09-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L16" t="n">
+        <v>599</v>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" t="n">
+        <v>105173</v>
+      </c>
+      <c r="C17" t="n">
+        <v>312176</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>09675</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>KEVIN MICHAEL GONZALEZ ALCANTAR</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>PASEO 2000</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>02-07-2026 15:58:26</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>01-09-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L17" t="n">
         <v>549</v>
       </c>
-      <c r="M13" t="n">
+      <c r="M17" t="n">
         <v>5</v>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="N17" t="inlineStr">
         <is>
           <t>29-12-2026 15:58:26</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
+      <c r="O17" t="inlineStr">
         <is>
           <t>Domiciliado</t>
         </is>
       </c>
-      <c r="P13" t="n">
+      <c r="P17" t="n">
         <v>76876</v>
       </c>
-      <c r="Q13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Reporte generado: 01-08-2026 04:05 p. m.</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" t="n">
+        <v>105018</v>
+      </c>
+      <c r="C18" t="n">
+        <v>65078</v>
+      </c>
+      <c r="D18" t="n">
+        <v>62916</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>ALEJANDRO MAGALLAN  LOPEZ</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>SEND CUL</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>01-07-2026 7:04:56</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>01-09-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L18" t="n">
+        <v>350</v>
+      </c>
+      <c r="M18" t="n">
+        <v>5</v>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>28-12-2026 7:04:56</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P18" t="n">
+        <v>98454</v>
+      </c>
+      <c r="Q18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" t="n">
+        <v>107632</v>
+      </c>
+      <c r="C19" t="n">
+        <v>376819</v>
+      </c>
+      <c r="D19" t="n">
+        <v>18979</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>GUILLERMINA  CELIS  ARENAS</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>IXTAPALUCA</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>01-08-2026 9:46:41</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>01-09-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L19" t="n">
+        <v>599</v>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" t="n">
+        <v>107630</v>
+      </c>
+      <c r="C20" t="n">
+        <v>337648</v>
+      </c>
+      <c r="D20" t="n">
+        <v>15467</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>CHRISTIAN RIVERA ZAVALETA</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>INSURGENTES</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>01-08-2026 8:29:26</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>01-09-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L20" t="n">
+        <v>699</v>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" t="n">
+        <v>107638</v>
+      </c>
+      <c r="C21" t="n">
+        <v>376843</v>
+      </c>
+      <c r="D21" t="n">
+        <v>19003</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>LIZBETH GUADALUPE ARROYO  DIAZ</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>SEND SALTILLO</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>01-08-2026 12:28:10</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>01-09-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L21" t="n">
+        <v>549</v>
+      </c>
+      <c r="M21" t="n">
+        <v>11</v>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>27-07-2027 12:28:10</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Reporte generado: 02-08-2026 04:05 p. m.</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/descargas/cargos_recurrentes.xlsx
+++ b/data/descargas/cargos_recurrentes.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q22"/>
+  <dimension ref="A1:Q100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -603,32 +603,32 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>106990</v>
+        <v>107652</v>
       </c>
       <c r="C3" t="n">
-        <v>186227</v>
+        <v>375904</v>
       </c>
       <c r="D3" t="n">
-        <v>83734</v>
+        <v>18064</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>ALEJANDRA GUADALUPE  PUENTE  MARTINEZ</t>
+          <t>MARIA JOSE  MENDOZA RAMIREZ</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>SEND SALTILLO</t>
+          <t>CARROUSEL TJ</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>27-07-2026 13:11:58</t>
+          <t>02-08-2026 11:26:36</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>06-05-2025 23:59:59</t>
+          <t>02-09-2026 23:59:59</t>
         </is>
       </c>
       <c r="I3" t="n">
@@ -641,28 +641,24 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>RENOVACIÓN</t>
+          <t>NUEVO</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>499</v>
-      </c>
-      <c r="M3" t="n">
-        <v>11</v>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>22-07-2027 13:11:58</t>
-        </is>
-      </c>
+        <v>599</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Domiciliado</t>
-        </is>
-      </c>
-      <c r="P3" t="n">
-        <v>52206</v>
-      </c>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr"/>
     </row>
     <row r="4">
@@ -804,32 +800,32 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>107631</v>
+        <v>106912</v>
       </c>
       <c r="C6" t="n">
-        <v>376815</v>
+        <v>339916</v>
       </c>
       <c r="D6" t="n">
-        <v>18975</v>
+        <v>17734</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RICARDO ALEJANDRO  CARRERA HERNANDEZ</t>
+          <t>JOSE ALFREDO  ROSAS  RODRIGUEZ</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>PASEO LA PAZ</t>
+          <t>METEPEC</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>01-08-2026 9:37:22</t>
+          <t>26-07-2026 10:20:48</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>01-09-2026 23:59:59</t>
+          <t>02-09-2026 23:59:59</t>
         </is>
       </c>
       <c r="I6" t="n">
@@ -842,26 +838,26 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>NUEVO</t>
+          <t>RENOVACIÓN</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>999</v>
-      </c>
-      <c r="M6" t="n">
-        <v>11</v>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>27-07-2027 9:37:22</t>
-        </is>
-      </c>
+        <v>549</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Domiciliado</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr"/>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>91288</v>
+      </c>
       <c r="Q6" t="inlineStr"/>
     </row>
     <row r="7">
@@ -869,32 +865,32 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>107641</v>
+        <v>107705</v>
       </c>
       <c r="C7" t="n">
-        <v>285430</v>
+        <v>376056</v>
       </c>
       <c r="D7" t="n">
-        <v>82931</v>
+        <v>18216</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>ALMA BELIA GARCIA LARA</t>
+          <t>EMILIANO GARCIA RAMIREZ</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>SEND MXL</t>
+          <t>SALTILLO VILLALTA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>01-08-2026 12:58:24</t>
+          <t>03-08-2026 9:39:54</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>01-09-2026 23:59:59</t>
+          <t>03-09-2026 23:59:59</t>
         </is>
       </c>
       <c r="I7" t="n">
@@ -911,17 +907,19 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>599</v>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>Indefinido</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
+        <v>649</v>
+      </c>
+      <c r="M7" t="n">
+        <v>11</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>29-07-2027 9:39:54</t>
+        </is>
+      </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Recurrente</t>
+          <t>Domiciliado</t>
         </is>
       </c>
       <c r="P7" t="inlineStr"/>
@@ -932,32 +930,32 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>107639</v>
+        <v>107659</v>
       </c>
       <c r="C8" t="n">
-        <v>144840</v>
+        <v>376891</v>
       </c>
       <c r="D8" t="n">
-        <v>42434</v>
+        <v>19051</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>MARIA TERESA LOPEZ GARCIA</t>
+          <t>SIRIAMI ANGELICA VEGA ARELLANO</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>TEC MXL</t>
+          <t>SEND CHIH</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>01-08-2026 12:34:01</t>
+          <t>02-08-2026 12:59:06</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>01-09-2026 23:59:59</t>
+          <t>02-09-2026 23:59:59</t>
         </is>
       </c>
       <c r="I8" t="n">
@@ -995,32 +993,32 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>105968</v>
+        <v>107678</v>
       </c>
       <c r="C9" t="n">
-        <v>164157</v>
+        <v>376936</v>
       </c>
       <c r="D9" t="n">
-        <v>61690</v>
+        <v>19096</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>BERTHA ALICIA GARCIA HERNANDEZ</t>
+          <t>ESBEYDE EZAIDYTH RAMIREZ QUINTERO</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>SEND MXL</t>
+          <t>PASEO 2000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>13-07-2026 18:05:03</t>
+          <t>03-08-2026 6:28:28</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>01-09-2026 23:59:59</t>
+          <t>03-09-2026 23:59:59</t>
         </is>
       </c>
       <c r="I9" t="n">
@@ -1033,28 +1031,24 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>RENOVACIÓN</t>
+          <t>NUEVO</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>499</v>
-      </c>
-      <c r="M9" t="n">
-        <v>11</v>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>08-07-2027 18:05:03</t>
-        </is>
-      </c>
+        <v>599</v>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Domiciliado</t>
-        </is>
-      </c>
-      <c r="P9" t="n">
-        <v>98409</v>
-      </c>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr"/>
       <c r="Q9" t="inlineStr"/>
     </row>
     <row r="10">
@@ -1062,34 +1056,32 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>105143</v>
+        <v>105284</v>
       </c>
       <c r="C10" t="n">
-        <v>307187</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>04686</t>
-        </is>
+        <v>277083</v>
+      </c>
+      <c r="D10" t="n">
+        <v>74584</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>MARIA GLORIA  SARABIA  CORONA</t>
+          <t>MIGUEL ANGEL CRISANTO PEDRO</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>TEC MXL</t>
+          <t>PASEO 2000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>02-07-2026 12:18:21</t>
+          <t>03-07-2026 17:01:00</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>01-09-2026 23:59:59</t>
+          <t>03-09-2026 23:59:59</t>
         </is>
       </c>
       <c r="I10" t="n">
@@ -1106,21 +1098,23 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>399</v>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>Indefinido</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
+        <v>499</v>
+      </c>
+      <c r="M10" t="n">
+        <v>11</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>28-06-2027 17:01:00</t>
+        </is>
+      </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Recurrente</t>
+          <t>Domiciliado</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>73904</v>
+        <v>103105</v>
       </c>
       <c r="Q10" t="inlineStr"/>
     </row>
@@ -1129,34 +1123,32 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>107555</v>
+        <v>107690</v>
       </c>
       <c r="C11" t="n">
-        <v>6276</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>05213</t>
-        </is>
+        <v>376957</v>
+      </c>
+      <c r="D11" t="n">
+        <v>19117</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>GERARDO HURTADO  BARON</t>
+          <t>ABRAHAM HEDIKEL BORREGO BUSTOS</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>MISION ENS</t>
+          <t>TLALNEPANTLA</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>31-07-2026 10:23:25</t>
+          <t>03-08-2026 8:25:03</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>01-09-2026 23:59:59</t>
+          <t>03-09-2026 23:59:59</t>
         </is>
       </c>
       <c r="I11" t="n">
@@ -1169,26 +1161,26 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>RENOVACIÓN</t>
+          <t>NUEVO</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>399</v>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>Indefinido</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
+        <v>549</v>
+      </c>
+      <c r="M11" t="n">
+        <v>11</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>29-07-2027 8:25:03</t>
+        </is>
+      </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Recurrente</t>
-        </is>
-      </c>
-      <c r="P11" t="n">
-        <v>28862</v>
-      </c>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr"/>
       <c r="Q11" t="inlineStr"/>
     </row>
     <row r="12">
@@ -1196,32 +1188,32 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>105425</v>
+        <v>107713</v>
       </c>
       <c r="C12" t="n">
-        <v>286072</v>
+        <v>354782</v>
       </c>
       <c r="D12" t="n">
-        <v>83572</v>
+        <v>96946</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>MARIEL ARIANA BARRAZA ARCE</t>
+          <t>DULCE MARIA VALDOVINOS GARAY</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>TEC MXL</t>
+          <t>PASEO 2000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>06-07-2026 18:05:56</t>
+          <t>03-08-2026 10:42:46</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>01-09-2026 23:59:59</t>
+          <t>03-09-2026 23:59:59</t>
         </is>
       </c>
       <c r="I12" t="n">
@@ -1234,28 +1226,24 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>RENOVACIÓN</t>
+          <t>NUEVO</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>499</v>
-      </c>
-      <c r="M12" t="n">
-        <v>11</v>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>01-07-2027 18:05:56</t>
-        </is>
-      </c>
+        <v>599</v>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Domiciliado</t>
-        </is>
-      </c>
-      <c r="P12" t="n">
-        <v>105424</v>
-      </c>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr"/>
       <c r="Q12" t="inlineStr"/>
     </row>
     <row r="13">
@@ -1263,27 +1251,27 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>107640</v>
+        <v>106938</v>
       </c>
       <c r="C13" t="n">
-        <v>144848</v>
+        <v>330015</v>
       </c>
       <c r="D13" t="n">
-        <v>42442</v>
+        <v>15069</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>SARAHI  LOPEZ GARCIA</t>
+          <t>NOEL GALLEGOS VARELA</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>TEC MXL</t>
+          <t>SEND CHIH</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>01-08-2026 12:38:22</t>
+          <t>27-07-2026 6:51:51</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1301,24 +1289,28 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>NUEVO</t>
+          <t>RENOVACIÓN</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>599</v>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>Indefinido</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
+        <v>549</v>
+      </c>
+      <c r="M13" t="n">
+        <v>11</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>22-07-2027 6:51:51</t>
+        </is>
+      </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Recurrente</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr"/>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>98376</v>
+      </c>
       <c r="Q13" t="inlineStr"/>
     </row>
     <row r="14">
@@ -1326,27 +1318,27 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>107644</v>
+        <v>107631</v>
       </c>
       <c r="C14" t="n">
-        <v>165704</v>
+        <v>376815</v>
       </c>
       <c r="D14" t="n">
-        <v>63237</v>
+        <v>18975</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>ESTEBAN ENRIQUE CALOCA  GOMEZ</t>
+          <t>RICARDO ALEJANDRO  CARRERA HERNANDEZ</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>CARROUSEL TJ</t>
+          <t>PASEO LA PAZ</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>01-08-2026 15:29:54</t>
+          <t>01-08-2026 9:37:22</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1364,26 +1356,26 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>RENOVACIÓN</t>
+          <t>NUEVO</t>
         </is>
       </c>
       <c r="L14" t="n">
         <v>999</v>
       </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>Indefinido</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
+      <c r="M14" t="n">
+        <v>11</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>27-07-2027 9:37:22</t>
+        </is>
+      </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Recurrente</t>
-        </is>
-      </c>
-      <c r="P14" t="n">
-        <v>51618</v>
-      </c>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr"/>
       <c r="Q14" t="inlineStr"/>
     </row>
     <row r="15">
@@ -1391,34 +1383,32 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>105109</v>
+        <v>107697</v>
       </c>
       <c r="C15" t="n">
-        <v>366026</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>08186</t>
-        </is>
+        <v>196182</v>
+      </c>
+      <c r="D15" t="n">
+        <v>93689</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>ERIK SALDAÑA  SANCHEZ</t>
+          <t>MYRNA AZUCENA ZARATE LOPEZ</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>STA CATARINA</t>
+          <t>AZAHARES CUL</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>02-07-2026 4:23:57</t>
+          <t>03-08-2026 8:58:32</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>01-09-2026 23:59:59</t>
+          <t>03-09-2026 23:59:59</t>
         </is>
       </c>
       <c r="I15" t="n">
@@ -1431,28 +1421,24 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>RENOVACIÓN</t>
+          <t>NUEVO</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>499</v>
-      </c>
-      <c r="M15" t="n">
-        <v>5</v>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>29-12-2026 4:23:57</t>
-        </is>
-      </c>
+        <v>599</v>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Domiciliado</t>
-        </is>
-      </c>
-      <c r="P15" t="n">
-        <v>102797</v>
-      </c>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr"/>
       <c r="Q15" t="inlineStr"/>
     </row>
     <row r="16">
@@ -1460,32 +1446,32 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>107636</v>
+        <v>107646</v>
       </c>
       <c r="C16" t="n">
-        <v>36616</v>
+        <v>140783</v>
       </c>
       <c r="D16" t="n">
-        <v>34520</v>
+        <v>38409</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>KEVYN URIAS SOTO</t>
+          <t>MARTHA IDALIA VASQUEZ BERLANGA</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>TEC MXL</t>
+          <t>SEND SALTILLO</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>01-08-2026 10:08:11</t>
+          <t>02-08-2026 9:42:55</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>01-09-2026 23:59:59</t>
+          <t>02-09-2026 23:59:59</t>
         </is>
       </c>
       <c r="I16" t="n">
@@ -1523,19 +1509,19 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>105173</v>
+        <v>106849</v>
       </c>
       <c r="C17" t="n">
-        <v>312176</v>
+        <v>307291</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>09675</t>
+          <t>04790</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>KEVIN MICHAEL GONZALEZ ALCANTAR</t>
+          <t>LUIS ENRIQUE HERNANDEZ ALTAMIRANO</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1545,12 +1531,12 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>02-07-2026 15:58:26</t>
+          <t>24-07-2026 7:05:34</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>01-09-2026 23:59:59</t>
+          <t>02-09-2026 23:59:59</t>
         </is>
       </c>
       <c r="I17" t="n">
@@ -1567,14 +1553,14 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>549</v>
+        <v>499</v>
       </c>
       <c r="M17" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>29-12-2026 15:58:26</t>
+          <t>19-07-2027 7:05:34</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -1583,7 +1569,7 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>76876</v>
+        <v>73977</v>
       </c>
       <c r="Q17" t="inlineStr"/>
     </row>
@@ -1592,32 +1578,32 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>105018</v>
+        <v>107684</v>
       </c>
       <c r="C18" t="n">
-        <v>65078</v>
+        <v>58222</v>
       </c>
       <c r="D18" t="n">
-        <v>62916</v>
+        <v>56066</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>ALEJANDRO MAGALLAN  LOPEZ</t>
+          <t>CRISTHIAN JOSE LOPEZ RAMIREZ</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>SEND CUL</t>
+          <t>LOMA BONITA</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>01-07-2026 7:04:56</t>
+          <t>03-08-2026 7:21:52</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>01-09-2026 23:59:59</t>
+          <t>03-09-2026 23:59:59</t>
         </is>
       </c>
       <c r="I18" t="n">
@@ -1634,23 +1620,21 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>350</v>
-      </c>
-      <c r="M18" t="n">
-        <v>5</v>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>28-12-2026 7:04:56</t>
-        </is>
-      </c>
+        <v>999</v>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Domiciliado</t>
+          <t>Recurrente</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>98454</v>
+        <v>26208</v>
       </c>
       <c r="Q18" t="inlineStr"/>
     </row>
@@ -1659,32 +1643,32 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>107632</v>
+        <v>106990</v>
       </c>
       <c r="C19" t="n">
-        <v>376819</v>
+        <v>186227</v>
       </c>
       <c r="D19" t="n">
-        <v>18979</v>
+        <v>83734</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>GUILLERMINA  CELIS  ARENAS</t>
+          <t>ALEJANDRA GUADALUPE  PUENTE  MARTINEZ</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>IXTAPALUCA</t>
+          <t>SEND SALTILLO</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>01-08-2026 9:46:41</t>
+          <t>27-07-2026 13:11:58</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>01-09-2026 23:59:59</t>
+          <t>06-07-2025 23:59:59</t>
         </is>
       </c>
       <c r="I19" t="n">
@@ -1697,24 +1681,28 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>NUEVO</t>
+          <t>RENOVACIÓN</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>599</v>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>Indefinido</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
+        <v>499</v>
+      </c>
+      <c r="M19" t="n">
+        <v>9</v>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>22-07-2027 13:11:58</t>
+        </is>
+      </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Recurrente</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr"/>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
+        <v>52206</v>
+      </c>
       <c r="Q19" t="inlineStr"/>
     </row>
     <row r="20">
@@ -1722,32 +1710,32 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>107630</v>
+        <v>107712</v>
       </c>
       <c r="C20" t="n">
-        <v>337648</v>
+        <v>376988</v>
       </c>
       <c r="D20" t="n">
-        <v>15467</v>
+        <v>19148</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>CHRISTIAN RIVERA ZAVALETA</t>
+          <t>MARIA  RIOS  RUIZ</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>INSURGENTES</t>
+          <t>SEND CUL</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>01-08-2026 8:29:26</t>
+          <t>03-08-2026 10:27:44</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>01-09-2026 23:59:59</t>
+          <t>03-09-2026 23:59:59</t>
         </is>
       </c>
       <c r="I20" t="n">
@@ -1764,7 +1752,7 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>699</v>
+        <v>599</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
@@ -1785,32 +1773,32 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>107638</v>
+        <v>107710</v>
       </c>
       <c r="C21" t="n">
-        <v>376843</v>
+        <v>376986</v>
       </c>
       <c r="D21" t="n">
-        <v>19003</v>
+        <v>19146</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>LIZBETH GUADALUPE ARROYO  DIAZ</t>
+          <t>CAMILA MAYTE MATA CASTILLA</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>SEND SALTILLO</t>
+          <t>STA CATARINA</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>01-08-2026 12:28:10</t>
+          <t>03-08-2026 10:14:12</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>01-09-2026 23:59:59</t>
+          <t>03-09-2026 23:59:59</t>
         </is>
       </c>
       <c r="I21" t="n">
@@ -1827,46 +1815,5074 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>549</v>
-      </c>
-      <c r="M21" t="n">
-        <v>11</v>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>27-07-2027 12:28:10</t>
-        </is>
-      </c>
+        <v>599</v>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Domiciliado</t>
+          <t>Recurrente</t>
         </is>
       </c>
       <c r="P21" t="inlineStr"/>
       <c r="Q21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Reporte generado: 02-08-2026 04:05 p. m.</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr"/>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr"/>
-      <c r="P22" t="inlineStr"/>
+      <c r="A22" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" t="n">
+        <v>106727</v>
+      </c>
+      <c r="C22" t="n">
+        <v>198883</v>
+      </c>
+      <c r="D22" t="n">
+        <v>96390</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>ERIKA ALEXANDRA GARCIA ARIAS</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>VILLA VERDE</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>22-07-2026 12:13:05</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>03-09-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L22" t="n">
+        <v>449</v>
+      </c>
+      <c r="M22" t="n">
+        <v>11</v>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>17-07-2027 12:13:05</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P22" t="n">
+        <v>49719</v>
+      </c>
       <c r="Q22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" t="n">
+        <v>107672</v>
+      </c>
+      <c r="C23" t="n">
+        <v>64120</v>
+      </c>
+      <c r="D23" t="n">
+        <v>61959</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>ISRAEL  FUENTES CASTILLO</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>MISION ENS</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>03-08-2026 5:29:26</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>03-09-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L23" t="n">
+        <v>599</v>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>22</v>
+      </c>
+      <c r="B24" t="n">
+        <v>107696</v>
+      </c>
+      <c r="C24" t="n">
+        <v>376965</v>
+      </c>
+      <c r="D24" t="n">
+        <v>19125</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>YUSEF SITLAELT TORRES SAAB</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>INSURGENTES</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>03-08-2026 8:47:21</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>03-09-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L24" t="n">
+        <v>699</v>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>23</v>
+      </c>
+      <c r="B25" t="n">
+        <v>106113</v>
+      </c>
+      <c r="C25" t="n">
+        <v>293590</v>
+      </c>
+      <c r="D25" t="n">
+        <v>91088</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>PORFIRIA BUSTILLOS QUEZADA</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>MISION ENS</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>14-07-2026 18:20:25</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>30-08-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L25" t="n">
+        <v>499</v>
+      </c>
+      <c r="M25" t="n">
+        <v>11</v>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>09-07-2027 18:20:25</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P25" t="n">
+        <v>66915</v>
+      </c>
+      <c r="Q25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>24</v>
+      </c>
+      <c r="B26" t="n">
+        <v>107651</v>
+      </c>
+      <c r="C26" t="n">
+        <v>111167</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>08904</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>VENUS RUIZ RIZO</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>SEND SALTILLO</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>02-08-2026 10:53:53</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>02-09-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L26" t="n">
+        <v>599</v>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>25</v>
+      </c>
+      <c r="B27" t="n">
+        <v>107701</v>
+      </c>
+      <c r="C27" t="n">
+        <v>376460</v>
+      </c>
+      <c r="D27" t="n">
+        <v>18620</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>SANTOS ISAIAS REYES BONILLA</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>STA CATARINA</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>03-08-2026 9:08:14</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>03-09-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L27" t="n">
+        <v>599</v>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>26</v>
+      </c>
+      <c r="B28" t="n">
+        <v>107702</v>
+      </c>
+      <c r="C28" t="n">
+        <v>376972</v>
+      </c>
+      <c r="D28" t="n">
+        <v>19132</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>JUAN HUMBERTO PULIDO SANDOVAL</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>SALTILLO VILLALTA</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>03-08-2026 9:16:37</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>03-09-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L28" t="n">
+        <v>799</v>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>27</v>
+      </c>
+      <c r="B29" t="n">
+        <v>107641</v>
+      </c>
+      <c r="C29" t="n">
+        <v>285430</v>
+      </c>
+      <c r="D29" t="n">
+        <v>82931</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>ALMA BELIA GARCIA LARA</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>SEND MXL</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>01-08-2026 12:58:24</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>01-09-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L29" t="n">
+        <v>599</v>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>28</v>
+      </c>
+      <c r="B30" t="n">
+        <v>107709</v>
+      </c>
+      <c r="C30" t="n">
+        <v>120176</v>
+      </c>
+      <c r="D30" t="n">
+        <v>17872</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>ROSARIO  HIDALGO  MENDEZ</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>SEND CHIH</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>03-08-2026 10:11:20</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>03-11-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L30" t="n">
+        <v>1449</v>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>29</v>
+      </c>
+      <c r="B31" t="n">
+        <v>105247</v>
+      </c>
+      <c r="C31" t="n">
+        <v>340206</v>
+      </c>
+      <c r="D31" t="n">
+        <v>18024</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>LIZETH GUADALUPE VALENZUELA  SOLANO</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>PABELLON RTO</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>02-07-2026 21:11:32</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>02-09-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L31" t="n">
+        <v>499</v>
+      </c>
+      <c r="M31" t="n">
+        <v>11</v>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>27-06-2027 21:11:32</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P31" t="n">
+        <v>104159</v>
+      </c>
+      <c r="Q31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>30</v>
+      </c>
+      <c r="B32" t="n">
+        <v>107687</v>
+      </c>
+      <c r="C32" t="n">
+        <v>186117</v>
+      </c>
+      <c r="D32" t="n">
+        <v>83624</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>OSCAR  GIL  ROMERO</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>VILLA VERDE</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>03-08-2026 8:07:03</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>03-09-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L32" t="n">
+        <v>999</v>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P32" t="n">
+        <v>48451</v>
+      </c>
+      <c r="Q32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>31</v>
+      </c>
+      <c r="B33" t="n">
+        <v>107708</v>
+      </c>
+      <c r="C33" t="n">
+        <v>376984</v>
+      </c>
+      <c r="D33" t="n">
+        <v>19144</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>ITZCRA ITZEL LOPEZ RODRIGUEZ</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>PASEO 2000</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>03-08-2026 10:11:04</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>03-09-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L33" t="n">
+        <v>599</v>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>32</v>
+      </c>
+      <c r="B34" t="n">
+        <v>105139</v>
+      </c>
+      <c r="C34" t="n">
+        <v>23556</v>
+      </c>
+      <c r="D34" t="n">
+        <v>22450</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>JESUS MONDRAGON  MURILLO</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>LOMA BONITA</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>02-07-2026 11:52:57</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>02-09-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L34" t="n">
+        <v>599</v>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P34" t="n">
+        <v>102870</v>
+      </c>
+      <c r="Q34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>33</v>
+      </c>
+      <c r="B35" t="n">
+        <v>107622</v>
+      </c>
+      <c r="C35" t="n">
+        <v>221245</v>
+      </c>
+      <c r="D35" t="n">
+        <v>18752</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>RICARDO ELIAS  MARTINEZ RUBIO</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>VILLA VERDE</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>31-07-2026 20:36:55</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>02-09-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I35" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L35" t="n">
+        <v>399</v>
+      </c>
+      <c r="M35" t="n">
+        <v>5</v>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>27-01-2027 20:36:55</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P35" t="n">
+        <v>49760</v>
+      </c>
+      <c r="Q35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>34</v>
+      </c>
+      <c r="B36" t="n">
+        <v>105968</v>
+      </c>
+      <c r="C36" t="n">
+        <v>164157</v>
+      </c>
+      <c r="D36" t="n">
+        <v>61690</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>BERTHA ALICIA GARCIA HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>SEND MXL</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>13-07-2026 18:05:03</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>01-09-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L36" t="n">
+        <v>499</v>
+      </c>
+      <c r="M36" t="n">
+        <v>11</v>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>08-07-2027 18:05:03</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P36" t="n">
+        <v>98409</v>
+      </c>
+      <c r="Q36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>35</v>
+      </c>
+      <c r="B37" t="n">
+        <v>107665</v>
+      </c>
+      <c r="C37" t="n">
+        <v>376914</v>
+      </c>
+      <c r="D37" t="n">
+        <v>19074</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>JORDAN HERUBIEL ARIAS APODACA</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>PAPALOTE TJ</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>02-08-2026 14:38:08</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>02-09-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L37" t="n">
+        <v>599</v>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>36</v>
+      </c>
+      <c r="B38" t="n">
+        <v>107699</v>
+      </c>
+      <c r="C38" t="n">
+        <v>376967</v>
+      </c>
+      <c r="D38" t="n">
+        <v>19127</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>ESTEBAN DE JESUS  ZAZUETA  VILLALOBOS</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>TEC MXL</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>03-08-2026 9:01:26</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>03-09-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I38" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L38" t="n">
+        <v>599</v>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr"/>
+      <c r="Q38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>37</v>
+      </c>
+      <c r="B39" t="n">
+        <v>107639</v>
+      </c>
+      <c r="C39" t="n">
+        <v>144840</v>
+      </c>
+      <c r="D39" t="n">
+        <v>42434</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>MARIA TERESA LOPEZ GARCIA</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>TEC MXL</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>01-08-2026 12:34:01</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>01-09-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I39" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L39" t="n">
+        <v>599</v>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>38</v>
+      </c>
+      <c r="B40" t="n">
+        <v>107657</v>
+      </c>
+      <c r="C40" t="n">
+        <v>376020</v>
+      </c>
+      <c r="D40" t="n">
+        <v>18180</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>SANTIAGO  RODRIGUEZ MORENO</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>INSURGENTES</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>02-08-2026 12:52:27</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>02-09-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I40" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L40" t="n">
+        <v>699</v>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr"/>
+      <c r="Q40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>39</v>
+      </c>
+      <c r="B41" t="n">
+        <v>107650</v>
+      </c>
+      <c r="C41" t="n">
+        <v>376877</v>
+      </c>
+      <c r="D41" t="n">
+        <v>19037</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>LIZBETH FIGUEROA VARELA</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>CARROUSEL TJ</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>02-08-2026 10:39:53</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>02-09-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I41" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L41" t="n">
+        <v>599</v>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr"/>
+      <c r="Q41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>40</v>
+      </c>
+      <c r="B42" t="n">
+        <v>107686</v>
+      </c>
+      <c r="C42" t="n">
+        <v>259557</v>
+      </c>
+      <c r="D42" t="n">
+        <v>57061</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>EVELIA DOLORES PALACIOS ZAZUETA</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>SEND MXL</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>03-08-2026 7:51:11</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>03-09-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I42" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L42" t="n">
+        <v>999</v>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P42" t="n">
+        <v>76418</v>
+      </c>
+      <c r="Q42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>41</v>
+      </c>
+      <c r="B43" t="n">
+        <v>105260</v>
+      </c>
+      <c r="C43" t="n">
+        <v>104164</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>01911</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>EDHER FERNANDO PERALTA MORALES</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>MISION ENS</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>03-07-2026 6:58:32</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>02-09-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L43" t="n">
+        <v>549</v>
+      </c>
+      <c r="M43" t="n">
+        <v>5</v>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>30-12-2026 6:58:32</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P43" t="n">
+        <v>68232</v>
+      </c>
+      <c r="Q43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>42</v>
+      </c>
+      <c r="B44" t="n">
+        <v>107658</v>
+      </c>
+      <c r="C44" t="n">
+        <v>376892</v>
+      </c>
+      <c r="D44" t="n">
+        <v>19052</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>MARIA DEL CARMEN  MORENO MARTINEZ</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>INSURGENTES</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>02-08-2026 12:57:55</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>02-09-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I44" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L44" t="n">
+        <v>699</v>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr"/>
+      <c r="Q44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>43</v>
+      </c>
+      <c r="B45" t="n">
+        <v>107677</v>
+      </c>
+      <c r="C45" t="n">
+        <v>376935</v>
+      </c>
+      <c r="D45" t="n">
+        <v>19095</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>ANAHI GUADALUPE  QUINTERO  GONZALEZ</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>SEND CUL</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>03-08-2026 6:25:49</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>03-09-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I45" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L45" t="n">
+        <v>599</v>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr"/>
+      <c r="Q45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>44</v>
+      </c>
+      <c r="B46" t="n">
+        <v>107711</v>
+      </c>
+      <c r="C46" t="n">
+        <v>376968</v>
+      </c>
+      <c r="D46" t="n">
+        <v>19128</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>SAMUEL IVAN  GARCIA  ROMERO</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>METEPEC</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>03-08-2026 10:24:56</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>04-09-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I46" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L46" t="n">
+        <v>649</v>
+      </c>
+      <c r="M46" t="n">
+        <v>11</v>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>29-07-2027 10:24:56</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr"/>
+      <c r="Q46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>45</v>
+      </c>
+      <c r="B47" t="n">
+        <v>107691</v>
+      </c>
+      <c r="C47" t="n">
+        <v>23392</v>
+      </c>
+      <c r="D47" t="n">
+        <v>22286</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>DANIEL IGNACIO LOPEZ LUGO</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>SEND MXL</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>03-08-2026 8:38:25</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>03-09-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I47" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L47" t="n">
+        <v>599</v>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr"/>
+      <c r="Q47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>46</v>
+      </c>
+      <c r="B48" t="n">
+        <v>107663</v>
+      </c>
+      <c r="C48" t="n">
+        <v>376909</v>
+      </c>
+      <c r="D48" t="n">
+        <v>19069</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>MARTHA CITLALIC JIMENEZ ESTRADA</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>PAPALOTE TJ</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>02-08-2026 14:27:28</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>02-09-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L48" t="n">
+        <v>599</v>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr"/>
+      <c r="Q48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>47</v>
+      </c>
+      <c r="B49" t="n">
+        <v>107674</v>
+      </c>
+      <c r="C49" t="n">
+        <v>228641</v>
+      </c>
+      <c r="D49" t="n">
+        <v>26146</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>SAMANTHA GUADALUPE  GUTIERREZ CORONADO</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>STA CATARINA</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>03-08-2026 6:08:27</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>03-09-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I49" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L49" t="n">
+        <v>599</v>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr"/>
+      <c r="Q49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>48</v>
+      </c>
+      <c r="B50" t="n">
+        <v>105274</v>
+      </c>
+      <c r="C50" t="n">
+        <v>347614</v>
+      </c>
+      <c r="D50" t="n">
+        <v>89779</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>KAREN ISABEL RAMIREZ SERRANO</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>PASEO 2000</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>03-07-2026 13:19:06</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>02-09-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L50" t="n">
+        <v>649</v>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P50" t="n">
+        <v>95495</v>
+      </c>
+      <c r="Q50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>49</v>
+      </c>
+      <c r="B51" t="n">
+        <v>106185</v>
+      </c>
+      <c r="C51" t="n">
+        <v>38715</v>
+      </c>
+      <c r="D51" t="n">
+        <v>36587</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>ELOINA  REYNOSO  TERRONES</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>SANTA FE</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>15-07-2026 15:30:47</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>02-09-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I51" t="n">
+        <v>0</v>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L51" t="n">
+        <v>399</v>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P51" t="n">
+        <v>99047</v>
+      </c>
+      <c r="Q51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>50</v>
+      </c>
+      <c r="B52" t="n">
+        <v>107671</v>
+      </c>
+      <c r="C52" t="n">
+        <v>110896</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>08633</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>MARIA ISABEL MATA MORALES</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>SEND CUL</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>03-08-2026 5:27:54</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>03-09-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I52" t="n">
+        <v>0</v>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L52" t="n">
+        <v>599</v>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr"/>
+      <c r="Q52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>51</v>
+      </c>
+      <c r="B53" t="n">
+        <v>107682</v>
+      </c>
+      <c r="C53" t="n">
+        <v>376942</v>
+      </c>
+      <c r="D53" t="n">
+        <v>19102</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>VALERIA MARISOL  MUÑIZ  CERDA</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>SEND SALTILLO</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>03-08-2026 7:08:59</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>03-09-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I53" t="n">
+        <v>0</v>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L53" t="n">
+        <v>549</v>
+      </c>
+      <c r="M53" t="n">
+        <v>11</v>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>29-07-2027 7:08:59</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr"/>
+      <c r="Q53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>52</v>
+      </c>
+      <c r="B54" t="n">
+        <v>107636</v>
+      </c>
+      <c r="C54" t="n">
+        <v>36616</v>
+      </c>
+      <c r="D54" t="n">
+        <v>34520</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>KEVYN URIAS SOTO</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>TEC MXL</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>01-08-2026 10:08:11</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>01-09-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I54" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L54" t="n">
+        <v>599</v>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr"/>
+      <c r="Q54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>53</v>
+      </c>
+      <c r="B55" t="n">
+        <v>107666</v>
+      </c>
+      <c r="C55" t="n">
+        <v>376915</v>
+      </c>
+      <c r="D55" t="n">
+        <v>19075</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>EVELIN KARINA  CISNEROS  MORALES</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>SALTILLO VILLALTA</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>02-08-2026 14:43:03</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>02-09-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I55" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L55" t="n">
+        <v>649</v>
+      </c>
+      <c r="M55" t="n">
+        <v>11</v>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>28-07-2027 14:43:03</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr"/>
+      <c r="Q55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>54</v>
+      </c>
+      <c r="B56" t="n">
+        <v>107670</v>
+      </c>
+      <c r="C56" t="n">
+        <v>189130</v>
+      </c>
+      <c r="D56" t="n">
+        <v>86637</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>NEREYDA  LEON  ROMERO</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>PASEO LA PAZ</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>03-08-2026 5:11:58</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>03-09-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I56" t="n">
+        <v>0</v>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L56" t="n">
+        <v>599</v>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr"/>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr"/>
+      <c r="Q56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>55</v>
+      </c>
+      <c r="B57" t="n">
+        <v>107528</v>
+      </c>
+      <c r="C57" t="n">
+        <v>154009</v>
+      </c>
+      <c r="D57" t="n">
+        <v>51565</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>AXEL LEONARDO BIBIANO GARCIA</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>VILLAS DEL REY</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>30-07-2026 21:22:02</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>03-09-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I57" t="n">
+        <v>0</v>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L57" t="n">
+        <v>449</v>
+      </c>
+      <c r="M57" t="n">
+        <v>5</v>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>26-01-2027 21:22:02</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P57" t="n">
+        <v>85202</v>
+      </c>
+      <c r="Q57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>56</v>
+      </c>
+      <c r="B58" t="n">
+        <v>107673</v>
+      </c>
+      <c r="C58" t="n">
+        <v>376929</v>
+      </c>
+      <c r="D58" t="n">
+        <v>19089</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>MAX ALEJANDRO RODRIGUEZ  OVALLE</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>SALTILLO VILLALTA</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>03-08-2026 5:51:20</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>03-09-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I58" t="n">
+        <v>0</v>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L58" t="n">
+        <v>649</v>
+      </c>
+      <c r="M58" t="n">
+        <v>11</v>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>29-07-2027 5:51:20</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr"/>
+      <c r="Q58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>57</v>
+      </c>
+      <c r="B59" t="n">
+        <v>107676</v>
+      </c>
+      <c r="C59" t="n">
+        <v>376934</v>
+      </c>
+      <c r="D59" t="n">
+        <v>19094</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>MARIA DE LOURES MEJIA SANCHEZ</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>PASEO 2000</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>03-08-2026 6:21:38</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>03-09-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I59" t="n">
+        <v>0</v>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L59" t="n">
+        <v>599</v>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr"/>
+      <c r="Q59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>58</v>
+      </c>
+      <c r="B60" t="n">
+        <v>107679</v>
+      </c>
+      <c r="C60" t="n">
+        <v>376937</v>
+      </c>
+      <c r="D60" t="n">
+        <v>19097</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>LILIANA CASAS  ESPINOSA</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>METEPEC</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>03-08-2026 6:39:41</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>03-09-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I60" t="n">
+        <v>0</v>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L60" t="n">
+        <v>549</v>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr"/>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr"/>
+      <c r="Q60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>59</v>
+      </c>
+      <c r="B61" t="n">
+        <v>107681</v>
+      </c>
+      <c r="C61" t="n">
+        <v>242779</v>
+      </c>
+      <c r="D61" t="n">
+        <v>40284</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>JUAN ANGEL  GALVAN  NAVARRO</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>STA CATARINA</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>03-08-2026 7:06:51</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>03-09-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I61" t="n">
+        <v>0</v>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L61" t="n">
+        <v>999</v>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr"/>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P61" t="n">
+        <v>43618</v>
+      </c>
+      <c r="Q61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>60</v>
+      </c>
+      <c r="B62" t="n">
+        <v>107706</v>
+      </c>
+      <c r="C62" t="n">
+        <v>183354</v>
+      </c>
+      <c r="D62" t="n">
+        <v>80861</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>DANIEL FRANCO MARQUEZ</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>TEC MXL</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>03-08-2026 9:53:05</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>03-09-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I62" t="n">
+        <v>0</v>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L62" t="n">
+        <v>599</v>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr"/>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr"/>
+      <c r="Q62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>61</v>
+      </c>
+      <c r="B63" t="n">
+        <v>107664</v>
+      </c>
+      <c r="C63" t="n">
+        <v>376911</v>
+      </c>
+      <c r="D63" t="n">
+        <v>19071</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>BRYAN HERNANDEZ VALLADAREZ</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>SANTA FE</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>02-08-2026 14:35:22</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>02-09-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I63" t="n">
+        <v>0</v>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L63" t="n">
+        <v>599</v>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr"/>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr"/>
+      <c r="Q63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>62</v>
+      </c>
+      <c r="B64" t="n">
+        <v>105360</v>
+      </c>
+      <c r="C64" t="n">
+        <v>108593</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>06334</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>LUCIA VALDES CARRANZA</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>SALTILLO VILLALTA</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>06-07-2026 8:44:49</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>02-09-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I64" t="n">
+        <v>0</v>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L64" t="n">
+        <v>649</v>
+      </c>
+      <c r="M64" t="n">
+        <v>11</v>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>01-07-2027 8:44:49</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P64" t="n">
+        <v>102847</v>
+      </c>
+      <c r="Q64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>63</v>
+      </c>
+      <c r="B65" t="n">
+        <v>107668</v>
+      </c>
+      <c r="C65" t="n">
+        <v>376922</v>
+      </c>
+      <c r="D65" t="n">
+        <v>19082</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>OLIVIER TOVAR  BARRAGAN</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>METEPEC</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>03-08-2026 4:28:20</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>03-09-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I65" t="n">
+        <v>0</v>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L65" t="n">
+        <v>799</v>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr"/>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr"/>
+      <c r="Q65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>64</v>
+      </c>
+      <c r="B66" t="n">
+        <v>107703</v>
+      </c>
+      <c r="C66" t="n">
+        <v>376974</v>
+      </c>
+      <c r="D66" t="n">
+        <v>19134</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>JORGE ANTONIO DE LA CRUZ   DOMINGUEZ</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>MISION ENS</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>03-08-2026 9:23:57</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>03-09-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I66" t="n">
+        <v>0</v>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L66" t="n">
+        <v>599</v>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr"/>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr"/>
+      <c r="Q66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>65</v>
+      </c>
+      <c r="B67" t="n">
+        <v>107683</v>
+      </c>
+      <c r="C67" t="n">
+        <v>376943</v>
+      </c>
+      <c r="D67" t="n">
+        <v>19103</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>MARIA ISABEL  SANCHEZ  RODRIGUEZ</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>TEC MXL</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>03-08-2026 7:13:11</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>03-09-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I67" t="n">
+        <v>0</v>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L67" t="n">
+        <v>599</v>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr"/>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr"/>
+      <c r="Q67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>66</v>
+      </c>
+      <c r="B68" t="n">
+        <v>105018</v>
+      </c>
+      <c r="C68" t="n">
+        <v>65078</v>
+      </c>
+      <c r="D68" t="n">
+        <v>62916</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>ALEJANDRO MAGALLAN  LOPEZ</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>SEND CUL</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>01-07-2026 7:04:56</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>01-09-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I68" t="n">
+        <v>0</v>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L68" t="n">
+        <v>350</v>
+      </c>
+      <c r="M68" t="n">
+        <v>5</v>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>28-12-2026 7:04:56</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P68" t="n">
+        <v>98454</v>
+      </c>
+      <c r="Q68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>67</v>
+      </c>
+      <c r="B69" t="n">
+        <v>107675</v>
+      </c>
+      <c r="C69" t="n">
+        <v>376933</v>
+      </c>
+      <c r="D69" t="n">
+        <v>19093</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>LIZBETH JIMENEZ MEJIA</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>PASEO 2000</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>03-08-2026 6:16:13</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>03-09-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I69" t="n">
+        <v>0</v>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L69" t="n">
+        <v>599</v>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr"/>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr"/>
+      <c r="Q69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>68</v>
+      </c>
+      <c r="B70" t="n">
+        <v>107630</v>
+      </c>
+      <c r="C70" t="n">
+        <v>337648</v>
+      </c>
+      <c r="D70" t="n">
+        <v>15467</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>CHRISTIAN RIVERA ZAVALETA</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>INSURGENTES</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>01-08-2026 8:29:26</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>01-09-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I70" t="n">
+        <v>0</v>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L70" t="n">
+        <v>699</v>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr"/>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr"/>
+      <c r="Q70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>69</v>
+      </c>
+      <c r="B71" t="n">
+        <v>107648</v>
+      </c>
+      <c r="C71" t="n">
+        <v>376876</v>
+      </c>
+      <c r="D71" t="n">
+        <v>19036</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>MEL ANGEL GUTIERREZ NEYOY</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>CARROUSEL TJ</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>02-08-2026 10:33:13</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>02-09-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I71" t="n">
+        <v>0</v>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L71" t="n">
+        <v>599</v>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr"/>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr"/>
+      <c r="Q71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>70</v>
+      </c>
+      <c r="B72" t="n">
+        <v>107655</v>
+      </c>
+      <c r="C72" t="n">
+        <v>264183</v>
+      </c>
+      <c r="D72" t="n">
+        <v>61687</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>ARTURO MOLINA ABREO</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>PASEO 2000</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>02-08-2026 12:17:56</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>30-08-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I72" t="n">
+        <v>0</v>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L72" t="n">
+        <v>449</v>
+      </c>
+      <c r="M72" t="n">
+        <v>11</v>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>28-07-2027 12:17:56</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P72" t="n">
+        <v>45596</v>
+      </c>
+      <c r="Q72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>71</v>
+      </c>
+      <c r="B73" t="n">
+        <v>107695</v>
+      </c>
+      <c r="C73" t="n">
+        <v>181088</v>
+      </c>
+      <c r="D73" t="n">
+        <v>78595</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>MARIA ENEDINAA ACEBO RODRIGUEZ</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>PASEO 2000</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>03-08-2026 8:46:08</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>03-09-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I73" t="n">
+        <v>0</v>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L73" t="n">
+        <v>599</v>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr"/>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr"/>
+      <c r="Q73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>72</v>
+      </c>
+      <c r="B74" t="n">
+        <v>105173</v>
+      </c>
+      <c r="C74" t="n">
+        <v>312176</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>09675</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>KEVIN MICHAEL GONZALEZ ALCANTAR</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>PASEO 2000</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>02-07-2026 15:58:26</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>01-09-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I74" t="n">
+        <v>0</v>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L74" t="n">
+        <v>549</v>
+      </c>
+      <c r="M74" t="n">
+        <v>5</v>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>29-12-2026 15:58:26</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P74" t="n">
+        <v>76876</v>
+      </c>
+      <c r="Q74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>73</v>
+      </c>
+      <c r="B75" t="n">
+        <v>107311</v>
+      </c>
+      <c r="C75" t="n">
+        <v>188976</v>
+      </c>
+      <c r="D75" t="n">
+        <v>86483</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>ANDREA MONTSERRATH GONZALEZ  AGUILAR</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>IXTAPALUCA</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>29-07-2026 7:56:03</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>03-09-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>0</v>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L75" t="n">
+        <v>449</v>
+      </c>
+      <c r="M75" t="n">
+        <v>5</v>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>25-01-2027 7:56:03</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P75" t="n">
+        <v>49603</v>
+      </c>
+      <c r="Q75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>74</v>
+      </c>
+      <c r="B76" t="n">
+        <v>107654</v>
+      </c>
+      <c r="C76" t="n">
+        <v>264184</v>
+      </c>
+      <c r="D76" t="n">
+        <v>61688</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>ISAAC  MOLINA ABREO</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>PASEO 2000</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>02-08-2026 12:13:53</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>30-08-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I76" t="n">
+        <v>0</v>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L76" t="n">
+        <v>449</v>
+      </c>
+      <c r="M76" t="n">
+        <v>11</v>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>28-07-2027 12:13:53</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P76" t="n">
+        <v>45597</v>
+      </c>
+      <c r="Q76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>75</v>
+      </c>
+      <c r="B77" t="n">
+        <v>107638</v>
+      </c>
+      <c r="C77" t="n">
+        <v>376843</v>
+      </c>
+      <c r="D77" t="n">
+        <v>19003</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>LIZBETH GUADALUPE ARROYO  DIAZ</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>SEND SALTILLO</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>01-08-2026 12:28:10</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>01-09-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I77" t="n">
+        <v>0</v>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L77" t="n">
+        <v>549</v>
+      </c>
+      <c r="M77" t="n">
+        <v>11</v>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>27-07-2027 12:28:10</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr"/>
+      <c r="Q77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>76</v>
+      </c>
+      <c r="B78" t="n">
+        <v>107632</v>
+      </c>
+      <c r="C78" t="n">
+        <v>376819</v>
+      </c>
+      <c r="D78" t="n">
+        <v>18979</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>GUILLERMINA  CELIS  ARENAS</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>IXTAPALUCA</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>01-08-2026 9:46:41</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>01-09-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I78" t="n">
+        <v>0</v>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L78" t="n">
+        <v>599</v>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr"/>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr"/>
+      <c r="Q78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>77</v>
+      </c>
+      <c r="B79" t="n">
+        <v>107689</v>
+      </c>
+      <c r="C79" t="n">
+        <v>376954</v>
+      </c>
+      <c r="D79" t="n">
+        <v>19114</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>JORGE EDUARDO DIAZ YAÑEZ</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>PASEO LA PAZ</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>03-08-2026 8:13:28</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>03-09-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I79" t="n">
+        <v>0</v>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L79" t="n">
+        <v>649</v>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr"/>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr"/>
+      <c r="Q79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>78</v>
+      </c>
+      <c r="B80" t="n">
+        <v>107707</v>
+      </c>
+      <c r="C80" t="n">
+        <v>376980</v>
+      </c>
+      <c r="D80" t="n">
+        <v>19140</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>EDITH NAVARRETE SANCHEZ</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>SAN LUIS</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>03-08-2026 10:09:15</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>03-09-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I80" t="n">
+        <v>0</v>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L80" t="n">
+        <v>549</v>
+      </c>
+      <c r="M80" t="n">
+        <v>11</v>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>29-07-2027 10:09:15</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr"/>
+      <c r="Q80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>79</v>
+      </c>
+      <c r="B81" t="n">
+        <v>107667</v>
+      </c>
+      <c r="C81" t="n">
+        <v>376916</v>
+      </c>
+      <c r="D81" t="n">
+        <v>19076</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>ALEXA DANAHI  CISNEROS  MORALES</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>SALTILLO VILLALTA</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>02-08-2026 14:49:22</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>02-09-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I81" t="n">
+        <v>0</v>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L81" t="n">
+        <v>649</v>
+      </c>
+      <c r="M81" t="n">
+        <v>11</v>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>28-07-2027 14:49:22</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr"/>
+      <c r="Q81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>80</v>
+      </c>
+      <c r="B82" t="n">
+        <v>107685</v>
+      </c>
+      <c r="C82" t="n">
+        <v>376947</v>
+      </c>
+      <c r="D82" t="n">
+        <v>19107</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>BRENDA LIZETH SALGADO ESPINOBARROS</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>PASEO 2000</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>03-08-2026 7:43:15</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>03-09-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I82" t="n">
+        <v>0</v>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L82" t="n">
+        <v>599</v>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr"/>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr"/>
+      <c r="Q82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>81</v>
+      </c>
+      <c r="B83" t="n">
+        <v>105143</v>
+      </c>
+      <c r="C83" t="n">
+        <v>307187</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>04686</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>MARIA GLORIA  SARABIA  CORONA</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>TEC MXL</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>02-07-2026 12:18:21</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>01-09-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I83" t="n">
+        <v>0</v>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L83" t="n">
+        <v>399</v>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr"/>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P83" t="n">
+        <v>73904</v>
+      </c>
+      <c r="Q83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>82</v>
+      </c>
+      <c r="B84" t="n">
+        <v>107694</v>
+      </c>
+      <c r="C84" t="n">
+        <v>376963</v>
+      </c>
+      <c r="D84" t="n">
+        <v>19123</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>MARIA DE JESUS CASILLAS TORRES</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>SANTA FE</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>03-08-2026 8:43:23</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>03-09-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I84" t="n">
+        <v>0</v>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L84" t="n">
+        <v>599</v>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr"/>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr"/>
+      <c r="Q84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>83</v>
+      </c>
+      <c r="B85" t="n">
+        <v>107555</v>
+      </c>
+      <c r="C85" t="n">
+        <v>6276</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>05213</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>GERARDO HURTADO  BARON</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>MISION ENS</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>31-07-2026 10:23:25</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>01-09-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I85" t="n">
+        <v>0</v>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L85" t="n">
+        <v>399</v>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr"/>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P85" t="n">
+        <v>28862</v>
+      </c>
+      <c r="Q85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>84</v>
+      </c>
+      <c r="B86" t="n">
+        <v>107698</v>
+      </c>
+      <c r="C86" t="n">
+        <v>366074</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>08234</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>VALERIA TORRES  LOPEZ</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>SALTILLO VILLALTA</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>03-08-2026 8:59:50</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>03-09-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I86" t="n">
+        <v>0</v>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L86" t="n">
+        <v>799</v>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr"/>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P86" t="inlineStr"/>
+      <c r="Q86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>85</v>
+      </c>
+      <c r="B87" t="n">
+        <v>107644</v>
+      </c>
+      <c r="C87" t="n">
+        <v>165704</v>
+      </c>
+      <c r="D87" t="n">
+        <v>63237</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>ESTEBAN ENRIQUE CALOCA  GOMEZ</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>CARROUSEL TJ</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>01-08-2026 15:29:54</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>01-09-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I87" t="n">
+        <v>0</v>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L87" t="n">
+        <v>999</v>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr"/>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P87" t="n">
+        <v>51618</v>
+      </c>
+      <c r="Q87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>86</v>
+      </c>
+      <c r="B88" t="n">
+        <v>105425</v>
+      </c>
+      <c r="C88" t="n">
+        <v>286072</v>
+      </c>
+      <c r="D88" t="n">
+        <v>83572</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>MARIEL ARIANA BARRAZA ARCE</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>TEC MXL</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>06-07-2026 18:05:56</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>01-09-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I88" t="n">
+        <v>0</v>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L88" t="n">
+        <v>499</v>
+      </c>
+      <c r="M88" t="n">
+        <v>11</v>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>01-07-2027 18:05:56</t>
+        </is>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P88" t="n">
+        <v>105424</v>
+      </c>
+      <c r="Q88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>87</v>
+      </c>
+      <c r="B89" t="n">
+        <v>107640</v>
+      </c>
+      <c r="C89" t="n">
+        <v>144848</v>
+      </c>
+      <c r="D89" t="n">
+        <v>42442</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>SARAHI  LOPEZ GARCIA</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>TEC MXL</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>01-08-2026 12:38:22</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>01-09-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I89" t="n">
+        <v>0</v>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L89" t="n">
+        <v>599</v>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr"/>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P89" t="inlineStr"/>
+      <c r="Q89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>88</v>
+      </c>
+      <c r="B90" t="n">
+        <v>105109</v>
+      </c>
+      <c r="C90" t="n">
+        <v>366026</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>08186</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>ERIK SALDAÑA  SANCHEZ</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>STA CATARINA</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>02-07-2026 4:23:57</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>01-09-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I90" t="n">
+        <v>0</v>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L90" t="n">
+        <v>499</v>
+      </c>
+      <c r="M90" t="n">
+        <v>5</v>
+      </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>29-12-2026 4:23:57</t>
+        </is>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P90" t="n">
+        <v>102797</v>
+      </c>
+      <c r="Q90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>89</v>
+      </c>
+      <c r="B91" t="n">
+        <v>107182</v>
+      </c>
+      <c r="C91" t="n">
+        <v>253901</v>
+      </c>
+      <c r="D91" t="n">
+        <v>51405</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>ABISAHI ANDRES MEZA MIRAMONTES</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>PASEO LA PAZ</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>28-07-2026 11:55:40</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>28-08-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I91" t="n">
+        <v>0</v>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L91" t="n">
+        <v>599</v>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr"/>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P91" t="inlineStr"/>
+      <c r="Q91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>90</v>
+      </c>
+      <c r="B92" t="n">
+        <v>107653</v>
+      </c>
+      <c r="C92" t="n">
+        <v>376882</v>
+      </c>
+      <c r="D92" t="n">
+        <v>19042</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>ARELI  ORTIZ  RIVERA</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>VILLAS DEL REY</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>02-08-2026 11:52:17</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>02-09-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I92" t="n">
+        <v>0</v>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L92" t="n">
+        <v>599</v>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr"/>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P92" t="inlineStr"/>
+      <c r="Q92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>91</v>
+      </c>
+      <c r="B93" t="n">
+        <v>105805</v>
+      </c>
+      <c r="C93" t="n">
+        <v>35200</v>
+      </c>
+      <c r="D93" t="n">
+        <v>33114</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>DIEGO DELGADO GARCIA</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>SAN LUIS</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>10-07-2026 16:55:11</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>02-09-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I93" t="n">
+        <v>0</v>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L93" t="n">
+        <v>599</v>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr"/>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P93" t="n">
+        <v>105159</v>
+      </c>
+      <c r="Q93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>92</v>
+      </c>
+      <c r="B94" t="n">
+        <v>107692</v>
+      </c>
+      <c r="C94" t="n">
+        <v>58378</v>
+      </c>
+      <c r="D94" t="n">
+        <v>56222</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>VANESSA ITZEL  MURGUIA  MELCHOR</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>SAN ISIDRO CUL</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>03-08-2026 8:39:24</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>03-09-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I94" t="n">
+        <v>0</v>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L94" t="n">
+        <v>599</v>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr"/>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P94" t="inlineStr"/>
+      <c r="Q94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>93</v>
+      </c>
+      <c r="B95" t="n">
+        <v>107662</v>
+      </c>
+      <c r="C95" t="n">
+        <v>376907</v>
+      </c>
+      <c r="D95" t="n">
+        <v>19067</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>ORLANDO  CERVANTES LEYVA</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>SEND CUL</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>02-08-2026 14:22:59</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>02-09-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I95" t="n">
+        <v>0</v>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L95" t="n">
+        <v>549</v>
+      </c>
+      <c r="M95" t="n">
+        <v>11</v>
+      </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>28-07-2027 14:22:59</t>
+        </is>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P95" t="inlineStr"/>
+      <c r="Q95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>94</v>
+      </c>
+      <c r="B96" t="n">
+        <v>107680</v>
+      </c>
+      <c r="C96" t="n">
+        <v>122794</v>
+      </c>
+      <c r="D96" t="n">
+        <v>20481</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>SAUL OSBALDO ORPINEDA CORRALES</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>VILLA VERDE</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>03-08-2026 6:51:00</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>03-09-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I96" t="n">
+        <v>0</v>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L96" t="n">
+        <v>599</v>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr"/>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P96" t="inlineStr"/>
+      <c r="Q96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>95</v>
+      </c>
+      <c r="B97" t="n">
+        <v>107647</v>
+      </c>
+      <c r="C97" t="n">
+        <v>376874</v>
+      </c>
+      <c r="D97" t="n">
+        <v>19034</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>JORGE ALBERTO FIGUEROA VARELA</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>CARROUSEL TJ</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>02-08-2026 10:26:37</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>02-09-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I97" t="n">
+        <v>0</v>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L97" t="n">
+        <v>599</v>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr"/>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P97" t="inlineStr"/>
+      <c r="Q97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>96</v>
+      </c>
+      <c r="B98" t="n">
+        <v>107656</v>
+      </c>
+      <c r="C98" t="n">
+        <v>216131</v>
+      </c>
+      <c r="D98" t="n">
+        <v>13639</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>LUIS ANGEL  OLMOS  GUTIERREZ</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>SEND CHIH</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>02-08-2026 12:50:37</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>02-09-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I98" t="n">
+        <v>0</v>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L98" t="n">
+        <v>599</v>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr"/>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P98" t="inlineStr"/>
+      <c r="Q98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>97</v>
+      </c>
+      <c r="B99" t="n">
+        <v>106661</v>
+      </c>
+      <c r="C99" t="n">
+        <v>44470</v>
+      </c>
+      <c r="D99" t="n">
+        <v>42333</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>JAVIER FRUTERO LOPEZ</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>SANTA FE</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>21-07-2026 18:13:58</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>02-09-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I99" t="n">
+        <v>0</v>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L99" t="n">
+        <v>599</v>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr"/>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P99" t="n">
+        <v>86654</v>
+      </c>
+      <c r="Q99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Reporte generado: 03-08-2026 05:51 p. m.</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr"/>
+      <c r="C100" t="inlineStr"/>
+      <c r="D100" t="inlineStr"/>
+      <c r="E100" t="inlineStr"/>
+      <c r="F100" t="inlineStr"/>
+      <c r="G100" t="inlineStr"/>
+      <c r="H100" t="inlineStr"/>
+      <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" t="inlineStr"/>
+      <c r="N100" t="inlineStr"/>
+      <c r="O100" t="inlineStr"/>
+      <c r="P100" t="inlineStr"/>
+      <c r="Q100" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/descargas/cargos_recurrentes.xlsx
+++ b/data/descargas/cargos_recurrentes.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q3"/>
+  <dimension ref="A1:Q35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -599,27 +599,2085 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Reporte generado: 01-09-2026 12:38 p. m.</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="n">
+        <v>109994</v>
+      </c>
+      <c r="C3" t="n">
+        <v>259111</v>
+      </c>
+      <c r="D3" t="n">
+        <v>56615</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>GIBRAN CONTRERAS DE LEON</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>STA CATARINA</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>01-09-2026 5:49:04</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>01-10-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>549</v>
+      </c>
+      <c r="M3" t="n">
+        <v>11</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>27-08-2027 5:49:04</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="n">
+        <v>109996</v>
+      </c>
+      <c r="C4" t="n">
+        <v>148921</v>
+      </c>
+      <c r="D4" t="n">
+        <v>46493</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>APOLONIA  RUIZ  GONZALEZ</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>SEND CUL</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>01-09-2026 6:09:11</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>01-10-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>649</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="n">
+        <v>109998</v>
+      </c>
+      <c r="C5" t="n">
+        <v>166282</v>
+      </c>
+      <c r="D5" t="n">
+        <v>63815</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>ERVIC YAHIR  SANCHEZ  INZUNZA</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>AZAHARES CUL</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>01-09-2026 6:45:32</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>01-10-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>649</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="n">
+        <v>110000</v>
+      </c>
+      <c r="C6" t="n">
+        <v>382151</v>
+      </c>
+      <c r="D6" t="n">
+        <v>24308</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>MARISA CARMINA  GALINDO MARTIN DEL CAMPO</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>TLALNEPANTLA</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>01-09-2026 7:26:03</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>01-10-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>649</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" t="n">
+        <v>107660</v>
+      </c>
+      <c r="C7" t="n">
+        <v>169016</v>
+      </c>
+      <c r="D7" t="n">
+        <v>66535</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>JIRONOVO  MONTOYA CASTRO</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>SEND CUL</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>02-08-2026 13:11:01</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>01-10-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>399</v>
+      </c>
+      <c r="M7" t="n">
+        <v>11</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>28-07-2027 13:11:01</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>79256</v>
+      </c>
+      <c r="Q7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" t="n">
+        <v>110024</v>
+      </c>
+      <c r="C8" t="n">
+        <v>382180</v>
+      </c>
+      <c r="D8" t="n">
+        <v>24337</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>CLAUDIA IVETTE ARAIZA PEREZ</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>PAPALOTE TJ</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>01-09-2026 10:26:18</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>01-10-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>999</v>
+      </c>
+      <c r="M8" t="n">
+        <v>11</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>27-08-2027 10:26:18</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" t="n">
+        <v>110005</v>
+      </c>
+      <c r="C9" t="n">
+        <v>325222</v>
+      </c>
+      <c r="D9" t="n">
+        <v>22161</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>JOSE GUSTAVO  CONTRERAS  ARGUMEDO</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>SEND MXL</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>01-09-2026 8:18:39</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>01-10-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>649</v>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" t="n">
+        <v>110020</v>
+      </c>
+      <c r="C10" t="n">
+        <v>382177</v>
+      </c>
+      <c r="D10" t="n">
+        <v>24334</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>BIANKA MORENO TREVIÑO</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>SERRANIA</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>01-09-2026 10:03:53</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>01-10-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>849</v>
+      </c>
+      <c r="M10" t="n">
+        <v>11</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>27-08-2027 10:03:53</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" t="n">
+        <v>109997</v>
+      </c>
+      <c r="C11" t="n">
+        <v>381033</v>
+      </c>
+      <c r="D11" t="n">
+        <v>23191</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>LUIS ERNESTO SALS REZA</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>INDEPENDENCIA</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>01-09-2026 6:10:30</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>01-10-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>649</v>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" t="n">
+        <v>110011</v>
+      </c>
+      <c r="C12" t="n">
+        <v>382171</v>
+      </c>
+      <c r="D12" t="n">
+        <v>24328</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>JAVIER ALFONSO RUIZ  TORRES</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>MISION ENS</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>01-09-2026 9:17:59</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>01-10-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>649</v>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" t="n">
+        <v>110013</v>
+      </c>
+      <c r="C13" t="n">
+        <v>381700</v>
+      </c>
+      <c r="D13" t="n">
+        <v>23858</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>MARIBEL BELTRAN PACHECO</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>VILLAS DEL REY</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>01-09-2026 9:35:39</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>01-10-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>549</v>
+      </c>
+      <c r="M13" t="n">
+        <v>11</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>27-08-2027 9:35:39</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" t="n">
+        <v>110022</v>
+      </c>
+      <c r="C14" t="n">
+        <v>382186</v>
+      </c>
+      <c r="D14" t="n">
+        <v>24343</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>GLORIA VALLE HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>CARROUSEL TJ</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>01-09-2026 10:21:36</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>01-10-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
+        <v>649</v>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" t="n">
+        <v>110010</v>
+      </c>
+      <c r="C15" t="n">
+        <v>28593</v>
+      </c>
+      <c r="D15" t="n">
+        <v>26524</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>IMELDA NANCY  GARCIA  TAVERA</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>SANTA FE</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>01-09-2026 9:17:17</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>01-10-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L15" t="n">
+        <v>649</v>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" t="n">
+        <v>110026</v>
+      </c>
+      <c r="C16" t="n">
+        <v>382188</v>
+      </c>
+      <c r="D16" t="n">
+        <v>24345</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>MAYRA LILIANA RIVERA OROZCO</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>SEND MXL</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>01-09-2026 10:34:08</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>01-10-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L16" t="n">
+        <v>649</v>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" t="n">
+        <v>108762</v>
+      </c>
+      <c r="C17" t="n">
+        <v>273408</v>
+      </c>
+      <c r="D17" t="n">
+        <v>70910</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>BLANCA ESTELA SOTELO DE LA CRUZ</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>IXTAPALUCA</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>17-08-2026 13:36:19</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>01-10-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L17" t="n">
+        <v>599</v>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>102719</v>
+      </c>
+      <c r="Q17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" t="n">
+        <v>110012</v>
+      </c>
+      <c r="C18" t="n">
+        <v>303209</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>00708</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>JOEL  QUINTERO  CEBALLOS</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>SAN ISIDRO CUL</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>01-09-2026 9:30:46</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>01-10-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L18" t="n">
+        <v>549</v>
+      </c>
+      <c r="M18" t="n">
+        <v>11</v>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>27-08-2027 9:30:46</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" t="n">
+        <v>110002</v>
+      </c>
+      <c r="C19" t="n">
+        <v>382154</v>
+      </c>
+      <c r="D19" t="n">
+        <v>24311</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>LUIS ENRIQUE  ZARATE  VARGAS</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>METEPEC</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>01-09-2026 7:52:04</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>01-12-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L19" t="n">
+        <v>1549</v>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" t="n">
+        <v>110008</v>
+      </c>
+      <c r="C20" t="n">
+        <v>167604</v>
+      </c>
+      <c r="D20" t="n">
+        <v>65137</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>ITZEL GUADALUPE SALAZAR VELAZQUEZ</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>SEND MXL</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>01-09-2026 8:43:21</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>01-10-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L20" t="n">
+        <v>649</v>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" t="n">
+        <v>107780</v>
+      </c>
+      <c r="C21" t="n">
+        <v>179187</v>
+      </c>
+      <c r="D21" t="n">
+        <v>76694</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>IVAN RAFAEL CASAS QUIÑONES</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>SEND MXL</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>03-08-2026 17:40:59</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>01-10-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L21" t="n">
+        <v>599</v>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P21" t="n">
+        <v>105044</v>
+      </c>
+      <c r="Q21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" t="n">
+        <v>109999</v>
+      </c>
+      <c r="C22" t="n">
+        <v>382150</v>
+      </c>
+      <c r="D22" t="n">
+        <v>24307</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>RODRIGO FIGUEROA MIGUEL</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>TLALNEPANTLA</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>01-09-2026 7:19:08</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>01-10-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L22" t="n">
+        <v>649</v>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" t="n">
+        <v>108037</v>
+      </c>
+      <c r="C23" t="n">
+        <v>32030</v>
+      </c>
+      <c r="D23" t="n">
+        <v>29953</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>ERIKA ALEJANDRA  VALVERDE PRIETO</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>SANTA FE</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>05-08-2026 21:19:04</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>01-10-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L23" t="n">
+        <v>399</v>
+      </c>
+      <c r="M23" t="n">
+        <v>11</v>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>31-07-2027 21:19:04</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P23" t="n">
+        <v>59590</v>
+      </c>
+      <c r="Q23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>22</v>
+      </c>
+      <c r="B24" t="n">
+        <v>110025</v>
+      </c>
+      <c r="C24" t="n">
+        <v>382187</v>
+      </c>
+      <c r="D24" t="n">
+        <v>24344</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>CARLOS ALBERTO MARTINEZ  DIPP</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>SEND MXL</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>01-09-2026 10:30:23</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>01-10-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L24" t="n">
+        <v>649</v>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>23</v>
+      </c>
+      <c r="B25" t="n">
+        <v>110004</v>
+      </c>
+      <c r="C25" t="n">
+        <v>251678</v>
+      </c>
+      <c r="D25" t="n">
+        <v>49182</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>MIGUEL ANGEL CARVAJAL GOMEZ</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>STA CATARINA</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>01-09-2026 8:06:40</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>01-10-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L25" t="n">
+        <v>649</v>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>24</v>
+      </c>
+      <c r="B26" t="n">
+        <v>110001</v>
+      </c>
+      <c r="C26" t="n">
+        <v>327378</v>
+      </c>
+      <c r="D26" t="n">
+        <v>24315</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>MARIO ENRIQUE RAMÍREZ MONTIEL</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>METEPEC</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>01-09-2026 7:46:34</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>01-10-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L26" t="n">
+        <v>999</v>
+      </c>
+      <c r="M26" t="n">
+        <v>11</v>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>27-08-2027 7:46:34</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P26" t="n">
+        <v>94313</v>
+      </c>
+      <c r="Q26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>25</v>
+      </c>
+      <c r="B27" t="n">
+        <v>110014</v>
+      </c>
+      <c r="C27" t="n">
+        <v>382176</v>
+      </c>
+      <c r="D27" t="n">
+        <v>24333</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>DANIEL DE JESUS PEREZ PEREZ</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>PASEO 2000</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>01-09-2026 9:44:23</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>01-10-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L27" t="n">
+        <v>649</v>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>26</v>
+      </c>
+      <c r="B28" t="n">
+        <v>110018</v>
+      </c>
+      <c r="C28" t="n">
+        <v>382178</v>
+      </c>
+      <c r="D28" t="n">
+        <v>24335</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>RITA STEPHANIE  GONZALEZ GUTIERREZ</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>VILLAS DEL REY</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>01-09-2026 10:00:35</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>01-10-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L28" t="n">
+        <v>649</v>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>27</v>
+      </c>
+      <c r="B29" t="n">
+        <v>110003</v>
+      </c>
+      <c r="C29" t="n">
+        <v>375807</v>
+      </c>
+      <c r="D29" t="n">
+        <v>17967</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>ALFREDO  MORALES RIVERA</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>CARROUSEL TJ</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>01-09-2026 8:05:44</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>01-10-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L29" t="n">
+        <v>549</v>
+      </c>
+      <c r="M29" t="n">
+        <v>11</v>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>27-08-2027 8:05:44</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>28</v>
+      </c>
+      <c r="B30" t="n">
+        <v>110007</v>
+      </c>
+      <c r="C30" t="n">
+        <v>135417</v>
+      </c>
+      <c r="D30" t="n">
+        <v>33065</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>MARTIN JONATHAN  HERNANDEZ  MARQUEZ</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>SEND CHIH</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>01-09-2026 8:33:37</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>01-10-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L30" t="n">
+        <v>649</v>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>29</v>
+      </c>
+      <c r="B31" t="n">
+        <v>110017</v>
+      </c>
+      <c r="C31" t="n">
+        <v>362784</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>04944</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>DANIELA LUCELY LLAMAS VARGAS</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>PASEO 2000</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>01-09-2026 10:00:20</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>01-10-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L31" t="n">
+        <v>649</v>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>30</v>
+      </c>
+      <c r="B32" t="n">
+        <v>110023</v>
+      </c>
+      <c r="C32" t="n">
+        <v>382185</v>
+      </c>
+      <c r="D32" t="n">
+        <v>24342</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>ALEXIS  ALEJANDRO MEJIA</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>PASEO 2000</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>01-09-2026 10:21:50</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>01-10-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L32" t="n">
+        <v>649</v>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>31</v>
+      </c>
+      <c r="B33" t="n">
+        <v>108151</v>
+      </c>
+      <c r="C33" t="n">
+        <v>282587</v>
+      </c>
+      <c r="D33" t="n">
+        <v>80088</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>MARIA DE JESUS PEREZ VAZQUEZ</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>MISION ENS</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>08-08-2026 6:25:08</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>01-10-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Activado</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L33" t="n">
+        <v>549</v>
+      </c>
+      <c r="M33" t="n">
+        <v>11</v>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>03-08-2027 6:25:08</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P33" t="n">
+        <v>102654</v>
+      </c>
+      <c r="Q33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>32</v>
+      </c>
+      <c r="B34" t="n">
+        <v>109589</v>
+      </c>
+      <c r="C34" t="n">
+        <v>9525</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>08454</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>MARIA DE LOS ANGELES CRUZ LARA</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>CARROUSEL TJ</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>28-08-2026 9:13:09</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>01-10-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L34" t="n">
+        <v>499</v>
+      </c>
+      <c r="M34" t="n">
+        <v>11</v>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>23-08-2027 9:13:09</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P34" t="n">
+        <v>90245</v>
+      </c>
+      <c r="Q34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Reporte generado: 01-09-2026 06:14 p. m.</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr"/>
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/descargas/cargos_recurrentes.xlsx
+++ b/data/descargas/cargos_recurrentes.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q35"/>
+  <dimension ref="A1:Q118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -603,32 +603,32 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>109994</v>
+        <v>110091</v>
       </c>
       <c r="C3" t="n">
-        <v>259111</v>
+        <v>382402</v>
       </c>
       <c r="D3" t="n">
-        <v>56615</v>
+        <v>24559</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>GIBRAN CONTRERAS DE LEON</t>
+          <t>GUADALUPE ZUÑIGA RAMIREZ</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>STA CATARINA</t>
+          <t>TLALNEPANTLA</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>01-09-2026 5:49:04</t>
+          <t>02-09-2026 7:25:50</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>01-10-2026 23:59:59</t>
+          <t>02-10-2026 23:59:59</t>
         </is>
       </c>
       <c r="I3" t="n">
@@ -652,7 +652,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>27-08-2027 5:49:04</t>
+          <t>28-08-2027 7:25:50</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -668,27 +668,27 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>109996</v>
+        <v>110051</v>
       </c>
       <c r="C4" t="n">
-        <v>148921</v>
+        <v>382261</v>
       </c>
       <c r="D4" t="n">
-        <v>46493</v>
+        <v>24418</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>APOLONIA  RUIZ  GONZALEZ</t>
+          <t>OSCAR RONALDO PUGA ESQUIVEL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>SEND CUL</t>
+          <t>SERRANIA</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>01-09-2026 6:09:11</t>
+          <t>01-09-2026 16:31:26</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -710,7 +710,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>649</v>
+        <v>949</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -731,32 +731,32 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>109998</v>
+        <v>110098</v>
       </c>
       <c r="C5" t="n">
-        <v>166282</v>
+        <v>382416</v>
       </c>
       <c r="D5" t="n">
-        <v>63815</v>
+        <v>24573</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>ERVIC YAHIR  SANCHEZ  INZUNZA</t>
+          <t>OSCAR HUMBERTO LOPEZ MUÑOZ</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>AZAHARES CUL</t>
+          <t>SERRANIA</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>01-09-2026 6:45:32</t>
+          <t>02-09-2026 10:11:19</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>01-10-2026 23:59:59</t>
+          <t>02-10-2026 23:59:59</t>
         </is>
       </c>
       <c r="I5" t="n">
@@ -773,17 +773,19 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>649</v>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>Indefinido</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
+        <v>849</v>
+      </c>
+      <c r="M5" t="n">
+        <v>11</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>28-08-2027 10:11:19</t>
+        </is>
+      </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Recurrente</t>
+          <t>Domiciliado</t>
         </is>
       </c>
       <c r="P5" t="inlineStr"/>
@@ -794,27 +796,27 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>110000</v>
+        <v>110020</v>
       </c>
       <c r="C6" t="n">
-        <v>382151</v>
+        <v>382177</v>
       </c>
       <c r="D6" t="n">
-        <v>24308</v>
+        <v>24334</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>MARISA CARMINA  GALINDO MARTIN DEL CAMPO</t>
+          <t>BIANKA MORENO TREVIÑO</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>TLALNEPANTLA</t>
+          <t>SERRANIA</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>01-09-2026 7:26:03</t>
+          <t>01-09-2026 10:03:53</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -836,17 +838,19 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>649</v>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>Indefinido</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
+        <v>849</v>
+      </c>
+      <c r="M6" t="n">
+        <v>11</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>27-08-2027 10:03:53</t>
+        </is>
+      </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Recurrente</t>
+          <t>Domiciliado</t>
         </is>
       </c>
       <c r="P6" t="inlineStr"/>
@@ -857,27 +861,27 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>107660</v>
+        <v>110038</v>
       </c>
       <c r="C7" t="n">
-        <v>169016</v>
+        <v>382223</v>
       </c>
       <c r="D7" t="n">
-        <v>66535</v>
+        <v>24380</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>JIRONOVO  MONTOYA CASTRO</t>
+          <t>VANIA RENATA BERZOZA TREVIÑO</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>SEND CUL</t>
+          <t>SERRANIA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>02-08-2026 13:11:01</t>
+          <t>01-09-2026 14:20:49</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -895,18 +899,18 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>RENOVACIÓN</t>
+          <t>NUEVO</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>399</v>
+        <v>849</v>
       </c>
       <c r="M7" t="n">
         <v>11</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>28-07-2027 13:11:01</t>
+          <t>27-08-2027 14:20:49</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -914,9 +918,7 @@
           <t>Domiciliado</t>
         </is>
       </c>
-      <c r="P7" t="n">
-        <v>79256</v>
-      </c>
+      <c r="P7" t="inlineStr"/>
       <c r="Q7" t="inlineStr"/>
     </row>
     <row r="8">
@@ -924,27 +926,27 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>110024</v>
+        <v>110052</v>
       </c>
       <c r="C8" t="n">
-        <v>382180</v>
+        <v>382265</v>
       </c>
       <c r="D8" t="n">
-        <v>24337</v>
+        <v>24422</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>CLAUDIA IVETTE ARAIZA PEREZ</t>
+          <t>JUAN JOSE CANTUA MORENO</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>PAPALOTE TJ</t>
+          <t>VILLA VERDE</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>01-09-2026 10:26:18</t>
+          <t>01-09-2026 16:40:47</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -966,19 +968,17 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>999</v>
-      </c>
-      <c r="M8" t="n">
-        <v>11</v>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>27-08-2027 10:26:18</t>
-        </is>
-      </c>
+        <v>649</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Domiciliado</t>
+          <t>Recurrente</t>
         </is>
       </c>
       <c r="P8" t="inlineStr"/>
@@ -989,32 +989,34 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>110005</v>
+        <v>107921</v>
       </c>
       <c r="C9" t="n">
-        <v>325222</v>
-      </c>
-      <c r="D9" t="n">
-        <v>22161</v>
+        <v>364918</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>07078</t>
+        </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>JOSE GUSTAVO  CONTRERAS  ARGUMEDO</t>
+          <t>RUBEN ANTONIO ALVAREZ GARZA</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>SEND MXL</t>
+          <t>SALTILLO VILLALTA</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>01-09-2026 8:18:39</t>
+          <t>04-08-2026 16:02:10</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>01-10-2026 23:59:59</t>
+          <t>25-09-2026 23:59:59</t>
         </is>
       </c>
       <c r="I9" t="n">
@@ -1027,24 +1029,28 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>NUEVO</t>
+          <t>RENOVACIÓN</t>
         </is>
       </c>
       <c r="L9" t="n">
         <v>649</v>
       </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>Indefinido</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
+      <c r="M9" t="n">
+        <v>11</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>30-07-2027 16:02:10</t>
+        </is>
+      </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Recurrente</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr"/>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
+        <v>102214</v>
+      </c>
       <c r="Q9" t="inlineStr"/>
     </row>
     <row r="10">
@@ -1052,27 +1058,27 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>110020</v>
+        <v>109997</v>
       </c>
       <c r="C10" t="n">
-        <v>382177</v>
+        <v>381033</v>
       </c>
       <c r="D10" t="n">
-        <v>24334</v>
+        <v>23191</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>BIANKA MORENO TREVIÑO</t>
+          <t>LUIS ERNESTO SALS REZA</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>SERRANIA</t>
+          <t>INDEPENDENCIA</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>01-09-2026 10:03:53</t>
+          <t>01-09-2026 6:10:30</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1094,19 +1100,17 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>849</v>
-      </c>
-      <c r="M10" t="n">
-        <v>11</v>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>27-08-2027 10:03:53</t>
-        </is>
-      </c>
+        <v>649</v>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Domiciliado</t>
+          <t>Recurrente</t>
         </is>
       </c>
       <c r="P10" t="inlineStr"/>
@@ -1117,27 +1121,27 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>109997</v>
+        <v>110011</v>
       </c>
       <c r="C11" t="n">
-        <v>381033</v>
+        <v>382171</v>
       </c>
       <c r="D11" t="n">
-        <v>23191</v>
+        <v>24328</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>LUIS ERNESTO SALS REZA</t>
+          <t>JAVIER ALFONSO RUIZ  TORRES</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>INDEPENDENCIA</t>
+          <t>MISION ENS</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>01-09-2026 6:10:30</t>
+          <t>01-09-2026 9:17:59</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1180,27 +1184,27 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>110011</v>
+        <v>110086</v>
       </c>
       <c r="C12" t="n">
-        <v>382171</v>
+        <v>382383</v>
       </c>
       <c r="D12" t="n">
-        <v>24328</v>
+        <v>24540</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>JAVIER ALFONSO RUIZ  TORRES</t>
+          <t>ANDRES ISRAEL  QUIÑONES  MEJIA</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>MISION ENS</t>
+          <t>SEND MXL</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>01-09-2026 9:17:59</t>
+          <t>01-09-2026 20:36:03</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1222,17 +1226,19 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>649</v>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>Indefinido</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
+        <v>549</v>
+      </c>
+      <c r="M12" t="n">
+        <v>11</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>27-08-2027 20:36:03</t>
+        </is>
+      </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Recurrente</t>
+          <t>Domiciliado</t>
         </is>
       </c>
       <c r="P12" t="inlineStr"/>
@@ -1243,27 +1249,29 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>110013</v>
+        <v>110050</v>
       </c>
       <c r="C13" t="n">
-        <v>381700</v>
-      </c>
-      <c r="D13" t="n">
-        <v>23858</v>
+        <v>8220</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>07154</t>
+        </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>MARIBEL BELTRAN PACHECO</t>
+          <t>MANUEL ALEXIS VALLE SANTIBAÑEZ</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>VILLAS DEL REY</t>
+          <t>SEND MXL</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>01-09-2026 9:35:39</t>
+          <t>01-09-2026 16:30:24</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1292,7 +1300,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>27-08-2027 9:35:39</t>
+          <t>27-08-2027 16:30:24</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1308,32 +1316,32 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>110022</v>
+        <v>110099</v>
       </c>
       <c r="C14" t="n">
-        <v>382186</v>
+        <v>382417</v>
       </c>
       <c r="D14" t="n">
-        <v>24343</v>
+        <v>24574</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>GLORIA VALLE HERNANDEZ</t>
+          <t>JOAN ARMANDO GARCIA  CAMACHO</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>CARROUSEL TJ</t>
+          <t>PASEO 2000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>01-09-2026 10:21:36</t>
+          <t>02-09-2026 10:17:56</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>01-10-2026 23:59:59</t>
+          <t>02-10-2026 23:59:59</t>
         </is>
       </c>
       <c r="I14" t="n">
@@ -1371,32 +1379,32 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>110010</v>
+        <v>110089</v>
       </c>
       <c r="C15" t="n">
-        <v>28593</v>
+        <v>376878</v>
       </c>
       <c r="D15" t="n">
-        <v>26524</v>
+        <v>19038</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>IMELDA NANCY  GARCIA  TAVERA</t>
+          <t>MARTA ELISA ASENCIO PEREZ</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>SANTA FE</t>
+          <t>SEND SALTILLO</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>01-09-2026 9:17:17</t>
+          <t>02-09-2026 7:14:02</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>01-10-2026 23:59:59</t>
+          <t>02-10-2026 23:59:59</t>
         </is>
       </c>
       <c r="I15" t="n">
@@ -1434,27 +1442,29 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>110026</v>
+        <v>110012</v>
       </c>
       <c r="C16" t="n">
-        <v>382188</v>
-      </c>
-      <c r="D16" t="n">
-        <v>24345</v>
+        <v>303209</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>00708</t>
+        </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>MAYRA LILIANA RIVERA OROZCO</t>
+          <t>JOEL  QUINTERO  CEBALLOS</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>SEND MXL</t>
+          <t>SAN ISIDRO CUL</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>01-09-2026 10:34:08</t>
+          <t>01-09-2026 9:30:46</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1476,17 +1486,19 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>649</v>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>Indefinido</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
+        <v>549</v>
+      </c>
+      <c r="M16" t="n">
+        <v>11</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>27-08-2027 9:30:46</t>
+        </is>
+      </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Recurrente</t>
+          <t>Domiciliado</t>
         </is>
       </c>
       <c r="P16" t="inlineStr"/>
@@ -1497,27 +1509,27 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>108762</v>
+        <v>110035</v>
       </c>
       <c r="C17" t="n">
-        <v>273408</v>
+        <v>382214</v>
       </c>
       <c r="D17" t="n">
-        <v>70910</v>
+        <v>24371</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>BLANCA ESTELA SOTELO DE LA CRUZ</t>
+          <t>VIVIANA  BARRIENTOS ESPINOZA</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>IXTAPALUCA</t>
+          <t>PASEO 2000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>17-08-2026 13:36:19</t>
+          <t>01-09-2026 13:41:56</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1535,11 +1547,11 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>RENOVACIÓN</t>
+          <t>NUEVO</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>599</v>
+        <v>649</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -1552,9 +1564,7 @@
           <t>Recurrente</t>
         </is>
       </c>
-      <c r="P17" t="n">
-        <v>102719</v>
-      </c>
+      <c r="P17" t="inlineStr"/>
       <c r="Q17" t="inlineStr"/>
     </row>
     <row r="18">
@@ -1562,19 +1572,17 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>110012</v>
+        <v>110092</v>
       </c>
       <c r="C18" t="n">
-        <v>303209</v>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>00708</t>
-        </is>
+        <v>215373</v>
+      </c>
+      <c r="D18" t="n">
+        <v>12881</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>JOEL  QUINTERO  CEBALLOS</t>
+          <t>ANA PAULA ALCALA CARDENAS</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1584,12 +1592,12 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>01-09-2026 9:30:46</t>
+          <t>02-09-2026 7:58:04</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>01-10-2026 23:59:59</t>
+          <t>02-10-2026 23:59:59</t>
         </is>
       </c>
       <c r="I18" t="n">
@@ -1606,19 +1614,17 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>549</v>
-      </c>
-      <c r="M18" t="n">
-        <v>11</v>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>27-08-2027 9:30:46</t>
-        </is>
-      </c>
+        <v>649</v>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Domiciliado</t>
+          <t>Recurrente</t>
         </is>
       </c>
       <c r="P18" t="inlineStr"/>
@@ -1629,32 +1635,32 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>110002</v>
+        <v>108762</v>
       </c>
       <c r="C19" t="n">
-        <v>382154</v>
+        <v>273408</v>
       </c>
       <c r="D19" t="n">
-        <v>24311</v>
+        <v>70910</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>LUIS ENRIQUE  ZARATE  VARGAS</t>
+          <t>BLANCA ESTELA SOTELO DE LA CRUZ</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>METEPEC</t>
+          <t>IXTAPALUCA</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>01-09-2026 7:52:04</t>
+          <t>17-08-2026 13:36:19</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>01-12-2026 23:59:59</t>
+          <t>01-10-2026 23:59:59</t>
         </is>
       </c>
       <c r="I19" t="n">
@@ -1667,11 +1673,11 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>NUEVO</t>
+          <t>RENOVACIÓN</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1549</v>
+        <v>599</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -1684,7 +1690,9 @@
           <t>Recurrente</t>
         </is>
       </c>
-      <c r="P19" t="inlineStr"/>
+      <c r="P19" t="n">
+        <v>102719</v>
+      </c>
       <c r="Q19" t="inlineStr"/>
     </row>
     <row r="20">
@@ -1692,32 +1700,32 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>110008</v>
+        <v>108062</v>
       </c>
       <c r="C20" t="n">
-        <v>167604</v>
+        <v>347583</v>
       </c>
       <c r="D20" t="n">
-        <v>65137</v>
+        <v>89748</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>ITZEL GUADALUPE SALAZAR VELAZQUEZ</t>
+          <t>JUAN SALVADOR PEREZ CASTRO</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>SEND MXL</t>
+          <t>INSURGENTES</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>01-09-2026 8:43:21</t>
+          <t>06-08-2026 12:41:08</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>01-10-2026 23:59:59</t>
+          <t>02-10-2026 23:59:59</t>
         </is>
       </c>
       <c r="I20" t="n">
@@ -1730,24 +1738,28 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>NUEVO</t>
+          <t>RENOVACIÓN</t>
         </is>
       </c>
       <c r="L20" t="n">
         <v>649</v>
       </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>Indefinido</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
+      <c r="M20" t="n">
+        <v>11</v>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>01-08-2027 12:41:08</t>
+        </is>
+      </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Recurrente</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr"/>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P20" t="n">
+        <v>95486</v>
+      </c>
       <c r="Q20" t="inlineStr"/>
     </row>
     <row r="21">
@@ -1755,27 +1767,27 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>107780</v>
+        <v>110063</v>
       </c>
       <c r="C21" t="n">
-        <v>179187</v>
+        <v>191605</v>
       </c>
       <c r="D21" t="n">
-        <v>76694</v>
+        <v>89112</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>IVAN RAFAEL CASAS QUIÑONES</t>
+          <t>GISEL BUELNA ROJO</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>SEND MXL</t>
+          <t>CARROUSEL TJ</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>03-08-2026 17:40:59</t>
+          <t>01-09-2026 17:56:03</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1793,11 +1805,11 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>RENOVACIÓN</t>
+          <t>NUEVO</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>599</v>
+        <v>649</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
@@ -1810,9 +1822,7 @@
           <t>Recurrente</t>
         </is>
       </c>
-      <c r="P21" t="n">
-        <v>105044</v>
-      </c>
+      <c r="P21" t="inlineStr"/>
       <c r="Q21" t="inlineStr"/>
     </row>
     <row r="22">
@@ -1820,32 +1830,32 @@
         <v>20</v>
       </c>
       <c r="B22" t="n">
-        <v>109999</v>
+        <v>108875</v>
       </c>
       <c r="C22" t="n">
-        <v>382150</v>
+        <v>145772</v>
       </c>
       <c r="D22" t="n">
-        <v>24307</v>
+        <v>43358</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RODRIGO FIGUEROA MIGUEL</t>
+          <t>GABRIELA LETICIA CRUZ JOHNSON</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>TLALNEPANTLA</t>
+          <t>TEC MXL</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>01-09-2026 7:19:08</t>
+          <t>17-08-2026 20:34:08</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>01-10-2026 23:59:59</t>
+          <t>20-09-2026 23:59:59</t>
         </is>
       </c>
       <c r="I22" t="n">
@@ -1853,16 +1863,16 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Sin filtro</t>
+          <t>Activado</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>NUEVO</t>
+          <t>CANCELADO</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>649</v>
+        <v>599</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
@@ -1875,7 +1885,9 @@
           <t>Recurrente</t>
         </is>
       </c>
-      <c r="P22" t="inlineStr"/>
+      <c r="P22" t="n">
+        <v>106471</v>
+      </c>
       <c r="Q22" t="inlineStr"/>
     </row>
     <row r="23">
@@ -1883,27 +1895,27 @@
         <v>21</v>
       </c>
       <c r="B23" t="n">
-        <v>108037</v>
+        <v>110072</v>
       </c>
       <c r="C23" t="n">
-        <v>32030</v>
+        <v>382318</v>
       </c>
       <c r="D23" t="n">
-        <v>29953</v>
+        <v>24475</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>ERIKA ALEJANDRA  VALVERDE PRIETO</t>
+          <t>BRENDA  MARTINEZ CRUZ</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>SANTA FE</t>
+          <t>TLALNEPANTLA</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>05-08-2026 21:19:04</t>
+          <t>01-09-2026 18:41:26</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1921,28 +1933,24 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>RENOVACIÓN</t>
+          <t>NUEVO</t>
         </is>
       </c>
       <c r="L23" t="n">
-        <v>399</v>
-      </c>
-      <c r="M23" t="n">
-        <v>11</v>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>31-07-2027 21:19:04</t>
-        </is>
-      </c>
+        <v>649</v>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Domiciliado</t>
-        </is>
-      </c>
-      <c r="P23" t="n">
-        <v>59590</v>
-      </c>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr"/>
       <c r="Q23" t="inlineStr"/>
     </row>
     <row r="24">
@@ -1950,32 +1958,32 @@
         <v>22</v>
       </c>
       <c r="B24" t="n">
-        <v>110025</v>
+        <v>110097</v>
       </c>
       <c r="C24" t="n">
-        <v>382187</v>
+        <v>381644</v>
       </c>
       <c r="D24" t="n">
-        <v>24344</v>
+        <v>23802</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>CARLOS ALBERTO MARTINEZ  DIPP</t>
+          <t>HECTOR EDUARDO ESTRADA GUTIERREZ</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>SEND MXL</t>
+          <t>SEND SALTILLO</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>01-09-2026 10:30:23</t>
+          <t>02-09-2026 9:24:05</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>01-10-2026 23:59:59</t>
+          <t>02-10-2026 23:59:59</t>
         </is>
       </c>
       <c r="I24" t="n">
@@ -1992,17 +2000,19 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>649</v>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>Indefinido</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
+        <v>549</v>
+      </c>
+      <c r="M24" t="n">
+        <v>11</v>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>28-08-2027 9:24:05</t>
+        </is>
+      </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>Recurrente</t>
+          <t>Domiciliado</t>
         </is>
       </c>
       <c r="P24" t="inlineStr"/>
@@ -2013,27 +2023,27 @@
         <v>23</v>
       </c>
       <c r="B25" t="n">
-        <v>110004</v>
+        <v>110010</v>
       </c>
       <c r="C25" t="n">
-        <v>251678</v>
+        <v>28593</v>
       </c>
       <c r="D25" t="n">
-        <v>49182</v>
+        <v>26524</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>MIGUEL ANGEL CARVAJAL GOMEZ</t>
+          <t>IMELDA NANCY  GARCIA  TAVERA</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>STA CATARINA</t>
+          <t>SANTA FE</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>01-09-2026 8:06:40</t>
+          <t>01-09-2026 9:17:17</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2076,27 +2086,27 @@
         <v>24</v>
       </c>
       <c r="B26" t="n">
-        <v>110001</v>
+        <v>110032</v>
       </c>
       <c r="C26" t="n">
-        <v>327378</v>
+        <v>382207</v>
       </c>
       <c r="D26" t="n">
-        <v>24315</v>
+        <v>24364</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>MARIO ENRIQUE RAMÍREZ MONTIEL</t>
+          <t>NIXSIA YANELI RODRIGUEZ ROMERO</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>METEPEC</t>
+          <t>PASEO 2000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>01-09-2026 7:46:34</t>
+          <t>01-09-2026 13:00:36</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2114,28 +2124,24 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>RENOVACIÓN</t>
+          <t>NUEVO</t>
         </is>
       </c>
       <c r="L26" t="n">
-        <v>999</v>
-      </c>
-      <c r="M26" t="n">
-        <v>11</v>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>27-08-2027 7:46:34</t>
-        </is>
-      </c>
+        <v>649</v>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr">
         <is>
-          <t>Domiciliado</t>
-        </is>
-      </c>
-      <c r="P26" t="n">
-        <v>94313</v>
-      </c>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr"/>
       <c r="Q26" t="inlineStr"/>
     </row>
     <row r="27">
@@ -2143,27 +2149,27 @@
         <v>25</v>
       </c>
       <c r="B27" t="n">
-        <v>110014</v>
+        <v>110085</v>
       </c>
       <c r="C27" t="n">
-        <v>382176</v>
+        <v>382369</v>
       </c>
       <c r="D27" t="n">
-        <v>24333</v>
+        <v>24526</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>DANIEL DE JESUS PEREZ PEREZ</t>
+          <t>ALFREDO ESQUIVEL LEDESMA</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>PASEO 2000</t>
+          <t>SANTA FE</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>01-09-2026 9:44:23</t>
+          <t>01-09-2026 20:09:58</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2185,17 +2191,19 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>649</v>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>Indefinido</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
+        <v>549</v>
+      </c>
+      <c r="M27" t="n">
+        <v>11</v>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>27-08-2027 20:09:58</t>
+        </is>
+      </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>Recurrente</t>
+          <t>Domiciliado</t>
         </is>
       </c>
       <c r="P27" t="inlineStr"/>
@@ -2206,17 +2214,17 @@
         <v>26</v>
       </c>
       <c r="B28" t="n">
-        <v>110018</v>
+        <v>110013</v>
       </c>
       <c r="C28" t="n">
-        <v>382178</v>
+        <v>381700</v>
       </c>
       <c r="D28" t="n">
-        <v>24335</v>
+        <v>23858</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RITA STEPHANIE  GONZALEZ GUTIERREZ</t>
+          <t>MARIBEL BELTRAN PACHECO</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -2226,7 +2234,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>01-09-2026 10:00:35</t>
+          <t>01-09-2026 9:35:39</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2248,17 +2256,19 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>649</v>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>Indefinido</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
+        <v>549</v>
+      </c>
+      <c r="M28" t="n">
+        <v>11</v>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>27-08-2027 9:35:39</t>
+        </is>
+      </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>Recurrente</t>
+          <t>Domiciliado</t>
         </is>
       </c>
       <c r="P28" t="inlineStr"/>
@@ -2269,17 +2279,17 @@
         <v>27</v>
       </c>
       <c r="B29" t="n">
-        <v>110003</v>
+        <v>110022</v>
       </c>
       <c r="C29" t="n">
-        <v>375807</v>
+        <v>382186</v>
       </c>
       <c r="D29" t="n">
-        <v>17967</v>
+        <v>24343</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>ALFREDO  MORALES RIVERA</t>
+          <t>GLORIA VALLE HERNANDEZ</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -2289,7 +2299,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>01-09-2026 8:05:44</t>
+          <t>01-09-2026 10:21:36</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2311,19 +2321,17 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>549</v>
-      </c>
-      <c r="M29" t="n">
-        <v>11</v>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>27-08-2027 8:05:44</t>
-        </is>
-      </c>
+        <v>649</v>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="O29" t="inlineStr">
         <is>
-          <t>Domiciliado</t>
+          <t>Recurrente</t>
         </is>
       </c>
       <c r="P29" t="inlineStr"/>
@@ -2334,27 +2342,27 @@
         <v>28</v>
       </c>
       <c r="B30" t="n">
-        <v>110007</v>
+        <v>110054</v>
       </c>
       <c r="C30" t="n">
-        <v>135417</v>
+        <v>201649</v>
       </c>
       <c r="D30" t="n">
-        <v>33065</v>
+        <v>99156</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>MARTIN JONATHAN  HERNANDEZ  MARQUEZ</t>
+          <t>HECTOR  PEREZ MEZA</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>SEND CHIH</t>
+          <t>VILLAS DEL REY</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>01-09-2026 8:33:37</t>
+          <t>01-09-2026 17:07:20</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2397,29 +2405,27 @@
         <v>29</v>
       </c>
       <c r="B31" t="n">
-        <v>110017</v>
+        <v>110033</v>
       </c>
       <c r="C31" t="n">
-        <v>362784</v>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>04944</t>
-        </is>
+        <v>21928</v>
+      </c>
+      <c r="D31" t="n">
+        <v>20826</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>DANIELA LUCELY LLAMAS VARGAS</t>
+          <t>DORA JACQUELINE GARCIA GARCIA</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>PASEO 2000</t>
+          <t>PABELLON RTO</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>01-09-2026 10:00:20</t>
+          <t>01-09-2026 13:08:47</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2437,11 +2443,11 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>NUEVO</t>
+          <t>RENOVACIÓN</t>
         </is>
       </c>
       <c r="L31" t="n">
-        <v>649</v>
+        <v>999</v>
       </c>
       <c r="M31" t="inlineStr">
         <is>
@@ -2454,7 +2460,9 @@
           <t>Recurrente</t>
         </is>
       </c>
-      <c r="P31" t="inlineStr"/>
+      <c r="P31" t="n">
+        <v>41545</v>
+      </c>
       <c r="Q31" t="inlineStr"/>
     </row>
     <row r="32">
@@ -2462,27 +2470,27 @@
         <v>30</v>
       </c>
       <c r="B32" t="n">
-        <v>110023</v>
+        <v>110026</v>
       </c>
       <c r="C32" t="n">
-        <v>382185</v>
+        <v>382188</v>
       </c>
       <c r="D32" t="n">
-        <v>24342</v>
+        <v>24345</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>ALEXIS  ALEJANDRO MEJIA</t>
+          <t>MAYRA LILIANA RIVERA OROZCO</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>PASEO 2000</t>
+          <t>SEND MXL</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>01-09-2026 10:21:50</t>
+          <t>01-09-2026 10:34:08</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2525,27 +2533,27 @@
         <v>31</v>
       </c>
       <c r="B33" t="n">
-        <v>108151</v>
+        <v>110039</v>
       </c>
       <c r="C33" t="n">
-        <v>282587</v>
+        <v>382224</v>
       </c>
       <c r="D33" t="n">
-        <v>80088</v>
+        <v>24381</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>MARIA DE JESUS PEREZ VAZQUEZ</t>
+          <t>ADRIAN OSWALDO GARZA CABELLO</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>MISION ENS</t>
+          <t>SERRANIA</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>08-08-2026 6:25:08</t>
+          <t>01-09-2026 14:27:04</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2558,23 +2566,23 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Activado</t>
+          <t>Sin filtro</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>RENOVACIÓN</t>
+          <t>NUEVO</t>
         </is>
       </c>
       <c r="L33" t="n">
-        <v>549</v>
+        <v>849</v>
       </c>
       <c r="M33" t="n">
         <v>11</v>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>03-08-2027 6:25:08</t>
+          <t>27-08-2027 14:27:04</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
@@ -2582,9 +2590,7 @@
           <t>Domiciliado</t>
         </is>
       </c>
-      <c r="P33" t="n">
-        <v>102654</v>
-      </c>
+      <c r="P33" t="inlineStr"/>
       <c r="Q33" t="inlineStr"/>
     </row>
     <row r="34">
@@ -2592,92 +2598,5429 @@
         <v>32</v>
       </c>
       <c r="B34" t="n">
+        <v>110069</v>
+      </c>
+      <c r="C34" t="n">
+        <v>382311</v>
+      </c>
+      <c r="D34" t="n">
+        <v>24468</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>EDIHT CASTILLO POBLETE</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>CARROUSEL TJ</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>01-09-2026 18:08:35</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>01-10-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L34" t="n">
+        <v>649</v>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>33</v>
+      </c>
+      <c r="B35" t="n">
+        <v>108170</v>
+      </c>
+      <c r="C35" t="n">
+        <v>340252</v>
+      </c>
+      <c r="D35" t="n">
+        <v>18070</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>SUSANA  BLANCAS  ESTRELLA</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>METEPEC</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>09-08-2026 13:10:27</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>02-10-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I35" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L35" t="n">
+        <v>649</v>
+      </c>
+      <c r="M35" t="n">
+        <v>11</v>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>04-08-2027 13:10:27</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P35" t="n">
+        <v>91459</v>
+      </c>
+      <c r="Q35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>34</v>
+      </c>
+      <c r="B36" t="n">
+        <v>110049</v>
+      </c>
+      <c r="C36" t="n">
+        <v>41038</v>
+      </c>
+      <c r="D36" t="n">
+        <v>38908</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>TERESITA DE JESUS LOZOYA HERREARA</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>CARROUSEL TJ</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>01-09-2026 16:18:54</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>01-10-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L36" t="n">
+        <v>649</v>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>35</v>
+      </c>
+      <c r="B37" t="n">
+        <v>108877</v>
+      </c>
+      <c r="C37" t="n">
+        <v>374526</v>
+      </c>
+      <c r="D37" t="n">
+        <v>16686</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>ANGEL GABRIEL CRUZ JOHNSON</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>TEC MXL</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>17-08-2026 20:36:47</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>20-09-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Activado</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L37" t="n">
+        <v>599</v>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P37" t="n">
+        <v>106476</v>
+      </c>
+      <c r="Q37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>36</v>
+      </c>
+      <c r="B38" t="n">
+        <v>110002</v>
+      </c>
+      <c r="C38" t="n">
+        <v>382154</v>
+      </c>
+      <c r="D38" t="n">
+        <v>24311</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>LUIS ENRIQUE  ZARATE  VARGAS</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>METEPEC</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>01-09-2026 7:52:04</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>01-12-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I38" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L38" t="n">
+        <v>1549</v>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr"/>
+      <c r="Q38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>37</v>
+      </c>
+      <c r="B39" t="n">
+        <v>110070</v>
+      </c>
+      <c r="C39" t="n">
+        <v>382313</v>
+      </c>
+      <c r="D39" t="n">
+        <v>24470</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>LIZBETH XIMENA LARA RUIZ</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>SEND CUL</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>01-09-2026 18:14:16</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>01-10-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I39" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L39" t="n">
+        <v>649</v>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>38</v>
+      </c>
+      <c r="B40" t="n">
+        <v>110088</v>
+      </c>
+      <c r="C40" t="n">
+        <v>73852</v>
+      </c>
+      <c r="D40" t="n">
+        <v>71668</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>EVA DEYANIRA GAMEZ AGUILAR</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>STA CATARINA</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>02-09-2026 7:12:05</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>02-10-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I40" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L40" t="n">
+        <v>999</v>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P40" t="n">
+        <v>43416</v>
+      </c>
+      <c r="Q40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>39</v>
+      </c>
+      <c r="B41" t="n">
+        <v>110095</v>
+      </c>
+      <c r="C41" t="n">
+        <v>220766</v>
+      </c>
+      <c r="D41" t="n">
+        <v>18273</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>JOSE MIGUEL JIMENEZ MUÑOZ</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>MISION ENS</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>02-09-2026 8:43:08</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>02-10-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I41" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L41" t="n">
+        <v>649</v>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr"/>
+      <c r="Q41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>40</v>
+      </c>
+      <c r="B42" t="n">
+        <v>110102</v>
+      </c>
+      <c r="C42" t="n">
+        <v>245782</v>
+      </c>
+      <c r="D42" t="n">
+        <v>43287</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>CAROL ANET  RUIZ  CAÑEDO</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>PASEO 2000</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>02-09-2026 11:08:26</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>02-10-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I42" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L42" t="n">
+        <v>649</v>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr"/>
+      <c r="Q42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>41</v>
+      </c>
+      <c r="B43" t="n">
+        <v>110029</v>
+      </c>
+      <c r="C43" t="n">
+        <v>382202</v>
+      </c>
+      <c r="D43" t="n">
+        <v>24359</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>FRANCINELLY RODRIGUEZ  LOPEZ</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>SEND SALTILLO</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>01-09-2026 12:13:24</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>01-10-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L43" t="n">
+        <v>549</v>
+      </c>
+      <c r="M43" t="n">
+        <v>11</v>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>27-08-2027 12:13:24</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr"/>
+      <c r="Q43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>42</v>
+      </c>
+      <c r="B44" t="n">
+        <v>110008</v>
+      </c>
+      <c r="C44" t="n">
+        <v>167604</v>
+      </c>
+      <c r="D44" t="n">
+        <v>65137</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>ITZEL GUADALUPE SALAZAR VELAZQUEZ</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>SEND MXL</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>01-09-2026 8:43:21</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>01-10-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I44" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L44" t="n">
+        <v>649</v>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr"/>
+      <c r="Q44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>43</v>
+      </c>
+      <c r="B45" t="n">
+        <v>110093</v>
+      </c>
+      <c r="C45" t="n">
+        <v>34894</v>
+      </c>
+      <c r="D45" t="n">
+        <v>32808</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>LAISHA KARIME LOPEZ RAMIREZ</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>LOMA BONITA</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>02-09-2026 7:59:08</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>02-10-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I45" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L45" t="n">
+        <v>499</v>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr"/>
+      <c r="Q45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>44</v>
+      </c>
+      <c r="B46" t="n">
+        <v>110005</v>
+      </c>
+      <c r="C46" t="n">
+        <v>325222</v>
+      </c>
+      <c r="D46" t="n">
+        <v>22161</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>JOSE GUSTAVO  CONTRERAS  ARGUMEDO</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>SEND MXL</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>01-09-2026 8:18:39</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>01-10-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I46" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L46" t="n">
+        <v>649</v>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr"/>
+      <c r="Q46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>45</v>
+      </c>
+      <c r="B47" t="n">
+        <v>110105</v>
+      </c>
+      <c r="C47" t="n">
+        <v>340153</v>
+      </c>
+      <c r="D47" t="n">
+        <v>17971</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>FRANCO VLADIMIR MERINO VALDEZ</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>SALTILLO VILLALTA</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>02-09-2026 11:28:58</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>02-10-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I47" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L47" t="n">
+        <v>549</v>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr"/>
+      <c r="Q47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>46</v>
+      </c>
+      <c r="B48" t="n">
+        <v>109994</v>
+      </c>
+      <c r="C48" t="n">
+        <v>259111</v>
+      </c>
+      <c r="D48" t="n">
+        <v>56615</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>GIBRAN CONTRERAS DE LEON</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>STA CATARINA</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>01-09-2026 5:49:04</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>01-10-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L48" t="n">
+        <v>549</v>
+      </c>
+      <c r="M48" t="n">
+        <v>11</v>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>27-08-2027 5:49:04</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr"/>
+      <c r="Q48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>47</v>
+      </c>
+      <c r="B49" t="n">
+        <v>109996</v>
+      </c>
+      <c r="C49" t="n">
+        <v>148921</v>
+      </c>
+      <c r="D49" t="n">
+        <v>46493</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>APOLONIA  RUIZ  GONZALEZ</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>SEND CUL</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>01-09-2026 6:09:11</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>01-10-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I49" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L49" t="n">
+        <v>649</v>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr"/>
+      <c r="Q49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>48</v>
+      </c>
+      <c r="B50" t="n">
+        <v>110053</v>
+      </c>
+      <c r="C50" t="n">
+        <v>382270</v>
+      </c>
+      <c r="D50" t="n">
+        <v>24427</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>MARIA TERESA LATAPI MARTINEZ</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>SALTILLO VILLALTA</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>01-09-2026 16:58:45</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>01-10-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L50" t="n">
+        <v>649</v>
+      </c>
+      <c r="M50" t="n">
+        <v>11</v>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>27-08-2027 16:58:45</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr"/>
+      <c r="Q50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>49</v>
+      </c>
+      <c r="B51" t="n">
+        <v>110024</v>
+      </c>
+      <c r="C51" t="n">
+        <v>382180</v>
+      </c>
+      <c r="D51" t="n">
+        <v>24337</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>CLAUDIA IVETTE ARAIZA PEREZ</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>PAPALOTE TJ</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>01-09-2026 10:26:18</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>01-10-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I51" t="n">
+        <v>0</v>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L51" t="n">
+        <v>999</v>
+      </c>
+      <c r="M51" t="n">
+        <v>11</v>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>27-08-2027 10:26:18</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr"/>
+      <c r="Q51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>50</v>
+      </c>
+      <c r="B52" t="n">
+        <v>110041</v>
+      </c>
+      <c r="C52" t="n">
+        <v>382231</v>
+      </c>
+      <c r="D52" t="n">
+        <v>24388</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>JORGE JESUS  ROCHA  SOTO</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>TEC MXL</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>01-09-2026 14:59:05</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>01-10-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I52" t="n">
+        <v>0</v>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L52" t="n">
+        <v>999</v>
+      </c>
+      <c r="M52" t="n">
+        <v>11</v>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>27-08-2027 14:59:05</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr"/>
+      <c r="Q52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>51</v>
+      </c>
+      <c r="B53" t="n">
+        <v>110073</v>
+      </c>
+      <c r="C53" t="n">
+        <v>382316</v>
+      </c>
+      <c r="D53" t="n">
+        <v>24473</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>FERNANDO MIGUEL VIDAL AGUIÑIGA</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>INSURGENTES</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>01-09-2026 18:47:14</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>01-10-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I53" t="n">
+        <v>0</v>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L53" t="n">
+        <v>749</v>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr"/>
+      <c r="Q53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>52</v>
+      </c>
+      <c r="B54" t="n">
+        <v>107660</v>
+      </c>
+      <c r="C54" t="n">
+        <v>169016</v>
+      </c>
+      <c r="D54" t="n">
+        <v>66535</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>JIRONOVO  MONTOYA CASTRO</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>SEND CUL</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>02-08-2026 13:11:01</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>01-10-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I54" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L54" t="n">
+        <v>399</v>
+      </c>
+      <c r="M54" t="n">
+        <v>11</v>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>28-07-2027 13:11:01</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P54" t="n">
+        <v>79256</v>
+      </c>
+      <c r="Q54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>53</v>
+      </c>
+      <c r="B55" t="n">
+        <v>109998</v>
+      </c>
+      <c r="C55" t="n">
+        <v>166282</v>
+      </c>
+      <c r="D55" t="n">
+        <v>63815</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>ERVIC YAHIR  SANCHEZ  INZUNZA</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>AZAHARES CUL</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>01-09-2026 6:45:32</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>01-10-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I55" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L55" t="n">
+        <v>649</v>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr"/>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr"/>
+      <c r="Q55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>54</v>
+      </c>
+      <c r="B56" t="n">
+        <v>110000</v>
+      </c>
+      <c r="C56" t="n">
+        <v>382151</v>
+      </c>
+      <c r="D56" t="n">
+        <v>24308</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>MARISA CARMINA  GALINDO MARTIN DEL CAMPO</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>TLALNEPANTLA</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>01-09-2026 7:26:03</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>01-10-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I56" t="n">
+        <v>0</v>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L56" t="n">
+        <v>649</v>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr"/>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr"/>
+      <c r="Q56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>55</v>
+      </c>
+      <c r="B57" t="n">
+        <v>110034</v>
+      </c>
+      <c r="C57" t="n">
+        <v>382209</v>
+      </c>
+      <c r="D57" t="n">
+        <v>24366</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>ESLI SANCHEZ CRESPO</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>PASEO 2000</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>01-09-2026 13:11:51</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>01-10-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I57" t="n">
+        <v>0</v>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L57" t="n">
+        <v>649</v>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr"/>
+      <c r="Q57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>56</v>
+      </c>
+      <c r="B58" t="n">
+        <v>108641</v>
+      </c>
+      <c r="C58" t="n">
+        <v>108940</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>06681</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>PEDRO ANTONIO LOPEZ MORALES</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>SEND CUL</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>14-08-2026 17:04:59</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>02-10-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I58" t="n">
+        <v>0</v>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>Activado</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L58" t="n">
+        <v>449</v>
+      </c>
+      <c r="M58" t="n">
+        <v>11</v>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>09-08-2027 17:04:59</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P58" t="n">
+        <v>24649</v>
+      </c>
+      <c r="Q58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>57</v>
+      </c>
+      <c r="B59" t="n">
+        <v>109870</v>
+      </c>
+      <c r="C59" t="n">
+        <v>381936</v>
+      </c>
+      <c r="D59" t="n">
+        <v>24093</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>DIANA LISSETTE LEON  CORDOVA</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>MISION ENS</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>31-08-2026 18:14:34</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>30-09-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I59" t="n">
+        <v>0</v>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L59" t="n">
+        <v>698</v>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr"/>
+      <c r="Q59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>58</v>
+      </c>
+      <c r="B60" t="n">
+        <v>110031</v>
+      </c>
+      <c r="C60" t="n">
+        <v>382206</v>
+      </c>
+      <c r="D60" t="n">
+        <v>24363</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>ANDREA DEL ROSARIO SALDAÑA BURCIAGA</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>SALTILLO VILLALTA</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>01-09-2026 12:48:19</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>01-10-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I60" t="n">
+        <v>0</v>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L60" t="n">
+        <v>799</v>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr"/>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr"/>
+      <c r="Q60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>59</v>
+      </c>
+      <c r="B61" t="n">
+        <v>110043</v>
+      </c>
+      <c r="C61" t="n">
+        <v>382233</v>
+      </c>
+      <c r="D61" t="n">
+        <v>24390</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>MARIA ELENA  ANGUIANO A</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>MISION ENS</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>01-09-2026 15:12:47</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>01-10-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I61" t="n">
+        <v>0</v>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L61" t="n">
+        <v>649</v>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr"/>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr"/>
+      <c r="Q61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>60</v>
+      </c>
+      <c r="B62" t="n">
+        <v>110058</v>
+      </c>
+      <c r="C62" t="n">
+        <v>382289</v>
+      </c>
+      <c r="D62" t="n">
+        <v>24446</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>VINICIO DAVID LOYOLA FALCON</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>SALTILLO VILLALTA</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>01-09-2026 17:36:00</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>01-10-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I62" t="n">
+        <v>0</v>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L62" t="n">
+        <v>649</v>
+      </c>
+      <c r="M62" t="n">
+        <v>11</v>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>27-08-2027 17:36:00</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr"/>
+      <c r="Q62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>61</v>
+      </c>
+      <c r="B63" t="n">
+        <v>110090</v>
+      </c>
+      <c r="C63" t="n">
+        <v>381675</v>
+      </c>
+      <c r="D63" t="n">
+        <v>23833</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>LAILA DEYANIRA SILVA FLORES</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>STA CATARINA</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>02-09-2026 7:18:45</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>02-10-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I63" t="n">
+        <v>0</v>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L63" t="n">
+        <v>649</v>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr"/>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr"/>
+      <c r="Q63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>62</v>
+      </c>
+      <c r="B64" t="n">
+        <v>110037</v>
+      </c>
+      <c r="C64" t="n">
+        <v>382218</v>
+      </c>
+      <c r="D64" t="n">
+        <v>24375</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>JOSE EULALIO GONZALEZ  LUNA</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>SEND SALTILLO</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>01-09-2026 13:52:29</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>01-10-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I64" t="n">
+        <v>0</v>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L64" t="n">
+        <v>999</v>
+      </c>
+      <c r="M64" t="n">
+        <v>11</v>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>27-08-2027 13:52:29</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr"/>
+      <c r="Q64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>63</v>
+      </c>
+      <c r="B65" t="n">
+        <v>110078</v>
+      </c>
+      <c r="C65" t="n">
+        <v>78977</v>
+      </c>
+      <c r="D65" t="n">
+        <v>76776</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>ALAN  RICART RAMIREZ</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>INDEPENDENCIA</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>01-09-2026 19:38:44</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>01-10-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I65" t="n">
+        <v>0</v>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L65" t="n">
+        <v>999</v>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr"/>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P65" t="n">
+        <v>41674</v>
+      </c>
+      <c r="Q65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>64</v>
+      </c>
+      <c r="B66" t="n">
+        <v>110094</v>
+      </c>
+      <c r="C66" t="n">
+        <v>305753</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>03252</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>DIANA SARAI MANZO MUÑOZ</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>SANTA FE</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>02-09-2026 8:19:55</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>02-10-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I66" t="n">
+        <v>0</v>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L66" t="n">
+        <v>649</v>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr"/>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr"/>
+      <c r="Q66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>65</v>
+      </c>
+      <c r="B67" t="n">
+        <v>108037</v>
+      </c>
+      <c r="C67" t="n">
+        <v>32030</v>
+      </c>
+      <c r="D67" t="n">
+        <v>29953</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>ERIKA ALEJANDRA  VALVERDE PRIETO</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>SANTA FE</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>05-08-2026 21:19:04</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>01-10-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I67" t="n">
+        <v>0</v>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L67" t="n">
+        <v>399</v>
+      </c>
+      <c r="M67" t="n">
+        <v>11</v>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>31-07-2027 21:19:04</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P67" t="n">
+        <v>59590</v>
+      </c>
+      <c r="Q67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>66</v>
+      </c>
+      <c r="B68" t="n">
+        <v>110081</v>
+      </c>
+      <c r="C68" t="n">
+        <v>56911</v>
+      </c>
+      <c r="D68" t="n">
+        <v>54762</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>LUIS FERNANDO CRUZ VALENZUELA</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>SEND CUL</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>01-09-2026 19:51:37</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>01-10-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I68" t="n">
+        <v>0</v>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L68" t="n">
+        <v>549</v>
+      </c>
+      <c r="M68" t="n">
+        <v>11</v>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>27-08-2027 19:51:37</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr"/>
+      <c r="Q68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>67</v>
+      </c>
+      <c r="B69" t="n">
+        <v>110083</v>
+      </c>
+      <c r="C69" t="n">
+        <v>382364</v>
+      </c>
+      <c r="D69" t="n">
+        <v>24521</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>RICARDO  ESPINOSA REYNA</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>SERRANIA</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>01-09-2026 20:04:06</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>01-10-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I69" t="n">
+        <v>0</v>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L69" t="n">
+        <v>849</v>
+      </c>
+      <c r="M69" t="n">
+        <v>11</v>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>27-08-2027 20:04:06</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr"/>
+      <c r="Q69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>68</v>
+      </c>
+      <c r="B70" t="n">
+        <v>107412</v>
+      </c>
+      <c r="C70" t="n">
+        <v>278025</v>
+      </c>
+      <c r="D70" t="n">
+        <v>75526</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>MIGUEL ANGEL LOPEZ  BRISEÑO</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>IXTAPALUCA</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>29-07-2026 19:44:02</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>27-09-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I70" t="n">
+        <v>0</v>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L70" t="n">
+        <v>499</v>
+      </c>
+      <c r="M70" t="n">
+        <v>11</v>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>24-07-2027 19:44:02</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P70" t="n">
+        <v>97991</v>
+      </c>
+      <c r="Q70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>69</v>
+      </c>
+      <c r="B71" t="n">
+        <v>107780</v>
+      </c>
+      <c r="C71" t="n">
+        <v>179187</v>
+      </c>
+      <c r="D71" t="n">
+        <v>76694</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>IVAN RAFAEL CASAS QUIÑONES</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>SEND MXL</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>03-08-2026 17:40:59</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>01-10-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I71" t="n">
+        <v>0</v>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L71" t="n">
+        <v>599</v>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr"/>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P71" t="n">
+        <v>105044</v>
+      </c>
+      <c r="Q71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>70</v>
+      </c>
+      <c r="B72" t="n">
+        <v>110027</v>
+      </c>
+      <c r="C72" t="n">
+        <v>324378</v>
+      </c>
+      <c r="D72" t="n">
+        <v>21317</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>MARIA AISPURO VALLES</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>PAPALOTE TJ</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>01-09-2026 11:46:28</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>01-10-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I72" t="n">
+        <v>0</v>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L72" t="n">
+        <v>549</v>
+      </c>
+      <c r="M72" t="n">
+        <v>11</v>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>27-08-2027 11:46:28</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr"/>
+      <c r="Q72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>71</v>
+      </c>
+      <c r="B73" t="n">
+        <v>110077</v>
+      </c>
+      <c r="C73" t="n">
+        <v>382345</v>
+      </c>
+      <c r="D73" t="n">
+        <v>24502</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>JOSSELIN  RODRIGUEZ GARCIA</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>SAN ISIDRO CUL</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>01-09-2026 19:33:17</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>01-10-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I73" t="n">
+        <v>0</v>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L73" t="n">
+        <v>649</v>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr"/>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr"/>
+      <c r="Q73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>72</v>
+      </c>
+      <c r="B74" t="n">
+        <v>110036</v>
+      </c>
+      <c r="C74" t="n">
+        <v>382217</v>
+      </c>
+      <c r="D74" t="n">
+        <v>24374</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>EVA NOEMI ESPINOZA VALTIERRA</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>PASEO 2000</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>01-09-2026 13:45:04</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>01-10-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I74" t="n">
+        <v>0</v>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L74" t="n">
+        <v>649</v>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr"/>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr"/>
+      <c r="Q74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>73</v>
+      </c>
+      <c r="B75" t="n">
+        <v>110061</v>
+      </c>
+      <c r="C75" t="n">
+        <v>382300</v>
+      </c>
+      <c r="D75" t="n">
+        <v>24457</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>JOSE DE JESUS  SANCHEZ RENDON</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>CARROUSEL TJ</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>01-09-2026 17:48:12</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>01-10-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>0</v>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L75" t="n">
+        <v>649</v>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr"/>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr"/>
+      <c r="Q75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>74</v>
+      </c>
+      <c r="B76" t="n">
+        <v>110079</v>
+      </c>
+      <c r="C76" t="n">
+        <v>382353</v>
+      </c>
+      <c r="D76" t="n">
+        <v>24510</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>MISAEL  RAMIREZ  IBARRA</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>SEND MXL</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>01-09-2026 19:48:01</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>01-10-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I76" t="n">
+        <v>0</v>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L76" t="n">
+        <v>649</v>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr"/>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr"/>
+      <c r="Q76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>75</v>
+      </c>
+      <c r="B77" t="n">
+        <v>109431</v>
+      </c>
+      <c r="C77" t="n">
+        <v>24835</v>
+      </c>
+      <c r="D77" t="n">
+        <v>22780</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>JOSE ENRIQUE CORRAL BORBON</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>MISION ENS</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>25-08-2026 18:02:23</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>02-10-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I77" t="n">
+        <v>0</v>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L77" t="n">
+        <v>399</v>
+      </c>
+      <c r="M77" t="n">
+        <v>11</v>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>20-08-2027 18:02:23</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P77" t="n">
+        <v>4966</v>
+      </c>
+      <c r="Q77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>76</v>
+      </c>
+      <c r="B78" t="n">
+        <v>109999</v>
+      </c>
+      <c r="C78" t="n">
+        <v>382150</v>
+      </c>
+      <c r="D78" t="n">
+        <v>24307</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>RODRIGO FIGUEROA MIGUEL</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>TLALNEPANTLA</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>01-09-2026 7:19:08</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>01-10-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I78" t="n">
+        <v>0</v>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L78" t="n">
+        <v>649</v>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr"/>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr"/>
+      <c r="Q78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>77</v>
+      </c>
+      <c r="B79" t="n">
+        <v>110048</v>
+      </c>
+      <c r="C79" t="n">
+        <v>382256</v>
+      </c>
+      <c r="D79" t="n">
+        <v>24413</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>CESAR JAIR CAMACHO FIGUEROA</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>TLALNEPANTLA</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>01-09-2026 16:18:32</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>01-10-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I79" t="n">
+        <v>0</v>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L79" t="n">
+        <v>549</v>
+      </c>
+      <c r="M79" t="n">
+        <v>11</v>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>27-08-2027 16:18:32</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr"/>
+      <c r="Q79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>78</v>
+      </c>
+      <c r="B80" t="n">
+        <v>110084</v>
+      </c>
+      <c r="C80" t="n">
+        <v>382361</v>
+      </c>
+      <c r="D80" t="n">
+        <v>24518</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>JULIO DE JESUS NAVARRO  YEPEZ</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>INSURGENTES</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>01-09-2026 20:04:42</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>01-10-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I80" t="n">
+        <v>0</v>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L80" t="n">
+        <v>749</v>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr"/>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr"/>
+      <c r="Q80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>79</v>
+      </c>
+      <c r="B81" t="n">
+        <v>110101</v>
+      </c>
+      <c r="C81" t="n">
+        <v>382421</v>
+      </c>
+      <c r="D81" t="n">
+        <v>24578</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>ALEJANDRA MICHEL LOPEZ CRUZ</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>VILLAS DEL REY</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>02-09-2026 10:39:23</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>02-10-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I81" t="n">
+        <v>0</v>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L81" t="n">
+        <v>649</v>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr"/>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr"/>
+      <c r="Q81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>80</v>
+      </c>
+      <c r="B82" t="n">
+        <v>110025</v>
+      </c>
+      <c r="C82" t="n">
+        <v>382187</v>
+      </c>
+      <c r="D82" t="n">
+        <v>24344</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>CARLOS ALBERTO MARTINEZ  DIPP</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>SEND MXL</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>01-09-2026 10:30:23</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>01-10-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I82" t="n">
+        <v>0</v>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L82" t="n">
+        <v>649</v>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr"/>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr"/>
+      <c r="Q82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>81</v>
+      </c>
+      <c r="B83" t="n">
+        <v>110040</v>
+      </c>
+      <c r="C83" t="n">
+        <v>381795</v>
+      </c>
+      <c r="D83" t="n">
+        <v>23953</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>CORINA ELIZABETH  CRUZ  MARTINEZ</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>SEND CHIH</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>01-09-2026 14:32:49</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>01-10-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I83" t="n">
+        <v>0</v>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L83" t="n">
+        <v>649</v>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr"/>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr"/>
+      <c r="Q83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>82</v>
+      </c>
+      <c r="B84" t="n">
+        <v>110076</v>
+      </c>
+      <c r="C84" t="n">
+        <v>382344</v>
+      </c>
+      <c r="D84" t="n">
+        <v>24501</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>CARLOS ANDRES OLIVAS  ALMARAS</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>SAN ISIDRO CUL</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>01-09-2026 19:23:55</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>01-10-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I84" t="n">
+        <v>0</v>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L84" t="n">
+        <v>649</v>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr"/>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr"/>
+      <c r="Q84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>83</v>
+      </c>
+      <c r="B85" t="n">
+        <v>110046</v>
+      </c>
+      <c r="C85" t="n">
+        <v>382249</v>
+      </c>
+      <c r="D85" t="n">
+        <v>24406</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>HECTOR NOE VILLARREAL SALAZAR</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>SALTILLO VILLALTA</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>01-09-2026 15:56:45</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>01-10-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I85" t="n">
+        <v>0</v>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L85" t="n">
+        <v>649</v>
+      </c>
+      <c r="M85" t="n">
+        <v>11</v>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>27-08-2027 15:56:45</t>
+        </is>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P85" t="inlineStr"/>
+      <c r="Q85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>84</v>
+      </c>
+      <c r="B86" t="n">
+        <v>110055</v>
+      </c>
+      <c r="C86" t="n">
+        <v>382282</v>
+      </c>
+      <c r="D86" t="n">
+        <v>24439</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>ALEXIS ARREDONDO MEZA</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>SAN ISIDRO CUL</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>01-09-2026 17:22:54</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>01-10-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I86" t="n">
+        <v>0</v>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L86" t="n">
+        <v>649</v>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr"/>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P86" t="inlineStr"/>
+      <c r="Q86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>85</v>
+      </c>
+      <c r="B87" t="n">
+        <v>110064</v>
+      </c>
+      <c r="C87" t="n">
+        <v>382307</v>
+      </c>
+      <c r="D87" t="n">
+        <v>24464</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>MARIELA AGUILAR SANTOS</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>CARROUSEL TJ</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>01-09-2026 17:57:55</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>01-10-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I87" t="n">
+        <v>0</v>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L87" t="n">
+        <v>649</v>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr"/>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P87" t="inlineStr"/>
+      <c r="Q87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>86</v>
+      </c>
+      <c r="B88" t="n">
+        <v>108151</v>
+      </c>
+      <c r="C88" t="n">
+        <v>282587</v>
+      </c>
+      <c r="D88" t="n">
+        <v>80088</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>MARIA DE JESUS PEREZ VAZQUEZ</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>MISION ENS</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>08-08-2026 6:25:08</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>01-10-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I88" t="n">
+        <v>0</v>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>Activado</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L88" t="n">
+        <v>549</v>
+      </c>
+      <c r="M88" t="n">
+        <v>11</v>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>03-08-2027 6:25:08</t>
+        </is>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P88" t="n">
+        <v>102654</v>
+      </c>
+      <c r="Q88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>87</v>
+      </c>
+      <c r="B89" t="n">
+        <v>110023</v>
+      </c>
+      <c r="C89" t="n">
+        <v>382185</v>
+      </c>
+      <c r="D89" t="n">
+        <v>24342</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>ALEXIS  ALEJANDRO MEJIA</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>PASEO 2000</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>01-09-2026 10:21:50</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>01-10-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I89" t="n">
+        <v>0</v>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L89" t="n">
+        <v>649</v>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr"/>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P89" t="inlineStr"/>
+      <c r="Q89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>88</v>
+      </c>
+      <c r="B90" t="n">
+        <v>110059</v>
+      </c>
+      <c r="C90" t="n">
+        <v>382295</v>
+      </c>
+      <c r="D90" t="n">
+        <v>24452</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>JESUS EDUARDO RAMOS  GARCIA</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>SALTILLO VILLALTA</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>01-09-2026 17:41:15</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>01-10-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I90" t="n">
+        <v>0</v>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L90" t="n">
+        <v>649</v>
+      </c>
+      <c r="M90" t="n">
+        <v>11</v>
+      </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>27-08-2027 17:41:15</t>
+        </is>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P90" t="inlineStr"/>
+      <c r="Q90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>89</v>
+      </c>
+      <c r="B91" t="n">
+        <v>110074</v>
+      </c>
+      <c r="C91" t="n">
+        <v>382323</v>
+      </c>
+      <c r="D91" t="n">
+        <v>24480</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>ELSA MINERVA MORALES HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>SERRANIA</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>01-09-2026 18:55:21</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>01-10-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I91" t="n">
+        <v>0</v>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L91" t="n">
+        <v>949</v>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr"/>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P91" t="inlineStr"/>
+      <c r="Q91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>90</v>
+      </c>
+      <c r="B92" t="n">
+        <v>110017</v>
+      </c>
+      <c r="C92" t="n">
+        <v>362784</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>04944</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>DANIELA LUCELY LLAMAS VARGAS</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>PASEO 2000</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>01-09-2026 10:00:20</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>01-10-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I92" t="n">
+        <v>0</v>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L92" t="n">
+        <v>649</v>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr"/>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P92" t="inlineStr"/>
+      <c r="Q92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>91</v>
+      </c>
+      <c r="B93" t="n">
+        <v>110047</v>
+      </c>
+      <c r="C93" t="n">
+        <v>3008</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>02009</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>MARTHA RAMOS  ROMERO</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>INDEPENDENCIA</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>01-09-2026 16:16:07</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>01-10-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I93" t="n">
+        <v>0</v>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L93" t="n">
+        <v>999</v>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr"/>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P93" t="n">
+        <v>57970</v>
+      </c>
+      <c r="Q93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>92</v>
+      </c>
+      <c r="B94" t="n">
+        <v>110067</v>
+      </c>
+      <c r="C94" t="n">
+        <v>382308</v>
+      </c>
+      <c r="D94" t="n">
+        <v>24465</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>EDUARDO  LEON HERRERA</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>SEND CUL</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>01-09-2026 18:02:33</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>01-10-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I94" t="n">
+        <v>0</v>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L94" t="n">
+        <v>649</v>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr"/>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P94" t="inlineStr"/>
+      <c r="Q94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>93</v>
+      </c>
+      <c r="B95" t="n">
+        <v>110082</v>
+      </c>
+      <c r="C95" t="n">
+        <v>382355</v>
+      </c>
+      <c r="D95" t="n">
+        <v>24512</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>BEATRIZ DEYANIRA CORONADO GONZALEZ</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>SERRANIA</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>01-09-2026 19:51:39</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>01-10-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I95" t="n">
+        <v>0</v>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L95" t="n">
+        <v>849</v>
+      </c>
+      <c r="M95" t="n">
+        <v>11</v>
+      </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>27-08-2027 19:51:39</t>
+        </is>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P95" t="inlineStr"/>
+      <c r="Q95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>94</v>
+      </c>
+      <c r="B96" t="n">
         <v>109589</v>
       </c>
-      <c r="C34" t="n">
+      <c r="C96" t="n">
         <v>9525</v>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="D96" t="inlineStr">
         <is>
           <t>08454</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="E96" t="inlineStr">
         <is>
           <t>MARIA DE LOS ANGELES CRUZ LARA</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="F96" t="inlineStr">
         <is>
           <t>CARROUSEL TJ</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="G96" t="inlineStr">
         <is>
           <t>28-08-2026 9:13:09</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>01-10-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="I34" t="n">
-        <v>0</v>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>Sin filtro</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>01-10-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I96" t="n">
+        <v>0</v>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
         <is>
           <t>RENOVACIÓN</t>
         </is>
       </c>
-      <c r="L34" t="n">
+      <c r="L96" t="n">
         <v>499</v>
       </c>
-      <c r="M34" t="n">
+      <c r="M96" t="n">
         <v>11</v>
       </c>
-      <c r="N34" t="inlineStr">
+      <c r="N96" t="inlineStr">
         <is>
           <t>23-08-2027 9:13:09</t>
         </is>
       </c>
-      <c r="O34" t="inlineStr">
+      <c r="O96" t="inlineStr">
         <is>
           <t>Domiciliado</t>
         </is>
       </c>
-      <c r="P34" t="n">
+      <c r="P96" t="n">
         <v>90245</v>
       </c>
-      <c r="Q34" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Reporte generado: 01-09-2026 06:14 p. m.</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr"/>
-      <c r="C35" t="inlineStr"/>
-      <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
-      <c r="O35" t="inlineStr"/>
-      <c r="P35" t="inlineStr"/>
-      <c r="Q35" t="inlineStr"/>
+      <c r="Q96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>95</v>
+      </c>
+      <c r="B97" t="n">
+        <v>110075</v>
+      </c>
+      <c r="C97" t="n">
+        <v>382341</v>
+      </c>
+      <c r="D97" t="n">
+        <v>24498</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>KEYLA MORALES HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>MISION ENS</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>01-09-2026 19:19:33</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>01-10-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I97" t="n">
+        <v>0</v>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L97" t="n">
+        <v>649</v>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr"/>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P97" t="inlineStr"/>
+      <c r="Q97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>96</v>
+      </c>
+      <c r="B98" t="n">
+        <v>107965</v>
+      </c>
+      <c r="C98" t="n">
+        <v>113340</v>
+      </c>
+      <c r="D98" t="n">
+        <v>11075</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>JORGE ENRIQUE  LARA  CAMARGO</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>INDEPENDENCIA</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>04-08-2026 21:12:33</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>02-10-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I98" t="n">
+        <v>0</v>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L98" t="n">
+        <v>449</v>
+      </c>
+      <c r="M98" t="n">
+        <v>5</v>
+      </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>31-01-2027 21:12:33</t>
+        </is>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P98" t="n">
+        <v>40228</v>
+      </c>
+      <c r="Q98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>97</v>
+      </c>
+      <c r="B99" t="n">
+        <v>110003</v>
+      </c>
+      <c r="C99" t="n">
+        <v>375807</v>
+      </c>
+      <c r="D99" t="n">
+        <v>17967</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>ALFREDO  MORALES RIVERA</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>CARROUSEL TJ</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>01-09-2026 8:05:44</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>01-10-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I99" t="n">
+        <v>0</v>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L99" t="n">
+        <v>549</v>
+      </c>
+      <c r="M99" t="n">
+        <v>11</v>
+      </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>27-08-2027 8:05:44</t>
+        </is>
+      </c>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P99" t="inlineStr"/>
+      <c r="Q99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>98</v>
+      </c>
+      <c r="B100" t="n">
+        <v>110044</v>
+      </c>
+      <c r="C100" t="n">
+        <v>133770</v>
+      </c>
+      <c r="D100" t="n">
+        <v>31420</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>JAZMIN ADRIANA MARTINEZ VARGAS</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>TEC MXL</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>01-09-2026 15:15:26</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>01-10-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I100" t="n">
+        <v>0</v>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L100" t="n">
+        <v>649</v>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr"/>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P100" t="inlineStr"/>
+      <c r="Q100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>99</v>
+      </c>
+      <c r="B101" t="n">
+        <v>110080</v>
+      </c>
+      <c r="C101" t="n">
+        <v>382358</v>
+      </c>
+      <c r="D101" t="n">
+        <v>24515</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>MARISOL  ACUÑA VAZQUEZ</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>VILLAS DEL REY</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>01-09-2026 19:50:54</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>01-10-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I101" t="n">
+        <v>0</v>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L101" t="n">
+        <v>649</v>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr"/>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P101" t="inlineStr"/>
+      <c r="Q101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>100</v>
+      </c>
+      <c r="B102" t="n">
+        <v>107413</v>
+      </c>
+      <c r="C102" t="n">
+        <v>278027</v>
+      </c>
+      <c r="D102" t="n">
+        <v>75528</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>MIGUEL ANGEL  LOPEZ ORTEGA</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>IXTAPALUCA</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>29-07-2026 19:46:58</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>27-09-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I102" t="n">
+        <v>0</v>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L102" t="n">
+        <v>499</v>
+      </c>
+      <c r="M102" t="n">
+        <v>11</v>
+      </c>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>24-07-2027 19:46:58</t>
+        </is>
+      </c>
+      <c r="O102" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P102" t="n">
+        <v>97988</v>
+      </c>
+      <c r="Q102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>101</v>
+      </c>
+      <c r="B103" t="n">
+        <v>110028</v>
+      </c>
+      <c r="C103" t="n">
+        <v>381747</v>
+      </c>
+      <c r="D103" t="n">
+        <v>23905</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>RENE ABEL ORTIZ AGUILAR</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>PAPALOTE TJ</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>01-09-2026 12:12:20</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>01-10-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I103" t="n">
+        <v>0</v>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L103" t="n">
+        <v>649</v>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N103" t="inlineStr"/>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P103" t="inlineStr"/>
+      <c r="Q103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>102</v>
+      </c>
+      <c r="B104" t="n">
+        <v>110030</v>
+      </c>
+      <c r="C104" t="n">
+        <v>382201</v>
+      </c>
+      <c r="D104" t="n">
+        <v>24358</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>GABRIELA TRISTAN MUÑIZ</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>SERRANIA</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>01-09-2026 12:13:54</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>01-10-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I104" t="n">
+        <v>0</v>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L104" t="n">
+        <v>849</v>
+      </c>
+      <c r="M104" t="n">
+        <v>11</v>
+      </c>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>27-08-2027 12:13:54</t>
+        </is>
+      </c>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P104" t="inlineStr"/>
+      <c r="Q104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>103</v>
+      </c>
+      <c r="B105" t="n">
+        <v>110060</v>
+      </c>
+      <c r="C105" t="n">
+        <v>382286</v>
+      </c>
+      <c r="D105" t="n">
+        <v>24443</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>XIMENA SANCHEZ SUMAYA</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>INSURGENTES</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>01-09-2026 17:46:33</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>01-10-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I105" t="n">
+        <v>0</v>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L105" t="n">
+        <v>749</v>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N105" t="inlineStr"/>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P105" t="inlineStr"/>
+      <c r="Q105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>104</v>
+      </c>
+      <c r="B106" t="n">
+        <v>110062</v>
+      </c>
+      <c r="C106" t="n">
+        <v>104465</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>02212</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>ROSA PAOLA ROSALES BRAVO</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>LOMA BONITA</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>01-09-2026 17:53:40</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>01-10-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I106" t="n">
+        <v>0</v>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L106" t="n">
+        <v>499</v>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr"/>
+      <c r="O106" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P106" t="inlineStr"/>
+      <c r="Q106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>105</v>
+      </c>
+      <c r="B107" t="n">
+        <v>110087</v>
+      </c>
+      <c r="C107" t="n">
+        <v>309971</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>07470</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>HECTOR GRACIA  CAMARGO</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>MISION ENS</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>01-09-2026 20:54:57</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>01-10-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I107" t="n">
+        <v>0</v>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L107" t="n">
+        <v>649</v>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N107" t="inlineStr"/>
+      <c r="O107" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P107" t="inlineStr"/>
+      <c r="Q107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>106</v>
+      </c>
+      <c r="B108" t="n">
+        <v>107633</v>
+      </c>
+      <c r="C108" t="n">
+        <v>289981</v>
+      </c>
+      <c r="D108" t="n">
+        <v>87479</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>RICARDO HERNANDEZ CASTILLO</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>SEND SALTILLO</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>01-08-2026 9:48:03</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>01-10-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I108" t="n">
+        <v>0</v>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>CANCELADO</t>
+        </is>
+      </c>
+      <c r="L108" t="n">
+        <v>499</v>
+      </c>
+      <c r="M108" t="n">
+        <v>11</v>
+      </c>
+      <c r="N108" t="inlineStr">
+        <is>
+          <t>27-07-2027 9:48:03</t>
+        </is>
+      </c>
+      <c r="O108" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P108" t="n">
+        <v>103090</v>
+      </c>
+      <c r="Q108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>107</v>
+      </c>
+      <c r="B109" t="n">
+        <v>110015</v>
+      </c>
+      <c r="C109" t="n">
+        <v>340240</v>
+      </c>
+      <c r="D109" t="n">
+        <v>18058</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>RICARDO GAMEZ CARRILLO</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>SALTILLO VILLALTA</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>01-09-2026 9:45:27</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>02-10-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I109" t="n">
+        <v>0</v>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L109" t="n">
+        <v>649</v>
+      </c>
+      <c r="M109" t="n">
+        <v>11</v>
+      </c>
+      <c r="N109" t="inlineStr">
+        <is>
+          <t>27-08-2027 9:45:27</t>
+        </is>
+      </c>
+      <c r="O109" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P109" t="n">
+        <v>91451</v>
+      </c>
+      <c r="Q109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>108</v>
+      </c>
+      <c r="B110" t="n">
+        <v>110068</v>
+      </c>
+      <c r="C110" t="n">
+        <v>382309</v>
+      </c>
+      <c r="D110" t="n">
+        <v>24466</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>MARIA YOLANDA  FIGUEROA  VEGA</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>AZAHARES CUL</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>01-09-2026 18:03:16</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>01-10-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I110" t="n">
+        <v>0</v>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L110" t="n">
+        <v>999</v>
+      </c>
+      <c r="M110" t="n">
+        <v>11</v>
+      </c>
+      <c r="N110" t="inlineStr">
+        <is>
+          <t>27-08-2027 18:03:16</t>
+        </is>
+      </c>
+      <c r="O110" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P110" t="inlineStr"/>
+      <c r="Q110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>109</v>
+      </c>
+      <c r="B111" t="n">
+        <v>110045</v>
+      </c>
+      <c r="C111" t="n">
+        <v>163758</v>
+      </c>
+      <c r="D111" t="n">
+        <v>61291</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>ELIZABETH  PEREZ  OCHOA</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>CARROUSEL TJ</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>01-09-2026 15:28:30</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>01-10-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I111" t="n">
+        <v>0</v>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L111" t="n">
+        <v>649</v>
+      </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N111" t="inlineStr"/>
+      <c r="O111" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P111" t="inlineStr"/>
+      <c r="Q111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>110</v>
+      </c>
+      <c r="B112" t="n">
+        <v>110004</v>
+      </c>
+      <c r="C112" t="n">
+        <v>251678</v>
+      </c>
+      <c r="D112" t="n">
+        <v>49182</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>MIGUEL ANGEL CARVAJAL GOMEZ</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>STA CATARINA</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>01-09-2026 8:06:40</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>01-10-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I112" t="n">
+        <v>0</v>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L112" t="n">
+        <v>649</v>
+      </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N112" t="inlineStr"/>
+      <c r="O112" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P112" t="inlineStr"/>
+      <c r="Q112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>111</v>
+      </c>
+      <c r="B113" t="n">
+        <v>107795</v>
+      </c>
+      <c r="C113" t="n">
+        <v>239694</v>
+      </c>
+      <c r="D113" t="n">
+        <v>37199</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>JAIME EDUARDO LOPEZ GALAVIZ</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>STA CATARINA</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>03-08-2026 18:21:40</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>23-09-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I113" t="n">
+        <v>0</v>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L113" t="n">
+        <v>549</v>
+      </c>
+      <c r="M113" t="n">
+        <v>5</v>
+      </c>
+      <c r="N113" t="inlineStr">
+        <is>
+          <t>30-01-2027 18:21:40</t>
+        </is>
+      </c>
+      <c r="O113" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P113" t="n">
+        <v>80649</v>
+      </c>
+      <c r="Q113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>112</v>
+      </c>
+      <c r="B114" t="n">
+        <v>110001</v>
+      </c>
+      <c r="C114" t="n">
+        <v>327378</v>
+      </c>
+      <c r="D114" t="n">
+        <v>24315</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>MARIO ENRIQUE RAMÍREZ MONTIEL</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>METEPEC</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>01-09-2026 7:46:34</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>01-10-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I114" t="n">
+        <v>0</v>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN</t>
+        </is>
+      </c>
+      <c r="L114" t="n">
+        <v>999</v>
+      </c>
+      <c r="M114" t="n">
+        <v>11</v>
+      </c>
+      <c r="N114" t="inlineStr">
+        <is>
+          <t>27-08-2027 7:46:34</t>
+        </is>
+      </c>
+      <c r="O114" t="inlineStr">
+        <is>
+          <t>Domiciliado</t>
+        </is>
+      </c>
+      <c r="P114" t="n">
+        <v>94313</v>
+      </c>
+      <c r="Q114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>113</v>
+      </c>
+      <c r="B115" t="n">
+        <v>110014</v>
+      </c>
+      <c r="C115" t="n">
+        <v>382176</v>
+      </c>
+      <c r="D115" t="n">
+        <v>24333</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>DANIEL DE JESUS PEREZ PEREZ</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>PASEO 2000</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>01-09-2026 9:44:23</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>01-10-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I115" t="n">
+        <v>0</v>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L115" t="n">
+        <v>649</v>
+      </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N115" t="inlineStr"/>
+      <c r="O115" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P115" t="inlineStr"/>
+      <c r="Q115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>114</v>
+      </c>
+      <c r="B116" t="n">
+        <v>110018</v>
+      </c>
+      <c r="C116" t="n">
+        <v>382178</v>
+      </c>
+      <c r="D116" t="n">
+        <v>24335</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>RITA STEPHANIE  GONZALEZ GUTIERREZ</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>VILLAS DEL REY</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>01-09-2026 10:00:35</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>01-10-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I116" t="n">
+        <v>0</v>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L116" t="n">
+        <v>649</v>
+      </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N116" t="inlineStr"/>
+      <c r="O116" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P116" t="inlineStr"/>
+      <c r="Q116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>115</v>
+      </c>
+      <c r="B117" t="n">
+        <v>110007</v>
+      </c>
+      <c r="C117" t="n">
+        <v>135417</v>
+      </c>
+      <c r="D117" t="n">
+        <v>33065</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>MARTIN JONATHAN  HERNANDEZ  MARQUEZ</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>SEND CHIH</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>01-09-2026 8:33:37</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>01-10-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="I117" t="n">
+        <v>0</v>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>Sin filtro</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>NUEVO</t>
+        </is>
+      </c>
+      <c r="L117" t="n">
+        <v>649</v>
+      </c>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>Indefinido</t>
+        </is>
+      </c>
+      <c r="N117" t="inlineStr"/>
+      <c r="O117" t="inlineStr">
+        <is>
+          <t>Recurrente</t>
+        </is>
+      </c>
+      <c r="P117" t="inlineStr"/>
+      <c r="Q117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Reporte generado: 02-09-2026 06:34 p. m.</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr"/>
+      <c r="C118" t="inlineStr"/>
+      <c r="D118" t="inlineStr"/>
+      <c r="E118" t="inlineStr"/>
+      <c r="F118" t="inlineStr"/>
+      <c r="G118" t="inlineStr"/>
+      <c r="H118" t="inlineStr"/>
+      <c r="I118" t="inlineStr"/>
+      <c r="J118" t="inlineStr"/>
+      <c r="K118" t="inlineStr"/>
+      <c r="L118" t="inlineStr"/>
+      <c r="M118" t="inlineStr"/>
+      <c r="N118" t="inlineStr"/>
+      <c r="O118" t="inlineStr"/>
+      <c r="P118" t="inlineStr"/>
+      <c r="Q118" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
